--- a/gsheet/xlsx/entities.xlsx
+++ b/gsheet/xlsx/entities.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="1366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="1385">
   <si>
     <t>Person-ID</t>
   </si>
@@ -1485,6 +1485,9 @@
   </si>
   <si>
     <t>Sohn des Satans (allegorisch/mythologisch)</t>
+  </si>
+  <si>
+    <t>Bedeutung noch unklar</t>
   </si>
   <si>
     <t>person_121</t>
@@ -3785,6 +3788,9 @@
     <t>place_095</t>
   </si>
   <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
     <t>place_096</t>
   </si>
   <si>
@@ -3845,9 +3851,18 @@
     <t>Hegner, Diethelm / Trigland, Jacobus</t>
   </si>
   <si>
+    <t>1651</t>
+  </si>
+  <si>
+    <t>Michael Schufelberger</t>
+  </si>
+  <si>
     <t>Kategorie 2</t>
   </si>
   <si>
+    <t>https://www.e-rara.ch/zuz/doi/10.3931/e-rara-13309</t>
+  </si>
+  <si>
     <t>work_003</t>
   </si>
   <si>
@@ -4004,10 +4019,64 @@
     <t>work_021</t>
   </si>
   <si>
+    <t>Sterbensspiegel/ das ist sonnenklare Vorstellung menschlicher Nichtigkeit durch alle Staend und Geschlechter</t>
+  </si>
+  <si>
+    <t>Meyer, Conrad / Meyer, Rudolf</t>
+  </si>
+  <si>
+    <t>1650</t>
+  </si>
+  <si>
+    <t>Johann Jacob Bodmer</t>
+  </si>
+  <si>
     <t>work_022</t>
   </si>
   <si>
+    <t>Warhaffte/ vnd in Gottes Wort wol gegründte Widerlegung Des newlich im Truck außgegangnen ohn-Catholischen Gesprächs von Religion oder Glaubens sachen/ geneñt der Augenspiegel</t>
+  </si>
+  <si>
+    <t>Vollenweider, Jakob</t>
+  </si>
+  <si>
+    <t>1642</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://doi.org/10.3931/e-rara-79716</t>
+    </r>
+  </si>
+  <si>
     <t>work_023</t>
+  </si>
+  <si>
+    <t>Augspiegels Wahrer Religion Erster Theil</t>
+  </si>
+  <si>
+    <t>Gothard, Johann Wilhelm</t>
+  </si>
+  <si>
+    <t>1639</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>David Hautt</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://doi.org/10.3931/e-rara-51775</t>
+    </r>
   </si>
   <si>
     <t>work_024</t>
@@ -4221,7 +4290,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd.MM.yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -4246,6 +4315,11 @@
     <font>
       <u/>
       <color rgb="FF434343"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
     <font>
@@ -4368,13 +4442,13 @@
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -8081,27 +8155,29 @@
         <v>227</v>
       </c>
       <c r="J120" s="9"/>
-      <c r="K120" s="9"/>
+      <c r="K120" s="3" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B121" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Damokles,  (-)</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
       <c r="G121" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="I121" s="12"/>
       <c r="J121" s="9"/>
@@ -8109,23 +8185,23 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B122" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dionysius I. von Syrakus,  (-)</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
       <c r="G122" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I122" s="12"/>
       <c r="J122" s="9"/>
@@ -8133,23 +8209,23 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B123" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kleopatra VII.,  (-)</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
       <c r="G123" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I123" s="12"/>
       <c r="J123" s="9"/>
@@ -8157,23 +8233,23 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B124" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Marcus Antonius,  (-)</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D124" s="3"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
       <c r="G124" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I124" s="12"/>
       <c r="J124" s="9"/>
@@ -8181,23 +8257,23 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B125" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klio,  (-)</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
       <c r="G125" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I125" s="7" t="s">
         <v>227</v>
@@ -8207,23 +8283,23 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B126" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Flora,  (-)</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
       <c r="G126" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I126" s="7" t="s">
         <v>227</v>
@@ -8233,7 +8309,7 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B127" s="4" t="str">
         <f t="shared" si="1"/>
@@ -8253,21 +8329,21 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B128" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. J. V.,  (-)</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
       <c r="G128" s="9"/>
       <c r="H128" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="I128" s="7" t="s">
         <v>16</v>
@@ -8277,21 +8353,21 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B129" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. J. V., dessen Frau,  (-)</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
       <c r="G129" s="9"/>
       <c r="H129" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I129" s="7" t="s">
         <v>16</v>
@@ -8301,21 +8377,21 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B130" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sch. H.,  (-)</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
       <c r="G130" s="9"/>
       <c r="H130" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="I130" s="7" t="s">
         <v>16</v>
@@ -8325,14 +8401,14 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B131" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser, Johann Heinrich (1600-1669)</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>43</v>
@@ -8344,66 +8420,66 @@
         <v>1669.0</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H131" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I131" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J131" s="14" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K131" s="9"/>
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B132" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser-Ziegler, Jahel (-)</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
       <c r="G132" s="9"/>
       <c r="H132" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I132" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K132" s="9"/>
     </row>
     <row r="133" ht="22.5" customHeight="1">
       <c r="A133" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B133" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caspar W.,  (-)</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
       <c r="G133" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I133" s="7" t="s">
         <v>16</v>
@@ -8413,21 +8489,21 @@
     </row>
     <row r="134" ht="22.5" customHeight="1">
       <c r="A134" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B134" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esther O.,  (-)</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
       <c r="G134" s="9"/>
       <c r="H134" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I134" s="7" t="s">
         <v>16</v>
@@ -8437,14 +8513,14 @@
     </row>
     <row r="135" ht="22.5" customHeight="1">
       <c r="A135" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B135" s="4" t="str">
         <f t="shared" si="1"/>
         <v>G. H.,  (-)</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="5"/>
@@ -8459,21 +8535,21 @@
     </row>
     <row r="136" ht="22.5" customHeight="1">
       <c r="A136" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B136" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. C.,  (-)</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
       <c r="G136" s="9"/>
       <c r="H136" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I136" s="7" t="s">
         <v>16</v>
@@ -8483,17 +8559,17 @@
     </row>
     <row r="137" ht="22.5" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B137" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Hercules von (1617-1686)</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E137" s="5">
         <v>1617.0</v>
@@ -8507,23 +8583,23 @@
         <v>16</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K137" s="9"/>
     </row>
     <row r="138" ht="22.5" customHeight="1">
       <c r="A138" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B138" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Barbara Dorothea von (1629-1660)</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E138" s="5">
         <v>1629.0</v>
@@ -8533,26 +8609,26 @@
       </c>
       <c r="G138" s="9"/>
       <c r="H138" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I138" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J138" s="8" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K138" s="9"/>
     </row>
     <row r="139" ht="22.5" customHeight="1">
       <c r="A139" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B139" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. L.,  (-)</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="5"/>
@@ -8567,21 +8643,21 @@
     </row>
     <row r="140" ht="22.5" customHeight="1">
       <c r="A140" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B140" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. A.,  (-)</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
       <c r="G140" s="9"/>
       <c r="H140" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I140" s="7" t="s">
         <v>16</v>
@@ -8591,21 +8667,21 @@
     </row>
     <row r="141" ht="22.5" customHeight="1">
       <c r="A141" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B141" s="4" t="str">
         <f t="shared" si="1"/>
         <v>B. M.,  (-)</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D141" s="3"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
       <c r="G141" s="9"/>
       <c r="H141" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I141" s="7" t="s">
         <v>16</v>
@@ -8615,73 +8691,73 @@
     </row>
     <row r="142" ht="22.5" customHeight="1">
       <c r="A142" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B142" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. H.,  (-)</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="9"/>
       <c r="H142" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="I142" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K142" s="9"/>
     </row>
     <row r="143" ht="22.5" customHeight="1">
       <c r="A143" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B143" s="4" t="str">
         <f t="shared" si="1"/>
         <v>D. M.,  (-)</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D143" s="3"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
       <c r="G143" s="9"/>
       <c r="H143" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="I143" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K143" s="9"/>
     </row>
     <row r="144" ht="22.5" customHeight="1">
       <c r="A144" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B144" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gottfrid,  (-)</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
       <c r="G144" s="9"/>
       <c r="H144" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I144" s="7" t="s">
         <v>16</v>
@@ -8691,7 +8767,7 @@
     </row>
     <row r="145" ht="22.5" customHeight="1">
       <c r="A145" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B145" s="4" t="str">
         <f t="shared" si="1"/>
@@ -8705,7 +8781,7 @@
       <c r="F145" s="5"/>
       <c r="G145" s="9"/>
       <c r="H145" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I145" s="7" t="s">
         <v>16</v>
@@ -8715,21 +8791,21 @@
     </row>
     <row r="146" ht="22.5" customHeight="1">
       <c r="A146" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B146" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. Schw.,  (-)</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D146" s="3"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
       <c r="G146" s="9"/>
       <c r="H146" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I146" s="7" t="s">
         <v>16</v>
@@ -8739,21 +8815,21 @@
     </row>
     <row r="147" ht="22.5" customHeight="1">
       <c r="A147" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B147" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. K.,  (-)</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
       <c r="G147" s="9"/>
       <c r="H147" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I147" s="7" t="s">
         <v>16</v>
@@ -8763,14 +8839,14 @@
     </row>
     <row r="148" ht="22.5" customHeight="1">
       <c r="A148" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B148" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ott, Hans Heinrich (-)</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>69</v>
@@ -8787,14 +8863,14 @@
     </row>
     <row r="149" ht="22.5" customHeight="1">
       <c r="A149" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B149" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. W.,  (-)</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D149" s="3"/>
       <c r="E149" s="5"/>
@@ -8809,21 +8885,21 @@
     </row>
     <row r="150" ht="22.5" customHeight="1">
       <c r="A150" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B150" s="4" t="str">
         <f t="shared" si="1"/>
         <v>V. L.,  (-)</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
       <c r="G150" s="9"/>
       <c r="H150" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I150" s="7" t="s">
         <v>16</v>
@@ -8833,14 +8909,14 @@
     </row>
     <row r="151" ht="22.5" customHeight="1">
       <c r="A151" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B151" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. Sch.,  (-)</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D151" s="3"/>
       <c r="E151" s="5"/>
@@ -8855,21 +8931,21 @@
     </row>
     <row r="152" ht="22.5" customHeight="1">
       <c r="A152" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B152" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. H.,  (-)</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
       <c r="G152" s="9"/>
       <c r="H152" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="I152" s="7" t="s">
         <v>16</v>
@@ -8879,14 +8955,14 @@
     </row>
     <row r="153" ht="22.5" customHeight="1">
       <c r="A153" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B153" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. H.,  (-)</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="5"/>
@@ -8897,55 +8973,55 @@
         <v>16</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="K153" s="9"/>
     </row>
     <row r="154" ht="22.5" customHeight="1">
       <c r="A154" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B154" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. W.,  (-)</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="9"/>
       <c r="H154" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I154" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K154" s="9"/>
     </row>
     <row r="155" ht="22.5" customHeight="1">
       <c r="A155" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B155" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Koller, Elisabeth (-)</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
       <c r="G155" s="9"/>
       <c r="H155" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="I155" s="7" t="s">
         <v>16</v>
@@ -8957,17 +9033,17 @@
     </row>
     <row r="156" ht="22.5" customHeight="1">
       <c r="A156" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B156" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lobwasser, Ambrosius (1515-1585)</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E156" s="5">
         <v>1515.0</v>
@@ -8976,10 +9052,10 @@
         <v>1585.0</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="I156" s="7" t="s">
         <v>16</v>
@@ -8989,14 +9065,14 @@
     </row>
     <row r="157" ht="22.5" customHeight="1">
       <c r="A157" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B157" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vollenweider, Jakob (-)</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>347</v>
@@ -9004,7 +9080,7 @@
       <c r="E157" s="5"/>
       <c r="F157" s="5"/>
       <c r="G157" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H157" s="3"/>
       <c r="I157" s="7" t="s">
@@ -9015,7 +9091,7 @@
     </row>
     <row r="158" ht="22.5" customHeight="1">
       <c r="A158" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B158" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9025,7 +9101,7 @@
         <v>219</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E158" s="5">
         <v>1606.0</v>
@@ -9034,7 +9110,7 @@
         <v>1660.0</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>222</v>
@@ -9047,23 +9123,23 @@
     </row>
     <row r="159" ht="22.5" customHeight="1">
       <c r="A159" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B159" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Burkharten, Kuenraht (-)</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E159" s="5"/>
       <c r="F159" s="5"/>
       <c r="G159" s="9"/>
       <c r="H159" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I159" s="7" t="s">
         <v>16</v>
@@ -9073,14 +9149,14 @@
     </row>
     <row r="160" ht="22.5" customHeight="1">
       <c r="A160" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B160" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ardüser, Johann (1585-1665)</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>106</v>
@@ -9092,7 +9168,7 @@
         <v>1665.0</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H160" s="3"/>
       <c r="I160" s="7" t="s">
@@ -9103,25 +9179,25 @@
     </row>
     <row r="161" ht="22.5" customHeight="1">
       <c r="A161" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B161" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hegner, Diethelm  (-)</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
       <c r="G161" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I161" s="7" t="s">
         <v>16</v>
@@ -9131,22 +9207,22 @@
     </row>
     <row r="162" ht="22.5" customHeight="1">
       <c r="A162" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B162" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Trigland, Jacobus (-)</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E162" s="5"/>
       <c r="F162" s="5"/>
       <c r="G162" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H162" s="3"/>
       <c r="I162" s="7" t="s">
@@ -9157,17 +9233,17 @@
     </row>
     <row r="163" ht="22.5" customHeight="1">
       <c r="A163" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B163" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwinger, D. (-)</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E163" s="5"/>
       <c r="F163" s="5"/>
@@ -9181,14 +9257,14 @@
     </row>
     <row r="164" ht="22.5" customHeight="1">
       <c r="A164" s="3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B164" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Genathen, Johann Jakob (-)</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>31</v>
@@ -9196,10 +9272,10 @@
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
       <c r="G164" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="I164" s="7" t="s">
         <v>16</v>
@@ -9209,7 +9285,7 @@
     </row>
     <row r="165" ht="22.5" customHeight="1">
       <c r="A165" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B165" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9235,27 +9311,27 @@
     </row>
     <row r="166" ht="22.5" customHeight="1">
       <c r="A166" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B166" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hess, Caspar (-1631)</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E166" s="5"/>
       <c r="F166" s="5">
         <v>1631.0</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="I166" s="7" t="s">
         <v>16</v>
@@ -9265,14 +9341,14 @@
     </row>
     <row r="167" ht="22.5" customHeight="1">
       <c r="A167" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B167" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wolfen, Hans Jakob (-)</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>215</v>
@@ -9289,22 +9365,22 @@
     </row>
     <row r="168" ht="22.5" customHeight="1">
       <c r="A168" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B168" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöri, Felix Christian (-)</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E168" s="15"/>
       <c r="F168" s="16"/>
       <c r="G168" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H168" s="3"/>
       <c r="I168" s="7" t="s">
@@ -9315,7 +9391,7 @@
     </row>
     <row r="169" ht="22.5" customHeight="1">
       <c r="A169" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B169" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9325,7 +9401,7 @@
         <v>12</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E169" s="15"/>
       <c r="F169" s="5">
@@ -9341,21 +9417,21 @@
     </row>
     <row r="170" ht="22.5" customHeight="1">
       <c r="A170" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B170" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther,  (-)</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D170" s="3"/>
       <c r="E170" s="15"/>
       <c r="F170" s="16"/>
       <c r="G170" s="9"/>
       <c r="H170" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="I170" s="7" t="s">
         <v>16</v>
@@ -9365,23 +9441,23 @@
     </row>
     <row r="171" ht="22.5" customHeight="1">
       <c r="A171" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B171" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Weiss, Caspar (-)</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E171" s="15"/>
       <c r="F171" s="16"/>
       <c r="G171" s="9"/>
       <c r="H171" s="17" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="I171" s="7" t="s">
         <v>16</v>
@@ -9391,7 +9467,7 @@
     </row>
     <row r="172" ht="22.5" customHeight="1">
       <c r="A172" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B172" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9405,7 +9481,7 @@
       <c r="F172" s="16"/>
       <c r="G172" s="9"/>
       <c r="H172" s="17" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="I172" s="7" t="s">
         <v>16</v>
@@ -9415,21 +9491,21 @@
     </row>
     <row r="173" ht="22.5" customHeight="1">
       <c r="A173" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B173" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bas,  (-)</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="15"/>
       <c r="F173" s="16"/>
       <c r="G173" s="9"/>
       <c r="H173" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I173" s="18"/>
       <c r="J173" s="9"/>
@@ -9437,14 +9513,14 @@
     </row>
     <row r="174" ht="22.5" customHeight="1">
       <c r="A174" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B174" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H.H.J. Gw. s. A.Z.Fr.M.,  (-)</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D174" s="3"/>
       <c r="E174" s="15"/>
@@ -9459,23 +9535,23 @@
     </row>
     <row r="175" ht="22.5" customHeight="1">
       <c r="A175" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B175" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hofm., Joh. (-)</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E175" s="15"/>
       <c r="F175" s="16"/>
       <c r="G175" s="9"/>
       <c r="H175" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I175" s="7" t="s">
         <v>16</v>
@@ -9485,22 +9561,22 @@
     </row>
     <row r="176" ht="22.5" customHeight="1">
       <c r="A176" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B176" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Cyrene, Simon von (-)</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="E176" s="15"/>
       <c r="F176" s="16"/>
       <c r="G176" s="3" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>245</v>
@@ -9513,20 +9589,20 @@
     </row>
     <row r="177" ht="22.5" customHeight="1">
       <c r="A177" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B177" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thomas,  (-)</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="15"/>
       <c r="F177" s="16"/>
       <c r="G177" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>319</v>
@@ -9539,23 +9615,23 @@
     </row>
     <row r="178" ht="22.5" customHeight="1">
       <c r="A178" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B178" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Phaeton,  (-)</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="15"/>
       <c r="F178" s="16"/>
       <c r="G178" s="3" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I178" s="7" t="s">
         <v>227</v>
@@ -9565,14 +9641,14 @@
     </row>
     <row r="179" ht="22.5" customHeight="1">
       <c r="A179" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B179" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lukas,  (-)</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D179" s="3"/>
       <c r="E179" s="15"/>
@@ -9589,20 +9665,20 @@
     </row>
     <row r="180" ht="22.5" customHeight="1">
       <c r="A180" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B180" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pallas Athena,  (-)</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="15"/>
       <c r="F180" s="16"/>
       <c r="G180" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>227</v>
@@ -9615,23 +9691,23 @@
     </row>
     <row r="181" ht="22.5" customHeight="1">
       <c r="A181" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B181" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bacchus,  (-)</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D181" s="3"/>
       <c r="E181" s="15"/>
       <c r="F181" s="16"/>
       <c r="G181" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="I181" s="7" t="s">
         <v>227</v>
@@ -9641,21 +9717,21 @@
     </row>
     <row r="182" ht="22.5" customHeight="1">
       <c r="A182" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B182" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Darius,  (-)</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="15"/>
       <c r="F182" s="16"/>
       <c r="G182" s="9"/>
       <c r="H182" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I182" s="7" t="s">
         <v>16</v>
@@ -9665,21 +9741,21 @@
     </row>
     <row r="183" ht="22.5" customHeight="1">
       <c r="A183" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B183" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kyros,  (-)</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D183" s="3"/>
       <c r="E183" s="15"/>
       <c r="F183" s="16"/>
       <c r="G183" s="9"/>
       <c r="H183" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I183" s="12"/>
       <c r="J183" s="9"/>
@@ -9687,25 +9763,25 @@
     </row>
     <row r="184" ht="22.5" customHeight="1">
       <c r="A184" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B184" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hippo, Augustinus von (-)</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E184" s="15"/>
       <c r="F184" s="16"/>
       <c r="G184" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="I184" s="12"/>
       <c r="J184" s="9"/>
@@ -9713,20 +9789,20 @@
     </row>
     <row r="185" ht="22.5" customHeight="1">
       <c r="A185" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B185" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lazarus,  (-)</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="D185" s="3"/>
       <c r="E185" s="15"/>
       <c r="F185" s="16"/>
       <c r="G185" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>245</v>
@@ -9739,20 +9815,20 @@
     </row>
     <row r="186" ht="22.5" customHeight="1">
       <c r="A186" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B186" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lot,  (-)</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="15"/>
       <c r="F186" s="16"/>
       <c r="G186" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>245</v>
@@ -9765,21 +9841,21 @@
     </row>
     <row r="187" ht="22.5" customHeight="1">
       <c r="A187" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B187" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hans Rudolf,  (-)</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D187" s="3"/>
       <c r="E187" s="15"/>
       <c r="F187" s="16"/>
       <c r="G187" s="9"/>
       <c r="H187" s="3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="I187" s="7" t="s">
         <v>16</v>
@@ -9789,7 +9865,7 @@
     </row>
     <row r="188" ht="22.5" customHeight="1">
       <c r="A188" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B188" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9802,16 +9878,16 @@
         <v>13</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F188" s="5">
         <v>1690.0</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="I188" s="7" t="s">
         <v>16</v>
@@ -9821,17 +9897,17 @@
     </row>
     <row r="189" ht="22.5" customHeight="1">
       <c r="A189" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B189" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bachofen, Johann Ulrich (1643-1700)</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E189" s="5">
         <v>1643.0</v>
@@ -9840,7 +9916,7 @@
         <v>1700.0</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>222</v>
@@ -9853,17 +9929,17 @@
     </row>
     <row r="190" ht="22.5" customHeight="1">
       <c r="A190" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B190" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grebel, Hans Konrad (1615-1674)</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E190" s="5">
         <v>1615.0</v>
@@ -9872,57 +9948,57 @@
         <v>1674.0</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="I190" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="K190" s="9"/>
     </row>
     <row r="191" ht="22.5" customHeight="1">
       <c r="A191" s="3" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B191" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gossweiler, Emerentia (-)</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E191" s="15"/>
       <c r="F191" s="16"/>
       <c r="G191" s="9"/>
       <c r="H191" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I191" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J191" s="8" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="K191" s="9"/>
     </row>
     <row r="192" ht="22.5" customHeight="1">
       <c r="A192" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B192" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lochmann, Heinrich (1613-1667)</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>37</v>
@@ -9934,29 +10010,29 @@
         <v>1667.0</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J192" s="8" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="K192" s="9"/>
     </row>
     <row r="193" ht="22.5" customHeight="1">
       <c r="A193" s="3" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B193" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Johann Jakob (1602-1668)</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>31</v>
@@ -9968,109 +10044,109 @@
         <v>1668.0</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J193" s="8" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="K193" s="9"/>
     </row>
     <row r="194" ht="22.5" customHeight="1">
       <c r="A194" s="3" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B194" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orelli, Anna (-)</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E194" s="15"/>
       <c r="F194" s="16"/>
       <c r="G194" s="9"/>
       <c r="H194" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="I194" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J194" s="10" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="K194" s="9"/>
     </row>
     <row r="195" ht="22.5" customHeight="1">
       <c r="A195" s="3" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B195" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. E. H.,  (-)</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="15"/>
       <c r="F195" s="16"/>
       <c r="G195" s="9"/>
       <c r="H195" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J195" s="20" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="K195" s="9"/>
     </row>
     <row r="196" ht="22.5" customHeight="1">
       <c r="A196" s="3" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B196" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. H.,  (-)</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D196" s="3"/>
       <c r="E196" s="15"/>
       <c r="F196" s="16"/>
       <c r="G196" s="9"/>
       <c r="H196" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I196" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J196" s="20" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="K196" s="9"/>
     </row>
     <row r="197" ht="22.5" customHeight="1">
       <c r="A197" s="3" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B197" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grob, Hans Jakob (-)</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>215</v>
@@ -10079,19 +10155,19 @@
       <c r="F197" s="16"/>
       <c r="G197" s="9"/>
       <c r="H197" s="3" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="I197" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J197" s="8" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="K197" s="9"/>
     </row>
     <row r="198" ht="22.5" customHeight="1">
       <c r="A198" s="3" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B198" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10101,7 +10177,7 @@
         <v>68</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E198" s="15"/>
       <c r="F198" s="16"/>
@@ -10111,23 +10187,23 @@
         <v>16</v>
       </c>
       <c r="J198" s="8" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="K198" s="9"/>
     </row>
     <row r="199" ht="22.5" customHeight="1">
       <c r="A199" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B199" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klingler, Kaspar (-)</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E199" s="15"/>
       <c r="F199" s="16"/>
@@ -10137,20 +10213,20 @@
         <v>16</v>
       </c>
       <c r="J199" s="8" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K199" s="9"/>
     </row>
     <row r="200" ht="22.5" customHeight="1">
       <c r="A200" s="3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B200" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöndli, Dorothea (-)</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>413</v>
@@ -10163,23 +10239,23 @@
         <v>16</v>
       </c>
       <c r="J200" s="8" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K200" s="9"/>
     </row>
     <row r="201" ht="22.5" customHeight="1">
       <c r="A201" s="3" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B201" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Hans Caspar (1617-1691)</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="E201" s="5">
         <v>1617.0</v>
@@ -10188,29 +10264,29 @@
         <v>1691.0</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="K201" s="9"/>
     </row>
     <row r="202" ht="22.5" customHeight="1">
       <c r="A202" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B202" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Salomon (1580-1652)</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>428</v>
@@ -10222,60 +10298,60 @@
         <v>1652.0</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J202" s="8" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="K202" s="9"/>
     </row>
     <row r="203" ht="22.5" customHeight="1">
       <c r="A203" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B203" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis-Soglio, Maria Ursina von  (-)</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E203" s="15"/>
       <c r="F203" s="16"/>
       <c r="G203" s="9"/>
       <c r="H203" s="3" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J203" s="8" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="K203" s="9"/>
     </row>
     <row r="204" ht="22.5" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B204" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Brügger, Andreas von (1588-1653)</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E204" s="5">
         <v>1588.0</v>
@@ -10284,36 +10360,36 @@
         <v>1653.0</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="I204" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J204" s="8" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="K204" s="9"/>
     </row>
     <row r="205" ht="22.5" customHeight="1">
       <c r="A205" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B205" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Anhorn,  (-)</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D205" s="3"/>
       <c r="E205" s="15"/>
       <c r="F205" s="16"/>
       <c r="G205" s="9"/>
       <c r="H205" s="3" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="I205" s="7" t="s">
         <v>16</v>
@@ -10323,14 +10399,14 @@
     </row>
     <row r="206" ht="22.5" customHeight="1">
       <c r="A206" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B206" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wilden, Abraham (-)</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>284</v>
@@ -10339,7 +10415,7 @@
       <c r="F206" s="16"/>
       <c r="G206" s="9"/>
       <c r="H206" s="3" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>16</v>
@@ -10349,23 +10425,23 @@
     </row>
     <row r="207" ht="22.5" customHeight="1">
       <c r="A207" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B207" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Groben, Jacob (evtl. Johannes) (-)</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E207" s="15"/>
       <c r="F207" s="16"/>
       <c r="G207" s="9"/>
       <c r="H207" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>16</v>
@@ -10375,21 +10451,21 @@
     </row>
     <row r="208" ht="22.5" customHeight="1">
       <c r="A208" s="3" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B208" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ziegler,  (-)</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="15"/>
       <c r="F208" s="16"/>
       <c r="G208" s="9"/>
       <c r="H208" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="I208" s="7" t="s">
         <v>16</v>
@@ -10399,7 +10475,7 @@
     </row>
     <row r="209" ht="22.5" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B209" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10415,7 +10491,7 @@
       <c r="F209" s="16"/>
       <c r="G209" s="9"/>
       <c r="H209" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="I209" s="7" t="s">
         <v>16</v>
@@ -10425,21 +10501,21 @@
     </row>
     <row r="210" ht="22.5" customHeight="1">
       <c r="A210" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B210" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Oeri,  (-)</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="15"/>
       <c r="F210" s="16"/>
       <c r="G210" s="9"/>
       <c r="H210" s="3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="I210" s="7" t="s">
         <v>16</v>
@@ -10449,21 +10525,21 @@
     </row>
     <row r="211" ht="22.5" customHeight="1">
       <c r="A211" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B211" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wittib,  (-)</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="15"/>
       <c r="F211" s="16"/>
       <c r="G211" s="9"/>
       <c r="H211" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="I211" s="12"/>
       <c r="J211" s="9"/>
@@ -10471,14 +10547,14 @@
     </row>
     <row r="212" ht="22.5" customHeight="1">
       <c r="A212" s="3" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B212" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Graf von Sultz,  (-)</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D212" s="3"/>
       <c r="E212" s="15"/>
@@ -10493,21 +10569,21 @@
     </row>
     <row r="213" ht="22.5" customHeight="1">
       <c r="A213" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B213" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Eglin,  (-)</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="D213" s="3"/>
       <c r="E213" s="15"/>
       <c r="F213" s="16"/>
       <c r="G213" s="9"/>
       <c r="H213" s="3" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="I213" s="7" t="s">
         <v>16</v>
@@ -10517,14 +10593,14 @@
     </row>
     <row r="214" ht="22.5" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B214" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wildhans von Breitenlandenberg,  (-1444)</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="15"/>
@@ -10533,7 +10609,7 @@
       </c>
       <c r="G214" s="9"/>
       <c r="H214" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="I214" s="7" t="s">
         <v>16</v>
@@ -10543,14 +10619,14 @@
     </row>
     <row r="215" ht="22.5" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B215" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pfarrherr,  (-)</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="15"/>
@@ -10565,17 +10641,17 @@
     </row>
     <row r="216" ht="22.5" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B216" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid von Schwarzenhorn, Johann Rudolf (1590-1667)</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E216" s="5">
         <v>1590.0</v>
@@ -10584,29 +10660,29 @@
         <v>1667.0</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="I216" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J216" s="8" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="K216" s="9"/>
     </row>
     <row r="217" ht="22.5" customHeight="1">
       <c r="A217" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B217" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid, Felix (-1598)</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>88</v>
@@ -10617,26 +10693,26 @@
       </c>
       <c r="G217" s="9"/>
       <c r="H217" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="I217" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J217" s="8" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="K217" s="9"/>
     </row>
     <row r="218" ht="22.5" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B218" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hessen, Heinrich (-)</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>37</v>
@@ -10645,7 +10721,7 @@
       <c r="F218" s="16"/>
       <c r="G218" s="9"/>
       <c r="H218" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="I218" s="7" t="s">
         <v>16</v>
@@ -10655,17 +10731,17 @@
     </row>
     <row r="219" ht="22.5" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B219" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulr., H. (-)</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E219" s="15"/>
       <c r="F219" s="16"/>
@@ -10681,7 +10757,7 @@
     </row>
     <row r="220" ht="22.5" customHeight="1">
       <c r="A220" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B220" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10691,13 +10767,13 @@
         <v>60</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E220" s="15"/>
       <c r="F220" s="16"/>
       <c r="G220" s="9"/>
       <c r="H220" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>16</v>
@@ -10707,7 +10783,7 @@
     </row>
     <row r="221" ht="22.5" customHeight="1">
       <c r="A221" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B221" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10721,7 +10797,7 @@
       <c r="F221" s="16"/>
       <c r="G221" s="9"/>
       <c r="H221" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="I221" s="7" t="s">
         <v>16</v>
@@ -10731,14 +10807,14 @@
     </row>
     <row r="222" ht="22.5" customHeight="1">
       <c r="A222" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B222" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Locher,  (-)</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="15"/>
@@ -10753,17 +10829,17 @@
     </row>
     <row r="223" ht="22.5" customHeight="1">
       <c r="A223" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B223" s="4" t="str">
         <f t="shared" si="1"/>
         <v>König, Caspar (-)</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E223" s="15"/>
       <c r="F223" s="16"/>
@@ -10775,7 +10851,7 @@
     </row>
     <row r="224" ht="22.5" customHeight="1">
       <c r="A224" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B224" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10797,7 +10873,7 @@
         <v>70</v>
       </c>
       <c r="H224" s="17" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I224" s="7" t="s">
         <v>16</v>
@@ -10809,7 +10885,7 @@
     </row>
     <row r="225" ht="22.5" customHeight="1">
       <c r="A225" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B225" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10823,7 +10899,7 @@
       <c r="F225" s="16"/>
       <c r="G225" s="9"/>
       <c r="H225" s="3" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>16</v>
@@ -10833,17 +10909,17 @@
     </row>
     <row r="226" ht="22.5" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B226" s="4" t="str">
         <f t="shared" si="1"/>
         <v>O., Jacob U. (-)</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E226" s="15"/>
       <c r="F226" s="16"/>
@@ -10859,21 +10935,21 @@
     </row>
     <row r="227" ht="22.5" customHeight="1">
       <c r="A227" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B227" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schneeberger,  (-)</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="15"/>
       <c r="F227" s="16"/>
       <c r="G227" s="9"/>
       <c r="H227" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="I227" s="7" t="s">
         <v>16</v>
@@ -10883,17 +10959,17 @@
     </row>
     <row r="228" ht="22.5" customHeight="1">
       <c r="A228" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B228" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwingli, Ulrich (1484-1531)</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E228" s="5">
         <v>1484.0</v>
@@ -10902,10 +10978,10 @@
         <v>1531.0</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="I228" s="7" t="s">
         <v>16</v>
@@ -10915,14 +10991,14 @@
     </row>
     <row r="229" ht="22.5" customHeight="1">
       <c r="A229" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B229" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bullinger, Heinrich (1504-1575)</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>37</v>
@@ -10934,10 +11010,10 @@
         <v>1575.0</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="I229" s="7" t="s">
         <v>16</v>
@@ -10947,17 +11023,17 @@
     </row>
     <row r="230" ht="22.5" customHeight="1">
       <c r="A230" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B230" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther, Rudolf (1519-1586)</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E230" s="5">
         <v>1519.0</v>
@@ -10966,7 +11042,7 @@
         <v>1586.0</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H230" s="3"/>
       <c r="I230" s="7" t="s">
@@ -10977,14 +11053,14 @@
     </row>
     <row r="231" ht="22.5" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B231" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Breitinger, Johann Jakob (1575-1645)</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>31</v>
@@ -10996,7 +11072,7 @@
         <v>1645.0</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H231" s="3"/>
       <c r="I231" s="7" t="s">
@@ -11007,17 +11083,17 @@
     </row>
     <row r="232" ht="22.5" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B232" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jrminger, Jacob (1588-1649)</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E232" s="5">
         <v>1588.0</v>
@@ -11026,7 +11102,7 @@
         <v>1649.0</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H232" s="3"/>
       <c r="I232" s="7" t="s">
@@ -11037,14 +11113,14 @@
     </row>
     <row r="233" ht="22.5" customHeight="1">
       <c r="A233" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B233" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fries, Jakob (-)</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>347</v>
@@ -11061,25 +11137,25 @@
     </row>
     <row r="234" ht="22.5" customHeight="1">
       <c r="A234" s="3" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B234" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Geiger, Joh. Rud. (-)</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E234" s="15"/>
       <c r="F234" s="16"/>
       <c r="G234" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="I234" s="7" t="s">
         <v>16</v>
@@ -11089,17 +11165,17 @@
     </row>
     <row r="235" ht="22.5" customHeight="1">
       <c r="A235" s="3" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B235" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maurer, C. (-)</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E235" s="15"/>
       <c r="F235" s="16"/>
@@ -11113,17 +11189,17 @@
     </row>
     <row r="236" ht="22.5" customHeight="1">
       <c r="A236" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="B236" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Suter, C. (-)</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>860</v>
+      </c>
+      <c r="D236" s="3" t="s">
         <v>858</v>
-      </c>
-      <c r="B236" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>Suter, C. (-)</v>
-      </c>
-      <c r="C236" s="6" t="s">
-        <v>859</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>857</v>
       </c>
       <c r="E236" s="15"/>
       <c r="F236" s="16"/>
@@ -11137,17 +11213,17 @@
     </row>
     <row r="237" ht="22.5" customHeight="1">
       <c r="A237" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B237" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Holzhalb, Joh. (-)</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E237" s="15"/>
       <c r="F237" s="16"/>
@@ -11163,17 +11239,17 @@
     </row>
     <row r="238" ht="22.5" customHeight="1">
       <c r="A238" s="3" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B238" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wirtz, H. C. (-)</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E238" s="15"/>
       <c r="F238" s="16"/>
@@ -11187,22 +11263,22 @@
     </row>
     <row r="239" ht="22.5" customHeight="1">
       <c r="A239" s="3" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B239" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser, Caspar (-)</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E239" s="15"/>
       <c r="F239" s="16"/>
       <c r="G239" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H239" s="3"/>
       <c r="I239" s="7" t="s">
@@ -11213,22 +11289,22 @@
     </row>
     <row r="240" ht="22.5" customHeight="1">
       <c r="A240" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B240" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hospinianus, R. (-)</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E240" s="15"/>
       <c r="F240" s="16"/>
       <c r="G240" s="3" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H240" s="3"/>
       <c r="I240" s="7" t="s">
@@ -11239,17 +11315,17 @@
     </row>
     <row r="241" ht="22.5" customHeight="1">
       <c r="A241" s="3" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B241" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Erni, H. (-)</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E241" s="15"/>
       <c r="F241" s="16"/>
@@ -11263,17 +11339,17 @@
     </row>
     <row r="242" ht="22.5" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B242" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Tomman, P. (-)</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="E242" s="15"/>
       <c r="F242" s="16"/>
@@ -11287,17 +11363,17 @@
     </row>
     <row r="243" ht="22.5" customHeight="1">
       <c r="A243" s="3" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B243" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Stukki, R. (-)</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="E243" s="15"/>
       <c r="F243" s="16"/>
@@ -11311,17 +11387,17 @@
     </row>
     <row r="244" ht="22.5" customHeight="1">
       <c r="A244" s="3" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B244" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zeller, H. (-)</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E244" s="15"/>
       <c r="F244" s="16"/>
@@ -11335,7 +11411,7 @@
     </row>
     <row r="245" ht="22.5" customHeight="1">
       <c r="A245" s="3" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B245" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11343,13 +11419,13 @@
       </c>
       <c r="C245" s="6"/>
       <c r="D245" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="E245" s="15"/>
       <c r="F245" s="16"/>
       <c r="G245" s="9"/>
       <c r="H245" s="3" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="I245" s="7" t="s">
         <v>16</v>
@@ -11359,21 +11435,21 @@
     </row>
     <row r="246" ht="22.5" customHeight="1">
       <c r="A246" s="3" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B246" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fr. Doctorin,  (-)</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="15"/>
       <c r="F246" s="16"/>
       <c r="G246" s="9"/>
       <c r="H246" s="3" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="I246" s="7" t="s">
         <v>16</v>
@@ -11383,17 +11459,17 @@
     </row>
     <row r="247" ht="22.5" customHeight="1">
       <c r="A247" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B247" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kusen, Jost von (1570-1630)</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="E247" s="5">
         <v>1570.0</v>
@@ -11402,10 +11478,10 @@
         <v>1630.0</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="I247" s="7" t="s">
         <v>16</v>
@@ -11415,14 +11491,14 @@
     </row>
     <row r="248" ht="22.5" customHeight="1">
       <c r="A248" s="3" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B248" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Heinrich (-)</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>37</v>
@@ -11431,7 +11507,7 @@
       <c r="F248" s="16"/>
       <c r="G248" s="9"/>
       <c r="H248" s="3" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="I248" s="7" t="s">
         <v>16</v>
@@ -11441,21 +11517,21 @@
     </row>
     <row r="249" ht="22.5" customHeight="1">
       <c r="A249" s="3" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B249" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gessner,  (-)</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="15"/>
       <c r="F249" s="16"/>
       <c r="G249" s="9"/>
       <c r="H249" s="3" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="I249" s="7" t="s">
         <v>16</v>
@@ -11465,17 +11541,17 @@
     </row>
     <row r="250" ht="22.5" customHeight="1">
       <c r="A250" s="3" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B250" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wöllwein, Johann Anton (1616-1659)</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="E250" s="5">
         <v>1616.0</v>
@@ -11484,10 +11560,10 @@
         <v>1659.0</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="I250" s="7" t="s">
         <v>16</v>
@@ -11497,42 +11573,42 @@
     </row>
     <row r="251" ht="22.5" customHeight="1">
       <c r="A251" s="3" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B251" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Anna (-)</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E251" s="15"/>
       <c r="F251" s="16"/>
       <c r="G251" s="9"/>
       <c r="H251" s="3" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="I251" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="K251" s="9"/>
     </row>
     <row r="252" ht="22.5" customHeight="1">
       <c r="A252" s="3" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B252" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. J. R. S.,  (-)</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D252" s="3"/>
       <c r="E252" s="15"/>
@@ -11545,17 +11621,17 @@
     </row>
     <row r="253" ht="22.5" customHeight="1">
       <c r="A253" s="3" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B253" s="4" t="str">
         <f t="shared" si="1"/>
         <v>de Ruyter, Michiel (1607-1676)</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="E253" s="5">
         <v>1607.0</v>
@@ -11564,10 +11640,10 @@
         <v>1676.0</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="I253" s="7" t="s">
         <v>16</v>
@@ -11577,21 +11653,21 @@
     </row>
     <row r="254" ht="22.5" customHeight="1">
       <c r="A254" s="3" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B254" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Frau Oberstin,  (-)</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="15"/>
       <c r="F254" s="16"/>
       <c r="G254" s="9"/>
       <c r="H254" s="3" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="I254" s="7" t="s">
         <v>16</v>
@@ -11601,23 +11677,23 @@
     </row>
     <row r="255" ht="22.5" customHeight="1">
       <c r="A255" s="3" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B255" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vulcanus,  (-)</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="15"/>
       <c r="F255" s="16"/>
       <c r="G255" s="3" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="I255" s="7" t="s">
         <v>227</v>
@@ -11627,23 +11703,23 @@
     </row>
     <row r="256" ht="22.5" customHeight="1">
       <c r="A256" s="3" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B256" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esau,  (-)</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="15"/>
       <c r="F256" s="16"/>
       <c r="G256" s="3" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="I256" s="7" t="s">
         <v>245</v>
@@ -11653,23 +11729,23 @@
     </row>
     <row r="257" ht="22.5" customHeight="1">
       <c r="A257" s="3" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B257" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Danaos,  (-)</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="15"/>
       <c r="F257" s="16"/>
       <c r="G257" s="3" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="I257" s="7" t="s">
         <v>227</v>
@@ -11679,20 +11755,20 @@
     </row>
     <row r="258" ht="22.5" customHeight="1">
       <c r="A258" s="3" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B258" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Medusa,  (-)</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="15"/>
       <c r="F258" s="16"/>
       <c r="G258" s="3" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>227</v>
@@ -11705,20 +11781,20 @@
     </row>
     <row r="259" ht="22.5" customHeight="1">
       <c r="A259" s="3" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B259" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pluton,  (-)</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="15"/>
       <c r="F259" s="16"/>
       <c r="G259" s="3" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>227</v>
@@ -11731,20 +11807,20 @@
     </row>
     <row r="260" ht="22.5" customHeight="1">
       <c r="A260" s="3" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B260" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mercur,  (-)</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="15"/>
       <c r="F260" s="16"/>
       <c r="G260" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>227</v>
@@ -11757,20 +11833,20 @@
     </row>
     <row r="261" ht="22.5" customHeight="1">
       <c r="A261" s="3" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B261" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Perseus,  (-)</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="15"/>
       <c r="F261" s="16"/>
       <c r="G261" s="3" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>227</v>
@@ -11783,23 +11859,23 @@
     </row>
     <row r="262" ht="22.5" customHeight="1">
       <c r="A262" s="3" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B262" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Atropos,  (-)</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="15"/>
       <c r="F262" s="16"/>
       <c r="G262" s="3" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="I262" s="7" t="s">
         <v>227</v>
@@ -11809,23 +11885,23 @@
     </row>
     <row r="263" ht="22.5" customHeight="1">
       <c r="A263" s="3" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B263" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Barbara von Nikomedien,  (-)</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="15"/>
       <c r="F263" s="16"/>
       <c r="G263" s="3" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H263" s="3" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="I263" s="7" t="s">
         <v>245</v>
@@ -11835,7 +11911,7 @@
     </row>
     <row r="264" ht="22.5" customHeight="1">
       <c r="A264" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B264" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11843,13 +11919,13 @@
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="3" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E264" s="15"/>
       <c r="F264" s="16"/>
       <c r="G264" s="9"/>
       <c r="H264" s="3" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="I264" s="12"/>
       <c r="J264" s="9"/>
@@ -11857,7 +11933,7 @@
     </row>
     <row r="265" ht="22.5" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B265" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11871,7 +11947,7 @@
       <c r="F265" s="16"/>
       <c r="G265" s="9"/>
       <c r="H265" s="3" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="I265" s="12"/>
       <c r="J265" s="9"/>
@@ -11879,21 +11955,21 @@
     </row>
     <row r="266" ht="22.5" customHeight="1">
       <c r="A266" s="3" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B266" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Karl,  (-)</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="15"/>
       <c r="F266" s="16"/>
       <c r="G266" s="9"/>
       <c r="H266" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="I266" s="7" t="s">
         <v>16</v>
@@ -11903,21 +11979,21 @@
     </row>
     <row r="267" ht="22.5" customHeight="1">
       <c r="A267" s="3" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B267" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Duraeum,  (-)</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="15"/>
       <c r="F267" s="16"/>
       <c r="G267" s="9"/>
       <c r="H267" s="3" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="I267" s="12"/>
       <c r="J267" s="9"/>
@@ -11925,17 +12001,17 @@
     </row>
     <row r="268" ht="22.5" customHeight="1">
       <c r="A268" s="3" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B268" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zesen, Philipp von (1619-1689)</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="E268" s="5">
         <v>1619.0</v>
@@ -11944,7 +12020,7 @@
         <v>1689.0</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H268" s="3"/>
       <c r="I268" s="7" t="s">
@@ -11955,23 +12031,23 @@
     </row>
     <row r="269" ht="22.5" customHeight="1">
       <c r="A269" s="3" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B269" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lucretia,  (-)</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D269" s="3"/>
       <c r="E269" s="15"/>
       <c r="F269" s="16"/>
       <c r="G269" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="I269" s="7" t="s">
         <v>227</v>
@@ -11981,23 +12057,23 @@
     </row>
     <row r="270" ht="22.5" customHeight="1">
       <c r="A270" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B270" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ovid,  (-)</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="15"/>
       <c r="F270" s="16"/>
       <c r="G270" s="3" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H270" s="3" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="I270" s="7" t="s">
         <v>16</v>
@@ -12007,17 +12083,17 @@
     </row>
     <row r="271" ht="22.5" customHeight="1">
       <c r="A271" s="3" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B271" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schweizer, Johann Caspar (1619-1688)</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="E271" s="5">
         <v>1619.0</v>
@@ -12026,29 +12102,29 @@
         <v>83</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H271" s="3" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="I271" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J271" s="8" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="K271" s="9"/>
     </row>
     <row r="272" ht="22.5" customHeight="1">
       <c r="A272" s="3" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B272" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Herder, Johann Heinrich (-)</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>43</v>
@@ -12063,7 +12139,7 @@
     </row>
     <row r="273" ht="22.5" customHeight="1">
       <c r="A273" s="3" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B273" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12081,7 +12157,7 @@
     </row>
     <row r="274" ht="22.5" customHeight="1">
       <c r="A274" s="3" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B274" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12099,7 +12175,7 @@
     </row>
     <row r="275" ht="22.5" customHeight="1">
       <c r="A275" s="3" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B275" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12117,7 +12193,7 @@
     </row>
     <row r="276" ht="22.5" customHeight="1">
       <c r="A276" s="3" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B276" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12135,7 +12211,7 @@
     </row>
     <row r="277" ht="22.5" customHeight="1">
       <c r="A277" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B277" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12153,7 +12229,7 @@
     </row>
     <row r="278" ht="22.5" customHeight="1">
       <c r="A278" s="3" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B278" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12171,7 +12247,7 @@
     </row>
     <row r="279" ht="22.5" customHeight="1">
       <c r="A279" s="3" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B279" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12189,7 +12265,7 @@
     </row>
     <row r="280" ht="22.5" customHeight="1">
       <c r="A280" s="3" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B280" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12293,16 +12369,16 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -12313,179 +12389,179 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B2" s="21" t="str">
         <f t="shared" ref="B2:B102" si="1">CONCATENATE(C2)</f>
         <v>Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="7" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B3" s="21" t="str">
         <f t="shared" si="1"/>
         <v>Basel</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="7" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B4" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Eidgenossenschaft</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E4" s="18"/>
       <c r="F4" s="3" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B5" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Limmat</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="7" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B6" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Weinfelden</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="7" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B7" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Main</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D7" s="23"/>
       <c r="E7" s="7" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B8" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Zürichsee</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D8" s="23"/>
       <c r="E8" s="7" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B9" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Thalwil</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="12"/>
       <c r="F9" s="3" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B10" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Bern</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="7" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B11" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Gottstatt</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D11" s="23"/>
       <c r="E11" s="12"/>
@@ -12493,48 +12569,48 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B12" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Thorberg</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="12"/>
       <c r="F12" s="3" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B13" s="22" t="str">
         <f t="shared" si="1"/>
         <v>London</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D13" s="23"/>
       <c r="E13" s="7" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B14" s="22" t="str">
         <f t="shared" si="1"/>
         <v>England</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D14" s="23"/>
       <c r="E14" s="12"/>
@@ -12542,52 +12618,52 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B15" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Bethlehem</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="7" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B16" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Parnass </v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="7" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B17" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Traubenberg</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="12"/>
@@ -12595,50 +12671,50 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B18" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Babylon</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="7" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B19" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Canaan</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="12"/>
       <c r="F19" s="3" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B20" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Ägypten</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="12"/>
@@ -12646,158 +12722,158 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B21" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Hermon</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="7" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B22" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Jerusalem</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B23" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Jordan</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="7" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B24" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Rotes Meer</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="7" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F24" s="9"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B25" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Juda</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D25" s="23"/>
       <c r="E25" s="12"/>
       <c r="F25" s="3" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B26" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Moab</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="D26" s="23"/>
       <c r="E26" s="12"/>
       <c r="F26" s="3" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B27" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Ammon</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="12"/>
       <c r="F27" s="3" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B28" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Zion</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D28" s="23"/>
       <c r="E28" s="7" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B29" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Assur</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D29" s="23"/>
       <c r="E29" s="12"/>
@@ -12805,101 +12881,101 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B30" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Israel</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="12"/>
       <c r="F30" s="3" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B31" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Nazaret</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D31" s="23"/>
       <c r="E31" s="7" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B32" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Rom</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="12"/>
       <c r="F32" s="3" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B33" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Samaria</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="12"/>
       <c r="F33" s="3" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B34" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Kedronbach</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="12"/>
       <c r="F34" s="3" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B35" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Garten von Getsemani</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D35" s="23"/>
       <c r="E35" s="12"/>
@@ -12907,14 +12983,14 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B36" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Urdorf</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="12"/>
@@ -12922,14 +12998,14 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B37" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Geiren-Rein</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="12"/>
@@ -12937,14 +13013,14 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B38" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Aeügst</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="D38" s="23"/>
       <c r="E38" s="12"/>
@@ -12952,14 +13028,14 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B39" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Riedt</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D39" s="23"/>
       <c r="E39" s="12"/>
@@ -12967,14 +13043,14 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B40" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Europa</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="D40" s="23"/>
       <c r="E40" s="12"/>
@@ -12982,48 +13058,48 @@
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B41" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Osir</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D41" s="23"/>
       <c r="E41" s="12"/>
       <c r="F41" s="3" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B42" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Basadingen</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D42" s="23"/>
       <c r="E42" s="12"/>
       <c r="F42" s="3" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B43" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Diessenhofen</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D43" s="23"/>
       <c r="E43" s="12"/>
@@ -13031,50 +13107,50 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B44" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Rhein</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D44" s="23"/>
       <c r="E44" s="7" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B45" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Arabisches Reich</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D45" s="23"/>
       <c r="E45" s="12"/>
       <c r="F45" s="3" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B46" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Libanon</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D46" s="23"/>
       <c r="E46" s="12"/>
@@ -13082,101 +13158,101 @@
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B47" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Emmaus</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D47" s="23"/>
       <c r="E47" s="12"/>
       <c r="F47" s="3" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B48" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Helikon</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D48" s="23"/>
       <c r="E48" s="12"/>
       <c r="F48" s="3" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B49" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Pindos</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D49" s="23"/>
       <c r="E49" s="12"/>
       <c r="F49" s="3" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B50" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Neckar</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D50" s="23"/>
       <c r="E50" s="7" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B51" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Kurpfalz</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D51" s="23"/>
       <c r="E51" s="12"/>
       <c r="F51" s="3" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B52" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Eglisau</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D52" s="23"/>
       <c r="E52" s="12"/>
@@ -13184,14 +13260,14 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B53" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Altenklingen</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D53" s="23"/>
       <c r="E53" s="12"/>
@@ -13199,14 +13275,14 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B54" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Altorff</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D54" s="23"/>
       <c r="E54" s="12"/>
@@ -13214,31 +13290,31 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B55" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Glarus</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D55" s="23"/>
       <c r="E55" s="12"/>
       <c r="F55" s="3" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B56" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Bergerkirche</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D56" s="23"/>
       <c r="E56" s="12"/>
@@ -13246,31 +13322,31 @@
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B57" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Sodom</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D57" s="23"/>
       <c r="E57" s="12"/>
       <c r="F57" s="3" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B58" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Haus zur Sonnenblume</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D58" s="23"/>
       <c r="E58" s="12"/>
@@ -13278,31 +13354,31 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B59" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Thurn/ genennt von Geissen</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D59" s="23"/>
       <c r="E59" s="12"/>
       <c r="F59" s="3" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B60" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Constantinopel</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="D60" s="23"/>
       <c r="E60" s="12"/>
@@ -13310,118 +13386,118 @@
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B61" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Stein am Rhein</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D61" s="23"/>
       <c r="E61" s="12"/>
       <c r="F61" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B62" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Marburg</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D62" s="23"/>
       <c r="E62" s="12"/>
       <c r="F62" s="3" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B63" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Elbląg</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="3" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B64" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Preußen</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D64" s="23"/>
       <c r="E64" s="12"/>
       <c r="F64" s="3" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B65" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Bad Baden</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D65" s="23"/>
       <c r="E65" s="12"/>
       <c r="F65" s="3" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B66" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Bad Schinznach</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="D66" s="23"/>
       <c r="E66" s="12"/>
       <c r="F66" s="3" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B67" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Gyrenbad</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D67" s="23"/>
       <c r="E67" s="12"/>
@@ -13429,48 +13505,48 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B68" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Wängibad</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D68" s="23"/>
       <c r="E68" s="12"/>
       <c r="F68" s="8" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B69" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Aeugst</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D69" s="23"/>
       <c r="E69" s="12"/>
       <c r="F69" s="3" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B70" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Bassersdorf</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D70" s="23"/>
       <c r="E70" s="12"/>
@@ -13478,14 +13554,14 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B71" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Hauptwil</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D71" s="23"/>
       <c r="E71" s="12"/>
@@ -13493,14 +13569,14 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B72" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Schaffhausen</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D72" s="23"/>
       <c r="E72" s="12"/>
@@ -13508,65 +13584,65 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B73" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Wädenswil</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D73" s="23"/>
       <c r="E73" s="12"/>
       <c r="F73" s="3" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B74" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Freie Ämter</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D74" s="23"/>
       <c r="E74" s="12"/>
       <c r="F74" s="3" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B75" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Grüningen</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D75" s="23"/>
       <c r="E75" s="12"/>
       <c r="F75" s="3" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B76" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Kefikon</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D76" s="23"/>
       <c r="E76" s="12"/>
@@ -13574,14 +13650,14 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B77" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Maienfeld</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D77" s="23"/>
       <c r="E77" s="12"/>
@@ -13589,14 +13665,14 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B78" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Greifensee (Schloss)</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D78" s="23"/>
       <c r="E78" s="12"/>
@@ -13604,31 +13680,31 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B79" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Lindenhof (Zürich)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D79" s="23"/>
       <c r="E79" s="12"/>
       <c r="F79" s="3" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B80" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Galg-Brunnen (Zürich)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="D80" s="23"/>
       <c r="E80" s="12"/>
@@ -13636,14 +13712,14 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B81" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Altes Kornhaus (Zürich)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="D81" s="23"/>
       <c r="E81" s="12"/>
@@ -13651,14 +13727,14 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B82" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Sparrenberg (Zürich)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D82" s="23"/>
       <c r="E82" s="12"/>
@@ -13666,14 +13742,14 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B83" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Thurgau</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="D83" s="23"/>
       <c r="E83" s="12"/>
@@ -13681,14 +13757,14 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B84" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Niederlande</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="D84" s="23"/>
       <c r="E84" s="12"/>
@@ -13696,31 +13772,31 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B85" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Holland</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D85" s="23"/>
       <c r="E85" s="12"/>
       <c r="F85" s="3" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B86" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Wigoltingen</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D86" s="23"/>
       <c r="E86" s="12"/>
@@ -13728,31 +13804,31 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B87" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Kastalia</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D87" s="23"/>
       <c r="E87" s="12"/>
       <c r="F87" s="3" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B88" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Legerberg</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="D88" s="23"/>
       <c r="E88" s="12"/>
@@ -13760,48 +13836,48 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B89" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Texel</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="D89" s="23"/>
       <c r="E89" s="12"/>
       <c r="F89" s="3" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B90" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Vlie</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D90" s="23"/>
       <c r="E90" s="12"/>
       <c r="F90" s="3" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B91" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Indien</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="D91" s="23"/>
       <c r="E91" s="12"/>
@@ -13809,14 +13885,14 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B92" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Wien</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="D92" s="23"/>
       <c r="E92" s="12"/>
@@ -13824,14 +13900,14 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B93" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Deutschland</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="D93" s="23"/>
       <c r="E93" s="12"/>
@@ -13839,54 +13915,58 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B94" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Ölberg</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="D94" s="23"/>
       <c r="E94" s="7" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F94" s="3"/>
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B95" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Dietikon</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="D95" s="23"/>
       <c r="E95" s="12"/>
       <c r="F95" s="3" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B96" s="22" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="C96" s="3"/>
+        <v>Winterthur</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>1224</v>
+      </c>
       <c r="D96" s="23"/>
-      <c r="E96" s="12"/>
+      <c r="E96" s="7" t="s">
+        <v>987</v>
+      </c>
       <c r="F96" s="3"/>
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="B97" s="22" t="str">
         <f t="shared" si="1"/>
@@ -13899,7 +13979,7 @@
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="B98" s="22" t="str">
         <f t="shared" si="1"/>
@@ -13912,7 +13992,7 @@
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B99" s="22" t="str">
         <f t="shared" si="1"/>
@@ -13925,7 +14005,7 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B100" s="22" t="str">
         <f t="shared" si="1"/>
@@ -13938,7 +14018,7 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="B101" s="22" t="str">
         <f t="shared" si="1"/>
@@ -13997,25 +14077,25 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
@@ -14026,67 +14106,75 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B2" s="24" t="str">
         <f t="shared" ref="B2:B30" si="1">CONCATENATE(C2)</f>
         <v>Teutsche Gedichte</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="I2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B3" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Die Krafft der Gottseligkeit</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1242</v>
-      </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="3"/>
+        <v>1244</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1246</v>
+      </c>
       <c r="H3" s="7" t="s">
-        <v>1243</v>
-      </c>
-      <c r="I3" s="9"/>
+        <v>1247</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>1248</v>
+      </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="B4" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Buch von Festen</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5"/>
@@ -14096,23 +14184,23 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
       <c r="B5" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Der Psalter dess Königlichen Propheten Dauids/ Jn deutsche reymen verstendiglich vnd deutlich gebracht/ mit vorgehender anzeigung der reymen weise/ auch eines jeden Psalmes Jnhalt</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="12"/>
@@ -14120,43 +14208,43 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="B6" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Hundert christliche Fäst-Predigen</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="B7" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Lehr- und trostreiche Predigen vom verlohrnen Sohn</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="23"/>
@@ -14166,17 +14254,17 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
       <c r="B8" s="24" t="str">
         <f t="shared" si="1"/>
         <v>verteütschte Rueh- oder Fridens-uebung</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="23"/>
@@ -14186,17 +14274,17 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="B9" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Nähefelser-Fahrt-Predigen</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="23"/>
@@ -14206,17 +14294,17 @@
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="B10" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kinder-lehr</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="23"/>
@@ -14226,17 +14314,17 @@
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="B11" s="24" t="str">
         <f t="shared" si="1"/>
         <v>neüaußgangenes Buech vom Vestungsbau</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="23"/>
@@ -14246,14 +14334,14 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="B12" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Buech der Freunden Stammen</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="9"/>
@@ -14264,17 +14352,17 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="B13" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Christen-spiegel</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="23"/>
@@ -14284,14 +14372,14 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="B14" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Viergeticht</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="D14" s="23"/>
       <c r="E14" s="9"/>
@@ -14302,14 +14390,14 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
       <c r="B15" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Regentenspiegel</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="9"/>
@@ -14320,18 +14408,18 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="B16" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Türckischer Jammerspiegel</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="3" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="F16" s="23"/>
       <c r="G16" s="9"/>
@@ -14340,17 +14428,17 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="B17" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Leitungs-faden</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="23"/>
@@ -14360,17 +14448,17 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="B18" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Buch von der Seelen-angſt Chriſti</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="23"/>
@@ -14380,17 +14468,17 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="B19" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Verſuchungs-gabe</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="23"/>
@@ -14400,14 +14488,14 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="B20" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kriegsbüchlin</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="9"/>
@@ -14418,14 +14506,14 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="B21" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Buch der Psalmen</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="9"/>
@@ -14436,55 +14524,89 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
       <c r="B22" s="24" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="9"/>
+        <v>Sterbensspiegel/ das ist sonnenklare Vorstellung menschlicher Nichtigkeit durch alle Staend und Geschlechter</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>1304</v>
+      </c>
       <c r="H22" s="12"/>
       <c r="I22" s="9"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1296</v>
+        <v>1305</v>
       </c>
       <c r="B23" s="24" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="9"/>
+        <v>Warhaffte/ vnd in Gottes Wort wol gegründte Widerlegung Des newlich im Truck außgegangnen ohn-Catholischen Gesprächs von Religion oder Glaubens sachen/ geneñt der Augenspiegel</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>1304</v>
+      </c>
       <c r="H23" s="12"/>
-      <c r="I23" s="9"/>
+      <c r="I23" s="25" t="s">
+        <v>1309</v>
+      </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1297</v>
+        <v>1310</v>
       </c>
       <c r="B24" s="24" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="9"/>
+        <v>Augspiegels Wahrer Religion Erster Theil</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>1315</v>
+      </c>
       <c r="H24" s="12"/>
-      <c r="I24" s="9"/>
+      <c r="I24" s="25" t="s">
+        <v>1316</v>
+      </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1298</v>
+        <v>1317</v>
       </c>
       <c r="B25" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14500,7 +14622,7 @@
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1299</v>
+        <v>1318</v>
       </c>
       <c r="B26" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14516,7 +14638,7 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1300</v>
+        <v>1319</v>
       </c>
       <c r="B27" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14532,7 +14654,7 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1301</v>
+        <v>1320</v>
       </c>
       <c r="B28" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14548,7 +14670,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1302</v>
+        <v>1321</v>
       </c>
       <c r="B29" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14564,7 +14686,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1303</v>
+        <v>1322</v>
       </c>
       <c r="B30" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14585,9 +14707,14 @@
     </dataValidation>
     <dataValidation allowBlank="1" showDropDown="1" sqref="A2:A30 C2:C30 E2:E30 G2:G30 I2:I30"/>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="I3"/>
+    <hyperlink r:id="rId2" ref="I23"/>
+    <hyperlink r:id="rId3" ref="I24"/>
+  </hyperlinks>
+  <drawing r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
@@ -14608,19 +14735,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1304</v>
+        <v>1323</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1305</v>
+        <v>1324</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -14628,69 +14755,69 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1306</v>
+        <v>1325</v>
       </c>
       <c r="B2" s="24" t="str">
         <f t="shared" ref="B2:B24" si="1">CONCATENATE(C2)</f>
         <v>Rat Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1307</v>
+        <v>1326</v>
       </c>
       <c r="D2" s="23"/>
       <c r="E2" s="26" t="s">
-        <v>1308</v>
+        <v>1327</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1309</v>
+        <v>1328</v>
       </c>
       <c r="B3" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Fruchtbringende Gesellschaft</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1310</v>
+        <v>1329</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1311</v>
+        <v>1330</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>1312</v>
+        <v>1331</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1313</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1314</v>
+        <v>1333</v>
       </c>
       <c r="B4" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Deutschgesinnte Genossenschaft (Lilien-Zunft)</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1315</v>
+        <v>1334</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1316</v>
+        <v>1335</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1317</v>
+        <v>1336</v>
       </c>
       <c r="B5" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Parthenicum</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1318</v>
+        <v>1337</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="12"/>
@@ -14698,105 +14825,105 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1319</v>
+        <v>1338</v>
       </c>
       <c r="B6" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Carolinum Zürich</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1320</v>
+        <v>1339</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1321</v>
+        <v>1340</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="3" t="s">
-        <v>1322</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1323</v>
+        <v>1342</v>
       </c>
       <c r="B7" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Sanhedrin</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1324</v>
+        <v>1343</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="12"/>
       <c r="F7" s="3" t="s">
-        <v>1325</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="B8" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Stadtbibliothek Zürich</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1327</v>
+        <v>1346</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="12"/>
       <c r="F8" s="3" t="s">
-        <v>1328</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1329</v>
+        <v>1348</v>
       </c>
       <c r="B9" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Grossmünster</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1330</v>
+        <v>1349</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="3" t="s">
-        <v>1332</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1333</v>
+        <v>1352</v>
       </c>
       <c r="B10" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Fraumünster Zürich</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1334</v>
+        <v>1353</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1335</v>
+        <v>1354</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="3" t="s">
-        <v>1336</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1337</v>
+        <v>1356</v>
       </c>
       <c r="B11" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Hohe Schule Marburg</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1338</v>
+        <v>1357</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="12"/>
@@ -14804,24 +14931,24 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1339</v>
+        <v>1358</v>
       </c>
       <c r="B12" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kartäuser</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1340</v>
+        <v>1359</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="12"/>
       <c r="F12" s="3" t="s">
-        <v>1341</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="B13" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14834,7 +14961,7 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1343</v>
+        <v>1362</v>
       </c>
       <c r="B14" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14847,7 +14974,7 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1344</v>
+        <v>1363</v>
       </c>
       <c r="B15" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14860,7 +14987,7 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1345</v>
+        <v>1364</v>
       </c>
       <c r="B16" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14873,7 +15000,7 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1346</v>
+        <v>1365</v>
       </c>
       <c r="B17" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14886,7 +15013,7 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1347</v>
+        <v>1366</v>
       </c>
       <c r="B18" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14899,7 +15026,7 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1348</v>
+        <v>1367</v>
       </c>
       <c r="B19" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14912,7 +15039,7 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1349</v>
+        <v>1368</v>
       </c>
       <c r="B20" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14925,7 +15052,7 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1350</v>
+        <v>1369</v>
       </c>
       <c r="B21" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14938,7 +15065,7 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1351</v>
+        <v>1370</v>
       </c>
       <c r="B22" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15001,19 +15128,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1352</v>
+        <v>1371</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1353</v>
+        <v>1372</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1354</v>
+        <v>1373</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1355</v>
+        <v>1374</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -15021,26 +15148,26 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1356</v>
+        <v>1375</v>
       </c>
       <c r="B2" s="21" t="str">
         <f t="shared" ref="B2:B8" si="1">CONCATENATE(C2)</f>
         <v>Runs</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1357</v>
+        <v>1376</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1358</v>
+        <v>1377</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>1359</v>
+        <v>1378</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1360</v>
+        <v>1379</v>
       </c>
       <c r="B3" s="21" t="str">
         <f t="shared" si="1"/>
@@ -15053,7 +15180,7 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1361</v>
+        <v>1380</v>
       </c>
       <c r="B4" s="21" t="str">
         <f t="shared" si="1"/>
@@ -15066,7 +15193,7 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1362</v>
+        <v>1381</v>
       </c>
       <c r="B5" s="21" t="str">
         <f t="shared" si="1"/>
@@ -15079,7 +15206,7 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1363</v>
+        <v>1382</v>
       </c>
       <c r="B6" s="21" t="str">
         <f t="shared" si="1"/>
@@ -15092,7 +15219,7 @@
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1364</v>
+        <v>1383</v>
       </c>
       <c r="B7" s="21" t="str">
         <f t="shared" si="1"/>
@@ -15105,7 +15232,7 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1365</v>
+        <v>1384</v>
       </c>
       <c r="B8" s="21" t="str">
         <f t="shared" si="1"/>

--- a/gsheet/xlsx/entities.xlsx
+++ b/gsheet/xlsx/entities.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="1385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="1387">
   <si>
     <t>Person-ID</t>
   </si>
@@ -1070,6 +1070,9 @@
     <t>Titus</t>
   </si>
   <si>
+    <t>118622951</t>
+  </si>
+  <si>
     <t>Römischer Kaiser</t>
   </si>
   <si>
@@ -1662,6 +1665,9 @@
   </si>
   <si>
     <t>Hercules von</t>
+  </si>
+  <si>
+    <t>1307114342</t>
   </si>
   <si>
     <t>http://www.hfls.ch/humo-gen/birthday_family/1/F135441?main_person=I110567</t>
@@ -4891,14 +4897,15 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="16.75"/>
     <col customWidth="1" min="2" max="2" width="34.0"/>
-    <col customWidth="1" min="3" max="3" width="20.38"/>
+    <col customWidth="1" min="3" max="3" width="28.75"/>
     <col customWidth="1" min="4" max="4" width="18.75"/>
     <col customWidth="1" min="5" max="5" width="11.5"/>
     <col customWidth="1" min="6" max="6" width="10.0"/>
     <col customWidth="1" min="7" max="7" width="36.75"/>
     <col customWidth="1" min="8" max="8" width="46.13"/>
     <col customWidth="1" min="9" max="9" width="22.13"/>
-    <col customWidth="1" min="10" max="11" width="20.13"/>
+    <col customWidth="1" min="10" max="10" width="31.38"/>
+    <col customWidth="1" min="11" max="11" width="20.13"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -6515,7 +6522,9 @@
       <c r="H53" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="I53" s="12"/>
+      <c r="I53" s="7" t="s">
+        <v>245</v>
+      </c>
       <c r="J53" s="9"/>
       <c r="K53" s="9"/>
     </row>
@@ -6535,7 +6544,9 @@
       <c r="F54" s="5"/>
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
-      <c r="I54" s="12"/>
+      <c r="I54" s="7" t="s">
+        <v>245</v>
+      </c>
       <c r="J54" s="9"/>
       <c r="K54" s="9"/>
     </row>
@@ -6961,30 +6972,34 @@
       <c r="D71" s="3"/>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
-      <c r="G71" s="9"/>
+      <c r="G71" s="3" t="s">
+        <v>340</v>
+      </c>
       <c r="H71" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I71" s="12"/>
+        <v>341</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="J71" s="9"/>
       <c r="K71" s="9"/>
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B72" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simon Petrus,  (-)</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
       <c r="G72" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>319</v>
@@ -6997,7 +7012,7 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B73" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7010,7 +7025,7 @@
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>319</v>
@@ -7023,14 +7038,14 @@
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B74" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jakob,  (-)</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="5"/>
@@ -7047,21 +7062,21 @@
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B75" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jonas,  (-)</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="9"/>
       <c r="H75" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I75" s="7" t="s">
         <v>245</v>
@@ -7071,14 +7086,14 @@
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B76" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Joseph,  (-)</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="5"/>
@@ -7095,14 +7110,14 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B77" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Saul, dessen Sohn,  (-)</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="5"/>
@@ -7119,20 +7134,20 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B78" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Satan,  (-)</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
       <c r="G78" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>245</v>
@@ -7145,14 +7160,14 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B79" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Abigail,  (-)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="5"/>
@@ -7169,14 +7184,14 @@
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B80" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hanna,  (-)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="5"/>
@@ -7193,14 +7208,14 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B81" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Susanna,  (-)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="5"/>
@@ -7217,14 +7232,14 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B82" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esther,  (-)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="5"/>
@@ -7241,14 +7256,14 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B83" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jaël,  (-)</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="5"/>
@@ -7265,7 +7280,7 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B84" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7289,21 +7304,21 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B85" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Asarias,  (-)</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D85" s="3"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
       <c r="G85" s="9"/>
       <c r="H85" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I85" s="7" t="s">
         <v>245</v>
@@ -7313,23 +7328,23 @@
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B86" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Boreas,  (-)</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="I86" s="7" t="s">
         <v>227</v>
@@ -7339,23 +7354,23 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B87" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ceres,  (-)</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
       <c r="G87" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I87" s="7" t="s">
         <v>227</v>
@@ -7365,23 +7380,23 @@
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B88" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Amor,  (-)</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I88" s="7" t="s">
         <v>227</v>
@@ -7391,71 +7406,75 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B89" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sokrates,  (-)</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
       <c r="G89" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="I89" s="12"/>
+        <v>388</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="J89" s="9"/>
       <c r="K89" s="9"/>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B90" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Xantippe,  (-)</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="I90" s="12"/>
+        <v>392</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="J90" s="9"/>
       <c r="K90" s="9"/>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B91" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mars,  (-)</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
       <c r="G91" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I91" s="7" t="s">
         <v>227</v>
@@ -7465,23 +7484,23 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B92" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Apollo (Phoebus),  (-)</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
       <c r="G92" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I92" s="7" t="s">
         <v>227</v>
@@ -7491,21 +7510,21 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B93" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sirius,  (-)</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
       <c r="G93" s="9"/>
       <c r="H93" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I93" s="7" t="s">
         <v>227</v>
@@ -7515,14 +7534,14 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B94" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rebecca,  (-)</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="5"/>
@@ -7539,21 +7558,21 @@
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B95" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Asteria,  (-)</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
       <c r="G95" s="9"/>
       <c r="H95" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I95" s="12"/>
       <c r="J95" s="9"/>
@@ -7561,21 +7580,21 @@
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B96" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sylvia,  (-)</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
       <c r="G96" s="9"/>
       <c r="H96" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I96" s="12"/>
       <c r="J96" s="9"/>
@@ -7583,21 +7602,21 @@
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B97" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Felicitas,  (-)</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
       <c r="G97" s="9"/>
       <c r="H97" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I97" s="12"/>
       <c r="J97" s="9"/>
@@ -7605,21 +7624,21 @@
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B98" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dorothea,  (-)</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="9"/>
       <c r="H98" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I98" s="12"/>
       <c r="J98" s="9"/>
@@ -7627,7 +7646,7 @@
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B99" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7641,7 +7660,7 @@
       <c r="F99" s="5"/>
       <c r="G99" s="9"/>
       <c r="H99" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I99" s="12"/>
       <c r="J99" s="9"/>
@@ -7649,14 +7668,14 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B100" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sara,  (-)</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="5"/>
@@ -7673,23 +7692,23 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B101" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hesiodus,  (-)</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5"/>
       <c r="G101" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I101" s="12"/>
       <c r="J101" s="9"/>
@@ -7697,23 +7716,23 @@
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B102" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Parmenides,  (-)</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
       <c r="G102" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I102" s="12"/>
       <c r="J102" s="9"/>
@@ -7721,20 +7740,20 @@
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B103" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salomon,  (-)</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D103" s="3"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
       <c r="G103" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>245</v>
@@ -7747,20 +7766,20 @@
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B104" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Isaak,  (-)</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
       <c r="G104" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>245</v>
@@ -7773,14 +7792,14 @@
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B105" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rahel,  (-)</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="5"/>
@@ -7797,20 +7816,20 @@
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B106" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hiob,  (-)</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5"/>
       <c r="G106" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>245</v>
@@ -7823,14 +7842,14 @@
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B107" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simson,  (-)</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="5"/>
@@ -7847,23 +7866,23 @@
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B108" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ben Sira,  (-)</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
       <c r="G108" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I108" s="12"/>
       <c r="J108" s="9"/>
@@ -7871,20 +7890,20 @@
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B109" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wilhelm Tell,  (-)</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D109" s="3"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
       <c r="G109" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="12"/>
@@ -7893,23 +7912,23 @@
     </row>
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B110" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zephyr,  (-)</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D110" s="3"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
       <c r="G110" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I110" s="7" t="s">
         <v>227</v>
@@ -7919,7 +7938,7 @@
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B111" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7943,21 +7962,21 @@
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B112" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Friedensfürst,  (-)</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
       <c r="G112" s="9"/>
       <c r="H112" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I112" s="12"/>
       <c r="J112" s="9"/>
@@ -7965,21 +7984,21 @@
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B113" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gracchus,  (-)</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
       <c r="G113" s="9"/>
       <c r="H113" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I113" s="12"/>
       <c r="J113" s="9"/>
@@ -7987,21 +8006,21 @@
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B114" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gracchus, dessen Frau,  (-)</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
       <c r="G114" s="9"/>
       <c r="H114" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I114" s="12"/>
       <c r="J114" s="9"/>
@@ -8009,20 +8028,20 @@
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B115" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Moses,  (-)</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D115" s="3"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
       <c r="G115" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>245</v>
@@ -8035,23 +8054,23 @@
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B116" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orestes,  (-)</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
       <c r="G116" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I116" s="7" t="s">
         <v>227</v>
@@ -8061,23 +8080,23 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B117" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pylades,  (-)</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
       <c r="G117" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="I117" s="7" t="s">
         <v>227</v>
@@ -8087,21 +8106,21 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B118" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thurik,  (-)</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
       <c r="G118" s="9"/>
       <c r="H118" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="I118" s="7" t="s">
         <v>227</v>
@@ -8111,21 +8130,21 @@
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B119" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Midas,  (-)</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
       <c r="G119" s="9"/>
       <c r="H119" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I119" s="7" t="s">
         <v>227</v>
@@ -8135,49 +8154,49 @@
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B120" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simon,  (-)</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
       <c r="G120" s="9"/>
       <c r="H120" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I120" s="7" t="s">
         <v>227</v>
       </c>
       <c r="J120" s="9"/>
       <c r="K120" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B121" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Damokles,  (-)</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
       <c r="G121" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I121" s="12"/>
       <c r="J121" s="9"/>
@@ -8185,23 +8204,23 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B122" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dionysius I. von Syrakus,  (-)</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
       <c r="G122" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="I122" s="12"/>
       <c r="J122" s="9"/>
@@ -8209,23 +8228,23 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B123" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kleopatra VII.,  (-)</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
       <c r="G123" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I123" s="12"/>
       <c r="J123" s="9"/>
@@ -8233,23 +8252,23 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B124" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Marcus Antonius,  (-)</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D124" s="3"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
       <c r="G124" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="I124" s="12"/>
       <c r="J124" s="9"/>
@@ -8257,23 +8276,23 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B125" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klio,  (-)</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
       <c r="G125" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="I125" s="7" t="s">
         <v>227</v>
@@ -8283,23 +8302,23 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B126" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Flora,  (-)</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
       <c r="G126" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I126" s="7" t="s">
         <v>227</v>
@@ -8309,14 +8328,14 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B127" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dorothea,  (-)</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D127" s="3"/>
       <c r="E127" s="5"/>
@@ -8329,21 +8348,21 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B128" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. J. V.,  (-)</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
       <c r="G128" s="9"/>
       <c r="H128" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I128" s="7" t="s">
         <v>16</v>
@@ -8353,21 +8372,21 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B129" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. J. V., dessen Frau,  (-)</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
       <c r="G129" s="9"/>
       <c r="H129" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I129" s="7" t="s">
         <v>16</v>
@@ -8377,21 +8396,21 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B130" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sch. H.,  (-)</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
       <c r="G130" s="9"/>
       <c r="H130" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I130" s="7" t="s">
         <v>16</v>
@@ -8401,14 +8420,14 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B131" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser, Johann Heinrich (1600-1669)</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>43</v>
@@ -8420,66 +8439,66 @@
         <v>1669.0</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H131" s="13" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="I131" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J131" s="14" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K131" s="9"/>
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B132" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser-Ziegler, Jahel (-)</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
       <c r="G132" s="9"/>
       <c r="H132" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I132" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K132" s="9"/>
     </row>
     <row r="133" ht="22.5" customHeight="1">
       <c r="A133" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B133" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caspar W.,  (-)</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
       <c r="G133" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I133" s="7" t="s">
         <v>16</v>
@@ -8489,21 +8508,21 @@
     </row>
     <row r="134" ht="22.5" customHeight="1">
       <c r="A134" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B134" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esther O.,  (-)</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
       <c r="G134" s="9"/>
       <c r="H134" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I134" s="7" t="s">
         <v>16</v>
@@ -8513,14 +8532,14 @@
     </row>
     <row r="135" ht="22.5" customHeight="1">
       <c r="A135" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B135" s="4" t="str">
         <f t="shared" si="1"/>
         <v>G. H.,  (-)</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="5"/>
@@ -8535,21 +8554,21 @@
     </row>
     <row r="136" ht="22.5" customHeight="1">
       <c r="A136" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B136" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. C.,  (-)</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
       <c r="G136" s="9"/>
       <c r="H136" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I136" s="7" t="s">
         <v>16</v>
@@ -8559,17 +8578,17 @@
     </row>
     <row r="137" ht="22.5" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B137" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Hercules von (1617-1686)</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E137" s="5">
         <v>1617.0</v>
@@ -8577,29 +8596,31 @@
       <c r="F137" s="5">
         <v>1686.0</v>
       </c>
-      <c r="G137" s="9"/>
+      <c r="G137" s="3" t="s">
+        <v>539</v>
+      </c>
       <c r="H137" s="3"/>
       <c r="I137" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K137" s="9"/>
     </row>
     <row r="138" ht="22.5" customHeight="1">
       <c r="A138" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B138" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Barbara Dorothea von (1629-1660)</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E138" s="5">
         <v>1629.0</v>
@@ -8609,26 +8630,26 @@
       </c>
       <c r="G138" s="9"/>
       <c r="H138" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I138" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J138" s="8" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="K138" s="9"/>
     </row>
     <row r="139" ht="22.5" customHeight="1">
       <c r="A139" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B139" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. L.,  (-)</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="5"/>
@@ -8643,21 +8664,21 @@
     </row>
     <row r="140" ht="22.5" customHeight="1">
       <c r="A140" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B140" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. A.,  (-)</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
       <c r="G140" s="9"/>
       <c r="H140" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="I140" s="7" t="s">
         <v>16</v>
@@ -8667,21 +8688,21 @@
     </row>
     <row r="141" ht="22.5" customHeight="1">
       <c r="A141" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B141" s="4" t="str">
         <f t="shared" si="1"/>
         <v>B. M.,  (-)</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D141" s="3"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
       <c r="G141" s="9"/>
       <c r="H141" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I141" s="7" t="s">
         <v>16</v>
@@ -8691,73 +8712,73 @@
     </row>
     <row r="142" ht="22.5" customHeight="1">
       <c r="A142" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B142" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. H.,  (-)</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="9"/>
       <c r="H142" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="I142" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K142" s="9"/>
     </row>
     <row r="143" ht="22.5" customHeight="1">
       <c r="A143" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B143" s="4" t="str">
         <f t="shared" si="1"/>
         <v>D. M.,  (-)</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D143" s="3"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
       <c r="G143" s="9"/>
       <c r="H143" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="I143" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="K143" s="9"/>
     </row>
     <row r="144" ht="22.5" customHeight="1">
       <c r="A144" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B144" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gottfrid,  (-)</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
       <c r="G144" s="9"/>
       <c r="H144" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="I144" s="7" t="s">
         <v>16</v>
@@ -8767,21 +8788,21 @@
     </row>
     <row r="145" ht="22.5" customHeight="1">
       <c r="A145" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B145" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jakob,  (-)</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D145" s="3"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
       <c r="G145" s="9"/>
       <c r="H145" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="I145" s="7" t="s">
         <v>16</v>
@@ -8791,21 +8812,21 @@
     </row>
     <row r="146" ht="22.5" customHeight="1">
       <c r="A146" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B146" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. Schw.,  (-)</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D146" s="3"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
       <c r="G146" s="9"/>
       <c r="H146" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="I146" s="7" t="s">
         <v>16</v>
@@ -8815,21 +8836,21 @@
     </row>
     <row r="147" ht="22.5" customHeight="1">
       <c r="A147" s="3" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B147" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. K.,  (-)</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
       <c r="G147" s="9"/>
       <c r="H147" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="I147" s="7" t="s">
         <v>16</v>
@@ -8839,14 +8860,14 @@
     </row>
     <row r="148" ht="22.5" customHeight="1">
       <c r="A148" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B148" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ott, Hans Heinrich (-)</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>69</v>
@@ -8863,14 +8884,14 @@
     </row>
     <row r="149" ht="22.5" customHeight="1">
       <c r="A149" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B149" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. W.,  (-)</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D149" s="3"/>
       <c r="E149" s="5"/>
@@ -8885,21 +8906,21 @@
     </row>
     <row r="150" ht="22.5" customHeight="1">
       <c r="A150" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B150" s="4" t="str">
         <f t="shared" si="1"/>
         <v>V. L.,  (-)</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
       <c r="G150" s="9"/>
       <c r="H150" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="I150" s="7" t="s">
         <v>16</v>
@@ -8909,14 +8930,14 @@
     </row>
     <row r="151" ht="22.5" customHeight="1">
       <c r="A151" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B151" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. Sch.,  (-)</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D151" s="3"/>
       <c r="E151" s="5"/>
@@ -8931,21 +8952,21 @@
     </row>
     <row r="152" ht="22.5" customHeight="1">
       <c r="A152" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B152" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. H.,  (-)</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
       <c r="G152" s="9"/>
       <c r="H152" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="I152" s="7" t="s">
         <v>16</v>
@@ -8955,14 +8976,14 @@
     </row>
     <row r="153" ht="22.5" customHeight="1">
       <c r="A153" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B153" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. H.,  (-)</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="5"/>
@@ -8973,55 +8994,55 @@
         <v>16</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K153" s="9"/>
     </row>
     <row r="154" ht="22.5" customHeight="1">
       <c r="A154" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B154" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. W.,  (-)</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="9"/>
       <c r="H154" s="3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="I154" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K154" s="9"/>
     </row>
     <row r="155" ht="22.5" customHeight="1">
       <c r="A155" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B155" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Koller, Elisabeth (-)</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
       <c r="G155" s="9"/>
       <c r="H155" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I155" s="7" t="s">
         <v>16</v>
@@ -9033,17 +9054,17 @@
     </row>
     <row r="156" ht="22.5" customHeight="1">
       <c r="A156" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B156" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lobwasser, Ambrosius (1515-1585)</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E156" s="5">
         <v>1515.0</v>
@@ -9052,10 +9073,10 @@
         <v>1585.0</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="I156" s="7" t="s">
         <v>16</v>
@@ -9065,22 +9086,22 @@
     </row>
     <row r="157" ht="22.5" customHeight="1">
       <c r="A157" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B157" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vollenweider, Jakob (-)</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E157" s="5"/>
       <c r="F157" s="5"/>
       <c r="G157" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H157" s="3"/>
       <c r="I157" s="7" t="s">
@@ -9091,7 +9112,7 @@
     </row>
     <row r="158" ht="22.5" customHeight="1">
       <c r="A158" s="3" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B158" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9101,7 +9122,7 @@
         <v>219</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E158" s="5">
         <v>1606.0</v>
@@ -9110,7 +9131,7 @@
         <v>1660.0</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>222</v>
@@ -9123,23 +9144,23 @@
     </row>
     <row r="159" ht="22.5" customHeight="1">
       <c r="A159" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B159" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Burkharten, Kuenraht (-)</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E159" s="5"/>
       <c r="F159" s="5"/>
       <c r="G159" s="9"/>
       <c r="H159" s="3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="I159" s="7" t="s">
         <v>16</v>
@@ -9149,14 +9170,14 @@
     </row>
     <row r="160" ht="22.5" customHeight="1">
       <c r="A160" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B160" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ardüser, Johann (1585-1665)</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>106</v>
@@ -9168,7 +9189,7 @@
         <v>1665.0</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H160" s="3"/>
       <c r="I160" s="7" t="s">
@@ -9179,25 +9200,25 @@
     </row>
     <row r="161" ht="22.5" customHeight="1">
       <c r="A161" s="3" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B161" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hegner, Diethelm  (-)</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
       <c r="G161" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="I161" s="7" t="s">
         <v>16</v>
@@ -9207,22 +9228,22 @@
     </row>
     <row r="162" ht="22.5" customHeight="1">
       <c r="A162" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B162" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Trigland, Jacobus (-)</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="E162" s="5"/>
       <c r="F162" s="5"/>
       <c r="G162" s="3" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H162" s="3"/>
       <c r="I162" s="7" t="s">
@@ -9233,17 +9254,17 @@
     </row>
     <row r="163" ht="22.5" customHeight="1">
       <c r="A163" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B163" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwinger, D. (-)</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E163" s="5"/>
       <c r="F163" s="5"/>
@@ -9257,14 +9278,14 @@
     </row>
     <row r="164" ht="22.5" customHeight="1">
       <c r="A164" s="3" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B164" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Genathen, Johann Jakob (-)</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>31</v>
@@ -9272,10 +9293,10 @@
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
       <c r="G164" s="3" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="I164" s="7" t="s">
         <v>16</v>
@@ -9285,7 +9306,7 @@
     </row>
     <row r="165" ht="22.5" customHeight="1">
       <c r="A165" s="3" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B165" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9311,27 +9332,27 @@
     </row>
     <row r="166" ht="22.5" customHeight="1">
       <c r="A166" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B166" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hess, Caspar (-1631)</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E166" s="5"/>
       <c r="F166" s="5">
         <v>1631.0</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="I166" s="7" t="s">
         <v>16</v>
@@ -9341,14 +9362,14 @@
     </row>
     <row r="167" ht="22.5" customHeight="1">
       <c r="A167" s="3" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B167" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wolfen, Hans Jakob (-)</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>215</v>
@@ -9365,22 +9386,22 @@
     </row>
     <row r="168" ht="22.5" customHeight="1">
       <c r="A168" s="3" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B168" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöri, Felix Christian (-)</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E168" s="15"/>
       <c r="F168" s="16"/>
       <c r="G168" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H168" s="3"/>
       <c r="I168" s="7" t="s">
@@ -9391,7 +9412,7 @@
     </row>
     <row r="169" ht="22.5" customHeight="1">
       <c r="A169" s="3" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B169" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9401,7 +9422,7 @@
         <v>12</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E169" s="15"/>
       <c r="F169" s="5">
@@ -9417,21 +9438,21 @@
     </row>
     <row r="170" ht="22.5" customHeight="1">
       <c r="A170" s="3" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B170" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther,  (-)</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D170" s="3"/>
       <c r="E170" s="15"/>
       <c r="F170" s="16"/>
       <c r="G170" s="9"/>
       <c r="H170" s="3" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="I170" s="7" t="s">
         <v>16</v>
@@ -9441,23 +9462,23 @@
     </row>
     <row r="171" ht="22.5" customHeight="1">
       <c r="A171" s="3" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B171" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Weiss, Caspar (-)</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E171" s="15"/>
       <c r="F171" s="16"/>
       <c r="G171" s="9"/>
       <c r="H171" s="17" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="I171" s="7" t="s">
         <v>16</v>
@@ -9467,7 +9488,7 @@
     </row>
     <row r="172" ht="22.5" customHeight="1">
       <c r="A172" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B172" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9481,7 +9502,7 @@
       <c r="F172" s="16"/>
       <c r="G172" s="9"/>
       <c r="H172" s="17" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="I172" s="7" t="s">
         <v>16</v>
@@ -9491,21 +9512,21 @@
     </row>
     <row r="173" ht="22.5" customHeight="1">
       <c r="A173" s="3" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B173" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bas,  (-)</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="15"/>
       <c r="F173" s="16"/>
       <c r="G173" s="9"/>
       <c r="H173" s="3" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="I173" s="18"/>
       <c r="J173" s="9"/>
@@ -9513,14 +9534,14 @@
     </row>
     <row r="174" ht="22.5" customHeight="1">
       <c r="A174" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B174" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H.H.J. Gw. s. A.Z.Fr.M.,  (-)</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="D174" s="3"/>
       <c r="E174" s="15"/>
@@ -9535,23 +9556,23 @@
     </row>
     <row r="175" ht="22.5" customHeight="1">
       <c r="A175" s="3" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B175" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hofm., Joh. (-)</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E175" s="15"/>
       <c r="F175" s="16"/>
       <c r="G175" s="9"/>
       <c r="H175" s="3" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="I175" s="7" t="s">
         <v>16</v>
@@ -9561,22 +9582,22 @@
     </row>
     <row r="176" ht="22.5" customHeight="1">
       <c r="A176" s="3" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B176" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Cyrene, Simon von (-)</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E176" s="15"/>
       <c r="F176" s="16"/>
       <c r="G176" s="3" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>245</v>
@@ -9589,20 +9610,20 @@
     </row>
     <row r="177" ht="22.5" customHeight="1">
       <c r="A177" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B177" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thomas,  (-)</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="15"/>
       <c r="F177" s="16"/>
       <c r="G177" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>319</v>
@@ -9615,23 +9636,23 @@
     </row>
     <row r="178" ht="22.5" customHeight="1">
       <c r="A178" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B178" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Phaeton,  (-)</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="15"/>
       <c r="F178" s="16"/>
       <c r="G178" s="3" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="I178" s="7" t="s">
         <v>227</v>
@@ -9641,14 +9662,14 @@
     </row>
     <row r="179" ht="22.5" customHeight="1">
       <c r="A179" s="3" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B179" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lukas,  (-)</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D179" s="3"/>
       <c r="E179" s="15"/>
@@ -9665,20 +9686,20 @@
     </row>
     <row r="180" ht="22.5" customHeight="1">
       <c r="A180" s="3" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B180" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pallas Athena,  (-)</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="15"/>
       <c r="F180" s="16"/>
       <c r="G180" s="3" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>227</v>
@@ -9691,23 +9712,23 @@
     </row>
     <row r="181" ht="22.5" customHeight="1">
       <c r="A181" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B181" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bacchus,  (-)</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D181" s="3"/>
       <c r="E181" s="15"/>
       <c r="F181" s="16"/>
       <c r="G181" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I181" s="7" t="s">
         <v>227</v>
@@ -9717,21 +9738,21 @@
     </row>
     <row r="182" ht="22.5" customHeight="1">
       <c r="A182" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B182" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Darius,  (-)</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="15"/>
       <c r="F182" s="16"/>
       <c r="G182" s="9"/>
       <c r="H182" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="I182" s="7" t="s">
         <v>16</v>
@@ -9741,21 +9762,21 @@
     </row>
     <row r="183" ht="22.5" customHeight="1">
       <c r="A183" s="3" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B183" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kyros,  (-)</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D183" s="3"/>
       <c r="E183" s="15"/>
       <c r="F183" s="16"/>
       <c r="G183" s="9"/>
       <c r="H183" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="I183" s="12"/>
       <c r="J183" s="9"/>
@@ -9763,25 +9784,25 @@
     </row>
     <row r="184" ht="22.5" customHeight="1">
       <c r="A184" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B184" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hippo, Augustinus von (-)</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="E184" s="15"/>
       <c r="F184" s="16"/>
       <c r="G184" s="3" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="I184" s="12"/>
       <c r="J184" s="9"/>
@@ -9789,20 +9810,20 @@
     </row>
     <row r="185" ht="22.5" customHeight="1">
       <c r="A185" s="3" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B185" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lazarus,  (-)</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D185" s="3"/>
       <c r="E185" s="15"/>
       <c r="F185" s="16"/>
       <c r="G185" s="3" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>245</v>
@@ -9815,20 +9836,20 @@
     </row>
     <row r="186" ht="22.5" customHeight="1">
       <c r="A186" s="3" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B186" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lot,  (-)</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="15"/>
       <c r="F186" s="16"/>
       <c r="G186" s="3" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>245</v>
@@ -9841,21 +9862,21 @@
     </row>
     <row r="187" ht="22.5" customHeight="1">
       <c r="A187" s="3" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B187" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hans Rudolf,  (-)</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D187" s="3"/>
       <c r="E187" s="15"/>
       <c r="F187" s="16"/>
       <c r="G187" s="9"/>
       <c r="H187" s="3" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="I187" s="7" t="s">
         <v>16</v>
@@ -9865,7 +9886,7 @@
     </row>
     <row r="188" ht="22.5" customHeight="1">
       <c r="A188" s="3" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B188" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9878,16 +9899,16 @@
         <v>13</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="F188" s="5">
         <v>1690.0</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="I188" s="7" t="s">
         <v>16</v>
@@ -9897,17 +9918,17 @@
     </row>
     <row r="189" ht="22.5" customHeight="1">
       <c r="A189" s="3" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B189" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bachofen, Johann Ulrich (1643-1700)</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E189" s="5">
         <v>1643.0</v>
@@ -9916,7 +9937,7 @@
         <v>1700.0</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>222</v>
@@ -9929,17 +9950,17 @@
     </row>
     <row r="190" ht="22.5" customHeight="1">
       <c r="A190" s="3" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B190" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grebel, Hans Konrad (1615-1674)</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="E190" s="5">
         <v>1615.0</v>
@@ -9948,57 +9969,57 @@
         <v>1674.0</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="I190" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K190" s="9"/>
     </row>
     <row r="191" ht="22.5" customHeight="1">
       <c r="A191" s="3" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B191" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gossweiler, Emerentia (-)</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E191" s="15"/>
       <c r="F191" s="16"/>
       <c r="G191" s="9"/>
       <c r="H191" s="3" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="I191" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J191" s="8" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K191" s="9"/>
     </row>
     <row r="192" ht="22.5" customHeight="1">
       <c r="A192" s="3" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B192" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lochmann, Heinrich (1613-1667)</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>37</v>
@@ -10010,29 +10031,29 @@
         <v>1667.0</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J192" s="8" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="K192" s="9"/>
     </row>
     <row r="193" ht="22.5" customHeight="1">
       <c r="A193" s="3" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B193" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Johann Jakob (1602-1668)</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>31</v>
@@ -10044,109 +10065,109 @@
         <v>1668.0</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J193" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K193" s="9"/>
     </row>
     <row r="194" ht="22.5" customHeight="1">
       <c r="A194" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B194" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orelli, Anna (-)</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E194" s="15"/>
       <c r="F194" s="16"/>
       <c r="G194" s="9"/>
       <c r="H194" s="3" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="I194" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J194" s="10" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K194" s="9"/>
     </row>
     <row r="195" ht="22.5" customHeight="1">
       <c r="A195" s="3" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B195" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. E. H.,  (-)</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="15"/>
       <c r="F195" s="16"/>
       <c r="G195" s="9"/>
       <c r="H195" s="3" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J195" s="20" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K195" s="9"/>
     </row>
     <row r="196" ht="22.5" customHeight="1">
       <c r="A196" s="3" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B196" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. H.,  (-)</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D196" s="3"/>
       <c r="E196" s="15"/>
       <c r="F196" s="16"/>
       <c r="G196" s="9"/>
       <c r="H196" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="I196" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J196" s="20" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K196" s="9"/>
     </row>
     <row r="197" ht="22.5" customHeight="1">
       <c r="A197" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B197" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grob, Hans Jakob (-)</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>215</v>
@@ -10155,19 +10176,19 @@
       <c r="F197" s="16"/>
       <c r="G197" s="9"/>
       <c r="H197" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="I197" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J197" s="8" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="K197" s="9"/>
     </row>
     <row r="198" ht="22.5" customHeight="1">
       <c r="A198" s="3" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B198" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10177,7 +10198,7 @@
         <v>68</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="E198" s="15"/>
       <c r="F198" s="16"/>
@@ -10187,23 +10208,23 @@
         <v>16</v>
       </c>
       <c r="J198" s="8" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="K198" s="9"/>
     </row>
     <row r="199" ht="22.5" customHeight="1">
       <c r="A199" s="3" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B199" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klingler, Kaspar (-)</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E199" s="15"/>
       <c r="F199" s="16"/>
@@ -10213,23 +10234,23 @@
         <v>16</v>
       </c>
       <c r="J199" s="8" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="K199" s="9"/>
     </row>
     <row r="200" ht="22.5" customHeight="1">
       <c r="A200" s="3" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B200" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöndli, Dorothea (-)</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E200" s="15"/>
       <c r="F200" s="16"/>
@@ -10239,23 +10260,23 @@
         <v>16</v>
       </c>
       <c r="J200" s="8" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="K200" s="9"/>
     </row>
     <row r="201" ht="22.5" customHeight="1">
       <c r="A201" s="3" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B201" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Hans Caspar (1617-1691)</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E201" s="5">
         <v>1617.0</v>
@@ -10264,32 +10285,32 @@
         <v>1691.0</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="K201" s="9"/>
     </row>
     <row r="202" ht="22.5" customHeight="1">
       <c r="A202" s="3" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B202" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Salomon (1580-1652)</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E202" s="5">
         <v>1580.0</v>
@@ -10298,60 +10319,60 @@
         <v>1652.0</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J202" s="8" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="K202" s="9"/>
     </row>
     <row r="203" ht="22.5" customHeight="1">
       <c r="A203" s="3" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B203" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis-Soglio, Maria Ursina von  (-)</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="E203" s="15"/>
       <c r="F203" s="16"/>
       <c r="G203" s="9"/>
       <c r="H203" s="3" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J203" s="8" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="K203" s="9"/>
     </row>
     <row r="204" ht="22.5" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B204" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Brügger, Andreas von (1588-1653)</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="E204" s="5">
         <v>1588.0</v>
@@ -10360,36 +10381,36 @@
         <v>1653.0</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I204" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J204" s="8" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="K204" s="9"/>
     </row>
     <row r="205" ht="22.5" customHeight="1">
       <c r="A205" s="3" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B205" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Anhorn,  (-)</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D205" s="3"/>
       <c r="E205" s="15"/>
       <c r="F205" s="16"/>
       <c r="G205" s="9"/>
       <c r="H205" s="3" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="I205" s="7" t="s">
         <v>16</v>
@@ -10399,14 +10420,14 @@
     </row>
     <row r="206" ht="22.5" customHeight="1">
       <c r="A206" s="3" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B206" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wilden, Abraham (-)</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>284</v>
@@ -10415,7 +10436,7 @@
       <c r="F206" s="16"/>
       <c r="G206" s="9"/>
       <c r="H206" s="3" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>16</v>
@@ -10425,23 +10446,23 @@
     </row>
     <row r="207" ht="22.5" customHeight="1">
       <c r="A207" s="3" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B207" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Groben, Jacob (evtl. Johannes) (-)</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="E207" s="15"/>
       <c r="F207" s="16"/>
       <c r="G207" s="9"/>
       <c r="H207" s="3" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>16</v>
@@ -10451,21 +10472,21 @@
     </row>
     <row r="208" ht="22.5" customHeight="1">
       <c r="A208" s="3" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B208" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ziegler,  (-)</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="15"/>
       <c r="F208" s="16"/>
       <c r="G208" s="9"/>
       <c r="H208" s="3" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="I208" s="7" t="s">
         <v>16</v>
@@ -10475,7 +10496,7 @@
     </row>
     <row r="209" ht="22.5" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B209" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10491,7 +10512,7 @@
       <c r="F209" s="16"/>
       <c r="G209" s="9"/>
       <c r="H209" s="3" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="I209" s="7" t="s">
         <v>16</v>
@@ -10501,21 +10522,21 @@
     </row>
     <row r="210" ht="22.5" customHeight="1">
       <c r="A210" s="3" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B210" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Oeri,  (-)</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="15"/>
       <c r="F210" s="16"/>
       <c r="G210" s="9"/>
       <c r="H210" s="3" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="I210" s="7" t="s">
         <v>16</v>
@@ -10525,21 +10546,21 @@
     </row>
     <row r="211" ht="22.5" customHeight="1">
       <c r="A211" s="3" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B211" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wittib,  (-)</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="15"/>
       <c r="F211" s="16"/>
       <c r="G211" s="9"/>
       <c r="H211" s="3" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="I211" s="12"/>
       <c r="J211" s="9"/>
@@ -10547,14 +10568,14 @@
     </row>
     <row r="212" ht="22.5" customHeight="1">
       <c r="A212" s="3" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B212" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Graf von Sultz,  (-)</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D212" s="3"/>
       <c r="E212" s="15"/>
@@ -10569,21 +10590,21 @@
     </row>
     <row r="213" ht="22.5" customHeight="1">
       <c r="A213" s="3" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B213" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Eglin,  (-)</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D213" s="3"/>
       <c r="E213" s="15"/>
       <c r="F213" s="16"/>
       <c r="G213" s="9"/>
       <c r="H213" s="3" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="I213" s="7" t="s">
         <v>16</v>
@@ -10593,14 +10614,14 @@
     </row>
     <row r="214" ht="22.5" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B214" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wildhans von Breitenlandenberg,  (-1444)</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="15"/>
@@ -10609,7 +10630,7 @@
       </c>
       <c r="G214" s="9"/>
       <c r="H214" s="3" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="I214" s="7" t="s">
         <v>16</v>
@@ -10619,14 +10640,14 @@
     </row>
     <row r="215" ht="22.5" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B215" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pfarrherr,  (-)</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="15"/>
@@ -10641,17 +10662,17 @@
     </row>
     <row r="216" ht="22.5" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B216" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid von Schwarzenhorn, Johann Rudolf (1590-1667)</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E216" s="5">
         <v>1590.0</v>
@@ -10660,29 +10681,29 @@
         <v>1667.0</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="I216" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J216" s="8" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="K216" s="9"/>
     </row>
     <row r="217" ht="22.5" customHeight="1">
       <c r="A217" s="3" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B217" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid, Felix (-1598)</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>88</v>
@@ -10693,26 +10714,26 @@
       </c>
       <c r="G217" s="9"/>
       <c r="H217" s="3" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="I217" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J217" s="8" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="K217" s="9"/>
     </row>
     <row r="218" ht="22.5" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B218" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hessen, Heinrich (-)</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>37</v>
@@ -10721,7 +10742,7 @@
       <c r="F218" s="16"/>
       <c r="G218" s="9"/>
       <c r="H218" s="3" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="I218" s="7" t="s">
         <v>16</v>
@@ -10731,17 +10752,17 @@
     </row>
     <row r="219" ht="22.5" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B219" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulr., H. (-)</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="E219" s="15"/>
       <c r="F219" s="16"/>
@@ -10757,7 +10778,7 @@
     </row>
     <row r="220" ht="22.5" customHeight="1">
       <c r="A220" s="3" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B220" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10767,13 +10788,13 @@
         <v>60</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E220" s="15"/>
       <c r="F220" s="16"/>
       <c r="G220" s="9"/>
       <c r="H220" s="3" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>16</v>
@@ -10783,7 +10804,7 @@
     </row>
     <row r="221" ht="22.5" customHeight="1">
       <c r="A221" s="3" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B221" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10797,7 +10818,7 @@
       <c r="F221" s="16"/>
       <c r="G221" s="9"/>
       <c r="H221" s="3" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="I221" s="7" t="s">
         <v>16</v>
@@ -10807,14 +10828,14 @@
     </row>
     <row r="222" ht="22.5" customHeight="1">
       <c r="A222" s="3" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B222" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Locher,  (-)</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="15"/>
@@ -10829,17 +10850,17 @@
     </row>
     <row r="223" ht="22.5" customHeight="1">
       <c r="A223" s="3" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B223" s="4" t="str">
         <f t="shared" si="1"/>
         <v>König, Caspar (-)</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E223" s="15"/>
       <c r="F223" s="16"/>
@@ -10851,7 +10872,7 @@
     </row>
     <row r="224" ht="22.5" customHeight="1">
       <c r="A224" s="3" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B224" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10873,7 +10894,7 @@
         <v>70</v>
       </c>
       <c r="H224" s="17" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="I224" s="7" t="s">
         <v>16</v>
@@ -10885,7 +10906,7 @@
     </row>
     <row r="225" ht="22.5" customHeight="1">
       <c r="A225" s="3" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B225" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10899,7 +10920,7 @@
       <c r="F225" s="16"/>
       <c r="G225" s="9"/>
       <c r="H225" s="3" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>16</v>
@@ -10909,17 +10930,17 @@
     </row>
     <row r="226" ht="22.5" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B226" s="4" t="str">
         <f t="shared" si="1"/>
         <v>O., Jacob U. (-)</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="E226" s="15"/>
       <c r="F226" s="16"/>
@@ -10935,21 +10956,21 @@
     </row>
     <row r="227" ht="22.5" customHeight="1">
       <c r="A227" s="3" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B227" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schneeberger,  (-)</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="15"/>
       <c r="F227" s="16"/>
       <c r="G227" s="9"/>
       <c r="H227" s="3" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="I227" s="7" t="s">
         <v>16</v>
@@ -10959,17 +10980,17 @@
     </row>
     <row r="228" ht="22.5" customHeight="1">
       <c r="A228" s="3" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B228" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwingli, Ulrich (1484-1531)</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E228" s="5">
         <v>1484.0</v>
@@ -10978,10 +10999,10 @@
         <v>1531.0</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="I228" s="7" t="s">
         <v>16</v>
@@ -10991,14 +11012,14 @@
     </row>
     <row r="229" ht="22.5" customHeight="1">
       <c r="A229" s="3" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B229" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bullinger, Heinrich (1504-1575)</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>37</v>
@@ -11010,10 +11031,10 @@
         <v>1575.0</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="I229" s="7" t="s">
         <v>16</v>
@@ -11023,17 +11044,17 @@
     </row>
     <row r="230" ht="22.5" customHeight="1">
       <c r="A230" s="3" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B230" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther, Rudolf (1519-1586)</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="E230" s="5">
         <v>1519.0</v>
@@ -11042,7 +11063,7 @@
         <v>1586.0</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="H230" s="3"/>
       <c r="I230" s="7" t="s">
@@ -11053,14 +11074,14 @@
     </row>
     <row r="231" ht="22.5" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B231" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Breitinger, Johann Jakob (1575-1645)</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>31</v>
@@ -11072,7 +11093,7 @@
         <v>1645.0</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H231" s="3"/>
       <c r="I231" s="7" t="s">
@@ -11083,17 +11104,17 @@
     </row>
     <row r="232" ht="22.5" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B232" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jrminger, Jacob (1588-1649)</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="E232" s="5">
         <v>1588.0</v>
@@ -11102,7 +11123,7 @@
         <v>1649.0</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="H232" s="3"/>
       <c r="I232" s="7" t="s">
@@ -11113,17 +11134,17 @@
     </row>
     <row r="233" ht="22.5" customHeight="1">
       <c r="A233" s="3" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B233" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fries, Jakob (-)</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E233" s="15"/>
       <c r="F233" s="16"/>
@@ -11137,25 +11158,25 @@
     </row>
     <row r="234" ht="22.5" customHeight="1">
       <c r="A234" s="3" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B234" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Geiger, Joh. Rud. (-)</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="E234" s="15"/>
       <c r="F234" s="16"/>
       <c r="G234" s="3" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="I234" s="7" t="s">
         <v>16</v>
@@ -11165,17 +11186,17 @@
     </row>
     <row r="235" ht="22.5" customHeight="1">
       <c r="A235" s="3" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B235" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maurer, C. (-)</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="E235" s="15"/>
       <c r="F235" s="16"/>
@@ -11189,17 +11210,17 @@
     </row>
     <row r="236" ht="22.5" customHeight="1">
       <c r="A236" s="3" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B236" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Suter, C. (-)</v>
       </c>
       <c r="C236" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="D236" s="3" t="s">
         <v>860</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>858</v>
       </c>
       <c r="E236" s="15"/>
       <c r="F236" s="16"/>
@@ -11213,17 +11234,17 @@
     </row>
     <row r="237" ht="22.5" customHeight="1">
       <c r="A237" s="3" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B237" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Holzhalb, Joh. (-)</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="E237" s="15"/>
       <c r="F237" s="16"/>
@@ -11239,17 +11260,17 @@
     </row>
     <row r="238" ht="22.5" customHeight="1">
       <c r="A238" s="3" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B238" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wirtz, H. C. (-)</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="E238" s="15"/>
       <c r="F238" s="16"/>
@@ -11263,22 +11284,22 @@
     </row>
     <row r="239" ht="22.5" customHeight="1">
       <c r="A239" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B239" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser, Caspar (-)</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E239" s="15"/>
       <c r="F239" s="16"/>
       <c r="G239" s="3" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="H239" s="3"/>
       <c r="I239" s="7" t="s">
@@ -11289,22 +11310,22 @@
     </row>
     <row r="240" ht="22.5" customHeight="1">
       <c r="A240" s="3" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B240" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hospinianus, R. (-)</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="E240" s="15"/>
       <c r="F240" s="16"/>
       <c r="G240" s="3" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="H240" s="3"/>
       <c r="I240" s="7" t="s">
@@ -11315,17 +11336,17 @@
     </row>
     <row r="241" ht="22.5" customHeight="1">
       <c r="A241" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B241" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Erni, H. (-)</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="E241" s="15"/>
       <c r="F241" s="16"/>
@@ -11339,17 +11360,17 @@
     </row>
     <row r="242" ht="22.5" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B242" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Tomman, P. (-)</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="E242" s="15"/>
       <c r="F242" s="16"/>
@@ -11363,17 +11384,17 @@
     </row>
     <row r="243" ht="22.5" customHeight="1">
       <c r="A243" s="3" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B243" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Stukki, R. (-)</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="E243" s="15"/>
       <c r="F243" s="16"/>
@@ -11387,17 +11408,17 @@
     </row>
     <row r="244" ht="22.5" customHeight="1">
       <c r="A244" s="3" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B244" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zeller, H. (-)</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="E244" s="15"/>
       <c r="F244" s="16"/>
@@ -11411,7 +11432,7 @@
     </row>
     <row r="245" ht="22.5" customHeight="1">
       <c r="A245" s="3" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B245" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11419,13 +11440,13 @@
       </c>
       <c r="C245" s="6"/>
       <c r="D245" s="3" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="E245" s="15"/>
       <c r="F245" s="16"/>
       <c r="G245" s="9"/>
       <c r="H245" s="3" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="I245" s="7" t="s">
         <v>16</v>
@@ -11435,21 +11456,21 @@
     </row>
     <row r="246" ht="22.5" customHeight="1">
       <c r="A246" s="3" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B246" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fr. Doctorin,  (-)</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="15"/>
       <c r="F246" s="16"/>
       <c r="G246" s="9"/>
       <c r="H246" s="3" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="I246" s="7" t="s">
         <v>16</v>
@@ -11459,17 +11480,17 @@
     </row>
     <row r="247" ht="22.5" customHeight="1">
       <c r="A247" s="3" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B247" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kusen, Jost von (1570-1630)</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="E247" s="5">
         <v>1570.0</v>
@@ -11478,10 +11499,10 @@
         <v>1630.0</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="I247" s="7" t="s">
         <v>16</v>
@@ -11491,14 +11512,14 @@
     </row>
     <row r="248" ht="22.5" customHeight="1">
       <c r="A248" s="3" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B248" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Heinrich (-)</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>37</v>
@@ -11507,7 +11528,7 @@
       <c r="F248" s="16"/>
       <c r="G248" s="9"/>
       <c r="H248" s="3" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="I248" s="7" t="s">
         <v>16</v>
@@ -11517,21 +11538,21 @@
     </row>
     <row r="249" ht="22.5" customHeight="1">
       <c r="A249" s="3" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B249" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gessner,  (-)</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="15"/>
       <c r="F249" s="16"/>
       <c r="G249" s="9"/>
       <c r="H249" s="3" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="I249" s="7" t="s">
         <v>16</v>
@@ -11541,17 +11562,17 @@
     </row>
     <row r="250" ht="22.5" customHeight="1">
       <c r="A250" s="3" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B250" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wöllwein, Johann Anton (1616-1659)</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="E250" s="5">
         <v>1616.0</v>
@@ -11560,10 +11581,10 @@
         <v>1659.0</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="I250" s="7" t="s">
         <v>16</v>
@@ -11573,42 +11594,42 @@
     </row>
     <row r="251" ht="22.5" customHeight="1">
       <c r="A251" s="3" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B251" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Anna (-)</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E251" s="15"/>
       <c r="F251" s="16"/>
       <c r="G251" s="9"/>
       <c r="H251" s="3" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="I251" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="K251" s="9"/>
     </row>
     <row r="252" ht="22.5" customHeight="1">
       <c r="A252" s="3" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B252" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. J. R. S.,  (-)</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="D252" s="3"/>
       <c r="E252" s="15"/>
@@ -11621,17 +11642,17 @@
     </row>
     <row r="253" ht="22.5" customHeight="1">
       <c r="A253" s="3" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B253" s="4" t="str">
         <f t="shared" si="1"/>
         <v>de Ruyter, Michiel (1607-1676)</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="E253" s="5">
         <v>1607.0</v>
@@ -11640,10 +11661,10 @@
         <v>1676.0</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="I253" s="7" t="s">
         <v>16</v>
@@ -11653,21 +11674,21 @@
     </row>
     <row r="254" ht="22.5" customHeight="1">
       <c r="A254" s="3" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B254" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Frau Oberstin,  (-)</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="15"/>
       <c r="F254" s="16"/>
       <c r="G254" s="9"/>
       <c r="H254" s="3" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="I254" s="7" t="s">
         <v>16</v>
@@ -11677,23 +11698,23 @@
     </row>
     <row r="255" ht="22.5" customHeight="1">
       <c r="A255" s="3" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B255" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vulcanus,  (-)</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="15"/>
       <c r="F255" s="16"/>
       <c r="G255" s="3" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="I255" s="7" t="s">
         <v>227</v>
@@ -11703,23 +11724,23 @@
     </row>
     <row r="256" ht="22.5" customHeight="1">
       <c r="A256" s="3" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B256" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esau,  (-)</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="15"/>
       <c r="F256" s="16"/>
       <c r="G256" s="3" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="I256" s="7" t="s">
         <v>245</v>
@@ -11729,23 +11750,23 @@
     </row>
     <row r="257" ht="22.5" customHeight="1">
       <c r="A257" s="3" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B257" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Danaos,  (-)</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="15"/>
       <c r="F257" s="16"/>
       <c r="G257" s="3" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="I257" s="7" t="s">
         <v>227</v>
@@ -11755,20 +11776,20 @@
     </row>
     <row r="258" ht="22.5" customHeight="1">
       <c r="A258" s="3" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B258" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Medusa,  (-)</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="15"/>
       <c r="F258" s="16"/>
       <c r="G258" s="3" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>227</v>
@@ -11781,20 +11802,20 @@
     </row>
     <row r="259" ht="22.5" customHeight="1">
       <c r="A259" s="3" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B259" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pluton,  (-)</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="15"/>
       <c r="F259" s="16"/>
       <c r="G259" s="3" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>227</v>
@@ -11807,20 +11828,20 @@
     </row>
     <row r="260" ht="22.5" customHeight="1">
       <c r="A260" s="3" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B260" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mercur,  (-)</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="15"/>
       <c r="F260" s="16"/>
       <c r="G260" s="3" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>227</v>
@@ -11833,20 +11854,20 @@
     </row>
     <row r="261" ht="22.5" customHeight="1">
       <c r="A261" s="3" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B261" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Perseus,  (-)</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="15"/>
       <c r="F261" s="16"/>
       <c r="G261" s="3" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>227</v>
@@ -11859,23 +11880,23 @@
     </row>
     <row r="262" ht="22.5" customHeight="1">
       <c r="A262" s="3" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B262" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Atropos,  (-)</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="15"/>
       <c r="F262" s="16"/>
       <c r="G262" s="3" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="I262" s="7" t="s">
         <v>227</v>
@@ -11885,23 +11906,23 @@
     </row>
     <row r="263" ht="22.5" customHeight="1">
       <c r="A263" s="3" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B263" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Barbara von Nikomedien,  (-)</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="15"/>
       <c r="F263" s="16"/>
       <c r="G263" s="3" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="H263" s="3" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="I263" s="7" t="s">
         <v>245</v>
@@ -11911,7 +11932,7 @@
     </row>
     <row r="264" ht="22.5" customHeight="1">
       <c r="A264" s="3" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B264" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11919,13 +11940,13 @@
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="3" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="E264" s="15"/>
       <c r="F264" s="16"/>
       <c r="G264" s="9"/>
       <c r="H264" s="3" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="I264" s="12"/>
       <c r="J264" s="9"/>
@@ -11933,7 +11954,7 @@
     </row>
     <row r="265" ht="22.5" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B265" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11947,7 +11968,7 @@
       <c r="F265" s="16"/>
       <c r="G265" s="9"/>
       <c r="H265" s="3" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="I265" s="12"/>
       <c r="J265" s="9"/>
@@ -11955,21 +11976,21 @@
     </row>
     <row r="266" ht="22.5" customHeight="1">
       <c r="A266" s="3" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B266" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Karl,  (-)</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="15"/>
       <c r="F266" s="16"/>
       <c r="G266" s="9"/>
       <c r="H266" s="3" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="I266" s="7" t="s">
         <v>16</v>
@@ -11979,21 +12000,21 @@
     </row>
     <row r="267" ht="22.5" customHeight="1">
       <c r="A267" s="3" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B267" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Duraeum,  (-)</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="15"/>
       <c r="F267" s="16"/>
       <c r="G267" s="9"/>
       <c r="H267" s="3" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="I267" s="12"/>
       <c r="J267" s="9"/>
@@ -12001,17 +12022,17 @@
     </row>
     <row r="268" ht="22.5" customHeight="1">
       <c r="A268" s="3" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B268" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zesen, Philipp von (1619-1689)</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="E268" s="5">
         <v>1619.0</v>
@@ -12020,7 +12041,7 @@
         <v>1689.0</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="H268" s="3"/>
       <c r="I268" s="7" t="s">
@@ -12031,23 +12052,23 @@
     </row>
     <row r="269" ht="22.5" customHeight="1">
       <c r="A269" s="3" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B269" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lucretia,  (-)</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="D269" s="3"/>
       <c r="E269" s="15"/>
       <c r="F269" s="16"/>
       <c r="G269" s="3" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="I269" s="7" t="s">
         <v>227</v>
@@ -12057,23 +12078,23 @@
     </row>
     <row r="270" ht="22.5" customHeight="1">
       <c r="A270" s="3" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B270" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ovid,  (-)</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="15"/>
       <c r="F270" s="16"/>
       <c r="G270" s="3" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="H270" s="3" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="I270" s="7" t="s">
         <v>16</v>
@@ -12083,17 +12104,17 @@
     </row>
     <row r="271" ht="22.5" customHeight="1">
       <c r="A271" s="3" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B271" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schweizer, Johann Caspar (1619-1688)</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="E271" s="5">
         <v>1619.0</v>
@@ -12102,29 +12123,29 @@
         <v>83</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="H271" s="3" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="I271" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J271" s="8" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="K271" s="9"/>
     </row>
     <row r="272" ht="22.5" customHeight="1">
       <c r="A272" s="3" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B272" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Herder, Johann Heinrich (-)</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>43</v>
@@ -12139,7 +12160,7 @@
     </row>
     <row r="273" ht="22.5" customHeight="1">
       <c r="A273" s="3" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B273" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12157,7 +12178,7 @@
     </row>
     <row r="274" ht="22.5" customHeight="1">
       <c r="A274" s="3" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B274" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12175,7 +12196,7 @@
     </row>
     <row r="275" ht="22.5" customHeight="1">
       <c r="A275" s="3" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B275" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12193,7 +12214,7 @@
     </row>
     <row r="276" ht="22.5" customHeight="1">
       <c r="A276" s="3" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B276" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12211,7 +12232,7 @@
     </row>
     <row r="277" ht="22.5" customHeight="1">
       <c r="A277" s="3" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B277" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12229,7 +12250,7 @@
     </row>
     <row r="278" ht="22.5" customHeight="1">
       <c r="A278" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B278" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12247,7 +12268,7 @@
     </row>
     <row r="279" ht="22.5" customHeight="1">
       <c r="A279" s="3" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B279" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12265,7 +12286,7 @@
     </row>
     <row r="280" ht="22.5" customHeight="1">
       <c r="A280" s="3" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B280" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12369,16 +12390,16 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -12389,179 +12410,179 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B2" s="21" t="str">
         <f t="shared" ref="B2:B102" si="1">CONCATENATE(C2)</f>
         <v>Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="7" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B3" s="21" t="str">
         <f t="shared" si="1"/>
         <v>Basel</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="7" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B4" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Eidgenossenschaft</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="E4" s="18"/>
       <c r="F4" s="3" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B5" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Limmat</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="7" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B6" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Weinfelden</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="7" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B7" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Main</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="D7" s="23"/>
       <c r="E7" s="7" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B8" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Zürichsee</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D8" s="23"/>
       <c r="E8" s="7" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B9" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Thalwil</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="D9" s="23"/>
       <c r="E9" s="12"/>
       <c r="F9" s="3" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B10" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Bern</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="7" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B11" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Gottstatt</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="D11" s="23"/>
       <c r="E11" s="12"/>
@@ -12569,48 +12590,48 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B12" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Thorberg</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="12"/>
       <c r="F12" s="3" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B13" s="22" t="str">
         <f t="shared" si="1"/>
         <v>London</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D13" s="23"/>
       <c r="E13" s="7" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B14" s="22" t="str">
         <f t="shared" si="1"/>
         <v>England</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="D14" s="23"/>
       <c r="E14" s="12"/>
@@ -12618,52 +12639,52 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B15" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Bethlehem</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="7" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B16" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Parnass </v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="7" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B17" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Traubenberg</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="D17" s="23"/>
       <c r="E17" s="12"/>
@@ -12671,50 +12692,50 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="B18" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Babylon</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="7" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B19" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Canaan</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="12"/>
       <c r="F19" s="3" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B20" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Ägypten</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="12"/>
@@ -12722,158 +12743,158 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B21" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Hermon</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="7" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B22" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Jerusalem</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B23" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Jordan</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="D23" s="23"/>
       <c r="E23" s="7" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B24" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Rotes Meer</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="7" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F24" s="9"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B25" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Juda</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D25" s="23"/>
       <c r="E25" s="12"/>
       <c r="F25" s="3" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B26" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Moab</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D26" s="23"/>
       <c r="E26" s="12"/>
       <c r="F26" s="3" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B27" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Ammon</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="D27" s="23"/>
       <c r="E27" s="12"/>
       <c r="F27" s="3" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B28" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Zion</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="D28" s="23"/>
       <c r="E28" s="7" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B29" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Assur</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D29" s="23"/>
       <c r="E29" s="12"/>
@@ -12881,101 +12902,101 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B30" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Israel</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D30" s="23"/>
       <c r="E30" s="12"/>
       <c r="F30" s="3" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B31" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Nazaret</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="D31" s="23"/>
       <c r="E31" s="7" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B32" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Rom</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="12"/>
       <c r="F32" s="3" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B33" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Samaria</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="12"/>
       <c r="F33" s="3" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="B34" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Kedronbach</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="12"/>
       <c r="F34" s="3" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B35" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Garten von Getsemani</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="D35" s="23"/>
       <c r="E35" s="12"/>
@@ -12983,14 +13004,14 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B36" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Urdorf</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="D36" s="23"/>
       <c r="E36" s="12"/>
@@ -12998,14 +13019,14 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B37" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Geiren-Rein</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="12"/>
@@ -13013,14 +13034,14 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B38" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Aeügst</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="D38" s="23"/>
       <c r="E38" s="12"/>
@@ -13028,14 +13049,14 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B39" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Riedt</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="D39" s="23"/>
       <c r="E39" s="12"/>
@@ -13043,14 +13064,14 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B40" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Europa</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="D40" s="23"/>
       <c r="E40" s="12"/>
@@ -13058,48 +13079,48 @@
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B41" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Osir</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="D41" s="23"/>
       <c r="E41" s="12"/>
       <c r="F41" s="3" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B42" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Basadingen</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="D42" s="23"/>
       <c r="E42" s="12"/>
       <c r="F42" s="3" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B43" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Diessenhofen</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="D43" s="23"/>
       <c r="E43" s="12"/>
@@ -13107,50 +13128,50 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B44" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Rhein</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="D44" s="23"/>
       <c r="E44" s="7" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B45" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Arabisches Reich</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="D45" s="23"/>
       <c r="E45" s="12"/>
       <c r="F45" s="3" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B46" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Libanon</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="D46" s="23"/>
       <c r="E46" s="12"/>
@@ -13158,101 +13179,101 @@
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B47" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Emmaus</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D47" s="23"/>
       <c r="E47" s="12"/>
       <c r="F47" s="3" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B48" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Helikon</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="D48" s="23"/>
       <c r="E48" s="12"/>
       <c r="F48" s="3" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B49" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Pindos</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="D49" s="23"/>
       <c r="E49" s="12"/>
       <c r="F49" s="3" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B50" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Neckar</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="D50" s="23"/>
       <c r="E50" s="7" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B51" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Kurpfalz</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="D51" s="23"/>
       <c r="E51" s="12"/>
       <c r="F51" s="3" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B52" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Eglisau</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D52" s="23"/>
       <c r="E52" s="12"/>
@@ -13260,14 +13281,14 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B53" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Altenklingen</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="D53" s="23"/>
       <c r="E53" s="12"/>
@@ -13275,14 +13296,14 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="B54" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Altorff</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="D54" s="23"/>
       <c r="E54" s="12"/>
@@ -13290,31 +13311,31 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B55" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Glarus</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D55" s="23"/>
       <c r="E55" s="12"/>
       <c r="F55" s="3" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B56" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Bergerkirche</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D56" s="23"/>
       <c r="E56" s="12"/>
@@ -13322,31 +13343,31 @@
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="B57" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Sodom</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D57" s="23"/>
       <c r="E57" s="12"/>
       <c r="F57" s="3" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B58" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Haus zur Sonnenblume</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="D58" s="23"/>
       <c r="E58" s="12"/>
@@ -13354,31 +13375,31 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B59" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Thurn/ genennt von Geissen</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D59" s="23"/>
       <c r="E59" s="12"/>
       <c r="F59" s="3" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B60" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Constantinopel</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D60" s="23"/>
       <c r="E60" s="12"/>
@@ -13386,118 +13407,118 @@
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B61" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Stein am Rhein</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D61" s="23"/>
       <c r="E61" s="12"/>
       <c r="F61" s="3" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B62" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Marburg</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="D62" s="23"/>
       <c r="E62" s="12"/>
       <c r="F62" s="3" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B63" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Elbląg</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="E63" s="12"/>
       <c r="F63" s="3" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="B64" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Preußen</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="D64" s="23"/>
       <c r="E64" s="12"/>
       <c r="F64" s="3" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="B65" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Bad Baden</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="D65" s="23"/>
       <c r="E65" s="12"/>
       <c r="F65" s="3" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="B66" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Bad Schinznach</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="D66" s="23"/>
       <c r="E66" s="12"/>
       <c r="F66" s="3" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="B67" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Gyrenbad</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D67" s="23"/>
       <c r="E67" s="12"/>
@@ -13505,48 +13526,48 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="B68" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Wängibad</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D68" s="23"/>
       <c r="E68" s="12"/>
       <c r="F68" s="8" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B69" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Aeugst</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="D69" s="23"/>
       <c r="E69" s="12"/>
       <c r="F69" s="3" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="B70" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Bassersdorf</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D70" s="23"/>
       <c r="E70" s="12"/>
@@ -13554,14 +13575,14 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="B71" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Hauptwil</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="D71" s="23"/>
       <c r="E71" s="12"/>
@@ -13569,14 +13590,14 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B72" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Schaffhausen</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="D72" s="23"/>
       <c r="E72" s="12"/>
@@ -13584,65 +13605,65 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="B73" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Wädenswil</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D73" s="23"/>
       <c r="E73" s="12"/>
       <c r="F73" s="3" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B74" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Freie Ämter</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="D74" s="23"/>
       <c r="E74" s="12"/>
       <c r="F74" s="3" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="B75" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Grüningen</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="D75" s="23"/>
       <c r="E75" s="12"/>
       <c r="F75" s="3" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="B76" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Kefikon</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="D76" s="23"/>
       <c r="E76" s="12"/>
@@ -13650,14 +13671,14 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="B77" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Maienfeld</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="D77" s="23"/>
       <c r="E77" s="12"/>
@@ -13665,14 +13686,14 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="B78" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Greifensee (Schloss)</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="D78" s="23"/>
       <c r="E78" s="12"/>
@@ -13680,31 +13701,31 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="B79" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Lindenhof (Zürich)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D79" s="23"/>
       <c r="E79" s="12"/>
       <c r="F79" s="3" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="B80" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Galg-Brunnen (Zürich)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="D80" s="23"/>
       <c r="E80" s="12"/>
@@ -13712,14 +13733,14 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="B81" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Altes Kornhaus (Zürich)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="D81" s="23"/>
       <c r="E81" s="12"/>
@@ -13727,14 +13748,14 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="B82" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Sparrenberg (Zürich)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="D82" s="23"/>
       <c r="E82" s="12"/>
@@ -13742,14 +13763,14 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="B83" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Thurgau</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D83" s="23"/>
       <c r="E83" s="12"/>
@@ -13757,14 +13778,14 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B84" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Niederlande</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="D84" s="23"/>
       <c r="E84" s="12"/>
@@ -13772,31 +13793,31 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="B85" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Holland</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="D85" s="23"/>
       <c r="E85" s="12"/>
       <c r="F85" s="3" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="B86" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Wigoltingen</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="D86" s="23"/>
       <c r="E86" s="12"/>
@@ -13804,31 +13825,31 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="B87" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Kastalia</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="D87" s="23"/>
       <c r="E87" s="12"/>
       <c r="F87" s="3" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B88" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Legerberg</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="D88" s="23"/>
       <c r="E88" s="12"/>
@@ -13836,48 +13857,48 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="B89" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Texel</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="D89" s="23"/>
       <c r="E89" s="12"/>
       <c r="F89" s="3" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B90" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Vlie</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="D90" s="23"/>
       <c r="E90" s="12"/>
       <c r="F90" s="3" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="B91" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Indien</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D91" s="23"/>
       <c r="E91" s="12"/>
@@ -13885,14 +13906,14 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="B92" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Wien</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="D92" s="23"/>
       <c r="E92" s="12"/>
@@ -13900,14 +13921,14 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="B93" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Deutschland</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="D93" s="23"/>
       <c r="E93" s="12"/>
@@ -13915,58 +13936,58 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="B94" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Ölberg</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D94" s="23"/>
       <c r="E94" s="7" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="F94" s="3"/>
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="B95" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Dietikon</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D95" s="23"/>
       <c r="E95" s="12"/>
       <c r="F95" s="3" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="B96" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Winterthur</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D96" s="23"/>
       <c r="E96" s="7" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="F96" s="3"/>
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B97" s="22" t="str">
         <f t="shared" si="1"/>
@@ -13979,7 +14000,7 @@
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B98" s="22" t="str">
         <f t="shared" si="1"/>
@@ -13992,7 +14013,7 @@
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="B99" s="22" t="str">
         <f t="shared" si="1"/>
@@ -14005,7 +14026,7 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B100" s="22" t="str">
         <f t="shared" si="1"/>
@@ -14018,7 +14039,7 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B101" s="22" t="str">
         <f t="shared" si="1"/>
@@ -14077,25 +14098,25 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
@@ -14106,75 +14127,75 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="B2" s="24" t="str">
         <f t="shared" ref="B2:B30" si="1">CONCATENATE(C2)</f>
         <v>Teutsche Gedichte</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="I2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="B3" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Die Krafft der Gottseligkeit</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="B4" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Buch von Festen</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5"/>
@@ -14184,23 +14205,23 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B5" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Der Psalter dess Königlichen Propheten Dauids/ Jn deutsche reymen verstendiglich vnd deutlich gebracht/ mit vorgehender anzeigung der reymen weise/ auch eines jeden Psalmes Jnhalt</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="12"/>
@@ -14208,43 +14229,43 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="B6" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Hundert christliche Fäst-Predigen</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="B7" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Lehr- und trostreiche Predigen vom verlohrnen Sohn</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="E7" s="9"/>
       <c r="F7" s="23"/>
@@ -14254,17 +14275,17 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="B8" s="24" t="str">
         <f t="shared" si="1"/>
         <v>verteütschte Rueh- oder Fridens-uebung</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="23"/>
@@ -14274,17 +14295,17 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="B9" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Nähefelser-Fahrt-Predigen</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="23"/>
@@ -14294,17 +14315,17 @@
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="B10" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kinder-lehr</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="E10" s="9"/>
       <c r="F10" s="23"/>
@@ -14314,17 +14335,17 @@
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="B11" s="24" t="str">
         <f t="shared" si="1"/>
         <v>neüaußgangenes Buech vom Vestungsbau</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="23"/>
@@ -14334,14 +14355,14 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="B12" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Buech der Freunden Stammen</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="D12" s="23"/>
       <c r="E12" s="9"/>
@@ -14352,17 +14373,17 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="B13" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Christen-spiegel</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="23"/>
@@ -14372,14 +14393,14 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="B14" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Viergeticht</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="D14" s="23"/>
       <c r="E14" s="9"/>
@@ -14390,14 +14411,14 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="B15" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Regentenspiegel</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="9"/>
@@ -14408,18 +14429,18 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="B16" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Türckischer Jammerspiegel</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="F16" s="23"/>
       <c r="G16" s="9"/>
@@ -14428,17 +14449,17 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="B17" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Leitungs-faden</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="23"/>
@@ -14448,17 +14469,17 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="B18" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Buch von der Seelen-angſt Chriſti</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="23"/>
@@ -14468,17 +14489,17 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="B19" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Verſuchungs-gabe</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="23"/>
@@ -14488,14 +14509,14 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="B20" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kriegsbüchlin</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="9"/>
@@ -14506,14 +14527,14 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="B21" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Buch der Psalmen</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="9"/>
@@ -14524,89 +14545,89 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="B22" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Sterbensspiegel/ das ist sonnenklare Vorstellung menschlicher Nichtigkeit durch alle Staend und Geschlechter</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="9"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="B23" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Warhaffte/ vnd in Gottes Wort wol gegründte Widerlegung Des newlich im Truck außgegangnen ohn-Catholischen Gesprächs von Religion oder Glaubens sachen/ geneñt der Augenspiegel</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>988</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>1306</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>1307</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>1308</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>986</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>1304</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="25" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="B24" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Augspiegels Wahrer Religion Erster Theil</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="25" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="B25" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14622,7 +14643,7 @@
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="B26" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14638,7 +14659,7 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="B27" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14654,7 +14675,7 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="B28" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14670,7 +14691,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="B29" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14686,7 +14707,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="B30" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14735,19 +14756,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -14755,69 +14776,69 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="B2" s="24" t="str">
         <f t="shared" ref="B2:B24" si="1">CONCATENATE(C2)</f>
         <v>Rat Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="D2" s="23"/>
       <c r="E2" s="26" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="B3" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Fruchtbringende Gesellschaft</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="B4" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Deutschgesinnte Genossenschaft (Lilien-Zunft)</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="B5" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Parthenicum</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="12"/>
@@ -14825,105 +14846,105 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="B6" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Carolinum Zürich</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="3" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="B7" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Sanhedrin</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="12"/>
       <c r="F7" s="3" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="B8" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Stadtbibliothek Zürich</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="12"/>
       <c r="F8" s="3" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="B9" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Grossmünster</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="E9" s="12"/>
       <c r="F9" s="3" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B10" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Fraumünster Zürich</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="3" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B11" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Hohe Schule Marburg</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="12"/>
@@ -14931,24 +14952,24 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="B12" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kartäuser</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="12"/>
       <c r="F12" s="3" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B13" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14961,7 +14982,7 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B14" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14974,7 +14995,7 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="B15" s="24" t="str">
         <f t="shared" si="1"/>
@@ -14987,7 +15008,7 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B16" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15000,7 +15021,7 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B17" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15013,7 +15034,7 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B18" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15026,7 +15047,7 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="B19" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15039,7 +15060,7 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="B20" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15052,7 +15073,7 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="B21" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15065,7 +15086,7 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="B22" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15128,19 +15149,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -15148,26 +15169,26 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="B2" s="21" t="str">
         <f t="shared" ref="B2:B8" si="1">CONCATENATE(C2)</f>
         <v>Runs</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="B3" s="21" t="str">
         <f t="shared" si="1"/>
@@ -15180,7 +15201,7 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="B4" s="21" t="str">
         <f t="shared" si="1"/>
@@ -15193,7 +15214,7 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="B5" s="21" t="str">
         <f t="shared" si="1"/>
@@ -15206,7 +15227,7 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B6" s="21" t="str">
         <f t="shared" si="1"/>
@@ -15219,7 +15240,7 @@
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="B7" s="21" t="str">
         <f t="shared" si="1"/>
@@ -15232,7 +15253,7 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="B8" s="21" t="str">
         <f t="shared" si="1"/>

--- a/gsheet/xlsx/entities.xlsx
+++ b/gsheet/xlsx/entities.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1858" uniqueCount="1428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="1436">
   <si>
     <t>Person-ID</t>
   </si>
@@ -1965,7 +1965,7 @@
     <t>129987409</t>
   </si>
   <si>
-    <t>Vogt zu Altenklingen</t>
+    <t>Übersetzer, Vogt zu Altenklingen</t>
   </si>
   <si>
     <t>person_167</t>
@@ -1977,7 +1977,10 @@
     <t>Jacobus</t>
   </si>
   <si>
-    <t>evtl. 122785703</t>
+    <t>122785703</t>
+  </si>
+  <si>
+    <t>Niederländischer reformierter Theologe</t>
   </si>
   <si>
     <t>person_168</t>
@@ -2064,7 +2067,7 @@
     <t>person_177</t>
   </si>
   <si>
-    <t>evtl. einer der Müller oben</t>
+    <t>das ist Georg Müller</t>
   </si>
   <si>
     <t>person_178</t>
@@ -3254,6 +3257,9 @@
     <t>England</t>
   </si>
   <si>
+    <t>Land</t>
+  </si>
+  <si>
     <t>place_014</t>
   </si>
   <si>
@@ -3861,6 +3867,9 @@
   </si>
   <si>
     <t>Dietikon</t>
+  </si>
+  <si>
+    <t>Politische Gemeinde</t>
   </si>
   <si>
     <t>Politische Gemeinde im Kanton Zürich</t>
@@ -4236,6 +4245,21 @@
   </si>
   <si>
     <t>work_024</t>
+  </si>
+  <si>
+    <t>De kracht der Godsaligheyt</t>
+  </si>
+  <si>
+    <t>Trigland, Jacobus</t>
+  </si>
+  <si>
+    <t>1631</t>
+  </si>
+  <si>
+    <t>Amsterdam</t>
+  </si>
+  <si>
+    <t>Marten Jansz Brandt</t>
   </si>
   <si>
     <t>work_025</t>
@@ -4574,6 +4598,9 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -4581,9 +4608,6 @@
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -9433,7 +9457,7 @@
       </c>
       <c r="B162" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Trigland, Jacobus (-)</v>
+        <v>Trigland, Jacobus (1583-1654)</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>627</v>
@@ -9441,12 +9465,18 @@
       <c r="D162" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="E162" s="5"/>
-      <c r="F162" s="5"/>
+      <c r="E162" s="16">
+        <v>1583.0</v>
+      </c>
+      <c r="F162" s="16">
+        <v>1654.0</v>
+      </c>
       <c r="G162" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="H162" s="3"/>
+      <c r="H162" s="3" t="s">
+        <v>630</v>
+      </c>
       <c r="I162" s="7" t="s">
         <v>16</v>
       </c>
@@ -9455,17 +9485,17 @@
     </row>
     <row r="163" ht="22.5" customHeight="1">
       <c r="A163" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B163" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwinger, D. (-)</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E163" s="5"/>
       <c r="F163" s="5"/>
@@ -9479,14 +9509,14 @@
     </row>
     <row r="164" ht="22.5" customHeight="1">
       <c r="A164" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B164" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Genathen, Johann Jakob (-)</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>31</v>
@@ -9494,10 +9524,10 @@
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
       <c r="G164" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="I164" s="7" t="s">
         <v>16</v>
@@ -9507,7 +9537,7 @@
     </row>
     <row r="165" ht="22.5" customHeight="1">
       <c r="A165" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B165" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9533,27 +9563,27 @@
     </row>
     <row r="166" ht="22.5" customHeight="1">
       <c r="A166" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B166" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hess, Caspar (-1631)</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E166" s="5"/>
       <c r="F166" s="5">
         <v>1631.0</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="I166" s="7" t="s">
         <v>16</v>
@@ -9563,20 +9593,20 @@
     </row>
     <row r="167" ht="22.5" customHeight="1">
       <c r="A167" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B167" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wolfen, Hans Jakob (-)</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E167" s="16"/>
-      <c r="F167" s="17"/>
+      <c r="E167" s="17"/>
+      <c r="F167" s="18"/>
       <c r="G167" s="9"/>
       <c r="H167" s="3"/>
       <c r="I167" s="7" t="s">
@@ -9587,22 +9617,22 @@
     </row>
     <row r="168" ht="22.5" customHeight="1">
       <c r="A168" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B168" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöri, Felix Christian (-)</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="E168" s="16"/>
-      <c r="F168" s="17"/>
+        <v>648</v>
+      </c>
+      <c r="E168" s="17"/>
+      <c r="F168" s="18"/>
       <c r="G168" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H168" s="3"/>
       <c r="I168" s="7" t="s">
@@ -9613,7 +9643,7 @@
     </row>
     <row r="169" ht="22.5" customHeight="1">
       <c r="A169" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B169" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9623,9 +9653,9 @@
         <v>12</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="E169" s="16"/>
+        <v>651</v>
+      </c>
+      <c r="E169" s="17"/>
       <c r="F169" s="5">
         <v>1654.0</v>
       </c>
@@ -9639,21 +9669,21 @@
     </row>
     <row r="170" ht="22.5" customHeight="1">
       <c r="A170" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B170" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther,  (-)</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D170" s="3"/>
-      <c r="E170" s="16"/>
-      <c r="F170" s="17"/>
+      <c r="E170" s="17"/>
+      <c r="F170" s="18"/>
       <c r="G170" s="9"/>
       <c r="H170" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I170" s="7" t="s">
         <v>16</v>
@@ -9663,23 +9693,23 @@
     </row>
     <row r="171" ht="22.5" customHeight="1">
       <c r="A171" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B171" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Weiss, Caspar (-)</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="E171" s="16"/>
-      <c r="F171" s="17"/>
+        <v>641</v>
+      </c>
+      <c r="E171" s="17"/>
+      <c r="F171" s="18"/>
       <c r="G171" s="9"/>
-      <c r="H171" s="18" t="s">
-        <v>656</v>
+      <c r="H171" s="19" t="s">
+        <v>657</v>
       </c>
       <c r="I171" s="7" t="s">
         <v>16</v>
@@ -9689,7 +9719,7 @@
     </row>
     <row r="172" ht="22.5" customHeight="1">
       <c r="A172" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B172" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9699,11 +9729,11 @@
         <v>60</v>
       </c>
       <c r="D172" s="3"/>
-      <c r="E172" s="16"/>
-      <c r="F172" s="17"/>
+      <c r="E172" s="17"/>
+      <c r="F172" s="18"/>
       <c r="G172" s="9"/>
-      <c r="H172" s="18" t="s">
-        <v>658</v>
+      <c r="H172" s="19" t="s">
+        <v>659</v>
       </c>
       <c r="I172" s="7" t="s">
         <v>16</v>
@@ -9713,40 +9743,40 @@
     </row>
     <row r="173" ht="22.5" customHeight="1">
       <c r="A173" s="3" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B173" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bas,  (-)</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D173" s="3"/>
-      <c r="E173" s="16"/>
-      <c r="F173" s="17"/>
+      <c r="E173" s="17"/>
+      <c r="F173" s="18"/>
       <c r="G173" s="9"/>
       <c r="H173" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="I173" s="19"/>
+        <v>662</v>
+      </c>
+      <c r="I173" s="20"/>
       <c r="J173" s="9"/>
       <c r="K173" s="9"/>
     </row>
     <row r="174" ht="22.5" customHeight="1">
       <c r="A174" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B174" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H.H.J. Gw. s. A.Z.Fr.M.,  (-)</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D174" s="3"/>
-      <c r="E174" s="16"/>
-      <c r="F174" s="17"/>
+      <c r="E174" s="17"/>
+      <c r="F174" s="18"/>
       <c r="G174" s="9"/>
       <c r="H174" s="3"/>
       <c r="I174" s="7" t="s">
@@ -9757,23 +9787,23 @@
     </row>
     <row r="175" ht="22.5" customHeight="1">
       <c r="A175" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B175" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hofm., Joh. (-)</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="E175" s="16"/>
-      <c r="F175" s="17"/>
+        <v>667</v>
+      </c>
+      <c r="E175" s="17"/>
+      <c r="F175" s="18"/>
       <c r="G175" s="9"/>
       <c r="H175" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="I175" s="7" t="s">
         <v>16</v>
@@ -9783,22 +9813,22 @@
     </row>
     <row r="176" ht="22.5" customHeight="1">
       <c r="A176" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B176" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Cyrene, Simon von (-)</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="E176" s="16"/>
-      <c r="F176" s="17"/>
+        <v>671</v>
+      </c>
+      <c r="E176" s="17"/>
+      <c r="F176" s="18"/>
       <c r="G176" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>249</v>
@@ -9811,20 +9841,20 @@
     </row>
     <row r="177" ht="22.5" customHeight="1">
       <c r="A177" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B177" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thomas,  (-)</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="D177" s="3"/>
-      <c r="E177" s="16"/>
-      <c r="F177" s="17"/>
+      <c r="E177" s="17"/>
+      <c r="F177" s="18"/>
       <c r="G177" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>323</v>
@@ -9837,23 +9867,23 @@
     </row>
     <row r="178" ht="22.5" customHeight="1">
       <c r="A178" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B178" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Phaeton,  (-)</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D178" s="3"/>
-      <c r="E178" s="16"/>
-      <c r="F178" s="17"/>
+      <c r="E178" s="17"/>
+      <c r="F178" s="18"/>
       <c r="G178" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="I178" s="7" t="s">
         <v>231</v>
@@ -9863,18 +9893,18 @@
     </row>
     <row r="179" ht="22.5" customHeight="1">
       <c r="A179" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B179" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lukas,  (-)</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D179" s="3"/>
-      <c r="E179" s="16"/>
-      <c r="F179" s="17"/>
+      <c r="E179" s="17"/>
+      <c r="F179" s="18"/>
       <c r="G179" s="9"/>
       <c r="H179" s="3" t="s">
         <v>249</v>
@@ -9887,20 +9917,20 @@
     </row>
     <row r="180" ht="22.5" customHeight="1">
       <c r="A180" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B180" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pallas Athena,  (-)</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D180" s="3"/>
-      <c r="E180" s="16"/>
-      <c r="F180" s="17"/>
+      <c r="E180" s="17"/>
+      <c r="F180" s="18"/>
       <c r="G180" s="3" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>231</v>
@@ -9913,23 +9943,23 @@
     </row>
     <row r="181" ht="22.5" customHeight="1">
       <c r="A181" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B181" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bacchus,  (-)</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D181" s="3"/>
-      <c r="E181" s="16"/>
-      <c r="F181" s="17"/>
+      <c r="E181" s="17"/>
+      <c r="F181" s="18"/>
       <c r="G181" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="I181" s="7" t="s">
         <v>231</v>
@@ -9939,23 +9969,23 @@
     </row>
     <row r="182" ht="22.5" customHeight="1">
       <c r="A182" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B182" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Darius I.,  (-)</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D182" s="3"/>
-      <c r="E182" s="16"/>
-      <c r="F182" s="17"/>
+      <c r="E182" s="17"/>
+      <c r="F182" s="18"/>
       <c r="G182" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="I182" s="7" t="s">
         <v>16</v>
@@ -9965,23 +9995,23 @@
     </row>
     <row r="183" ht="22.5" customHeight="1">
       <c r="A183" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="B183" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Kyros II.,  (-)</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="D183" s="3"/>
+      <c r="E183" s="17"/>
+      <c r="F183" s="18"/>
+      <c r="G183" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="H183" s="3" t="s">
         <v>692</v>
-      </c>
-      <c r="B183" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>Kyros II.,  (-)</v>
-      </c>
-      <c r="C183" s="6" t="s">
-        <v>693</v>
-      </c>
-      <c r="D183" s="3"/>
-      <c r="E183" s="16"/>
-      <c r="F183" s="17"/>
-      <c r="G183" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="H183" s="3" t="s">
-        <v>691</v>
       </c>
       <c r="I183" s="7" t="s">
         <v>16</v>
@@ -9991,25 +10021,25 @@
     </row>
     <row r="184" ht="22.5" customHeight="1">
       <c r="A184" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B184" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hippo, Augustinus von (-)</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>697</v>
-      </c>
-      <c r="E184" s="16"/>
-      <c r="F184" s="17"/>
+        <v>698</v>
+      </c>
+      <c r="E184" s="17"/>
+      <c r="F184" s="18"/>
       <c r="G184" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I184" s="7" t="s">
         <v>16</v>
@@ -10019,20 +10049,20 @@
     </row>
     <row r="185" ht="22.5" customHeight="1">
       <c r="A185" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B185" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lazarus,  (-)</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D185" s="3"/>
-      <c r="E185" s="16"/>
-      <c r="F185" s="17"/>
+      <c r="E185" s="17"/>
+      <c r="F185" s="18"/>
       <c r="G185" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>249</v>
@@ -10045,20 +10075,20 @@
     </row>
     <row r="186" ht="22.5" customHeight="1">
       <c r="A186" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B186" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lot,  (-)</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D186" s="3"/>
-      <c r="E186" s="16"/>
-      <c r="F186" s="17"/>
+      <c r="E186" s="17"/>
+      <c r="F186" s="18"/>
       <c r="G186" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>249</v>
@@ -10071,21 +10101,21 @@
     </row>
     <row r="187" ht="22.5" customHeight="1">
       <c r="A187" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B187" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hans Rudolf,  (-)</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D187" s="3"/>
-      <c r="E187" s="16"/>
-      <c r="F187" s="17"/>
+      <c r="E187" s="17"/>
+      <c r="F187" s="18"/>
       <c r="G187" s="9"/>
       <c r="H187" s="3" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I187" s="7" t="s">
         <v>16</v>
@@ -10095,7 +10125,7 @@
     </row>
     <row r="188" ht="22.5" customHeight="1">
       <c r="A188" s="3" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B188" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10108,16 +10138,16 @@
         <v>13</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="F188" s="5">
         <v>1690.0</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I188" s="7" t="s">
         <v>16</v>
@@ -10127,17 +10157,17 @@
     </row>
     <row r="189" ht="22.5" customHeight="1">
       <c r="A189" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B189" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bachofen, Johann Ulrich (1643-1700)</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="E189" s="5">
         <v>1643.0</v>
@@ -10146,7 +10176,7 @@
         <v>1700.0</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>226</v>
@@ -10159,14 +10189,14 @@
     </row>
     <row r="190" ht="22.5" customHeight="1">
       <c r="A190" s="3" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B190" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grebel, Hans Konrad (1615-1674)</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D190" s="3" t="s">
         <v>613</v>
@@ -10178,91 +10208,91 @@
         <v>1674.0</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="I190" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="K190" s="9"/>
     </row>
     <row r="191" ht="22.5" customHeight="1">
       <c r="A191" s="3" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B191" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gossweiler, Emerentia (-)</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="E191" s="16"/>
-      <c r="F191" s="17"/>
+        <v>725</v>
+      </c>
+      <c r="E191" s="17"/>
+      <c r="F191" s="18"/>
       <c r="G191" s="9"/>
       <c r="H191" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I191" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J191" s="8" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="K191" s="9"/>
     </row>
     <row r="192" ht="22.5" customHeight="1">
       <c r="A192" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B192" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lochmann, Heinrich (1613-1667)</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E192" s="20">
+      <c r="E192" s="16">
         <v>1613.0</v>
       </c>
       <c r="F192" s="5">
         <v>1667.0</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J192" s="8" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="K192" s="9"/>
     </row>
     <row r="193" ht="22.5" customHeight="1">
       <c r="A193" s="3" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B193" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Johann Jakob (1602-1668)</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>31</v>
@@ -10274,130 +10304,130 @@
         <v>1668.0</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J193" s="8" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="K193" s="9"/>
     </row>
     <row r="194" ht="22.5" customHeight="1">
       <c r="A194" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B194" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orelli, Anna (-)</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="E194" s="16"/>
-      <c r="F194" s="17"/>
+        <v>739</v>
+      </c>
+      <c r="E194" s="17"/>
+      <c r="F194" s="18"/>
       <c r="G194" s="9"/>
       <c r="H194" s="3" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="I194" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J194" s="10" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="K194" s="9"/>
     </row>
     <row r="195" ht="22.5" customHeight="1">
       <c r="A195" s="3" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B195" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. E. H.,  (-)</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D195" s="3"/>
-      <c r="E195" s="16"/>
-      <c r="F195" s="17"/>
+      <c r="E195" s="17"/>
+      <c r="F195" s="18"/>
       <c r="G195" s="9"/>
       <c r="H195" s="3" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J195" s="21" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="K195" s="9"/>
     </row>
     <row r="196" ht="22.5" customHeight="1">
       <c r="A196" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B196" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. H.,  (-)</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D196" s="3"/>
-      <c r="E196" s="16"/>
-      <c r="F196" s="17"/>
+      <c r="E196" s="17"/>
+      <c r="F196" s="18"/>
       <c r="G196" s="9"/>
       <c r="H196" s="3" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="I196" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J196" s="21" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="K196" s="9"/>
     </row>
     <row r="197" ht="22.5" customHeight="1">
       <c r="A197" s="3" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B197" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grob, Hans Jakob (-)</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E197" s="16"/>
-      <c r="F197" s="17"/>
+      <c r="E197" s="17"/>
+      <c r="F197" s="18"/>
       <c r="G197" s="9"/>
       <c r="H197" s="3" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="I197" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J197" s="8" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="K197" s="9"/>
     </row>
     <row r="198" ht="22.5" customHeight="1">
       <c r="A198" s="3" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B198" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10407,85 +10437,85 @@
         <v>68</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="E198" s="16"/>
-      <c r="F198" s="17"/>
+        <v>754</v>
+      </c>
+      <c r="E198" s="17"/>
+      <c r="F198" s="18"/>
       <c r="G198" s="9"/>
       <c r="H198" s="3"/>
       <c r="I198" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J198" s="8" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="K198" s="9"/>
     </row>
     <row r="199" ht="22.5" customHeight="1">
       <c r="A199" s="3" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B199" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klingler, Kaspar (-)</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="E199" s="16"/>
-      <c r="F199" s="17"/>
+        <v>757</v>
+      </c>
+      <c r="E199" s="17"/>
+      <c r="F199" s="18"/>
       <c r="G199" s="9"/>
       <c r="H199" s="3"/>
       <c r="I199" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J199" s="8" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="K199" s="9"/>
     </row>
     <row r="200" ht="22.5" customHeight="1">
       <c r="A200" s="3" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B200" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöndli, Dorothea (-)</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="E200" s="16"/>
-      <c r="F200" s="17"/>
+      <c r="E200" s="17"/>
+      <c r="F200" s="18"/>
       <c r="G200" s="9"/>
       <c r="H200" s="3"/>
       <c r="I200" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J200" s="8" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="K200" s="9"/>
     </row>
     <row r="201" ht="22.5" customHeight="1">
       <c r="A201" s="3" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B201" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Hans Caspar (1617-1691)</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E201" s="5">
         <v>1617.0</v>
@@ -10494,29 +10524,29 @@
         <v>1691.0</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="K201" s="9"/>
     </row>
     <row r="202" ht="22.5" customHeight="1">
       <c r="A202" s="3" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B202" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Salomon (1580-1652)</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>434</v>
@@ -10528,60 +10558,60 @@
         <v>1652.0</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J202" s="8" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="K202" s="9"/>
     </row>
     <row r="203" ht="22.5" customHeight="1">
       <c r="A203" s="3" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B203" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis-Soglio, Maria Ursina von  (-)</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="E203" s="16"/>
-      <c r="F203" s="17"/>
+        <v>773</v>
+      </c>
+      <c r="E203" s="17"/>
+      <c r="F203" s="18"/>
       <c r="G203" s="9"/>
       <c r="H203" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J203" s="8" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="K203" s="9"/>
     </row>
     <row r="204" ht="22.5" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B204" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Brügger, Andreas von (1588-1653)</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E204" s="5">
         <v>1588.0</v>
@@ -10590,36 +10620,36 @@
         <v>1653.0</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="I204" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J204" s="8" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="K204" s="9"/>
     </row>
     <row r="205" ht="22.5" customHeight="1">
       <c r="A205" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B205" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Anhorn,  (-)</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D205" s="3"/>
-      <c r="E205" s="16"/>
-      <c r="F205" s="17"/>
+      <c r="E205" s="17"/>
+      <c r="F205" s="18"/>
       <c r="G205" s="9"/>
       <c r="H205" s="3" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="I205" s="7" t="s">
         <v>16</v>
@@ -10629,23 +10659,23 @@
     </row>
     <row r="206" ht="22.5" customHeight="1">
       <c r="A206" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B206" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wilden, Abraham (-)</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="E206" s="16"/>
-      <c r="F206" s="17"/>
+      <c r="E206" s="17"/>
+      <c r="F206" s="18"/>
       <c r="G206" s="9"/>
       <c r="H206" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>16</v>
@@ -10655,23 +10685,23 @@
     </row>
     <row r="207" ht="22.5" customHeight="1">
       <c r="A207" s="3" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B207" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Groben, Jacob (evtl. Johannes) (-)</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="E207" s="16"/>
-      <c r="F207" s="17"/>
+        <v>789</v>
+      </c>
+      <c r="E207" s="17"/>
+      <c r="F207" s="18"/>
       <c r="G207" s="9"/>
       <c r="H207" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>16</v>
@@ -10681,21 +10711,21 @@
     </row>
     <row r="208" ht="22.5" customHeight="1">
       <c r="A208" s="3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B208" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ziegler,  (-)</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D208" s="3"/>
-      <c r="E208" s="16"/>
-      <c r="F208" s="17"/>
+      <c r="E208" s="17"/>
+      <c r="F208" s="18"/>
       <c r="G208" s="9"/>
       <c r="H208" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="I208" s="7" t="s">
         <v>16</v>
@@ -10705,7 +10735,7 @@
     </row>
     <row r="209" ht="22.5" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B209" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10717,11 +10747,11 @@
       <c r="D209" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E209" s="16"/>
-      <c r="F209" s="17"/>
+      <c r="E209" s="17"/>
+      <c r="F209" s="18"/>
       <c r="G209" s="9"/>
       <c r="H209" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="I209" s="7" t="s">
         <v>16</v>
@@ -10731,21 +10761,21 @@
     </row>
     <row r="210" ht="22.5" customHeight="1">
       <c r="A210" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B210" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Oeri,  (-)</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D210" s="3"/>
-      <c r="E210" s="16"/>
-      <c r="F210" s="17"/>
+      <c r="E210" s="17"/>
+      <c r="F210" s="18"/>
       <c r="G210" s="9"/>
       <c r="H210" s="3" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="I210" s="7" t="s">
         <v>16</v>
@@ -10755,21 +10785,21 @@
     </row>
     <row r="211" ht="22.5" customHeight="1">
       <c r="A211" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B211" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wittib,  (-)</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D211" s="3"/>
-      <c r="E211" s="16"/>
-      <c r="F211" s="17"/>
+      <c r="E211" s="17"/>
+      <c r="F211" s="18"/>
       <c r="G211" s="9"/>
       <c r="H211" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I211" s="13"/>
       <c r="J211" s="9"/>
@@ -10777,18 +10807,18 @@
     </row>
     <row r="212" ht="22.5" customHeight="1">
       <c r="A212" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B212" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Graf von Sultz,  (-)</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D212" s="3"/>
-      <c r="E212" s="16"/>
-      <c r="F212" s="17"/>
+      <c r="E212" s="17"/>
+      <c r="F212" s="18"/>
       <c r="G212" s="9"/>
       <c r="H212" s="3"/>
       <c r="I212" s="7" t="s">
@@ -10799,21 +10829,21 @@
     </row>
     <row r="213" ht="22.5" customHeight="1">
       <c r="A213" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B213" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Eglin,  (-)</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D213" s="3"/>
-      <c r="E213" s="16"/>
-      <c r="F213" s="17"/>
+      <c r="E213" s="17"/>
+      <c r="F213" s="18"/>
       <c r="G213" s="9"/>
       <c r="H213" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="I213" s="7" t="s">
         <v>16</v>
@@ -10823,23 +10853,23 @@
     </row>
     <row r="214" ht="22.5" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B214" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wildhans von Breitenlandenberg,  (-1444)</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D214" s="3"/>
-      <c r="E214" s="16"/>
+      <c r="E214" s="17"/>
       <c r="F214" s="5">
         <v>1444.0</v>
       </c>
       <c r="G214" s="9"/>
       <c r="H214" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="I214" s="7" t="s">
         <v>16</v>
@@ -10849,18 +10879,18 @@
     </row>
     <row r="215" ht="22.5" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B215" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pfarrherr,  (-)</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D215" s="3"/>
-      <c r="E215" s="16"/>
-      <c r="F215" s="17"/>
+      <c r="E215" s="17"/>
+      <c r="F215" s="18"/>
       <c r="G215" s="9"/>
       <c r="H215" s="3"/>
       <c r="I215" s="7" t="s">
@@ -10871,17 +10901,17 @@
     </row>
     <row r="216" ht="22.5" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B216" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid von Schwarzenhorn, Johann Rudolf (1590-1667)</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="E216" s="5">
         <v>1590.0</v>
@@ -10890,68 +10920,68 @@
         <v>1667.0</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="I216" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J216" s="8" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="K216" s="9"/>
     </row>
     <row r="217" ht="22.5" customHeight="1">
       <c r="A217" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B217" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid, Felix (-1598)</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E217" s="16"/>
+      <c r="E217" s="17"/>
       <c r="F217" s="5">
         <v>1598.0</v>
       </c>
       <c r="G217" s="9"/>
       <c r="H217" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="I217" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J217" s="8" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="K217" s="9"/>
     </row>
     <row r="218" ht="22.5" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B218" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hessen, Heinrich (-)</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E218" s="16"/>
-      <c r="F218" s="17"/>
+      <c r="E218" s="17"/>
+      <c r="F218" s="18"/>
       <c r="G218" s="9"/>
       <c r="H218" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="I218" s="7" t="s">
         <v>16</v>
@@ -10961,20 +10991,20 @@
     </row>
     <row r="219" ht="22.5" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B219" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulr., H. (-)</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="E219" s="16"/>
-      <c r="F219" s="17"/>
+        <v>825</v>
+      </c>
+      <c r="E219" s="17"/>
+      <c r="F219" s="18"/>
       <c r="G219" s="9"/>
       <c r="H219" s="3" t="s">
         <v>226</v>
@@ -10987,7 +11017,7 @@
     </row>
     <row r="220" ht="22.5" customHeight="1">
       <c r="A220" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B220" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10997,13 +11027,13 @@
         <v>60</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>826</v>
-      </c>
-      <c r="E220" s="16"/>
-      <c r="F220" s="17"/>
+        <v>827</v>
+      </c>
+      <c r="E220" s="17"/>
+      <c r="F220" s="18"/>
       <c r="G220" s="9"/>
       <c r="H220" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>16</v>
@@ -11013,7 +11043,7 @@
     </row>
     <row r="221" ht="22.5" customHeight="1">
       <c r="A221" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B221" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11023,11 +11053,11 @@
         <v>60</v>
       </c>
       <c r="D221" s="3"/>
-      <c r="E221" s="16"/>
-      <c r="F221" s="17"/>
+      <c r="E221" s="17"/>
+      <c r="F221" s="18"/>
       <c r="G221" s="9"/>
       <c r="H221" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="I221" s="7" t="s">
         <v>16</v>
@@ -11037,18 +11067,18 @@
     </row>
     <row r="222" ht="22.5" customHeight="1">
       <c r="A222" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B222" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Locher,  (-)</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D222" s="3"/>
-      <c r="E222" s="16"/>
-      <c r="F222" s="17"/>
+      <c r="E222" s="17"/>
+      <c r="F222" s="18"/>
       <c r="G222" s="9"/>
       <c r="H222" s="3"/>
       <c r="I222" s="7" t="s">
@@ -11059,20 +11089,20 @@
     </row>
     <row r="223" ht="22.5" customHeight="1">
       <c r="A223" s="3" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B223" s="4" t="str">
         <f t="shared" si="1"/>
         <v>König, Caspar (-)</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="E223" s="16"/>
-      <c r="F223" s="17"/>
+        <v>641</v>
+      </c>
+      <c r="E223" s="17"/>
+      <c r="F223" s="18"/>
       <c r="G223" s="9"/>
       <c r="H223" s="3"/>
       <c r="I223" s="13"/>
@@ -11081,7 +11111,7 @@
     </row>
     <row r="224" ht="22.5" customHeight="1">
       <c r="A224" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B224" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11102,8 +11132,8 @@
       <c r="G224" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H224" s="18" t="s">
-        <v>835</v>
+      <c r="H224" s="19" t="s">
+        <v>836</v>
       </c>
       <c r="I224" s="7" t="s">
         <v>16</v>
@@ -11115,7 +11145,7 @@
     </row>
     <row r="225" ht="22.5" customHeight="1">
       <c r="A225" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B225" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11125,11 +11155,11 @@
         <v>37</v>
       </c>
       <c r="D225" s="3"/>
-      <c r="E225" s="16"/>
-      <c r="F225" s="17"/>
+      <c r="E225" s="17"/>
+      <c r="F225" s="18"/>
       <c r="G225" s="9"/>
       <c r="H225" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>16</v>
@@ -11139,20 +11169,20 @@
     </row>
     <row r="226" ht="22.5" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B226" s="4" t="str">
         <f t="shared" si="1"/>
         <v>O., Jacob U. (-)</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="E226" s="16"/>
-      <c r="F226" s="17"/>
+        <v>841</v>
+      </c>
+      <c r="E226" s="17"/>
+      <c r="F226" s="18"/>
       <c r="G226" s="9"/>
       <c r="H226" s="3" t="s">
         <v>226</v>
@@ -11165,21 +11195,21 @@
     </row>
     <row r="227" ht="22.5" customHeight="1">
       <c r="A227" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B227" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schneeberger,  (-)</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D227" s="3"/>
-      <c r="E227" s="16"/>
-      <c r="F227" s="17"/>
+      <c r="E227" s="17"/>
+      <c r="F227" s="18"/>
       <c r="G227" s="9"/>
       <c r="H227" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="I227" s="7" t="s">
         <v>16</v>
@@ -11189,17 +11219,17 @@
     </row>
     <row r="228" ht="22.5" customHeight="1">
       <c r="A228" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B228" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwingli, Ulrich (1484-1531)</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E228" s="5">
         <v>1484.0</v>
@@ -11208,10 +11238,10 @@
         <v>1531.0</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="I228" s="7" t="s">
         <v>16</v>
@@ -11221,14 +11251,14 @@
     </row>
     <row r="229" ht="22.5" customHeight="1">
       <c r="A229" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B229" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bullinger, Heinrich (1504-1575)</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>37</v>
@@ -11240,10 +11270,10 @@
         <v>1575.0</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="I229" s="7" t="s">
         <v>16</v>
@@ -11253,17 +11283,17 @@
     </row>
     <row r="230" ht="22.5" customHeight="1">
       <c r="A230" s="3" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B230" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther, Rudolf (1519-1586)</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="E230" s="5">
         <v>1519.0</v>
@@ -11272,7 +11302,7 @@
         <v>1586.0</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H230" s="3"/>
       <c r="I230" s="7" t="s">
@@ -11283,14 +11313,14 @@
     </row>
     <row r="231" ht="22.5" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B231" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Breitinger, Johann Jakob (1575-1645)</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>31</v>
@@ -11302,7 +11332,7 @@
         <v>1645.0</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H231" s="3"/>
       <c r="I231" s="7" t="s">
@@ -11313,17 +11343,17 @@
     </row>
     <row r="232" ht="22.5" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B232" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jrminger, Jacob (1588-1649)</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E232" s="5">
         <v>1588.0</v>
@@ -11332,7 +11362,7 @@
         <v>1649.0</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H232" s="3"/>
       <c r="I232" s="7" t="s">
@@ -11343,20 +11373,20 @@
     </row>
     <row r="233" ht="22.5" customHeight="1">
       <c r="A233" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B233" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fries, Jakob (-)</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="E233" s="16"/>
-      <c r="F233" s="17"/>
+      <c r="E233" s="17"/>
+      <c r="F233" s="18"/>
       <c r="G233" s="9"/>
       <c r="H233" s="3"/>
       <c r="I233" s="7" t="s">
@@ -11367,25 +11397,25 @@
     </row>
     <row r="234" ht="22.5" customHeight="1">
       <c r="A234" s="3" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B234" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Geiger, Joh. Rud. (-)</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="E234" s="16"/>
-      <c r="F234" s="17"/>
+        <v>866</v>
+      </c>
+      <c r="E234" s="17"/>
+      <c r="F234" s="18"/>
       <c r="G234" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="I234" s="7" t="s">
         <v>16</v>
@@ -11395,20 +11425,20 @@
     </row>
     <row r="235" ht="22.5" customHeight="1">
       <c r="A235" s="3" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B235" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maurer, C. (-)</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="E235" s="16"/>
-      <c r="F235" s="17"/>
+        <v>871</v>
+      </c>
+      <c r="E235" s="17"/>
+      <c r="F235" s="18"/>
       <c r="G235" s="9"/>
       <c r="H235" s="3"/>
       <c r="I235" s="7" t="s">
@@ -11419,20 +11449,20 @@
     </row>
     <row r="236" ht="22.5" customHeight="1">
       <c r="A236" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="B236" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Suter, C. (-)</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="D236" s="3" t="s">
         <v>871</v>
       </c>
-      <c r="B236" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>Suter, C. (-)</v>
-      </c>
-      <c r="C236" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="E236" s="16"/>
-      <c r="F236" s="17"/>
+      <c r="E236" s="17"/>
+      <c r="F236" s="18"/>
       <c r="G236" s="9"/>
       <c r="H236" s="3"/>
       <c r="I236" s="7" t="s">
@@ -11443,20 +11473,20 @@
     </row>
     <row r="237" ht="22.5" customHeight="1">
       <c r="A237" s="3" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B237" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Holzhalb, Joh. (-)</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="E237" s="16"/>
-      <c r="F237" s="17"/>
+        <v>667</v>
+      </c>
+      <c r="E237" s="17"/>
+      <c r="F237" s="18"/>
       <c r="G237" s="9"/>
       <c r="H237" s="3" t="s">
         <v>226</v>
@@ -11469,20 +11499,20 @@
     </row>
     <row r="238" ht="22.5" customHeight="1">
       <c r="A238" s="3" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B238" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wirtz, H. C. (-)</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>877</v>
-      </c>
-      <c r="E238" s="16"/>
-      <c r="F238" s="17"/>
+        <v>878</v>
+      </c>
+      <c r="E238" s="17"/>
+      <c r="F238" s="18"/>
       <c r="G238" s="9"/>
       <c r="H238" s="3"/>
       <c r="I238" s="7" t="s">
@@ -11493,7 +11523,7 @@
     </row>
     <row r="239" ht="22.5" customHeight="1">
       <c r="A239" s="3" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B239" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11503,12 +11533,12 @@
         <v>521</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="E239" s="16"/>
-      <c r="F239" s="17"/>
+        <v>641</v>
+      </c>
+      <c r="E239" s="17"/>
+      <c r="F239" s="18"/>
       <c r="G239" s="3" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H239" s="3"/>
       <c r="I239" s="7" t="s">
@@ -11519,22 +11549,22 @@
     </row>
     <row r="240" ht="22.5" customHeight="1">
       <c r="A240" s="3" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B240" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hospinianus, R. (-)</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="E240" s="16"/>
-      <c r="F240" s="17"/>
+        <v>883</v>
+      </c>
+      <c r="E240" s="17"/>
+      <c r="F240" s="18"/>
       <c r="G240" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H240" s="3"/>
       <c r="I240" s="7" t="s">
@@ -11545,20 +11575,20 @@
     </row>
     <row r="241" ht="22.5" customHeight="1">
       <c r="A241" s="3" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B241" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Erni, H. (-)</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="E241" s="16"/>
-      <c r="F241" s="17"/>
+        <v>825</v>
+      </c>
+      <c r="E241" s="17"/>
+      <c r="F241" s="18"/>
       <c r="G241" s="9"/>
       <c r="H241" s="3"/>
       <c r="I241" s="7" t="s">
@@ -11569,20 +11599,20 @@
     </row>
     <row r="242" ht="22.5" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B242" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Tomman, P. (-)</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>888</v>
-      </c>
-      <c r="E242" s="16"/>
-      <c r="F242" s="17"/>
+        <v>889</v>
+      </c>
+      <c r="E242" s="17"/>
+      <c r="F242" s="18"/>
       <c r="G242" s="9"/>
       <c r="H242" s="3"/>
       <c r="I242" s="7" t="s">
@@ -11593,20 +11623,20 @@
     </row>
     <row r="243" ht="22.5" customHeight="1">
       <c r="A243" s="3" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B243" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Stukki, R. (-)</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="E243" s="16"/>
-      <c r="F243" s="17"/>
+        <v>883</v>
+      </c>
+      <c r="E243" s="17"/>
+      <c r="F243" s="18"/>
       <c r="G243" s="9"/>
       <c r="H243" s="3"/>
       <c r="I243" s="7" t="s">
@@ -11617,20 +11647,20 @@
     </row>
     <row r="244" ht="22.5" customHeight="1">
       <c r="A244" s="3" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B244" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zeller, H. (-)</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="E244" s="16"/>
-      <c r="F244" s="17"/>
+        <v>825</v>
+      </c>
+      <c r="E244" s="17"/>
+      <c r="F244" s="18"/>
       <c r="G244" s="9"/>
       <c r="H244" s="3"/>
       <c r="I244" s="7" t="s">
@@ -11641,7 +11671,7 @@
     </row>
     <row r="245" ht="22.5" customHeight="1">
       <c r="A245" s="3" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B245" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11649,13 +11679,13 @@
       </c>
       <c r="C245" s="6"/>
       <c r="D245" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="E245" s="16"/>
-      <c r="F245" s="17"/>
+        <v>860</v>
+      </c>
+      <c r="E245" s="17"/>
+      <c r="F245" s="18"/>
       <c r="G245" s="9"/>
       <c r="H245" s="3" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="I245" s="7" t="s">
         <v>16</v>
@@ -11665,21 +11695,21 @@
     </row>
     <row r="246" ht="22.5" customHeight="1">
       <c r="A246" s="3" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B246" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fr. Doctorin,  (-)</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D246" s="3"/>
-      <c r="E246" s="16"/>
-      <c r="F246" s="17"/>
+      <c r="E246" s="17"/>
+      <c r="F246" s="18"/>
       <c r="G246" s="9"/>
       <c r="H246" s="3" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="I246" s="7" t="s">
         <v>16</v>
@@ -11689,17 +11719,17 @@
     </row>
     <row r="247" ht="22.5" customHeight="1">
       <c r="A247" s="3" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B247" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kusen, Jost von (1570-1630)</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E247" s="5">
         <v>1570.0</v>
@@ -11708,10 +11738,10 @@
         <v>1630.0</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="I247" s="7" t="s">
         <v>16</v>
@@ -11721,23 +11751,23 @@
     </row>
     <row r="248" ht="22.5" customHeight="1">
       <c r="A248" s="3" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B248" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Heinrich (-)</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E248" s="16"/>
-      <c r="F248" s="17"/>
+      <c r="E248" s="17"/>
+      <c r="F248" s="18"/>
       <c r="G248" s="9"/>
       <c r="H248" s="3" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="I248" s="7" t="s">
         <v>16</v>
@@ -11747,21 +11777,21 @@
     </row>
     <row r="249" ht="22.5" customHeight="1">
       <c r="A249" s="3" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B249" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gessner,  (-)</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D249" s="3"/>
-      <c r="E249" s="16"/>
-      <c r="F249" s="17"/>
+      <c r="E249" s="17"/>
+      <c r="F249" s="18"/>
       <c r="G249" s="9"/>
       <c r="H249" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="I249" s="7" t="s">
         <v>16</v>
@@ -11771,17 +11801,17 @@
     </row>
     <row r="250" ht="22.5" customHeight="1">
       <c r="A250" s="3" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B250" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wöllwein, Johann Anton (1616-1659)</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="E250" s="5">
         <v>1616.0</v>
@@ -11790,10 +11820,10 @@
         <v>1659.0</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="I250" s="7" t="s">
         <v>16</v>
@@ -11803,46 +11833,46 @@
     </row>
     <row r="251" ht="22.5" customHeight="1">
       <c r="A251" s="3" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B251" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Anna (-)</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="E251" s="16"/>
-      <c r="F251" s="17"/>
+        <v>739</v>
+      </c>
+      <c r="E251" s="17"/>
+      <c r="F251" s="18"/>
       <c r="G251" s="9"/>
       <c r="H251" s="3" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I251" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="K251" s="9"/>
     </row>
     <row r="252" ht="22.5" customHeight="1">
       <c r="A252" s="3" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B252" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. J. R. S.,  (-)</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D252" s="3"/>
-      <c r="E252" s="16"/>
-      <c r="F252" s="17"/>
+      <c r="E252" s="17"/>
+      <c r="F252" s="18"/>
       <c r="G252" s="9"/>
       <c r="H252" s="3"/>
       <c r="I252" s="13"/>
@@ -11851,17 +11881,17 @@
     </row>
     <row r="253" ht="22.5" customHeight="1">
       <c r="A253" s="3" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B253" s="4" t="str">
         <f t="shared" si="1"/>
         <v>de Ruyter, Michiel (1607-1676)</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E253" s="5">
         <v>1607.0</v>
@@ -11870,10 +11900,10 @@
         <v>1676.0</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="I253" s="7" t="s">
         <v>16</v>
@@ -11883,21 +11913,21 @@
     </row>
     <row r="254" ht="22.5" customHeight="1">
       <c r="A254" s="3" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B254" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Frau Oberstin,  (-)</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D254" s="3"/>
-      <c r="E254" s="16"/>
-      <c r="F254" s="17"/>
+      <c r="E254" s="17"/>
+      <c r="F254" s="18"/>
       <c r="G254" s="9"/>
       <c r="H254" s="3" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="I254" s="7" t="s">
         <v>16</v>
@@ -11907,23 +11937,23 @@
     </row>
     <row r="255" ht="22.5" customHeight="1">
       <c r="A255" s="3" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B255" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vulcanus,  (-)</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D255" s="3"/>
-      <c r="E255" s="16"/>
-      <c r="F255" s="17"/>
+      <c r="E255" s="17"/>
+      <c r="F255" s="18"/>
       <c r="G255" s="3" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="I255" s="7" t="s">
         <v>231</v>
@@ -11933,23 +11963,23 @@
     </row>
     <row r="256" ht="22.5" customHeight="1">
       <c r="A256" s="3" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B256" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esau,  (-)</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D256" s="3"/>
-      <c r="E256" s="16"/>
-      <c r="F256" s="17"/>
+      <c r="E256" s="17"/>
+      <c r="F256" s="18"/>
       <c r="G256" s="3" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="I256" s="7" t="s">
         <v>249</v>
@@ -11959,23 +11989,23 @@
     </row>
     <row r="257" ht="22.5" customHeight="1">
       <c r="A257" s="3" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B257" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Danaos,  (-)</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="D257" s="3"/>
-      <c r="E257" s="16"/>
-      <c r="F257" s="17"/>
+      <c r="E257" s="17"/>
+      <c r="F257" s="18"/>
       <c r="G257" s="3" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="I257" s="7" t="s">
         <v>231</v>
@@ -11985,20 +12015,20 @@
     </row>
     <row r="258" ht="22.5" customHeight="1">
       <c r="A258" s="3" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B258" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Medusa,  (-)</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D258" s="3"/>
-      <c r="E258" s="16"/>
-      <c r="F258" s="17"/>
+      <c r="E258" s="17"/>
+      <c r="F258" s="18"/>
       <c r="G258" s="3" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>231</v>
@@ -12011,20 +12041,20 @@
     </row>
     <row r="259" ht="22.5" customHeight="1">
       <c r="A259" s="3" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B259" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pluton,  (-)</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D259" s="3"/>
-      <c r="E259" s="16"/>
-      <c r="F259" s="17"/>
+      <c r="E259" s="17"/>
+      <c r="F259" s="18"/>
       <c r="G259" s="3" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>231</v>
@@ -12037,20 +12067,20 @@
     </row>
     <row r="260" ht="22.5" customHeight="1">
       <c r="A260" s="3" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B260" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mercur,  (-)</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="D260" s="3"/>
-      <c r="E260" s="16"/>
-      <c r="F260" s="17"/>
+      <c r="E260" s="17"/>
+      <c r="F260" s="18"/>
       <c r="G260" s="3" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>231</v>
@@ -12063,20 +12093,20 @@
     </row>
     <row r="261" ht="22.5" customHeight="1">
       <c r="A261" s="3" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B261" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Perseus,  (-)</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D261" s="3"/>
-      <c r="E261" s="16"/>
-      <c r="F261" s="17"/>
+      <c r="E261" s="17"/>
+      <c r="F261" s="18"/>
       <c r="G261" s="3" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>231</v>
@@ -12089,23 +12119,23 @@
     </row>
     <row r="262" ht="22.5" customHeight="1">
       <c r="A262" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B262" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Atropos,  (-)</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="D262" s="3"/>
-      <c r="E262" s="16"/>
-      <c r="F262" s="17"/>
+      <c r="E262" s="17"/>
+      <c r="F262" s="18"/>
       <c r="G262" s="3" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="I262" s="7" t="s">
         <v>231</v>
@@ -12115,23 +12145,23 @@
     </row>
     <row r="263" ht="22.5" customHeight="1">
       <c r="A263" s="3" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B263" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Barbara von Nikomedien,  (-)</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="D263" s="3"/>
-      <c r="E263" s="16"/>
-      <c r="F263" s="17"/>
+      <c r="E263" s="17"/>
+      <c r="F263" s="18"/>
       <c r="G263" s="3" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H263" s="3" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="I263" s="7" t="s">
         <v>249</v>
@@ -12141,7 +12171,7 @@
     </row>
     <row r="264" ht="22.5" customHeight="1">
       <c r="A264" s="3" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B264" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12149,13 +12179,13 @@
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="3" t="s">
-        <v>852</v>
-      </c>
-      <c r="E264" s="16"/>
-      <c r="F264" s="17"/>
+        <v>853</v>
+      </c>
+      <c r="E264" s="17"/>
+      <c r="F264" s="18"/>
       <c r="G264" s="9"/>
       <c r="H264" s="3" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="I264" s="13"/>
       <c r="J264" s="9"/>
@@ -12163,7 +12193,7 @@
     </row>
     <row r="265" ht="22.5" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B265" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12173,11 +12203,11 @@
       <c r="D265" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E265" s="16"/>
-      <c r="F265" s="17"/>
+      <c r="E265" s="17"/>
+      <c r="F265" s="18"/>
       <c r="G265" s="9"/>
       <c r="H265" s="3" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="I265" s="13"/>
       <c r="J265" s="9"/>
@@ -12185,21 +12215,21 @@
     </row>
     <row r="266" ht="22.5" customHeight="1">
       <c r="A266" s="3" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B266" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Karl,  (-)</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D266" s="3"/>
-      <c r="E266" s="16"/>
-      <c r="F266" s="17"/>
+      <c r="E266" s="17"/>
+      <c r="F266" s="18"/>
       <c r="G266" s="9"/>
       <c r="H266" s="3" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="I266" s="7" t="s">
         <v>16</v>
@@ -12209,21 +12239,21 @@
     </row>
     <row r="267" ht="22.5" customHeight="1">
       <c r="A267" s="3" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B267" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Duraeum,  (-)</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D267" s="3"/>
-      <c r="E267" s="16"/>
-      <c r="F267" s="17"/>
+      <c r="E267" s="17"/>
+      <c r="F267" s="18"/>
       <c r="G267" s="9"/>
       <c r="H267" s="3" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="I267" s="13"/>
       <c r="J267" s="9"/>
@@ -12231,17 +12261,17 @@
     </row>
     <row r="268" ht="22.5" customHeight="1">
       <c r="A268" s="3" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B268" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zesen, Philipp von (1619-1689)</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="E268" s="5">
         <v>1619.0</v>
@@ -12250,7 +12280,7 @@
         <v>1689.0</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H268" s="3"/>
       <c r="I268" s="7" t="s">
@@ -12261,23 +12291,23 @@
     </row>
     <row r="269" ht="22.5" customHeight="1">
       <c r="A269" s="3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B269" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lucretia,  (-)</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D269" s="3"/>
-      <c r="E269" s="16"/>
-      <c r="F269" s="17"/>
+      <c r="E269" s="17"/>
+      <c r="F269" s="18"/>
       <c r="G269" s="3" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="I269" s="7" t="s">
         <v>231</v>
@@ -12287,23 +12317,23 @@
     </row>
     <row r="270" ht="22.5" customHeight="1">
       <c r="A270" s="3" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B270" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ovid,  (-)</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D270" s="3"/>
-      <c r="E270" s="16"/>
-      <c r="F270" s="17"/>
+      <c r="E270" s="17"/>
+      <c r="F270" s="18"/>
       <c r="G270" s="3" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H270" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="I270" s="7" t="s">
         <v>16</v>
@@ -12313,17 +12343,17 @@
     </row>
     <row r="271" ht="22.5" customHeight="1">
       <c r="A271" s="3" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B271" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schweizer, Johann Caspar (1619-1688)</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="E271" s="5">
         <v>1619.0</v>
@@ -12335,34 +12365,34 @@
         <v>138</v>
       </c>
       <c r="H271" s="3" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="I271" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J271" s="8" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="K271" s="9"/>
     </row>
     <row r="272" ht="22.5" customHeight="1">
       <c r="A272" s="3" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B272" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Herder, Johann Heinrich (-)</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E272" s="16"/>
-      <c r="F272" s="17"/>
+      <c r="E272" s="17"/>
+      <c r="F272" s="18"/>
       <c r="G272" s="3" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H272" s="3"/>
       <c r="I272" s="13"/>
@@ -12371,23 +12401,23 @@
     </row>
     <row r="273" ht="22.5" customHeight="1">
       <c r="A273" s="3" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B273" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Elischa,  (-)</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D273" s="3"/>
-      <c r="E273" s="16"/>
-      <c r="F273" s="17"/>
+      <c r="E273" s="17"/>
+      <c r="F273" s="18"/>
       <c r="G273" s="3" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H273" s="3" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="I273" s="7" t="s">
         <v>249</v>
@@ -12397,23 +12427,23 @@
     </row>
     <row r="274" ht="22.5" customHeight="1">
       <c r="A274" s="3" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B274" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Johannes der Täufer,  (-)</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D274" s="3"/>
-      <c r="E274" s="16"/>
-      <c r="F274" s="17"/>
+      <c r="E274" s="17"/>
+      <c r="F274" s="18"/>
       <c r="G274" s="3" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="I274" s="7" t="s">
         <v>249</v>
@@ -12423,29 +12453,29 @@
     </row>
     <row r="275" ht="22.5" customHeight="1">
       <c r="A275" s="3" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B275" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caesar, Gaius Iulius (100 v. Chr.-44 v. Chr.)</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H275" s="3" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="I275" s="7" t="s">
         <v>16</v>
@@ -12455,23 +12485,23 @@
     </row>
     <row r="276" ht="22.5" customHeight="1">
       <c r="A276" s="3" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B276" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Helios,  (-)</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D276" s="3"/>
-      <c r="E276" s="16"/>
-      <c r="F276" s="17"/>
+      <c r="E276" s="17"/>
+      <c r="F276" s="18"/>
       <c r="G276" s="3" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H276" s="3" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="I276" s="7" t="s">
         <v>231</v>
@@ -12481,7 +12511,7 @@
     </row>
     <row r="277" ht="22.5" customHeight="1">
       <c r="A277" s="3" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B277" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12489,8 +12519,8 @@
       </c>
       <c r="C277" s="6"/>
       <c r="D277" s="3"/>
-      <c r="E277" s="16"/>
-      <c r="F277" s="17"/>
+      <c r="E277" s="17"/>
+      <c r="F277" s="18"/>
       <c r="G277" s="9"/>
       <c r="H277" s="3"/>
       <c r="I277" s="13"/>
@@ -12499,7 +12529,7 @@
     </row>
     <row r="278" ht="22.5" customHeight="1">
       <c r="A278" s="3" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B278" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12507,8 +12537,8 @@
       </c>
       <c r="C278" s="6"/>
       <c r="D278" s="3"/>
-      <c r="E278" s="16"/>
-      <c r="F278" s="17"/>
+      <c r="E278" s="17"/>
+      <c r="F278" s="18"/>
       <c r="G278" s="9"/>
       <c r="H278" s="3"/>
       <c r="I278" s="13"/>
@@ -12517,7 +12547,7 @@
     </row>
     <row r="279" ht="22.5" customHeight="1">
       <c r="A279" s="3" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B279" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12525,8 +12555,8 @@
       </c>
       <c r="C279" s="6"/>
       <c r="D279" s="3"/>
-      <c r="E279" s="16"/>
-      <c r="F279" s="17"/>
+      <c r="E279" s="17"/>
+      <c r="F279" s="18"/>
       <c r="G279" s="9"/>
       <c r="H279" s="3"/>
       <c r="I279" s="13"/>
@@ -12535,7 +12565,7 @@
     </row>
     <row r="280" ht="22.5" customHeight="1">
       <c r="A280" s="3" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B280" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12543,8 +12573,8 @@
       </c>
       <c r="C280" s="6"/>
       <c r="D280" s="3"/>
-      <c r="E280" s="16"/>
-      <c r="F280" s="17"/>
+      <c r="E280" s="17"/>
+      <c r="F280" s="18"/>
       <c r="G280" s="9"/>
       <c r="H280" s="3"/>
       <c r="I280" s="13"/>
@@ -12641,16 +12671,16 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -12661,179 +12691,179 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B2" s="22" t="str">
         <f t="shared" ref="B2:B102" si="1">CONCATENATE(C2)</f>
         <v>Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B3" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Basel</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B4" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Eidgenossenschaft</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1020</v>
-      </c>
-      <c r="E4" s="19"/>
+        <v>1021</v>
+      </c>
+      <c r="E4" s="20"/>
       <c r="F4" s="3" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B5" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Limmat</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D5" s="24"/>
       <c r="E5" s="7" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B6" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Weinfelden</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D6" s="24"/>
       <c r="E6" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B7" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Main</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="7" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B8" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Zürichsee</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D8" s="24"/>
       <c r="E8" s="7" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B9" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Thalwil</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B10" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bern</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B11" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Gottstatt</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="13"/>
@@ -12841,101 +12871,103 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B12" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Thorberg</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B13" s="23" t="str">
         <f t="shared" si="1"/>
         <v>London</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B14" s="23" t="str">
         <f t="shared" si="1"/>
         <v>England</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D14" s="24"/>
-      <c r="E14" s="13"/>
+      <c r="E14" s="7" t="s">
+        <v>1047</v>
+      </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B15" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bethlehem</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B16" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Parnass </v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="7" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B17" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Traubenberg</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="13"/>
@@ -12943,50 +12975,50 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B18" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Babylon</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B19" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Canaan</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="13"/>
       <c r="F19" s="3" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B20" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Ägypten</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="13"/>
@@ -12994,158 +13026,158 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B21" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Hermon</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="7" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B22" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Jerusalem</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B23" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Jordan</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="D23" s="24"/>
       <c r="E23" s="7" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B24" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Rotes Meer</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="D24" s="24"/>
       <c r="E24" s="7" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F24" s="9"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B25" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Juda</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="13"/>
       <c r="F25" s="3" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="B26" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Moab</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="13"/>
       <c r="F26" s="3" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B27" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Ammon</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="13"/>
       <c r="F27" s="3" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B28" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Zion</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="7" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B29" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Assur</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="13"/>
@@ -13153,101 +13185,101 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B30" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Israel</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="13"/>
       <c r="F30" s="3" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B31" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Nazaret</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B32" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Rom</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="13"/>
       <c r="F32" s="3" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="B33" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Samaria</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D33" s="24"/>
       <c r="E33" s="13"/>
       <c r="F33" s="3" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B34" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Kedronbach</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D34" s="24"/>
       <c r="E34" s="13"/>
       <c r="F34" s="3" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B35" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Garten von Getsemani</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="13"/>
@@ -13255,14 +13287,14 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B36" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Urdorf</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="13"/>
@@ -13270,14 +13302,14 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B37" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Geiren-Rein</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D37" s="24"/>
       <c r="E37" s="13"/>
@@ -13285,14 +13317,14 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B38" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Aeügst</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="D38" s="24"/>
       <c r="E38" s="13"/>
@@ -13300,14 +13332,14 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B39" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Riedt</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="13"/>
@@ -13315,14 +13347,14 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B40" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Europa</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="D40" s="24"/>
       <c r="E40" s="13"/>
@@ -13330,48 +13362,48 @@
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B41" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Osir</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="D41" s="24"/>
       <c r="E41" s="13"/>
       <c r="F41" s="3" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B42" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Basadingen</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D42" s="24"/>
       <c r="E42" s="13"/>
       <c r="F42" s="3" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B43" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Diessenhofen</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="D43" s="24"/>
       <c r="E43" s="13"/>
@@ -13379,50 +13411,50 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B44" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Rhein</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="7" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B45" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Arabisches Reich</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="D45" s="24"/>
       <c r="E45" s="13"/>
       <c r="F45" s="3" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="B46" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Libanon</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D46" s="24"/>
       <c r="E46" s="13"/>
@@ -13430,103 +13462,105 @@
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="B47" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Emmaus</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="D47" s="24"/>
       <c r="E47" s="13"/>
       <c r="F47" s="3" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="B48" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Helikon</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="7" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B49" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Pindos</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D49" s="24"/>
-      <c r="E49" s="13"/>
+      <c r="E49" s="7" t="s">
+        <v>1053</v>
+      </c>
       <c r="F49" s="3" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B50" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Neckar</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="D50" s="24"/>
       <c r="E50" s="7" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="B51" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Kurpfalz</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="D51" s="24"/>
       <c r="E51" s="13"/>
       <c r="F51" s="3" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="B52" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Eglisau</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="D52" s="24"/>
       <c r="E52" s="13"/>
@@ -13534,14 +13568,14 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B53" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Altenklingen</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="D53" s="24"/>
       <c r="E53" s="13"/>
@@ -13549,14 +13583,14 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B54" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Altorff</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="D54" s="24"/>
       <c r="E54" s="13"/>
@@ -13564,31 +13598,31 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="B55" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Glarus</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="D55" s="24"/>
       <c r="E55" s="13"/>
       <c r="F55" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="B56" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bergerkirche</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="D56" s="24"/>
       <c r="E56" s="13"/>
@@ -13596,31 +13630,31 @@
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="B57" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Sodom</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="D57" s="24"/>
       <c r="E57" s="13"/>
       <c r="F57" s="3" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="B58" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Haus zur Sonnenblume</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D58" s="24"/>
       <c r="E58" s="13"/>
@@ -13628,31 +13662,31 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="B59" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Thurn/ genennt von Geissen</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="13"/>
       <c r="F59" s="3" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="B60" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Constantinopel</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="13"/>
@@ -13660,118 +13694,118 @@
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="B61" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Stein am Rhein</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="13"/>
       <c r="F61" s="3" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="B62" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Marburg</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="D62" s="24"/>
       <c r="E62" s="13"/>
       <c r="F62" s="3" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="B63" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Elbląg</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="E63" s="13"/>
       <c r="F63" s="3" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="B64" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Preußen</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="13"/>
       <c r="F64" s="3" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="B65" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bad Baden</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="D65" s="24"/>
       <c r="E65" s="13"/>
       <c r="F65" s="3" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="B66" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bad Schinznach</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="D66" s="24"/>
       <c r="E66" s="13"/>
       <c r="F66" s="3" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="B67" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Gyrenbad</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D67" s="24"/>
       <c r="E67" s="13"/>
@@ -13779,48 +13813,48 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="B68" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Wängibad</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="D68" s="24"/>
       <c r="E68" s="13"/>
       <c r="F68" s="8" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="B69" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Aeugst</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="D69" s="24"/>
       <c r="E69" s="13"/>
       <c r="F69" s="3" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="B70" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bassersdorf</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="D70" s="24"/>
       <c r="E70" s="13"/>
@@ -13828,14 +13862,14 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="B71" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Hauptwil</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D71" s="24"/>
       <c r="E71" s="13"/>
@@ -13843,14 +13877,14 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B72" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Schaffhausen</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="D72" s="24"/>
       <c r="E72" s="13"/>
@@ -13858,65 +13892,65 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="B73" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Wädenswil</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="D73" s="24"/>
       <c r="E73" s="13"/>
       <c r="F73" s="3" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="B74" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Freie Ämter</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="D74" s="24"/>
       <c r="E74" s="13"/>
       <c r="F74" s="3" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="B75" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Grüningen</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="D75" s="24"/>
       <c r="E75" s="13"/>
       <c r="F75" s="3" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B76" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Kefikon</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="D76" s="24"/>
       <c r="E76" s="13"/>
@@ -13924,14 +13958,14 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="B77" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Maienfeld</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="D77" s="24"/>
       <c r="E77" s="13"/>
@@ -13939,14 +13973,14 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="B78" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Greifensee (Schloss)</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="D78" s="24"/>
       <c r="E78" s="13"/>
@@ -13954,31 +13988,31 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="B79" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Lindenhof (Zürich)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D79" s="24"/>
       <c r="E79" s="13"/>
       <c r="F79" s="3" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="B80" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Galg-Brunnen (Zürich)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="D80" s="24"/>
       <c r="E80" s="13"/>
@@ -13986,14 +14020,14 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="B81" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Altes Kornhaus (Zürich)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D81" s="24"/>
       <c r="E81" s="13"/>
@@ -14001,14 +14035,14 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B82" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Sparrenberg (Zürich)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="13"/>
@@ -14016,14 +14050,14 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="B83" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Thurgau</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="D83" s="24"/>
       <c r="E83" s="13"/>
@@ -14031,14 +14065,14 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="B84" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Niederlande</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="D84" s="24"/>
       <c r="E84" s="13"/>
@@ -14046,31 +14080,31 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="B85" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Holland</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D85" s="24"/>
       <c r="E85" s="13"/>
       <c r="F85" s="3" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="B86" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Wigoltingen</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="D86" s="24"/>
       <c r="E86" s="13"/>
@@ -14078,31 +14112,31 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B87" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Kastalia</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="D87" s="24"/>
       <c r="E87" s="13"/>
       <c r="F87" s="3" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B88" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Legerberg</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="D88" s="24"/>
       <c r="E88" s="13"/>
@@ -14110,48 +14144,48 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="B89" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Texel</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="D89" s="24"/>
       <c r="E89" s="13"/>
       <c r="F89" s="3" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="B90" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Vlie</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D90" s="24"/>
       <c r="E90" s="13"/>
       <c r="F90" s="3" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="B91" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Indien</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="D91" s="24"/>
       <c r="E91" s="13"/>
@@ -14159,14 +14193,14 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="B92" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Wien</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="D92" s="24"/>
       <c r="E92" s="13"/>
@@ -14174,14 +14208,14 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B93" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Deutschland</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="D93" s="24"/>
       <c r="E93" s="13"/>
@@ -14189,58 +14223,60 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="B94" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Ölberg</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="D94" s="24"/>
       <c r="E94" s="7" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="F94" s="3"/>
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="B95" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Dietikon</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D95" s="24"/>
-      <c r="E95" s="13"/>
+      <c r="E95" s="7" t="s">
+        <v>1251</v>
+      </c>
       <c r="F95" s="3" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="B96" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Winterthur</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="D96" s="24"/>
       <c r="E96" s="7" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F96" s="3"/>
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="B97" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14253,7 +14289,7 @@
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="B98" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14266,7 +14302,7 @@
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="B99" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14279,7 +14315,7 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="B100" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14292,7 +14328,7 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="B101" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14317,7 +14353,7 @@
   </sheetData>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" sqref="E2:E102">
-      <formula1>"Stadt,Gewässer,Berg"</formula1>
+      <formula1>"Stadt,Gewässer,Berg,Land,Politische Gemeinde"</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showDropDown="1" sqref="A2:A102 C2:C102 F2:F102"/>
   </dataValidations>
@@ -14351,25 +14387,25 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
@@ -14380,75 +14416,75 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="B2" s="25" t="str">
         <f t="shared" ref="B2:B30" si="1">CONCATENATE(C2)</f>
         <v>Teutsche Gedichte</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="I2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="B3" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Die Krafft der Gottseligkeit</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="B4" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Buch von Festen</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5"/>
@@ -14458,23 +14494,23 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="B5" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Der Psalter dess Königlichen Propheten Dauids/ Jn deutsche reymen verstendiglich vnd deutlich gebracht/ mit vorgehender anzeigung der reymen weise/ auch eines jeden Psalmes Jnhalt</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="13"/>
@@ -14482,73 +14518,73 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B6" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Hundert christliche Fäst-Predigen</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="B7" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Spiegel der Unermesslichen Gnad Gottes gegen den rewenden bussfertigen Sünderen/ Jn XLV. Predigen vber das XV. capitel Lucae/ vom verlohrnen Schaaf/ Pfenning/ vnd Sohn verfasset</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="B8" s="25" t="str">
         <f t="shared" si="1"/>
         <v>verteütschte Rueh- oder Fridens-uebung</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="24"/>
@@ -14558,98 +14594,98 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="B9" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Nähefelser-Fahrt: in zehen erbaulichen Jahrzeit-Predigen zu schuldigem Danck dem Höhesten für den im Jahr 1388 gemeinen Landleuthen dess lobl. Eydgnössischen Bundorths Glarus wider ihre Feind bey und umb Nähefels verliehenen Wundersieg </v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="10" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="B10" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Die vier Haubtpuncten der christlichen seligmachenden Religion: auf alle Sontag des gantzen Jahrs ordenlich abgetheilt, grundtlich nach der heiligen Schrifft erklärt und zur Erbawung gerichtet </v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="B11" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Architectura von Vestungen</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="8" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="B12" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Buech der Freunden Stammen</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="9"/>
@@ -14660,42 +14696,42 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="B13" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Christen-Spiegel, das ist, Bedenkliche Erinnerungen über die Beruoffspflichten aller Ständen </v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="B14" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Viergeticht</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="9"/>
@@ -14706,14 +14742,14 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="B15" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Regentenspiegel</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="9"/>
@@ -14724,18 +14760,18 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="B16" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Türckischer Jammerspiegel</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="3" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="F16" s="24"/>
       <c r="G16" s="9"/>
@@ -14744,17 +14780,17 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="B17" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Leitungs-faden</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="24"/>
@@ -14764,17 +14800,17 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="B18" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Buch von der Seelen-angſt Chriſti</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="24"/>
@@ -14784,17 +14820,17 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="B19" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Verſuchungs-gabe</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="24"/>
@@ -14804,14 +14840,14 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="B20" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Kriegsbüchlin</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="9"/>
@@ -14822,14 +14858,14 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="B21" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Buch der Psalmen</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="9"/>
@@ -14840,107 +14876,117 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="B22" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Sterbensspiegel/ das ist sonnenklare Vorstellung menschlicher Nichtigkeit durch alle Staend und Geschlechter</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="B23" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Warhaffte/ vnd in Gottes Wort wol gegründte Widerlegung Des newlich im Truck außgegangnen ohn-Catholischen Gesprächs von Religion oder Glaubens sachen/ geneñt der Augenspiegel</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>1348</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>1349</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>1350</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>1345</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="B24" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Augspiegels Wahrer Religion Erster Theil</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="B25" s="25" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="9"/>
+        <v>De kracht der Godsaligheyt</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>1367</v>
+      </c>
       <c r="H25" s="13"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="B26" s="25" t="str">
         <f t="shared" si="1"/>
@@ -14956,7 +15002,7 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="B27" s="25" t="str">
         <f t="shared" si="1"/>
@@ -14972,7 +15018,7 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
       <c r="B28" s="25" t="str">
         <f t="shared" si="1"/>
@@ -14988,7 +15034,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="B29" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15004,7 +15050,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="B30" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15060,19 +15106,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1365</v>
+        <v>1373</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1366</v>
+        <v>1374</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -15080,326 +15126,326 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="B2" s="25" t="str">
         <f t="shared" ref="B2:B24" si="1">CONCATENATE(C2)</f>
         <v>Rat Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="26" t="s">
-        <v>1369</v>
+        <v>1377</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1370</v>
+        <v>1378</v>
       </c>
       <c r="B3" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Fruchtbringende Gesellschaft</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1371</v>
+        <v>1379</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1372</v>
+        <v>1380</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>1373</v>
+        <v>1381</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1374</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1375</v>
+        <v>1383</v>
       </c>
       <c r="B4" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Deutschgesinnte Genossenschaft (Lilien-Zunft)</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1376</v>
+        <v>1384</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1377</v>
+        <v>1385</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1378</v>
+        <v>1386</v>
       </c>
       <c r="B5" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Parthenicum</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1379</v>
-      </c>
-      <c r="D5" s="17"/>
+        <v>1387</v>
+      </c>
+      <c r="D5" s="18"/>
       <c r="E5" s="13"/>
       <c r="F5" s="9"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1380</v>
+        <v>1388</v>
       </c>
       <c r="B6" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Carolinum Zürich</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1381</v>
+        <v>1389</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1382</v>
+        <v>1390</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="3" t="s">
-        <v>1383</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1384</v>
+        <v>1392</v>
       </c>
       <c r="B7" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Sanhedrin</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1385</v>
-      </c>
-      <c r="D7" s="17"/>
+        <v>1393</v>
+      </c>
+      <c r="D7" s="18"/>
       <c r="E7" s="13"/>
       <c r="F7" s="3" t="s">
-        <v>1386</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1387</v>
+        <v>1395</v>
       </c>
       <c r="B8" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Bürgerbibliothek Zürich</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1388</v>
+        <v>1396</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1389</v>
+        <v>1397</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="3" t="s">
-        <v>1390</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1391</v>
+        <v>1399</v>
       </c>
       <c r="B9" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Grossmünster</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1393</v>
+        <v>1401</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1394</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1395</v>
+        <v>1403</v>
       </c>
       <c r="B10" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Fraumünster Zürich</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1397</v>
+        <v>1405</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="3" t="s">
-        <v>1398</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1399</v>
+        <v>1407</v>
       </c>
       <c r="B11" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Hohe Schule Marburg</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1400</v>
-      </c>
-      <c r="D11" s="17"/>
+        <v>1408</v>
+      </c>
+      <c r="D11" s="18"/>
       <c r="E11" s="13"/>
       <c r="F11" s="9"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1401</v>
+        <v>1409</v>
       </c>
       <c r="B12" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Kartäuser</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1402</v>
-      </c>
-      <c r="D12" s="17"/>
+        <v>1410</v>
+      </c>
+      <c r="D12" s="18"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1403</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1404</v>
+        <v>1412</v>
       </c>
       <c r="B13" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C13" s="9"/>
-      <c r="D13" s="17"/>
+      <c r="D13" s="18"/>
       <c r="E13" s="13"/>
       <c r="F13" s="9"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1405</v>
+        <v>1413</v>
       </c>
       <c r="B14" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="17"/>
+      <c r="D14" s="18"/>
       <c r="E14" s="13"/>
       <c r="F14" s="9"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1406</v>
+        <v>1414</v>
       </c>
       <c r="B15" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C15" s="9"/>
-      <c r="D15" s="17"/>
+      <c r="D15" s="18"/>
       <c r="E15" s="13"/>
       <c r="F15" s="9"/>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="B16" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C16" s="9"/>
-      <c r="D16" s="17"/>
+      <c r="D16" s="18"/>
       <c r="E16" s="13"/>
       <c r="F16" s="9"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1408</v>
+        <v>1416</v>
       </c>
       <c r="B17" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="17"/>
+      <c r="D17" s="18"/>
       <c r="E17" s="13"/>
       <c r="F17" s="9"/>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1409</v>
+        <v>1417</v>
       </c>
       <c r="B18" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C18" s="9"/>
-      <c r="D18" s="17"/>
+      <c r="D18" s="18"/>
       <c r="E18" s="13"/>
       <c r="F18" s="9"/>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1410</v>
+        <v>1418</v>
       </c>
       <c r="B19" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C19" s="9"/>
-      <c r="D19" s="17"/>
+      <c r="D19" s="18"/>
       <c r="E19" s="13"/>
       <c r="F19" s="9"/>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1411</v>
+        <v>1419</v>
       </c>
       <c r="B20" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="17"/>
+      <c r="D20" s="18"/>
       <c r="E20" s="13"/>
       <c r="F20" s="9"/>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1412</v>
+        <v>1420</v>
       </c>
       <c r="B21" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C21" s="9"/>
-      <c r="D21" s="17"/>
+      <c r="D21" s="18"/>
       <c r="E21" s="13"/>
       <c r="F21" s="9"/>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1413</v>
+        <v>1421</v>
       </c>
       <c r="B22" s="25" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C22" s="9"/>
-      <c r="D22" s="17"/>
+      <c r="D22" s="18"/>
       <c r="E22" s="13"/>
       <c r="F22" s="9"/>
     </row>
@@ -15410,7 +15456,7 @@
         <v/>
       </c>
       <c r="C23" s="9"/>
-      <c r="D23" s="17"/>
+      <c r="D23" s="18"/>
       <c r="E23" s="13"/>
       <c r="F23" s="9"/>
     </row>
@@ -15421,7 +15467,7 @@
         <v/>
       </c>
       <c r="C24" s="9"/>
-      <c r="D24" s="17"/>
+      <c r="D24" s="18"/>
       <c r="E24" s="13"/>
       <c r="F24" s="9"/>
     </row>
@@ -15455,19 +15501,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1414</v>
+        <v>1422</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1415</v>
+        <v>1423</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1416</v>
+        <v>1424</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1417</v>
+        <v>1425</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -15475,99 +15521,99 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1418</v>
+        <v>1426</v>
       </c>
       <c r="B2" s="22" t="str">
         <f t="shared" ref="B2:B8" si="1">CONCATENATE(C2)</f>
         <v>Runs</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1419</v>
+        <v>1427</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1420</v>
+        <v>1428</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>1421</v>
+        <v>1429</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1422</v>
+        <v>1430</v>
       </c>
       <c r="B3" s="22" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C3" s="9"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1423</v>
+        <v>1431</v>
       </c>
       <c r="B4" s="22" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C4" s="9"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1424</v>
+        <v>1432</v>
       </c>
       <c r="B5" s="22" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C5" s="9"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
       <c r="F5" s="9"/>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1425</v>
+        <v>1433</v>
       </c>
       <c r="B6" s="22" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1426</v>
+        <v>1434</v>
       </c>
       <c r="B7" s="22" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C7" s="9"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1427</v>
+        <v>1435</v>
       </c>
       <c r="B8" s="22" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C8" s="9"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
       <c r="F8" s="9"/>
     </row>
   </sheetData>

--- a/gsheet/xlsx/entities.xlsx
+++ b/gsheet/xlsx/entities.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="1436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="1442">
   <si>
     <t>Person-ID</t>
   </si>
@@ -646,7 +646,7 @@
     <t>Christophe de</t>
   </si>
   <si>
-    <t>evtl. 1120134897 oder 1055548807</t>
+    <t>1055548807</t>
   </si>
   <si>
     <t>person_036</t>
@@ -875,10 +875,13 @@
     <t>Torquato</t>
   </si>
   <si>
-    <t>evtl. 118867687 oder 118620916</t>
+    <t>118620916</t>
   </si>
   <si>
     <t>Italienischer Dichter</t>
+  </si>
+  <si>
+    <t>https://de.wikipedia.org/wiki/Torquato_Tasso</t>
   </si>
   <si>
     <t>person_052</t>
@@ -3062,19 +3065,34 @@
     <t>Johann Caspar</t>
   </si>
   <si>
+    <t>1619/1620</t>
+  </si>
+  <si>
+    <t>1684/1688</t>
+  </si>
+  <si>
+    <t>11565402X</t>
+  </si>
+  <si>
     <t>Pfarrer, Professor für Hebräisch, Katechetik, Griechisch und Latei</t>
   </si>
   <si>
     <t>https://hls-dhs-dss.ch/de/articles/010844/2011-05-20/</t>
   </si>
   <si>
+    <t>Lebensdaten im HSL stimmen nicht mit Lebensdaten auf Lobid überein</t>
+  </si>
+  <si>
     <t>person_277</t>
   </si>
   <si>
     <t>Herder</t>
   </si>
   <si>
-    <t>??</t>
+    <t>1089544901</t>
+  </si>
+  <si>
+    <t>Pfarrer und Konrektor in der Pfalz</t>
   </si>
   <si>
     <t>person_278</t>
@@ -6682,28 +6700,30 @@
       <c r="I51" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J51" s="9"/>
+      <c r="J51" s="10" t="s">
+        <v>277</v>
+      </c>
       <c r="K51" s="9"/>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B52" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Saul,  (-)</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>249</v>
@@ -6713,23 +6733,23 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B53" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Abschalom,  (-)</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I53" s="7" t="s">
         <v>249</v>
@@ -6739,14 +6759,14 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B54" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Abimelechs,  (-)</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="5"/>
@@ -6761,20 +6781,20 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B55" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Abraham,  (-)</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>249</v>
@@ -6787,23 +6807,23 @@
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B56" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Aron,  (-)</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="I56" s="7" t="s">
         <v>249</v>
@@ -6813,14 +6833,14 @@
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B57" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Asaph,  (-)</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="5"/>
@@ -6837,20 +6857,20 @@
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B58" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Doëg,  (-)</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D58" s="3"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H58" s="9"/>
       <c r="I58" s="7" t="s">
@@ -6861,21 +6881,21 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B59" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ezechias,  (-)</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D59" s="3"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="9"/>
       <c r="H59" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I59" s="7" t="s">
         <v>249</v>
@@ -6885,23 +6905,23 @@
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B60" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jakob ("Israel"),  (-)</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
       <c r="G60" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>249</v>
@@ -6911,20 +6931,20 @@
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B61" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Adam,  (-)</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
       <c r="G61" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>249</v>
@@ -6937,20 +6957,20 @@
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B62" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Eva,  (-)</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>249</v>
@@ -6963,23 +6983,23 @@
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B63" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Barrabas,  (-)</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
       <c r="G63" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I63" s="7" t="s">
         <v>249</v>
@@ -6989,23 +7009,23 @@
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B64" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kajaphas,  (-)</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I64" s="7" t="s">
         <v>249</v>
@@ -7015,23 +7035,23 @@
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B65" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Judas Iskariot,  (-)</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
       <c r="G65" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I65" s="7" t="s">
         <v>249</v>
@@ -7041,21 +7061,21 @@
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B66" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gabriel,  (-)</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
       <c r="G66" s="9"/>
       <c r="H66" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I66" s="7" t="s">
         <v>249</v>
@@ -7065,23 +7085,23 @@
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B67" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Herodes,  (-)</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
       <c r="G67" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I67" s="7" t="s">
         <v>249</v>
@@ -7091,23 +7111,23 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B68" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maria von Nazaret,  (-)</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
       <c r="G68" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I68" s="7" t="s">
         <v>249</v>
@@ -7117,14 +7137,14 @@
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B69" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Nikodemus,  (-)</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="5"/>
@@ -7141,25 +7161,25 @@
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B70" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pilatus, Pontius (-)</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
       <c r="G70" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I70" s="7" t="s">
         <v>249</v>
@@ -7169,23 +7189,23 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B71" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Titus,  (-)</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
       <c r="G71" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I71" s="7" t="s">
         <v>16</v>
@@ -7195,23 +7215,23 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B72" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simon Petrus,  (-)</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
       <c r="G72" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I72" s="7" t="s">
         <v>249</v>
@@ -7221,7 +7241,7 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B73" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7234,10 +7254,10 @@
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I73" s="7" t="s">
         <v>249</v>
@@ -7247,21 +7267,21 @@
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B74" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jakob,  (-)</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="9"/>
       <c r="H74" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I74" s="7" t="s">
         <v>249</v>
@@ -7271,21 +7291,21 @@
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B75" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jonas,  (-)</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="9"/>
       <c r="H75" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I75" s="7" t="s">
         <v>249</v>
@@ -7295,14 +7315,14 @@
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B76" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Joseph,  (-)</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="5"/>
@@ -7319,14 +7339,14 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B77" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Saul, dessen Sohn,  (-)</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="5"/>
@@ -7343,20 +7363,20 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B78" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Satan,  (-)</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
       <c r="G78" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>249</v>
@@ -7369,14 +7389,14 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B79" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Abigail,  (-)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="5"/>
@@ -7393,14 +7413,14 @@
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B80" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hanna,  (-)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="5"/>
@@ -7417,14 +7437,14 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B81" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Susanna,  (-)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="5"/>
@@ -7441,14 +7461,14 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B82" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esther,  (-)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="5"/>
@@ -7465,14 +7485,14 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B83" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jaël,  (-)</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="5"/>
@@ -7489,7 +7509,7 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B84" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7513,21 +7533,21 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B85" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Asarias,  (-)</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D85" s="3"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
       <c r="G85" s="9"/>
       <c r="H85" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I85" s="7" t="s">
         <v>249</v>
@@ -7537,23 +7557,23 @@
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B86" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Boreas,  (-)</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I86" s="7" t="s">
         <v>231</v>
@@ -7563,23 +7583,23 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B87" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ceres,  (-)</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
       <c r="G87" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I87" s="7" t="s">
         <v>231</v>
@@ -7589,23 +7609,23 @@
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B88" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Amor,  (-)</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I88" s="7" t="s">
         <v>231</v>
@@ -7615,23 +7635,23 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B89" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sokrates,  (-)</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
       <c r="G89" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I89" s="7" t="s">
         <v>16</v>
@@ -7641,23 +7661,23 @@
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B90" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Xantippe,  (-)</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I90" s="7" t="s">
         <v>16</v>
@@ -7667,23 +7687,23 @@
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B91" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mars,  (-)</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
       <c r="G91" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="I91" s="7" t="s">
         <v>231</v>
@@ -7693,23 +7713,23 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B92" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Apollo (Phoebus),  (-)</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
       <c r="G92" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I92" s="7" t="s">
         <v>231</v>
@@ -7719,21 +7739,21 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B93" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sirius,  (-)</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
       <c r="G93" s="9"/>
       <c r="H93" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I93" s="7" t="s">
         <v>231</v>
@@ -7743,14 +7763,14 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B94" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rebecca,  (-)</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="5"/>
@@ -7767,21 +7787,21 @@
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B95" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Asteria,  (-)</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
       <c r="G95" s="9"/>
       <c r="H95" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I95" s="13"/>
       <c r="J95" s="9"/>
@@ -7789,21 +7809,21 @@
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B96" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sylvia,  (-)</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
       <c r="G96" s="9"/>
       <c r="H96" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I96" s="13"/>
       <c r="J96" s="9"/>
@@ -7811,21 +7831,21 @@
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B97" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Felicitas,  (-)</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
       <c r="G97" s="9"/>
       <c r="H97" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="I97" s="13"/>
       <c r="J97" s="9"/>
@@ -7833,21 +7853,21 @@
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B98" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dorothea,  (-)</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="9"/>
       <c r="H98" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I98" s="13"/>
       <c r="J98" s="9"/>
@@ -7855,7 +7875,7 @@
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B99" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7869,7 +7889,7 @@
       <c r="F99" s="5"/>
       <c r="G99" s="9"/>
       <c r="H99" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="I99" s="13"/>
       <c r="J99" s="9"/>
@@ -7877,14 +7897,14 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B100" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sara,  (-)</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="5"/>
@@ -7901,23 +7921,23 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B101" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hesiodus,  (-)</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5"/>
       <c r="G101" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I101" s="13"/>
       <c r="J101" s="9"/>
@@ -7925,23 +7945,23 @@
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B102" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Parmenides,  (-)</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
       <c r="G102" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I102" s="13"/>
       <c r="J102" s="9"/>
@@ -7949,20 +7969,20 @@
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B103" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salomon,  (-)</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D103" s="3"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
       <c r="G103" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>249</v>
@@ -7975,20 +7995,20 @@
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B104" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Isaak,  (-)</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
       <c r="G104" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>249</v>
@@ -8001,14 +8021,14 @@
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B105" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rahel,  (-)</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="5"/>
@@ -8025,20 +8045,20 @@
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B106" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hiob,  (-)</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5"/>
       <c r="G106" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>249</v>
@@ -8051,14 +8071,14 @@
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B107" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simson,  (-)</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="5"/>
@@ -8075,23 +8095,23 @@
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B108" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ben Sira,  (-)</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
       <c r="G108" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I108" s="13"/>
       <c r="J108" s="9"/>
@@ -8099,20 +8119,20 @@
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B109" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wilhelm Tell,  (-)</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D109" s="3"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
       <c r="G109" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="13"/>
@@ -8121,23 +8141,23 @@
     </row>
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B110" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zephyr,  (-)</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D110" s="3"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
       <c r="G110" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I110" s="7" t="s">
         <v>231</v>
@@ -8147,7 +8167,7 @@
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B111" s="4" t="str">
         <f t="shared" si="1"/>
@@ -8161,7 +8181,7 @@
       <c r="F111" s="5"/>
       <c r="G111" s="9"/>
       <c r="H111" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I111" s="7" t="s">
         <v>249</v>
@@ -8171,21 +8191,21 @@
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B112" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Friedensfürst,  (-)</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
       <c r="G112" s="9"/>
       <c r="H112" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I112" s="13"/>
       <c r="J112" s="9"/>
@@ -8193,21 +8213,21 @@
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B113" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gracchus,  (-)</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
       <c r="G113" s="9"/>
       <c r="H113" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I113" s="13"/>
       <c r="J113" s="9"/>
@@ -8215,21 +8235,21 @@
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B114" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gracchus, dessen Frau,  (-)</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
       <c r="G114" s="9"/>
       <c r="H114" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I114" s="13"/>
       <c r="J114" s="9"/>
@@ -8237,20 +8257,20 @@
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B115" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Moses,  (-)</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D115" s="3"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
       <c r="G115" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>249</v>
@@ -8263,23 +8283,23 @@
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B116" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orestes,  (-)</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
       <c r="G116" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I116" s="7" t="s">
         <v>231</v>
@@ -8289,23 +8309,23 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B117" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pylades,  (-)</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
       <c r="G117" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I117" s="7" t="s">
         <v>231</v>
@@ -8315,21 +8335,21 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B118" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thurik,  (-)</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
       <c r="G118" s="9"/>
       <c r="H118" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I118" s="7" t="s">
         <v>231</v>
@@ -8339,21 +8359,21 @@
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B119" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Midas,  (-)</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
       <c r="G119" s="9"/>
       <c r="H119" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I119" s="7" t="s">
         <v>231</v>
@@ -8363,49 +8383,49 @@
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B120" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simon,  (-)</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
       <c r="G120" s="9"/>
       <c r="H120" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I120" s="7" t="s">
         <v>231</v>
       </c>
       <c r="J120" s="9"/>
       <c r="K120" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B121" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Damokles,  (-)</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
       <c r="G121" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I121" s="13"/>
       <c r="J121" s="9"/>
@@ -8413,23 +8433,23 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B122" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dionysius I. von Syrakus,  (-)</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
       <c r="G122" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I122" s="13"/>
       <c r="J122" s="9"/>
@@ -8437,23 +8457,23 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B123" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kleopatra VII.,  (-)</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
       <c r="G123" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I123" s="13"/>
       <c r="J123" s="9"/>
@@ -8461,23 +8481,23 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B124" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Marcus Antonius,  (-)</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D124" s="3"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
       <c r="G124" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I124" s="13"/>
       <c r="J124" s="9"/>
@@ -8485,23 +8505,23 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B125" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klio,  (-)</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
       <c r="G125" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I125" s="7" t="s">
         <v>231</v>
@@ -8511,23 +8531,23 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B126" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Flora,  (-)</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
       <c r="G126" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I126" s="7" t="s">
         <v>231</v>
@@ -8537,14 +8557,14 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B127" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dorothea,  (-)</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D127" s="3"/>
       <c r="E127" s="5"/>
@@ -8557,21 +8577,21 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B128" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. J. V.,  (-)</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
       <c r="G128" s="9"/>
       <c r="H128" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I128" s="7" t="s">
         <v>16</v>
@@ -8581,21 +8601,21 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B129" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. J. V., dessen Frau,  (-)</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
       <c r="G129" s="9"/>
       <c r="H129" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I129" s="7" t="s">
         <v>16</v>
@@ -8605,21 +8625,21 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B130" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sch. H.,  (-)</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
       <c r="G130" s="9"/>
       <c r="H130" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I130" s="7" t="s">
         <v>16</v>
@@ -8629,14 +8649,14 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="3" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B131" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser, Johann Heinrich (1600-1669)</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>43</v>
@@ -8648,66 +8668,66 @@
         <v>1669.0</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H131" s="14" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I131" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J131" s="15" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K131" s="9"/>
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B132" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser-Ziegler, Jahel (-)</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
       <c r="G132" s="9"/>
       <c r="H132" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I132" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K132" s="9"/>
     </row>
     <row r="133" ht="22.5" customHeight="1">
       <c r="A133" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B133" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caspar W.,  (-)</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
       <c r="G133" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I133" s="7" t="s">
         <v>16</v>
@@ -8717,21 +8737,21 @@
     </row>
     <row r="134" ht="22.5" customHeight="1">
       <c r="A134" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B134" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esther O.,  (-)</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
       <c r="G134" s="9"/>
       <c r="H134" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I134" s="7" t="s">
         <v>16</v>
@@ -8741,14 +8761,14 @@
     </row>
     <row r="135" ht="22.5" customHeight="1">
       <c r="A135" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B135" s="4" t="str">
         <f t="shared" si="1"/>
         <v>G. H.,  (-)</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="5"/>
@@ -8763,21 +8783,21 @@
     </row>
     <row r="136" ht="22.5" customHeight="1">
       <c r="A136" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B136" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. C.,  (-)</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
       <c r="G136" s="9"/>
       <c r="H136" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I136" s="7" t="s">
         <v>16</v>
@@ -8787,17 +8807,17 @@
     </row>
     <row r="137" ht="22.5" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B137" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Hercules von (1617-1686)</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E137" s="5">
         <v>1617.0</v>
@@ -8806,30 +8826,30 @@
         <v>1686.0</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H137" s="3"/>
       <c r="I137" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K137" s="9"/>
     </row>
     <row r="138" ht="22.5" customHeight="1">
       <c r="A138" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B138" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Barbara Dorothea von (1629-1660)</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E138" s="5">
         <v>1629.0</v>
@@ -8839,26 +8859,26 @@
       </c>
       <c r="G138" s="9"/>
       <c r="H138" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="I138" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J138" s="8" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K138" s="9"/>
     </row>
     <row r="139" ht="22.5" customHeight="1">
       <c r="A139" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B139" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. L.,  (-)</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="5"/>
@@ -8873,21 +8893,21 @@
     </row>
     <row r="140" ht="22.5" customHeight="1">
       <c r="A140" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B140" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. A.,  (-)</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
       <c r="G140" s="9"/>
       <c r="H140" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I140" s="7" t="s">
         <v>16</v>
@@ -8897,21 +8917,21 @@
     </row>
     <row r="141" ht="22.5" customHeight="1">
       <c r="A141" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B141" s="4" t="str">
         <f t="shared" si="1"/>
         <v>B. M.,  (-)</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D141" s="3"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
       <c r="G141" s="9"/>
       <c r="H141" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I141" s="7" t="s">
         <v>16</v>
@@ -8921,73 +8941,73 @@
     </row>
     <row r="142" ht="22.5" customHeight="1">
       <c r="A142" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B142" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. H.,  (-)</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="9"/>
       <c r="H142" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I142" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="K142" s="9"/>
     </row>
     <row r="143" ht="22.5" customHeight="1">
       <c r="A143" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B143" s="4" t="str">
         <f t="shared" si="1"/>
         <v>D. M.,  (-)</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D143" s="3"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
       <c r="G143" s="9"/>
       <c r="H143" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="I143" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="K143" s="9"/>
     </row>
     <row r="144" ht="22.5" customHeight="1">
       <c r="A144" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B144" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gottfrid,  (-)</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
       <c r="G144" s="9"/>
       <c r="H144" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I144" s="7" t="s">
         <v>16</v>
@@ -8997,21 +9017,21 @@
     </row>
     <row r="145" ht="22.5" customHeight="1">
       <c r="A145" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B145" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jakob,  (-)</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D145" s="3"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
       <c r="G145" s="9"/>
       <c r="H145" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="I145" s="7" t="s">
         <v>16</v>
@@ -9021,21 +9041,21 @@
     </row>
     <row r="146" ht="22.5" customHeight="1">
       <c r="A146" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B146" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. Schw.,  (-)</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D146" s="3"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
       <c r="G146" s="9"/>
       <c r="H146" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I146" s="7" t="s">
         <v>16</v>
@@ -9045,21 +9065,21 @@
     </row>
     <row r="147" ht="22.5" customHeight="1">
       <c r="A147" s="3" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B147" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. K.,  (-)</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
       <c r="G147" s="9"/>
       <c r="H147" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I147" s="7" t="s">
         <v>16</v>
@@ -9069,14 +9089,14 @@
     </row>
     <row r="148" ht="22.5" customHeight="1">
       <c r="A148" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B148" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ott, Hans Heinrich (-)</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>69</v>
@@ -9093,14 +9113,14 @@
     </row>
     <row r="149" ht="22.5" customHeight="1">
       <c r="A149" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B149" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. W.,  (-)</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D149" s="3"/>
       <c r="E149" s="5"/>
@@ -9115,21 +9135,21 @@
     </row>
     <row r="150" ht="22.5" customHeight="1">
       <c r="A150" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B150" s="4" t="str">
         <f t="shared" si="1"/>
         <v>V. L.,  (-)</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
       <c r="G150" s="9"/>
       <c r="H150" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I150" s="7" t="s">
         <v>16</v>
@@ -9139,14 +9159,14 @@
     </row>
     <row r="151" ht="22.5" customHeight="1">
       <c r="A151" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B151" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. Sch.,  (-)</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D151" s="3"/>
       <c r="E151" s="5"/>
@@ -9161,21 +9181,21 @@
     </row>
     <row r="152" ht="22.5" customHeight="1">
       <c r="A152" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B152" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. H.,  (-)</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
       <c r="G152" s="9"/>
       <c r="H152" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="I152" s="7" t="s">
         <v>16</v>
@@ -9185,14 +9205,14 @@
     </row>
     <row r="153" ht="22.5" customHeight="1">
       <c r="A153" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B153" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. H.,  (-)</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="5"/>
@@ -9203,55 +9223,55 @@
         <v>16</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="K153" s="9"/>
     </row>
     <row r="154" ht="22.5" customHeight="1">
       <c r="A154" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B154" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. W.,  (-)</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="9"/>
       <c r="H154" s="3" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I154" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="K154" s="9"/>
     </row>
     <row r="155" ht="22.5" customHeight="1">
       <c r="A155" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B155" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Koller, Elisabeth (-)</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
       <c r="G155" s="9"/>
       <c r="H155" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="I155" s="7" t="s">
         <v>16</v>
@@ -9263,17 +9283,17 @@
     </row>
     <row r="156" ht="22.5" customHeight="1">
       <c r="A156" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B156" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lobwasser, Ambrosius (1515-1585)</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E156" s="5">
         <v>1515.0</v>
@@ -9282,10 +9302,10 @@
         <v>1585.0</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="I156" s="7" t="s">
         <v>16</v>
@@ -9295,17 +9315,17 @@
     </row>
     <row r="157" ht="22.5" customHeight="1">
       <c r="A157" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B157" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vollenweider, Jakob (1594-1647)</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E157" s="5">
         <v>1594.0</v>
@@ -9314,10 +9334,10 @@
         <v>1647.0</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I157" s="7" t="s">
         <v>16</v>
@@ -9327,7 +9347,7 @@
     </row>
     <row r="158" ht="22.5" customHeight="1">
       <c r="A158" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B158" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9337,7 +9357,7 @@
         <v>223</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E158" s="5">
         <v>1606.0</v>
@@ -9346,7 +9366,7 @@
         <v>1660.0</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>226</v>
@@ -9359,17 +9379,17 @@
     </row>
     <row r="159" ht="22.5" customHeight="1">
       <c r="A159" s="3" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B159" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Burkhard, Hans Konrad (1613-1681)</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E159" s="5">
         <v>1613.0</v>
@@ -9378,10 +9398,10 @@
         <v>1681.0</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I159" s="7" t="s">
         <v>16</v>
@@ -9391,14 +9411,14 @@
     </row>
     <row r="160" ht="22.5" customHeight="1">
       <c r="A160" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B160" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ardüser, Johann (1585-1665)</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>107</v>
@@ -9410,40 +9430,40 @@
         <v>1665.0</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="I160" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J160" s="12" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K160" s="9"/>
     </row>
     <row r="161" ht="22.5" customHeight="1">
       <c r="A161" s="3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B161" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hegner, Diethelm  (-)</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
       <c r="G161" s="3" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="I161" s="7" t="s">
         <v>16</v>
@@ -9453,17 +9473,17 @@
     </row>
     <row r="162" ht="22.5" customHeight="1">
       <c r="A162" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B162" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Trigland, Jacobus (1583-1654)</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E162" s="16">
         <v>1583.0</v>
@@ -9472,10 +9492,10 @@
         <v>1654.0</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="I162" s="7" t="s">
         <v>16</v>
@@ -9485,17 +9505,17 @@
     </row>
     <row r="163" ht="22.5" customHeight="1">
       <c r="A163" s="3" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B163" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwinger, D. (-)</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E163" s="5"/>
       <c r="F163" s="5"/>
@@ -9509,14 +9529,14 @@
     </row>
     <row r="164" ht="22.5" customHeight="1">
       <c r="A164" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B164" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Genathen, Johann Jakob (-)</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>31</v>
@@ -9524,10 +9544,10 @@
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
       <c r="G164" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I164" s="7" t="s">
         <v>16</v>
@@ -9537,7 +9557,7 @@
     </row>
     <row r="165" ht="22.5" customHeight="1">
       <c r="A165" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B165" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9563,27 +9583,27 @@
     </row>
     <row r="166" ht="22.5" customHeight="1">
       <c r="A166" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B166" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hess, Caspar (-1631)</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E166" s="5"/>
       <c r="F166" s="5">
         <v>1631.0</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="I166" s="7" t="s">
         <v>16</v>
@@ -9593,14 +9613,14 @@
     </row>
     <row r="167" ht="22.5" customHeight="1">
       <c r="A167" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B167" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wolfen, Hans Jakob (-)</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>219</v>
@@ -9617,22 +9637,22 @@
     </row>
     <row r="168" ht="22.5" customHeight="1">
       <c r="A168" s="3" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B168" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöri, Felix Christian (-)</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E168" s="17"/>
       <c r="F168" s="18"/>
       <c r="G168" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H168" s="3"/>
       <c r="I168" s="7" t="s">
@@ -9643,7 +9663,7 @@
     </row>
     <row r="169" ht="22.5" customHeight="1">
       <c r="A169" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B169" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9653,7 +9673,7 @@
         <v>12</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E169" s="17"/>
       <c r="F169" s="5">
@@ -9669,21 +9689,21 @@
     </row>
     <row r="170" ht="22.5" customHeight="1">
       <c r="A170" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B170" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther,  (-)</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D170" s="3"/>
       <c r="E170" s="17"/>
       <c r="F170" s="18"/>
       <c r="G170" s="9"/>
       <c r="H170" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="I170" s="7" t="s">
         <v>16</v>
@@ -9693,23 +9713,23 @@
     </row>
     <row r="171" ht="22.5" customHeight="1">
       <c r="A171" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B171" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Weiss, Caspar (-)</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E171" s="17"/>
       <c r="F171" s="18"/>
       <c r="G171" s="9"/>
       <c r="H171" s="19" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="I171" s="7" t="s">
         <v>16</v>
@@ -9719,7 +9739,7 @@
     </row>
     <row r="172" ht="22.5" customHeight="1">
       <c r="A172" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B172" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9733,7 +9753,7 @@
       <c r="F172" s="18"/>
       <c r="G172" s="9"/>
       <c r="H172" s="19" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I172" s="7" t="s">
         <v>16</v>
@@ -9743,21 +9763,21 @@
     </row>
     <row r="173" ht="22.5" customHeight="1">
       <c r="A173" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B173" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bas,  (-)</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="17"/>
       <c r="F173" s="18"/>
       <c r="G173" s="9"/>
       <c r="H173" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I173" s="20"/>
       <c r="J173" s="9"/>
@@ -9765,14 +9785,14 @@
     </row>
     <row r="174" ht="22.5" customHeight="1">
       <c r="A174" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B174" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H.H.J. Gw. s. A.Z.Fr.M.,  (-)</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D174" s="3"/>
       <c r="E174" s="17"/>
@@ -9787,23 +9807,23 @@
     </row>
     <row r="175" ht="22.5" customHeight="1">
       <c r="A175" s="3" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B175" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hofm., Joh. (-)</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E175" s="17"/>
       <c r="F175" s="18"/>
       <c r="G175" s="9"/>
       <c r="H175" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I175" s="7" t="s">
         <v>16</v>
@@ -9813,22 +9833,22 @@
     </row>
     <row r="176" ht="22.5" customHeight="1">
       <c r="A176" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B176" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Cyrene, Simon von (-)</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E176" s="17"/>
       <c r="F176" s="18"/>
       <c r="G176" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>249</v>
@@ -9841,23 +9861,23 @@
     </row>
     <row r="177" ht="22.5" customHeight="1">
       <c r="A177" s="3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B177" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thomas,  (-)</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="17"/>
       <c r="F177" s="18"/>
       <c r="G177" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I177" s="7" t="s">
         <v>249</v>
@@ -9867,23 +9887,23 @@
     </row>
     <row r="178" ht="22.5" customHeight="1">
       <c r="A178" s="3" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B178" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Phaeton,  (-)</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="17"/>
       <c r="F178" s="18"/>
       <c r="G178" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I178" s="7" t="s">
         <v>231</v>
@@ -9893,14 +9913,14 @@
     </row>
     <row r="179" ht="22.5" customHeight="1">
       <c r="A179" s="3" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B179" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lukas,  (-)</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D179" s="3"/>
       <c r="E179" s="17"/>
@@ -9917,20 +9937,20 @@
     </row>
     <row r="180" ht="22.5" customHeight="1">
       <c r="A180" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B180" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pallas Athena,  (-)</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="17"/>
       <c r="F180" s="18"/>
       <c r="G180" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>231</v>
@@ -9943,23 +9963,23 @@
     </row>
     <row r="181" ht="22.5" customHeight="1">
       <c r="A181" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B181" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bacchus,  (-)</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D181" s="3"/>
       <c r="E181" s="17"/>
       <c r="F181" s="18"/>
       <c r="G181" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I181" s="7" t="s">
         <v>231</v>
@@ -9969,23 +9989,23 @@
     </row>
     <row r="182" ht="22.5" customHeight="1">
       <c r="A182" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B182" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Darius I.,  (-)</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="17"/>
       <c r="F182" s="18"/>
       <c r="G182" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I182" s="7" t="s">
         <v>16</v>
@@ -9995,23 +10015,23 @@
     </row>
     <row r="183" ht="22.5" customHeight="1">
       <c r="A183" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B183" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kyros II.,  (-)</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D183" s="3"/>
       <c r="E183" s="17"/>
       <c r="F183" s="18"/>
       <c r="G183" s="3" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I183" s="7" t="s">
         <v>16</v>
@@ -10021,25 +10041,25 @@
     </row>
     <row r="184" ht="22.5" customHeight="1">
       <c r="A184" s="3" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B184" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hippo, Augustinus von (-)</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E184" s="17"/>
       <c r="F184" s="18"/>
       <c r="G184" s="3" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="I184" s="7" t="s">
         <v>16</v>
@@ -10049,20 +10069,20 @@
     </row>
     <row r="185" ht="22.5" customHeight="1">
       <c r="A185" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B185" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lazarus,  (-)</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D185" s="3"/>
       <c r="E185" s="17"/>
       <c r="F185" s="18"/>
       <c r="G185" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>249</v>
@@ -10075,20 +10095,20 @@
     </row>
     <row r="186" ht="22.5" customHeight="1">
       <c r="A186" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B186" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lot,  (-)</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="17"/>
       <c r="F186" s="18"/>
       <c r="G186" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>249</v>
@@ -10101,21 +10121,21 @@
     </row>
     <row r="187" ht="22.5" customHeight="1">
       <c r="A187" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B187" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hans Rudolf,  (-)</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D187" s="3"/>
       <c r="E187" s="17"/>
       <c r="F187" s="18"/>
       <c r="G187" s="9"/>
       <c r="H187" s="3" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="I187" s="7" t="s">
         <v>16</v>
@@ -10125,7 +10145,7 @@
     </row>
     <row r="188" ht="22.5" customHeight="1">
       <c r="A188" s="3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B188" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10138,16 +10158,16 @@
         <v>13</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F188" s="5">
         <v>1690.0</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="I188" s="7" t="s">
         <v>16</v>
@@ -10157,17 +10177,17 @@
     </row>
     <row r="189" ht="22.5" customHeight="1">
       <c r="A189" s="3" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B189" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bachofen, Johann Ulrich (1643-1700)</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E189" s="5">
         <v>1643.0</v>
@@ -10176,7 +10196,7 @@
         <v>1700.0</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>226</v>
@@ -10189,17 +10209,17 @@
     </row>
     <row r="190" ht="22.5" customHeight="1">
       <c r="A190" s="3" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B190" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grebel, Hans Konrad (1615-1674)</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E190" s="5">
         <v>1615.0</v>
@@ -10208,57 +10228,57 @@
         <v>1674.0</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I190" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="K190" s="9"/>
     </row>
     <row r="191" ht="22.5" customHeight="1">
       <c r="A191" s="3" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B191" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gossweiler, Emerentia (-)</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E191" s="17"/>
       <c r="F191" s="18"/>
       <c r="G191" s="9"/>
       <c r="H191" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="I191" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J191" s="8" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="K191" s="9"/>
     </row>
     <row r="192" ht="22.5" customHeight="1">
       <c r="A192" s="3" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B192" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lochmann, Heinrich (1613-1667)</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>37</v>
@@ -10270,29 +10290,29 @@
         <v>1667.0</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J192" s="8" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="K192" s="9"/>
     </row>
     <row r="193" ht="22.5" customHeight="1">
       <c r="A193" s="3" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B193" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Johann Jakob (1602-1668)</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>31</v>
@@ -10304,109 +10324,109 @@
         <v>1668.0</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J193" s="8" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="K193" s="9"/>
     </row>
     <row r="194" ht="22.5" customHeight="1">
       <c r="A194" s="3" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B194" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orelli, Anna (-)</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E194" s="17"/>
       <c r="F194" s="18"/>
       <c r="G194" s="9"/>
       <c r="H194" s="3" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="I194" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J194" s="10" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="K194" s="9"/>
     </row>
     <row r="195" ht="22.5" customHeight="1">
       <c r="A195" s="3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B195" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. E. H.,  (-)</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="17"/>
       <c r="F195" s="18"/>
       <c r="G195" s="9"/>
       <c r="H195" s="3" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J195" s="21" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K195" s="9"/>
     </row>
     <row r="196" ht="22.5" customHeight="1">
       <c r="A196" s="3" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B196" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. H.,  (-)</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D196" s="3"/>
       <c r="E196" s="17"/>
       <c r="F196" s="18"/>
       <c r="G196" s="9"/>
       <c r="H196" s="3" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="I196" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J196" s="21" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="K196" s="9"/>
     </row>
     <row r="197" ht="22.5" customHeight="1">
       <c r="A197" s="3" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B197" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grob, Hans Jakob (-)</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>219</v>
@@ -10415,19 +10435,19 @@
       <c r="F197" s="18"/>
       <c r="G197" s="9"/>
       <c r="H197" s="3" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="I197" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J197" s="8" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="K197" s="9"/>
     </row>
     <row r="198" ht="22.5" customHeight="1">
       <c r="A198" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B198" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10437,7 +10457,7 @@
         <v>68</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E198" s="17"/>
       <c r="F198" s="18"/>
@@ -10447,23 +10467,23 @@
         <v>16</v>
       </c>
       <c r="J198" s="8" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="K198" s="9"/>
     </row>
     <row r="199" ht="22.5" customHeight="1">
       <c r="A199" s="3" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B199" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klingler, Kaspar (-)</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E199" s="17"/>
       <c r="F199" s="18"/>
@@ -10473,23 +10493,23 @@
         <v>16</v>
       </c>
       <c r="J199" s="8" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K199" s="9"/>
     </row>
     <row r="200" ht="22.5" customHeight="1">
       <c r="A200" s="3" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B200" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöndli, Dorothea (-)</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E200" s="17"/>
       <c r="F200" s="18"/>
@@ -10499,23 +10519,23 @@
         <v>16</v>
       </c>
       <c r="J200" s="8" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K200" s="9"/>
     </row>
     <row r="201" ht="22.5" customHeight="1">
       <c r="A201" s="3" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B201" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Hans Caspar (1617-1691)</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E201" s="5">
         <v>1617.0</v>
@@ -10524,32 +10544,32 @@
         <v>1691.0</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="K201" s="9"/>
     </row>
     <row r="202" ht="22.5" customHeight="1">
       <c r="A202" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B202" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Salomon (1580-1652)</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E202" s="5">
         <v>1580.0</v>
@@ -10558,60 +10578,60 @@
         <v>1652.0</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J202" s="8" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="K202" s="9"/>
     </row>
     <row r="203" ht="22.5" customHeight="1">
       <c r="A203" s="3" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B203" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis-Soglio, Maria Ursina von  (-)</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E203" s="17"/>
       <c r="F203" s="18"/>
       <c r="G203" s="9"/>
       <c r="H203" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J203" s="8" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="K203" s="9"/>
     </row>
     <row r="204" ht="22.5" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B204" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Brügger, Andreas von (1588-1653)</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E204" s="5">
         <v>1588.0</v>
@@ -10620,36 +10640,36 @@
         <v>1653.0</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="I204" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J204" s="8" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="K204" s="9"/>
     </row>
     <row r="205" ht="22.5" customHeight="1">
       <c r="A205" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B205" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Anhorn,  (-)</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D205" s="3"/>
       <c r="E205" s="17"/>
       <c r="F205" s="18"/>
       <c r="G205" s="9"/>
       <c r="H205" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="I205" s="7" t="s">
         <v>16</v>
@@ -10659,23 +10679,23 @@
     </row>
     <row r="206" ht="22.5" customHeight="1">
       <c r="A206" s="3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B206" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wilden, Abraham (-)</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E206" s="17"/>
       <c r="F206" s="18"/>
       <c r="G206" s="9"/>
       <c r="H206" s="3" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>16</v>
@@ -10685,23 +10705,23 @@
     </row>
     <row r="207" ht="22.5" customHeight="1">
       <c r="A207" s="3" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B207" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Groben, Jacob (evtl. Johannes) (-)</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E207" s="17"/>
       <c r="F207" s="18"/>
       <c r="G207" s="9"/>
       <c r="H207" s="3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>16</v>
@@ -10711,21 +10731,21 @@
     </row>
     <row r="208" ht="22.5" customHeight="1">
       <c r="A208" s="3" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B208" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ziegler,  (-)</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="17"/>
       <c r="F208" s="18"/>
       <c r="G208" s="9"/>
       <c r="H208" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="I208" s="7" t="s">
         <v>16</v>
@@ -10735,7 +10755,7 @@
     </row>
     <row r="209" ht="22.5" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B209" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10751,7 +10771,7 @@
       <c r="F209" s="18"/>
       <c r="G209" s="9"/>
       <c r="H209" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="I209" s="7" t="s">
         <v>16</v>
@@ -10761,21 +10781,21 @@
     </row>
     <row r="210" ht="22.5" customHeight="1">
       <c r="A210" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B210" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Oeri,  (-)</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="17"/>
       <c r="F210" s="18"/>
       <c r="G210" s="9"/>
       <c r="H210" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="I210" s="7" t="s">
         <v>16</v>
@@ -10785,21 +10805,21 @@
     </row>
     <row r="211" ht="22.5" customHeight="1">
       <c r="A211" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B211" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wittib,  (-)</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="17"/>
       <c r="F211" s="18"/>
       <c r="G211" s="9"/>
       <c r="H211" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="I211" s="13"/>
       <c r="J211" s="9"/>
@@ -10807,14 +10827,14 @@
     </row>
     <row r="212" ht="22.5" customHeight="1">
       <c r="A212" s="3" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B212" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Graf von Sultz,  (-)</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D212" s="3"/>
       <c r="E212" s="17"/>
@@ -10829,21 +10849,21 @@
     </row>
     <row r="213" ht="22.5" customHeight="1">
       <c r="A213" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B213" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Eglin,  (-)</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D213" s="3"/>
       <c r="E213" s="17"/>
       <c r="F213" s="18"/>
       <c r="G213" s="9"/>
       <c r="H213" s="3" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="I213" s="7" t="s">
         <v>16</v>
@@ -10853,14 +10873,14 @@
     </row>
     <row r="214" ht="22.5" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B214" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wildhans von Breitenlandenberg,  (-1444)</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="17"/>
@@ -10869,7 +10889,7 @@
       </c>
       <c r="G214" s="9"/>
       <c r="H214" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="I214" s="7" t="s">
         <v>16</v>
@@ -10879,14 +10899,14 @@
     </row>
     <row r="215" ht="22.5" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B215" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pfarrherr,  (-)</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="17"/>
@@ -10901,17 +10921,17 @@
     </row>
     <row r="216" ht="22.5" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B216" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid von Schwarzenhorn, Johann Rudolf (1590-1667)</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E216" s="5">
         <v>1590.0</v>
@@ -10920,29 +10940,29 @@
         <v>1667.0</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="I216" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J216" s="8" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="K216" s="9"/>
     </row>
     <row r="217" ht="22.5" customHeight="1">
       <c r="A217" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B217" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid, Felix (-1598)</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>88</v>
@@ -10953,26 +10973,26 @@
       </c>
       <c r="G217" s="9"/>
       <c r="H217" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="I217" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J217" s="8" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="K217" s="9"/>
     </row>
     <row r="218" ht="22.5" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B218" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hessen, Heinrich (-)</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>37</v>
@@ -10981,7 +11001,7 @@
       <c r="F218" s="18"/>
       <c r="G218" s="9"/>
       <c r="H218" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I218" s="7" t="s">
         <v>16</v>
@@ -10991,17 +11011,17 @@
     </row>
     <row r="219" ht="22.5" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B219" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulr., H. (-)</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E219" s="17"/>
       <c r="F219" s="18"/>
@@ -11017,7 +11037,7 @@
     </row>
     <row r="220" ht="22.5" customHeight="1">
       <c r="A220" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B220" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11027,13 +11047,13 @@
         <v>60</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E220" s="17"/>
       <c r="F220" s="18"/>
       <c r="G220" s="9"/>
       <c r="H220" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>16</v>
@@ -11043,7 +11063,7 @@
     </row>
     <row r="221" ht="22.5" customHeight="1">
       <c r="A221" s="3" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B221" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11057,7 +11077,7 @@
       <c r="F221" s="18"/>
       <c r="G221" s="9"/>
       <c r="H221" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="I221" s="7" t="s">
         <v>16</v>
@@ -11067,14 +11087,14 @@
     </row>
     <row r="222" ht="22.5" customHeight="1">
       <c r="A222" s="3" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B222" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Locher,  (-)</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="17"/>
@@ -11089,17 +11109,17 @@
     </row>
     <row r="223" ht="22.5" customHeight="1">
       <c r="A223" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B223" s="4" t="str">
         <f t="shared" si="1"/>
         <v>König, Caspar (-)</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E223" s="17"/>
       <c r="F223" s="18"/>
@@ -11111,7 +11131,7 @@
     </row>
     <row r="224" ht="22.5" customHeight="1">
       <c r="A224" s="3" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B224" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11133,7 +11153,7 @@
         <v>70</v>
       </c>
       <c r="H224" s="19" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="I224" s="7" t="s">
         <v>16</v>
@@ -11145,7 +11165,7 @@
     </row>
     <row r="225" ht="22.5" customHeight="1">
       <c r="A225" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B225" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11159,7 +11179,7 @@
       <c r="F225" s="18"/>
       <c r="G225" s="9"/>
       <c r="H225" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>16</v>
@@ -11169,17 +11189,17 @@
     </row>
     <row r="226" ht="22.5" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B226" s="4" t="str">
         <f t="shared" si="1"/>
         <v>O., Jacob U. (-)</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E226" s="17"/>
       <c r="F226" s="18"/>
@@ -11195,21 +11215,21 @@
     </row>
     <row r="227" ht="22.5" customHeight="1">
       <c r="A227" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B227" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schneeberger,  (-)</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="17"/>
       <c r="F227" s="18"/>
       <c r="G227" s="9"/>
       <c r="H227" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="I227" s="7" t="s">
         <v>16</v>
@@ -11219,17 +11239,17 @@
     </row>
     <row r="228" ht="22.5" customHeight="1">
       <c r="A228" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B228" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwingli, Ulrich (1484-1531)</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E228" s="5">
         <v>1484.0</v>
@@ -11238,10 +11258,10 @@
         <v>1531.0</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="I228" s="7" t="s">
         <v>16</v>
@@ -11251,14 +11271,14 @@
     </row>
     <row r="229" ht="22.5" customHeight="1">
       <c r="A229" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B229" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bullinger, Heinrich (1504-1575)</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>37</v>
@@ -11270,10 +11290,10 @@
         <v>1575.0</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="I229" s="7" t="s">
         <v>16</v>
@@ -11283,17 +11303,17 @@
     </row>
     <row r="230" ht="22.5" customHeight="1">
       <c r="A230" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B230" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther, Rudolf (1519-1586)</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E230" s="5">
         <v>1519.0</v>
@@ -11302,7 +11322,7 @@
         <v>1586.0</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H230" s="3"/>
       <c r="I230" s="7" t="s">
@@ -11313,14 +11333,14 @@
     </row>
     <row r="231" ht="22.5" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B231" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Breitinger, Johann Jakob (1575-1645)</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>31</v>
@@ -11332,7 +11352,7 @@
         <v>1645.0</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H231" s="3"/>
       <c r="I231" s="7" t="s">
@@ -11343,17 +11363,17 @@
     </row>
     <row r="232" ht="22.5" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B232" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jrminger, Jacob (1588-1649)</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E232" s="5">
         <v>1588.0</v>
@@ -11362,7 +11382,7 @@
         <v>1649.0</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H232" s="3"/>
       <c r="I232" s="7" t="s">
@@ -11373,17 +11393,17 @@
     </row>
     <row r="233" ht="22.5" customHeight="1">
       <c r="A233" s="3" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B233" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fries, Jakob (-)</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E233" s="17"/>
       <c r="F233" s="18"/>
@@ -11397,25 +11417,25 @@
     </row>
     <row r="234" ht="22.5" customHeight="1">
       <c r="A234" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B234" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Geiger, Joh. Rud. (-)</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E234" s="17"/>
       <c r="F234" s="18"/>
       <c r="G234" s="3" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="I234" s="7" t="s">
         <v>16</v>
@@ -11425,17 +11445,17 @@
     </row>
     <row r="235" ht="22.5" customHeight="1">
       <c r="A235" s="3" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B235" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maurer, C. (-)</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="E235" s="17"/>
       <c r="F235" s="18"/>
@@ -11449,17 +11469,17 @@
     </row>
     <row r="236" ht="22.5" customHeight="1">
       <c r="A236" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="B236" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Suter, C. (-)</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>874</v>
+      </c>
+      <c r="D236" s="3" t="s">
         <v>872</v>
-      </c>
-      <c r="B236" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>Suter, C. (-)</v>
-      </c>
-      <c r="C236" s="6" t="s">
-        <v>873</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>871</v>
       </c>
       <c r="E236" s="17"/>
       <c r="F236" s="18"/>
@@ -11473,17 +11493,17 @@
     </row>
     <row r="237" ht="22.5" customHeight="1">
       <c r="A237" s="3" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B237" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Holzhalb, Joh. (-)</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E237" s="17"/>
       <c r="F237" s="18"/>
@@ -11499,17 +11519,17 @@
     </row>
     <row r="238" ht="22.5" customHeight="1">
       <c r="A238" s="3" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B238" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wirtz, H. C. (-)</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="E238" s="17"/>
       <c r="F238" s="18"/>
@@ -11523,22 +11543,22 @@
     </row>
     <row r="239" ht="22.5" customHeight="1">
       <c r="A239" s="3" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B239" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser, Caspar (-)</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E239" s="17"/>
       <c r="F239" s="18"/>
       <c r="G239" s="3" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H239" s="3"/>
       <c r="I239" s="7" t="s">
@@ -11549,22 +11569,22 @@
     </row>
     <row r="240" ht="22.5" customHeight="1">
       <c r="A240" s="3" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B240" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hospinianus, R. (-)</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E240" s="17"/>
       <c r="F240" s="18"/>
       <c r="G240" s="3" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H240" s="3"/>
       <c r="I240" s="7" t="s">
@@ -11575,17 +11595,17 @@
     </row>
     <row r="241" ht="22.5" customHeight="1">
       <c r="A241" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B241" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Erni, H. (-)</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E241" s="17"/>
       <c r="F241" s="18"/>
@@ -11599,17 +11619,17 @@
     </row>
     <row r="242" ht="22.5" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B242" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Tomman, P. (-)</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E242" s="17"/>
       <c r="F242" s="18"/>
@@ -11623,17 +11643,17 @@
     </row>
     <row r="243" ht="22.5" customHeight="1">
       <c r="A243" s="3" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B243" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Stukki, R. (-)</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E243" s="17"/>
       <c r="F243" s="18"/>
@@ -11647,17 +11667,17 @@
     </row>
     <row r="244" ht="22.5" customHeight="1">
       <c r="A244" s="3" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B244" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zeller, H. (-)</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E244" s="17"/>
       <c r="F244" s="18"/>
@@ -11671,7 +11691,7 @@
     </row>
     <row r="245" ht="22.5" customHeight="1">
       <c r="A245" s="3" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B245" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11679,13 +11699,13 @@
       </c>
       <c r="C245" s="6"/>
       <c r="D245" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="E245" s="17"/>
       <c r="F245" s="18"/>
       <c r="G245" s="9"/>
       <c r="H245" s="3" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I245" s="7" t="s">
         <v>16</v>
@@ -11695,21 +11715,21 @@
     </row>
     <row r="246" ht="22.5" customHeight="1">
       <c r="A246" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B246" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fr. Doctorin,  (-)</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="17"/>
       <c r="F246" s="18"/>
       <c r="G246" s="9"/>
       <c r="H246" s="3" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="I246" s="7" t="s">
         <v>16</v>
@@ -11719,17 +11739,17 @@
     </row>
     <row r="247" ht="22.5" customHeight="1">
       <c r="A247" s="3" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B247" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kusen, Jost von (1570-1630)</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E247" s="5">
         <v>1570.0</v>
@@ -11738,10 +11758,10 @@
         <v>1630.0</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="I247" s="7" t="s">
         <v>16</v>
@@ -11751,14 +11771,14 @@
     </row>
     <row r="248" ht="22.5" customHeight="1">
       <c r="A248" s="3" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B248" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Heinrich (-)</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>37</v>
@@ -11767,7 +11787,7 @@
       <c r="F248" s="18"/>
       <c r="G248" s="9"/>
       <c r="H248" s="3" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="I248" s="7" t="s">
         <v>16</v>
@@ -11777,21 +11797,21 @@
     </row>
     <row r="249" ht="22.5" customHeight="1">
       <c r="A249" s="3" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B249" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gessner,  (-)</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="17"/>
       <c r="F249" s="18"/>
       <c r="G249" s="9"/>
       <c r="H249" s="3" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="I249" s="7" t="s">
         <v>16</v>
@@ -11801,17 +11821,17 @@
     </row>
     <row r="250" ht="22.5" customHeight="1">
       <c r="A250" s="3" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B250" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wöllwein, Johann Anton (1616-1659)</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="E250" s="5">
         <v>1616.0</v>
@@ -11820,10 +11840,10 @@
         <v>1659.0</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="I250" s="7" t="s">
         <v>16</v>
@@ -11833,42 +11853,42 @@
     </row>
     <row r="251" ht="22.5" customHeight="1">
       <c r="A251" s="3" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B251" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Anna (-)</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E251" s="17"/>
       <c r="F251" s="18"/>
       <c r="G251" s="9"/>
       <c r="H251" s="3" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="I251" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="K251" s="9"/>
     </row>
     <row r="252" ht="22.5" customHeight="1">
       <c r="A252" s="3" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B252" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. J. R. S.,  (-)</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D252" s="3"/>
       <c r="E252" s="17"/>
@@ -11881,17 +11901,17 @@
     </row>
     <row r="253" ht="22.5" customHeight="1">
       <c r="A253" s="3" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B253" s="4" t="str">
         <f t="shared" si="1"/>
         <v>de Ruyter, Michiel (1607-1676)</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E253" s="5">
         <v>1607.0</v>
@@ -11900,10 +11920,10 @@
         <v>1676.0</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="I253" s="7" t="s">
         <v>16</v>
@@ -11913,21 +11933,21 @@
     </row>
     <row r="254" ht="22.5" customHeight="1">
       <c r="A254" s="3" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B254" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Frau Oberstin,  (-)</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="17"/>
       <c r="F254" s="18"/>
       <c r="G254" s="9"/>
       <c r="H254" s="3" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="I254" s="7" t="s">
         <v>16</v>
@@ -11937,23 +11957,23 @@
     </row>
     <row r="255" ht="22.5" customHeight="1">
       <c r="A255" s="3" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B255" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vulcanus,  (-)</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="17"/>
       <c r="F255" s="18"/>
       <c r="G255" s="3" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="I255" s="7" t="s">
         <v>231</v>
@@ -11963,23 +11983,23 @@
     </row>
     <row r="256" ht="22.5" customHeight="1">
       <c r="A256" s="3" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B256" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esau,  (-)</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="17"/>
       <c r="F256" s="18"/>
       <c r="G256" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="I256" s="7" t="s">
         <v>249</v>
@@ -11989,23 +12009,23 @@
     </row>
     <row r="257" ht="22.5" customHeight="1">
       <c r="A257" s="3" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B257" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Danaos,  (-)</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="17"/>
       <c r="F257" s="18"/>
       <c r="G257" s="3" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="I257" s="7" t="s">
         <v>231</v>
@@ -12015,20 +12035,20 @@
     </row>
     <row r="258" ht="22.5" customHeight="1">
       <c r="A258" s="3" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B258" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Medusa,  (-)</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="17"/>
       <c r="F258" s="18"/>
       <c r="G258" s="3" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>231</v>
@@ -12041,20 +12061,20 @@
     </row>
     <row r="259" ht="22.5" customHeight="1">
       <c r="A259" s="3" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B259" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pluton,  (-)</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="17"/>
       <c r="F259" s="18"/>
       <c r="G259" s="3" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>231</v>
@@ -12067,20 +12087,20 @@
     </row>
     <row r="260" ht="22.5" customHeight="1">
       <c r="A260" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B260" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mercur,  (-)</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="17"/>
       <c r="F260" s="18"/>
       <c r="G260" s="3" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>231</v>
@@ -12093,20 +12113,20 @@
     </row>
     <row r="261" ht="22.5" customHeight="1">
       <c r="A261" s="3" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B261" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Perseus,  (-)</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="17"/>
       <c r="F261" s="18"/>
       <c r="G261" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>231</v>
@@ -12119,23 +12139,23 @@
     </row>
     <row r="262" ht="22.5" customHeight="1">
       <c r="A262" s="3" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B262" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Atropos,  (-)</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="17"/>
       <c r="F262" s="18"/>
       <c r="G262" s="3" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="I262" s="7" t="s">
         <v>231</v>
@@ -12145,23 +12165,23 @@
     </row>
     <row r="263" ht="22.5" customHeight="1">
       <c r="A263" s="3" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B263" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Barbara von Nikomedien,  (-)</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="17"/>
       <c r="F263" s="18"/>
       <c r="G263" s="3" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H263" s="3" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="I263" s="7" t="s">
         <v>249</v>
@@ -12171,7 +12191,7 @@
     </row>
     <row r="264" ht="22.5" customHeight="1">
       <c r="A264" s="3" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B264" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12179,13 +12199,13 @@
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="E264" s="17"/>
       <c r="F264" s="18"/>
       <c r="G264" s="9"/>
       <c r="H264" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="I264" s="13"/>
       <c r="J264" s="9"/>
@@ -12193,7 +12213,7 @@
     </row>
     <row r="265" ht="22.5" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B265" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12207,7 +12227,7 @@
       <c r="F265" s="18"/>
       <c r="G265" s="9"/>
       <c r="H265" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="I265" s="13"/>
       <c r="J265" s="9"/>
@@ -12215,21 +12235,21 @@
     </row>
     <row r="266" ht="22.5" customHeight="1">
       <c r="A266" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B266" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Karl,  (-)</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="17"/>
       <c r="F266" s="18"/>
       <c r="G266" s="9"/>
       <c r="H266" s="3" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="I266" s="7" t="s">
         <v>16</v>
@@ -12239,21 +12259,21 @@
     </row>
     <row r="267" ht="22.5" customHeight="1">
       <c r="A267" s="3" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B267" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Duraeum,  (-)</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="17"/>
       <c r="F267" s="18"/>
       <c r="G267" s="9"/>
       <c r="H267" s="3" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="I267" s="13"/>
       <c r="J267" s="9"/>
@@ -12261,17 +12281,17 @@
     </row>
     <row r="268" ht="22.5" customHeight="1">
       <c r="A268" s="3" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B268" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zesen, Philipp von (1619-1689)</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E268" s="5">
         <v>1619.0</v>
@@ -12280,7 +12300,7 @@
         <v>1689.0</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H268" s="3"/>
       <c r="I268" s="7" t="s">
@@ -12291,23 +12311,23 @@
     </row>
     <row r="269" ht="22.5" customHeight="1">
       <c r="A269" s="3" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B269" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lucretia,  (-)</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D269" s="3"/>
       <c r="E269" s="17"/>
       <c r="F269" s="18"/>
       <c r="G269" s="3" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="I269" s="7" t="s">
         <v>231</v>
@@ -12317,23 +12337,23 @@
     </row>
     <row r="270" ht="22.5" customHeight="1">
       <c r="A270" s="3" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B270" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ovid,  (-)</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="17"/>
       <c r="F270" s="18"/>
       <c r="G270" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H270" s="3" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="I270" s="7" t="s">
         <v>16</v>
@@ -12343,81 +12363,91 @@
     </row>
     <row r="271" ht="22.5" customHeight="1">
       <c r="A271" s="3" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B271" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Schweizer, Johann Caspar (1619-1688)</v>
+        <v>Schweizer, Johann Caspar (1619/1620-1684/1688)</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>981</v>
-      </c>
-      <c r="E271" s="5">
-        <v>1619.0</v>
+        <v>982</v>
+      </c>
+      <c r="E271" s="5" t="s">
+        <v>983</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>83</v>
+        <v>984</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>138</v>
+        <v>985</v>
       </c>
       <c r="H271" s="3" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="I271" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J271" s="8" t="s">
-        <v>983</v>
-      </c>
-      <c r="K271" s="9"/>
+        <v>987</v>
+      </c>
+      <c r="K271" s="3" t="s">
+        <v>988</v>
+      </c>
     </row>
     <row r="272" ht="22.5" customHeight="1">
       <c r="A272" s="3" t="s">
-        <v>984</v>
+        <v>989</v>
       </c>
       <c r="B272" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Herder, Johann Heinrich (-)</v>
+        <v>Herder, Johann Heinrich (1629-1665)</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E272" s="17"/>
-      <c r="F272" s="18"/>
+      <c r="E272" s="5">
+        <v>1629.0</v>
+      </c>
+      <c r="F272" s="5">
+        <v>1665.0</v>
+      </c>
       <c r="G272" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="H272" s="3"/>
-      <c r="I272" s="13"/>
+        <v>991</v>
+      </c>
+      <c r="H272" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="I272" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="J272" s="9"/>
       <c r="K272" s="9"/>
     </row>
     <row r="273" ht="22.5" customHeight="1">
       <c r="A273" s="3" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="B273" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Elischa,  (-)</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="D273" s="3"/>
       <c r="E273" s="17"/>
       <c r="F273" s="18"/>
       <c r="G273" s="3" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="H273" s="3" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="I273" s="7" t="s">
         <v>249</v>
@@ -12427,23 +12457,23 @@
     </row>
     <row r="274" ht="22.5" customHeight="1">
       <c r="A274" s="3" t="s">
-        <v>991</v>
+        <v>997</v>
       </c>
       <c r="B274" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Johannes der Täufer,  (-)</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>992</v>
+        <v>998</v>
       </c>
       <c r="D274" s="3"/>
       <c r="E274" s="17"/>
       <c r="F274" s="18"/>
       <c r="G274" s="3" t="s">
-        <v>993</v>
+        <v>999</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>994</v>
+        <v>1000</v>
       </c>
       <c r="I274" s="7" t="s">
         <v>249</v>
@@ -12453,29 +12483,29 @@
     </row>
     <row r="275" ht="22.5" customHeight="1">
       <c r="A275" s="3" t="s">
-        <v>995</v>
+        <v>1001</v>
       </c>
       <c r="B275" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caesar, Gaius Iulius (100 v. Chr.-44 v. Chr.)</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>997</v>
+        <v>1003</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>998</v>
+        <v>1004</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>999</v>
+        <v>1005</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="H275" s="3" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="I275" s="7" t="s">
         <v>16</v>
@@ -12485,23 +12515,23 @@
     </row>
     <row r="276" ht="22.5" customHeight="1">
       <c r="A276" s="3" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="B276" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Helios,  (-)</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="D276" s="3"/>
       <c r="E276" s="17"/>
       <c r="F276" s="18"/>
       <c r="G276" s="3" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="H276" s="3" t="s">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="I276" s="7" t="s">
         <v>231</v>
@@ -12511,7 +12541,7 @@
     </row>
     <row r="277" ht="22.5" customHeight="1">
       <c r="A277" s="3" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="B277" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12529,7 +12559,7 @@
     </row>
     <row r="278" ht="22.5" customHeight="1">
       <c r="A278" s="3" t="s">
-        <v>1007</v>
+        <v>1013</v>
       </c>
       <c r="B278" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12547,7 +12577,7 @@
     </row>
     <row r="279" ht="22.5" customHeight="1">
       <c r="A279" s="3" t="s">
-        <v>1008</v>
+        <v>1014</v>
       </c>
       <c r="B279" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12565,7 +12595,7 @@
     </row>
     <row r="280" ht="22.5" customHeight="1">
       <c r="A280" s="3" t="s">
-        <v>1009</v>
+        <v>1015</v>
       </c>
       <c r="B280" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12619,37 +12649,38 @@
     <hyperlink r:id="rId26" ref="J42"/>
     <hyperlink r:id="rId27" ref="J43"/>
     <hyperlink r:id="rId28" ref="J48"/>
-    <hyperlink r:id="rId29" ref="J131"/>
-    <hyperlink r:id="rId30" ref="J132"/>
-    <hyperlink r:id="rId31" ref="J137"/>
-    <hyperlink r:id="rId32" ref="J138"/>
-    <hyperlink r:id="rId33" ref="J142"/>
-    <hyperlink r:id="rId34" ref="J143"/>
-    <hyperlink r:id="rId35" ref="J153"/>
-    <hyperlink r:id="rId36" ref="J154"/>
-    <hyperlink r:id="rId37" ref="J155"/>
-    <hyperlink r:id="rId38" ref="J160"/>
-    <hyperlink r:id="rId39" ref="J190"/>
-    <hyperlink r:id="rId40" ref="J191"/>
-    <hyperlink r:id="rId41" ref="J192"/>
-    <hyperlink r:id="rId42" ref="J193"/>
-    <hyperlink r:id="rId43" ref="J194"/>
-    <hyperlink r:id="rId44" ref="J197"/>
-    <hyperlink r:id="rId45" ref="J198"/>
-    <hyperlink r:id="rId46" ref="J199"/>
-    <hyperlink r:id="rId47" ref="J200"/>
-    <hyperlink r:id="rId48" ref="J201"/>
-    <hyperlink r:id="rId49" ref="J202"/>
-    <hyperlink r:id="rId50" ref="J203"/>
-    <hyperlink r:id="rId51" ref="J204"/>
-    <hyperlink r:id="rId52" ref="J216"/>
-    <hyperlink r:id="rId53" ref="J217"/>
-    <hyperlink r:id="rId54" ref="J224"/>
-    <hyperlink r:id="rId55" ref="J271"/>
+    <hyperlink r:id="rId29" ref="J51"/>
+    <hyperlink r:id="rId30" ref="J131"/>
+    <hyperlink r:id="rId31" ref="J132"/>
+    <hyperlink r:id="rId32" ref="J137"/>
+    <hyperlink r:id="rId33" ref="J138"/>
+    <hyperlink r:id="rId34" ref="J142"/>
+    <hyperlink r:id="rId35" ref="J143"/>
+    <hyperlink r:id="rId36" ref="J153"/>
+    <hyperlink r:id="rId37" ref="J154"/>
+    <hyperlink r:id="rId38" ref="J155"/>
+    <hyperlink r:id="rId39" ref="J160"/>
+    <hyperlink r:id="rId40" ref="J190"/>
+    <hyperlink r:id="rId41" ref="J191"/>
+    <hyperlink r:id="rId42" ref="J192"/>
+    <hyperlink r:id="rId43" ref="J193"/>
+    <hyperlink r:id="rId44" ref="J194"/>
+    <hyperlink r:id="rId45" ref="J197"/>
+    <hyperlink r:id="rId46" ref="J198"/>
+    <hyperlink r:id="rId47" ref="J199"/>
+    <hyperlink r:id="rId48" ref="J200"/>
+    <hyperlink r:id="rId49" ref="J201"/>
+    <hyperlink r:id="rId50" ref="J202"/>
+    <hyperlink r:id="rId51" ref="J203"/>
+    <hyperlink r:id="rId52" ref="J204"/>
+    <hyperlink r:id="rId53" ref="J216"/>
+    <hyperlink r:id="rId54" ref="J217"/>
+    <hyperlink r:id="rId55" ref="J224"/>
+    <hyperlink r:id="rId56" ref="J271"/>
   </hyperlinks>
-  <drawing r:id="rId56"/>
+  <drawing r:id="rId57"/>
   <tableParts count="1">
-    <tablePart r:id="rId58"/>
+    <tablePart r:id="rId59"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12671,16 +12702,16 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1010</v>
+        <v>1016</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -12691,179 +12722,179 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="B2" s="22" t="str">
         <f t="shared" ref="B2:B102" si="1">CONCATENATE(C2)</f>
         <v>Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="7" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1017</v>
+        <v>1023</v>
       </c>
       <c r="B3" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Basel</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="7" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="B4" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Eidgenossenschaft</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1020</v>
+        <v>1026</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="E4" s="20"/>
       <c r="F4" s="3" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="B5" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Limmat</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="D5" s="24"/>
       <c r="E5" s="7" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="B6" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Weinfelden</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1028</v>
+        <v>1034</v>
       </c>
       <c r="D6" s="24"/>
       <c r="E6" s="7" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1029</v>
+        <v>1035</v>
       </c>
       <c r="B7" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Main</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1030</v>
+        <v>1036</v>
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="7" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1031</v>
+        <v>1037</v>
       </c>
       <c r="B8" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Zürichsee</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1032</v>
+        <v>1038</v>
       </c>
       <c r="D8" s="24"/>
       <c r="E8" s="7" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1033</v>
+        <v>1039</v>
       </c>
       <c r="B9" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Thalwil</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1034</v>
+        <v>1040</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1035</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1036</v>
+        <v>1042</v>
       </c>
       <c r="B10" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bern</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1037</v>
+        <v>1043</v>
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="7" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="B11" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Gottstatt</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1039</v>
+        <v>1045</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="13"/>
@@ -12871,103 +12902,103 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="B12" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Thorberg</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1041</v>
+        <v>1047</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1042</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1043</v>
+        <v>1049</v>
       </c>
       <c r="B13" s="23" t="str">
         <f t="shared" si="1"/>
         <v>London</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="7" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1045</v>
+        <v>1051</v>
       </c>
       <c r="B14" s="23" t="str">
         <f t="shared" si="1"/>
         <v>England</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1046</v>
+        <v>1052</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="7" t="s">
-        <v>1047</v>
+        <v>1053</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="B15" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bethlehem</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1049</v>
+        <v>1055</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="7" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="B16" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Parnass </v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="7" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="B17" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Traubenberg</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="13"/>
@@ -12975,50 +13006,50 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="B18" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Babylon</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="7" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="B19" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Canaan</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="13"/>
       <c r="F19" s="3" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="B20" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Ägypten</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="13"/>
@@ -13026,158 +13057,158 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="B21" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Hermon</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="7" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="B22" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Jerusalem</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
       <c r="B23" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Jordan</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="D23" s="24"/>
       <c r="E23" s="7" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="B24" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Rotes Meer</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="D24" s="24"/>
       <c r="E24" s="7" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="F24" s="9"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="B25" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Juda</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="13"/>
       <c r="F25" s="3" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="B26" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Moab</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="13"/>
       <c r="F26" s="3" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="B27" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Ammon</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="13"/>
       <c r="F27" s="3" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="B28" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Zion</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="7" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="B29" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Assur</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="13"/>
@@ -13185,101 +13216,101 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="B30" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Israel</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="13"/>
       <c r="F30" s="3" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="B31" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Nazaret</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="7" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="B32" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Rom</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="13"/>
       <c r="F32" s="3" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="B33" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Samaria</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="D33" s="24"/>
       <c r="E33" s="13"/>
       <c r="F33" s="3" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="B34" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Kedronbach</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="D34" s="24"/>
       <c r="E34" s="13"/>
       <c r="F34" s="3" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="B35" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Garten von Getsemani</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="13"/>
@@ -13287,14 +13318,14 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="B36" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Urdorf</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="13"/>
@@ -13302,14 +13333,14 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B37" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Geiren-Rein</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="D37" s="24"/>
       <c r="E37" s="13"/>
@@ -13317,14 +13348,14 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="B38" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Aeügst</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="D38" s="24"/>
       <c r="E38" s="13"/>
@@ -13332,14 +13363,14 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="B39" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Riedt</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="13"/>
@@ -13347,14 +13378,14 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="B40" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Europa</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="D40" s="24"/>
       <c r="E40" s="13"/>
@@ -13362,48 +13393,48 @@
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="B41" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Osir</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="D41" s="24"/>
       <c r="E41" s="13"/>
       <c r="F41" s="3" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="B42" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Basadingen</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="D42" s="24"/>
       <c r="E42" s="13"/>
       <c r="F42" s="3" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="B43" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Diessenhofen</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="D43" s="24"/>
       <c r="E43" s="13"/>
@@ -13411,50 +13442,50 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="B44" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Rhein</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="7" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="B45" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Arabisches Reich</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="D45" s="24"/>
       <c r="E45" s="13"/>
       <c r="F45" s="3" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="B46" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Libanon</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="D46" s="24"/>
       <c r="E46" s="13"/>
@@ -13462,105 +13493,105 @@
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="B47" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Emmaus</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="D47" s="24"/>
       <c r="E47" s="13"/>
       <c r="F47" s="3" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="B48" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Helikon</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="7" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="B49" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Pindos</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="D49" s="24"/>
       <c r="E49" s="7" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="B50" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Neckar</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="D50" s="24"/>
       <c r="E50" s="7" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="B51" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Kurpfalz</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="D51" s="24"/>
       <c r="E51" s="13"/>
       <c r="F51" s="3" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="B52" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Eglisau</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="D52" s="24"/>
       <c r="E52" s="13"/>
@@ -13568,14 +13599,14 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="B53" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Altenklingen</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="D53" s="24"/>
       <c r="E53" s="13"/>
@@ -13583,14 +13614,14 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="B54" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Altorff</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="D54" s="24"/>
       <c r="E54" s="13"/>
@@ -13598,31 +13629,31 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="B55" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Glarus</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="D55" s="24"/>
       <c r="E55" s="13"/>
       <c r="F55" s="3" t="s">
-        <v>1016</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="B56" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bergerkirche</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="D56" s="24"/>
       <c r="E56" s="13"/>
@@ -13630,31 +13661,31 @@
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="B57" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Sodom</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
       <c r="D57" s="24"/>
       <c r="E57" s="13"/>
       <c r="F57" s="3" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="B58" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Haus zur Sonnenblume</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="D58" s="24"/>
       <c r="E58" s="13"/>
@@ -13662,31 +13693,31 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="B59" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Thurn/ genennt von Geissen</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="13"/>
       <c r="F59" s="3" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="B60" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Constantinopel</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="13"/>
@@ -13694,118 +13725,118 @@
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="B61" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Stein am Rhein</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="13"/>
       <c r="F61" s="3" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="B62" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Marburg</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="D62" s="24"/>
       <c r="E62" s="13"/>
       <c r="F62" s="3" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
       <c r="B63" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Elbląg</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="E63" s="13"/>
       <c r="F63" s="3" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="B64" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Preußen</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="13"/>
       <c r="F64" s="3" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
       <c r="B65" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bad Baden</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="D65" s="24"/>
       <c r="E65" s="13"/>
       <c r="F65" s="3" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>1183</v>
+        <v>1189</v>
       </c>
       <c r="B66" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bad Schinznach</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1184</v>
+        <v>1190</v>
       </c>
       <c r="D66" s="24"/>
       <c r="E66" s="13"/>
       <c r="F66" s="3" t="s">
-        <v>1182</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>1185</v>
+        <v>1191</v>
       </c>
       <c r="B67" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Gyrenbad</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="D67" s="24"/>
       <c r="E67" s="13"/>
@@ -13813,48 +13844,48 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="B68" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Wängibad</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="D68" s="24"/>
       <c r="E68" s="13"/>
       <c r="F68" s="8" t="s">
-        <v>1189</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>1190</v>
+        <v>1196</v>
       </c>
       <c r="B69" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Aeugst</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1191</v>
+        <v>1197</v>
       </c>
       <c r="D69" s="24"/>
       <c r="E69" s="13"/>
       <c r="F69" s="3" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
       <c r="B70" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bassersdorf</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="D70" s="24"/>
       <c r="E70" s="13"/>
@@ -13862,14 +13893,14 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>1194</v>
+        <v>1200</v>
       </c>
       <c r="B71" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Hauptwil</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1195</v>
+        <v>1201</v>
       </c>
       <c r="D71" s="24"/>
       <c r="E71" s="13"/>
@@ -13877,14 +13908,14 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="B72" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Schaffhausen</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="D72" s="24"/>
       <c r="E72" s="13"/>
@@ -13892,65 +13923,65 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
       <c r="B73" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Wädenswil</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="D73" s="24"/>
       <c r="E73" s="13"/>
       <c r="F73" s="3" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
       <c r="B74" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Freie Ämter</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="D74" s="24"/>
       <c r="E74" s="13"/>
       <c r="F74" s="3" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
       <c r="B75" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Grüningen</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="D75" s="24"/>
       <c r="E75" s="13"/>
       <c r="F75" s="3" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="B76" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Kefikon</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
       <c r="D76" s="24"/>
       <c r="E76" s="13"/>
@@ -13958,14 +13989,14 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="B77" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Maienfeld</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="D77" s="24"/>
       <c r="E77" s="13"/>
@@ -13973,14 +14004,14 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
       <c r="B78" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Greifensee (Schloss)</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="D78" s="24"/>
       <c r="E78" s="13"/>
@@ -13988,31 +14019,31 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="B79" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Lindenhof (Zürich)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
       <c r="D79" s="24"/>
       <c r="E79" s="13"/>
       <c r="F79" s="3" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="B80" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Galg-Brunnen (Zürich)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
       <c r="D80" s="24"/>
       <c r="E80" s="13"/>
@@ -14020,14 +14051,14 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="B81" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Altes Kornhaus (Zürich)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
       <c r="D81" s="24"/>
       <c r="E81" s="13"/>
@@ -14035,14 +14066,14 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="B82" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Sparrenberg (Zürich)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="13"/>
@@ -14050,14 +14081,14 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="B83" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Thurgau</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
       <c r="D83" s="24"/>
       <c r="E83" s="13"/>
@@ -14065,14 +14096,14 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="B84" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Niederlande</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="D84" s="24"/>
       <c r="E84" s="13"/>
@@ -14080,31 +14111,31 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="B85" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Holland</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D85" s="24"/>
       <c r="E85" s="13"/>
       <c r="F85" s="3" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
       <c r="B86" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Wigoltingen</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="D86" s="24"/>
       <c r="E86" s="13"/>
@@ -14112,31 +14143,31 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="B87" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Kastalia</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="D87" s="24"/>
       <c r="E87" s="13"/>
       <c r="F87" s="3" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="B88" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Legerberg</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
       <c r="D88" s="24"/>
       <c r="E88" s="13"/>
@@ -14144,48 +14175,48 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="B89" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Texel</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="D89" s="24"/>
       <c r="E89" s="13"/>
       <c r="F89" s="3" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="B90" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Vlie</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="D90" s="24"/>
       <c r="E90" s="13"/>
       <c r="F90" s="3" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>1241</v>
+        <v>1247</v>
       </c>
       <c r="B91" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Indien</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="D91" s="24"/>
       <c r="E91" s="13"/>
@@ -14193,14 +14224,14 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
       <c r="B92" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Wien</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>1244</v>
+        <v>1250</v>
       </c>
       <c r="D92" s="24"/>
       <c r="E92" s="13"/>
@@ -14208,14 +14239,14 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B93" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Deutschland</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
       <c r="D93" s="24"/>
       <c r="E93" s="13"/>
@@ -14223,60 +14254,60 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="B94" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Ölberg</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="D94" s="24"/>
       <c r="E94" s="7" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="F94" s="3"/>
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="B95" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Dietikon</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="D95" s="24"/>
       <c r="E95" s="7" t="s">
-        <v>1251</v>
+        <v>1257</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
       <c r="B96" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Winterthur</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
       <c r="D96" s="24"/>
       <c r="E96" s="7" t="s">
-        <v>1015</v>
+        <v>1021</v>
       </c>
       <c r="F96" s="3"/>
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="B97" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14289,7 +14320,7 @@
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B98" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14302,7 +14333,7 @@
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
       <c r="B99" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14315,7 +14346,7 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
       <c r="B100" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14328,7 +14359,7 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B101" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14387,25 +14418,25 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
@@ -14416,75 +14447,75 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="B2" s="25" t="str">
         <f t="shared" ref="B2:B30" si="1">CONCATENATE(C2)</f>
         <v>Teutsche Gedichte</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="I2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="B3" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Die Krafft der Gottseligkeit</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="B4" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Buch von Festen</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5"/>
@@ -14494,23 +14525,23 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="B5" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Der Psalter dess Königlichen Propheten Dauids/ Jn deutsche reymen verstendiglich vnd deutlich gebracht/ mit vorgehender anzeigung der reymen weise/ auch eines jeden Psalmes Jnhalt</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="13"/>
@@ -14518,73 +14549,73 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
       <c r="B6" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Hundert christliche Fäst-Predigen</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="B7" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Spiegel der Unermesslichen Gnad Gottes gegen den rewenden bussfertigen Sünderen/ Jn XLV. Predigen vber das XV. capitel Lucae/ vom verlohrnen Schaaf/ Pfenning/ vnd Sohn verfasset</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1018</v>
+        <v>1024</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="B8" s="25" t="str">
         <f t="shared" si="1"/>
         <v>verteütschte Rueh- oder Fridens-uebung</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="24"/>
@@ -14594,98 +14625,98 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="B9" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Nähefelser-Fahrt: in zehen erbaulichen Jahrzeit-Predigen zu schuldigem Danck dem Höhesten für den im Jahr 1388 gemeinen Landleuthen dess lobl. Eydgnössischen Bundorths Glarus wider ihre Feind bey und umb Nähefels verliehenen Wundersieg </v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="10" t="s">
-        <v>1306</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="B10" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Die vier Haubtpuncten der christlichen seligmachenden Religion: auf alle Sontag des gantzen Jahrs ordenlich abgetheilt, grundtlich nach der heiligen Schrifft erklärt und zur Erbawung gerichtet </v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="B11" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Architectura von Vestungen</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="8" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1318</v>
+        <v>1324</v>
       </c>
       <c r="B12" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Buech der Freunden Stammen</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="9"/>
@@ -14696,42 +14727,42 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="B13" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Christen-Spiegel, das ist, Bedenkliche Erinnerungen über die Beruoffspflichten aller Ständen </v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="B14" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Viergeticht</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="9"/>
@@ -14742,14 +14773,14 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="B15" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Regentenspiegel</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="9"/>
@@ -14760,18 +14791,18 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="B16" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Türckischer Jammerspiegel</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="3" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
       <c r="F16" s="24"/>
       <c r="G16" s="9"/>
@@ -14780,17 +14811,17 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="B17" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Leitungs-faden</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="24"/>
@@ -14800,17 +14831,17 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
       <c r="B18" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Buch von der Seelen-angſt Chriſti</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="24"/>
@@ -14820,17 +14851,17 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
       <c r="B19" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Verſuchungs-gabe</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1339</v>
+        <v>1345</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1340</v>
+        <v>1346</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="24"/>
@@ -14840,14 +14871,14 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
       <c r="B20" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Kriegsbüchlin</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1342</v>
+        <v>1348</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="9"/>
@@ -14858,14 +14889,14 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="B21" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Buch der Psalmen</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="9"/>
@@ -14876,117 +14907,117 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="B22" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Sterbensspiegel/ das ist sonnenklare Vorstellung menschlicher Nichtigkeit durch alle Staend und Geschlechter</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="B23" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Warhaffte/ vnd in Gottes Wort wol gegründte Widerlegung Des newlich im Truck außgegangnen ohn-Catholischen Gesprächs von Religion oder Glaubens sachen/ geneñt der Augenspiegel</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>1014</v>
+        <v>1020</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1355</v>
+        <v>1361</v>
       </c>
       <c r="B24" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Augspiegels Wahrer Religion Erster Theil</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1356</v>
+        <v>1362</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>1357</v>
+        <v>1363</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1360</v>
+        <v>1366</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="B25" s="25" t="str">
         <f t="shared" si="1"/>
         <v>De kracht der Godsaligheyt</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1365</v>
+        <v>1371</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>1366</v>
+        <v>1372</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="H25" s="13"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1368</v>
+        <v>1374</v>
       </c>
       <c r="B26" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15002,7 +15033,7 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="B27" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15018,7 +15049,7 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
       <c r="B28" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15034,7 +15065,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1371</v>
+        <v>1377</v>
       </c>
       <c r="B29" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15050,7 +15081,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
       <c r="B30" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15106,19 +15137,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1373</v>
+        <v>1379</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1011</v>
+        <v>1017</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1374</v>
+        <v>1380</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -15126,69 +15157,69 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1375</v>
+        <v>1381</v>
       </c>
       <c r="B2" s="25" t="str">
         <f t="shared" ref="B2:B24" si="1">CONCATENATE(C2)</f>
         <v>Rat Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="26" t="s">
-        <v>1377</v>
+        <v>1383</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
       <c r="B3" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Fruchtbringende Gesellschaft</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1382</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1383</v>
+        <v>1389</v>
       </c>
       <c r="B4" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Deutschgesinnte Genossenschaft (Lilien-Zunft)</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1385</v>
+        <v>1391</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1386</v>
+        <v>1392</v>
       </c>
       <c r="B5" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Parthenicum</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="13"/>
@@ -15196,107 +15227,107 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
       <c r="B6" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Carolinum Zürich</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="3" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
       <c r="B7" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Sanhedrin</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="13"/>
       <c r="F7" s="3" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="B8" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Bürgerbibliothek Zürich</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="3" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="B9" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Grossmünster</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="B10" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Fraumünster Zürich</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="3" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
       <c r="B11" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Hohe Schule Marburg</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="13"/>
@@ -15304,24 +15335,24 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="B12" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Kartäuser</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1412</v>
+        <v>1418</v>
       </c>
       <c r="B13" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15334,7 +15365,7 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="B14" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15347,7 +15378,7 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="B15" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15360,7 +15391,7 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="B16" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15373,7 +15404,7 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="B17" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15386,7 +15417,7 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="B18" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15399,7 +15430,7 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="B19" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15412,7 +15443,7 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
       <c r="B20" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15425,7 +15456,7 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="B21" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15438,7 +15469,7 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1421</v>
+        <v>1427</v>
       </c>
       <c r="B22" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15501,19 +15532,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -15521,26 +15552,26 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="B2" s="22" t="str">
         <f t="shared" ref="B2:B8" si="1">CONCATENATE(C2)</f>
         <v>Runs</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="B3" s="22" t="str">
         <f t="shared" si="1"/>
@@ -15553,7 +15584,7 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="B4" s="22" t="str">
         <f t="shared" si="1"/>
@@ -15566,7 +15597,7 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="B5" s="22" t="str">
         <f t="shared" si="1"/>
@@ -15579,7 +15610,7 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="B6" s="22" t="str">
         <f t="shared" si="1"/>
@@ -15592,7 +15623,7 @@
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="B7" s="22" t="str">
         <f t="shared" si="1"/>
@@ -15605,7 +15636,7 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="B8" s="22" t="str">
         <f t="shared" si="1"/>

--- a/gsheet/xlsx/entities.xlsx
+++ b/gsheet/xlsx/entities.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="1442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="1446">
   <si>
     <t>Person-ID</t>
   </si>
@@ -815,7 +815,10 @@
     <t>Neidhart</t>
   </si>
   <si>
-    <t>Figur des Neides</t>
+    <t>Eine zum Appellativ gewordener Eigenname, personizifierter Neid</t>
+  </si>
+  <si>
+    <t>https://www.dwds.de/wb/dwb/neidhard</t>
   </si>
   <si>
     <t>person_047</t>
@@ -1488,6 +1491,9 @@
   </si>
   <si>
     <t>Sagenhafter Gründer von Zürich</t>
+  </si>
+  <si>
+    <t>Wird auch auf den Wappenscheiben des Klosters Wettingen erwähnt https://als.wikipedia.org/wiki/Wappenscheiben_des_Klosters_Wettingen</t>
   </si>
   <si>
     <t>person_119</t>
@@ -2217,10 +2223,16 @@
     <t>person_192</t>
   </si>
   <si>
-    <t>Hans Rudolf</t>
-  </si>
-  <si>
-    <t>Doctor</t>
+    <t>Gyger</t>
+  </si>
+  <si>
+    <t>Johann Rudolf</t>
+  </si>
+  <si>
+    <t>140325301</t>
+  </si>
+  <si>
+    <t>Arzt</t>
   </si>
   <si>
     <t>person_193</t>
@@ -2558,9 +2570,6 @@
     <t>Schmid von Schwarzenhorn</t>
   </si>
   <si>
-    <t>Johann Rudolf</t>
-  </si>
-  <si>
     <t>108194221</t>
   </si>
   <si>
@@ -3153,6 +3162,9 @@
   </si>
   <si>
     <t>person_282</t>
+  </si>
+  <si>
+    <t>Suevus</t>
   </si>
   <si>
     <t>person_283</t>
@@ -6566,26 +6578,28 @@
         <v>255</v>
       </c>
       <c r="I46" s="7"/>
-      <c r="J46" s="9"/>
+      <c r="J46" s="10" t="s">
+        <v>256</v>
+      </c>
       <c r="K46" s="9"/>
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B47" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grimmefol,  (-)</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="9"/>
       <c r="H47" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I47" s="7"/>
       <c r="J47" s="9"/>
@@ -6593,51 +6607,51 @@
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B48" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pegasus/Pegasos,  (-)</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>231</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K48" s="9"/>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B49" s="4" t="str">
         <f t="shared" si="1"/>
         <v>David,  (-)</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I49" s="7" t="s">
         <v>249</v>
@@ -6647,23 +6661,23 @@
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B50" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fama,  (-)</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>231</v>
@@ -6673,17 +6687,17 @@
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B51" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Tasso, Torquato (1544-1595)</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E51" s="5">
         <v>1544.0</v>
@@ -6692,38 +6706,38 @@
         <v>1595.0</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I51" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J51" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K51" s="9"/>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B52" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Saul,  (-)</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>249</v>
@@ -6733,23 +6747,23 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B53" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Abschalom,  (-)</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I53" s="7" t="s">
         <v>249</v>
@@ -6759,14 +6773,14 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B54" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Abimelechs,  (-)</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="5"/>
@@ -6781,20 +6795,20 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B55" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Abraham,  (-)</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>249</v>
@@ -6807,23 +6821,23 @@
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B56" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Aron,  (-)</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I56" s="7" t="s">
         <v>249</v>
@@ -6833,14 +6847,14 @@
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B57" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Asaph,  (-)</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D57" s="3"/>
       <c r="E57" s="5"/>
@@ -6857,20 +6871,20 @@
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B58" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Doëg,  (-)</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D58" s="3"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H58" s="9"/>
       <c r="I58" s="7" t="s">
@@ -6881,21 +6895,21 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B59" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ezechias,  (-)</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D59" s="3"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="9"/>
       <c r="H59" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I59" s="7" t="s">
         <v>249</v>
@@ -6905,23 +6919,23 @@
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B60" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jakob ("Israel"),  (-)</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D60" s="3"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
       <c r="G60" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>249</v>
@@ -6931,20 +6945,20 @@
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B61" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Adam,  (-)</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
       <c r="G61" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>249</v>
@@ -6957,20 +6971,20 @@
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B62" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Eva,  (-)</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>249</v>
@@ -6983,23 +6997,23 @@
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B63" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Barrabas,  (-)</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
       <c r="G63" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I63" s="7" t="s">
         <v>249</v>
@@ -7009,23 +7023,23 @@
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B64" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kajaphas,  (-)</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D64" s="3"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I64" s="7" t="s">
         <v>249</v>
@@ -7035,23 +7049,23 @@
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B65" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Judas Iskariot,  (-)</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D65" s="3"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
       <c r="G65" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I65" s="7" t="s">
         <v>249</v>
@@ -7061,21 +7075,21 @@
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B66" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gabriel,  (-)</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
       <c r="G66" s="9"/>
       <c r="H66" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I66" s="7" t="s">
         <v>249</v>
@@ -7085,23 +7099,23 @@
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B67" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Herodes,  (-)</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
       <c r="G67" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I67" s="7" t="s">
         <v>249</v>
@@ -7111,23 +7125,23 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B68" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maria von Nazaret,  (-)</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
       <c r="G68" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I68" s="7" t="s">
         <v>249</v>
@@ -7137,14 +7151,14 @@
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B69" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Nikodemus,  (-)</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="5"/>
@@ -7161,25 +7175,25 @@
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B70" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pilatus, Pontius (-)</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
       <c r="G70" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I70" s="7" t="s">
         <v>249</v>
@@ -7189,23 +7203,23 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B71" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Titus,  (-)</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
       <c r="G71" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I71" s="7" t="s">
         <v>16</v>
@@ -7215,23 +7229,23 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B72" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simon Petrus,  (-)</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
       <c r="G72" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I72" s="7" t="s">
         <v>249</v>
@@ -7241,7 +7255,7 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B73" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7254,10 +7268,10 @@
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I73" s="7" t="s">
         <v>249</v>
@@ -7267,21 +7281,21 @@
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B74" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jakob,  (-)</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D74" s="3"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="9"/>
       <c r="H74" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I74" s="7" t="s">
         <v>249</v>
@@ -7291,21 +7305,21 @@
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B75" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jonas,  (-)</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D75" s="3"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="9"/>
       <c r="H75" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I75" s="7" t="s">
         <v>249</v>
@@ -7315,14 +7329,14 @@
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B76" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Joseph,  (-)</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D76" s="3"/>
       <c r="E76" s="5"/>
@@ -7339,14 +7353,14 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B77" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Saul, dessen Sohn,  (-)</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="5"/>
@@ -7363,20 +7377,20 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B78" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Satan,  (-)</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
       <c r="G78" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>249</v>
@@ -7389,14 +7403,14 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B79" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Abigail,  (-)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="5"/>
@@ -7413,14 +7427,14 @@
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B80" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hanna,  (-)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="5"/>
@@ -7437,14 +7451,14 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B81" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Susanna,  (-)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="5"/>
@@ -7461,14 +7475,14 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B82" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esther,  (-)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="5"/>
@@ -7485,14 +7499,14 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B83" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jaël,  (-)</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="5"/>
@@ -7509,7 +7523,7 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B84" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7533,21 +7547,21 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B85" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Asarias,  (-)</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D85" s="3"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
       <c r="G85" s="9"/>
       <c r="H85" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I85" s="7" t="s">
         <v>249</v>
@@ -7557,23 +7571,23 @@
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B86" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Boreas,  (-)</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I86" s="7" t="s">
         <v>231</v>
@@ -7583,23 +7597,23 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B87" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ceres,  (-)</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
       <c r="G87" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I87" s="7" t="s">
         <v>231</v>
@@ -7609,23 +7623,23 @@
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B88" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Amor,  (-)</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I88" s="7" t="s">
         <v>231</v>
@@ -7635,23 +7649,23 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B89" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sokrates,  (-)</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
       <c r="G89" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I89" s="7" t="s">
         <v>16</v>
@@ -7661,23 +7675,23 @@
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B90" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Xantippe,  (-)</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I90" s="7" t="s">
         <v>16</v>
@@ -7687,23 +7701,23 @@
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B91" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mars,  (-)</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
       <c r="G91" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="I91" s="7" t="s">
         <v>231</v>
@@ -7713,23 +7727,23 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B92" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Apollo (Phoebus),  (-)</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
       <c r="G92" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I92" s="7" t="s">
         <v>231</v>
@@ -7739,21 +7753,21 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B93" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sirius,  (-)</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
       <c r="G93" s="9"/>
       <c r="H93" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I93" s="7" t="s">
         <v>231</v>
@@ -7763,14 +7777,14 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B94" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rebecca,  (-)</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="5"/>
@@ -7787,21 +7801,21 @@
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B95" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Asteria,  (-)</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
       <c r="G95" s="9"/>
       <c r="H95" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I95" s="13"/>
       <c r="J95" s="9"/>
@@ -7809,21 +7823,21 @@
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B96" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sylvia,  (-)</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
       <c r="G96" s="9"/>
       <c r="H96" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I96" s="13"/>
       <c r="J96" s="9"/>
@@ -7831,21 +7845,21 @@
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B97" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Felicitas,  (-)</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
       <c r="G97" s="9"/>
       <c r="H97" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I97" s="13"/>
       <c r="J97" s="9"/>
@@ -7853,21 +7867,21 @@
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B98" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dorothea,  (-)</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="9"/>
       <c r="H98" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I98" s="13"/>
       <c r="J98" s="9"/>
@@ -7875,7 +7889,7 @@
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B99" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7889,7 +7903,7 @@
       <c r="F99" s="5"/>
       <c r="G99" s="9"/>
       <c r="H99" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I99" s="13"/>
       <c r="J99" s="9"/>
@@ -7897,14 +7911,14 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B100" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sara,  (-)</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="5"/>
@@ -7921,23 +7935,23 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B101" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hesiodus,  (-)</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5"/>
       <c r="G101" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I101" s="13"/>
       <c r="J101" s="9"/>
@@ -7945,23 +7959,23 @@
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B102" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Parmenides,  (-)</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
       <c r="G102" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I102" s="13"/>
       <c r="J102" s="9"/>
@@ -7969,20 +7983,20 @@
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B103" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salomon,  (-)</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D103" s="3"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
       <c r="G103" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>249</v>
@@ -7995,20 +8009,20 @@
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B104" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Isaak,  (-)</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
       <c r="G104" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>249</v>
@@ -8021,14 +8035,14 @@
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B105" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rahel,  (-)</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="5"/>
@@ -8045,20 +8059,20 @@
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B106" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hiob,  (-)</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5"/>
       <c r="G106" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>249</v>
@@ -8071,14 +8085,14 @@
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B107" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simson,  (-)</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="5"/>
@@ -8095,23 +8109,23 @@
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B108" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ben Sira,  (-)</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
       <c r="G108" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I108" s="13"/>
       <c r="J108" s="9"/>
@@ -8119,20 +8133,20 @@
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B109" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wilhelm Tell,  (-)</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D109" s="3"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
       <c r="G109" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="13"/>
@@ -8141,23 +8155,23 @@
     </row>
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B110" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zephyr,  (-)</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D110" s="3"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
       <c r="G110" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I110" s="7" t="s">
         <v>231</v>
@@ -8167,7 +8181,7 @@
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B111" s="4" t="str">
         <f t="shared" si="1"/>
@@ -8181,7 +8195,7 @@
       <c r="F111" s="5"/>
       <c r="G111" s="9"/>
       <c r="H111" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I111" s="7" t="s">
         <v>249</v>
@@ -8191,21 +8205,21 @@
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B112" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Friedensfürst,  (-)</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
       <c r="G112" s="9"/>
       <c r="H112" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="I112" s="13"/>
       <c r="J112" s="9"/>
@@ -8213,21 +8227,21 @@
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B113" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gracchus,  (-)</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
       <c r="G113" s="9"/>
       <c r="H113" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="I113" s="13"/>
       <c r="J113" s="9"/>
@@ -8235,21 +8249,21 @@
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B114" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gracchus, dessen Frau,  (-)</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
       <c r="G114" s="9"/>
       <c r="H114" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I114" s="13"/>
       <c r="J114" s="9"/>
@@ -8257,20 +8271,20 @@
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B115" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Moses,  (-)</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D115" s="3"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
       <c r="G115" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>249</v>
@@ -8283,23 +8297,23 @@
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B116" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orestes,  (-)</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
       <c r="G116" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I116" s="7" t="s">
         <v>231</v>
@@ -8309,23 +8323,23 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B117" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pylades,  (-)</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
       <c r="G117" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I117" s="7" t="s">
         <v>231</v>
@@ -8335,45 +8349,47 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B118" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thurik,  (-)</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
       <c r="G118" s="9"/>
       <c r="H118" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I118" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="J118" s="9"/>
-      <c r="K118" s="9"/>
+      <c r="J118" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="K118" s="11"/>
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B119" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Midas,  (-)</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
       <c r="G119" s="9"/>
       <c r="H119" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I119" s="7" t="s">
         <v>231</v>
@@ -8383,49 +8399,49 @@
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B120" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simon,  (-)</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
       <c r="G120" s="9"/>
       <c r="H120" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="I120" s="7" t="s">
         <v>231</v>
       </c>
       <c r="J120" s="9"/>
       <c r="K120" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B121" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Damokles,  (-)</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
       <c r="G121" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I121" s="13"/>
       <c r="J121" s="9"/>
@@ -8433,23 +8449,23 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B122" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dionysius I. von Syrakus,  (-)</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
       <c r="G122" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="I122" s="13"/>
       <c r="J122" s="9"/>
@@ -8457,23 +8473,23 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B123" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kleopatra VII.,  (-)</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
       <c r="G123" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="I123" s="13"/>
       <c r="J123" s="9"/>
@@ -8481,23 +8497,23 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B124" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Marcus Antonius,  (-)</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D124" s="3"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
       <c r="G124" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I124" s="13"/>
       <c r="J124" s="9"/>
@@ -8505,23 +8521,23 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B125" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klio,  (-)</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
       <c r="G125" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I125" s="7" t="s">
         <v>231</v>
@@ -8531,23 +8547,23 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B126" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Flora,  (-)</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
       <c r="G126" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I126" s="7" t="s">
         <v>231</v>
@@ -8557,14 +8573,14 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B127" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dorothea,  (-)</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D127" s="3"/>
       <c r="E127" s="5"/>
@@ -8577,21 +8593,21 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B128" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. J. V.,  (-)</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
       <c r="G128" s="9"/>
       <c r="H128" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I128" s="7" t="s">
         <v>16</v>
@@ -8601,21 +8617,21 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B129" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. J. V., dessen Frau,  (-)</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
       <c r="G129" s="9"/>
       <c r="H129" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I129" s="7" t="s">
         <v>16</v>
@@ -8625,21 +8641,21 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B130" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sch. H.,  (-)</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
       <c r="G130" s="9"/>
       <c r="H130" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="I130" s="7" t="s">
         <v>16</v>
@@ -8649,14 +8665,14 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B131" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser, Johann Heinrich (1600-1669)</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>43</v>
@@ -8668,66 +8684,66 @@
         <v>1669.0</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H131" s="14" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="I131" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J131" s="15" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="K131" s="9"/>
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B132" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser-Ziegler, Jahel (-)</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
       <c r="G132" s="9"/>
       <c r="H132" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I132" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="K132" s="9"/>
     </row>
     <row r="133" ht="22.5" customHeight="1">
       <c r="A133" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B133" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caspar W.,  (-)</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
       <c r="G133" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I133" s="7" t="s">
         <v>16</v>
@@ -8737,21 +8753,21 @@
     </row>
     <row r="134" ht="22.5" customHeight="1">
       <c r="A134" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B134" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esther O.,  (-)</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
       <c r="G134" s="9"/>
       <c r="H134" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I134" s="7" t="s">
         <v>16</v>
@@ -8761,14 +8777,14 @@
     </row>
     <row r="135" ht="22.5" customHeight="1">
       <c r="A135" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B135" s="4" t="str">
         <f t="shared" si="1"/>
         <v>G. H.,  (-)</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="5"/>
@@ -8783,21 +8799,21 @@
     </row>
     <row r="136" ht="22.5" customHeight="1">
       <c r="A136" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B136" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. C.,  (-)</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
       <c r="G136" s="9"/>
       <c r="H136" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I136" s="7" t="s">
         <v>16</v>
@@ -8807,17 +8823,17 @@
     </row>
     <row r="137" ht="22.5" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B137" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Hercules von (1617-1686)</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E137" s="5">
         <v>1617.0</v>
@@ -8826,30 +8842,30 @@
         <v>1686.0</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="H137" s="3"/>
       <c r="I137" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="K137" s="9"/>
     </row>
     <row r="138" ht="22.5" customHeight="1">
       <c r="A138" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B138" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Barbara Dorothea von (1629-1660)</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E138" s="5">
         <v>1629.0</v>
@@ -8859,26 +8875,26 @@
       </c>
       <c r="G138" s="9"/>
       <c r="H138" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I138" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J138" s="8" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="K138" s="9"/>
     </row>
     <row r="139" ht="22.5" customHeight="1">
       <c r="A139" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B139" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. L.,  (-)</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="5"/>
@@ -8893,21 +8909,21 @@
     </row>
     <row r="140" ht="22.5" customHeight="1">
       <c r="A140" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B140" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. A.,  (-)</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
       <c r="G140" s="9"/>
       <c r="H140" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="I140" s="7" t="s">
         <v>16</v>
@@ -8917,21 +8933,21 @@
     </row>
     <row r="141" ht="22.5" customHeight="1">
       <c r="A141" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B141" s="4" t="str">
         <f t="shared" si="1"/>
         <v>B. M.,  (-)</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D141" s="3"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
       <c r="G141" s="9"/>
       <c r="H141" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I141" s="7" t="s">
         <v>16</v>
@@ -8941,73 +8957,73 @@
     </row>
     <row r="142" ht="22.5" customHeight="1">
       <c r="A142" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B142" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. H.,  (-)</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="9"/>
       <c r="H142" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="I142" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K142" s="9"/>
     </row>
     <row r="143" ht="22.5" customHeight="1">
       <c r="A143" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B143" s="4" t="str">
         <f t="shared" si="1"/>
         <v>D. M.,  (-)</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D143" s="3"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
       <c r="G143" s="9"/>
       <c r="H143" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="I143" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="K143" s="9"/>
     </row>
     <row r="144" ht="22.5" customHeight="1">
       <c r="A144" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B144" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gottfrid,  (-)</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
       <c r="G144" s="9"/>
       <c r="H144" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I144" s="7" t="s">
         <v>16</v>
@@ -9017,21 +9033,21 @@
     </row>
     <row r="145" ht="22.5" customHeight="1">
       <c r="A145" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B145" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jakob,  (-)</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D145" s="3"/>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
       <c r="G145" s="9"/>
       <c r="H145" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I145" s="7" t="s">
         <v>16</v>
@@ -9041,21 +9057,21 @@
     </row>
     <row r="146" ht="22.5" customHeight="1">
       <c r="A146" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B146" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. Schw.,  (-)</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D146" s="3"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
       <c r="G146" s="9"/>
       <c r="H146" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="I146" s="7" t="s">
         <v>16</v>
@@ -9065,21 +9081,21 @@
     </row>
     <row r="147" ht="22.5" customHeight="1">
       <c r="A147" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B147" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. K.,  (-)</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
       <c r="G147" s="9"/>
       <c r="H147" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="I147" s="7" t="s">
         <v>16</v>
@@ -9089,14 +9105,14 @@
     </row>
     <row r="148" ht="22.5" customHeight="1">
       <c r="A148" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B148" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ott, Hans Heinrich (-)</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>69</v>
@@ -9113,14 +9129,14 @@
     </row>
     <row r="149" ht="22.5" customHeight="1">
       <c r="A149" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B149" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. W.,  (-)</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D149" s="3"/>
       <c r="E149" s="5"/>
@@ -9135,21 +9151,21 @@
     </row>
     <row r="150" ht="22.5" customHeight="1">
       <c r="A150" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B150" s="4" t="str">
         <f t="shared" si="1"/>
         <v>V. L.,  (-)</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
       <c r="G150" s="9"/>
       <c r="H150" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="I150" s="7" t="s">
         <v>16</v>
@@ -9159,14 +9175,14 @@
     </row>
     <row r="151" ht="22.5" customHeight="1">
       <c r="A151" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B151" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. Sch.,  (-)</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D151" s="3"/>
       <c r="E151" s="5"/>
@@ -9181,21 +9197,21 @@
     </row>
     <row r="152" ht="22.5" customHeight="1">
       <c r="A152" s="3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B152" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. H.,  (-)</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
       <c r="G152" s="9"/>
       <c r="H152" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="I152" s="7" t="s">
         <v>16</v>
@@ -9205,14 +9221,14 @@
     </row>
     <row r="153" ht="22.5" customHeight="1">
       <c r="A153" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B153" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. H.,  (-)</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="5"/>
@@ -9223,55 +9239,55 @@
         <v>16</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K153" s="9"/>
     </row>
     <row r="154" ht="22.5" customHeight="1">
       <c r="A154" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B154" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. W.,  (-)</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="9"/>
       <c r="H154" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="I154" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="K154" s="9"/>
     </row>
     <row r="155" ht="22.5" customHeight="1">
       <c r="A155" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B155" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Koller, Elisabeth (-)</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
       <c r="G155" s="9"/>
       <c r="H155" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="I155" s="7" t="s">
         <v>16</v>
@@ -9283,17 +9299,17 @@
     </row>
     <row r="156" ht="22.5" customHeight="1">
       <c r="A156" s="3" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B156" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lobwasser, Ambrosius (1515-1585)</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E156" s="5">
         <v>1515.0</v>
@@ -9302,10 +9318,10 @@
         <v>1585.0</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="I156" s="7" t="s">
         <v>16</v>
@@ -9315,17 +9331,17 @@
     </row>
     <row r="157" ht="22.5" customHeight="1">
       <c r="A157" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B157" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vollenweider, Jakob (1594-1647)</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E157" s="5">
         <v>1594.0</v>
@@ -9334,10 +9350,10 @@
         <v>1647.0</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="I157" s="7" t="s">
         <v>16</v>
@@ -9347,7 +9363,7 @@
     </row>
     <row r="158" ht="22.5" customHeight="1">
       <c r="A158" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B158" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9357,7 +9373,7 @@
         <v>223</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E158" s="5">
         <v>1606.0</v>
@@ -9366,7 +9382,7 @@
         <v>1660.0</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>226</v>
@@ -9379,17 +9395,17 @@
     </row>
     <row r="159" ht="22.5" customHeight="1">
       <c r="A159" s="3" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B159" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Burkhard, Hans Konrad (1613-1681)</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E159" s="5">
         <v>1613.0</v>
@@ -9398,10 +9414,10 @@
         <v>1681.0</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="I159" s="7" t="s">
         <v>16</v>
@@ -9411,14 +9427,14 @@
     </row>
     <row r="160" ht="22.5" customHeight="1">
       <c r="A160" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B160" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ardüser, Johann (1585-1665)</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>107</v>
@@ -9430,40 +9446,40 @@
         <v>1665.0</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="I160" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J160" s="12" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K160" s="9"/>
     </row>
     <row r="161" ht="22.5" customHeight="1">
       <c r="A161" s="3" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B161" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hegner, Diethelm  (-)</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
       <c r="G161" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="I161" s="7" t="s">
         <v>16</v>
@@ -9473,17 +9489,17 @@
     </row>
     <row r="162" ht="22.5" customHeight="1">
       <c r="A162" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B162" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Trigland, Jacobus (1583-1654)</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E162" s="16">
         <v>1583.0</v>
@@ -9492,10 +9508,10 @@
         <v>1654.0</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="I162" s="7" t="s">
         <v>16</v>
@@ -9505,17 +9521,17 @@
     </row>
     <row r="163" ht="22.5" customHeight="1">
       <c r="A163" s="3" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B163" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwinger, D. (-)</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="E163" s="5"/>
       <c r="F163" s="5"/>
@@ -9529,14 +9545,14 @@
     </row>
     <row r="164" ht="22.5" customHeight="1">
       <c r="A164" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B164" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Genathen, Johann Jakob (-)</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>31</v>
@@ -9544,10 +9560,10 @@
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
       <c r="G164" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="I164" s="7" t="s">
         <v>16</v>
@@ -9557,7 +9573,7 @@
     </row>
     <row r="165" ht="22.5" customHeight="1">
       <c r="A165" s="3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B165" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9583,27 +9599,27 @@
     </row>
     <row r="166" ht="22.5" customHeight="1">
       <c r="A166" s="3" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B166" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hess, Caspar (-1631)</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E166" s="5"/>
       <c r="F166" s="5">
         <v>1631.0</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="I166" s="7" t="s">
         <v>16</v>
@@ -9613,14 +9629,14 @@
     </row>
     <row r="167" ht="22.5" customHeight="1">
       <c r="A167" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B167" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wolfen, Hans Jakob (-)</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>219</v>
@@ -9637,22 +9653,22 @@
     </row>
     <row r="168" ht="22.5" customHeight="1">
       <c r="A168" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B168" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöri, Felix Christian (-)</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E168" s="17"/>
       <c r="F168" s="18"/>
       <c r="G168" s="3" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="H168" s="3"/>
       <c r="I168" s="7" t="s">
@@ -9663,7 +9679,7 @@
     </row>
     <row r="169" ht="22.5" customHeight="1">
       <c r="A169" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B169" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9673,7 +9689,7 @@
         <v>12</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E169" s="17"/>
       <c r="F169" s="5">
@@ -9689,21 +9705,21 @@
     </row>
     <row r="170" ht="22.5" customHeight="1">
       <c r="A170" s="3" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B170" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther,  (-)</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D170" s="3"/>
       <c r="E170" s="17"/>
       <c r="F170" s="18"/>
       <c r="G170" s="9"/>
       <c r="H170" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="I170" s="7" t="s">
         <v>16</v>
@@ -9713,23 +9729,23 @@
     </row>
     <row r="171" ht="22.5" customHeight="1">
       <c r="A171" s="3" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B171" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Weiss, Caspar (-)</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E171" s="17"/>
       <c r="F171" s="18"/>
       <c r="G171" s="9"/>
       <c r="H171" s="19" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="I171" s="7" t="s">
         <v>16</v>
@@ -9739,7 +9755,7 @@
     </row>
     <row r="172" ht="22.5" customHeight="1">
       <c r="A172" s="3" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B172" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9753,7 +9769,7 @@
       <c r="F172" s="18"/>
       <c r="G172" s="9"/>
       <c r="H172" s="19" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="I172" s="7" t="s">
         <v>16</v>
@@ -9763,21 +9779,21 @@
     </row>
     <row r="173" ht="22.5" customHeight="1">
       <c r="A173" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B173" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bas,  (-)</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="17"/>
       <c r="F173" s="18"/>
       <c r="G173" s="9"/>
       <c r="H173" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="I173" s="20"/>
       <c r="J173" s="9"/>
@@ -9785,14 +9801,14 @@
     </row>
     <row r="174" ht="22.5" customHeight="1">
       <c r="A174" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B174" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H.H.J. Gw. s. A.Z.Fr.M.,  (-)</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D174" s="3"/>
       <c r="E174" s="17"/>
@@ -9807,23 +9823,23 @@
     </row>
     <row r="175" ht="22.5" customHeight="1">
       <c r="A175" s="3" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B175" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hofm., Joh. (-)</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E175" s="17"/>
       <c r="F175" s="18"/>
       <c r="G175" s="9"/>
       <c r="H175" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="I175" s="7" t="s">
         <v>16</v>
@@ -9833,22 +9849,22 @@
     </row>
     <row r="176" ht="22.5" customHeight="1">
       <c r="A176" s="3" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B176" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Cyrene, Simon von (-)</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E176" s="17"/>
       <c r="F176" s="18"/>
       <c r="G176" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>249</v>
@@ -9861,23 +9877,23 @@
     </row>
     <row r="177" ht="22.5" customHeight="1">
       <c r="A177" s="3" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B177" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thomas,  (-)</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="17"/>
       <c r="F177" s="18"/>
       <c r="G177" s="3" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I177" s="7" t="s">
         <v>249</v>
@@ -9887,23 +9903,23 @@
     </row>
     <row r="178" ht="22.5" customHeight="1">
       <c r="A178" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B178" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Phaeton,  (-)</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="17"/>
       <c r="F178" s="18"/>
       <c r="G178" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="I178" s="7" t="s">
         <v>231</v>
@@ -9913,14 +9929,14 @@
     </row>
     <row r="179" ht="22.5" customHeight="1">
       <c r="A179" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B179" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lukas,  (-)</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D179" s="3"/>
       <c r="E179" s="17"/>
@@ -9937,20 +9953,20 @@
     </row>
     <row r="180" ht="22.5" customHeight="1">
       <c r="A180" s="3" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B180" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pallas Athena,  (-)</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="17"/>
       <c r="F180" s="18"/>
       <c r="G180" s="3" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>231</v>
@@ -9963,23 +9979,23 @@
     </row>
     <row r="181" ht="22.5" customHeight="1">
       <c r="A181" s="3" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B181" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bacchus,  (-)</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D181" s="3"/>
       <c r="E181" s="17"/>
       <c r="F181" s="18"/>
       <c r="G181" s="3" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="I181" s="7" t="s">
         <v>231</v>
@@ -9989,23 +10005,23 @@
     </row>
     <row r="182" ht="22.5" customHeight="1">
       <c r="A182" s="3" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B182" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Darius I.,  (-)</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="17"/>
       <c r="F182" s="18"/>
       <c r="G182" s="3" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="I182" s="7" t="s">
         <v>16</v>
@@ -10015,23 +10031,23 @@
     </row>
     <row r="183" ht="22.5" customHeight="1">
       <c r="A183" s="3" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B183" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kyros II.,  (-)</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D183" s="3"/>
       <c r="E183" s="17"/>
       <c r="F183" s="18"/>
       <c r="G183" s="3" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="I183" s="7" t="s">
         <v>16</v>
@@ -10041,25 +10057,25 @@
     </row>
     <row r="184" ht="22.5" customHeight="1">
       <c r="A184" s="3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B184" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hippo, Augustinus von (-)</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="E184" s="17"/>
       <c r="F184" s="18"/>
       <c r="G184" s="3" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="I184" s="7" t="s">
         <v>16</v>
@@ -10069,20 +10085,20 @@
     </row>
     <row r="185" ht="22.5" customHeight="1">
       <c r="A185" s="3" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B185" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lazarus,  (-)</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D185" s="3"/>
       <c r="E185" s="17"/>
       <c r="F185" s="18"/>
       <c r="G185" s="3" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>249</v>
@@ -10095,20 +10111,20 @@
     </row>
     <row r="186" ht="22.5" customHeight="1">
       <c r="A186" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B186" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lot,  (-)</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="17"/>
       <c r="F186" s="18"/>
       <c r="G186" s="3" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="H186" s="3" t="s">
         <v>249</v>
@@ -10121,21 +10137,29 @@
     </row>
     <row r="187" ht="22.5" customHeight="1">
       <c r="A187" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B187" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Hans Rudolf,  (-)</v>
+        <v>Gyger, Johann Rudolf (1603-1662)</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>709</v>
-      </c>
-      <c r="D187" s="3"/>
-      <c r="E187" s="17"/>
-      <c r="F187" s="18"/>
-      <c r="G187" s="9"/>
+        <v>711</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E187" s="5">
+        <v>1603.0</v>
+      </c>
+      <c r="F187" s="5">
+        <v>1662.0</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>713</v>
+      </c>
       <c r="H187" s="3" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="I187" s="7" t="s">
         <v>16</v>
@@ -10145,7 +10169,7 @@
     </row>
     <row r="188" ht="22.5" customHeight="1">
       <c r="A188" s="3" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="B188" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10158,16 +10182,16 @@
         <v>13</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="F188" s="5">
         <v>1690.0</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="I188" s="7" t="s">
         <v>16</v>
@@ -10177,17 +10201,17 @@
     </row>
     <row r="189" ht="22.5" customHeight="1">
       <c r="A189" s="3" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="B189" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bachofen, Johann Ulrich (1643-1700)</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="E189" s="5">
         <v>1643.0</v>
@@ -10196,7 +10220,7 @@
         <v>1700.0</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>226</v>
@@ -10209,17 +10233,17 @@
     </row>
     <row r="190" ht="22.5" customHeight="1">
       <c r="A190" s="3" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="B190" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grebel, Hans Konrad (1615-1674)</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="E190" s="5">
         <v>1615.0</v>
@@ -10228,57 +10252,57 @@
         <v>1674.0</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="I190" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="K190" s="9"/>
     </row>
     <row r="191" ht="22.5" customHeight="1">
       <c r="A191" s="3" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B191" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gossweiler, Emerentia (-)</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E191" s="17"/>
       <c r="F191" s="18"/>
       <c r="G191" s="9"/>
       <c r="H191" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="I191" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J191" s="8" t="s">
         <v>727</v>
-      </c>
-      <c r="I191" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J191" s="8" t="s">
-        <v>723</v>
       </c>
       <c r="K191" s="9"/>
     </row>
     <row r="192" ht="22.5" customHeight="1">
       <c r="A192" s="3" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="B192" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lochmann, Heinrich (1613-1667)</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>37</v>
@@ -10290,29 +10314,29 @@
         <v>1667.0</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J192" s="8" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="K192" s="9"/>
     </row>
     <row r="193" ht="22.5" customHeight="1">
       <c r="A193" s="3" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B193" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Johann Jakob (1602-1668)</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>31</v>
@@ -10324,109 +10348,109 @@
         <v>1668.0</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J193" s="8" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="K193" s="9"/>
     </row>
     <row r="194" ht="22.5" customHeight="1">
       <c r="A194" s="3" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="B194" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orelli, Anna (-)</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="E194" s="17"/>
       <c r="F194" s="18"/>
       <c r="G194" s="9"/>
       <c r="H194" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="I194" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J194" s="10" t="s">
         <v>741</v>
-      </c>
-      <c r="I194" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J194" s="10" t="s">
-        <v>737</v>
       </c>
       <c r="K194" s="9"/>
     </row>
     <row r="195" ht="22.5" customHeight="1">
       <c r="A195" s="3" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B195" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. E. H.,  (-)</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="17"/>
       <c r="F195" s="18"/>
       <c r="G195" s="9"/>
       <c r="H195" s="3" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J195" s="21" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="K195" s="9"/>
     </row>
     <row r="196" ht="22.5" customHeight="1">
       <c r="A196" s="3" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B196" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. H.,  (-)</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="D196" s="3"/>
       <c r="E196" s="17"/>
       <c r="F196" s="18"/>
       <c r="G196" s="9"/>
       <c r="H196" s="3" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="I196" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J196" s="21" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="K196" s="9"/>
     </row>
     <row r="197" ht="22.5" customHeight="1">
       <c r="A197" s="3" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B197" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grob, Hans Jakob (-)</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>219</v>
@@ -10435,19 +10459,19 @@
       <c r="F197" s="18"/>
       <c r="G197" s="9"/>
       <c r="H197" s="3" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="I197" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J197" s="8" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="K197" s="9"/>
     </row>
     <row r="198" ht="22.5" customHeight="1">
       <c r="A198" s="3" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="B198" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10457,7 +10481,7 @@
         <v>68</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="E198" s="17"/>
       <c r="F198" s="18"/>
@@ -10467,23 +10491,23 @@
         <v>16</v>
       </c>
       <c r="J198" s="8" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="K198" s="9"/>
     </row>
     <row r="199" ht="22.5" customHeight="1">
       <c r="A199" s="3" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="B199" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klingler, Kaspar (-)</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="E199" s="17"/>
       <c r="F199" s="18"/>
@@ -10493,23 +10517,23 @@
         <v>16</v>
       </c>
       <c r="J199" s="8" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="K199" s="9"/>
     </row>
     <row r="200" ht="22.5" customHeight="1">
       <c r="A200" s="3" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B200" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöndli, Dorothea (-)</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E200" s="17"/>
       <c r="F200" s="18"/>
@@ -10519,23 +10543,23 @@
         <v>16</v>
       </c>
       <c r="J200" s="8" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="K200" s="9"/>
     </row>
     <row r="201" ht="22.5" customHeight="1">
       <c r="A201" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B201" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Hans Caspar (1617-1691)</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="E201" s="5">
         <v>1617.0</v>
@@ -10544,32 +10568,32 @@
         <v>1691.0</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="K201" s="9"/>
     </row>
     <row r="202" ht="22.5" customHeight="1">
       <c r="A202" s="3" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B202" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Salomon (1580-1652)</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E202" s="5">
         <v>1580.0</v>
@@ -10578,60 +10602,60 @@
         <v>1652.0</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J202" s="8" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="K202" s="9"/>
     </row>
     <row r="203" ht="22.5" customHeight="1">
       <c r="A203" s="3" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B203" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis-Soglio, Maria Ursina von  (-)</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="E203" s="17"/>
       <c r="F203" s="18"/>
       <c r="G203" s="9"/>
       <c r="H203" s="3" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J203" s="8" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="K203" s="9"/>
     </row>
     <row r="204" ht="22.5" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="B204" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Brügger, Andreas von (1588-1653)</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="E204" s="5">
         <v>1588.0</v>
@@ -10640,36 +10664,36 @@
         <v>1653.0</v>
       </c>
       <c r="G204" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="H204" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="I204" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J204" s="8" t="s">
         <v>780</v>
-      </c>
-      <c r="H204" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="I204" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J204" s="8" t="s">
-        <v>776</v>
       </c>
       <c r="K204" s="9"/>
     </row>
     <row r="205" ht="22.5" customHeight="1">
       <c r="A205" s="3" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B205" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Anhorn,  (-)</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D205" s="3"/>
       <c r="E205" s="17"/>
       <c r="F205" s="18"/>
       <c r="G205" s="9"/>
       <c r="H205" s="3" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="I205" s="7" t="s">
         <v>16</v>
@@ -10679,23 +10703,23 @@
     </row>
     <row r="206" ht="22.5" customHeight="1">
       <c r="A206" s="3" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="B206" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wilden, Abraham (-)</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E206" s="17"/>
       <c r="F206" s="18"/>
       <c r="G206" s="9"/>
       <c r="H206" s="3" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>16</v>
@@ -10705,23 +10729,23 @@
     </row>
     <row r="207" ht="22.5" customHeight="1">
       <c r="A207" s="3" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B207" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Groben, Jacob (evtl. Johannes) (-)</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="E207" s="17"/>
       <c r="F207" s="18"/>
       <c r="G207" s="9"/>
       <c r="H207" s="3" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>16</v>
@@ -10731,21 +10755,21 @@
     </row>
     <row r="208" ht="22.5" customHeight="1">
       <c r="A208" s="3" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B208" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ziegler,  (-)</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="17"/>
       <c r="F208" s="18"/>
       <c r="G208" s="9"/>
       <c r="H208" s="3" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="I208" s="7" t="s">
         <v>16</v>
@@ -10755,7 +10779,7 @@
     </row>
     <row r="209" ht="22.5" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="B209" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10771,7 +10795,7 @@
       <c r="F209" s="18"/>
       <c r="G209" s="9"/>
       <c r="H209" s="3" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="I209" s="7" t="s">
         <v>16</v>
@@ -10781,21 +10805,21 @@
     </row>
     <row r="210" ht="22.5" customHeight="1">
       <c r="A210" s="3" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="B210" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Oeri,  (-)</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="17"/>
       <c r="F210" s="18"/>
       <c r="G210" s="9"/>
       <c r="H210" s="3" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="I210" s="7" t="s">
         <v>16</v>
@@ -10805,21 +10829,21 @@
     </row>
     <row r="211" ht="22.5" customHeight="1">
       <c r="A211" s="3" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="B211" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wittib,  (-)</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="17"/>
       <c r="F211" s="18"/>
       <c r="G211" s="9"/>
       <c r="H211" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="I211" s="13"/>
       <c r="J211" s="9"/>
@@ -10827,14 +10851,14 @@
     </row>
     <row r="212" ht="22.5" customHeight="1">
       <c r="A212" s="3" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="B212" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Graf von Sultz,  (-)</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="D212" s="3"/>
       <c r="E212" s="17"/>
@@ -10849,21 +10873,21 @@
     </row>
     <row r="213" ht="22.5" customHeight="1">
       <c r="A213" s="3" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="B213" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Eglin,  (-)</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="D213" s="3"/>
       <c r="E213" s="17"/>
       <c r="F213" s="18"/>
       <c r="G213" s="9"/>
       <c r="H213" s="3" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="I213" s="7" t="s">
         <v>16</v>
@@ -10873,14 +10897,14 @@
     </row>
     <row r="214" ht="22.5" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="B214" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wildhans von Breitenlandenberg,  (-1444)</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="17"/>
@@ -10889,7 +10913,7 @@
       </c>
       <c r="G214" s="9"/>
       <c r="H214" s="3" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="I214" s="7" t="s">
         <v>16</v>
@@ -10899,14 +10923,14 @@
     </row>
     <row r="215" ht="22.5" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B215" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pfarrherr,  (-)</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="17"/>
@@ -10921,17 +10945,17 @@
     </row>
     <row r="216" ht="22.5" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="B216" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid von Schwarzenhorn, Johann Rudolf (1590-1667)</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>814</v>
+        <v>712</v>
       </c>
       <c r="E216" s="5">
         <v>1590.0</v>
@@ -10940,29 +10964,29 @@
         <v>1667.0</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="I216" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J216" s="8" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="K216" s="9"/>
     </row>
     <row r="217" ht="22.5" customHeight="1">
       <c r="A217" s="3" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B217" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid, Felix (-1598)</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>88</v>
@@ -10973,26 +10997,26 @@
       </c>
       <c r="G217" s="9"/>
       <c r="H217" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="I217" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J217" s="8" t="s">
         <v>820</v>
-      </c>
-      <c r="I217" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J217" s="8" t="s">
-        <v>817</v>
       </c>
       <c r="K217" s="9"/>
     </row>
     <row r="218" ht="22.5" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B218" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hessen, Heinrich (-)</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>37</v>
@@ -11001,7 +11025,7 @@
       <c r="F218" s="18"/>
       <c r="G218" s="9"/>
       <c r="H218" s="3" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="I218" s="7" t="s">
         <v>16</v>
@@ -11011,17 +11035,17 @@
     </row>
     <row r="219" ht="22.5" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="B219" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulr., H. (-)</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E219" s="17"/>
       <c r="F219" s="18"/>
@@ -11037,7 +11061,7 @@
     </row>
     <row r="220" ht="22.5" customHeight="1">
       <c r="A220" s="3" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B220" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11047,13 +11071,13 @@
         <v>60</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E220" s="17"/>
       <c r="F220" s="18"/>
       <c r="G220" s="9"/>
       <c r="H220" s="3" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>16</v>
@@ -11063,7 +11087,7 @@
     </row>
     <row r="221" ht="22.5" customHeight="1">
       <c r="A221" s="3" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B221" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11077,7 +11101,7 @@
       <c r="F221" s="18"/>
       <c r="G221" s="9"/>
       <c r="H221" s="3" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="I221" s="7" t="s">
         <v>16</v>
@@ -11087,14 +11111,14 @@
     </row>
     <row r="222" ht="22.5" customHeight="1">
       <c r="A222" s="3" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B222" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Locher,  (-)</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="17"/>
@@ -11109,17 +11133,17 @@
     </row>
     <row r="223" ht="22.5" customHeight="1">
       <c r="A223" s="3" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B223" s="4" t="str">
         <f t="shared" si="1"/>
         <v>König, Caspar (-)</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E223" s="17"/>
       <c r="F223" s="18"/>
@@ -11131,7 +11155,7 @@
     </row>
     <row r="224" ht="22.5" customHeight="1">
       <c r="A224" s="3" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B224" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11153,7 +11177,7 @@
         <v>70</v>
       </c>
       <c r="H224" s="19" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="I224" s="7" t="s">
         <v>16</v>
@@ -11165,7 +11189,7 @@
     </row>
     <row r="225" ht="22.5" customHeight="1">
       <c r="A225" s="3" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="B225" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11179,7 +11203,7 @@
       <c r="F225" s="18"/>
       <c r="G225" s="9"/>
       <c r="H225" s="3" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>16</v>
@@ -11189,17 +11213,17 @@
     </row>
     <row r="226" ht="22.5" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="B226" s="4" t="str">
         <f t="shared" si="1"/>
         <v>O., Jacob U. (-)</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E226" s="17"/>
       <c r="F226" s="18"/>
@@ -11215,21 +11239,21 @@
     </row>
     <row r="227" ht="22.5" customHeight="1">
       <c r="A227" s="3" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B227" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schneeberger,  (-)</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="17"/>
       <c r="F227" s="18"/>
       <c r="G227" s="9"/>
       <c r="H227" s="3" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="I227" s="7" t="s">
         <v>16</v>
@@ -11239,17 +11263,17 @@
     </row>
     <row r="228" ht="22.5" customHeight="1">
       <c r="A228" s="3" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="B228" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwingli, Ulrich (1484-1531)</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="E228" s="5">
         <v>1484.0</v>
@@ -11258,10 +11282,10 @@
         <v>1531.0</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="I228" s="7" t="s">
         <v>16</v>
@@ -11271,14 +11295,14 @@
     </row>
     <row r="229" ht="22.5" customHeight="1">
       <c r="A229" s="3" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B229" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bullinger, Heinrich (1504-1575)</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>37</v>
@@ -11290,10 +11314,10 @@
         <v>1575.0</v>
       </c>
       <c r="G229" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="H229" s="3" t="s">
         <v>852</v>
-      </c>
-      <c r="H229" s="3" t="s">
-        <v>849</v>
       </c>
       <c r="I229" s="7" t="s">
         <v>16</v>
@@ -11303,17 +11327,17 @@
     </row>
     <row r="230" ht="22.5" customHeight="1">
       <c r="A230" s="3" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B230" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther, Rudolf (1519-1586)</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E230" s="5">
         <v>1519.0</v>
@@ -11322,7 +11346,7 @@
         <v>1586.0</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="H230" s="3"/>
       <c r="I230" s="7" t="s">
@@ -11333,14 +11357,14 @@
     </row>
     <row r="231" ht="22.5" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B231" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Breitinger, Johann Jakob (1575-1645)</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>31</v>
@@ -11352,7 +11376,7 @@
         <v>1645.0</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="H231" s="3"/>
       <c r="I231" s="7" t="s">
@@ -11363,17 +11387,17 @@
     </row>
     <row r="232" ht="22.5" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="B232" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jrminger, Jacob (1588-1649)</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="E232" s="5">
         <v>1588.0</v>
@@ -11382,7 +11406,7 @@
         <v>1649.0</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="H232" s="3"/>
       <c r="I232" s="7" t="s">
@@ -11393,17 +11417,17 @@
     </row>
     <row r="233" ht="22.5" customHeight="1">
       <c r="A233" s="3" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="B233" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fries, Jakob (-)</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E233" s="17"/>
       <c r="F233" s="18"/>
@@ -11417,25 +11441,25 @@
     </row>
     <row r="234" ht="22.5" customHeight="1">
       <c r="A234" s="3" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B234" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Geiger, Joh. Rud. (-)</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="E234" s="17"/>
       <c r="F234" s="18"/>
       <c r="G234" s="3" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I234" s="7" t="s">
         <v>16</v>
@@ -11445,17 +11469,17 @@
     </row>
     <row r="235" ht="22.5" customHeight="1">
       <c r="A235" s="3" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B235" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maurer, C. (-)</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="E235" s="17"/>
       <c r="F235" s="18"/>
@@ -11469,17 +11493,17 @@
     </row>
     <row r="236" ht="22.5" customHeight="1">
       <c r="A236" s="3" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="B236" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Suter, C. (-)</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="E236" s="17"/>
       <c r="F236" s="18"/>
@@ -11493,17 +11517,17 @@
     </row>
     <row r="237" ht="22.5" customHeight="1">
       <c r="A237" s="3" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="B237" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Holzhalb, Joh. (-)</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E237" s="17"/>
       <c r="F237" s="18"/>
@@ -11519,17 +11543,17 @@
     </row>
     <row r="238" ht="22.5" customHeight="1">
       <c r="A238" s="3" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B238" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wirtz, H. C. (-)</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="E238" s="17"/>
       <c r="F238" s="18"/>
@@ -11543,22 +11567,22 @@
     </row>
     <row r="239" ht="22.5" customHeight="1">
       <c r="A239" s="3" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="B239" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser, Caspar (-)</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E239" s="17"/>
       <c r="F239" s="18"/>
       <c r="G239" s="3" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="H239" s="3"/>
       <c r="I239" s="7" t="s">
@@ -11569,22 +11593,22 @@
     </row>
     <row r="240" ht="22.5" customHeight="1">
       <c r="A240" s="3" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B240" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hospinianus, R. (-)</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E240" s="17"/>
       <c r="F240" s="18"/>
       <c r="G240" s="3" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="H240" s="3"/>
       <c r="I240" s="7" t="s">
@@ -11595,17 +11619,17 @@
     </row>
     <row r="241" ht="22.5" customHeight="1">
       <c r="A241" s="3" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="B241" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Erni, H. (-)</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E241" s="17"/>
       <c r="F241" s="18"/>
@@ -11619,17 +11643,17 @@
     </row>
     <row r="242" ht="22.5" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="B242" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Tomman, P. (-)</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="E242" s="17"/>
       <c r="F242" s="18"/>
@@ -11643,17 +11667,17 @@
     </row>
     <row r="243" ht="22.5" customHeight="1">
       <c r="A243" s="3" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="B243" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Stukki, R. (-)</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="E243" s="17"/>
       <c r="F243" s="18"/>
@@ -11667,17 +11691,17 @@
     </row>
     <row r="244" ht="22.5" customHeight="1">
       <c r="A244" s="3" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B244" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zeller, H. (-)</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="E244" s="17"/>
       <c r="F244" s="18"/>
@@ -11691,7 +11715,7 @@
     </row>
     <row r="245" ht="22.5" customHeight="1">
       <c r="A245" s="3" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B245" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11699,13 +11723,13 @@
       </c>
       <c r="C245" s="6"/>
       <c r="D245" s="3" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="E245" s="17"/>
       <c r="F245" s="18"/>
       <c r="G245" s="9"/>
       <c r="H245" s="3" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="I245" s="7" t="s">
         <v>16</v>
@@ -11715,21 +11739,21 @@
     </row>
     <row r="246" ht="22.5" customHeight="1">
       <c r="A246" s="3" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B246" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fr. Doctorin,  (-)</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="17"/>
       <c r="F246" s="18"/>
       <c r="G246" s="9"/>
       <c r="H246" s="3" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="I246" s="7" t="s">
         <v>16</v>
@@ -11739,17 +11763,17 @@
     </row>
     <row r="247" ht="22.5" customHeight="1">
       <c r="A247" s="3" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B247" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kusen, Jost von (1570-1630)</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="E247" s="5">
         <v>1570.0</v>
@@ -11758,10 +11782,10 @@
         <v>1630.0</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="I247" s="7" t="s">
         <v>16</v>
@@ -11771,14 +11795,14 @@
     </row>
     <row r="248" ht="22.5" customHeight="1">
       <c r="A248" s="3" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B248" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Heinrich (-)</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>37</v>
@@ -11787,7 +11811,7 @@
       <c r="F248" s="18"/>
       <c r="G248" s="9"/>
       <c r="H248" s="3" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="I248" s="7" t="s">
         <v>16</v>
@@ -11797,21 +11821,21 @@
     </row>
     <row r="249" ht="22.5" customHeight="1">
       <c r="A249" s="3" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="B249" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gessner,  (-)</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="17"/>
       <c r="F249" s="18"/>
       <c r="G249" s="9"/>
       <c r="H249" s="3" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="I249" s="7" t="s">
         <v>16</v>
@@ -11821,17 +11845,17 @@
     </row>
     <row r="250" ht="22.5" customHeight="1">
       <c r="A250" s="3" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="B250" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wöllwein, Johann Anton (1616-1659)</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="E250" s="5">
         <v>1616.0</v>
@@ -11840,10 +11864,10 @@
         <v>1659.0</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="I250" s="7" t="s">
         <v>16</v>
@@ -11853,42 +11877,42 @@
     </row>
     <row r="251" ht="22.5" customHeight="1">
       <c r="A251" s="3" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="B251" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Anna (-)</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="E251" s="17"/>
       <c r="F251" s="18"/>
       <c r="G251" s="9"/>
       <c r="H251" s="3" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="I251" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="K251" s="9"/>
     </row>
     <row r="252" ht="22.5" customHeight="1">
       <c r="A252" s="3" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="B252" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. J. R. S.,  (-)</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="D252" s="3"/>
       <c r="E252" s="17"/>
@@ -11901,17 +11925,17 @@
     </row>
     <row r="253" ht="22.5" customHeight="1">
       <c r="A253" s="3" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="B253" s="4" t="str">
         <f t="shared" si="1"/>
         <v>de Ruyter, Michiel (1607-1676)</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E253" s="5">
         <v>1607.0</v>
@@ -11920,10 +11944,10 @@
         <v>1676.0</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="I253" s="7" t="s">
         <v>16</v>
@@ -11933,21 +11957,21 @@
     </row>
     <row r="254" ht="22.5" customHeight="1">
       <c r="A254" s="3" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B254" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Frau Oberstin,  (-)</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="17"/>
       <c r="F254" s="18"/>
       <c r="G254" s="9"/>
       <c r="H254" s="3" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="I254" s="7" t="s">
         <v>16</v>
@@ -11957,23 +11981,23 @@
     </row>
     <row r="255" ht="22.5" customHeight="1">
       <c r="A255" s="3" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B255" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vulcanus,  (-)</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="17"/>
       <c r="F255" s="18"/>
       <c r="G255" s="3" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="I255" s="7" t="s">
         <v>231</v>
@@ -11983,23 +12007,23 @@
     </row>
     <row r="256" ht="22.5" customHeight="1">
       <c r="A256" s="3" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B256" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esau,  (-)</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="17"/>
       <c r="F256" s="18"/>
       <c r="G256" s="3" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="I256" s="7" t="s">
         <v>249</v>
@@ -12009,23 +12033,23 @@
     </row>
     <row r="257" ht="22.5" customHeight="1">
       <c r="A257" s="3" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="B257" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Danaos,  (-)</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="17"/>
       <c r="F257" s="18"/>
       <c r="G257" s="3" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="I257" s="7" t="s">
         <v>231</v>
@@ -12035,20 +12059,20 @@
     </row>
     <row r="258" ht="22.5" customHeight="1">
       <c r="A258" s="3" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="B258" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Medusa,  (-)</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="17"/>
       <c r="F258" s="18"/>
       <c r="G258" s="3" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>231</v>
@@ -12061,20 +12085,20 @@
     </row>
     <row r="259" ht="22.5" customHeight="1">
       <c r="A259" s="3" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="B259" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pluton,  (-)</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="17"/>
       <c r="F259" s="18"/>
       <c r="G259" s="3" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>231</v>
@@ -12087,20 +12111,20 @@
     </row>
     <row r="260" ht="22.5" customHeight="1">
       <c r="A260" s="3" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B260" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mercur,  (-)</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="17"/>
       <c r="F260" s="18"/>
       <c r="G260" s="3" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>231</v>
@@ -12113,20 +12137,20 @@
     </row>
     <row r="261" ht="22.5" customHeight="1">
       <c r="A261" s="3" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B261" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Perseus,  (-)</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="17"/>
       <c r="F261" s="18"/>
       <c r="G261" s="3" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>231</v>
@@ -12139,23 +12163,23 @@
     </row>
     <row r="262" ht="22.5" customHeight="1">
       <c r="A262" s="3" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="B262" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Atropos,  (-)</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="17"/>
       <c r="F262" s="18"/>
       <c r="G262" s="3" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="I262" s="7" t="s">
         <v>231</v>
@@ -12165,23 +12189,23 @@
     </row>
     <row r="263" ht="22.5" customHeight="1">
       <c r="A263" s="3" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="B263" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Barbara von Nikomedien,  (-)</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="17"/>
       <c r="F263" s="18"/>
       <c r="G263" s="3" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="H263" s="3" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="I263" s="7" t="s">
         <v>249</v>
@@ -12191,7 +12215,7 @@
     </row>
     <row r="264" ht="22.5" customHeight="1">
       <c r="A264" s="3" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="B264" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12199,13 +12223,13 @@
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="3" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="E264" s="17"/>
       <c r="F264" s="18"/>
       <c r="G264" s="9"/>
       <c r="H264" s="3" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="I264" s="13"/>
       <c r="J264" s="9"/>
@@ -12213,7 +12237,7 @@
     </row>
     <row r="265" ht="22.5" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="B265" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12227,7 +12251,7 @@
       <c r="F265" s="18"/>
       <c r="G265" s="9"/>
       <c r="H265" s="3" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="I265" s="13"/>
       <c r="J265" s="9"/>
@@ -12235,21 +12259,21 @@
     </row>
     <row r="266" ht="22.5" customHeight="1">
       <c r="A266" s="3" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="B266" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Karl,  (-)</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="17"/>
       <c r="F266" s="18"/>
       <c r="G266" s="9"/>
       <c r="H266" s="3" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="I266" s="7" t="s">
         <v>16</v>
@@ -12259,21 +12283,21 @@
     </row>
     <row r="267" ht="22.5" customHeight="1">
       <c r="A267" s="3" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="B267" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Duraeum,  (-)</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="17"/>
       <c r="F267" s="18"/>
       <c r="G267" s="9"/>
       <c r="H267" s="3" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="I267" s="13"/>
       <c r="J267" s="9"/>
@@ -12281,17 +12305,17 @@
     </row>
     <row r="268" ht="22.5" customHeight="1">
       <c r="A268" s="3" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="B268" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zesen, Philipp von (1619-1689)</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="E268" s="5">
         <v>1619.0</v>
@@ -12300,7 +12324,7 @@
         <v>1689.0</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="H268" s="3"/>
       <c r="I268" s="7" t="s">
@@ -12311,23 +12335,23 @@
     </row>
     <row r="269" ht="22.5" customHeight="1">
       <c r="A269" s="3" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="B269" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lucretia,  (-)</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="D269" s="3"/>
       <c r="E269" s="17"/>
       <c r="F269" s="18"/>
       <c r="G269" s="3" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="I269" s="7" t="s">
         <v>231</v>
@@ -12337,23 +12361,23 @@
     </row>
     <row r="270" ht="22.5" customHeight="1">
       <c r="A270" s="3" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B270" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ovid,  (-)</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="17"/>
       <c r="F270" s="18"/>
       <c r="G270" s="3" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="H270" s="3" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="I270" s="7" t="s">
         <v>16</v>
@@ -12363,50 +12387,50 @@
     </row>
     <row r="271" ht="22.5" customHeight="1">
       <c r="A271" s="3" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="B271" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schweizer, Johann Caspar (1619/1620-1684/1688)</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="H271" s="3" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="I271" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J271" s="8" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="K271" s="3" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
     </row>
     <row r="272" ht="22.5" customHeight="1">
       <c r="A272" s="3" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="B272" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Herder, Johann Heinrich (1629-1665)</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>43</v>
@@ -12418,10 +12442,10 @@
         <v>1665.0</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="H272" s="3" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="I272" s="7" t="s">
         <v>16</v>
@@ -12431,23 +12455,23 @@
     </row>
     <row r="273" ht="22.5" customHeight="1">
       <c r="A273" s="3" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B273" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Elischa,  (-)</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="D273" s="3"/>
       <c r="E273" s="17"/>
       <c r="F273" s="18"/>
       <c r="G273" s="3" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="H273" s="3" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="I273" s="7" t="s">
         <v>249</v>
@@ -12457,23 +12481,23 @@
     </row>
     <row r="274" ht="22.5" customHeight="1">
       <c r="A274" s="3" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="B274" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Johannes der Täufer,  (-)</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D274" s="3"/>
       <c r="E274" s="17"/>
       <c r="F274" s="18"/>
       <c r="G274" s="3" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="I274" s="7" t="s">
         <v>249</v>
@@ -12483,29 +12507,29 @@
     </row>
     <row r="275" ht="22.5" customHeight="1">
       <c r="A275" s="3" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="B275" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caesar, Gaius Iulius (100 v. Chr.-44 v. Chr.)</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="H275" s="3" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="I275" s="7" t="s">
         <v>16</v>
@@ -12515,23 +12539,23 @@
     </row>
     <row r="276" ht="22.5" customHeight="1">
       <c r="A276" s="3" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="B276" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Helios,  (-)</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="D276" s="3"/>
       <c r="E276" s="17"/>
       <c r="F276" s="18"/>
       <c r="G276" s="3" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="H276" s="3" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="I276" s="7" t="s">
         <v>231</v>
@@ -12541,25 +12565,33 @@
     </row>
     <row r="277" ht="22.5" customHeight="1">
       <c r="A277" s="3" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="B277" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>,  (-)</v>
-      </c>
-      <c r="C277" s="6"/>
+        <v>Suevus,  (-)</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>1016</v>
+      </c>
       <c r="D277" s="3"/>
       <c r="E277" s="17"/>
       <c r="F277" s="18"/>
       <c r="G277" s="9"/>
-      <c r="H277" s="3"/>
-      <c r="I277" s="13"/>
-      <c r="J277" s="9"/>
-      <c r="K277" s="9"/>
+      <c r="H277" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="I277" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="J277" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="K277" s="11"/>
     </row>
     <row r="278" ht="22.5" customHeight="1">
       <c r="A278" s="3" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="B278" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12577,7 +12609,7 @@
     </row>
     <row r="279" ht="22.5" customHeight="1">
       <c r="A279" s="3" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="B279" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12595,7 +12627,7 @@
     </row>
     <row r="280" ht="22.5" customHeight="1">
       <c r="A280" s="3" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="B280" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12648,39 +12680,40 @@
     <hyperlink r:id="rId25" ref="J41"/>
     <hyperlink r:id="rId26" ref="J42"/>
     <hyperlink r:id="rId27" ref="J43"/>
-    <hyperlink r:id="rId28" ref="J48"/>
-    <hyperlink r:id="rId29" ref="J51"/>
-    <hyperlink r:id="rId30" ref="J131"/>
-    <hyperlink r:id="rId31" ref="J132"/>
-    <hyperlink r:id="rId32" ref="J137"/>
-    <hyperlink r:id="rId33" ref="J138"/>
-    <hyperlink r:id="rId34" ref="J142"/>
-    <hyperlink r:id="rId35" ref="J143"/>
-    <hyperlink r:id="rId36" ref="J153"/>
-    <hyperlink r:id="rId37" ref="J154"/>
-    <hyperlink r:id="rId38" ref="J155"/>
-    <hyperlink r:id="rId39" ref="J160"/>
-    <hyperlink r:id="rId40" ref="J190"/>
-    <hyperlink r:id="rId41" ref="J191"/>
-    <hyperlink r:id="rId42" ref="J192"/>
-    <hyperlink r:id="rId43" ref="J193"/>
-    <hyperlink r:id="rId44" ref="J194"/>
-    <hyperlink r:id="rId45" ref="J197"/>
-    <hyperlink r:id="rId46" ref="J198"/>
-    <hyperlink r:id="rId47" ref="J199"/>
-    <hyperlink r:id="rId48" ref="J200"/>
-    <hyperlink r:id="rId49" ref="J201"/>
-    <hyperlink r:id="rId50" ref="J202"/>
-    <hyperlink r:id="rId51" ref="J203"/>
-    <hyperlink r:id="rId52" ref="J204"/>
-    <hyperlink r:id="rId53" ref="J216"/>
-    <hyperlink r:id="rId54" ref="J217"/>
-    <hyperlink r:id="rId55" ref="J224"/>
-    <hyperlink r:id="rId56" ref="J271"/>
+    <hyperlink r:id="rId28" ref="J46"/>
+    <hyperlink r:id="rId29" ref="J48"/>
+    <hyperlink r:id="rId30" ref="J51"/>
+    <hyperlink r:id="rId31" ref="J131"/>
+    <hyperlink r:id="rId32" ref="J132"/>
+    <hyperlink r:id="rId33" ref="J137"/>
+    <hyperlink r:id="rId34" ref="J138"/>
+    <hyperlink r:id="rId35" ref="J142"/>
+    <hyperlink r:id="rId36" ref="J143"/>
+    <hyperlink r:id="rId37" ref="J153"/>
+    <hyperlink r:id="rId38" ref="J154"/>
+    <hyperlink r:id="rId39" ref="J155"/>
+    <hyperlink r:id="rId40" ref="J160"/>
+    <hyperlink r:id="rId41" ref="J190"/>
+    <hyperlink r:id="rId42" ref="J191"/>
+    <hyperlink r:id="rId43" ref="J192"/>
+    <hyperlink r:id="rId44" ref="J193"/>
+    <hyperlink r:id="rId45" ref="J194"/>
+    <hyperlink r:id="rId46" ref="J197"/>
+    <hyperlink r:id="rId47" ref="J198"/>
+    <hyperlink r:id="rId48" ref="J199"/>
+    <hyperlink r:id="rId49" ref="J200"/>
+    <hyperlink r:id="rId50" ref="J201"/>
+    <hyperlink r:id="rId51" ref="J202"/>
+    <hyperlink r:id="rId52" ref="J203"/>
+    <hyperlink r:id="rId53" ref="J204"/>
+    <hyperlink r:id="rId54" ref="J216"/>
+    <hyperlink r:id="rId55" ref="J217"/>
+    <hyperlink r:id="rId56" ref="J224"/>
+    <hyperlink r:id="rId57" ref="J271"/>
   </hyperlinks>
-  <drawing r:id="rId57"/>
+  <drawing r:id="rId58"/>
   <tableParts count="1">
-    <tablePart r:id="rId59"/>
+    <tablePart r:id="rId60"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12702,16 +12735,16 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -12722,179 +12755,179 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="B2" s="22" t="str">
         <f t="shared" ref="B2:B102" si="1">CONCATENATE(C2)</f>
         <v>Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="7" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="B3" s="22" t="str">
         <f t="shared" si="1"/>
         <v>Basel</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="7" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="B4" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Eidgenossenschaft</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="E4" s="20"/>
       <c r="F4" s="3" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="B5" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Limmat</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D5" s="24"/>
       <c r="E5" s="7" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="B6" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Weinfelden</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="D6" s="24"/>
       <c r="E6" s="7" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="B7" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Main</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="7" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="B8" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Zürichsee</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="D8" s="24"/>
       <c r="E8" s="7" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="B9" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Thalwil</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="B10" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bern</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="7" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="B11" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Gottstatt</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="13"/>
@@ -12902,103 +12935,103 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="B12" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Thorberg</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="B13" s="23" t="str">
         <f t="shared" si="1"/>
         <v>London</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="D13" s="24"/>
       <c r="E13" s="7" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="B14" s="23" t="str">
         <f t="shared" si="1"/>
         <v>England</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="7" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="B15" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bethlehem</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="7" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="B16" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Parnass </v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="7" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="B17" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Traubenberg</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="13"/>
@@ -13006,50 +13039,50 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="B18" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Babylon</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="7" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="B19" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Canaan</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="13"/>
       <c r="F19" s="3" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="B20" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Ägypten</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="13"/>
@@ -13057,158 +13090,158 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="B21" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Hermon</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="7" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="B22" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Jerusalem</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="B23" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Jordan</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="D23" s="24"/>
       <c r="E23" s="7" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="B24" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Rotes Meer</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="D24" s="24"/>
       <c r="E24" s="7" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="F24" s="9"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="B25" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Juda</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="13"/>
       <c r="F25" s="3" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="B26" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Moab</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="13"/>
       <c r="F26" s="3" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="B27" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Ammon</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="13"/>
       <c r="F27" s="3" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="B28" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Zion</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="D28" s="24"/>
       <c r="E28" s="7" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="B29" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Assur</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="D29" s="24"/>
       <c r="E29" s="13"/>
@@ -13216,101 +13249,101 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="B30" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Israel</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="D30" s="24"/>
       <c r="E30" s="13"/>
       <c r="F30" s="3" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="B31" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Nazaret</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="7" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="B32" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Rom</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="D32" s="24"/>
       <c r="E32" s="13"/>
       <c r="F32" s="3" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="B33" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Samaria</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="D33" s="24"/>
       <c r="E33" s="13"/>
       <c r="F33" s="3" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="B34" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Kedronbach</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="D34" s="24"/>
       <c r="E34" s="13"/>
       <c r="F34" s="3" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="B35" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Garten von Getsemani</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="13"/>
@@ -13318,14 +13351,14 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="B36" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Urdorf</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="D36" s="24"/>
       <c r="E36" s="13"/>
@@ -13333,14 +13366,14 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="B37" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Geiren-Rein</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="D37" s="24"/>
       <c r="E37" s="13"/>
@@ -13348,14 +13381,14 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="B38" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Aeügst</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D38" s="24"/>
       <c r="E38" s="13"/>
@@ -13363,14 +13396,14 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="B39" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Riedt</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="D39" s="24"/>
       <c r="E39" s="13"/>
@@ -13378,14 +13411,14 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="B40" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Europa</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="D40" s="24"/>
       <c r="E40" s="13"/>
@@ -13393,48 +13426,48 @@
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="B41" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Osir</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="D41" s="24"/>
       <c r="E41" s="13"/>
       <c r="F41" s="3" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="B42" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Basadingen</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="D42" s="24"/>
       <c r="E42" s="13"/>
       <c r="F42" s="3" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="B43" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Diessenhofen</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="D43" s="24"/>
       <c r="E43" s="13"/>
@@ -13442,50 +13475,50 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="B44" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Rhein</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="D44" s="24"/>
       <c r="E44" s="7" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="B45" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Arabisches Reich</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="D45" s="24"/>
       <c r="E45" s="13"/>
       <c r="F45" s="3" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="B46" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Libanon</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="D46" s="24"/>
       <c r="E46" s="13"/>
@@ -13493,105 +13526,105 @@
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="B47" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Emmaus</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="D47" s="24"/>
       <c r="E47" s="13"/>
       <c r="F47" s="3" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="B48" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Helikon</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="7" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="B49" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Pindos</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="D49" s="24"/>
       <c r="E49" s="7" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="B50" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Neckar</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="D50" s="24"/>
       <c r="E50" s="7" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="B51" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Kurpfalz</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="D51" s="24"/>
       <c r="E51" s="13"/>
       <c r="F51" s="3" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="B52" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Eglisau</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="D52" s="24"/>
       <c r="E52" s="13"/>
@@ -13599,14 +13632,14 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="B53" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Altenklingen</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="D53" s="24"/>
       <c r="E53" s="13"/>
@@ -13614,14 +13647,14 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="B54" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Altorff</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="D54" s="24"/>
       <c r="E54" s="13"/>
@@ -13629,31 +13662,31 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="B55" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Glarus</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="D55" s="24"/>
       <c r="E55" s="13"/>
       <c r="F55" s="3" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="B56" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bergerkirche</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="D56" s="24"/>
       <c r="E56" s="13"/>
@@ -13661,31 +13694,31 @@
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="B57" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Sodom</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="D57" s="24"/>
       <c r="E57" s="13"/>
       <c r="F57" s="3" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="B58" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Haus zur Sonnenblume</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="D58" s="24"/>
       <c r="E58" s="13"/>
@@ -13693,31 +13726,31 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="B59" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Thurn/ genennt von Geissen</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="D59" s="24"/>
       <c r="E59" s="13"/>
       <c r="F59" s="3" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="B60" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Constantinopel</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="D60" s="24"/>
       <c r="E60" s="13"/>
@@ -13725,118 +13758,118 @@
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="B61" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Stein am Rhein</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="D61" s="24"/>
       <c r="E61" s="13"/>
       <c r="F61" s="3" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="B62" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Marburg</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="D62" s="24"/>
       <c r="E62" s="13"/>
       <c r="F62" s="3" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="B63" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Elbląg</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="E63" s="13"/>
       <c r="F63" s="3" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="B64" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Preußen</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="D64" s="24"/>
       <c r="E64" s="13"/>
       <c r="F64" s="3" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="B65" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bad Baden</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="D65" s="24"/>
       <c r="E65" s="13"/>
       <c r="F65" s="3" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>1189</v>
+        <v>1193</v>
       </c>
       <c r="B66" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bad Schinznach</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="D66" s="24"/>
       <c r="E66" s="13"/>
       <c r="F66" s="3" t="s">
-        <v>1188</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>1191</v>
+        <v>1195</v>
       </c>
       <c r="B67" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Gyrenbad</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="D67" s="24"/>
       <c r="E67" s="13"/>
@@ -13844,48 +13877,48 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>1193</v>
+        <v>1197</v>
       </c>
       <c r="B68" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Wängibad</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1194</v>
+        <v>1198</v>
       </c>
       <c r="D68" s="24"/>
       <c r="E68" s="13"/>
       <c r="F68" s="8" t="s">
-        <v>1195</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="B69" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Aeugst</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="D69" s="24"/>
       <c r="E69" s="13"/>
       <c r="F69" s="3" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>1198</v>
+        <v>1202</v>
       </c>
       <c r="B70" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Bassersdorf</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1199</v>
+        <v>1203</v>
       </c>
       <c r="D70" s="24"/>
       <c r="E70" s="13"/>
@@ -13893,14 +13926,14 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="B71" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Hauptwil</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
       <c r="D71" s="24"/>
       <c r="E71" s="13"/>
@@ -13908,14 +13941,14 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>1202</v>
+        <v>1206</v>
       </c>
       <c r="B72" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Schaffhausen</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1203</v>
+        <v>1207</v>
       </c>
       <c r="D72" s="24"/>
       <c r="E72" s="13"/>
@@ -13923,65 +13956,65 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>1204</v>
+        <v>1208</v>
       </c>
       <c r="B73" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Wädenswil</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="D73" s="24"/>
       <c r="E73" s="13"/>
       <c r="F73" s="3" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>1207</v>
+        <v>1211</v>
       </c>
       <c r="B74" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Freie Ämter</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1208</v>
+        <v>1212</v>
       </c>
       <c r="D74" s="24"/>
       <c r="E74" s="13"/>
       <c r="F74" s="3" t="s">
-        <v>1209</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>1210</v>
+        <v>1214</v>
       </c>
       <c r="B75" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Grüningen</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="D75" s="24"/>
       <c r="E75" s="13"/>
       <c r="F75" s="3" t="s">
-        <v>1206</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>1212</v>
+        <v>1216</v>
       </c>
       <c r="B76" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Kefikon</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="D76" s="24"/>
       <c r="E76" s="13"/>
@@ -13989,14 +14022,14 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="B77" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Maienfeld</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1215</v>
+        <v>1219</v>
       </c>
       <c r="D77" s="24"/>
       <c r="E77" s="13"/>
@@ -14004,14 +14037,14 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>1216</v>
+        <v>1220</v>
       </c>
       <c r="B78" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Greifensee (Schloss)</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1217</v>
+        <v>1221</v>
       </c>
       <c r="D78" s="24"/>
       <c r="E78" s="13"/>
@@ -14019,31 +14052,31 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="B79" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Lindenhof (Zürich)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1219</v>
+        <v>1223</v>
       </c>
       <c r="D79" s="24"/>
       <c r="E79" s="13"/>
       <c r="F79" s="3" t="s">
-        <v>1220</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>1221</v>
+        <v>1225</v>
       </c>
       <c r="B80" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Galg-Brunnen (Zürich)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="D80" s="24"/>
       <c r="E80" s="13"/>
@@ -14051,14 +14084,14 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
       <c r="B81" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Altes Kornhaus (Zürich)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1224</v>
+        <v>1228</v>
       </c>
       <c r="D81" s="24"/>
       <c r="E81" s="13"/>
@@ -14066,14 +14099,14 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="B82" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Sparrenberg (Zürich)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="D82" s="24"/>
       <c r="E82" s="13"/>
@@ -14081,14 +14114,14 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="B83" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Thurgau</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="D83" s="24"/>
       <c r="E83" s="13"/>
@@ -14096,14 +14129,14 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="B84" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Niederlande</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1230</v>
+        <v>1234</v>
       </c>
       <c r="D84" s="24"/>
       <c r="E84" s="13"/>
@@ -14111,31 +14144,31 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="B85" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Holland</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="D85" s="24"/>
       <c r="E85" s="13"/>
       <c r="F85" s="3" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>1234</v>
+        <v>1238</v>
       </c>
       <c r="B86" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Wigoltingen</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="D86" s="24"/>
       <c r="E86" s="13"/>
@@ -14143,31 +14176,31 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="B87" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Kastalia</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1237</v>
+        <v>1241</v>
       </c>
       <c r="D87" s="24"/>
       <c r="E87" s="13"/>
       <c r="F87" s="3" t="s">
-        <v>1238</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>1239</v>
+        <v>1243</v>
       </c>
       <c r="B88" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Legerberg</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="D88" s="24"/>
       <c r="E88" s="13"/>
@@ -14175,48 +14208,48 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>1241</v>
+        <v>1245</v>
       </c>
       <c r="B89" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Texel</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1242</v>
+        <v>1246</v>
       </c>
       <c r="D89" s="24"/>
       <c r="E89" s="13"/>
       <c r="F89" s="3" t="s">
-        <v>1243</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="B90" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Vlie</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="D90" s="24"/>
       <c r="E90" s="13"/>
       <c r="F90" s="3" t="s">
-        <v>1246</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>1247</v>
+        <v>1251</v>
       </c>
       <c r="B91" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Indien</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="D91" s="24"/>
       <c r="E91" s="13"/>
@@ -14224,14 +14257,14 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
       <c r="B92" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Wien</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>1250</v>
+        <v>1254</v>
       </c>
       <c r="D92" s="24"/>
       <c r="E92" s="13"/>
@@ -14239,14 +14272,14 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>1251</v>
+        <v>1255</v>
       </c>
       <c r="B93" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Deutschland</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1252</v>
+        <v>1256</v>
       </c>
       <c r="D93" s="24"/>
       <c r="E93" s="13"/>
@@ -14254,60 +14287,60 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
       <c r="B94" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Ölberg</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1254</v>
+        <v>1258</v>
       </c>
       <c r="D94" s="24"/>
       <c r="E94" s="7" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="F94" s="3"/>
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>1255</v>
+        <v>1259</v>
       </c>
       <c r="B95" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Dietikon</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="D95" s="24"/>
       <c r="E95" s="7" t="s">
-        <v>1257</v>
+        <v>1261</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="B96" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Winterthur</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1260</v>
+        <v>1264</v>
       </c>
       <c r="D96" s="24"/>
       <c r="E96" s="7" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="F96" s="3"/>
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>1261</v>
+        <v>1265</v>
       </c>
       <c r="B97" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14320,7 +14353,7 @@
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="B98" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14333,7 +14366,7 @@
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
       <c r="B99" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14346,7 +14379,7 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="B100" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14359,7 +14392,7 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="B101" s="23" t="str">
         <f t="shared" si="1"/>
@@ -14418,25 +14451,25 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1270</v>
+        <v>1274</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
@@ -14447,75 +14480,75 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1272</v>
+        <v>1276</v>
       </c>
       <c r="B2" s="25" t="str">
         <f t="shared" ref="B2:B30" si="1">CONCATENATE(C2)</f>
         <v>Teutsche Gedichte</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1273</v>
+        <v>1277</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1274</v>
+        <v>1278</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="I2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="B3" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Die Krafft der Gottseligkeit</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B4" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Buch von Festen</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5"/>
@@ -14525,23 +14558,23 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="B5" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Der Psalter dess Königlichen Propheten Dauids/ Jn deutsche reymen verstendiglich vnd deutlich gebracht/ mit vorgehender anzeigung der reymen weise/ auch eines jeden Psalmes Jnhalt</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1290</v>
+        <v>1294</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1291</v>
+        <v>1295</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="13"/>
@@ -14549,73 +14582,73 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B6" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Hundert christliche Fäst-Predigen</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>1297</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
       <c r="B7" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Spiegel der Unermesslichen Gnad Gottes gegen den rewenden bussfertigen Sünderen/ Jn XLV. Predigen vber das XV. capitel Lucae/ vom verlohrnen Schaaf/ Pfenning/ vnd Sohn verfasset</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="B8" s="25" t="str">
         <f t="shared" si="1"/>
         <v>verteütschte Rueh- oder Fridens-uebung</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="24"/>
@@ -14625,98 +14658,98 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="B9" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Nähefelser-Fahrt: in zehen erbaulichen Jahrzeit-Predigen zu schuldigem Danck dem Höhesten für den im Jahr 1388 gemeinen Landleuthen dess lobl. Eydgnössischen Bundorths Glarus wider ihre Feind bey und umb Nähefels verliehenen Wundersieg </v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="10" t="s">
-        <v>1312</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1313</v>
+        <v>1317</v>
       </c>
       <c r="B10" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Die vier Haubtpuncten der christlichen seligmachenden Religion: auf alle Sontag des gantzen Jahrs ordenlich abgetheilt, grundtlich nach der heiligen Schrifft erklärt und zur Erbawung gerichtet </v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1314</v>
+        <v>1318</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1317</v>
+        <v>1321</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>1318</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1319</v>
+        <v>1323</v>
       </c>
       <c r="B11" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Architectura von Vestungen</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1320</v>
+        <v>1324</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="8" t="s">
-        <v>1323</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="B12" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Buech der Freunden Stammen</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="D12" s="24"/>
       <c r="E12" s="9"/>
@@ -14727,42 +14760,42 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="B13" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Christen-Spiegel, das ist, Bedenkliche Erinnerungen über die Beruoffspflichten aller Ständen </v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1327</v>
+        <v>1331</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1332</v>
+        <v>1336</v>
       </c>
       <c r="B14" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Viergeticht</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="9"/>
@@ -14773,14 +14806,14 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1334</v>
+        <v>1338</v>
       </c>
       <c r="B15" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Regentenspiegel</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1335</v>
+        <v>1339</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="9"/>
@@ -14791,18 +14824,18 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1336</v>
+        <v>1340</v>
       </c>
       <c r="B16" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Türckischer Jammerspiegel</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1337</v>
+        <v>1341</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="3" t="s">
-        <v>1338</v>
+        <v>1342</v>
       </c>
       <c r="F16" s="24"/>
       <c r="G16" s="9"/>
@@ -14811,17 +14844,17 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="B17" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Leitungs-faden</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1340</v>
+        <v>1344</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="24"/>
@@ -14831,17 +14864,17 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1341</v>
+        <v>1345</v>
       </c>
       <c r="B18" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Buch von der Seelen-angſt Chriſti</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="24"/>
@@ -14851,17 +14884,17 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
       <c r="B19" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Verſuchungs-gabe</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1345</v>
+        <v>1349</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1346</v>
+        <v>1350</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="24"/>
@@ -14871,14 +14904,14 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="B20" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Kriegsbüchlin</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="9"/>
@@ -14889,14 +14922,14 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="B21" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Buch der Psalmen</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="9"/>
@@ -14907,117 +14940,117 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="B22" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Sterbensspiegel/ das ist sonnenklare Vorstellung menschlicher Nichtigkeit durch alle Staend und Geschlechter</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="B23" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Warhaffte/ vnd in Gottes Wort wol gegründte Widerlegung Des newlich im Truck außgegangnen ohn-Catholischen Gesprächs von Religion oder Glaubens sachen/ geneñt der Augenspiegel</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1357</v>
+        <v>1361</v>
       </c>
       <c r="D23" s="5" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>1358</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>1359</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>1020</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>1354</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>1360</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1361</v>
+        <v>1365</v>
       </c>
       <c r="B24" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Augspiegels Wahrer Religion Erster Theil</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="B25" s="25" t="str">
         <f t="shared" si="1"/>
         <v>De kracht der Godsaligheyt</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="H25" s="13"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="B26" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15033,7 +15066,7 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="B27" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15049,7 +15082,7 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="B28" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15065,7 +15098,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1377</v>
+        <v>1381</v>
       </c>
       <c r="B29" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15081,7 +15114,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
       <c r="B30" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15137,19 +15170,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1379</v>
+        <v>1383</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -15157,69 +15190,69 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1381</v>
+        <v>1385</v>
       </c>
       <c r="B2" s="25" t="str">
         <f t="shared" ref="B2:B24" si="1">CONCATENATE(C2)</f>
         <v>Rat Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1382</v>
+        <v>1386</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="26" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1384</v>
+        <v>1388</v>
       </c>
       <c r="B3" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Fruchtbringende Gesellschaft</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1385</v>
+        <v>1389</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="B4" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Deutschgesinnte Genossenschaft (Lilien-Zunft)</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="B5" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Parthenicum</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="13"/>
@@ -15227,107 +15260,107 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="B6" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Carolinum Zürich</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="3" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1398</v>
+        <v>1402</v>
       </c>
       <c r="B7" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Sanhedrin</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="13"/>
       <c r="F7" s="3" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="B8" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Bürgerbibliothek Zürich</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="3" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="B9" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Grossmünster</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="B10" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Fraumünster Zürich</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="3" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="B11" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Hohe Schule Marburg</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="13"/>
@@ -15335,24 +15368,24 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="B12" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Kartäuser</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1418</v>
+        <v>1422</v>
       </c>
       <c r="B13" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15365,7 +15398,7 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="B14" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15378,7 +15411,7 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1420</v>
+        <v>1424</v>
       </c>
       <c r="B15" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15391,7 +15424,7 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1421</v>
+        <v>1425</v>
       </c>
       <c r="B16" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15404,7 +15437,7 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="B17" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15417,7 +15450,7 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="B18" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15430,7 +15463,7 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="B19" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15443,7 +15476,7 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1425</v>
+        <v>1429</v>
       </c>
       <c r="B20" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15456,7 +15489,7 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1426</v>
+        <v>1430</v>
       </c>
       <c r="B21" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15469,7 +15502,7 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="B22" s="25" t="str">
         <f t="shared" si="1"/>
@@ -15532,19 +15565,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -15552,26 +15585,26 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1432</v>
+        <v>1436</v>
       </c>
       <c r="B2" s="22" t="str">
         <f t="shared" ref="B2:B8" si="1">CONCATENATE(C2)</f>
         <v>Runs</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1433</v>
+        <v>1437</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>1435</v>
+        <v>1439</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="B3" s="22" t="str">
         <f t="shared" si="1"/>
@@ -15584,7 +15617,7 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="B4" s="22" t="str">
         <f t="shared" si="1"/>
@@ -15597,7 +15630,7 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="B5" s="22" t="str">
         <f t="shared" si="1"/>
@@ -15610,7 +15643,7 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="B6" s="22" t="str">
         <f t="shared" si="1"/>
@@ -15623,7 +15656,7 @@
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="B7" s="22" t="str">
         <f t="shared" si="1"/>
@@ -15636,7 +15669,7 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="B8" s="22" t="str">
         <f t="shared" si="1"/>

--- a/gsheet/xlsx/entities.xlsx
+++ b/gsheet/xlsx/entities.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="1593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="1603">
   <si>
     <t>Person-ID</t>
   </si>
@@ -1185,6 +1185,12 @@
   </si>
   <si>
     <t>Joseph</t>
+  </si>
+  <si>
+    <t>118639986</t>
+  </si>
+  <si>
+    <t>Sohn des Erzvaters Jakob</t>
   </si>
   <si>
     <t>person_077</t>
@@ -3383,9 +3389,30 @@
     <t>person_286</t>
   </si>
   <si>
+    <t>Agapetus</t>
+  </si>
+  <si>
+    <t>6. Jh.</t>
+  </si>
+  <si>
+    <t>118920898</t>
+  </si>
+  <si>
+    <t>Diakon</t>
+  </si>
+  <si>
+    <t>https://de.wikipedia.org/wiki/Agapetos</t>
+  </si>
+  <si>
     <t>person_287</t>
   </si>
   <si>
+    <t>Justinian I.</t>
+  </si>
+  <si>
+    <t>11855896X</t>
+  </si>
+  <si>
     <t>person_288</t>
   </si>
   <si>
@@ -3956,7 +3983,10 @@
     <t>place_059</t>
   </si>
   <si>
-    <t>Constantinopel</t>
+    <t>Konstantinopel</t>
+  </si>
+  <si>
+    <t>Istanbul</t>
   </si>
   <si>
     <t>place_060</t>
@@ -7856,9 +7886,11 @@
       <c r="D76" s="3"/>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
-      <c r="G76" s="9"/>
+      <c r="G76" s="3" t="s">
+        <v>379</v>
+      </c>
       <c r="H76" s="3" t="s">
-        <v>271</v>
+        <v>380</v>
       </c>
       <c r="I76" s="7" t="s">
         <v>271</v>
@@ -7868,14 +7900,14 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B77" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Saul, dessen Sohn,  (-)</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="5"/>
@@ -7892,20 +7924,20 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B78" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Satan,  (-)</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D78" s="3"/>
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
       <c r="G78" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>271</v>
@@ -7918,14 +7950,14 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B79" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Abigail,  (-)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D79" s="3"/>
       <c r="E79" s="5"/>
@@ -7942,14 +7974,14 @@
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B80" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hanna,  (-)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D80" s="3"/>
       <c r="E80" s="5"/>
@@ -7966,14 +7998,14 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B81" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Susanna,  (-)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D81" s="3"/>
       <c r="E81" s="5"/>
@@ -7990,14 +8022,14 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B82" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esther,  (-)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="5"/>
@@ -8014,14 +8046,14 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B83" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jaël,  (-)</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D83" s="3"/>
       <c r="E83" s="5"/>
@@ -8038,7 +8070,7 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B84" s="4" t="str">
         <f t="shared" si="1"/>
@@ -8062,21 +8094,21 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B85" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Asarias,  (-)</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D85" s="3"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
       <c r="G85" s="9"/>
       <c r="H85" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I85" s="7" t="s">
         <v>271</v>
@@ -8086,23 +8118,23 @@
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B86" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Boreas,  (-)</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D86" s="3"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="I86" s="7" t="s">
         <v>234</v>
@@ -8112,23 +8144,23 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B87" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ceres,  (-)</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D87" s="3"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
       <c r="G87" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I87" s="7" t="s">
         <v>234</v>
@@ -8138,23 +8170,23 @@
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B88" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Amor,  (-)</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I88" s="7" t="s">
         <v>234</v>
@@ -8164,23 +8196,23 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B89" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sokrates,  (-)</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
       <c r="G89" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="I89" s="7" t="s">
         <v>16</v>
@@ -8190,23 +8222,23 @@
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B90" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Xantippe,  (-)</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I90" s="7" t="s">
         <v>16</v>
@@ -8216,23 +8248,23 @@
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B91" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mars,  (-)</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
       <c r="G91" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I91" s="7" t="s">
         <v>234</v>
@@ -8242,23 +8274,23 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B92" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Apollo (Phoebus),  (-)</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
       <c r="G92" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I92" s="7" t="s">
         <v>234</v>
@@ -8268,21 +8300,21 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B93" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sirius,  (-)</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
       <c r="G93" s="9"/>
       <c r="H93" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I93" s="7" t="s">
         <v>234</v>
@@ -8292,14 +8324,14 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B94" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rebecca,  (-)</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="5"/>
@@ -8316,21 +8348,21 @@
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B95" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Asteria,  (-)</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
       <c r="G95" s="9"/>
       <c r="H95" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="I95" s="13"/>
       <c r="J95" s="9"/>
@@ -8338,21 +8370,21 @@
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B96" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sylvia,  (-)</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
       <c r="G96" s="9"/>
       <c r="H96" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="I96" s="13"/>
       <c r="J96" s="9"/>
@@ -8360,21 +8392,21 @@
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B97" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Felicitas,  (-)</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
       <c r="G97" s="9"/>
       <c r="H97" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="I97" s="13"/>
       <c r="J97" s="9"/>
@@ -8382,21 +8414,21 @@
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B98" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dorothea,  (-)</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="9"/>
       <c r="H98" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I98" s="13"/>
       <c r="J98" s="9"/>
@@ -8404,7 +8436,7 @@
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B99" s="4" t="str">
         <f t="shared" si="1"/>
@@ -8418,7 +8450,7 @@
       <c r="F99" s="5"/>
       <c r="G99" s="9"/>
       <c r="H99" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="I99" s="13"/>
       <c r="J99" s="9"/>
@@ -8426,14 +8458,14 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B100" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sara,  (-)</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="5"/>
@@ -8450,23 +8482,23 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B101" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hesiodus,  (-)</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="5"/>
       <c r="F101" s="5"/>
       <c r="G101" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="I101" s="13"/>
       <c r="J101" s="9"/>
@@ -8474,23 +8506,23 @@
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B102" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Parmenides,  (-)</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
       <c r="G102" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="I102" s="13"/>
       <c r="J102" s="9"/>
@@ -8498,48 +8530,48 @@
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B103" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salomon/Salomo,  (-)</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D103" s="3"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
       <c r="G103" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I103" s="7" t="s">
         <v>271</v>
       </c>
       <c r="J103" s="10" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K103" s="9"/>
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B104" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Isaak,  (-)</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
       <c r="G104" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>271</v>
@@ -8552,14 +8584,14 @@
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B105" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Rahel,  (-)</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="5"/>
@@ -8576,20 +8608,20 @@
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B106" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hiob,  (-)</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="5"/>
       <c r="F106" s="5"/>
       <c r="G106" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>271</v>
@@ -8602,14 +8634,14 @@
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B107" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simson,  (-)</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="5"/>
@@ -8626,23 +8658,23 @@
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B108" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ben Sira,  (-)</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
       <c r="G108" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I108" s="13"/>
       <c r="J108" s="9"/>
@@ -8650,20 +8682,20 @@
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B109" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wilhelm Tell,  (-)</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D109" s="3"/>
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
       <c r="G109" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="13"/>
@@ -8672,23 +8704,23 @@
     </row>
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B110" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zephyr,  (-)</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D110" s="3"/>
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
       <c r="G110" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I110" s="7" t="s">
         <v>234</v>
@@ -8698,7 +8730,7 @@
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B111" s="4" t="str">
         <f t="shared" si="1"/>
@@ -8722,21 +8754,21 @@
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B112" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Friedensfürst,  (-)</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
       <c r="G112" s="9"/>
       <c r="H112" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I112" s="13"/>
       <c r="J112" s="9"/>
@@ -8744,21 +8776,21 @@
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B113" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gracchus,  (-)</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
       <c r="G113" s="9"/>
       <c r="H113" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="I113" s="13"/>
       <c r="J113" s="9"/>
@@ -8766,21 +8798,21 @@
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B114" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gracchus, dessen Frau,  (-)</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
       <c r="G114" s="9"/>
       <c r="H114" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="I114" s="13"/>
       <c r="J114" s="9"/>
@@ -8788,20 +8820,20 @@
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B115" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Moses,  (-)</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D115" s="3"/>
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
       <c r="G115" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>271</v>
@@ -8814,23 +8846,23 @@
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B116" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orestes,  (-)</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
       <c r="G116" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I116" s="7" t="s">
         <v>234</v>
@@ -8840,23 +8872,23 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B117" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pylades,  (-)</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
       <c r="G117" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I117" s="7" t="s">
         <v>234</v>
@@ -8866,47 +8898,47 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B118" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thurik,  (-)</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
       <c r="G118" s="9"/>
       <c r="H118" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="I118" s="7" t="s">
         <v>234</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K118" s="11"/>
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B119" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Midas,  (-)</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
       <c r="G119" s="9"/>
       <c r="H119" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I119" s="7" t="s">
         <v>234</v>
@@ -8916,49 +8948,49 @@
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B120" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simon,  (-)</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
       <c r="G120" s="9"/>
       <c r="H120" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I120" s="7" t="s">
         <v>234</v>
       </c>
       <c r="J120" s="9"/>
       <c r="K120" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B121" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Damokles,  (-)</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
       <c r="G121" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I121" s="13"/>
       <c r="J121" s="9"/>
@@ -8966,23 +8998,23 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B122" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dionysius I. von Syrakus,  (-)</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
       <c r="G122" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I122" s="13"/>
       <c r="J122" s="9"/>
@@ -8990,23 +9022,23 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B123" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kleopatra VII.,  (-)</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
       <c r="G123" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="I123" s="7" t="s">
         <v>16</v>
@@ -9016,25 +9048,25 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B124" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Antonius, Marcus (-)</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
       <c r="G124" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I124" s="7" t="s">
         <v>16</v>
@@ -9044,23 +9076,23 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B125" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klio,  (-)</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
       <c r="G125" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I125" s="7" t="s">
         <v>234</v>
@@ -9070,23 +9102,23 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B126" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Flora,  (-)</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
       <c r="G126" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I126" s="7" t="s">
         <v>234</v>
@@ -9096,14 +9128,14 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B127" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dorothea,  (-)</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D127" s="3"/>
       <c r="E127" s="5"/>
@@ -9116,21 +9148,21 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B128" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. J. V.,  (-)</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
       <c r="G128" s="9"/>
       <c r="H128" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I128" s="7" t="s">
         <v>16</v>
@@ -9140,21 +9172,21 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B129" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. J. V., dessen Frau,  (-)</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
       <c r="G129" s="9"/>
       <c r="H129" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="I129" s="7" t="s">
         <v>16</v>
@@ -9164,21 +9196,21 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B130" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sch. H.,  (-)</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
       <c r="G130" s="9"/>
       <c r="H130" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I130" s="7" t="s">
         <v>16</v>
@@ -9188,14 +9220,14 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B131" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser, Johann Heinrich (1600-1669)</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>44</v>
@@ -9207,66 +9239,66 @@
         <v>1669.0</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="H131" s="15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="I131" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J131" s="14" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K131" s="9"/>
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B132" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser-Ziegler, Jahel (-)</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
       <c r="G132" s="9"/>
       <c r="H132" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I132" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="K132" s="9"/>
     </row>
     <row r="133" ht="22.5" customHeight="1">
       <c r="A133" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B133" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caspar W.,  (-)</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
       <c r="G133" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I133" s="7" t="s">
         <v>16</v>
@@ -9276,21 +9308,21 @@
     </row>
     <row r="134" ht="22.5" customHeight="1">
       <c r="A134" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B134" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esther O.,  (-)</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
       <c r="G134" s="9"/>
       <c r="H134" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="I134" s="7" t="s">
         <v>16</v>
@@ -9300,14 +9332,14 @@
     </row>
     <row r="135" ht="22.5" customHeight="1">
       <c r="A135" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B135" s="4" t="str">
         <f t="shared" si="1"/>
         <v>G. H.,  (-)</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="5"/>
@@ -9322,21 +9354,21 @@
     </row>
     <row r="136" ht="22.5" customHeight="1">
       <c r="A136" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B136" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. C.,  (-)</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
       <c r="G136" s="9"/>
       <c r="H136" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="I136" s="7" t="s">
         <v>16</v>
@@ -9346,17 +9378,17 @@
     </row>
     <row r="137" ht="22.5" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B137" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Hercules von (1617-1686)</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E137" s="5">
         <v>1617.0</v>
@@ -9365,30 +9397,30 @@
         <v>1686.0</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="H137" s="3"/>
       <c r="I137" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="K137" s="9"/>
     </row>
     <row r="138" ht="22.5" customHeight="1">
       <c r="A138" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B138" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Barbara Dorothea von (1629-1660)</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E138" s="5">
         <v>1629.0</v>
@@ -9398,26 +9430,26 @@
       </c>
       <c r="G138" s="9"/>
       <c r="H138" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="I138" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J138" s="8" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K138" s="9"/>
     </row>
     <row r="139" ht="22.5" customHeight="1">
       <c r="A139" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B139" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. L.,  (-)</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="5"/>
@@ -9432,21 +9464,21 @@
     </row>
     <row r="140" ht="22.5" customHeight="1">
       <c r="A140" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B140" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. A.,  (-)</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
       <c r="G140" s="9"/>
       <c r="H140" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="I140" s="7" t="s">
         <v>16</v>
@@ -9456,21 +9488,21 @@
     </row>
     <row r="141" ht="22.5" customHeight="1">
       <c r="A141" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B141" s="4" t="str">
         <f t="shared" si="1"/>
         <v>B. M.,  (-)</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D141" s="3"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
       <c r="G141" s="9"/>
       <c r="H141" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="I141" s="7" t="s">
         <v>16</v>
@@ -9480,73 +9512,73 @@
     </row>
     <row r="142" ht="22.5" customHeight="1">
       <c r="A142" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B142" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. H.,  (-)</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="9"/>
       <c r="H142" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="I142" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K142" s="9"/>
     </row>
     <row r="143" ht="22.5" customHeight="1">
       <c r="A143" s="3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B143" s="4" t="str">
         <f t="shared" si="1"/>
         <v>D. M.,  (-)</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D143" s="3"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
       <c r="G143" s="9"/>
       <c r="H143" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="I143" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K143" s="9"/>
     </row>
     <row r="144" ht="22.5" customHeight="1">
       <c r="A144" s="3" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B144" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gottfrid,  (-)</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
       <c r="G144" s="9"/>
       <c r="H144" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="I144" s="7" t="s">
         <v>16</v>
@@ -9556,7 +9588,7 @@
     </row>
     <row r="145" ht="22.5" customHeight="1">
       <c r="A145" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B145" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9570,7 +9602,7 @@
       <c r="F145" s="5"/>
       <c r="G145" s="9"/>
       <c r="H145" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="I145" s="7" t="s">
         <v>16</v>
@@ -9580,21 +9612,21 @@
     </row>
     <row r="146" ht="22.5" customHeight="1">
       <c r="A146" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B146" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. Schw.,  (-)</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D146" s="3"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
       <c r="G146" s="9"/>
       <c r="H146" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="I146" s="7" t="s">
         <v>16</v>
@@ -9604,21 +9636,21 @@
     </row>
     <row r="147" ht="22.5" customHeight="1">
       <c r="A147" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B147" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. K.,  (-)</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
       <c r="G147" s="9"/>
       <c r="H147" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="I147" s="7" t="s">
         <v>16</v>
@@ -9628,14 +9660,14 @@
     </row>
     <row r="148" ht="22.5" customHeight="1">
       <c r="A148" s="3" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B148" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ott, Hans Heinrich (-)</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>70</v>
@@ -9652,14 +9684,14 @@
     </row>
     <row r="149" ht="22.5" customHeight="1">
       <c r="A149" s="3" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B149" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. W.,  (-)</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D149" s="3"/>
       <c r="E149" s="5"/>
@@ -9674,21 +9706,21 @@
     </row>
     <row r="150" ht="22.5" customHeight="1">
       <c r="A150" s="3" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B150" s="4" t="str">
         <f t="shared" si="1"/>
         <v>V. L.,  (-)</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
       <c r="G150" s="9"/>
       <c r="H150" s="3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="I150" s="7" t="s">
         <v>16</v>
@@ -9698,14 +9730,14 @@
     </row>
     <row r="151" ht="22.5" customHeight="1">
       <c r="A151" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B151" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. Sch.,  (-)</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D151" s="3"/>
       <c r="E151" s="5"/>
@@ -9720,21 +9752,21 @@
     </row>
     <row r="152" ht="22.5" customHeight="1">
       <c r="A152" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B152" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. H.,  (-)</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
       <c r="G152" s="9"/>
       <c r="H152" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="I152" s="7" t="s">
         <v>16</v>
@@ -9744,14 +9776,14 @@
     </row>
     <row r="153" ht="22.5" customHeight="1">
       <c r="A153" s="3" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B153" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. H.,  (-)</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="5"/>
@@ -9762,55 +9794,55 @@
         <v>16</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K153" s="9"/>
     </row>
     <row r="154" ht="22.5" customHeight="1">
       <c r="A154" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B154" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. W.,  (-)</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="9"/>
       <c r="H154" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="I154" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="K154" s="9"/>
     </row>
     <row r="155" ht="22.5" customHeight="1">
       <c r="A155" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B155" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Koller, Elisabeth (-)</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
       <c r="G155" s="9"/>
       <c r="H155" s="3" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="I155" s="7" t="s">
         <v>16</v>
@@ -9822,17 +9854,17 @@
     </row>
     <row r="156" ht="22.5" customHeight="1">
       <c r="A156" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B156" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lobwasser, Ambrosius (1515-1585)</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E156" s="5">
         <v>1515.0</v>
@@ -9841,10 +9873,10 @@
         <v>1585.0</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="I156" s="7" t="s">
         <v>16</v>
@@ -9854,14 +9886,14 @@
     </row>
     <row r="157" ht="22.5" customHeight="1">
       <c r="A157" s="3" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B157" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vollenweider, Jakob (1594-1647)</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>373</v>
@@ -9873,10 +9905,10 @@
         <v>1647.0</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="I157" s="7" t="s">
         <v>16</v>
@@ -9886,7 +9918,7 @@
     </row>
     <row r="158" ht="22.5" customHeight="1">
       <c r="A158" s="3" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B158" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9896,7 +9928,7 @@
         <v>226</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="E158" s="5">
         <v>1606.0</v>
@@ -9905,7 +9937,7 @@
         <v>1660.0</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>229</v>
@@ -9918,17 +9950,17 @@
     </row>
     <row r="159" ht="22.5" customHeight="1">
       <c r="A159" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B159" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Burkhard, Hans Konrad (1613-1681)</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E159" s="5">
         <v>1613.0</v>
@@ -9937,10 +9969,10 @@
         <v>1681.0</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="I159" s="7" t="s">
         <v>16</v>
@@ -9950,14 +9982,14 @@
     </row>
     <row r="160" ht="22.5" customHeight="1">
       <c r="A160" s="3" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B160" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ardüser, Johann (1585-1665)</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>108</v>
@@ -9969,40 +10001,40 @@
         <v>1665.0</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="I160" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J160" s="12" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="K160" s="9"/>
     </row>
     <row r="161" ht="22.5" customHeight="1">
       <c r="A161" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B161" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hegner, Diethelm  (-)</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
       <c r="G161" s="3" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="I161" s="7" t="s">
         <v>16</v>
@@ -10012,17 +10044,17 @@
     </row>
     <row r="162" ht="22.5" customHeight="1">
       <c r="A162" s="3" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B162" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Trigland, Jacobus (1583-1654)</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E162" s="16">
         <v>1583.0</v>
@@ -10031,10 +10063,10 @@
         <v>1654.0</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="I162" s="7" t="s">
         <v>16</v>
@@ -10044,17 +10076,17 @@
     </row>
     <row r="163" ht="22.5" customHeight="1">
       <c r="A163" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B163" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwinger, Theodor (?) (1597-1654)</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E163" s="5">
         <v>1597.0</v>
@@ -10063,32 +10095,32 @@
         <v>1654.0</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="I163" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J163" s="10" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="K163" s="3"/>
     </row>
     <row r="164" ht="22.5" customHeight="1">
       <c r="A164" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B164" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Genath, Johann Jacob (1582-1654)</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E164" s="5">
         <v>1582.0</v>
@@ -10097,10 +10129,10 @@
         <v>1654.0</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="I164" s="7" t="s">
         <v>16</v>
@@ -10110,49 +10142,49 @@
     </row>
     <row r="165" ht="22.5" customHeight="1">
       <c r="A165" s="3" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B165" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Escher vom Luchs‏, Johannes (‎1646-1659)</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>125</v>
       </c>
       <c r="E165" s="17" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="F165" s="5">
         <v>1659.0</v>
       </c>
       <c r="G165" s="9"/>
       <c r="H165" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="I165" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J165" s="10" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="K165" s="9"/>
     </row>
     <row r="166" ht="22.5" customHeight="1">
       <c r="A166" s="3" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B166" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hess, Caspar (1578-1631)</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E166" s="5">
         <v>1578.0</v>
@@ -10161,29 +10193,29 @@
         <v>1631.0</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="I166" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J166" s="10" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="K166" s="9"/>
     </row>
     <row r="167" ht="22.5" customHeight="1">
       <c r="A167" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B167" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wolf, Johann Jakob (1601-1641)</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>32</v>
@@ -10195,10 +10227,10 @@
         <v>1641.0</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="I167" s="7" t="s">
         <v>16</v>
@@ -10208,14 +10240,14 @@
     </row>
     <row r="168" ht="22.5" customHeight="1">
       <c r="A168" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B168" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spörri, Felix (1581-1643)</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>89</v>
@@ -10227,22 +10259,22 @@
         <v>1643.0</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="I168" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J168" s="9"/>
       <c r="K168" s="3" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="169" ht="22.5" customHeight="1">
       <c r="A169" s="3" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B169" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10252,7 +10284,7 @@
         <v>12</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="E169" s="5">
         <v>1604.0</v>
@@ -10268,27 +10300,27 @@
         <v>16</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="K169" s="9"/>
     </row>
     <row r="170" ht="22.5" customHeight="1">
       <c r="A170" s="3" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B170" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther,  (-)</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D170" s="3"/>
       <c r="E170" s="18"/>
       <c r="F170" s="19"/>
       <c r="G170" s="9"/>
       <c r="H170" s="3" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="I170" s="7" t="s">
         <v>16</v>
@@ -10298,23 +10330,23 @@
     </row>
     <row r="171" ht="22.5" customHeight="1">
       <c r="A171" s="3" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B171" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Weiss, Caspar (-)</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E171" s="18"/>
       <c r="F171" s="19"/>
       <c r="G171" s="9"/>
       <c r="H171" s="20" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="I171" s="7" t="s">
         <v>16</v>
@@ -10324,7 +10356,7 @@
     </row>
     <row r="172" ht="22.5" customHeight="1">
       <c r="A172" s="3" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B172" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10338,7 +10370,7 @@
       <c r="F172" s="19"/>
       <c r="G172" s="9"/>
       <c r="H172" s="20" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I172" s="7" t="s">
         <v>16</v>
@@ -10348,21 +10380,21 @@
     </row>
     <row r="173" ht="22.5" customHeight="1">
       <c r="A173" s="3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B173" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bas,  (-)</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="18"/>
       <c r="F173" s="19"/>
       <c r="G173" s="9"/>
       <c r="H173" s="3" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="I173" s="21"/>
       <c r="J173" s="9"/>
@@ -10370,82 +10402,82 @@
     </row>
     <row r="174" ht="22.5" customHeight="1">
       <c r="A174" s="3" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B174" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gw., H. H. J. (-)</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E174" s="18"/>
       <c r="F174" s="19"/>
       <c r="G174" s="9"/>
       <c r="H174" s="3" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="I174" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J174" s="9"/>
       <c r="K174" s="10" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="175" ht="22.5" customHeight="1">
       <c r="A175" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B175" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hofmeister, Johann (‎1622-‎1656‎)</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>108</v>
       </c>
       <c r="E175" s="17" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="F175" s="17" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="G175" s="9"/>
       <c r="H175" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="I175" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="K175" s="9"/>
     </row>
     <row r="176" ht="22.5" customHeight="1">
       <c r="A176" s="3" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B176" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Cyrene, Simon von (-)</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E176" s="18"/>
       <c r="F176" s="19"/>
       <c r="G176" s="3" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>271</v>
@@ -10458,20 +10490,20 @@
     </row>
     <row r="177" ht="22.5" customHeight="1">
       <c r="A177" s="3" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B177" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thomas,  (-)</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="18"/>
       <c r="F177" s="19"/>
       <c r="G177" s="3" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>343</v>
@@ -10484,23 +10516,23 @@
     </row>
     <row r="178" ht="22.5" customHeight="1">
       <c r="A178" s="3" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B178" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Phaeton,  (-)</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="18"/>
       <c r="F178" s="19"/>
       <c r="G178" s="3" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="I178" s="7" t="s">
         <v>234</v>
@@ -10510,14 +10542,14 @@
     </row>
     <row r="179" ht="22.5" customHeight="1">
       <c r="A179" s="3" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B179" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lukas,  (-)</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D179" s="3"/>
       <c r="E179" s="18"/>
@@ -10534,20 +10566,20 @@
     </row>
     <row r="180" ht="22.5" customHeight="1">
       <c r="A180" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B180" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pallas Athena,  (-)</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="18"/>
       <c r="F180" s="19"/>
       <c r="G180" s="3" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>234</v>
@@ -10560,23 +10592,23 @@
     </row>
     <row r="181" ht="22.5" customHeight="1">
       <c r="A181" s="3" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B181" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bacchus,  (-)</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D181" s="3"/>
       <c r="E181" s="18"/>
       <c r="F181" s="19"/>
       <c r="G181" s="3" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="I181" s="7" t="s">
         <v>234</v>
@@ -10586,23 +10618,23 @@
     </row>
     <row r="182" ht="22.5" customHeight="1">
       <c r="A182" s="3" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B182" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Darius I.,  (-)</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="18"/>
       <c r="F182" s="19"/>
       <c r="G182" s="3" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="I182" s="7" t="s">
         <v>16</v>
@@ -10612,23 +10644,23 @@
     </row>
     <row r="183" ht="22.5" customHeight="1">
       <c r="A183" s="3" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B183" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kyros II.,  (-)</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D183" s="3"/>
       <c r="E183" s="18"/>
       <c r="F183" s="19"/>
       <c r="G183" s="3" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="I183" s="7" t="s">
         <v>16</v>
@@ -10638,25 +10670,25 @@
     </row>
     <row r="184" ht="22.5" customHeight="1">
       <c r="A184" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B184" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hippo, Augustinus von (-)</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E184" s="18"/>
       <c r="F184" s="19"/>
       <c r="G184" s="3" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="I184" s="7" t="s">
         <v>16</v>
@@ -10666,23 +10698,23 @@
     </row>
     <row r="185" ht="22.5" customHeight="1">
       <c r="A185" s="3" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B185" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lazarus,  (-)</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="D185" s="3"/>
       <c r="E185" s="18"/>
       <c r="F185" s="19"/>
       <c r="G185" s="3" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="I185" s="7" t="s">
         <v>271</v>
@@ -10692,23 +10724,23 @@
     </row>
     <row r="186" ht="22.5" customHeight="1">
       <c r="A186" s="3" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B186" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lot,  (-)</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="18"/>
       <c r="F186" s="19"/>
       <c r="G186" s="3" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="I186" s="7" t="s">
         <v>271</v>
@@ -10718,17 +10750,17 @@
     </row>
     <row r="187" ht="22.5" customHeight="1">
       <c r="A187" s="3" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B187" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gyger, Johann Rudolf (1603-1662)</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E187" s="5">
         <v>1603.0</v>
@@ -10737,10 +10769,10 @@
         <v>1662.0</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="I187" s="7" t="s">
         <v>16</v>
@@ -10750,7 +10782,7 @@
     </row>
     <row r="188" ht="22.5" customHeight="1">
       <c r="A188" s="3" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B188" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10763,16 +10795,16 @@
         <v>13</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F188" s="5">
         <v>1690.0</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="I188" s="7" t="s">
         <v>16</v>
@@ -10782,17 +10814,17 @@
     </row>
     <row r="189" ht="22.5" customHeight="1">
       <c r="A189" s="3" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B189" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bachofen, Johann Ulrich (1643-1700)</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="E189" s="5">
         <v>1643.0</v>
@@ -10801,7 +10833,7 @@
         <v>1700.0</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>229</v>
@@ -10814,17 +10846,17 @@
     </row>
     <row r="190" ht="22.5" customHeight="1">
       <c r="A190" s="3" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B190" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grebel, Hans Konrad (1615-1674)</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="E190" s="5">
         <v>1615.0</v>
@@ -10833,57 +10865,57 @@
         <v>1674.0</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I190" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="K190" s="9"/>
     </row>
     <row r="191" ht="22.5" customHeight="1">
       <c r="A191" s="3" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B191" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gossweiler, Emerentia (-)</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E191" s="18"/>
       <c r="F191" s="19"/>
       <c r="G191" s="9"/>
       <c r="H191" s="3" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="I191" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J191" s="8" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="K191" s="9"/>
     </row>
     <row r="192" ht="22.5" customHeight="1">
       <c r="A192" s="3" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B192" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lochmann, Heinrich (1613-1667)</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>38</v>
@@ -10895,29 +10927,29 @@
         <v>1667.0</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J192" s="8" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="K192" s="9"/>
     </row>
     <row r="193" ht="22.5" customHeight="1">
       <c r="A193" s="3" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B193" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Johann Jakob (1602-1668)</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>32</v>
@@ -10929,109 +10961,109 @@
         <v>1668.0</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J193" s="8" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="K193" s="9"/>
     </row>
     <row r="194" ht="22.5" customHeight="1">
       <c r="A194" s="3" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B194" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orelli, Anna (-)</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E194" s="18"/>
       <c r="F194" s="19"/>
       <c r="G194" s="9"/>
       <c r="H194" s="3" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="I194" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J194" s="10" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="K194" s="9"/>
     </row>
     <row r="195" ht="22.5" customHeight="1">
       <c r="A195" s="3" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B195" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. E. H.,  (-)</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="18"/>
       <c r="F195" s="19"/>
       <c r="G195" s="9"/>
       <c r="H195" s="3" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J195" s="22" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="K195" s="9"/>
     </row>
     <row r="196" ht="22.5" customHeight="1">
       <c r="A196" s="3" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B196" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. H.,  (-)</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D196" s="3"/>
       <c r="E196" s="18"/>
       <c r="F196" s="19"/>
       <c r="G196" s="9"/>
       <c r="H196" s="3" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="I196" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J196" s="22" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="K196" s="9"/>
     </row>
     <row r="197" ht="22.5" customHeight="1">
       <c r="A197" s="3" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B197" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grob, Hans Jakob (-)</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>222</v>
@@ -11040,19 +11072,19 @@
       <c r="F197" s="19"/>
       <c r="G197" s="9"/>
       <c r="H197" s="3" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="I197" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J197" s="8" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="K197" s="9"/>
     </row>
     <row r="198" ht="22.5" customHeight="1">
       <c r="A198" s="3" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B198" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11062,7 +11094,7 @@
         <v>69</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="E198" s="18"/>
       <c r="F198" s="19"/>
@@ -11072,23 +11104,23 @@
         <v>16</v>
       </c>
       <c r="J198" s="8" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="K198" s="9"/>
     </row>
     <row r="199" ht="22.5" customHeight="1">
       <c r="A199" s="3" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B199" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klingler, Kaspar (-)</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="E199" s="18"/>
       <c r="F199" s="19"/>
@@ -11098,23 +11130,23 @@
         <v>16</v>
       </c>
       <c r="J199" s="8" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="K199" s="9"/>
     </row>
     <row r="200" ht="22.5" customHeight="1">
       <c r="A200" s="3" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B200" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöndli, Dorothea (-)</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E200" s="18"/>
       <c r="F200" s="19"/>
@@ -11124,23 +11156,23 @@
         <v>16</v>
       </c>
       <c r="J200" s="8" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="K200" s="9"/>
     </row>
     <row r="201" ht="22.5" customHeight="1">
       <c r="A201" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B201" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Hans Caspar (1617-1691)</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="E201" s="5">
         <v>1617.0</v>
@@ -11149,32 +11181,32 @@
         <v>1691.0</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="K201" s="9"/>
     </row>
     <row r="202" ht="22.5" customHeight="1">
       <c r="A202" s="3" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B202" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Salomon (1580-1652)</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="E202" s="5">
         <v>1580.0</v>
@@ -11183,60 +11215,60 @@
         <v>1652.0</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J202" s="8" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="K202" s="9"/>
     </row>
     <row r="203" ht="22.5" customHeight="1">
       <c r="A203" s="3" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B203" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis-Soglio, Maria Ursina von  (-)</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="E203" s="18"/>
       <c r="F203" s="19"/>
       <c r="G203" s="9"/>
       <c r="H203" s="3" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J203" s="8" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="K203" s="9"/>
     </row>
     <row r="204" ht="22.5" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B204" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Brügger, Andreas von (1588-1653)</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E204" s="5">
         <v>1588.0</v>
@@ -11245,36 +11277,36 @@
         <v>1653.0</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="I204" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J204" s="8" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="K204" s="9"/>
     </row>
     <row r="205" ht="22.5" customHeight="1">
       <c r="A205" s="3" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B205" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Anhorn,  (-)</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D205" s="3"/>
       <c r="E205" s="18"/>
       <c r="F205" s="19"/>
       <c r="G205" s="9"/>
       <c r="H205" s="3" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="I205" s="7" t="s">
         <v>16</v>
@@ -11284,14 +11316,14 @@
     </row>
     <row r="206" ht="22.5" customHeight="1">
       <c r="A206" s="3" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B206" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wilden, Abraham (-)</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>298</v>
@@ -11300,7 +11332,7 @@
       <c r="F206" s="19"/>
       <c r="G206" s="9"/>
       <c r="H206" s="3" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>16</v>
@@ -11310,23 +11342,23 @@
     </row>
     <row r="207" ht="22.5" customHeight="1">
       <c r="A207" s="3" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B207" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Groben, Jacob (evtl. Johannes) (-)</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="E207" s="18"/>
       <c r="F207" s="19"/>
       <c r="G207" s="9"/>
       <c r="H207" s="3" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>16</v>
@@ -11336,21 +11368,21 @@
     </row>
     <row r="208" ht="22.5" customHeight="1">
       <c r="A208" s="3" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B208" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ziegler,  (-)</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="18"/>
       <c r="F208" s="19"/>
       <c r="G208" s="9"/>
       <c r="H208" s="3" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="I208" s="7" t="s">
         <v>16</v>
@@ -11360,7 +11392,7 @@
     </row>
     <row r="209" ht="22.5" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B209" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11376,7 +11408,7 @@
       <c r="F209" s="19"/>
       <c r="G209" s="9"/>
       <c r="H209" s="3" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="I209" s="7" t="s">
         <v>16</v>
@@ -11386,21 +11418,21 @@
     </row>
     <row r="210" ht="22.5" customHeight="1">
       <c r="A210" s="3" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B210" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Oeri,  (-)</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="18"/>
       <c r="F210" s="19"/>
       <c r="G210" s="9"/>
       <c r="H210" s="3" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="I210" s="7" t="s">
         <v>16</v>
@@ -11410,21 +11442,21 @@
     </row>
     <row r="211" ht="22.5" customHeight="1">
       <c r="A211" s="3" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B211" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wittib,  (-)</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="18"/>
       <c r="F211" s="19"/>
       <c r="G211" s="9"/>
       <c r="H211" s="3" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="I211" s="13"/>
       <c r="J211" s="9"/>
@@ -11432,14 +11464,14 @@
     </row>
     <row r="212" ht="22.5" customHeight="1">
       <c r="A212" s="3" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B212" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Graf von Sultz,  (-)</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D212" s="3"/>
       <c r="E212" s="18"/>
@@ -11454,21 +11486,21 @@
     </row>
     <row r="213" ht="22.5" customHeight="1">
       <c r="A213" s="3" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B213" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Eglin,  (-)</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D213" s="3"/>
       <c r="E213" s="18"/>
       <c r="F213" s="19"/>
       <c r="G213" s="9"/>
       <c r="H213" s="3" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="I213" s="7" t="s">
         <v>16</v>
@@ -11478,14 +11510,14 @@
     </row>
     <row r="214" ht="22.5" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B214" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wildhans von Breitenlandenberg,  (-1444)</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="18"/>
@@ -11494,7 +11526,7 @@
       </c>
       <c r="G214" s="9"/>
       <c r="H214" s="3" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="I214" s="7" t="s">
         <v>16</v>
@@ -11504,14 +11536,14 @@
     </row>
     <row r="215" ht="22.5" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B215" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pfarrherr,  (-)</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="18"/>
@@ -11526,17 +11558,17 @@
     </row>
     <row r="216" ht="22.5" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B216" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid von Schwarzenhorn, Johann Rudolf (1590-1667)</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E216" s="5">
         <v>1590.0</v>
@@ -11545,29 +11577,29 @@
         <v>1667.0</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="I216" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J216" s="8" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="K216" s="9"/>
     </row>
     <row r="217" ht="22.5" customHeight="1">
       <c r="A217" s="3" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B217" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid, Felix (-1598)</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>89</v>
@@ -11578,26 +11610,26 @@
       </c>
       <c r="G217" s="9"/>
       <c r="H217" s="3" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="I217" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J217" s="8" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="K217" s="9"/>
     </row>
     <row r="218" ht="22.5" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B218" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hessen, Heinrich (-)</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>38</v>
@@ -11606,7 +11638,7 @@
       <c r="F218" s="19"/>
       <c r="G218" s="9"/>
       <c r="H218" s="3" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="I218" s="7" t="s">
         <v>16</v>
@@ -11616,17 +11648,17 @@
     </row>
     <row r="219" ht="22.5" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B219" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulr., H. (-)</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="E219" s="18"/>
       <c r="F219" s="19"/>
@@ -11642,7 +11674,7 @@
     </row>
     <row r="220" ht="22.5" customHeight="1">
       <c r="A220" s="3" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B220" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11652,13 +11684,13 @@
         <v>61</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E220" s="18"/>
       <c r="F220" s="19"/>
       <c r="G220" s="9"/>
       <c r="H220" s="3" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>16</v>
@@ -11668,7 +11700,7 @@
     </row>
     <row r="221" ht="22.5" customHeight="1">
       <c r="A221" s="3" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B221" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11682,7 +11714,7 @@
       <c r="F221" s="19"/>
       <c r="G221" s="9"/>
       <c r="H221" s="3" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="I221" s="7" t="s">
         <v>16</v>
@@ -11692,14 +11724,14 @@
     </row>
     <row r="222" ht="22.5" customHeight="1">
       <c r="A222" s="3" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B222" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Locher,  (-)</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="18"/>
@@ -11714,17 +11746,17 @@
     </row>
     <row r="223" ht="22.5" customHeight="1">
       <c r="A223" s="3" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B223" s="4" t="str">
         <f t="shared" si="1"/>
         <v>König, Caspar (-)</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E223" s="18"/>
       <c r="F223" s="19"/>
@@ -11736,7 +11768,7 @@
     </row>
     <row r="224" ht="22.5" customHeight="1">
       <c r="A224" s="3" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B224" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11758,7 +11790,7 @@
         <v>71</v>
       </c>
       <c r="H224" s="20" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="I224" s="7" t="s">
         <v>16</v>
@@ -11770,7 +11802,7 @@
     </row>
     <row r="225" ht="22.5" customHeight="1">
       <c r="A225" s="3" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B225" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11784,7 +11816,7 @@
       <c r="F225" s="19"/>
       <c r="G225" s="9"/>
       <c r="H225" s="3" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>16</v>
@@ -11794,17 +11826,17 @@
     </row>
     <row r="226" ht="22.5" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B226" s="4" t="str">
         <f t="shared" si="1"/>
         <v>O., Jacob U. (-)</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="E226" s="18"/>
       <c r="F226" s="19"/>
@@ -11820,21 +11852,21 @@
     </row>
     <row r="227" ht="22.5" customHeight="1">
       <c r="A227" s="3" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B227" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schneeberger,  (-)</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="18"/>
       <c r="F227" s="19"/>
       <c r="G227" s="9"/>
       <c r="H227" s="3" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="I227" s="7" t="s">
         <v>16</v>
@@ -11844,17 +11876,17 @@
     </row>
     <row r="228" ht="22.5" customHeight="1">
       <c r="A228" s="3" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B228" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwingli, Ulrich (1484-1531)</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E228" s="5">
         <v>1484.0</v>
@@ -11863,10 +11895,10 @@
         <v>1531.0</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="I228" s="7" t="s">
         <v>16</v>
@@ -11876,14 +11908,14 @@
     </row>
     <row r="229" ht="22.5" customHeight="1">
       <c r="A229" s="3" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B229" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bullinger, Heinrich (1504-1575)</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>38</v>
@@ -11895,10 +11927,10 @@
         <v>1575.0</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="I229" s="7" t="s">
         <v>16</v>
@@ -11908,17 +11940,17 @@
     </row>
     <row r="230" ht="22.5" customHeight="1">
       <c r="A230" s="3" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B230" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther, Rudolf (1519-1586)</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="E230" s="5">
         <v>1519.0</v>
@@ -11927,7 +11959,7 @@
         <v>1586.0</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="H230" s="3"/>
       <c r="I230" s="7" t="s">
@@ -11938,14 +11970,14 @@
     </row>
     <row r="231" ht="22.5" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B231" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Breitinger, Johann Jakob (1575-1645)</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>32</v>
@@ -11957,7 +11989,7 @@
         <v>1645.0</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="H231" s="3"/>
       <c r="I231" s="7" t="s">
@@ -11968,17 +12000,17 @@
     </row>
     <row r="232" ht="22.5" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B232" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jrminger, Jacob (1588-1649)</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="E232" s="5">
         <v>1588.0</v>
@@ -11987,7 +12019,7 @@
         <v>1649.0</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="H232" s="3"/>
       <c r="I232" s="7" t="s">
@@ -11998,14 +12030,14 @@
     </row>
     <row r="233" ht="22.5" customHeight="1">
       <c r="A233" s="3" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B233" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fries, Jakob (-)</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>373</v>
@@ -12022,25 +12054,25 @@
     </row>
     <row r="234" ht="22.5" customHeight="1">
       <c r="A234" s="3" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B234" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Geiger, Joh. Rud. (-)</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="E234" s="18"/>
       <c r="F234" s="19"/>
       <c r="G234" s="3" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="I234" s="7" t="s">
         <v>16</v>
@@ -12050,17 +12082,17 @@
     </row>
     <row r="235" ht="22.5" customHeight="1">
       <c r="A235" s="3" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B235" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maurer, C. (-)</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="E235" s="18"/>
       <c r="F235" s="19"/>
@@ -12074,17 +12106,17 @@
     </row>
     <row r="236" ht="22.5" customHeight="1">
       <c r="A236" s="3" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B236" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Suter, C. (-)</v>
       </c>
       <c r="C236" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="D236" s="3" t="s">
         <v>919</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>917</v>
       </c>
       <c r="E236" s="18"/>
       <c r="F236" s="19"/>
@@ -12098,17 +12130,17 @@
     </row>
     <row r="237" ht="22.5" customHeight="1">
       <c r="A237" s="3" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B237" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Holzhalb, Joh. (-)</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="E237" s="18"/>
       <c r="F237" s="19"/>
@@ -12124,17 +12156,17 @@
     </row>
     <row r="238" ht="22.5" customHeight="1">
       <c r="A238" s="3" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B238" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wirtz, H. C. (-)</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="E238" s="18"/>
       <c r="F238" s="19"/>
@@ -12148,22 +12180,22 @@
     </row>
     <row r="239" ht="22.5" customHeight="1">
       <c r="A239" s="3" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B239" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser, Caspar (-)</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E239" s="18"/>
       <c r="F239" s="19"/>
       <c r="G239" s="3" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="H239" s="3"/>
       <c r="I239" s="7" t="s">
@@ -12174,22 +12206,22 @@
     </row>
     <row r="240" ht="22.5" customHeight="1">
       <c r="A240" s="3" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B240" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hospinianus, R. (-)</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E240" s="18"/>
       <c r="F240" s="19"/>
       <c r="G240" s="3" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="H240" s="3"/>
       <c r="I240" s="7" t="s">
@@ -12200,17 +12232,17 @@
     </row>
     <row r="241" ht="22.5" customHeight="1">
       <c r="A241" s="3" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B241" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Erni, H. (-)</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="E241" s="18"/>
       <c r="F241" s="19"/>
@@ -12224,17 +12256,17 @@
     </row>
     <row r="242" ht="22.5" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B242" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Tomman, P. (-)</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="E242" s="18"/>
       <c r="F242" s="19"/>
@@ -12248,17 +12280,17 @@
     </row>
     <row r="243" ht="22.5" customHeight="1">
       <c r="A243" s="3" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B243" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Stukki, R. (-)</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="E243" s="18"/>
       <c r="F243" s="19"/>
@@ -12272,17 +12304,17 @@
     </row>
     <row r="244" ht="22.5" customHeight="1">
       <c r="A244" s="3" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B244" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zeller, H. (-)</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="E244" s="18"/>
       <c r="F244" s="19"/>
@@ -12296,7 +12328,7 @@
     </row>
     <row r="245" ht="22.5" customHeight="1">
       <c r="A245" s="3" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B245" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12304,13 +12336,13 @@
       </c>
       <c r="C245" s="6"/>
       <c r="D245" s="3" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="E245" s="18"/>
       <c r="F245" s="19"/>
       <c r="G245" s="9"/>
       <c r="H245" s="3" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="I245" s="7" t="s">
         <v>16</v>
@@ -12320,21 +12352,21 @@
     </row>
     <row r="246" ht="22.5" customHeight="1">
       <c r="A246" s="3" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B246" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fr. Doctorin,  (-)</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="18"/>
       <c r="F246" s="19"/>
       <c r="G246" s="9"/>
       <c r="H246" s="3" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="I246" s="7" t="s">
         <v>16</v>
@@ -12344,17 +12376,17 @@
     </row>
     <row r="247" ht="22.5" customHeight="1">
       <c r="A247" s="3" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B247" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kusen, Jost von (1570-1630)</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="E247" s="5">
         <v>1570.0</v>
@@ -12363,10 +12395,10 @@
         <v>1630.0</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="I247" s="7" t="s">
         <v>16</v>
@@ -12376,14 +12408,14 @@
     </row>
     <row r="248" ht="22.5" customHeight="1">
       <c r="A248" s="3" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B248" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Heinrich (-)</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>38</v>
@@ -12392,7 +12424,7 @@
       <c r="F248" s="19"/>
       <c r="G248" s="9"/>
       <c r="H248" s="3" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="I248" s="7" t="s">
         <v>16</v>
@@ -12402,21 +12434,21 @@
     </row>
     <row r="249" ht="22.5" customHeight="1">
       <c r="A249" s="3" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B249" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gessner,  (-)</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="18"/>
       <c r="F249" s="19"/>
       <c r="G249" s="9"/>
       <c r="H249" s="3" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="I249" s="7" t="s">
         <v>16</v>
@@ -12426,17 +12458,17 @@
     </row>
     <row r="250" ht="22.5" customHeight="1">
       <c r="A250" s="3" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B250" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wöllwein, Johann Anton (1616-1659)</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="E250" s="5">
         <v>1616.0</v>
@@ -12445,10 +12477,10 @@
         <v>1659.0</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="I250" s="7" t="s">
         <v>16</v>
@@ -12458,42 +12490,42 @@
     </row>
     <row r="251" ht="22.5" customHeight="1">
       <c r="A251" s="3" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B251" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Anna (-)</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="E251" s="18"/>
       <c r="F251" s="19"/>
       <c r="G251" s="9"/>
       <c r="H251" s="3" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="I251" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="K251" s="9"/>
     </row>
     <row r="252" ht="22.5" customHeight="1">
       <c r="A252" s="3" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B252" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. J. R. S.,  (-)</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="D252" s="3"/>
       <c r="E252" s="18"/>
@@ -12506,17 +12538,17 @@
     </row>
     <row r="253" ht="22.5" customHeight="1">
       <c r="A253" s="3" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B253" s="4" t="str">
         <f t="shared" si="1"/>
         <v>de Ruyter, Michiel (1607-1676)</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="E253" s="5">
         <v>1607.0</v>
@@ -12525,10 +12557,10 @@
         <v>1676.0</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="I253" s="7" t="s">
         <v>16</v>
@@ -12538,21 +12570,21 @@
     </row>
     <row r="254" ht="22.5" customHeight="1">
       <c r="A254" s="3" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B254" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Frau Oberstin,  (-)</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="18"/>
       <c r="F254" s="19"/>
       <c r="G254" s="9"/>
       <c r="H254" s="3" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="I254" s="7" t="s">
         <v>16</v>
@@ -12562,23 +12594,23 @@
     </row>
     <row r="255" ht="22.5" customHeight="1">
       <c r="A255" s="3" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B255" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vulcanus,  (-)</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="18"/>
       <c r="F255" s="19"/>
       <c r="G255" s="3" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="I255" s="7" t="s">
         <v>234</v>
@@ -12588,23 +12620,23 @@
     </row>
     <row r="256" ht="22.5" customHeight="1">
       <c r="A256" s="3" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B256" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esau,  (-)</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="18"/>
       <c r="F256" s="19"/>
       <c r="G256" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="I256" s="7" t="s">
         <v>271</v>
@@ -12614,23 +12646,23 @@
     </row>
     <row r="257" ht="22.5" customHeight="1">
       <c r="A257" s="3" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B257" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Danaos,  (-)</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="18"/>
       <c r="F257" s="19"/>
       <c r="G257" s="3" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="I257" s="7" t="s">
         <v>234</v>
@@ -12640,20 +12672,20 @@
     </row>
     <row r="258" ht="22.5" customHeight="1">
       <c r="A258" s="3" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B258" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Medusa,  (-)</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="18"/>
       <c r="F258" s="19"/>
       <c r="G258" s="3" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>234</v>
@@ -12666,20 +12698,20 @@
     </row>
     <row r="259" ht="22.5" customHeight="1">
       <c r="A259" s="3" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B259" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pluton,  (-)</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="18"/>
       <c r="F259" s="19"/>
       <c r="G259" s="3" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>234</v>
@@ -12692,20 +12724,20 @@
     </row>
     <row r="260" ht="22.5" customHeight="1">
       <c r="A260" s="3" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B260" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mercur,  (-)</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="18"/>
       <c r="F260" s="19"/>
       <c r="G260" s="3" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>234</v>
@@ -12718,20 +12750,20 @@
     </row>
     <row r="261" ht="22.5" customHeight="1">
       <c r="A261" s="3" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B261" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Perseus,  (-)</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="18"/>
       <c r="F261" s="19"/>
       <c r="G261" s="3" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>234</v>
@@ -12744,23 +12776,23 @@
     </row>
     <row r="262" ht="22.5" customHeight="1">
       <c r="A262" s="3" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B262" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Atropos,  (-)</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="18"/>
       <c r="F262" s="19"/>
       <c r="G262" s="3" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="I262" s="7" t="s">
         <v>234</v>
@@ -12770,23 +12802,23 @@
     </row>
     <row r="263" ht="22.5" customHeight="1">
       <c r="A263" s="3" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B263" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Barbara von Nikomedien,  (-)</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="18"/>
       <c r="F263" s="19"/>
       <c r="G263" s="3" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="H263" s="3" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="I263" s="7" t="s">
         <v>271</v>
@@ -12796,7 +12828,7 @@
     </row>
     <row r="264" ht="22.5" customHeight="1">
       <c r="A264" s="3" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B264" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12804,13 +12836,13 @@
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="3" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="E264" s="18"/>
       <c r="F264" s="19"/>
       <c r="G264" s="9"/>
       <c r="H264" s="3" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="I264" s="13"/>
       <c r="J264" s="9"/>
@@ -12818,7 +12850,7 @@
     </row>
     <row r="265" ht="22.5" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B265" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12832,7 +12864,7 @@
       <c r="F265" s="19"/>
       <c r="G265" s="9"/>
       <c r="H265" s="3" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="I265" s="13"/>
       <c r="J265" s="9"/>
@@ -12840,21 +12872,21 @@
     </row>
     <row r="266" ht="22.5" customHeight="1">
       <c r="A266" s="3" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B266" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Karl,  (-)</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="18"/>
       <c r="F266" s="19"/>
       <c r="G266" s="9"/>
       <c r="H266" s="3" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="I266" s="7" t="s">
         <v>16</v>
@@ -12864,21 +12896,21 @@
     </row>
     <row r="267" ht="22.5" customHeight="1">
       <c r="A267" s="3" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B267" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Duraeum,  (-)</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="18"/>
       <c r="F267" s="19"/>
       <c r="G267" s="9"/>
       <c r="H267" s="3" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="I267" s="13"/>
       <c r="J267" s="9"/>
@@ -12886,17 +12918,17 @@
     </row>
     <row r="268" ht="22.5" customHeight="1">
       <c r="A268" s="3" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B268" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zesen, Philipp von (1619-1689)</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="E268" s="5">
         <v>1619.0</v>
@@ -12905,7 +12937,7 @@
         <v>1689.0</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="H268" s="3"/>
       <c r="I268" s="7" t="s">
@@ -12916,23 +12948,23 @@
     </row>
     <row r="269" ht="22.5" customHeight="1">
       <c r="A269" s="3" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B269" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lucretia,  (-)</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="D269" s="3"/>
       <c r="E269" s="18"/>
       <c r="F269" s="19"/>
       <c r="G269" s="3" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="I269" s="7" t="s">
         <v>234</v>
@@ -12942,23 +12974,23 @@
     </row>
     <row r="270" ht="22.5" customHeight="1">
       <c r="A270" s="3" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B270" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ovid,  (-)</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="18"/>
       <c r="F270" s="19"/>
       <c r="G270" s="3" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="H270" s="3" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="I270" s="7" t="s">
         <v>16</v>
@@ -12968,50 +13000,50 @@
     </row>
     <row r="271" ht="22.5" customHeight="1">
       <c r="A271" s="3" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B271" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schweizer, Johann Caspar (1619/1620-1684/1688)</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="H271" s="3" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="I271" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J271" s="8" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="K271" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="272" ht="22.5" customHeight="1">
       <c r="A272" s="3" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B272" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Herder, Johann Heinrich (1629-1665)</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>44</v>
@@ -13023,10 +13055,10 @@
         <v>1665.0</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="H272" s="3" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="I272" s="7" t="s">
         <v>16</v>
@@ -13036,23 +13068,23 @@
     </row>
     <row r="273" ht="22.5" customHeight="1">
       <c r="A273" s="3" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B273" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Elischa,  (-)</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D273" s="3"/>
       <c r="E273" s="18"/>
       <c r="F273" s="19"/>
       <c r="G273" s="3" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="H273" s="3" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="I273" s="7" t="s">
         <v>271</v>
@@ -13062,23 +13094,23 @@
     </row>
     <row r="274" ht="22.5" customHeight="1">
       <c r="A274" s="3" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B274" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Johannes der Täufer,  (-)</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D274" s="3"/>
       <c r="E274" s="18"/>
       <c r="F274" s="19"/>
       <c r="G274" s="3" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="I274" s="7" t="s">
         <v>271</v>
@@ -13088,29 +13120,29 @@
     </row>
     <row r="275" ht="22.5" customHeight="1">
       <c r="A275" s="3" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B275" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caesar, Gaius Iulius (100 v. Chr.-44 v. Chr.)</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="H275" s="3" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="I275" s="7" t="s">
         <v>16</v>
@@ -13120,23 +13152,23 @@
     </row>
     <row r="276" ht="22.5" customHeight="1">
       <c r="A276" s="3" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B276" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Helios,  (-)</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D276" s="3"/>
       <c r="E276" s="18"/>
       <c r="F276" s="19"/>
       <c r="G276" s="3" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="H276" s="3" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="I276" s="7" t="s">
         <v>234</v>
@@ -13146,77 +13178,77 @@
     </row>
     <row r="277" ht="22.5" customHeight="1">
       <c r="A277" s="3" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B277" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Suevus,  (-)</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D277" s="3"/>
       <c r="E277" s="18"/>
       <c r="F277" s="19"/>
       <c r="G277" s="9"/>
       <c r="H277" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="I277" s="7" t="s">
         <v>234</v>
       </c>
       <c r="J277" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K277" s="11"/>
     </row>
     <row r="278" ht="22.5" customHeight="1">
       <c r="A278" s="3" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B278" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Momos,  (-)</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="D278" s="3"/>
       <c r="E278" s="18"/>
       <c r="F278" s="19"/>
       <c r="G278" s="3" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="H278" s="3" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="I278" s="7" t="s">
         <v>234</v>
       </c>
       <c r="J278" s="10" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="K278" s="9"/>
     </row>
     <row r="279" ht="22.5" customHeight="1">
       <c r="A279" s="3" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="B279" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Galatea,  (-)</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D279" s="3"/>
       <c r="E279" s="18"/>
       <c r="F279" s="19"/>
       <c r="G279" s="3" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="H279" s="3" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="I279" s="7" t="s">
         <v>234</v>
@@ -13226,77 +13258,103 @@
     </row>
     <row r="280" ht="22.5" customHeight="1">
       <c r="A280" s="3" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B280" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Escher vom Luchs‏‎, Hans Heinrich (‎1644-1714)</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E280" s="17" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="F280" s="5">
         <v>1714.0</v>
       </c>
       <c r="G280" s="9"/>
       <c r="H280" s="3" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="I280" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J280" s="10" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="K280" s="10" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="281" ht="22.5" customHeight="1">
       <c r="A281" s="3" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B281" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>,  (-)</v>
-      </c>
-      <c r="C281" s="6"/>
+        <v>Agapetus,  (6. Jh.-6. Jh.)</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>1078</v>
+      </c>
       <c r="D281" s="3"/>
-      <c r="E281" s="17"/>
-      <c r="F281" s="5"/>
-      <c r="G281" s="9"/>
-      <c r="H281" s="3"/>
-      <c r="I281" s="7"/>
-      <c r="J281" s="15"/>
+      <c r="E281" s="17" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F281" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H281" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="I281" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J281" s="10" t="s">
+        <v>1082</v>
+      </c>
       <c r="K281" s="15"/>
     </row>
     <row r="282" ht="22.5" customHeight="1">
       <c r="A282" s="3" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="B282" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>,  (-)</v>
-      </c>
-      <c r="C282" s="6"/>
+        <v>Justinian I.,  (482-565)</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>1084</v>
+      </c>
       <c r="D282" s="3"/>
-      <c r="E282" s="17"/>
-      <c r="F282" s="5"/>
-      <c r="G282" s="9"/>
-      <c r="H282" s="3"/>
-      <c r="I282" s="7"/>
+      <c r="E282" s="17">
+        <v>482.0</v>
+      </c>
+      <c r="F282" s="5">
+        <v>565.0</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H282" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I282" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="J282" s="15"/>
       <c r="K282" s="15"/>
     </row>
     <row r="283" ht="22.5" customHeight="1">
       <c r="A283" s="3" t="s">
-        <v>1077</v>
+        <v>1086</v>
       </c>
       <c r="B283" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13314,7 +13372,7 @@
     </row>
     <row r="284" ht="22.5" customHeight="1">
       <c r="A284" s="3" t="s">
-        <v>1078</v>
+        <v>1087</v>
       </c>
       <c r="B284" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13332,7 +13390,7 @@
     </row>
     <row r="285" ht="22.5" customHeight="1">
       <c r="A285" s="3" t="s">
-        <v>1079</v>
+        <v>1088</v>
       </c>
       <c r="B285" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13350,7 +13408,7 @@
     </row>
     <row r="286" ht="22.5" customHeight="1">
       <c r="A286" s="3" t="s">
-        <v>1080</v>
+        <v>1089</v>
       </c>
       <c r="B286" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13368,7 +13426,7 @@
     </row>
     <row r="287" ht="22.5" customHeight="1">
       <c r="A287" s="3" t="s">
-        <v>1081</v>
+        <v>1090</v>
       </c>
       <c r="B287" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13386,7 +13444,7 @@
     </row>
     <row r="288" ht="22.5" customHeight="1">
       <c r="A288" s="3" t="s">
-        <v>1082</v>
+        <v>1091</v>
       </c>
       <c r="B288" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13404,7 +13462,7 @@
     </row>
     <row r="289" ht="22.5" customHeight="1">
       <c r="A289" s="3" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="B289" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13422,7 +13480,7 @@
     </row>
     <row r="290" ht="22.5" customHeight="1">
       <c r="A290" s="3" t="s">
-        <v>1084</v>
+        <v>1093</v>
       </c>
       <c r="B290" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13440,7 +13498,7 @@
     </row>
     <row r="291" ht="22.5" customHeight="1">
       <c r="A291" s="3" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="B291" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13458,7 +13516,7 @@
     </row>
     <row r="292" ht="22.5" customHeight="1">
       <c r="A292" s="3" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="B292" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13476,7 +13534,7 @@
     </row>
     <row r="293" ht="22.5" customHeight="1">
       <c r="A293" s="3" t="s">
-        <v>1087</v>
+        <v>1096</v>
       </c>
       <c r="B293" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13494,7 +13552,7 @@
     </row>
     <row r="294" ht="22.5" customHeight="1">
       <c r="A294" s="3" t="s">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="B294" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13512,7 +13570,7 @@
     </row>
     <row r="295" ht="22.5" customHeight="1">
       <c r="A295" s="3" t="s">
-        <v>1089</v>
+        <v>1098</v>
       </c>
       <c r="B295" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13530,7 +13588,7 @@
     </row>
     <row r="296" ht="22.5" customHeight="1">
       <c r="A296" s="3" t="s">
-        <v>1090</v>
+        <v>1099</v>
       </c>
       <c r="B296" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13548,7 +13606,7 @@
     </row>
     <row r="297" ht="22.5" customHeight="1">
       <c r="A297" s="3" t="s">
-        <v>1091</v>
+        <v>1100</v>
       </c>
       <c r="B297" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13566,7 +13624,7 @@
     </row>
     <row r="298" ht="22.5" customHeight="1">
       <c r="A298" s="3" t="s">
-        <v>1092</v>
+        <v>1101</v>
       </c>
       <c r="B298" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13584,7 +13642,7 @@
     </row>
     <row r="299" ht="22.5" customHeight="1">
       <c r="A299" s="3" t="s">
-        <v>1093</v>
+        <v>1102</v>
       </c>
       <c r="B299" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13602,7 +13660,7 @@
     </row>
     <row r="300" ht="22.5" customHeight="1">
       <c r="A300" s="3" t="s">
-        <v>1094</v>
+        <v>1103</v>
       </c>
       <c r="B300" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13620,7 +13678,7 @@
     </row>
     <row r="301" ht="22.5" customHeight="1">
       <c r="A301" s="3" t="s">
-        <v>1095</v>
+        <v>1104</v>
       </c>
       <c r="B301" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13638,7 +13696,7 @@
     </row>
     <row r="302" ht="22.5" customHeight="1">
       <c r="A302" s="3" t="s">
-        <v>1096</v>
+        <v>1105</v>
       </c>
       <c r="B302" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13656,7 +13714,7 @@
     </row>
     <row r="303" ht="22.5" customHeight="1">
       <c r="A303" s="3" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="B303" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13674,7 +13732,7 @@
     </row>
     <row r="304" ht="22.5" customHeight="1">
       <c r="A304" s="3" t="s">
-        <v>1098</v>
+        <v>1107</v>
       </c>
       <c r="B304" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13692,7 +13750,7 @@
     </row>
     <row r="305" ht="22.5" customHeight="1">
       <c r="A305" s="3" t="s">
-        <v>1099</v>
+        <v>1108</v>
       </c>
       <c r="B305" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13710,7 +13768,7 @@
     </row>
     <row r="306" ht="22.5" customHeight="1">
       <c r="A306" s="3" t="s">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="B306" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13728,7 +13786,7 @@
     </row>
     <row r="307" ht="22.5" customHeight="1">
       <c r="A307" s="3" t="s">
-        <v>1101</v>
+        <v>1110</v>
       </c>
       <c r="B307" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13746,7 +13804,7 @@
     </row>
     <row r="308" ht="22.5" customHeight="1">
       <c r="A308" s="3" t="s">
-        <v>1102</v>
+        <v>1111</v>
       </c>
       <c r="B308" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13764,7 +13822,7 @@
     </row>
     <row r="309" ht="22.5" customHeight="1">
       <c r="A309" s="3" t="s">
-        <v>1103</v>
+        <v>1112</v>
       </c>
       <c r="B309" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13782,7 +13840,7 @@
     </row>
     <row r="310" ht="22.5" customHeight="1">
       <c r="A310" s="3" t="s">
-        <v>1104</v>
+        <v>1113</v>
       </c>
       <c r="B310" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13884,10 +13942,11 @@
     <hyperlink r:id="rId74" ref="J278"/>
     <hyperlink r:id="rId75" ref="J280"/>
     <hyperlink r:id="rId76" ref="K280"/>
+    <hyperlink r:id="rId77" ref="J281"/>
   </hyperlinks>
-  <drawing r:id="rId77"/>
+  <drawing r:id="rId78"/>
   <tableParts count="1">
-    <tablePart r:id="rId79"/>
+    <tablePart r:id="rId80"/>
   </tableParts>
 </worksheet>
 </file>
@@ -13909,16 +13968,16 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1105</v>
+        <v>1114</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1107</v>
+        <v>1116</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -13929,179 +13988,179 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1108</v>
+        <v>1117</v>
       </c>
       <c r="B2" s="23" t="str">
         <f t="shared" ref="B2:B132" si="1">CONCATENATE(C2)</f>
         <v>Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="7" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1111</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1112</v>
+        <v>1121</v>
       </c>
       <c r="B3" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Basel</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1113</v>
+        <v>1122</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="7" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1111</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1114</v>
+        <v>1123</v>
       </c>
       <c r="B4" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Eidgenossenschaft</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1115</v>
+        <v>1124</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
       <c r="E4" s="21"/>
       <c r="F4" s="3" t="s">
-        <v>1117</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="B5" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Limmat</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="7" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1121</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1122</v>
+        <v>1131</v>
       </c>
       <c r="B6" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Weinfelden</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1123</v>
+        <v>1132</v>
       </c>
       <c r="D6" s="25"/>
       <c r="E6" s="7" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1124</v>
+        <v>1133</v>
       </c>
       <c r="B7" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Main</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1125</v>
+        <v>1134</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="7" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1121</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1126</v>
+        <v>1135</v>
       </c>
       <c r="B8" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Zürichsee</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1127</v>
+        <v>1136</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="7" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1128</v>
+        <v>1137</v>
       </c>
       <c r="B9" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Thalwil</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1130</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1131</v>
+        <v>1140</v>
       </c>
       <c r="B10" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bern</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1132</v>
+        <v>1141</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="7" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1111</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1133</v>
+        <v>1142</v>
       </c>
       <c r="B11" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Gottstatt</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1134</v>
+        <v>1143</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="13"/>
@@ -14109,325 +14168,325 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1135</v>
+        <v>1144</v>
       </c>
       <c r="B12" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Thorberg</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1136</v>
+        <v>1145</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1137</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1138</v>
+        <v>1147</v>
       </c>
       <c r="B13" s="24" t="str">
         <f t="shared" si="1"/>
         <v>London</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1139</v>
+        <v>1148</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="7" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1140</v>
+        <v>1149</v>
       </c>
       <c r="B14" s="24" t="str">
         <f t="shared" si="1"/>
         <v>England</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1141</v>
+        <v>1150</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="7" t="s">
-        <v>1142</v>
+        <v>1151</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1143</v>
+        <v>1152</v>
       </c>
       <c r="B15" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bethlehem</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="7" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1145</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1146</v>
+        <v>1155</v>
       </c>
       <c r="B16" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Parnass </v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1147</v>
+        <v>1156</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="7" t="s">
-        <v>1148</v>
+        <v>1157</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1149</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1150</v>
+        <v>1159</v>
       </c>
       <c r="B17" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Traubenberg</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1151</v>
+        <v>1160</v>
       </c>
       <c r="D17" s="25"/>
       <c r="E17" s="13"/>
       <c r="F17" s="3" t="s">
-        <v>1152</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1153</v>
+        <v>1162</v>
       </c>
       <c r="B18" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Babylon</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1154</v>
+        <v>1163</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1155</v>
+        <v>1164</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1156</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1157</v>
+        <v>1166</v>
       </c>
       <c r="B19" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Canaan</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="7" t="s">
-        <v>1159</v>
+        <v>1168</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1160</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1161</v>
+        <v>1170</v>
       </c>
       <c r="B20" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Ägypten</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1162</v>
+        <v>1171</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1163</v>
+        <v>1172</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1142</v>
+        <v>1151</v>
       </c>
       <c r="F20" s="9"/>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1164</v>
+        <v>1173</v>
       </c>
       <c r="B21" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Hermon</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1165</v>
+        <v>1174</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="7" t="s">
-        <v>1148</v>
+        <v>1157</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1166</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1167</v>
+        <v>1176</v>
       </c>
       <c r="B22" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Jerusalem</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1168</v>
+        <v>1177</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1169</v>
+        <v>1178</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1170</v>
+        <v>1179</v>
       </c>
       <c r="B23" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Jordan</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1171</v>
+        <v>1180</v>
       </c>
       <c r="D23" s="25"/>
       <c r="E23" s="7" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1172</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1173</v>
+        <v>1182</v>
       </c>
       <c r="B24" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Rotes Meer</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1174</v>
+        <v>1183</v>
       </c>
       <c r="D24" s="25"/>
       <c r="E24" s="7" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="F24" s="9"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1175</v>
+        <v>1184</v>
       </c>
       <c r="B25" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Juda</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1176</v>
+        <v>1185</v>
       </c>
       <c r="D25" s="25"/>
       <c r="E25" s="13"/>
       <c r="F25" s="3" t="s">
-        <v>1177</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1178</v>
+        <v>1187</v>
       </c>
       <c r="B26" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Moab</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1179</v>
+        <v>1188</v>
       </c>
       <c r="D26" s="25"/>
       <c r="E26" s="13"/>
       <c r="F26" s="3" t="s">
-        <v>1180</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1181</v>
+        <v>1190</v>
       </c>
       <c r="B27" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Ammon</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1182</v>
+        <v>1191</v>
       </c>
       <c r="D27" s="25"/>
       <c r="E27" s="13"/>
       <c r="F27" s="3" t="s">
-        <v>1183</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1184</v>
+        <v>1193</v>
       </c>
       <c r="B28" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Zion</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1185</v>
+        <v>1194</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>1186</v>
+        <v>1195</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1148</v>
+        <v>1157</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>1187</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1188</v>
+        <v>1197</v>
       </c>
       <c r="B29" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Assur</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1189</v>
+        <v>1198</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="13"/>
@@ -14435,101 +14494,101 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1190</v>
+        <v>1199</v>
       </c>
       <c r="B30" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Israel</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1191</v>
+        <v>1200</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="13"/>
       <c r="F30" s="3" t="s">
-        <v>1192</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1193</v>
+        <v>1202</v>
       </c>
       <c r="B31" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Nazaret</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1194</v>
+        <v>1203</v>
       </c>
       <c r="D31" s="25"/>
       <c r="E31" s="7" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>1195</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1196</v>
+        <v>1205</v>
       </c>
       <c r="B32" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Rom</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1197</v>
+        <v>1206</v>
       </c>
       <c r="D32" s="25"/>
       <c r="E32" s="13"/>
       <c r="F32" s="3" t="s">
-        <v>1198</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1199</v>
+        <v>1208</v>
       </c>
       <c r="B33" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Samaria</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1200</v>
+        <v>1209</v>
       </c>
       <c r="D33" s="25"/>
       <c r="E33" s="13"/>
       <c r="F33" s="3" t="s">
-        <v>1201</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1202</v>
+        <v>1211</v>
       </c>
       <c r="B34" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kedronbach</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1203</v>
+        <v>1212</v>
       </c>
       <c r="D34" s="25"/>
       <c r="E34" s="13"/>
       <c r="F34" s="3" t="s">
-        <v>1204</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1205</v>
+        <v>1214</v>
       </c>
       <c r="B35" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Garten von Getsemani</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1206</v>
+        <v>1215</v>
       </c>
       <c r="D35" s="25"/>
       <c r="E35" s="13"/>
@@ -14537,14 +14596,14 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1207</v>
+        <v>1216</v>
       </c>
       <c r="B36" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Urdorf</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1208</v>
+        <v>1217</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="13"/>
@@ -14552,14 +14611,14 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1209</v>
+        <v>1218</v>
       </c>
       <c r="B37" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Geiren-Rein</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1210</v>
+        <v>1219</v>
       </c>
       <c r="D37" s="25"/>
       <c r="E37" s="13"/>
@@ -14567,14 +14626,14 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1211</v>
+        <v>1220</v>
       </c>
       <c r="B38" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Aeügst</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1212</v>
+        <v>1221</v>
       </c>
       <c r="D38" s="25"/>
       <c r="E38" s="13"/>
@@ -14582,14 +14641,14 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1213</v>
+        <v>1222</v>
       </c>
       <c r="B39" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Riedt</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1214</v>
+        <v>1223</v>
       </c>
       <c r="D39" s="25"/>
       <c r="E39" s="13"/>
@@ -14597,14 +14656,14 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1215</v>
+        <v>1224</v>
       </c>
       <c r="B40" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Europa</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1216</v>
+        <v>1225</v>
       </c>
       <c r="D40" s="25"/>
       <c r="E40" s="13"/>
@@ -14612,48 +14671,48 @@
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>1217</v>
+        <v>1226</v>
       </c>
       <c r="B41" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Osir</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1218</v>
+        <v>1227</v>
       </c>
       <c r="D41" s="25"/>
       <c r="E41" s="13"/>
       <c r="F41" s="3" t="s">
-        <v>1219</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>1220</v>
+        <v>1229</v>
       </c>
       <c r="B42" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Basadingen</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1221</v>
+        <v>1230</v>
       </c>
       <c r="D42" s="25"/>
       <c r="E42" s="13"/>
       <c r="F42" s="3" t="s">
-        <v>1222</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>1223</v>
+        <v>1232</v>
       </c>
       <c r="B43" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Diessenhofen</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1224</v>
+        <v>1233</v>
       </c>
       <c r="D43" s="25"/>
       <c r="E43" s="13"/>
@@ -14661,50 +14720,50 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>1225</v>
+        <v>1234</v>
       </c>
       <c r="B44" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Rhein</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1226</v>
+        <v>1235</v>
       </c>
       <c r="D44" s="25"/>
       <c r="E44" s="7" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1121</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>1227</v>
+        <v>1236</v>
       </c>
       <c r="B45" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Arabisches Reich</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1228</v>
+        <v>1237</v>
       </c>
       <c r="D45" s="25"/>
       <c r="E45" s="13"/>
       <c r="F45" s="3" t="s">
-        <v>1229</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>1230</v>
+        <v>1239</v>
       </c>
       <c r="B46" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Libanon</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1231</v>
+        <v>1240</v>
       </c>
       <c r="D46" s="25"/>
       <c r="E46" s="13"/>
@@ -14712,105 +14771,105 @@
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>1232</v>
+        <v>1241</v>
       </c>
       <c r="B47" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Emmaus</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1233</v>
+        <v>1242</v>
       </c>
       <c r="D47" s="25"/>
       <c r="E47" s="13"/>
       <c r="F47" s="3" t="s">
-        <v>1234</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>1235</v>
+        <v>1244</v>
       </c>
       <c r="B48" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Helikon</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1236</v>
+        <v>1245</v>
       </c>
       <c r="D48" s="25"/>
       <c r="E48" s="7" t="s">
-        <v>1148</v>
+        <v>1157</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>1237</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>1238</v>
+        <v>1247</v>
       </c>
       <c r="B49" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Pindos</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1239</v>
+        <v>1248</v>
       </c>
       <c r="D49" s="25"/>
       <c r="E49" s="7" t="s">
-        <v>1148</v>
+        <v>1157</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>1240</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>1241</v>
+        <v>1250</v>
       </c>
       <c r="B50" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Neckar</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1242</v>
+        <v>1251</v>
       </c>
       <c r="D50" s="25"/>
       <c r="E50" s="7" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1243</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>1244</v>
+        <v>1253</v>
       </c>
       <c r="B51" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kurpfalz</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1245</v>
+        <v>1254</v>
       </c>
       <c r="D51" s="25"/>
       <c r="E51" s="13"/>
       <c r="F51" s="3" t="s">
-        <v>1246</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>1247</v>
+        <v>1256</v>
       </c>
       <c r="B52" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Eglisau</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1248</v>
+        <v>1257</v>
       </c>
       <c r="D52" s="25"/>
       <c r="E52" s="13"/>
@@ -14818,14 +14877,14 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>1249</v>
+        <v>1258</v>
       </c>
       <c r="B53" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Altenklingen</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1250</v>
+        <v>1259</v>
       </c>
       <c r="D53" s="25"/>
       <c r="E53" s="13"/>
@@ -14833,14 +14892,14 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>1251</v>
+        <v>1260</v>
       </c>
       <c r="B54" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Altorff</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1252</v>
+        <v>1261</v>
       </c>
       <c r="D54" s="25"/>
       <c r="E54" s="13"/>
@@ -14848,65 +14907,65 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>1253</v>
+        <v>1262</v>
       </c>
       <c r="B55" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Glarus</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1254</v>
+        <v>1263</v>
       </c>
       <c r="D55" s="25"/>
       <c r="E55" s="13"/>
       <c r="F55" s="3" t="s">
-        <v>1111</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>1255</v>
+        <v>1264</v>
       </c>
       <c r="B56" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Reformierte Kirche Berg am Irchel</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1256</v>
+        <v>1265</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>1257</v>
+        <v>1266</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="3"/>
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>1258</v>
+        <v>1267</v>
       </c>
       <c r="B57" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Sodom</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1259</v>
+        <v>1268</v>
       </c>
       <c r="D57" s="25"/>
       <c r="E57" s="13"/>
       <c r="F57" s="3" t="s">
-        <v>1260</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>1261</v>
+        <v>1270</v>
       </c>
       <c r="B58" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Haus zur Sonnenblume</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1262</v>
+        <v>1271</v>
       </c>
       <c r="D58" s="25"/>
       <c r="E58" s="13"/>
@@ -14914,150 +14973,154 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>1263</v>
+        <v>1272</v>
       </c>
       <c r="B59" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Thurn/ genennt von Geissen</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1264</v>
+        <v>1273</v>
       </c>
       <c r="D59" s="25"/>
       <c r="E59" s="13"/>
       <c r="F59" s="3" t="s">
-        <v>1265</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="B60" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>Constantinopel</v>
+        <v>Konstantinopel</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1267</v>
-      </c>
-      <c r="D60" s="25"/>
-      <c r="E60" s="13"/>
+        <v>1276</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>1119</v>
+      </c>
       <c r="F60" s="3"/>
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>1268</v>
+        <v>1278</v>
       </c>
       <c r="B61" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Stein am Rhein</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1269</v>
+        <v>1279</v>
       </c>
       <c r="D61" s="25"/>
       <c r="E61" s="13"/>
       <c r="F61" s="3" t="s">
-        <v>1270</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>1271</v>
+        <v>1281</v>
       </c>
       <c r="B62" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Marburg</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1272</v>
+        <v>1282</v>
       </c>
       <c r="D62" s="25"/>
       <c r="E62" s="13"/>
       <c r="F62" s="3" t="s">
-        <v>1273</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>1274</v>
+        <v>1284</v>
       </c>
       <c r="B63" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Elbląg</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1275</v>
+        <v>1285</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>1276</v>
+        <v>1286</v>
       </c>
       <c r="E63" s="13"/>
       <c r="F63" s="3" t="s">
-        <v>1277</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>1278</v>
+        <v>1288</v>
       </c>
       <c r="B64" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Preußen</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1279</v>
+        <v>1289</v>
       </c>
       <c r="D64" s="25"/>
       <c r="E64" s="13"/>
       <c r="F64" s="3" t="s">
-        <v>1280</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>1281</v>
+        <v>1291</v>
       </c>
       <c r="B65" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bad Baden</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1282</v>
+        <v>1292</v>
       </c>
       <c r="D65" s="25"/>
       <c r="E65" s="13"/>
       <c r="F65" s="3" t="s">
-        <v>1283</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>1284</v>
+        <v>1294</v>
       </c>
       <c r="B66" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bad Schinznach</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1285</v>
+        <v>1295</v>
       </c>
       <c r="D66" s="25"/>
       <c r="E66" s="13"/>
       <c r="F66" s="3" t="s">
-        <v>1283</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>1286</v>
+        <v>1296</v>
       </c>
       <c r="B67" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Gyrenbad</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1287</v>
+        <v>1297</v>
       </c>
       <c r="D67" s="25"/>
       <c r="E67" s="13"/>
@@ -15065,48 +15128,48 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>1288</v>
+        <v>1298</v>
       </c>
       <c r="B68" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wängibad</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1289</v>
+        <v>1299</v>
       </c>
       <c r="D68" s="25"/>
       <c r="E68" s="13"/>
       <c r="F68" s="8" t="s">
-        <v>1290</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>1291</v>
+        <v>1301</v>
       </c>
       <c r="B69" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Aeugst</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1292</v>
+        <v>1302</v>
       </c>
       <c r="D69" s="25"/>
       <c r="E69" s="13"/>
       <c r="F69" s="3" t="s">
-        <v>1222</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>1293</v>
+        <v>1303</v>
       </c>
       <c r="B70" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bassersdorf</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1294</v>
+        <v>1304</v>
       </c>
       <c r="D70" s="25"/>
       <c r="E70" s="13"/>
@@ -15114,14 +15177,14 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>1295</v>
+        <v>1305</v>
       </c>
       <c r="B71" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Hauptwil</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1296</v>
+        <v>1306</v>
       </c>
       <c r="D71" s="25"/>
       <c r="E71" s="13"/>
@@ -15129,14 +15192,14 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>1297</v>
+        <v>1307</v>
       </c>
       <c r="B72" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Schaffhausen</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1298</v>
+        <v>1308</v>
       </c>
       <c r="D72" s="25"/>
       <c r="E72" s="13"/>
@@ -15144,65 +15207,65 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>1299</v>
+        <v>1309</v>
       </c>
       <c r="B73" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wädenswil</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1300</v>
+        <v>1310</v>
       </c>
       <c r="D73" s="25"/>
       <c r="E73" s="13"/>
       <c r="F73" s="3" t="s">
-        <v>1301</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>1302</v>
+        <v>1312</v>
       </c>
       <c r="B74" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Freie Ämter</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1303</v>
+        <v>1313</v>
       </c>
       <c r="D74" s="25"/>
       <c r="E74" s="13"/>
       <c r="F74" s="3" t="s">
-        <v>1304</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>1305</v>
+        <v>1315</v>
       </c>
       <c r="B75" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Grüningen</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1306</v>
+        <v>1316</v>
       </c>
       <c r="D75" s="25"/>
       <c r="E75" s="13"/>
       <c r="F75" s="3" t="s">
-        <v>1301</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>1307</v>
+        <v>1317</v>
       </c>
       <c r="B76" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kefikon</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1308</v>
+        <v>1318</v>
       </c>
       <c r="D76" s="25"/>
       <c r="E76" s="13"/>
@@ -15210,14 +15273,14 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>1309</v>
+        <v>1319</v>
       </c>
       <c r="B77" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Maienfeld</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1310</v>
+        <v>1320</v>
       </c>
       <c r="D77" s="25"/>
       <c r="E77" s="13"/>
@@ -15225,14 +15288,14 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>1311</v>
+        <v>1321</v>
       </c>
       <c r="B78" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Greifensee (Schloss)</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1312</v>
+        <v>1322</v>
       </c>
       <c r="D78" s="25"/>
       <c r="E78" s="13"/>
@@ -15240,31 +15303,31 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>1313</v>
+        <v>1323</v>
       </c>
       <c r="B79" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Lindenhof (Zürich)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1314</v>
+        <v>1324</v>
       </c>
       <c r="D79" s="25"/>
       <c r="E79" s="13"/>
       <c r="F79" s="3" t="s">
-        <v>1315</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>1316</v>
+        <v>1326</v>
       </c>
       <c r="B80" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Galg-Brunnen (Zürich)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1317</v>
+        <v>1327</v>
       </c>
       <c r="D80" s="25"/>
       <c r="E80" s="13"/>
@@ -15272,14 +15335,14 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>1318</v>
+        <v>1328</v>
       </c>
       <c r="B81" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Altes Kornhaus (Zürich)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1319</v>
+        <v>1329</v>
       </c>
       <c r="D81" s="25"/>
       <c r="E81" s="13"/>
@@ -15287,14 +15350,14 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>1320</v>
+        <v>1330</v>
       </c>
       <c r="B82" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Sparrenberg (Zürich)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1321</v>
+        <v>1331</v>
       </c>
       <c r="D82" s="25"/>
       <c r="E82" s="13"/>
@@ -15302,14 +15365,14 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>1322</v>
+        <v>1332</v>
       </c>
       <c r="B83" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Thurgau</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1323</v>
+        <v>1333</v>
       </c>
       <c r="D83" s="25"/>
       <c r="E83" s="13"/>
@@ -15317,14 +15380,14 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>1324</v>
+        <v>1334</v>
       </c>
       <c r="B84" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Niederlande</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1325</v>
+        <v>1335</v>
       </c>
       <c r="D84" s="25"/>
       <c r="E84" s="13"/>
@@ -15332,31 +15395,31 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>1326</v>
+        <v>1336</v>
       </c>
       <c r="B85" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Holland</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1327</v>
+        <v>1337</v>
       </c>
       <c r="D85" s="25"/>
       <c r="E85" s="13"/>
       <c r="F85" s="3" t="s">
-        <v>1328</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>1329</v>
+        <v>1339</v>
       </c>
       <c r="B86" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wigoltingen</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1330</v>
+        <v>1340</v>
       </c>
       <c r="D86" s="25"/>
       <c r="E86" s="13"/>
@@ -15364,31 +15427,31 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>1331</v>
+        <v>1341</v>
       </c>
       <c r="B87" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kastalia</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1332</v>
+        <v>1342</v>
       </c>
       <c r="D87" s="25"/>
       <c r="E87" s="13"/>
       <c r="F87" s="3" t="s">
-        <v>1333</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>1334</v>
+        <v>1344</v>
       </c>
       <c r="B88" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Legerberg</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1335</v>
+        <v>1345</v>
       </c>
       <c r="D88" s="25"/>
       <c r="E88" s="13"/>
@@ -15396,48 +15459,48 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>1336</v>
+        <v>1346</v>
       </c>
       <c r="B89" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Texel</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1337</v>
+        <v>1347</v>
       </c>
       <c r="D89" s="25"/>
       <c r="E89" s="13"/>
       <c r="F89" s="3" t="s">
-        <v>1338</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>1339</v>
+        <v>1349</v>
       </c>
       <c r="B90" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Vlie</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1340</v>
+        <v>1350</v>
       </c>
       <c r="D90" s="25"/>
       <c r="E90" s="13"/>
       <c r="F90" s="3" t="s">
-        <v>1341</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>1342</v>
+        <v>1352</v>
       </c>
       <c r="B91" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Indien</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1343</v>
+        <v>1353</v>
       </c>
       <c r="D91" s="25"/>
       <c r="E91" s="13"/>
@@ -15445,14 +15508,14 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>1344</v>
+        <v>1354</v>
       </c>
       <c r="B92" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wien</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>1345</v>
+        <v>1355</v>
       </c>
       <c r="D92" s="25"/>
       <c r="E92" s="13"/>
@@ -15460,14 +15523,14 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>1346</v>
+        <v>1356</v>
       </c>
       <c r="B93" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Deutschland</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1347</v>
+        <v>1357</v>
       </c>
       <c r="D93" s="25"/>
       <c r="E93" s="13"/>
@@ -15475,96 +15538,96 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>1348</v>
+        <v>1358</v>
       </c>
       <c r="B94" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Ölberg</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1349</v>
+        <v>1359</v>
       </c>
       <c r="D94" s="25"/>
       <c r="E94" s="7" t="s">
-        <v>1148</v>
+        <v>1157</v>
       </c>
       <c r="F94" s="3"/>
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>1350</v>
+        <v>1360</v>
       </c>
       <c r="B95" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Dietikon</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1351</v>
+        <v>1361</v>
       </c>
       <c r="D95" s="25"/>
       <c r="E95" s="7" t="s">
-        <v>1352</v>
+        <v>1362</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1353</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>1354</v>
+        <v>1364</v>
       </c>
       <c r="B96" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Winterthur</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1355</v>
+        <v>1365</v>
       </c>
       <c r="D96" s="25"/>
       <c r="E96" s="7" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="F96" s="3"/>
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>1356</v>
+        <v>1366</v>
       </c>
       <c r="B97" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Pfalz</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1357</v>
+        <v>1367</v>
       </c>
       <c r="D97" s="25"/>
       <c r="E97" s="7" t="s">
-        <v>1159</v>
+        <v>1168</v>
       </c>
       <c r="F97" s="3"/>
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>1358</v>
+        <v>1368</v>
       </c>
       <c r="B98" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Edenkoben</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1359</v>
+        <v>1369</v>
       </c>
       <c r="D98" s="25"/>
       <c r="E98" s="7" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>1360</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>1361</v>
+        <v>1371</v>
       </c>
       <c r="B99" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15577,7 +15640,7 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>1362</v>
+        <v>1372</v>
       </c>
       <c r="B100" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15590,7 +15653,7 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>1363</v>
+        <v>1373</v>
       </c>
       <c r="B101" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15603,7 +15666,7 @@
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>1364</v>
+        <v>1374</v>
       </c>
       <c r="B102" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15616,7 +15679,7 @@
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="3" t="s">
-        <v>1365</v>
+        <v>1375</v>
       </c>
       <c r="B103" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15629,7 +15692,7 @@
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>1366</v>
+        <v>1376</v>
       </c>
       <c r="B104" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15642,7 +15705,7 @@
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="3" t="s">
-        <v>1367</v>
+        <v>1377</v>
       </c>
       <c r="B105" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15655,7 +15718,7 @@
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>1368</v>
+        <v>1378</v>
       </c>
       <c r="B106" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15668,7 +15731,7 @@
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="3" t="s">
-        <v>1369</v>
+        <v>1379</v>
       </c>
       <c r="B107" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15681,7 +15744,7 @@
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>1370</v>
+        <v>1380</v>
       </c>
       <c r="B108" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15694,7 +15757,7 @@
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="3" t="s">
-        <v>1371</v>
+        <v>1381</v>
       </c>
       <c r="B109" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15707,7 +15770,7 @@
     </row>
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>1372</v>
+        <v>1382</v>
       </c>
       <c r="B110" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15720,7 +15783,7 @@
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="3" t="s">
-        <v>1373</v>
+        <v>1383</v>
       </c>
       <c r="B111" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15733,7 +15796,7 @@
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>1374</v>
+        <v>1384</v>
       </c>
       <c r="B112" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15746,7 +15809,7 @@
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="3" t="s">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="B113" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15759,7 +15822,7 @@
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>1376</v>
+        <v>1386</v>
       </c>
       <c r="B114" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15772,7 +15835,7 @@
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="3" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="B115" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15785,7 +15848,7 @@
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>1378</v>
+        <v>1388</v>
       </c>
       <c r="B116" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15798,7 +15861,7 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>1379</v>
+        <v>1389</v>
       </c>
       <c r="B117" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15811,7 +15874,7 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>1380</v>
+        <v>1390</v>
       </c>
       <c r="B118" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15824,7 +15887,7 @@
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>1381</v>
+        <v>1391</v>
       </c>
       <c r="B119" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15837,7 +15900,7 @@
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>1382</v>
+        <v>1392</v>
       </c>
       <c r="B120" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15850,7 +15913,7 @@
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>1383</v>
+        <v>1393</v>
       </c>
       <c r="B121" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15863,7 +15926,7 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>1384</v>
+        <v>1394</v>
       </c>
       <c r="B122" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15876,7 +15939,7 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>1385</v>
+        <v>1395</v>
       </c>
       <c r="B123" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15889,7 +15952,7 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>1386</v>
+        <v>1396</v>
       </c>
       <c r="B124" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15902,7 +15965,7 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>1387</v>
+        <v>1397</v>
       </c>
       <c r="B125" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15915,7 +15978,7 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>1388</v>
+        <v>1398</v>
       </c>
       <c r="B126" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15928,7 +15991,7 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>1389</v>
+        <v>1399</v>
       </c>
       <c r="B127" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15941,7 +16004,7 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="B128" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15954,7 +16017,7 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>1391</v>
+        <v>1401</v>
       </c>
       <c r="B129" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15967,7 +16030,7 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>1392</v>
+        <v>1402</v>
       </c>
       <c r="B130" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15980,7 +16043,7 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="3" t="s">
-        <v>1393</v>
+        <v>1403</v>
       </c>
       <c r="B131" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15993,7 +16056,7 @@
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>1394</v>
+        <v>1404</v>
       </c>
       <c r="B132" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16041,25 +16104,25 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1395</v>
+        <v>1405</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1396</v>
+        <v>1406</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1397</v>
+        <v>1407</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1398</v>
+        <v>1408</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1399</v>
+        <v>1409</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1400</v>
+        <v>1410</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
@@ -16070,75 +16133,75 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1401</v>
+        <v>1411</v>
       </c>
       <c r="B2" s="26" t="str">
         <f t="shared" ref="B2:B40" si="1">CONCATENATE(C2)</f>
         <v>Teutsche Gedichte</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1402</v>
+        <v>1412</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1403</v>
+        <v>1413</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1404</v>
+        <v>1414</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1405</v>
+        <v>1415</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>1406</v>
+        <v>1416</v>
       </c>
       <c r="I2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1407</v>
+        <v>1417</v>
       </c>
       <c r="B3" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Die Krafft der Gottseligkeit</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1408</v>
+        <v>1418</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1409</v>
+        <v>1419</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1411</v>
+        <v>1421</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1412</v>
+        <v>1422</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>1413</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1414</v>
+        <v>1424</v>
       </c>
       <c r="B4" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Buch von Festen</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1415</v>
+        <v>1425</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="5"/>
@@ -16148,23 +16211,23 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1416</v>
+        <v>1426</v>
       </c>
       <c r="B5" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Der Psalter dess Königlichen Propheten Dauids/ Jn deutsche reymen verstendiglich vnd deutlich gebracht/ mit vorgehender anzeigung der reymen weise/ auch eines jeden Psalmes Jnhalt</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1417</v>
+        <v>1427</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1418</v>
+        <v>1428</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1419</v>
+        <v>1429</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1420</v>
+        <v>1430</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="13"/>
@@ -16172,73 +16235,73 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1421</v>
+        <v>1431</v>
       </c>
       <c r="B6" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Hundert christliche Fäst-Predigen</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1422</v>
+        <v>1432</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1423</v>
+        <v>1433</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1424</v>
+        <v>1434</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1425</v>
+        <v>1435</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>1426</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1427</v>
+        <v>1437</v>
       </c>
       <c r="B7" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Spiegel der Unermesslichen Gnad Gottes gegen den rewenden bussfertigen Sünderen/ Jn XLV. Predigen vber das XV. capitel Lucae/ vom verlohrnen Schaaf/ Pfenning/ vnd Sohn verfasset</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1428</v>
+        <v>1438</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1429</v>
+        <v>1439</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1430</v>
+        <v>1440</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1113</v>
+        <v>1122</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1431</v>
+        <v>1441</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>1432</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1433</v>
+        <v>1443</v>
       </c>
       <c r="B8" s="26" t="str">
         <f t="shared" si="1"/>
         <v>verteütschte Rueh- oder Fridens-uebung</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1434</v>
+        <v>1444</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1435</v>
+        <v>1445</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="25"/>
@@ -16248,98 +16311,98 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1436</v>
+        <v>1446</v>
       </c>
       <c r="B9" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Nähefelser-Fahrt: in zehen erbaulichen Jahrzeit-Predigen zu schuldigem Danck dem Höhesten für den im Jahr 1388 gemeinen Landleuthen dess lobl. Eydgnössischen Bundorths Glarus wider ihre Feind bey und umb Nähefels verliehenen Wundersieg </v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1437</v>
+        <v>1447</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1438</v>
+        <v>1448</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1439</v>
+        <v>1449</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1440</v>
+        <v>1450</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="10" t="s">
-        <v>1441</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1442</v>
+        <v>1452</v>
       </c>
       <c r="B10" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Die vier Haubtpuncten der christlichen seligmachenden Religion: auf alle Sontag des gantzen Jahrs ordenlich abgetheilt, grundtlich nach der heiligen Schrifft erklärt und zur Erbawung gerichtet </v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1443</v>
+        <v>1453</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1444</v>
+        <v>1454</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1445</v>
+        <v>1455</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1446</v>
+        <v>1456</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>1447</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1448</v>
+        <v>1458</v>
       </c>
       <c r="B11" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Architectura von Vestungen</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1449</v>
+        <v>1459</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1450</v>
+        <v>1460</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1410</v>
+        <v>1420</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1451</v>
+        <v>1461</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="8" t="s">
-        <v>1452</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1453</v>
+        <v>1463</v>
       </c>
       <c r="B12" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Buech der Freunden Stammen</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1454</v>
+        <v>1464</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="9"/>
@@ -16350,42 +16413,42 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1455</v>
+        <v>1465</v>
       </c>
       <c r="B13" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Christen-Spiegel, das ist, Bedenkliche Erinnerungen über die Beruoffspflichten aller Ständen </v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1456</v>
+        <v>1466</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1457</v>
+        <v>1467</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1458</v>
+        <v>1468</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>1459</v>
+        <v>1469</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>1460</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1461</v>
+        <v>1471</v>
       </c>
       <c r="B14" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Viergeticht</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1462</v>
+        <v>1472</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="9"/>
@@ -16396,14 +16459,14 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="B15" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Regentenspiegel</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1464</v>
+        <v>1474</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="9"/>
@@ -16414,18 +16477,18 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1465</v>
+        <v>1475</v>
       </c>
       <c r="B16" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Türckischer Jammerspiegel</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1466</v>
+        <v>1476</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="3" t="s">
-        <v>1467</v>
+        <v>1477</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="9"/>
@@ -16434,17 +16497,17 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1468</v>
+        <v>1478</v>
       </c>
       <c r="B17" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Leitungs-faden</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1469</v>
+        <v>1479</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="25"/>
@@ -16454,17 +16517,17 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1470</v>
+        <v>1480</v>
       </c>
       <c r="B18" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Buch von der Seelen-angſt Chriſti</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1471</v>
+        <v>1481</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1472</v>
+        <v>1482</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="25"/>
@@ -16474,17 +16537,17 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1473</v>
+        <v>1483</v>
       </c>
       <c r="B19" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Verſuchungs-gabe</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1474</v>
+        <v>1484</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1475</v>
+        <v>1485</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="25"/>
@@ -16494,14 +16557,14 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1476</v>
+        <v>1486</v>
       </c>
       <c r="B20" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kriegsbüchlin</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1477</v>
+        <v>1487</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="9"/>
@@ -16512,14 +16575,14 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1478</v>
+        <v>1488</v>
       </c>
       <c r="B21" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Buch der Psalmen</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1479</v>
+        <v>1489</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="9"/>
@@ -16530,117 +16593,117 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1480</v>
+        <v>1490</v>
       </c>
       <c r="B22" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Sterbensspiegel/ das ist sonnenklare Vorstellung menschlicher Nichtigkeit durch alle Staend und Geschlechter</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1481</v>
+        <v>1491</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1482</v>
+        <v>1492</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1430</v>
+        <v>1440</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1483</v>
+        <v>1493</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>1484</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1485</v>
+        <v>1495</v>
       </c>
       <c r="B23" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Warhaffte/ vnd in Gottes Wort wol gegründte Widerlegung Des newlich im Truck außgegangnen ohn-Catholischen Gesprächs von Religion oder Glaubens sachen/ geneñt der Augenspiegel</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1486</v>
+        <v>1496</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1487</v>
+        <v>1497</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1488</v>
+        <v>1498</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1483</v>
+        <v>1493</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>1489</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1490</v>
+        <v>1500</v>
       </c>
       <c r="B24" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Augspiegels Wahrer Religion Erster Theil</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1491</v>
+        <v>1501</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>1492</v>
+        <v>1502</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1493</v>
+        <v>1503</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1494</v>
+        <v>1504</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>1496</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1497</v>
+        <v>1507</v>
       </c>
       <c r="B25" s="26" t="str">
         <f t="shared" si="1"/>
         <v>De kracht der Godsaligheyt</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1498</v>
+        <v>1508</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>1499</v>
+        <v>1509</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1500</v>
+        <v>1510</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>1501</v>
+        <v>1511</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>1502</v>
+        <v>1512</v>
       </c>
       <c r="H25" s="13"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1503</v>
+        <v>1513</v>
       </c>
       <c r="B26" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16656,7 +16719,7 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1504</v>
+        <v>1514</v>
       </c>
       <c r="B27" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16672,7 +16735,7 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1505</v>
+        <v>1515</v>
       </c>
       <c r="B28" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16688,7 +16751,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1506</v>
+        <v>1516</v>
       </c>
       <c r="B29" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16704,7 +16767,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1507</v>
+        <v>1517</v>
       </c>
       <c r="B30" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16720,7 +16783,7 @@
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1508</v>
+        <v>1518</v>
       </c>
       <c r="B31" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16736,7 +16799,7 @@
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1509</v>
+        <v>1519</v>
       </c>
       <c r="B32" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16752,7 +16815,7 @@
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1510</v>
+        <v>1520</v>
       </c>
       <c r="B33" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16768,7 +16831,7 @@
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1511</v>
+        <v>1521</v>
       </c>
       <c r="B34" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16784,7 +16847,7 @@
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1512</v>
+        <v>1522</v>
       </c>
       <c r="B35" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16800,7 +16863,7 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1513</v>
+        <v>1523</v>
       </c>
       <c r="B36" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16816,7 +16879,7 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1514</v>
+        <v>1524</v>
       </c>
       <c r="B37" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16832,7 +16895,7 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1515</v>
+        <v>1525</v>
       </c>
       <c r="B38" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16848,7 +16911,7 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1516</v>
+        <v>1526</v>
       </c>
       <c r="B39" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16864,7 +16927,7 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1517</v>
+        <v>1527</v>
       </c>
       <c r="B40" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16920,19 +16983,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1518</v>
+        <v>1528</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -16940,69 +17003,69 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="B2" s="26" t="str">
         <f t="shared" ref="B2:B34" si="1">CONCATENATE(C2)</f>
         <v>Rat Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1521</v>
+        <v>1531</v>
       </c>
       <c r="D2" s="25"/>
       <c r="E2" s="27" t="s">
-        <v>1522</v>
+        <v>1532</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1523</v>
+        <v>1533</v>
       </c>
       <c r="B3" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Fruchtbringende Gesellschaft</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1524</v>
+        <v>1534</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1525</v>
+        <v>1535</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>1526</v>
+        <v>1536</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1527</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1528</v>
+        <v>1538</v>
       </c>
       <c r="B4" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Deutschgesinnte Genossenschaft (Lilien-Zunft)</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1529</v>
+        <v>1539</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1530</v>
+        <v>1540</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1531</v>
+        <v>1541</v>
       </c>
       <c r="B5" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Parthenicum</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1532</v>
+        <v>1542</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="13"/>
@@ -17010,107 +17073,107 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1533</v>
+        <v>1543</v>
       </c>
       <c r="B6" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Carolinum Zürich</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1534</v>
+        <v>1544</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1535</v>
+        <v>1545</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="3" t="s">
-        <v>1536</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1537</v>
+        <v>1547</v>
       </c>
       <c r="B7" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Sanhedrin</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1538</v>
+        <v>1548</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="13"/>
       <c r="F7" s="3" t="s">
-        <v>1539</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1540</v>
+        <v>1550</v>
       </c>
       <c r="B8" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Bürgerbibliothek Zürich</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1541</v>
+        <v>1551</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1542</v>
+        <v>1552</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="3" t="s">
-        <v>1543</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1544</v>
+        <v>1554</v>
       </c>
       <c r="B9" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Grossmünster</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1545</v>
+        <v>1555</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1546</v>
+        <v>1556</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1547</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1548</v>
+        <v>1558</v>
       </c>
       <c r="B10" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Fraumünster Zürich</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1549</v>
+        <v>1559</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1550</v>
+        <v>1560</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="3" t="s">
-        <v>1551</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1552</v>
+        <v>1562</v>
       </c>
       <c r="B11" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Hohe Schule Marburg</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1553</v>
+        <v>1563</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="13"/>
@@ -17118,24 +17181,24 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1554</v>
+        <v>1564</v>
       </c>
       <c r="B12" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kartäuser</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1555</v>
+        <v>1565</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1556</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1557</v>
+        <v>1567</v>
       </c>
       <c r="B13" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17148,7 +17211,7 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1558</v>
+        <v>1568</v>
       </c>
       <c r="B14" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17161,7 +17224,7 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1559</v>
+        <v>1569</v>
       </c>
       <c r="B15" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17174,7 +17237,7 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1560</v>
+        <v>1570</v>
       </c>
       <c r="B16" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17187,7 +17250,7 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1561</v>
+        <v>1571</v>
       </c>
       <c r="B17" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17200,7 +17263,7 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1562</v>
+        <v>1572</v>
       </c>
       <c r="B18" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17213,7 +17276,7 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1563</v>
+        <v>1573</v>
       </c>
       <c r="B19" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17226,7 +17289,7 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1564</v>
+        <v>1574</v>
       </c>
       <c r="B20" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17239,7 +17302,7 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1565</v>
+        <v>1575</v>
       </c>
       <c r="B21" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17252,7 +17315,7 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1566</v>
+        <v>1576</v>
       </c>
       <c r="B22" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17265,7 +17328,7 @@
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1567</v>
+        <v>1577</v>
       </c>
       <c r="B23" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17278,7 +17341,7 @@
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1568</v>
+        <v>1578</v>
       </c>
       <c r="B24" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17291,7 +17354,7 @@
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1569</v>
+        <v>1579</v>
       </c>
       <c r="B25" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17304,7 +17367,7 @@
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1570</v>
+        <v>1580</v>
       </c>
       <c r="B26" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17317,7 +17380,7 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1571</v>
+        <v>1581</v>
       </c>
       <c r="B27" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17330,7 +17393,7 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1572</v>
+        <v>1582</v>
       </c>
       <c r="B28" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17343,7 +17406,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1573</v>
+        <v>1583</v>
       </c>
       <c r="B29" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17356,7 +17419,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1574</v>
+        <v>1584</v>
       </c>
       <c r="B30" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17369,7 +17432,7 @@
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1575</v>
+        <v>1585</v>
       </c>
       <c r="B31" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17382,7 +17445,7 @@
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1576</v>
+        <v>1586</v>
       </c>
       <c r="B32" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17395,7 +17458,7 @@
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1577</v>
+        <v>1587</v>
       </c>
       <c r="B33" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17408,7 +17471,7 @@
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1578</v>
+        <v>1588</v>
       </c>
       <c r="B34" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17449,19 +17512,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1579</v>
+        <v>1589</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1580</v>
+        <v>1590</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1581</v>
+        <v>1591</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1582</v>
+        <v>1592</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -17469,26 +17532,26 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1583</v>
+        <v>1593</v>
       </c>
       <c r="B2" s="23" t="str">
         <f t="shared" ref="B2:B8" si="1">CONCATENATE(C2)</f>
         <v>Runs</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1584</v>
+        <v>1594</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1585</v>
+        <v>1595</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>1586</v>
+        <v>1596</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1587</v>
+        <v>1597</v>
       </c>
       <c r="B3" s="23" t="str">
         <f t="shared" si="1"/>
@@ -17501,7 +17564,7 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1588</v>
+        <v>1598</v>
       </c>
       <c r="B4" s="23" t="str">
         <f t="shared" si="1"/>
@@ -17514,7 +17577,7 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1589</v>
+        <v>1599</v>
       </c>
       <c r="B5" s="23" t="str">
         <f t="shared" si="1"/>
@@ -17527,7 +17590,7 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1590</v>
+        <v>1600</v>
       </c>
       <c r="B6" s="23" t="str">
         <f t="shared" si="1"/>
@@ -17540,7 +17603,7 @@
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1591</v>
+        <v>1601</v>
       </c>
       <c r="B7" s="23" t="str">
         <f t="shared" si="1"/>
@@ -17553,7 +17616,7 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1592</v>
+        <v>1602</v>
       </c>
       <c r="B8" s="23" t="str">
         <f t="shared" si="1"/>

--- a/gsheet/xlsx/entities.xlsx
+++ b/gsheet/xlsx/entities.xlsx
@@ -3974,10 +3974,10 @@
     <t>place_058</t>
   </si>
   <si>
-    <t>Thurn/ genennt von Geissen</t>
-  </si>
-  <si>
-    <t>ein Turm?</t>
+    <t>Geissturm</t>
+  </si>
+  <si>
+    <t>Pulverturm</t>
   </si>
   <si>
     <t>place_059</t>
@@ -14977,7 +14977,7 @@
       </c>
       <c r="B59" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>Thurn/ genennt von Geissen</v>
+        <v>Geissturm</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>1273</v>

--- a/gsheet/xlsx/entities.xlsx
+++ b/gsheet/xlsx/entities.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="1603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="1618">
   <si>
     <t>Person-ID</t>
   </si>
@@ -1541,6 +1541,9 @@
     <t>118736558</t>
   </si>
   <si>
+    <t>Sohn von Agamemnon, wegen des Mordes an seiner Mutter von Erinnyen geplagt</t>
+  </si>
+  <si>
     <t>person_117</t>
   </si>
   <si>
@@ -1548,6 +1551,9 @@
   </si>
   <si>
     <t>1371663513</t>
+  </si>
+  <si>
+    <t>Gefährte von Orestes</t>
   </si>
   <si>
     <t>person_118</t>
@@ -2169,7 +2175,16 @@
     <t>Gwalther</t>
   </si>
   <si>
-    <t>Herr</t>
+    <t>Rudolf</t>
+  </si>
+  <si>
+    <t>11854392X</t>
+  </si>
+  <si>
+    <t>Zürcher Theologe, Dichter und Übersetzer</t>
+  </si>
+  <si>
+    <t>https://hls-dhs-dss.ch/de/articles/028298</t>
   </si>
   <si>
     <t>person_176</t>
@@ -2844,12 +2859,6 @@
     <t>person_235</t>
   </si>
   <si>
-    <t>Rudolf</t>
-  </si>
-  <si>
-    <t>11854392X</t>
-  </si>
-  <si>
     <t>person_236</t>
   </si>
   <si>
@@ -3416,9 +3425,27 @@
     <t>person_288</t>
   </si>
   <si>
+    <t>Theodora I.</t>
+  </si>
+  <si>
+    <t>11862170X</t>
+  </si>
+  <si>
+    <t>Ehefrau Justinians</t>
+  </si>
+  <si>
     <t>person_289</t>
   </si>
   <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>Das Volk Israels, Isrealit:innen, Nachkommen von Jakob</t>
+  </si>
+  <si>
+    <t>https://de.wikipedia.org/wiki/Israeliten</t>
+  </si>
+  <si>
     <t>person_290</t>
   </si>
   <si>
@@ -3755,9 +3782,6 @@
     <t>place_029</t>
   </si>
   <si>
-    <t>Israel</t>
-  </si>
-  <si>
     <t>Historisches Königreich Israel</t>
   </si>
   <si>
@@ -4271,6 +4295,15 @@
     <t>place_098</t>
   </si>
   <si>
+    <t>Wüste Juda</t>
+  </si>
+  <si>
+    <t>Judäische Wüste</t>
+  </si>
+  <si>
+    <t>Halbwüste zwischen Israel und dem Westjordanland</t>
+  </si>
+  <si>
     <t>place_099</t>
   </si>
   <si>
@@ -4430,7 +4463,29 @@
     <t>work_003</t>
   </si>
   <si>
-    <t>Buch von Festen</t>
+    <t>Archetypi homiliarum in quatuor evangelia dn. nostri Iesu Christi</t>
+  </si>
+  <si>
+    <t>Gwalther, Rudolf</t>
+  </si>
+  <si>
+    <t>1601</t>
+  </si>
+  <si>
+    <t>Johannes Wolf</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">Viele verschiedene Ausgaben. Hier die erste von Rudolf Simler angegeben. </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.e-rara.ch/zuz/content/titleinfo/2617861</t>
+    </r>
   </si>
   <si>
     <t>work_004</t>
@@ -8862,7 +8917,7 @@
         <v>496</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>407</v>
+        <v>497</v>
       </c>
       <c r="I116" s="7" t="s">
         <v>234</v>
@@ -8872,23 +8927,23 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B117" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pylades,  (-)</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
       <c r="G117" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>407</v>
+        <v>501</v>
       </c>
       <c r="I117" s="7" t="s">
         <v>234</v>
@@ -8898,47 +8953,47 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B118" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thurik,  (-)</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
       <c r="G118" s="9"/>
       <c r="H118" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I118" s="7" t="s">
         <v>234</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K118" s="11"/>
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B119" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Midas,  (-)</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
       <c r="G119" s="9"/>
       <c r="H119" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I119" s="7" t="s">
         <v>234</v>
@@ -8948,97 +9003,101 @@
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B120" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simon,  (-)</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
       <c r="G120" s="9"/>
       <c r="H120" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I120" s="7" t="s">
         <v>234</v>
       </c>
       <c r="J120" s="9"/>
       <c r="K120" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B121" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Damokles,  (-)</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
       <c r="G121" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="I121" s="13"/>
+        <v>516</v>
+      </c>
+      <c r="I121" s="7" t="s">
+        <v>234</v>
+      </c>
       <c r="J121" s="9"/>
       <c r="K121" s="9"/>
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B122" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Dionysius I. von Syrakus,  (-)</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
       <c r="G122" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="I122" s="13"/>
+        <v>520</v>
+      </c>
+      <c r="I122" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="J122" s="9"/>
       <c r="K122" s="9"/>
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B123" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kleopatra VII.,  (-)</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
       <c r="G123" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I123" s="7" t="s">
         <v>16</v>
@@ -9048,25 +9107,25 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B124" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Antonius, Marcus (-)</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
       <c r="G124" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I124" s="7" t="s">
         <v>16</v>
@@ -9076,23 +9135,23 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B125" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klio,  (-)</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
       <c r="G125" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="I125" s="7" t="s">
         <v>234</v>
@@ -9102,23 +9161,23 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B126" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Flora,  (-)</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
       <c r="G126" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="I126" s="7" t="s">
         <v>234</v>
@@ -9128,7 +9187,7 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B127" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9148,21 +9207,21 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B128" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. J. V.,  (-)</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
       <c r="G128" s="9"/>
       <c r="H128" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="I128" s="7" t="s">
         <v>16</v>
@@ -9172,21 +9231,21 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B129" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. J. V., dessen Frau,  (-)</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
       <c r="G129" s="9"/>
       <c r="H129" s="3" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I129" s="7" t="s">
         <v>16</v>
@@ -9196,21 +9255,21 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B130" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Sch. H.,  (-)</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
       <c r="G130" s="9"/>
       <c r="H130" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I130" s="7" t="s">
         <v>16</v>
@@ -9220,14 +9279,14 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B131" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser, Johann Heinrich (1600-1669)</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>44</v>
@@ -9239,66 +9298,66 @@
         <v>1669.0</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H131" s="15" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I131" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J131" s="14" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="K131" s="9"/>
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B132" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser-Ziegler, Jahel (-)</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
       <c r="G132" s="9"/>
       <c r="H132" s="3" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I132" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="K132" s="9"/>
     </row>
     <row r="133" ht="22.5" customHeight="1">
       <c r="A133" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B133" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caspar W.,  (-)</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
       <c r="G133" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I133" s="7" t="s">
         <v>16</v>
@@ -9308,21 +9367,21 @@
     </row>
     <row r="134" ht="22.5" customHeight="1">
       <c r="A134" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B134" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esther O.,  (-)</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
       <c r="G134" s="9"/>
       <c r="H134" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="I134" s="7" t="s">
         <v>16</v>
@@ -9332,14 +9391,14 @@
     </row>
     <row r="135" ht="22.5" customHeight="1">
       <c r="A135" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B135" s="4" t="str">
         <f t="shared" si="1"/>
         <v>G. H.,  (-)</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="5"/>
@@ -9354,21 +9413,21 @@
     </row>
     <row r="136" ht="22.5" customHeight="1">
       <c r="A136" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B136" s="4" t="str">
         <f t="shared" si="1"/>
         <v>J. C.,  (-)</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
       <c r="G136" s="9"/>
       <c r="H136" s="3" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="I136" s="7" t="s">
         <v>16</v>
@@ -9378,17 +9437,17 @@
     </row>
     <row r="137" ht="22.5" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B137" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Hercules von (1617-1686)</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E137" s="5">
         <v>1617.0</v>
@@ -9397,30 +9456,30 @@
         <v>1686.0</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="H137" s="3"/>
       <c r="I137" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K137" s="9"/>
     </row>
     <row r="138" ht="22.5" customHeight="1">
       <c r="A138" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B138" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Barbara Dorothea von (1629-1660)</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E138" s="5">
         <v>1629.0</v>
@@ -9430,26 +9489,26 @@
       </c>
       <c r="G138" s="9"/>
       <c r="H138" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I138" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J138" s="8" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="K138" s="9"/>
     </row>
     <row r="139" ht="22.5" customHeight="1">
       <c r="A139" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B139" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. L.,  (-)</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="5"/>
@@ -9464,21 +9523,21 @@
     </row>
     <row r="140" ht="22.5" customHeight="1">
       <c r="A140" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B140" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. A.,  (-)</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
       <c r="G140" s="9"/>
       <c r="H140" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="I140" s="7" t="s">
         <v>16</v>
@@ -9488,21 +9547,21 @@
     </row>
     <row r="141" ht="22.5" customHeight="1">
       <c r="A141" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B141" s="4" t="str">
         <f t="shared" si="1"/>
         <v>B. M.,  (-)</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D141" s="3"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
       <c r="G141" s="9"/>
       <c r="H141" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="I141" s="7" t="s">
         <v>16</v>
@@ -9512,73 +9571,73 @@
     </row>
     <row r="142" ht="22.5" customHeight="1">
       <c r="A142" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B142" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. H.,  (-)</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="9"/>
       <c r="H142" s="3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="I142" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K142" s="9"/>
     </row>
     <row r="143" ht="22.5" customHeight="1">
       <c r="A143" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B143" s="4" t="str">
         <f t="shared" si="1"/>
         <v>D. M.,  (-)</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D143" s="3"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
       <c r="G143" s="9"/>
       <c r="H143" s="3" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="I143" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="K143" s="9"/>
     </row>
     <row r="144" ht="22.5" customHeight="1">
       <c r="A144" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B144" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gottfrid,  (-)</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
       <c r="G144" s="9"/>
       <c r="H144" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="I144" s="7" t="s">
         <v>16</v>
@@ -9588,7 +9647,7 @@
     </row>
     <row r="145" ht="22.5" customHeight="1">
       <c r="A145" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B145" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9602,7 +9661,7 @@
       <c r="F145" s="5"/>
       <c r="G145" s="9"/>
       <c r="H145" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="I145" s="7" t="s">
         <v>16</v>
@@ -9612,21 +9671,21 @@
     </row>
     <row r="146" ht="22.5" customHeight="1">
       <c r="A146" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B146" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. Schw.,  (-)</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D146" s="3"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
       <c r="G146" s="9"/>
       <c r="H146" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="I146" s="7" t="s">
         <v>16</v>
@@ -9636,21 +9695,21 @@
     </row>
     <row r="147" ht="22.5" customHeight="1">
       <c r="A147" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B147" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. K.,  (-)</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
       <c r="G147" s="9"/>
       <c r="H147" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="I147" s="7" t="s">
         <v>16</v>
@@ -9660,14 +9719,14 @@
     </row>
     <row r="148" ht="22.5" customHeight="1">
       <c r="A148" s="3" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B148" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ott, Hans Heinrich (-)</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>70</v>
@@ -9684,14 +9743,14 @@
     </row>
     <row r="149" ht="22.5" customHeight="1">
       <c r="A149" s="3" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B149" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. W.,  (-)</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D149" s="3"/>
       <c r="E149" s="5"/>
@@ -9706,21 +9765,21 @@
     </row>
     <row r="150" ht="22.5" customHeight="1">
       <c r="A150" s="3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B150" s="4" t="str">
         <f t="shared" si="1"/>
         <v>V. L.,  (-)</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
       <c r="G150" s="9"/>
       <c r="H150" s="3" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="I150" s="7" t="s">
         <v>16</v>
@@ -9730,14 +9789,14 @@
     </row>
     <row r="151" ht="22.5" customHeight="1">
       <c r="A151" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B151" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. Sch.,  (-)</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D151" s="3"/>
       <c r="E151" s="5"/>
@@ -9752,21 +9811,21 @@
     </row>
     <row r="152" ht="22.5" customHeight="1">
       <c r="A152" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B152" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. H.,  (-)</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
       <c r="G152" s="9"/>
       <c r="H152" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="I152" s="7" t="s">
         <v>16</v>
@@ -9776,14 +9835,14 @@
     </row>
     <row r="153" ht="22.5" customHeight="1">
       <c r="A153" s="3" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B153" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. H.,  (-)</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="5"/>
@@ -9794,55 +9853,55 @@
         <v>16</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="K153" s="9"/>
     </row>
     <row r="154" ht="22.5" customHeight="1">
       <c r="A154" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B154" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. W.,  (-)</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="9"/>
       <c r="H154" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="I154" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="K154" s="9"/>
     </row>
     <row r="155" ht="22.5" customHeight="1">
       <c r="A155" s="3" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B155" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Koller, Elisabeth (-)</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
       <c r="G155" s="9"/>
       <c r="H155" s="3" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="I155" s="7" t="s">
         <v>16</v>
@@ -9854,17 +9913,17 @@
     </row>
     <row r="156" ht="22.5" customHeight="1">
       <c r="A156" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B156" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lobwasser, Ambrosius (1515-1585)</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="E156" s="5">
         <v>1515.0</v>
@@ -9873,10 +9932,10 @@
         <v>1585.0</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="I156" s="7" t="s">
         <v>16</v>
@@ -9886,14 +9945,14 @@
     </row>
     <row r="157" ht="22.5" customHeight="1">
       <c r="A157" s="3" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B157" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vollenweider, Jakob (1594-1647)</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>373</v>
@@ -9905,10 +9964,10 @@
         <v>1647.0</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="I157" s="7" t="s">
         <v>16</v>
@@ -9918,7 +9977,7 @@
     </row>
     <row r="158" ht="22.5" customHeight="1">
       <c r="A158" s="3" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B158" s="4" t="str">
         <f t="shared" si="1"/>
@@ -9928,7 +9987,7 @@
         <v>226</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E158" s="5">
         <v>1606.0</v>
@@ -9937,7 +9996,7 @@
         <v>1660.0</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>229</v>
@@ -9950,17 +10009,17 @@
     </row>
     <row r="159" ht="22.5" customHeight="1">
       <c r="A159" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B159" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Burkhard, Hans Konrad (1613-1681)</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E159" s="5">
         <v>1613.0</v>
@@ -9969,10 +10028,10 @@
         <v>1681.0</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="I159" s="7" t="s">
         <v>16</v>
@@ -9982,14 +10041,14 @@
     </row>
     <row r="160" ht="22.5" customHeight="1">
       <c r="A160" s="3" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B160" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ardüser, Johann (1585-1665)</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>108</v>
@@ -10001,40 +10060,40 @@
         <v>1665.0</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="I160" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J160" s="12" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="K160" s="9"/>
     </row>
     <row r="161" ht="22.5" customHeight="1">
       <c r="A161" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B161" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hegner, Diethelm  (-)</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
       <c r="G161" s="3" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="I161" s="7" t="s">
         <v>16</v>
@@ -10044,17 +10103,17 @@
     </row>
     <row r="162" ht="22.5" customHeight="1">
       <c r="A162" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B162" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Trigland, Jacobus (1583-1654)</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E162" s="16">
         <v>1583.0</v>
@@ -10063,10 +10122,10 @@
         <v>1654.0</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="I162" s="7" t="s">
         <v>16</v>
@@ -10076,17 +10135,17 @@
     </row>
     <row r="163" ht="22.5" customHeight="1">
       <c r="A163" s="3" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B163" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwinger, Theodor (?) (1597-1654)</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="E163" s="5">
         <v>1597.0</v>
@@ -10095,32 +10154,32 @@
         <v>1654.0</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="I163" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J163" s="10" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="K163" s="3"/>
     </row>
     <row r="164" ht="22.5" customHeight="1">
       <c r="A164" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B164" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Genath, Johann Jacob (1582-1654)</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="E164" s="5">
         <v>1582.0</v>
@@ -10129,10 +10188,10 @@
         <v>1654.0</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="I164" s="7" t="s">
         <v>16</v>
@@ -10142,49 +10201,49 @@
     </row>
     <row r="165" ht="22.5" customHeight="1">
       <c r="A165" s="3" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B165" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Escher vom Luchs‏, Johannes (‎1646-1659)</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>125</v>
       </c>
       <c r="E165" s="17" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="F165" s="5">
         <v>1659.0</v>
       </c>
       <c r="G165" s="9"/>
       <c r="H165" s="3" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="I165" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J165" s="10" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="K165" s="9"/>
     </row>
     <row r="166" ht="22.5" customHeight="1">
       <c r="A166" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B166" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hess, Caspar (1578-1631)</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E166" s="5">
         <v>1578.0</v>
@@ -10193,29 +10252,29 @@
         <v>1631.0</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="I166" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J166" s="10" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K166" s="9"/>
     </row>
     <row r="167" ht="22.5" customHeight="1">
       <c r="A167" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B167" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wolf, Johann Jakob (1601-1641)</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>32</v>
@@ -10227,10 +10286,10 @@
         <v>1641.0</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I167" s="7" t="s">
         <v>16</v>
@@ -10240,14 +10299,14 @@
     </row>
     <row r="168" ht="22.5" customHeight="1">
       <c r="A168" s="3" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B168" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spörri, Felix (1581-1643)</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>89</v>
@@ -10259,22 +10318,22 @@
         <v>1643.0</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="I168" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J168" s="9"/>
       <c r="K168" s="3" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="169" ht="22.5" customHeight="1">
       <c r="A169" s="3" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B169" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10284,7 +10343,7 @@
         <v>12</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="E169" s="5">
         <v>1604.0</v>
@@ -10300,53 +10359,63 @@
         <v>16</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="K169" s="9"/>
     </row>
     <row r="170" ht="22.5" customHeight="1">
       <c r="A170" s="3" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B170" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Gwalther,  (-)</v>
+        <v>Gwalther, Rudolf (1519-1586)</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>692</v>
-      </c>
-      <c r="D170" s="3"/>
-      <c r="E170" s="18"/>
-      <c r="F170" s="19"/>
-      <c r="G170" s="9"/>
+        <v>694</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="E170" s="5">
+        <v>1519.0</v>
+      </c>
+      <c r="F170" s="5">
+        <v>1586.0</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>696</v>
+      </c>
       <c r="H170" s="3" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="I170" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J170" s="9"/>
+      <c r="J170" s="10" t="s">
+        <v>698</v>
+      </c>
       <c r="K170" s="9"/>
     </row>
     <row r="171" ht="22.5" customHeight="1">
       <c r="A171" s="3" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="B171" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Weiss, Caspar (-)</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E171" s="18"/>
       <c r="F171" s="19"/>
       <c r="G171" s="9"/>
       <c r="H171" s="20" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="I171" s="7" t="s">
         <v>16</v>
@@ -10356,7 +10425,7 @@
     </row>
     <row r="172" ht="22.5" customHeight="1">
       <c r="A172" s="3" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="B172" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10370,7 +10439,7 @@
       <c r="F172" s="19"/>
       <c r="G172" s="9"/>
       <c r="H172" s="20" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="I172" s="7" t="s">
         <v>16</v>
@@ -10380,21 +10449,21 @@
     </row>
     <row r="173" ht="22.5" customHeight="1">
       <c r="A173" s="3" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="B173" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bas,  (-)</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="18"/>
       <c r="F173" s="19"/>
       <c r="G173" s="9"/>
       <c r="H173" s="3" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="I173" s="21"/>
       <c r="J173" s="9"/>
@@ -10402,82 +10471,82 @@
     </row>
     <row r="174" ht="22.5" customHeight="1">
       <c r="A174" s="3" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="B174" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gw., H. H. J. (-)</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="E174" s="18"/>
       <c r="F174" s="19"/>
       <c r="G174" s="9"/>
       <c r="H174" s="3" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="I174" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J174" s="9"/>
       <c r="K174" s="10" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
     </row>
     <row r="175" ht="22.5" customHeight="1">
       <c r="A175" s="3" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="B175" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hofmeister, Johann (‎1622-‎1656‎)</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>108</v>
       </c>
       <c r="E175" s="17" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="F175" s="17" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="G175" s="9"/>
       <c r="H175" s="3" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="I175" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="K175" s="9"/>
     </row>
     <row r="176" ht="22.5" customHeight="1">
       <c r="A176" s="3" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="B176" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Cyrene, Simon von (-)</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="E176" s="18"/>
       <c r="F176" s="19"/>
       <c r="G176" s="3" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>271</v>
@@ -10490,20 +10559,20 @@
     </row>
     <row r="177" ht="22.5" customHeight="1">
       <c r="A177" s="3" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="B177" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thomas,  (-)</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="18"/>
       <c r="F177" s="19"/>
       <c r="G177" s="3" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>343</v>
@@ -10516,23 +10585,23 @@
     </row>
     <row r="178" ht="22.5" customHeight="1">
       <c r="A178" s="3" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="B178" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Phaeton,  (-)</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="18"/>
       <c r="F178" s="19"/>
       <c r="G178" s="3" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="I178" s="7" t="s">
         <v>234</v>
@@ -10542,14 +10611,14 @@
     </row>
     <row r="179" ht="22.5" customHeight="1">
       <c r="A179" s="3" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="B179" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lukas,  (-)</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="D179" s="3"/>
       <c r="E179" s="18"/>
@@ -10566,20 +10635,20 @@
     </row>
     <row r="180" ht="22.5" customHeight="1">
       <c r="A180" s="3" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="B180" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pallas Athena,  (-)</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="18"/>
       <c r="F180" s="19"/>
       <c r="G180" s="3" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>234</v>
@@ -10592,23 +10661,23 @@
     </row>
     <row r="181" ht="22.5" customHeight="1">
       <c r="A181" s="3" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="B181" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bacchus,  (-)</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="D181" s="3"/>
       <c r="E181" s="18"/>
       <c r="F181" s="19"/>
       <c r="G181" s="3" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="I181" s="7" t="s">
         <v>234</v>
@@ -10618,23 +10687,23 @@
     </row>
     <row r="182" ht="22.5" customHeight="1">
       <c r="A182" s="3" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="B182" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Darius I.,  (-)</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="18"/>
       <c r="F182" s="19"/>
       <c r="G182" s="3" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="I182" s="7" t="s">
         <v>16</v>
@@ -10644,23 +10713,23 @@
     </row>
     <row r="183" ht="22.5" customHeight="1">
       <c r="A183" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="B183" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kyros II.,  (-)</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="D183" s="3"/>
       <c r="E183" s="18"/>
       <c r="F183" s="19"/>
       <c r="G183" s="3" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="I183" s="7" t="s">
         <v>16</v>
@@ -10670,25 +10739,25 @@
     </row>
     <row r="184" ht="22.5" customHeight="1">
       <c r="A184" s="3" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="B184" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hippo, Augustinus von (-)</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>742</v>
+        <v>747</v>
       </c>
       <c r="E184" s="18"/>
       <c r="F184" s="19"/>
       <c r="G184" s="3" t="s">
-        <v>743</v>
+        <v>748</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="I184" s="7" t="s">
         <v>16</v>
@@ -10698,23 +10767,23 @@
     </row>
     <row r="185" ht="22.5" customHeight="1">
       <c r="A185" s="3" t="s">
-        <v>745</v>
+        <v>750</v>
       </c>
       <c r="B185" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lazarus,  (-)</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>746</v>
+        <v>751</v>
       </c>
       <c r="D185" s="3"/>
       <c r="E185" s="18"/>
       <c r="F185" s="19"/>
       <c r="G185" s="3" t="s">
-        <v>747</v>
+        <v>752</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>748</v>
+        <v>753</v>
       </c>
       <c r="I185" s="7" t="s">
         <v>271</v>
@@ -10724,23 +10793,23 @@
     </row>
     <row r="186" ht="22.5" customHeight="1">
       <c r="A186" s="3" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B186" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lot,  (-)</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="18"/>
       <c r="F186" s="19"/>
       <c r="G186" s="3" t="s">
-        <v>751</v>
+        <v>756</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="I186" s="7" t="s">
         <v>271</v>
@@ -10750,17 +10819,17 @@
     </row>
     <row r="187" ht="22.5" customHeight="1">
       <c r="A187" s="3" t="s">
-        <v>753</v>
+        <v>758</v>
       </c>
       <c r="B187" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gyger, Johann Rudolf (1603-1662)</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>754</v>
+        <v>759</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="E187" s="5">
         <v>1603.0</v>
@@ -10769,10 +10838,10 @@
         <v>1662.0</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="I187" s="7" t="s">
         <v>16</v>
@@ -10782,7 +10851,7 @@
     </row>
     <row r="188" ht="22.5" customHeight="1">
       <c r="A188" s="3" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="B188" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10795,16 +10864,16 @@
         <v>13</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>759</v>
+        <v>764</v>
       </c>
       <c r="F188" s="5">
         <v>1690.0</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="I188" s="7" t="s">
         <v>16</v>
@@ -10814,17 +10883,17 @@
     </row>
     <row r="189" ht="22.5" customHeight="1">
       <c r="A189" s="3" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="B189" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bachofen, Johann Ulrich (1643-1700)</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>763</v>
+        <v>768</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>764</v>
+        <v>769</v>
       </c>
       <c r="E189" s="5">
         <v>1643.0</v>
@@ -10833,7 +10902,7 @@
         <v>1700.0</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>229</v>
@@ -10846,17 +10915,17 @@
     </row>
     <row r="190" ht="22.5" customHeight="1">
       <c r="A190" s="3" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="B190" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grebel, Hans Konrad (1615-1674)</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E190" s="5">
         <v>1615.0</v>
@@ -10865,57 +10934,57 @@
         <v>1674.0</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>768</v>
+        <v>773</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>769</v>
+        <v>774</v>
       </c>
       <c r="I190" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="K190" s="9"/>
     </row>
     <row r="191" ht="22.5" customHeight="1">
       <c r="A191" s="3" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="B191" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gossweiler, Emerentia (-)</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>772</v>
+        <v>777</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="E191" s="18"/>
       <c r="F191" s="19"/>
       <c r="G191" s="9"/>
       <c r="H191" s="3" t="s">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="I191" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J191" s="8" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="K191" s="9"/>
     </row>
     <row r="192" ht="22.5" customHeight="1">
       <c r="A192" s="3" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
       <c r="B192" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lochmann, Heinrich (1613-1667)</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>38</v>
@@ -10927,29 +10996,29 @@
         <v>1667.0</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J192" s="8" t="s">
-        <v>779</v>
+        <v>784</v>
       </c>
       <c r="K192" s="9"/>
     </row>
     <row r="193" ht="22.5" customHeight="1">
       <c r="A193" s="3" t="s">
-        <v>780</v>
+        <v>785</v>
       </c>
       <c r="B193" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Johann Jakob (1602-1668)</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>32</v>
@@ -10961,109 +11030,109 @@
         <v>1668.0</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J193" s="8" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="K193" s="9"/>
     </row>
     <row r="194" ht="22.5" customHeight="1">
       <c r="A194" s="3" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="B194" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orelli, Anna (-)</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="E194" s="18"/>
       <c r="F194" s="19"/>
       <c r="G194" s="9"/>
       <c r="H194" s="3" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="I194" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J194" s="10" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="K194" s="9"/>
     </row>
     <row r="195" ht="22.5" customHeight="1">
       <c r="A195" s="3" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="B195" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. E. H.,  (-)</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="18"/>
       <c r="F195" s="19"/>
       <c r="G195" s="9"/>
       <c r="H195" s="3" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J195" s="22" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="K195" s="9"/>
     </row>
     <row r="196" ht="22.5" customHeight="1">
       <c r="A196" s="3" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="B196" s="4" t="str">
         <f t="shared" si="1"/>
         <v>C. H.,  (-)</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="D196" s="3"/>
       <c r="E196" s="18"/>
       <c r="F196" s="19"/>
       <c r="G196" s="9"/>
       <c r="H196" s="3" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="I196" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J196" s="22" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="K196" s="9"/>
     </row>
     <row r="197" ht="22.5" customHeight="1">
       <c r="A197" s="3" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="B197" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grob, Hans Jakob (-)</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>222</v>
@@ -11072,19 +11141,19 @@
       <c r="F197" s="19"/>
       <c r="G197" s="9"/>
       <c r="H197" s="3" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="I197" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J197" s="8" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="K197" s="9"/>
     </row>
     <row r="198" ht="22.5" customHeight="1">
       <c r="A198" s="3" t="s">
-        <v>801</v>
+        <v>806</v>
       </c>
       <c r="B198" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11094,7 +11163,7 @@
         <v>69</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="E198" s="18"/>
       <c r="F198" s="19"/>
@@ -11104,23 +11173,23 @@
         <v>16</v>
       </c>
       <c r="J198" s="8" t="s">
-        <v>800</v>
+        <v>805</v>
       </c>
       <c r="K198" s="9"/>
     </row>
     <row r="199" ht="22.5" customHeight="1">
       <c r="A199" s="3" t="s">
-        <v>803</v>
+        <v>808</v>
       </c>
       <c r="B199" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klingler, Kaspar (-)</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>805</v>
+        <v>810</v>
       </c>
       <c r="E199" s="18"/>
       <c r="F199" s="19"/>
@@ -11130,20 +11199,20 @@
         <v>16</v>
       </c>
       <c r="J199" s="8" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="K199" s="9"/>
     </row>
     <row r="200" ht="22.5" customHeight="1">
       <c r="A200" s="3" t="s">
-        <v>807</v>
+        <v>812</v>
       </c>
       <c r="B200" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöndli, Dorothea (-)</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>441</v>
@@ -11156,23 +11225,23 @@
         <v>16</v>
       </c>
       <c r="J200" s="8" t="s">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="K200" s="9"/>
     </row>
     <row r="201" ht="22.5" customHeight="1">
       <c r="A201" s="3" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="B201" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Hans Caspar (1617-1691)</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="E201" s="5">
         <v>1617.0</v>
@@ -11181,32 +11250,32 @@
         <v>1691.0</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>813</v>
+        <v>818</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="K201" s="9"/>
     </row>
     <row r="202" ht="22.5" customHeight="1">
       <c r="A202" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B202" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>Hirzel, Salomon (1580-1652)</v>
+      </c>
+      <c r="C202" s="6" t="s">
         <v>815</v>
       </c>
-      <c r="B202" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>Hirzel, Salomon (1580-1652)</v>
-      </c>
-      <c r="C202" s="6" t="s">
-        <v>810</v>
-      </c>
       <c r="D202" s="3" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="E202" s="5">
         <v>1580.0</v>
@@ -11215,60 +11284,60 @@
         <v>1652.0</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>818</v>
+        <v>823</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J202" s="8" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="K202" s="9"/>
     </row>
     <row r="203" ht="22.5" customHeight="1">
       <c r="A203" s="3" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="B203" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis-Soglio, Maria Ursina von  (-)</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>821</v>
+        <v>826</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="E203" s="18"/>
       <c r="F203" s="19"/>
       <c r="G203" s="9"/>
       <c r="H203" s="3" t="s">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J203" s="8" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="K203" s="9"/>
     </row>
     <row r="204" ht="22.5" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="B204" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Brügger, Andreas von (1588-1653)</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>826</v>
+        <v>831</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>827</v>
+        <v>832</v>
       </c>
       <c r="E204" s="5">
         <v>1588.0</v>
@@ -11277,36 +11346,36 @@
         <v>1653.0</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>828</v>
+        <v>833</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>829</v>
+        <v>834</v>
       </c>
       <c r="I204" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J204" s="8" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="K204" s="9"/>
     </row>
     <row r="205" ht="22.5" customHeight="1">
       <c r="A205" s="3" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="B205" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Anhorn,  (-)</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="D205" s="3"/>
       <c r="E205" s="18"/>
       <c r="F205" s="19"/>
       <c r="G205" s="9"/>
       <c r="H205" s="3" t="s">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="I205" s="7" t="s">
         <v>16</v>
@@ -11316,14 +11385,14 @@
     </row>
     <row r="206" ht="22.5" customHeight="1">
       <c r="A206" s="3" t="s">
-        <v>833</v>
+        <v>838</v>
       </c>
       <c r="B206" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wilden, Abraham (-)</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>298</v>
@@ -11332,7 +11401,7 @@
       <c r="F206" s="19"/>
       <c r="G206" s="9"/>
       <c r="H206" s="3" t="s">
-        <v>835</v>
+        <v>840</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>16</v>
@@ -11342,23 +11411,23 @@
     </row>
     <row r="207" ht="22.5" customHeight="1">
       <c r="A207" s="3" t="s">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="B207" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Groben, Jacob (evtl. Johannes) (-)</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="E207" s="18"/>
       <c r="F207" s="19"/>
       <c r="G207" s="9"/>
       <c r="H207" s="3" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>16</v>
@@ -11368,21 +11437,21 @@
     </row>
     <row r="208" ht="22.5" customHeight="1">
       <c r="A208" s="3" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="B208" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ziegler,  (-)</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="18"/>
       <c r="F208" s="19"/>
       <c r="G208" s="9"/>
       <c r="H208" s="3" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="I208" s="7" t="s">
         <v>16</v>
@@ -11392,7 +11461,7 @@
     </row>
     <row r="209" ht="22.5" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="B209" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11408,7 +11477,7 @@
       <c r="F209" s="19"/>
       <c r="G209" s="9"/>
       <c r="H209" s="3" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="I209" s="7" t="s">
         <v>16</v>
@@ -11418,21 +11487,21 @@
     </row>
     <row r="210" ht="22.5" customHeight="1">
       <c r="A210" s="3" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="B210" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Oeri,  (-)</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="18"/>
       <c r="F210" s="19"/>
       <c r="G210" s="9"/>
       <c r="H210" s="3" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="I210" s="7" t="s">
         <v>16</v>
@@ -11442,21 +11511,21 @@
     </row>
     <row r="211" ht="22.5" customHeight="1">
       <c r="A211" s="3" t="s">
-        <v>848</v>
+        <v>853</v>
       </c>
       <c r="B211" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wittib,  (-)</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>849</v>
+        <v>854</v>
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="18"/>
       <c r="F211" s="19"/>
       <c r="G211" s="9"/>
       <c r="H211" s="3" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="I211" s="13"/>
       <c r="J211" s="9"/>
@@ -11464,14 +11533,14 @@
     </row>
     <row r="212" ht="22.5" customHeight="1">
       <c r="A212" s="3" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="B212" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Graf von Sultz,  (-)</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="D212" s="3"/>
       <c r="E212" s="18"/>
@@ -11486,21 +11555,21 @@
     </row>
     <row r="213" ht="22.5" customHeight="1">
       <c r="A213" s="3" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="B213" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Eglin,  (-)</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
       <c r="D213" s="3"/>
       <c r="E213" s="18"/>
       <c r="F213" s="19"/>
       <c r="G213" s="9"/>
       <c r="H213" s="3" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="I213" s="7" t="s">
         <v>16</v>
@@ -11510,14 +11579,14 @@
     </row>
     <row r="214" ht="22.5" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="B214" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wildhans von Breitenlandenberg,  (-1444)</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="18"/>
@@ -11526,7 +11595,7 @@
       </c>
       <c r="G214" s="9"/>
       <c r="H214" s="3" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="I214" s="7" t="s">
         <v>16</v>
@@ -11536,14 +11605,14 @@
     </row>
     <row r="215" ht="22.5" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="B215" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pfarrherr,  (-)</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="18"/>
@@ -11558,17 +11627,17 @@
     </row>
     <row r="216" ht="22.5" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="B216" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid von Schwarzenhorn, Johann Rudolf (1590-1667)</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="E216" s="5">
         <v>1590.0</v>
@@ -11577,29 +11646,29 @@
         <v>1667.0</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="I216" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J216" s="8" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="K216" s="9"/>
     </row>
     <row r="217" ht="22.5" customHeight="1">
       <c r="A217" s="3" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="B217" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid, Felix (-1598)</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>89</v>
@@ -11610,26 +11679,26 @@
       </c>
       <c r="G217" s="9"/>
       <c r="H217" s="3" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="I217" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J217" s="8" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="K217" s="9"/>
     </row>
     <row r="218" ht="22.5" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="B218" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hessen, Heinrich (-)</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>38</v>
@@ -11638,7 +11707,7 @@
       <c r="F218" s="19"/>
       <c r="G218" s="9"/>
       <c r="H218" s="3" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="I218" s="7" t="s">
         <v>16</v>
@@ -11648,17 +11717,17 @@
     </row>
     <row r="219" ht="22.5" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="B219" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulr., H. (-)</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="E219" s="18"/>
       <c r="F219" s="19"/>
@@ -11674,7 +11743,7 @@
     </row>
     <row r="220" ht="22.5" customHeight="1">
       <c r="A220" s="3" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="B220" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11684,13 +11753,13 @@
         <v>61</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="E220" s="18"/>
       <c r="F220" s="19"/>
       <c r="G220" s="9"/>
       <c r="H220" s="3" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>16</v>
@@ -11700,7 +11769,7 @@
     </row>
     <row r="221" ht="22.5" customHeight="1">
       <c r="A221" s="3" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B221" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11714,7 +11783,7 @@
       <c r="F221" s="19"/>
       <c r="G221" s="9"/>
       <c r="H221" s="3" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="I221" s="7" t="s">
         <v>16</v>
@@ -11724,14 +11793,14 @@
     </row>
     <row r="222" ht="22.5" customHeight="1">
       <c r="A222" s="3" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="B222" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Locher,  (-)</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="18"/>
@@ -11746,17 +11815,17 @@
     </row>
     <row r="223" ht="22.5" customHeight="1">
       <c r="A223" s="3" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="B223" s="4" t="str">
         <f t="shared" si="1"/>
         <v>König, Caspar (-)</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E223" s="18"/>
       <c r="F223" s="19"/>
@@ -11768,7 +11837,7 @@
     </row>
     <row r="224" ht="22.5" customHeight="1">
       <c r="A224" s="3" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="B224" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11790,7 +11859,7 @@
         <v>71</v>
       </c>
       <c r="H224" s="20" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="I224" s="7" t="s">
         <v>16</v>
@@ -11802,7 +11871,7 @@
     </row>
     <row r="225" ht="22.5" customHeight="1">
       <c r="A225" s="3" t="s">
-        <v>885</v>
+        <v>890</v>
       </c>
       <c r="B225" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11816,7 +11885,7 @@
       <c r="F225" s="19"/>
       <c r="G225" s="9"/>
       <c r="H225" s="3" t="s">
-        <v>886</v>
+        <v>891</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>16</v>
@@ -11826,17 +11895,17 @@
     </row>
     <row r="226" ht="22.5" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>887</v>
+        <v>892</v>
       </c>
       <c r="B226" s="4" t="str">
         <f t="shared" si="1"/>
         <v>O., Jacob U. (-)</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>888</v>
+        <v>893</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>889</v>
+        <v>894</v>
       </c>
       <c r="E226" s="18"/>
       <c r="F226" s="19"/>
@@ -11852,21 +11921,21 @@
     </row>
     <row r="227" ht="22.5" customHeight="1">
       <c r="A227" s="3" t="s">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="B227" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schneeberger,  (-)</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="18"/>
       <c r="F227" s="19"/>
       <c r="G227" s="9"/>
       <c r="H227" s="3" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="I227" s="7" t="s">
         <v>16</v>
@@ -11876,17 +11945,17 @@
     </row>
     <row r="228" ht="22.5" customHeight="1">
       <c r="A228" s="3" t="s">
-        <v>893</v>
+        <v>898</v>
       </c>
       <c r="B228" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwingli, Ulrich (1484-1531)</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="E228" s="5">
         <v>1484.0</v>
@@ -11895,10 +11964,10 @@
         <v>1531.0</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="I228" s="7" t="s">
         <v>16</v>
@@ -11908,14 +11977,14 @@
     </row>
     <row r="229" ht="22.5" customHeight="1">
       <c r="A229" s="3" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="B229" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bullinger, Heinrich (1504-1575)</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>38</v>
@@ -11927,10 +11996,10 @@
         <v>1575.0</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="I229" s="7" t="s">
         <v>16</v>
@@ -11940,17 +12009,17 @@
     </row>
     <row r="230" ht="22.5" customHeight="1">
       <c r="A230" s="3" t="s">
-        <v>900</v>
+        <v>905</v>
       </c>
       <c r="B230" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther, Rudolf (1519-1586)</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>901</v>
+        <v>695</v>
       </c>
       <c r="E230" s="5">
         <v>1519.0</v>
@@ -11959,7 +12028,7 @@
         <v>1586.0</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>902</v>
+        <v>696</v>
       </c>
       <c r="H230" s="3"/>
       <c r="I230" s="7" t="s">
@@ -11970,14 +12039,14 @@
     </row>
     <row r="231" ht="22.5" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="B231" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Breitinger, Johann Jakob (1575-1645)</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>32</v>
@@ -11989,7 +12058,7 @@
         <v>1645.0</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="H231" s="3"/>
       <c r="I231" s="7" t="s">
@@ -12000,17 +12069,17 @@
     </row>
     <row r="232" ht="22.5" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B232" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jrminger, Jacob (1588-1649)</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="E232" s="5">
         <v>1588.0</v>
@@ -12019,7 +12088,7 @@
         <v>1649.0</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="H232" s="3"/>
       <c r="I232" s="7" t="s">
@@ -12030,14 +12099,14 @@
     </row>
     <row r="233" ht="22.5" customHeight="1">
       <c r="A233" s="3" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="B233" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fries, Jakob (-)</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>373</v>
@@ -12054,25 +12123,25 @@
     </row>
     <row r="234" ht="22.5" customHeight="1">
       <c r="A234" s="3" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="B234" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Geiger, Joh. Rud. (-)</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="E234" s="18"/>
       <c r="F234" s="19"/>
       <c r="G234" s="3" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="I234" s="7" t="s">
         <v>16</v>
@@ -12082,17 +12151,17 @@
     </row>
     <row r="235" ht="22.5" customHeight="1">
       <c r="A235" s="3" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="B235" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maurer, C. (-)</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="E235" s="18"/>
       <c r="F235" s="19"/>
@@ -12106,17 +12175,17 @@
     </row>
     <row r="236" ht="22.5" customHeight="1">
       <c r="A236" s="3" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="B236" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Suter, C. (-)</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="E236" s="18"/>
       <c r="F236" s="19"/>
@@ -12130,17 +12199,17 @@
     </row>
     <row r="237" ht="22.5" customHeight="1">
       <c r="A237" s="3" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="B237" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Holzhalb, Joh. (-)</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="E237" s="18"/>
       <c r="F237" s="19"/>
@@ -12156,17 +12225,17 @@
     </row>
     <row r="238" ht="22.5" customHeight="1">
       <c r="A238" s="3" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B238" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wirtz, H. C. (-)</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="E238" s="18"/>
       <c r="F238" s="19"/>
@@ -12180,22 +12249,22 @@
     </row>
     <row r="239" ht="22.5" customHeight="1">
       <c r="A239" s="3" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B239" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Waser, Caspar (-)</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E239" s="18"/>
       <c r="F239" s="19"/>
       <c r="G239" s="3" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="H239" s="3"/>
       <c r="I239" s="7" t="s">
@@ -12206,22 +12275,22 @@
     </row>
     <row r="240" ht="22.5" customHeight="1">
       <c r="A240" s="3" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="B240" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hospinianus, R. (-)</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="E240" s="18"/>
       <c r="F240" s="19"/>
       <c r="G240" s="3" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="H240" s="3"/>
       <c r="I240" s="7" t="s">
@@ -12232,17 +12301,17 @@
     </row>
     <row r="241" ht="22.5" customHeight="1">
       <c r="A241" s="3" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B241" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Erni, H. (-)</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="E241" s="18"/>
       <c r="F241" s="19"/>
@@ -12256,17 +12325,17 @@
     </row>
     <row r="242" ht="22.5" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B242" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Tomman, P. (-)</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="E242" s="18"/>
       <c r="F242" s="19"/>
@@ -12280,17 +12349,17 @@
     </row>
     <row r="243" ht="22.5" customHeight="1">
       <c r="A243" s="3" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="B243" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Stukki, R. (-)</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="E243" s="18"/>
       <c r="F243" s="19"/>
@@ -12304,17 +12373,17 @@
     </row>
     <row r="244" ht="22.5" customHeight="1">
       <c r="A244" s="3" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B244" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zeller, H. (-)</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="E244" s="18"/>
       <c r="F244" s="19"/>
@@ -12328,7 +12397,7 @@
     </row>
     <row r="245" ht="22.5" customHeight="1">
       <c r="A245" s="3" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B245" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12336,13 +12405,13 @@
       </c>
       <c r="C245" s="6"/>
       <c r="D245" s="3" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="E245" s="18"/>
       <c r="F245" s="19"/>
       <c r="G245" s="9"/>
       <c r="H245" s="3" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="I245" s="7" t="s">
         <v>16</v>
@@ -12352,21 +12421,21 @@
     </row>
     <row r="246" ht="22.5" customHeight="1">
       <c r="A246" s="3" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B246" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fr. Doctorin,  (-)</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="18"/>
       <c r="F246" s="19"/>
       <c r="G246" s="9"/>
       <c r="H246" s="3" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="I246" s="7" t="s">
         <v>16</v>
@@ -12376,17 +12445,17 @@
     </row>
     <row r="247" ht="22.5" customHeight="1">
       <c r="A247" s="3" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B247" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kusen, Jost von (1570-1630)</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="E247" s="5">
         <v>1570.0</v>
@@ -12395,10 +12464,10 @@
         <v>1630.0</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="I247" s="7" t="s">
         <v>16</v>
@@ -12408,14 +12477,14 @@
     </row>
     <row r="248" ht="22.5" customHeight="1">
       <c r="A248" s="3" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B248" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Heinrich (-)</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>38</v>
@@ -12424,7 +12493,7 @@
       <c r="F248" s="19"/>
       <c r="G248" s="9"/>
       <c r="H248" s="3" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="I248" s="7" t="s">
         <v>16</v>
@@ -12434,21 +12503,21 @@
     </row>
     <row r="249" ht="22.5" customHeight="1">
       <c r="A249" s="3" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="B249" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gessner,  (-)</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="18"/>
       <c r="F249" s="19"/>
       <c r="G249" s="9"/>
       <c r="H249" s="3" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="I249" s="7" t="s">
         <v>16</v>
@@ -12458,17 +12527,17 @@
     </row>
     <row r="250" ht="22.5" customHeight="1">
       <c r="A250" s="3" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B250" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wöllwein, Johann Anton (1616-1659)</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E250" s="5">
         <v>1616.0</v>
@@ -12477,10 +12546,10 @@
         <v>1659.0</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="I250" s="7" t="s">
         <v>16</v>
@@ -12490,42 +12559,42 @@
     </row>
     <row r="251" ht="22.5" customHeight="1">
       <c r="A251" s="3" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="B251" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Anna (-)</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="E251" s="18"/>
       <c r="F251" s="19"/>
       <c r="G251" s="9"/>
       <c r="H251" s="3" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="I251" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="K251" s="9"/>
     </row>
     <row r="252" ht="22.5" customHeight="1">
       <c r="A252" s="3" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="B252" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. J. R. S.,  (-)</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="D252" s="3"/>
       <c r="E252" s="18"/>
@@ -12538,17 +12607,17 @@
     </row>
     <row r="253" ht="22.5" customHeight="1">
       <c r="A253" s="3" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="B253" s="4" t="str">
         <f t="shared" si="1"/>
         <v>de Ruyter, Michiel (1607-1676)</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="E253" s="5">
         <v>1607.0</v>
@@ -12557,10 +12626,10 @@
         <v>1676.0</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="I253" s="7" t="s">
         <v>16</v>
@@ -12570,21 +12639,21 @@
     </row>
     <row r="254" ht="22.5" customHeight="1">
       <c r="A254" s="3" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="B254" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Frau Oberstin,  (-)</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="18"/>
       <c r="F254" s="19"/>
       <c r="G254" s="9"/>
       <c r="H254" s="3" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="I254" s="7" t="s">
         <v>16</v>
@@ -12594,23 +12663,23 @@
     </row>
     <row r="255" ht="22.5" customHeight="1">
       <c r="A255" s="3" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B255" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vulcanus,  (-)</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="18"/>
       <c r="F255" s="19"/>
       <c r="G255" s="3" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="I255" s="7" t="s">
         <v>234</v>
@@ -12620,23 +12689,23 @@
     </row>
     <row r="256" ht="22.5" customHeight="1">
       <c r="A256" s="3" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B256" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esau,  (-)</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="18"/>
       <c r="F256" s="19"/>
       <c r="G256" s="3" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="I256" s="7" t="s">
         <v>271</v>
@@ -12646,23 +12715,23 @@
     </row>
     <row r="257" ht="22.5" customHeight="1">
       <c r="A257" s="3" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B257" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Danaos,  (-)</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="18"/>
       <c r="F257" s="19"/>
       <c r="G257" s="3" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="I257" s="7" t="s">
         <v>234</v>
@@ -12672,20 +12741,20 @@
     </row>
     <row r="258" ht="22.5" customHeight="1">
       <c r="A258" s="3" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B258" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Medusa,  (-)</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="18"/>
       <c r="F258" s="19"/>
       <c r="G258" s="3" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>234</v>
@@ -12698,20 +12767,20 @@
     </row>
     <row r="259" ht="22.5" customHeight="1">
       <c r="A259" s="3" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="B259" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pluton,  (-)</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="18"/>
       <c r="F259" s="19"/>
       <c r="G259" s="3" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>234</v>
@@ -12724,20 +12793,20 @@
     </row>
     <row r="260" ht="22.5" customHeight="1">
       <c r="A260" s="3" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B260" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mercur,  (-)</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="18"/>
       <c r="F260" s="19"/>
       <c r="G260" s="3" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>234</v>
@@ -12750,20 +12819,20 @@
     </row>
     <row r="261" ht="22.5" customHeight="1">
       <c r="A261" s="3" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="B261" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Perseus,  (-)</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="18"/>
       <c r="F261" s="19"/>
       <c r="G261" s="3" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>234</v>
@@ -12776,23 +12845,23 @@
     </row>
     <row r="262" ht="22.5" customHeight="1">
       <c r="A262" s="3" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="B262" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Atropos,  (-)</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="18"/>
       <c r="F262" s="19"/>
       <c r="G262" s="3" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="I262" s="7" t="s">
         <v>234</v>
@@ -12802,23 +12871,23 @@
     </row>
     <row r="263" ht="22.5" customHeight="1">
       <c r="A263" s="3" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="B263" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Barbara von Nikomedien,  (-)</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="18"/>
       <c r="F263" s="19"/>
       <c r="G263" s="3" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H263" s="3" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="I263" s="7" t="s">
         <v>271</v>
@@ -12828,7 +12897,7 @@
     </row>
     <row r="264" ht="22.5" customHeight="1">
       <c r="A264" s="3" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="B264" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12836,13 +12905,13 @@
       </c>
       <c r="C264" s="6"/>
       <c r="D264" s="3" t="s">
-        <v>901</v>
+        <v>695</v>
       </c>
       <c r="E264" s="18"/>
       <c r="F264" s="19"/>
       <c r="G264" s="9"/>
       <c r="H264" s="3" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="I264" s="13"/>
       <c r="J264" s="9"/>
@@ -12850,7 +12919,7 @@
     </row>
     <row r="265" ht="22.5" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B265" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12864,7 +12933,7 @@
       <c r="F265" s="19"/>
       <c r="G265" s="9"/>
       <c r="H265" s="3" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="I265" s="13"/>
       <c r="J265" s="9"/>
@@ -12872,21 +12941,21 @@
     </row>
     <row r="266" ht="22.5" customHeight="1">
       <c r="A266" s="3" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B266" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Karl,  (-)</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="18"/>
       <c r="F266" s="19"/>
       <c r="G266" s="9"/>
       <c r="H266" s="3" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="I266" s="7" t="s">
         <v>16</v>
@@ -12896,21 +12965,21 @@
     </row>
     <row r="267" ht="22.5" customHeight="1">
       <c r="A267" s="3" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="B267" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Duraeum,  (-)</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="18"/>
       <c r="F267" s="19"/>
       <c r="G267" s="9"/>
       <c r="H267" s="3" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="I267" s="13"/>
       <c r="J267" s="9"/>
@@ -12918,17 +12987,17 @@
     </row>
     <row r="268" ht="22.5" customHeight="1">
       <c r="A268" s="3" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="B268" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zesen, Philipp von (1619-1689)</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="E268" s="5">
         <v>1619.0</v>
@@ -12937,7 +13006,7 @@
         <v>1689.0</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="H268" s="3"/>
       <c r="I268" s="7" t="s">
@@ -12948,23 +13017,23 @@
     </row>
     <row r="269" ht="22.5" customHeight="1">
       <c r="A269" s="3" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="B269" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lucretia,  (-)</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="D269" s="3"/>
       <c r="E269" s="18"/>
       <c r="F269" s="19"/>
       <c r="G269" s="3" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="I269" s="7" t="s">
         <v>234</v>
@@ -12974,23 +13043,23 @@
     </row>
     <row r="270" ht="22.5" customHeight="1">
       <c r="A270" s="3" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B270" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ovid,  (-)</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="18"/>
       <c r="F270" s="19"/>
       <c r="G270" s="3" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="H270" s="3" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="I270" s="7" t="s">
         <v>16</v>
@@ -13000,50 +13069,50 @@
     </row>
     <row r="271" ht="22.5" customHeight="1">
       <c r="A271" s="3" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="B271" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schweizer, Johann Caspar (1619/1620-1684/1688)</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="H271" s="3" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="I271" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J271" s="8" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="K271" s="3" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="272" ht="22.5" customHeight="1">
       <c r="A272" s="3" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="B272" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Herder, Johann Heinrich (1629-1665)</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>44</v>
@@ -13055,10 +13124,10 @@
         <v>1665.0</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="H272" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="I272" s="7" t="s">
         <v>16</v>
@@ -13068,23 +13137,23 @@
     </row>
     <row r="273" ht="22.5" customHeight="1">
       <c r="A273" s="3" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="B273" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Elischa,  (-)</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="D273" s="3"/>
       <c r="E273" s="18"/>
       <c r="F273" s="19"/>
       <c r="G273" s="3" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="H273" s="3" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="I273" s="7" t="s">
         <v>271</v>
@@ -13094,23 +13163,23 @@
     </row>
     <row r="274" ht="22.5" customHeight="1">
       <c r="A274" s="3" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B274" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Johannes der Täufer,  (-)</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="D274" s="3"/>
       <c r="E274" s="18"/>
       <c r="F274" s="19"/>
       <c r="G274" s="3" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="I274" s="7" t="s">
         <v>271</v>
@@ -13120,29 +13189,29 @@
     </row>
     <row r="275" ht="22.5" customHeight="1">
       <c r="A275" s="3" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="B275" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caesar, Gaius Iulius (100 v. Chr.-44 v. Chr.)</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="H275" s="3" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="I275" s="7" t="s">
         <v>16</v>
@@ -13152,23 +13221,23 @@
     </row>
     <row r="276" ht="22.5" customHeight="1">
       <c r="A276" s="3" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B276" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Helios,  (-)</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="D276" s="3"/>
       <c r="E276" s="18"/>
       <c r="F276" s="19"/>
       <c r="G276" s="3" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="H276" s="3" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="I276" s="7" t="s">
         <v>234</v>
@@ -13178,77 +13247,77 @@
     </row>
     <row r="277" ht="22.5" customHeight="1">
       <c r="A277" s="3" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="B277" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Suevus,  (-)</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="D277" s="3"/>
       <c r="E277" s="18"/>
       <c r="F277" s="19"/>
       <c r="G277" s="9"/>
       <c r="H277" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I277" s="7" t="s">
         <v>234</v>
       </c>
       <c r="J277" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="K277" s="11"/>
     </row>
     <row r="278" ht="22.5" customHeight="1">
       <c r="A278" s="3" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B278" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Momos,  (-)</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D278" s="3"/>
       <c r="E278" s="18"/>
       <c r="F278" s="19"/>
       <c r="G278" s="3" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="H278" s="3" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="I278" s="7" t="s">
         <v>234</v>
       </c>
       <c r="J278" s="10" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="K278" s="9"/>
     </row>
     <row r="279" ht="22.5" customHeight="1">
       <c r="A279" s="3" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="B279" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Galatea,  (-)</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="D279" s="3"/>
       <c r="E279" s="18"/>
       <c r="F279" s="19"/>
       <c r="G279" s="3" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="H279" s="3" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="I279" s="7" t="s">
         <v>234</v>
@@ -13258,80 +13327,80 @@
     </row>
     <row r="280" ht="22.5" customHeight="1">
       <c r="A280" s="3" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="B280" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Escher vom Luchs‏‎, Hans Heinrich (‎1644-1714)</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E280" s="17" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="F280" s="5">
         <v>1714.0</v>
       </c>
       <c r="G280" s="9"/>
       <c r="H280" s="3" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="I280" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J280" s="10" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="K280" s="10" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="281" ht="22.5" customHeight="1">
       <c r="A281" s="3" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B281" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Agapetus,  (6. Jh.-6. Jh.)</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D281" s="3"/>
       <c r="E281" s="17" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="H281" s="3" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="I281" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J281" s="10" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="K281" s="15"/>
     </row>
     <row r="282" ht="22.5" customHeight="1">
       <c r="A282" s="3" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="B282" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Justinian I.,  (482-565)</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="D282" s="3"/>
       <c r="E282" s="17">
@@ -13341,7 +13410,7 @@
         <v>565.0</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="H282" s="3" t="s">
         <v>365</v>
@@ -13354,43 +13423,63 @@
     </row>
     <row r="283" ht="22.5" customHeight="1">
       <c r="A283" s="3" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="B283" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>,  (-)</v>
-      </c>
-      <c r="C283" s="6"/>
+        <v>Theodora I.,  (497-548)</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>1090</v>
+      </c>
       <c r="D283" s="3"/>
-      <c r="E283" s="17"/>
-      <c r="F283" s="5"/>
-      <c r="G283" s="9"/>
-      <c r="H283" s="3"/>
-      <c r="I283" s="7"/>
+      <c r="E283" s="17">
+        <v>497.0</v>
+      </c>
+      <c r="F283" s="5">
+        <v>548.0</v>
+      </c>
+      <c r="G283" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H283" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="I283" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="J283" s="15"/>
       <c r="K283" s="15"/>
     </row>
     <row r="284" ht="22.5" customHeight="1">
       <c r="A284" s="3" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="B284" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>,  (-)</v>
-      </c>
-      <c r="C284" s="6"/>
+        <v>Israel,  (-)</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>1094</v>
+      </c>
       <c r="D284" s="3"/>
       <c r="E284" s="17"/>
       <c r="F284" s="5"/>
       <c r="G284" s="9"/>
-      <c r="H284" s="3"/>
-      <c r="I284" s="7"/>
-      <c r="J284" s="15"/>
+      <c r="H284" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I284" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="J284" s="10" t="s">
+        <v>1096</v>
+      </c>
       <c r="K284" s="15"/>
     </row>
     <row r="285" ht="22.5" customHeight="1">
       <c r="A285" s="3" t="s">
-        <v>1088</v>
+        <v>1097</v>
       </c>
       <c r="B285" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13408,7 +13497,7 @@
     </row>
     <row r="286" ht="22.5" customHeight="1">
       <c r="A286" s="3" t="s">
-        <v>1089</v>
+        <v>1098</v>
       </c>
       <c r="B286" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13426,7 +13515,7 @@
     </row>
     <row r="287" ht="22.5" customHeight="1">
       <c r="A287" s="3" t="s">
-        <v>1090</v>
+        <v>1099</v>
       </c>
       <c r="B287" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13444,7 +13533,7 @@
     </row>
     <row r="288" ht="22.5" customHeight="1">
       <c r="A288" s="3" t="s">
-        <v>1091</v>
+        <v>1100</v>
       </c>
       <c r="B288" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13462,7 +13551,7 @@
     </row>
     <row r="289" ht="22.5" customHeight="1">
       <c r="A289" s="3" t="s">
-        <v>1092</v>
+        <v>1101</v>
       </c>
       <c r="B289" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13480,7 +13569,7 @@
     </row>
     <row r="290" ht="22.5" customHeight="1">
       <c r="A290" s="3" t="s">
-        <v>1093</v>
+        <v>1102</v>
       </c>
       <c r="B290" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13498,7 +13587,7 @@
     </row>
     <row r="291" ht="22.5" customHeight="1">
       <c r="A291" s="3" t="s">
-        <v>1094</v>
+        <v>1103</v>
       </c>
       <c r="B291" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13516,7 +13605,7 @@
     </row>
     <row r="292" ht="22.5" customHeight="1">
       <c r="A292" s="3" t="s">
-        <v>1095</v>
+        <v>1104</v>
       </c>
       <c r="B292" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13534,7 +13623,7 @@
     </row>
     <row r="293" ht="22.5" customHeight="1">
       <c r="A293" s="3" t="s">
-        <v>1096</v>
+        <v>1105</v>
       </c>
       <c r="B293" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13552,7 +13641,7 @@
     </row>
     <row r="294" ht="22.5" customHeight="1">
       <c r="A294" s="3" t="s">
-        <v>1097</v>
+        <v>1106</v>
       </c>
       <c r="B294" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13570,7 +13659,7 @@
     </row>
     <row r="295" ht="22.5" customHeight="1">
       <c r="A295" s="3" t="s">
-        <v>1098</v>
+        <v>1107</v>
       </c>
       <c r="B295" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13588,7 +13677,7 @@
     </row>
     <row r="296" ht="22.5" customHeight="1">
       <c r="A296" s="3" t="s">
-        <v>1099</v>
+        <v>1108</v>
       </c>
       <c r="B296" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13606,7 +13695,7 @@
     </row>
     <row r="297" ht="22.5" customHeight="1">
       <c r="A297" s="3" t="s">
-        <v>1100</v>
+        <v>1109</v>
       </c>
       <c r="B297" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13624,7 +13713,7 @@
     </row>
     <row r="298" ht="22.5" customHeight="1">
       <c r="A298" s="3" t="s">
-        <v>1101</v>
+        <v>1110</v>
       </c>
       <c r="B298" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13642,7 +13731,7 @@
     </row>
     <row r="299" ht="22.5" customHeight="1">
       <c r="A299" s="3" t="s">
-        <v>1102</v>
+        <v>1111</v>
       </c>
       <c r="B299" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13660,7 +13749,7 @@
     </row>
     <row r="300" ht="22.5" customHeight="1">
       <c r="A300" s="3" t="s">
-        <v>1103</v>
+        <v>1112</v>
       </c>
       <c r="B300" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13678,7 +13767,7 @@
     </row>
     <row r="301" ht="22.5" customHeight="1">
       <c r="A301" s="3" t="s">
-        <v>1104</v>
+        <v>1113</v>
       </c>
       <c r="B301" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13696,7 +13785,7 @@
     </row>
     <row r="302" ht="22.5" customHeight="1">
       <c r="A302" s="3" t="s">
-        <v>1105</v>
+        <v>1114</v>
       </c>
       <c r="B302" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13714,7 +13803,7 @@
     </row>
     <row r="303" ht="22.5" customHeight="1">
       <c r="A303" s="3" t="s">
-        <v>1106</v>
+        <v>1115</v>
       </c>
       <c r="B303" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13732,7 +13821,7 @@
     </row>
     <row r="304" ht="22.5" customHeight="1">
       <c r="A304" s="3" t="s">
-        <v>1107</v>
+        <v>1116</v>
       </c>
       <c r="B304" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13750,7 +13839,7 @@
     </row>
     <row r="305" ht="22.5" customHeight="1">
       <c r="A305" s="3" t="s">
-        <v>1108</v>
+        <v>1117</v>
       </c>
       <c r="B305" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13768,7 +13857,7 @@
     </row>
     <row r="306" ht="22.5" customHeight="1">
       <c r="A306" s="3" t="s">
-        <v>1109</v>
+        <v>1118</v>
       </c>
       <c r="B306" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13786,7 +13875,7 @@
     </row>
     <row r="307" ht="22.5" customHeight="1">
       <c r="A307" s="3" t="s">
-        <v>1110</v>
+        <v>1119</v>
       </c>
       <c r="B307" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13804,7 +13893,7 @@
     </row>
     <row r="308" ht="22.5" customHeight="1">
       <c r="A308" s="3" t="s">
-        <v>1111</v>
+        <v>1120</v>
       </c>
       <c r="B308" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13822,7 +13911,7 @@
     </row>
     <row r="309" ht="22.5" customHeight="1">
       <c r="A309" s="3" t="s">
-        <v>1112</v>
+        <v>1121</v>
       </c>
       <c r="B309" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13840,7 +13929,7 @@
     </row>
     <row r="310" ht="22.5" customHeight="1">
       <c r="A310" s="3" t="s">
-        <v>1113</v>
+        <v>1122</v>
       </c>
       <c r="B310" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13920,33 +14009,35 @@
     <hyperlink r:id="rId52" location="person_I298580" ref="J165"/>
     <hyperlink r:id="rId53" ref="J166"/>
     <hyperlink r:id="rId54" ref="J169"/>
-    <hyperlink r:id="rId55" ref="K174"/>
-    <hyperlink r:id="rId56" location="person_I295072" ref="J175"/>
-    <hyperlink r:id="rId57" ref="J190"/>
-    <hyperlink r:id="rId58" ref="J191"/>
-    <hyperlink r:id="rId59" ref="J192"/>
-    <hyperlink r:id="rId60" ref="J193"/>
-    <hyperlink r:id="rId61" ref="J194"/>
-    <hyperlink r:id="rId62" ref="J197"/>
-    <hyperlink r:id="rId63" ref="J198"/>
-    <hyperlink r:id="rId64" ref="J199"/>
-    <hyperlink r:id="rId65" ref="J200"/>
-    <hyperlink r:id="rId66" ref="J201"/>
-    <hyperlink r:id="rId67" ref="J202"/>
-    <hyperlink r:id="rId68" ref="J203"/>
-    <hyperlink r:id="rId69" ref="J204"/>
-    <hyperlink r:id="rId70" ref="J216"/>
-    <hyperlink r:id="rId71" ref="J217"/>
-    <hyperlink r:id="rId72" ref="J224"/>
-    <hyperlink r:id="rId73" ref="J271"/>
-    <hyperlink r:id="rId74" ref="J278"/>
-    <hyperlink r:id="rId75" ref="J280"/>
-    <hyperlink r:id="rId76" ref="K280"/>
-    <hyperlink r:id="rId77" ref="J281"/>
+    <hyperlink r:id="rId55" ref="J170"/>
+    <hyperlink r:id="rId56" ref="K174"/>
+    <hyperlink r:id="rId57" location="person_I295072" ref="J175"/>
+    <hyperlink r:id="rId58" ref="J190"/>
+    <hyperlink r:id="rId59" ref="J191"/>
+    <hyperlink r:id="rId60" ref="J192"/>
+    <hyperlink r:id="rId61" ref="J193"/>
+    <hyperlink r:id="rId62" ref="J194"/>
+    <hyperlink r:id="rId63" ref="J197"/>
+    <hyperlink r:id="rId64" ref="J198"/>
+    <hyperlink r:id="rId65" ref="J199"/>
+    <hyperlink r:id="rId66" ref="J200"/>
+    <hyperlink r:id="rId67" ref="J201"/>
+    <hyperlink r:id="rId68" ref="J202"/>
+    <hyperlink r:id="rId69" ref="J203"/>
+    <hyperlink r:id="rId70" ref="J204"/>
+    <hyperlink r:id="rId71" ref="J216"/>
+    <hyperlink r:id="rId72" ref="J217"/>
+    <hyperlink r:id="rId73" ref="J224"/>
+    <hyperlink r:id="rId74" ref="J271"/>
+    <hyperlink r:id="rId75" ref="J278"/>
+    <hyperlink r:id="rId76" ref="J280"/>
+    <hyperlink r:id="rId77" ref="K280"/>
+    <hyperlink r:id="rId78" ref="J281"/>
+    <hyperlink r:id="rId79" ref="J284"/>
   </hyperlinks>
-  <drawing r:id="rId78"/>
+  <drawing r:id="rId80"/>
   <tableParts count="1">
-    <tablePart r:id="rId80"/>
+    <tablePart r:id="rId82"/>
   </tableParts>
 </worksheet>
 </file>
@@ -13968,16 +14059,16 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1114</v>
+        <v>1123</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1115</v>
+        <v>1124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1116</v>
+        <v>1125</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -13988,179 +14079,179 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1117</v>
+        <v>1126</v>
       </c>
       <c r="B2" s="23" t="str">
         <f t="shared" ref="B2:B132" si="1">CONCATENATE(C2)</f>
         <v>Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="7" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1121</v>
+        <v>1130</v>
       </c>
       <c r="B3" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Basel</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1122</v>
+        <v>1131</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="7" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1123</v>
+        <v>1132</v>
       </c>
       <c r="B4" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Eidgenossenschaft</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1124</v>
+        <v>1133</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1125</v>
+        <v>1134</v>
       </c>
       <c r="E4" s="21"/>
       <c r="F4" s="3" t="s">
-        <v>1126</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1127</v>
+        <v>1136</v>
       </c>
       <c r="B5" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Limmat</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1128</v>
+        <v>1137</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="7" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1130</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1131</v>
+        <v>1140</v>
       </c>
       <c r="B6" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Weinfelden</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1132</v>
+        <v>1141</v>
       </c>
       <c r="D6" s="25"/>
       <c r="E6" s="7" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1133</v>
+        <v>1142</v>
       </c>
       <c r="B7" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Main</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1134</v>
+        <v>1143</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="7" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1130</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1135</v>
+        <v>1144</v>
       </c>
       <c r="B8" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Zürichsee</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1136</v>
+        <v>1145</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="7" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1137</v>
+        <v>1146</v>
       </c>
       <c r="B9" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Thalwil</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1138</v>
+        <v>1147</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1139</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1140</v>
+        <v>1149</v>
       </c>
       <c r="B10" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bern</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1141</v>
+        <v>1150</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="7" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1142</v>
+        <v>1151</v>
       </c>
       <c r="B11" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Gottstatt</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1143</v>
+        <v>1152</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="13"/>
@@ -14168,325 +14259,325 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1144</v>
+        <v>1153</v>
       </c>
       <c r="B12" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Thorberg</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1145</v>
+        <v>1154</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1146</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1147</v>
+        <v>1156</v>
       </c>
       <c r="B13" s="24" t="str">
         <f t="shared" si="1"/>
         <v>London</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1148</v>
+        <v>1157</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="7" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1149</v>
+        <v>1158</v>
       </c>
       <c r="B14" s="24" t="str">
         <f t="shared" si="1"/>
         <v>England</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1150</v>
+        <v>1159</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="7" t="s">
-        <v>1151</v>
+        <v>1160</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1152</v>
+        <v>1161</v>
       </c>
       <c r="B15" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bethlehem</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1153</v>
+        <v>1162</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="7" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1154</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1155</v>
+        <v>1164</v>
       </c>
       <c r="B16" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Parnass </v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1156</v>
+        <v>1165</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="7" t="s">
-        <v>1157</v>
+        <v>1166</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1158</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1159</v>
+        <v>1168</v>
       </c>
       <c r="B17" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Traubenberg</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1160</v>
+        <v>1169</v>
       </c>
       <c r="D17" s="25"/>
       <c r="E17" s="13"/>
       <c r="F17" s="3" t="s">
-        <v>1161</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1162</v>
+        <v>1171</v>
       </c>
       <c r="B18" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Babylon</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1163</v>
+        <v>1172</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1164</v>
+        <v>1173</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1165</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1166</v>
+        <v>1175</v>
       </c>
       <c r="B19" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Canaan</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1167</v>
+        <v>1176</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="7" t="s">
-        <v>1168</v>
+        <v>1177</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1169</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1170</v>
+        <v>1179</v>
       </c>
       <c r="B20" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Ägypten</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1171</v>
+        <v>1180</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1172</v>
+        <v>1181</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1151</v>
+        <v>1160</v>
       </c>
       <c r="F20" s="9"/>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1173</v>
+        <v>1182</v>
       </c>
       <c r="B21" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Hermon</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1174</v>
+        <v>1183</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="7" t="s">
-        <v>1157</v>
+        <v>1166</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1175</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1176</v>
+        <v>1185</v>
       </c>
       <c r="B22" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Jerusalem</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1177</v>
+        <v>1186</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1178</v>
+        <v>1187</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1179</v>
+        <v>1188</v>
       </c>
       <c r="B23" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Jordan</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1180</v>
+        <v>1189</v>
       </c>
       <c r="D23" s="25"/>
       <c r="E23" s="7" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1181</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1182</v>
+        <v>1191</v>
       </c>
       <c r="B24" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Rotes Meer</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1183</v>
+        <v>1192</v>
       </c>
       <c r="D24" s="25"/>
       <c r="E24" s="7" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="F24" s="9"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1184</v>
+        <v>1193</v>
       </c>
       <c r="B25" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Juda</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1185</v>
+        <v>1194</v>
       </c>
       <c r="D25" s="25"/>
       <c r="E25" s="13"/>
       <c r="F25" s="3" t="s">
-        <v>1186</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1187</v>
+        <v>1196</v>
       </c>
       <c r="B26" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Moab</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1188</v>
+        <v>1197</v>
       </c>
       <c r="D26" s="25"/>
       <c r="E26" s="13"/>
       <c r="F26" s="3" t="s">
-        <v>1189</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1190</v>
+        <v>1199</v>
       </c>
       <c r="B27" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Ammon</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1191</v>
+        <v>1200</v>
       </c>
       <c r="D27" s="25"/>
       <c r="E27" s="13"/>
       <c r="F27" s="3" t="s">
-        <v>1192</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1193</v>
+        <v>1202</v>
       </c>
       <c r="B28" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Zion</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1194</v>
+        <v>1203</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>1195</v>
+        <v>1204</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1157</v>
+        <v>1166</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>1196</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1197</v>
+        <v>1206</v>
       </c>
       <c r="B29" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Assur</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1198</v>
+        <v>1207</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="13"/>
@@ -14494,101 +14585,101 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1199</v>
+        <v>1208</v>
       </c>
       <c r="B30" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Israel</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1200</v>
+        <v>1094</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="13"/>
       <c r="F30" s="3" t="s">
-        <v>1201</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1202</v>
+        <v>1210</v>
       </c>
       <c r="B31" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Nazaret</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="D31" s="25"/>
       <c r="E31" s="7" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="B32" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Rom</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="D32" s="25"/>
       <c r="E32" s="13"/>
       <c r="F32" s="3" t="s">
-        <v>1207</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1208</v>
+        <v>1216</v>
       </c>
       <c r="B33" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Samaria</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1209</v>
+        <v>1217</v>
       </c>
       <c r="D33" s="25"/>
       <c r="E33" s="13"/>
       <c r="F33" s="3" t="s">
-        <v>1210</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="B34" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kedronbach</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1212</v>
+        <v>1220</v>
       </c>
       <c r="D34" s="25"/>
       <c r="E34" s="13"/>
       <c r="F34" s="3" t="s">
-        <v>1213</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1214</v>
+        <v>1222</v>
       </c>
       <c r="B35" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Garten von Getsemani</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1215</v>
+        <v>1223</v>
       </c>
       <c r="D35" s="25"/>
       <c r="E35" s="13"/>
@@ -14596,14 +14687,14 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="B36" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Urdorf</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="13"/>
@@ -14611,14 +14702,14 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="B37" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Geiren-Rein</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1219</v>
+        <v>1227</v>
       </c>
       <c r="D37" s="25"/>
       <c r="E37" s="13"/>
@@ -14626,14 +14717,14 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="B38" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Aeügst</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="D38" s="25"/>
       <c r="E38" s="13"/>
@@ -14641,14 +14732,14 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1222</v>
+        <v>1230</v>
       </c>
       <c r="B39" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Riedt</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1223</v>
+        <v>1231</v>
       </c>
       <c r="D39" s="25"/>
       <c r="E39" s="13"/>
@@ -14656,14 +14747,14 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1224</v>
+        <v>1232</v>
       </c>
       <c r="B40" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Europa</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="D40" s="25"/>
       <c r="E40" s="13"/>
@@ -14671,48 +14762,48 @@
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>1226</v>
+        <v>1234</v>
       </c>
       <c r="B41" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Osir</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1227</v>
+        <v>1235</v>
       </c>
       <c r="D41" s="25"/>
       <c r="E41" s="13"/>
       <c r="F41" s="3" t="s">
-        <v>1228</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="B42" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Basadingen</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1230</v>
+        <v>1238</v>
       </c>
       <c r="D42" s="25"/>
       <c r="E42" s="13"/>
       <c r="F42" s="3" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>1232</v>
+        <v>1240</v>
       </c>
       <c r="B43" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Diessenhofen</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="D43" s="25"/>
       <c r="E43" s="13"/>
@@ -14720,50 +14811,50 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>1234</v>
+        <v>1242</v>
       </c>
       <c r="B44" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Rhein</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1235</v>
+        <v>1243</v>
       </c>
       <c r="D44" s="25"/>
       <c r="E44" s="7" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1130</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>1236</v>
+        <v>1244</v>
       </c>
       <c r="B45" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Arabisches Reich</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1237</v>
+        <v>1245</v>
       </c>
       <c r="D45" s="25"/>
       <c r="E45" s="13"/>
       <c r="F45" s="3" t="s">
-        <v>1238</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>1239</v>
+        <v>1247</v>
       </c>
       <c r="B46" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Libanon</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1240</v>
+        <v>1248</v>
       </c>
       <c r="D46" s="25"/>
       <c r="E46" s="13"/>
@@ -14771,105 +14862,105 @@
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>1241</v>
+        <v>1249</v>
       </c>
       <c r="B47" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Emmaus</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1242</v>
+        <v>1250</v>
       </c>
       <c r="D47" s="25"/>
       <c r="E47" s="13"/>
       <c r="F47" s="3" t="s">
-        <v>1243</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>1244</v>
+        <v>1252</v>
       </c>
       <c r="B48" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Helikon</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1245</v>
+        <v>1253</v>
       </c>
       <c r="D48" s="25"/>
       <c r="E48" s="7" t="s">
-        <v>1157</v>
+        <v>1166</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>1246</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="B49" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Pindos</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="D49" s="25"/>
       <c r="E49" s="7" t="s">
-        <v>1157</v>
+        <v>1166</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="B50" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Neckar</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1251</v>
+        <v>1259</v>
       </c>
       <c r="D50" s="25"/>
       <c r="E50" s="7" t="s">
-        <v>1129</v>
+        <v>1138</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1252</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>1253</v>
+        <v>1261</v>
       </c>
       <c r="B51" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kurpfalz</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="D51" s="25"/>
       <c r="E51" s="13"/>
       <c r="F51" s="3" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="B52" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Eglisau</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="D52" s="25"/>
       <c r="E52" s="13"/>
@@ -14877,14 +14968,14 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="B53" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Altenklingen</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="D53" s="25"/>
       <c r="E53" s="13"/>
@@ -14892,14 +14983,14 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="B54" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Altorff</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="D54" s="25"/>
       <c r="E54" s="13"/>
@@ -14907,65 +14998,65 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
       <c r="B55" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Glarus</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="D55" s="25"/>
       <c r="E55" s="13"/>
       <c r="F55" s="3" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="B56" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Reformierte Kirche Berg am Irchel</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1265</v>
+        <v>1273</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="3"/>
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>1267</v>
+        <v>1275</v>
       </c>
       <c r="B57" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Sodom</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1268</v>
+        <v>1276</v>
       </c>
       <c r="D57" s="25"/>
       <c r="E57" s="13"/>
       <c r="F57" s="3" t="s">
-        <v>1269</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="B58" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Haus zur Sonnenblume</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="D58" s="25"/>
       <c r="E58" s="13"/>
@@ -14973,154 +15064,154 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="B59" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Geissturm</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="D59" s="25"/>
       <c r="E59" s="13"/>
       <c r="F59" s="3" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="B60" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Konstantinopel</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F60" s="3"/>
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
       <c r="B61" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Stein am Rhein</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="D61" s="25"/>
       <c r="E61" s="13"/>
       <c r="F61" s="3" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>1281</v>
+        <v>1289</v>
       </c>
       <c r="B62" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Marburg</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1282</v>
+        <v>1290</v>
       </c>
       <c r="D62" s="25"/>
       <c r="E62" s="13"/>
       <c r="F62" s="3" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="B63" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Elbląg</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="E63" s="13"/>
       <c r="F63" s="3" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="B64" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Preußen</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="D64" s="25"/>
       <c r="E64" s="13"/>
       <c r="F64" s="3" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>1291</v>
+        <v>1299</v>
       </c>
       <c r="B65" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bad Baden</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1292</v>
+        <v>1300</v>
       </c>
       <c r="D65" s="25"/>
       <c r="E65" s="13"/>
       <c r="F65" s="3" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>1294</v>
+        <v>1302</v>
       </c>
       <c r="B66" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bad Schinznach</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1295</v>
+        <v>1303</v>
       </c>
       <c r="D66" s="25"/>
       <c r="E66" s="13"/>
       <c r="F66" s="3" t="s">
-        <v>1293</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>1296</v>
+        <v>1304</v>
       </c>
       <c r="B67" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Gyrenbad</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="D67" s="25"/>
       <c r="E67" s="13"/>
@@ -15128,48 +15219,48 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>1298</v>
+        <v>1306</v>
       </c>
       <c r="B68" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wängibad</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="D68" s="25"/>
       <c r="E68" s="13"/>
       <c r="F68" s="8" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>1301</v>
+        <v>1309</v>
       </c>
       <c r="B69" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Aeugst</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
       <c r="D69" s="25"/>
       <c r="E69" s="13"/>
       <c r="F69" s="3" t="s">
-        <v>1231</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>1303</v>
+        <v>1311</v>
       </c>
       <c r="B70" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bassersdorf</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="D70" s="25"/>
       <c r="E70" s="13"/>
@@ -15177,14 +15268,14 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>1305</v>
+        <v>1313</v>
       </c>
       <c r="B71" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Hauptwil</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1306</v>
+        <v>1314</v>
       </c>
       <c r="D71" s="25"/>
       <c r="E71" s="13"/>
@@ -15192,14 +15283,14 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>1307</v>
+        <v>1315</v>
       </c>
       <c r="B72" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Schaffhausen</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1308</v>
+        <v>1316</v>
       </c>
       <c r="D72" s="25"/>
       <c r="E72" s="13"/>
@@ -15207,65 +15298,65 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>1309</v>
+        <v>1317</v>
       </c>
       <c r="B73" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wädenswil</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="D73" s="25"/>
       <c r="E73" s="13"/>
       <c r="F73" s="3" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="B74" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Freie Ämter</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1313</v>
+        <v>1321</v>
       </c>
       <c r="D74" s="25"/>
       <c r="E74" s="13"/>
       <c r="F74" s="3" t="s">
-        <v>1314</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="B75" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Grüningen</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1316</v>
+        <v>1324</v>
       </c>
       <c r="D75" s="25"/>
       <c r="E75" s="13"/>
       <c r="F75" s="3" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>1317</v>
+        <v>1325</v>
       </c>
       <c r="B76" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kefikon</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1318</v>
+        <v>1326</v>
       </c>
       <c r="D76" s="25"/>
       <c r="E76" s="13"/>
@@ -15273,14 +15364,14 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>1319</v>
+        <v>1327</v>
       </c>
       <c r="B77" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Maienfeld</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1320</v>
+        <v>1328</v>
       </c>
       <c r="D77" s="25"/>
       <c r="E77" s="13"/>
@@ -15288,14 +15379,14 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>1321</v>
+        <v>1329</v>
       </c>
       <c r="B78" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Greifensee (Schloss)</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1322</v>
+        <v>1330</v>
       </c>
       <c r="D78" s="25"/>
       <c r="E78" s="13"/>
@@ -15303,31 +15394,31 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="B79" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Lindenhof (Zürich)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="D79" s="25"/>
       <c r="E79" s="13"/>
       <c r="F79" s="3" t="s">
-        <v>1325</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>1326</v>
+        <v>1334</v>
       </c>
       <c r="B80" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Galg-Brunnen (Zürich)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1327</v>
+        <v>1335</v>
       </c>
       <c r="D80" s="25"/>
       <c r="E80" s="13"/>
@@ -15335,14 +15426,14 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>1328</v>
+        <v>1336</v>
       </c>
       <c r="B81" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Altes Kornhaus (Zürich)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1329</v>
+        <v>1337</v>
       </c>
       <c r="D81" s="25"/>
       <c r="E81" s="13"/>
@@ -15350,14 +15441,14 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>1330</v>
+        <v>1338</v>
       </c>
       <c r="B82" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Sparrenberg (Zürich)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1331</v>
+        <v>1339</v>
       </c>
       <c r="D82" s="25"/>
       <c r="E82" s="13"/>
@@ -15365,14 +15456,14 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>1332</v>
+        <v>1340</v>
       </c>
       <c r="B83" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Thurgau</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1333</v>
+        <v>1341</v>
       </c>
       <c r="D83" s="25"/>
       <c r="E83" s="13"/>
@@ -15380,14 +15471,14 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>1334</v>
+        <v>1342</v>
       </c>
       <c r="B84" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Niederlande</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1335</v>
+        <v>1343</v>
       </c>
       <c r="D84" s="25"/>
       <c r="E84" s="13"/>
@@ -15395,31 +15486,31 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>1336</v>
+        <v>1344</v>
       </c>
       <c r="B85" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Holland</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="D85" s="25"/>
       <c r="E85" s="13"/>
       <c r="F85" s="3" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
       <c r="B86" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wigoltingen</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
       <c r="D86" s="25"/>
       <c r="E86" s="13"/>
@@ -15427,31 +15518,31 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>1341</v>
+        <v>1349</v>
       </c>
       <c r="B87" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kastalia</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1342</v>
+        <v>1350</v>
       </c>
       <c r="D87" s="25"/>
       <c r="E87" s="13"/>
       <c r="F87" s="3" t="s">
-        <v>1343</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>1344</v>
+        <v>1352</v>
       </c>
       <c r="B88" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Legerberg</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="D88" s="25"/>
       <c r="E88" s="13"/>
@@ -15459,48 +15550,48 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="B89" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Texel</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
       <c r="D89" s="25"/>
       <c r="E89" s="13"/>
       <c r="F89" s="3" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>1349</v>
+        <v>1357</v>
       </c>
       <c r="B90" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Vlie</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1350</v>
+        <v>1358</v>
       </c>
       <c r="D90" s="25"/>
       <c r="E90" s="13"/>
       <c r="F90" s="3" t="s">
-        <v>1351</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>1352</v>
+        <v>1360</v>
       </c>
       <c r="B91" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Indien</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1353</v>
+        <v>1361</v>
       </c>
       <c r="D91" s="25"/>
       <c r="E91" s="13"/>
@@ -15508,14 +15599,14 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>1354</v>
+        <v>1362</v>
       </c>
       <c r="B92" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wien</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>1355</v>
+        <v>1363</v>
       </c>
       <c r="D92" s="25"/>
       <c r="E92" s="13"/>
@@ -15523,14 +15614,14 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>1356</v>
+        <v>1364</v>
       </c>
       <c r="B93" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Deutschland</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1357</v>
+        <v>1365</v>
       </c>
       <c r="D93" s="25"/>
       <c r="E93" s="13"/>
@@ -15538,109 +15629,117 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>1358</v>
+        <v>1366</v>
       </c>
       <c r="B94" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Ölberg</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1359</v>
+        <v>1367</v>
       </c>
       <c r="D94" s="25"/>
       <c r="E94" s="7" t="s">
-        <v>1157</v>
+        <v>1166</v>
       </c>
       <c r="F94" s="3"/>
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>1360</v>
+        <v>1368</v>
       </c>
       <c r="B95" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Dietikon</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1361</v>
+        <v>1369</v>
       </c>
       <c r="D95" s="25"/>
       <c r="E95" s="7" t="s">
-        <v>1362</v>
+        <v>1370</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1363</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>1364</v>
+        <v>1372</v>
       </c>
       <c r="B96" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Winterthur</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1365</v>
+        <v>1373</v>
       </c>
       <c r="D96" s="25"/>
       <c r="E96" s="7" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F96" s="3"/>
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>1366</v>
+        <v>1374</v>
       </c>
       <c r="B97" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Pfalz</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1367</v>
+        <v>1375</v>
       </c>
       <c r="D97" s="25"/>
       <c r="E97" s="7" t="s">
-        <v>1168</v>
+        <v>1177</v>
       </c>
       <c r="F97" s="3"/>
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>1368</v>
+        <v>1376</v>
       </c>
       <c r="B98" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Edenkoben</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1369</v>
+        <v>1377</v>
       </c>
       <c r="D98" s="25"/>
       <c r="E98" s="7" t="s">
-        <v>1119</v>
+        <v>1128</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>1370</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>1371</v>
+        <v>1379</v>
       </c>
       <c r="B99" s="24" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="C99" s="3"/>
-      <c r="D99" s="25"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="3"/>
+        <v>Wüste Juda</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>1382</v>
+      </c>
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>1372</v>
+        <v>1383</v>
       </c>
       <c r="B100" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15653,7 +15752,7 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>1373</v>
+        <v>1384</v>
       </c>
       <c r="B101" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15666,7 +15765,7 @@
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>1374</v>
+        <v>1385</v>
       </c>
       <c r="B102" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15679,7 +15778,7 @@
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="3" t="s">
-        <v>1375</v>
+        <v>1386</v>
       </c>
       <c r="B103" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15692,7 +15791,7 @@
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>1376</v>
+        <v>1387</v>
       </c>
       <c r="B104" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15705,7 +15804,7 @@
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="3" t="s">
-        <v>1377</v>
+        <v>1388</v>
       </c>
       <c r="B105" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15718,7 +15817,7 @@
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>1378</v>
+        <v>1389</v>
       </c>
       <c r="B106" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15731,7 +15830,7 @@
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="3" t="s">
-        <v>1379</v>
+        <v>1390</v>
       </c>
       <c r="B107" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15744,7 +15843,7 @@
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>1380</v>
+        <v>1391</v>
       </c>
       <c r="B108" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15757,7 +15856,7 @@
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="3" t="s">
-        <v>1381</v>
+        <v>1392</v>
       </c>
       <c r="B109" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15770,7 +15869,7 @@
     </row>
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>1382</v>
+        <v>1393</v>
       </c>
       <c r="B110" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15783,7 +15882,7 @@
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="3" t="s">
-        <v>1383</v>
+        <v>1394</v>
       </c>
       <c r="B111" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15796,7 +15895,7 @@
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>1384</v>
+        <v>1395</v>
       </c>
       <c r="B112" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15809,7 +15908,7 @@
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="3" t="s">
-        <v>1385</v>
+        <v>1396</v>
       </c>
       <c r="B113" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15822,7 +15921,7 @@
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>1386</v>
+        <v>1397</v>
       </c>
       <c r="B114" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15835,7 +15934,7 @@
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="3" t="s">
-        <v>1387</v>
+        <v>1398</v>
       </c>
       <c r="B115" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15848,7 +15947,7 @@
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>1388</v>
+        <v>1399</v>
       </c>
       <c r="B116" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15861,7 +15960,7 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>1389</v>
+        <v>1400</v>
       </c>
       <c r="B117" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15874,7 +15973,7 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>1390</v>
+        <v>1401</v>
       </c>
       <c r="B118" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15887,7 +15986,7 @@
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>1391</v>
+        <v>1402</v>
       </c>
       <c r="B119" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15900,7 +15999,7 @@
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>1392</v>
+        <v>1403</v>
       </c>
       <c r="B120" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15913,7 +16012,7 @@
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>1393</v>
+        <v>1404</v>
       </c>
       <c r="B121" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15926,7 +16025,7 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>1394</v>
+        <v>1405</v>
       </c>
       <c r="B122" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15939,7 +16038,7 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>1395</v>
+        <v>1406</v>
       </c>
       <c r="B123" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15952,7 +16051,7 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>1396</v>
+        <v>1407</v>
       </c>
       <c r="B124" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15965,7 +16064,7 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>1397</v>
+        <v>1408</v>
       </c>
       <c r="B125" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15978,7 +16077,7 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>1398</v>
+        <v>1409</v>
       </c>
       <c r="B126" s="24" t="str">
         <f t="shared" si="1"/>
@@ -15991,7 +16090,7 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>1399</v>
+        <v>1410</v>
       </c>
       <c r="B127" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16004,7 +16103,7 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>1400</v>
+        <v>1411</v>
       </c>
       <c r="B128" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16017,7 +16116,7 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>1401</v>
+        <v>1412</v>
       </c>
       <c r="B129" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16030,7 +16129,7 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>1402</v>
+        <v>1413</v>
       </c>
       <c r="B130" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16043,7 +16142,7 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="3" t="s">
-        <v>1403</v>
+        <v>1414</v>
       </c>
       <c r="B131" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16056,7 +16155,7 @@
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>1404</v>
+        <v>1415</v>
       </c>
       <c r="B132" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16104,25 +16203,25 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1405</v>
+        <v>1416</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1406</v>
+        <v>1417</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1407</v>
+        <v>1418</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1408</v>
+        <v>1419</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1409</v>
+        <v>1420</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1410</v>
+        <v>1421</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
@@ -16133,101 +16232,109 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1411</v>
+        <v>1422</v>
       </c>
       <c r="B2" s="26" t="str">
         <f t="shared" ref="B2:B40" si="1">CONCATENATE(C2)</f>
         <v>Teutsche Gedichte</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1412</v>
+        <v>1423</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1413</v>
+        <v>1424</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1414</v>
+        <v>1425</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1415</v>
+        <v>1426</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>1416</v>
+        <v>1427</v>
       </c>
       <c r="I2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1417</v>
+        <v>1428</v>
       </c>
       <c r="B3" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Die Krafft der Gottseligkeit</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1418</v>
+        <v>1429</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1419</v>
+        <v>1430</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1420</v>
+        <v>1431</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1421</v>
+        <v>1432</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1422</v>
+        <v>1433</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>1423</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1424</v>
+        <v>1435</v>
       </c>
       <c r="B4" s="26" t="str">
         <f t="shared" si="1"/>
-        <v>Buch von Festen</v>
+        <v>Archetypi homiliarum in quatuor evangelia dn. nostri Iesu Christi</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1425</v>
+        <v>1436</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>692</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="9"/>
+        <v>1437</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1438</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1439</v>
+      </c>
       <c r="H4" s="13"/>
-      <c r="I4" s="9"/>
+      <c r="I4" s="10" t="s">
+        <v>1440</v>
+      </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1426</v>
+        <v>1441</v>
       </c>
       <c r="B5" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Der Psalter dess Königlichen Propheten Dauids/ Jn deutsche reymen verstendiglich vnd deutlich gebracht/ mit vorgehender anzeigung der reymen weise/ auch eines jeden Psalmes Jnhalt</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1427</v>
+        <v>1442</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1428</v>
+        <v>1443</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1429</v>
+        <v>1444</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1430</v>
+        <v>1445</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="13"/>
@@ -16235,73 +16342,73 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1431</v>
+        <v>1446</v>
       </c>
       <c r="B6" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Hundert christliche Fäst-Predigen</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1432</v>
+        <v>1447</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1433</v>
+        <v>1448</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1434</v>
+        <v>1449</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1435</v>
+        <v>1450</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>1436</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1437</v>
+        <v>1452</v>
       </c>
       <c r="B7" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Spiegel der Unermesslichen Gnad Gottes gegen den rewenden bussfertigen Sünderen/ Jn XLV. Predigen vber das XV. capitel Lucae/ vom verlohrnen Schaaf/ Pfenning/ vnd Sohn verfasset</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1438</v>
+        <v>1453</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1439</v>
+        <v>1454</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1440</v>
+        <v>1455</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1122</v>
+        <v>1131</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1441</v>
+        <v>1456</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>1442</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1443</v>
+        <v>1458</v>
       </c>
       <c r="B8" s="26" t="str">
         <f t="shared" si="1"/>
         <v>verteütschte Rueh- oder Fridens-uebung</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1444</v>
+        <v>1459</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1445</v>
+        <v>1460</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="25"/>
@@ -16311,98 +16418,98 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1446</v>
+        <v>1461</v>
       </c>
       <c r="B9" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Nähefelser-Fahrt: in zehen erbaulichen Jahrzeit-Predigen zu schuldigem Danck dem Höhesten für den im Jahr 1388 gemeinen Landleuthen dess lobl. Eydgnössischen Bundorths Glarus wider ihre Feind bey und umb Nähefels verliehenen Wundersieg </v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1447</v>
+        <v>1462</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1448</v>
+        <v>1463</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1449</v>
+        <v>1464</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1450</v>
+        <v>1465</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="10" t="s">
-        <v>1451</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1452</v>
+        <v>1467</v>
       </c>
       <c r="B10" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Die vier Haubtpuncten der christlichen seligmachenden Religion: auf alle Sontag des gantzen Jahrs ordenlich abgetheilt, grundtlich nach der heiligen Schrifft erklärt und zur Erbawung gerichtet </v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1453</v>
+        <v>1468</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1454</v>
+        <v>1469</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1455</v>
+        <v>1470</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1456</v>
+        <v>1471</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>1457</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1458</v>
+        <v>1473</v>
       </c>
       <c r="B11" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Architectura von Vestungen</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1459</v>
+        <v>1474</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1460</v>
+        <v>1475</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1420</v>
+        <v>1431</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1461</v>
+        <v>1476</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="8" t="s">
-        <v>1462</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1463</v>
+        <v>1478</v>
       </c>
       <c r="B12" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Buech der Freunden Stammen</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1464</v>
+        <v>1479</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="9"/>
@@ -16413,42 +16520,42 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1465</v>
+        <v>1480</v>
       </c>
       <c r="B13" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Christen-Spiegel, das ist, Bedenkliche Erinnerungen über die Beruoffspflichten aller Ständen </v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1466</v>
+        <v>1481</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1467</v>
+        <v>1482</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1468</v>
+        <v>1483</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>1469</v>
+        <v>1484</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>1470</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1471</v>
+        <v>1486</v>
       </c>
       <c r="B14" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Viergeticht</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1472</v>
+        <v>1487</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="9"/>
@@ -16459,14 +16566,14 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1473</v>
+        <v>1488</v>
       </c>
       <c r="B15" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Regentenspiegel</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1474</v>
+        <v>1489</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="9"/>
@@ -16477,18 +16584,18 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1475</v>
+        <v>1490</v>
       </c>
       <c r="B16" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Türckischer Jammerspiegel</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1476</v>
+        <v>1491</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="3" t="s">
-        <v>1477</v>
+        <v>1492</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="9"/>
@@ -16497,17 +16604,17 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1478</v>
+        <v>1493</v>
       </c>
       <c r="B17" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Leitungs-faden</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1479</v>
+        <v>1494</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="25"/>
@@ -16517,17 +16624,17 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1480</v>
+        <v>1495</v>
       </c>
       <c r="B18" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Buch von der Seelen-angſt Chriſti</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1481</v>
+        <v>1496</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1482</v>
+        <v>1497</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="25"/>
@@ -16537,17 +16644,17 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1483</v>
+        <v>1498</v>
       </c>
       <c r="B19" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Verſuchungs-gabe</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1484</v>
+        <v>1499</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1485</v>
+        <v>1500</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="25"/>
@@ -16557,14 +16664,14 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1486</v>
+        <v>1501</v>
       </c>
       <c r="B20" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kriegsbüchlin</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1487</v>
+        <v>1502</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="9"/>
@@ -16575,14 +16682,14 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1488</v>
+        <v>1503</v>
       </c>
       <c r="B21" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Buch der Psalmen</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1489</v>
+        <v>1504</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="9"/>
@@ -16593,117 +16700,117 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1490</v>
+        <v>1505</v>
       </c>
       <c r="B22" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Sterbensspiegel/ das ist sonnenklare Vorstellung menschlicher Nichtigkeit durch alle Staend und Geschlechter</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1491</v>
+        <v>1506</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1492</v>
+        <v>1507</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1440</v>
+        <v>1455</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1493</v>
+        <v>1508</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>1494</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1495</v>
+        <v>1510</v>
       </c>
       <c r="B23" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Warhaffte/ vnd in Gottes Wort wol gegründte Widerlegung Des newlich im Truck außgegangnen ohn-Catholischen Gesprächs von Religion oder Glaubens sachen/ geneñt der Augenspiegel</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1496</v>
+        <v>1511</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1497</v>
+        <v>1512</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1498</v>
+        <v>1513</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>1118</v>
+        <v>1127</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1493</v>
+        <v>1508</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>1499</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1500</v>
+        <v>1515</v>
       </c>
       <c r="B24" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Augspiegels Wahrer Religion Erster Theil</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1501</v>
+        <v>1516</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>1502</v>
+        <v>1517</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1503</v>
+        <v>1518</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1504</v>
+        <v>1519</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1505</v>
+        <v>1520</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>1506</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1507</v>
+        <v>1522</v>
       </c>
       <c r="B25" s="26" t="str">
         <f t="shared" si="1"/>
         <v>De kracht der Godsaligheyt</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1508</v>
+        <v>1523</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>1509</v>
+        <v>1524</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1510</v>
+        <v>1525</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>1511</v>
+        <v>1526</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>1512</v>
+        <v>1527</v>
       </c>
       <c r="H25" s="13"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1513</v>
+        <v>1528</v>
       </c>
       <c r="B26" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16719,7 +16826,7 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1514</v>
+        <v>1529</v>
       </c>
       <c r="B27" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16735,7 +16842,7 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1515</v>
+        <v>1530</v>
       </c>
       <c r="B28" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16751,7 +16858,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1516</v>
+        <v>1531</v>
       </c>
       <c r="B29" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16767,7 +16874,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1517</v>
+        <v>1532</v>
       </c>
       <c r="B30" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16783,7 +16890,7 @@
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1518</v>
+        <v>1533</v>
       </c>
       <c r="B31" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16799,7 +16906,7 @@
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1519</v>
+        <v>1534</v>
       </c>
       <c r="B32" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16815,7 +16922,7 @@
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1520</v>
+        <v>1535</v>
       </c>
       <c r="B33" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16831,7 +16938,7 @@
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1521</v>
+        <v>1536</v>
       </c>
       <c r="B34" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16847,7 +16954,7 @@
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1522</v>
+        <v>1537</v>
       </c>
       <c r="B35" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16863,7 +16970,7 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1523</v>
+        <v>1538</v>
       </c>
       <c r="B36" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16879,7 +16986,7 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1524</v>
+        <v>1539</v>
       </c>
       <c r="B37" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16895,7 +17002,7 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1525</v>
+        <v>1540</v>
       </c>
       <c r="B38" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16911,7 +17018,7 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1526</v>
+        <v>1541</v>
       </c>
       <c r="B39" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16927,7 +17034,7 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1527</v>
+        <v>1542</v>
       </c>
       <c r="B40" s="26" t="str">
         <f t="shared" si="1"/>
@@ -16950,19 +17057,20 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="I3"/>
-    <hyperlink r:id="rId2" ref="I6"/>
-    <hyperlink r:id="rId3" ref="I7"/>
-    <hyperlink r:id="rId4" ref="I9"/>
-    <hyperlink r:id="rId5" ref="I10"/>
-    <hyperlink r:id="rId6" ref="I11"/>
-    <hyperlink r:id="rId7" ref="I13"/>
-    <hyperlink r:id="rId8" ref="I22"/>
-    <hyperlink r:id="rId9" ref="I23"/>
-    <hyperlink r:id="rId10" ref="I24"/>
+    <hyperlink r:id="rId2" ref="I4"/>
+    <hyperlink r:id="rId3" ref="I6"/>
+    <hyperlink r:id="rId4" ref="I7"/>
+    <hyperlink r:id="rId5" ref="I9"/>
+    <hyperlink r:id="rId6" ref="I10"/>
+    <hyperlink r:id="rId7" ref="I11"/>
+    <hyperlink r:id="rId8" ref="I13"/>
+    <hyperlink r:id="rId9" ref="I22"/>
+    <hyperlink r:id="rId10" ref="I23"/>
+    <hyperlink r:id="rId11" ref="I24"/>
   </hyperlinks>
-  <drawing r:id="rId11"/>
+  <drawing r:id="rId12"/>
   <tableParts count="1">
-    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId14"/>
   </tableParts>
 </worksheet>
 </file>
@@ -16983,19 +17091,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1528</v>
+        <v>1543</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1115</v>
+        <v>1124</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1529</v>
+        <v>1544</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -17003,69 +17111,69 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1530</v>
+        <v>1545</v>
       </c>
       <c r="B2" s="26" t="str">
         <f t="shared" ref="B2:B34" si="1">CONCATENATE(C2)</f>
         <v>Rat Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1531</v>
+        <v>1546</v>
       </c>
       <c r="D2" s="25"/>
       <c r="E2" s="27" t="s">
-        <v>1532</v>
+        <v>1547</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1533</v>
+        <v>1548</v>
       </c>
       <c r="B3" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Fruchtbringende Gesellschaft</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1534</v>
+        <v>1549</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1535</v>
+        <v>1550</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>1536</v>
+        <v>1551</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1537</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1538</v>
+        <v>1553</v>
       </c>
       <c r="B4" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Deutschgesinnte Genossenschaft (Lilien-Zunft)</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1539</v>
+        <v>1554</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1540</v>
+        <v>1555</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1541</v>
+        <v>1556</v>
       </c>
       <c r="B5" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Parthenicum</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1542</v>
+        <v>1557</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="13"/>
@@ -17073,107 +17181,107 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1543</v>
+        <v>1558</v>
       </c>
       <c r="B6" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Carolinum Zürich</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1544</v>
+        <v>1559</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1545</v>
+        <v>1560</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="3" t="s">
-        <v>1546</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1547</v>
+        <v>1562</v>
       </c>
       <c r="B7" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Sanhedrin</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1548</v>
+        <v>1563</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="13"/>
       <c r="F7" s="3" t="s">
-        <v>1549</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1550</v>
+        <v>1565</v>
       </c>
       <c r="B8" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Bürgerbibliothek Zürich</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1551</v>
+        <v>1566</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1552</v>
+        <v>1567</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="3" t="s">
-        <v>1553</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1554</v>
+        <v>1569</v>
       </c>
       <c r="B9" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Grossmünster</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1555</v>
+        <v>1570</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1556</v>
+        <v>1571</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1557</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1558</v>
+        <v>1573</v>
       </c>
       <c r="B10" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Fraumünster Zürich</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1559</v>
+        <v>1574</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1560</v>
+        <v>1575</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="3" t="s">
-        <v>1561</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1562</v>
+        <v>1577</v>
       </c>
       <c r="B11" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Hohe Schule Marburg</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1563</v>
+        <v>1578</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="13"/>
@@ -17181,24 +17289,24 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1564</v>
+        <v>1579</v>
       </c>
       <c r="B12" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kartäuser</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1565</v>
+        <v>1580</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1566</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1567</v>
+        <v>1582</v>
       </c>
       <c r="B13" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17211,7 +17319,7 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1568</v>
+        <v>1583</v>
       </c>
       <c r="B14" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17224,7 +17332,7 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1569</v>
+        <v>1584</v>
       </c>
       <c r="B15" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17237,7 +17345,7 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1570</v>
+        <v>1585</v>
       </c>
       <c r="B16" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17250,7 +17358,7 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1571</v>
+        <v>1586</v>
       </c>
       <c r="B17" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17263,7 +17371,7 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1572</v>
+        <v>1587</v>
       </c>
       <c r="B18" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17276,7 +17384,7 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1573</v>
+        <v>1588</v>
       </c>
       <c r="B19" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17289,7 +17397,7 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1574</v>
+        <v>1589</v>
       </c>
       <c r="B20" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17302,7 +17410,7 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1575</v>
+        <v>1590</v>
       </c>
       <c r="B21" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17315,7 +17423,7 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1576</v>
+        <v>1591</v>
       </c>
       <c r="B22" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17328,7 +17436,7 @@
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1577</v>
+        <v>1592</v>
       </c>
       <c r="B23" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17341,7 +17449,7 @@
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1578</v>
+        <v>1593</v>
       </c>
       <c r="B24" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17354,7 +17462,7 @@
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1579</v>
+        <v>1594</v>
       </c>
       <c r="B25" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17367,7 +17475,7 @@
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1580</v>
+        <v>1595</v>
       </c>
       <c r="B26" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17380,7 +17488,7 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1581</v>
+        <v>1596</v>
       </c>
       <c r="B27" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17393,7 +17501,7 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1582</v>
+        <v>1597</v>
       </c>
       <c r="B28" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17406,7 +17514,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1583</v>
+        <v>1598</v>
       </c>
       <c r="B29" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17419,7 +17527,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1584</v>
+        <v>1599</v>
       </c>
       <c r="B30" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17432,7 +17540,7 @@
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1585</v>
+        <v>1600</v>
       </c>
       <c r="B31" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17445,7 +17553,7 @@
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1586</v>
+        <v>1601</v>
       </c>
       <c r="B32" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17458,7 +17566,7 @@
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1587</v>
+        <v>1602</v>
       </c>
       <c r="B33" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17471,7 +17579,7 @@
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1588</v>
+        <v>1603</v>
       </c>
       <c r="B34" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17512,19 +17620,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1589</v>
+        <v>1604</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1590</v>
+        <v>1605</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1591</v>
+        <v>1606</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1592</v>
+        <v>1607</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -17532,26 +17640,26 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1593</v>
+        <v>1608</v>
       </c>
       <c r="B2" s="23" t="str">
         <f t="shared" ref="B2:B8" si="1">CONCATENATE(C2)</f>
         <v>Runs</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1594</v>
+        <v>1609</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1595</v>
+        <v>1610</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>1596</v>
+        <v>1611</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1597</v>
+        <v>1612</v>
       </c>
       <c r="B3" s="23" t="str">
         <f t="shared" si="1"/>
@@ -17564,7 +17672,7 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1598</v>
+        <v>1613</v>
       </c>
       <c r="B4" s="23" t="str">
         <f t="shared" si="1"/>
@@ -17577,7 +17685,7 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1599</v>
+        <v>1614</v>
       </c>
       <c r="B5" s="23" t="str">
         <f t="shared" si="1"/>
@@ -17590,7 +17698,7 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1600</v>
+        <v>1615</v>
       </c>
       <c r="B6" s="23" t="str">
         <f t="shared" si="1"/>
@@ -17603,7 +17711,7 @@
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1601</v>
+        <v>1616</v>
       </c>
       <c r="B7" s="23" t="str">
         <f t="shared" si="1"/>
@@ -17616,7 +17724,7 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1602</v>
+        <v>1617</v>
       </c>
       <c r="B8" s="23" t="str">
         <f t="shared" si="1"/>

--- a/gsheet/xlsx/entities.xlsx
+++ b/gsheet/xlsx/entities.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2133" uniqueCount="1673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2199" uniqueCount="1719">
   <si>
     <t>Person-ID</t>
   </si>
@@ -974,7 +974,7 @@
     <t>person_056</t>
   </si>
   <si>
-    <t>Aron</t>
+    <t>Aaron</t>
   </si>
   <si>
     <t>118500031</t>
@@ -2698,28 +2698,46 @@
     <t>Anhorn</t>
   </si>
   <si>
-    <t>Verfasser eines "Leitungs-fadens"</t>
+    <t>Bartholomäus</t>
+  </si>
+  <si>
+    <t>121076717</t>
+  </si>
+  <si>
+    <t>Pfarrer, Theologe</t>
+  </si>
+  <si>
+    <t>https://hls-dhs-dss.ch/de/articles/010505</t>
   </si>
   <si>
     <t>person_211</t>
   </si>
   <si>
-    <t>Wilden</t>
-  </si>
-  <si>
-    <t>Verfasser des Buchs von der Seelen-Angst Christi</t>
+    <t>Wild</t>
+  </si>
+  <si>
+    <t>1089323042</t>
+  </si>
+  <si>
+    <t>Glarner Pfarrer und Dekan</t>
+  </si>
+  <si>
+    <t>https://hls-dhs-dss.ch/de/articles/010916</t>
   </si>
   <si>
     <t>person_212</t>
   </si>
   <si>
-    <t>Groben</t>
-  </si>
-  <si>
-    <t>Jacob (evtl. Johannes)</t>
-  </si>
-  <si>
-    <t>Verfasser des Buches 'Verſuchungs-gabe'; wohl Johannes Grob, cf. https://de.wikipedia.org/wiki/Johannes_Grob</t>
+    <t>10014568X</t>
+  </si>
+  <si>
+    <t>Dichter, Soldat</t>
+  </si>
+  <si>
+    <t>https://hls-dhs-dss.ch/de/articles/011842</t>
+  </si>
+  <si>
+    <t>In Druck D ist als Vorname Jakob angegeben</t>
   </si>
   <si>
     <t>person_213</t>
@@ -2731,10 +2749,26 @@
     <t>Verfasser des "Bernerischen Apothecker-Taxes"</t>
   </si>
   <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">Noch unklar. Evtl. </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://www.hfls.ch/humo-gen/info_family/1/F107269?main_person=I308255</t>
+    </r>
+  </si>
+  <si>
     <t>person_214</t>
   </si>
   <si>
-    <t>Erfinder</t>
+    <t>108959500X</t>
+  </si>
+  <si>
+    <t>Goldschmied, Büchsenmacher</t>
   </si>
   <si>
     <t>person_215</t>
@@ -2785,21 +2819,36 @@
     <t>person_218</t>
   </si>
   <si>
-    <t>Eglin</t>
-  </si>
-  <si>
-    <t>Hauptmann, Landvogt zu Greifensee</t>
+    <t>Egli</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>1627/29</t>
+  </si>
+  <si>
+    <t>Landvogt von Greifensee</t>
+  </si>
+  <si>
+    <t>https://personae.ssrq-sds-fds.ch/?query=per015033&amp;query-type=perid</t>
   </si>
   <si>
     <t>person_219</t>
   </si>
   <si>
-    <t>Wildhans von Breitenlandenberg</t>
+    <t>von Breitenlandenberg</t>
+  </si>
+  <si>
+    <t>Wildhans</t>
   </si>
   <si>
     <t>Verteidiger von Greifensee und Opfer der «Blutnacht von Greifensee»</t>
   </si>
   <si>
+    <t>https://hls-dhs-dss.ch/de/articles/046021/2008-11-11/</t>
+  </si>
+  <si>
     <t>person_220</t>
   </si>
   <si>
@@ -3190,7 +3239,7 @@
     <t>1047814412</t>
   </si>
   <si>
-    <t>König von Argos</t>
+    <t>König von Argos, Vater der Danaiden</t>
   </si>
   <si>
     <t>person_263</t>
@@ -3606,12 +3655,42 @@
     <t>person_296</t>
   </si>
   <si>
+    <t>M. G. H. H. H. D. J. H. H.</t>
+  </si>
+  <si>
+    <t>Bisher nicht entschlüsselt</t>
+  </si>
+  <si>
     <t>person_297</t>
   </si>
   <si>
+    <t>Horaz</t>
+  </si>
+  <si>
+    <t>65 v. Chr.</t>
+  </si>
+  <si>
+    <t>8 v. Chr.</t>
+  </si>
+  <si>
+    <t>118553569</t>
+  </si>
+  <si>
     <t>person_298</t>
   </si>
   <si>
+    <t>Lavater</t>
+  </si>
+  <si>
+    <t>Hans Conrad</t>
+  </si>
+  <si>
+    <t>129810452</t>
+  </si>
+  <si>
+    <t>https://hls-dhs-dss.ch/de/articles/023963</t>
+  </si>
+  <si>
     <t>person_299</t>
   </si>
   <si>
@@ -4287,7 +4366,10 @@
     <t>place_077</t>
   </si>
   <si>
-    <t>Greifensee (Schloss)</t>
+    <t>Schloss Greifensee</t>
+  </si>
+  <si>
+    <t>Bauwerk</t>
   </si>
   <si>
     <t>place_078</t>
@@ -4443,7 +4525,13 @@
     <t>place_099</t>
   </si>
   <si>
+    <t>Greifensee</t>
+  </si>
+  <si>
     <t>place_100</t>
+  </si>
+  <si>
+    <t>Lichtensteig</t>
   </si>
   <si>
     <t>place_101</t>
@@ -4807,31 +4895,88 @@
     <t>work_016</t>
   </si>
   <si>
-    <t>Leitungs-faden</t>
+    <t>Theatrum concionum sacr. topicum</t>
+  </si>
+  <si>
+    <t>Anhorn, Bartholomäus</t>
+  </si>
+  <si>
+    <t>1670</t>
+  </si>
+  <si>
+    <t>Johann Jakob Birr</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://doi.org/10.3931/e-rara-80050</t>
+    </r>
   </si>
   <si>
     <t>work_017</t>
   </si>
   <si>
-    <t>Buch von der Seelen-angſt Chriſti</t>
-  </si>
-  <si>
-    <t>Wilden, Abraham</t>
+    <t>Seelen-Angst Christi</t>
+  </si>
+  <si>
+    <t>Wild, Abraham</t>
+  </si>
+  <si>
+    <t>Johann Wilhelm Simler</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3931/e-rara-9901</t>
   </si>
   <si>
     <t>work_018</t>
   </si>
   <si>
-    <t>Verſuchungs-gabe</t>
-  </si>
-  <si>
-    <t>Groben, Jacob</t>
+    <t>Dichterische Versuchgabe</t>
+  </si>
+  <si>
+    <t>Grob, Johannes</t>
+  </si>
+  <si>
+    <t>1678</t>
+  </si>
+  <si>
+    <t>Johann Brandmüller</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://doi.org/10.3931/e-rara-78709</t>
+    </r>
   </si>
   <si>
     <t>work_019</t>
   </si>
   <si>
-    <t>Kriegsbüchlin</t>
+    <t>Kriegs-Büchlein</t>
+  </si>
+  <si>
+    <t>Lavater, Hans Conrad</t>
+  </si>
+  <si>
+    <t>1644</t>
+  </si>
+  <si>
+    <t>Hans Conrad Lavater</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://doi.org/10.3931/e-rara-9832</t>
+    </r>
   </si>
   <si>
     <t>work_020</t>
@@ -4930,7 +5075,28 @@
     <t>work_025</t>
   </si>
   <si>
+    <t>Christlicher Wandersmann</t>
+  </si>
+  <si>
+    <t>Hottinger, Johann Heinrich</t>
+  </si>
+  <si>
+    <t>1666</t>
+  </si>
+  <si>
+    <t>Michael Schauffelberger</t>
+  </si>
+  <si>
+    <t>https://www.e-rara.ch/zuz/content/titleinfo/3198523</t>
+  </si>
+  <si>
     <t>work_026</t>
+  </si>
+  <si>
+    <t>"Bernerischer Apothecker-Tax"</t>
+  </si>
+  <si>
+    <t>Noch unklar</t>
   </si>
   <si>
     <t>work_027</t>
@@ -7560,7 +7726,7 @@
       </c>
       <c r="B56" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Aron,  (-)</v>
+        <v>Aaron,  (-)</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>308</v>
@@ -11572,107 +11738,137 @@
       </c>
       <c r="B205" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Anhorn,  (-)</v>
+        <v>Anhorn, Bartholomäus (1616-1700)</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>860</v>
       </c>
-      <c r="D205" s="3"/>
-      <c r="E205" s="18"/>
-      <c r="F205" s="19"/>
-      <c r="G205" s="9"/>
+      <c r="D205" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="E205" s="5">
+        <v>1616.0</v>
+      </c>
+      <c r="F205" s="5">
+        <v>1700.0</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>862</v>
+      </c>
       <c r="H205" s="3" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="I205" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J205" s="9"/>
+      <c r="J205" s="12" t="s">
+        <v>864</v>
+      </c>
       <c r="K205" s="9"/>
     </row>
     <row r="206" ht="22.5" customHeight="1">
       <c r="A206" s="3" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B206" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Wilden, Abraham (-)</v>
+        <v>Wild, Abraham (1628-1689)</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="E206" s="18"/>
-      <c r="F206" s="19"/>
-      <c r="G206" s="9"/>
+      <c r="E206" s="5">
+        <v>1628.0</v>
+      </c>
+      <c r="F206" s="5">
+        <v>1689.0</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>867</v>
+      </c>
       <c r="H206" s="3" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J206" s="9"/>
+      <c r="J206" s="12" t="s">
+        <v>869</v>
+      </c>
       <c r="K206" s="9"/>
     </row>
     <row r="207" ht="22.5" customHeight="1">
       <c r="A207" s="3" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="B207" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Groben, Jacob (evtl. Johannes) (-)</v>
+        <v>Grob, Johannes (1643-1697)</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>866</v>
+        <v>817</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="E207" s="18"/>
-      <c r="F207" s="19"/>
-      <c r="G207" s="9"/>
+        <v>125</v>
+      </c>
+      <c r="E207" s="5">
+        <v>1643.0</v>
+      </c>
+      <c r="F207" s="5">
+        <v>1697.0</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>871</v>
+      </c>
       <c r="H207" s="3" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J207" s="9"/>
-      <c r="K207" s="9"/>
+      <c r="J207" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="K207" s="3" t="s">
+        <v>874</v>
+      </c>
     </row>
     <row r="208" ht="22.5" customHeight="1">
       <c r="A208" s="3" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="B208" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ziegler,  (-)</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="18"/>
       <c r="F208" s="19"/>
       <c r="G208" s="9"/>
       <c r="H208" s="3" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="I208" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J208" s="9"/>
-      <c r="K208" s="9"/>
+      <c r="K208" s="10" t="s">
+        <v>878</v>
+      </c>
     </row>
     <row r="209" ht="22.5" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="B209" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Werder, Felix (-)</v>
+        <v>Werder, Felix (1591-1673)</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>209</v>
@@ -11680,11 +11876,17 @@
       <c r="D209" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E209" s="18"/>
-      <c r="F209" s="19"/>
-      <c r="G209" s="9"/>
+      <c r="E209" s="5">
+        <v>1591.0</v>
+      </c>
+      <c r="F209" s="5">
+        <v>1673.0</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>880</v>
+      </c>
       <c r="H209" s="3" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="I209" s="7" t="s">
         <v>16</v>
@@ -11694,21 +11896,21 @@
     </row>
     <row r="210" ht="22.5" customHeight="1">
       <c r="A210" s="3" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="B210" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Oeri,  (-)</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="18"/>
       <c r="F210" s="19"/>
       <c r="G210" s="9"/>
       <c r="H210" s="3" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="I210" s="7" t="s">
         <v>16</v>
@@ -11718,49 +11920,49 @@
     </row>
     <row r="211" ht="22.5" customHeight="1">
       <c r="A211" s="3" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="B211" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Keller vom Steinbock‏, Anna Kleophea (‎1609-1673)</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="F211" s="5">
         <v>1673.0</v>
       </c>
       <c r="G211" s="9"/>
       <c r="H211" s="3" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="I211" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J211" s="8" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="K211" s="9"/>
     </row>
     <row r="212" ht="22.5" customHeight="1">
       <c r="A212" s="3" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="B212" s="4" t="str">
         <f t="shared" si="1"/>
         <v>von Sultz, Johann Ludwig II. (1626-1687)</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="E212" s="5">
         <v>1626.0</v>
@@ -11769,79 +11971,93 @@
         <v>1687.0</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="I212" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J212" s="8" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="K212" s="9"/>
     </row>
     <row r="213" ht="22.5" customHeight="1">
       <c r="A213" s="3" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="B213" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Eglin,  (-)</v>
+        <v>Egli, Samuel (1627/29-1666)</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>890</v>
-      </c>
-      <c r="D213" s="3"/>
-      <c r="E213" s="18"/>
-      <c r="F213" s="19"/>
+        <v>898</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="E213" s="17" t="s">
+        <v>900</v>
+      </c>
+      <c r="F213" s="5">
+        <v>1666.0</v>
+      </c>
       <c r="G213" s="9"/>
       <c r="H213" s="3" t="s">
-        <v>891</v>
+        <v>901</v>
       </c>
       <c r="I213" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J213" s="9"/>
+      <c r="J213" s="8" t="s">
+        <v>902</v>
+      </c>
       <c r="K213" s="9"/>
     </row>
     <row r="214" ht="22.5" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>892</v>
+        <v>903</v>
       </c>
       <c r="B214" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Wildhans von Breitenlandenberg,  (-1444)</v>
+        <v>von Breitenlandenberg, Wildhans (1410-1444)</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>893</v>
-      </c>
-      <c r="D214" s="3"/>
-      <c r="E214" s="18"/>
+        <v>904</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="E214" s="5">
+        <v>1410.0</v>
+      </c>
       <c r="F214" s="5">
         <v>1444.0</v>
       </c>
       <c r="G214" s="9"/>
       <c r="H214" s="3" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="I214" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J214" s="9"/>
+      <c r="J214" s="10" t="s">
+        <v>907</v>
+      </c>
       <c r="K214" s="9"/>
     </row>
     <row r="215" ht="22.5" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>895</v>
+        <v>908</v>
       </c>
       <c r="B215" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pfarrherr,  (-)</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>896</v>
+        <v>909</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="18"/>
@@ -11856,14 +12072,14 @@
     </row>
     <row r="216" ht="22.5" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>897</v>
+        <v>910</v>
       </c>
       <c r="B216" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid von Schwarzenhorn, Johann Rudolf (1590-1667)</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>898</v>
+        <v>911</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>767</v>
@@ -11875,29 +12091,29 @@
         <v>1667.0</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>899</v>
+        <v>912</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>900</v>
+        <v>913</v>
       </c>
       <c r="I216" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J216" s="8" t="s">
-        <v>901</v>
+        <v>914</v>
       </c>
       <c r="K216" s="9"/>
     </row>
     <row r="217" ht="22.5" customHeight="1">
       <c r="A217" s="3" t="s">
-        <v>902</v>
+        <v>915</v>
       </c>
       <c r="B217" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid, Felix (-1598)</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>89</v>
@@ -11908,26 +12124,26 @@
       </c>
       <c r="G217" s="9"/>
       <c r="H217" s="3" t="s">
-        <v>904</v>
+        <v>917</v>
       </c>
       <c r="I217" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J217" s="8" t="s">
-        <v>901</v>
+        <v>914</v>
       </c>
       <c r="K217" s="9"/>
     </row>
     <row r="218" ht="22.5" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>905</v>
+        <v>918</v>
       </c>
       <c r="B218" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hessen, Heinrich (-)</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>38</v>
@@ -11936,7 +12152,7 @@
       <c r="F218" s="19"/>
       <c r="G218" s="9"/>
       <c r="H218" s="3" t="s">
-        <v>907</v>
+        <v>920</v>
       </c>
       <c r="I218" s="7" t="s">
         <v>16</v>
@@ -11946,17 +12162,17 @@
     </row>
     <row r="219" ht="22.5" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>908</v>
+        <v>921</v>
       </c>
       <c r="B219" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulr., H. (-)</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>909</v>
+        <v>922</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>910</v>
+        <v>923</v>
       </c>
       <c r="E219" s="18"/>
       <c r="F219" s="19"/>
@@ -11972,7 +12188,7 @@
     </row>
     <row r="220" ht="22.5" customHeight="1">
       <c r="A220" s="3" t="s">
-        <v>911</v>
+        <v>924</v>
       </c>
       <c r="B220" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11982,13 +12198,13 @@
         <v>61</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>912</v>
+        <v>925</v>
       </c>
       <c r="E220" s="18"/>
       <c r="F220" s="19"/>
       <c r="G220" s="9"/>
       <c r="H220" s="3" t="s">
-        <v>913</v>
+        <v>926</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>16</v>
@@ -11998,7 +12214,7 @@
     </row>
     <row r="221" ht="22.5" customHeight="1">
       <c r="A221" s="3" t="s">
-        <v>914</v>
+        <v>927</v>
       </c>
       <c r="B221" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12012,7 +12228,7 @@
       <c r="F221" s="19"/>
       <c r="G221" s="9"/>
       <c r="H221" s="3" t="s">
-        <v>915</v>
+        <v>928</v>
       </c>
       <c r="I221" s="7" t="s">
         <v>16</v>
@@ -12022,14 +12238,14 @@
     </row>
     <row r="222" ht="22.5" customHeight="1">
       <c r="A222" s="3" t="s">
-        <v>916</v>
+        <v>929</v>
       </c>
       <c r="B222" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Locher,  (-)</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>917</v>
+        <v>930</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="18"/>
@@ -12044,14 +12260,14 @@
     </row>
     <row r="223" ht="22.5" customHeight="1">
       <c r="A223" s="3" t="s">
-        <v>918</v>
+        <v>931</v>
       </c>
       <c r="B223" s="4" t="str">
         <f t="shared" si="1"/>
         <v>König, Caspar (-)</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>919</v>
+        <v>932</v>
       </c>
       <c r="D223" s="3" t="s">
         <v>685</v>
@@ -12066,7 +12282,7 @@
     </row>
     <row r="224" ht="22.5" customHeight="1">
       <c r="A224" s="3" t="s">
-        <v>920</v>
+        <v>933</v>
       </c>
       <c r="B224" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12088,7 +12304,7 @@
         <v>71</v>
       </c>
       <c r="H224" s="20" t="s">
-        <v>921</v>
+        <v>934</v>
       </c>
       <c r="I224" s="7" t="s">
         <v>16</v>
@@ -12100,7 +12316,7 @@
     </row>
     <row r="225" ht="22.5" customHeight="1">
       <c r="A225" s="3" t="s">
-        <v>922</v>
+        <v>935</v>
       </c>
       <c r="B225" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12114,7 +12330,7 @@
       <c r="F225" s="19"/>
       <c r="G225" s="9"/>
       <c r="H225" s="3" t="s">
-        <v>923</v>
+        <v>936</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>16</v>
@@ -12124,17 +12340,17 @@
     </row>
     <row r="226" ht="22.5" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>924</v>
+        <v>937</v>
       </c>
       <c r="B226" s="4" t="str">
         <f t="shared" si="1"/>
         <v>O., Jacob U. (-)</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>925</v>
+        <v>938</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>926</v>
+        <v>939</v>
       </c>
       <c r="E226" s="18"/>
       <c r="F226" s="19"/>
@@ -12150,21 +12366,21 @@
     </row>
     <row r="227" ht="22.5" customHeight="1">
       <c r="A227" s="3" t="s">
-        <v>927</v>
+        <v>940</v>
       </c>
       <c r="B227" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schneeberger,  (-)</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>928</v>
+        <v>941</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="18"/>
       <c r="F227" s="19"/>
       <c r="G227" s="9"/>
       <c r="H227" s="3" t="s">
-        <v>929</v>
+        <v>942</v>
       </c>
       <c r="I227" s="7" t="s">
         <v>16</v>
@@ -12174,14 +12390,14 @@
     </row>
     <row r="228" ht="22.5" customHeight="1">
       <c r="A228" s="3" t="s">
-        <v>930</v>
+        <v>943</v>
       </c>
       <c r="B228" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwingli, Ulrich (1484-1531)</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>931</v>
+        <v>944</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>797</v>
@@ -12193,10 +12409,10 @@
         <v>1531.0</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="I228" s="7" t="s">
         <v>16</v>
@@ -12206,14 +12422,14 @@
     </row>
     <row r="229" ht="22.5" customHeight="1">
       <c r="A229" s="3" t="s">
-        <v>934</v>
+        <v>947</v>
       </c>
       <c r="B229" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bullinger, Heinrich (1504-1575)</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>935</v>
+        <v>948</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>38</v>
@@ -12225,10 +12441,10 @@
         <v>1575.0</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>936</v>
+        <v>949</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="I229" s="7" t="s">
         <v>16</v>
@@ -12238,7 +12454,7 @@
     </row>
     <row r="230" ht="22.5" customHeight="1">
       <c r="A230" s="3" t="s">
-        <v>937</v>
+        <v>950</v>
       </c>
       <c r="B230" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12268,14 +12484,14 @@
     </row>
     <row r="231" ht="22.5" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>938</v>
+        <v>951</v>
       </c>
       <c r="B231" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Breitinger, Johann Jakob (1575-1645)</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>939</v>
+        <v>952</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>32</v>
@@ -12287,7 +12503,7 @@
         <v>1645.0</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>940</v>
+        <v>953</v>
       </c>
       <c r="H231" s="3"/>
       <c r="I231" s="7" t="s">
@@ -12298,17 +12514,17 @@
     </row>
     <row r="232" ht="22.5" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>941</v>
+        <v>954</v>
       </c>
       <c r="B232" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jrminger, Jacob (1588-1649)</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>942</v>
+        <v>955</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>943</v>
+        <v>956</v>
       </c>
       <c r="E232" s="5">
         <v>1588.0</v>
@@ -12317,7 +12533,7 @@
         <v>1649.0</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>944</v>
+        <v>957</v>
       </c>
       <c r="H232" s="3"/>
       <c r="I232" s="7" t="s">
@@ -12328,14 +12544,14 @@
     </row>
     <row r="233" ht="22.5" customHeight="1">
       <c r="A233" s="3" t="s">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="B233" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fries, Jakob (-)</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>946</v>
+        <v>959</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>328</v>
@@ -12352,25 +12568,25 @@
     </row>
     <row r="234" ht="22.5" customHeight="1">
       <c r="A234" s="3" t="s">
-        <v>947</v>
+        <v>960</v>
       </c>
       <c r="B234" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Geiger, Joh. Rud. (-)</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>949</v>
+        <v>962</v>
       </c>
       <c r="E234" s="18"/>
       <c r="F234" s="19"/>
       <c r="G234" s="3" t="s">
-        <v>950</v>
+        <v>963</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>951</v>
+        <v>964</v>
       </c>
       <c r="I234" s="7" t="s">
         <v>16</v>
@@ -12380,17 +12596,17 @@
     </row>
     <row r="235" ht="22.5" customHeight="1">
       <c r="A235" s="3" t="s">
-        <v>952</v>
+        <v>965</v>
       </c>
       <c r="B235" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maurer, C. (-)</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>953</v>
+        <v>966</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>954</v>
+        <v>967</v>
       </c>
       <c r="E235" s="18"/>
       <c r="F235" s="19"/>
@@ -12404,17 +12620,17 @@
     </row>
     <row r="236" ht="22.5" customHeight="1">
       <c r="A236" s="3" t="s">
-        <v>955</v>
+        <v>968</v>
       </c>
       <c r="B236" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Suter, C. (-)</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>956</v>
+        <v>969</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>954</v>
+        <v>967</v>
       </c>
       <c r="E236" s="18"/>
       <c r="F236" s="19"/>
@@ -12428,17 +12644,17 @@
     </row>
     <row r="237" ht="22.5" customHeight="1">
       <c r="A237" s="3" t="s">
-        <v>957</v>
+        <v>970</v>
       </c>
       <c r="B237" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Holzhalb, Joh. (-)</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>958</v>
+        <v>971</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>959</v>
+        <v>972</v>
       </c>
       <c r="E237" s="18"/>
       <c r="F237" s="19"/>
@@ -12454,17 +12670,17 @@
     </row>
     <row r="238" ht="22.5" customHeight="1">
       <c r="A238" s="3" t="s">
-        <v>960</v>
+        <v>973</v>
       </c>
       <c r="B238" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wirtz, H. C. (-)</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>961</v>
+        <v>974</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>962</v>
+        <v>975</v>
       </c>
       <c r="E238" s="18"/>
       <c r="F238" s="19"/>
@@ -12478,7 +12694,7 @@
     </row>
     <row r="239" ht="22.5" customHeight="1">
       <c r="A239" s="3" t="s">
-        <v>963</v>
+        <v>976</v>
       </c>
       <c r="B239" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12493,7 +12709,7 @@
       <c r="E239" s="18"/>
       <c r="F239" s="19"/>
       <c r="G239" s="3" t="s">
-        <v>964</v>
+        <v>977</v>
       </c>
       <c r="H239" s="3"/>
       <c r="I239" s="7" t="s">
@@ -12504,22 +12720,22 @@
     </row>
     <row r="240" ht="22.5" customHeight="1">
       <c r="A240" s="3" t="s">
-        <v>965</v>
+        <v>978</v>
       </c>
       <c r="B240" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hospinianus, R. (-)</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>966</v>
+        <v>979</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>967</v>
+        <v>980</v>
       </c>
       <c r="E240" s="18"/>
       <c r="F240" s="19"/>
       <c r="G240" s="3" t="s">
-        <v>968</v>
+        <v>981</v>
       </c>
       <c r="H240" s="3"/>
       <c r="I240" s="7" t="s">
@@ -12530,17 +12746,17 @@
     </row>
     <row r="241" ht="22.5" customHeight="1">
       <c r="A241" s="3" t="s">
-        <v>969</v>
+        <v>982</v>
       </c>
       <c r="B241" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Erni, H. (-)</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>970</v>
+        <v>983</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>910</v>
+        <v>923</v>
       </c>
       <c r="E241" s="18"/>
       <c r="F241" s="19"/>
@@ -12554,17 +12770,17 @@
     </row>
     <row r="242" ht="22.5" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>971</v>
+        <v>984</v>
       </c>
       <c r="B242" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Tomman, P. (-)</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>972</v>
+        <v>985</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>973</v>
+        <v>986</v>
       </c>
       <c r="E242" s="18"/>
       <c r="F242" s="19"/>
@@ -12578,17 +12794,17 @@
     </row>
     <row r="243" ht="22.5" customHeight="1">
       <c r="A243" s="3" t="s">
-        <v>974</v>
+        <v>987</v>
       </c>
       <c r="B243" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Stukki, R. (-)</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>975</v>
+        <v>988</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>967</v>
+        <v>980</v>
       </c>
       <c r="E243" s="18"/>
       <c r="F243" s="19"/>
@@ -12602,17 +12818,17 @@
     </row>
     <row r="244" ht="22.5" customHeight="1">
       <c r="A244" s="3" t="s">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="B244" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zeller, H. (-)</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>977</v>
+        <v>990</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>910</v>
+        <v>923</v>
       </c>
       <c r="E244" s="18"/>
       <c r="F244" s="19"/>
@@ -12626,7 +12842,7 @@
     </row>
     <row r="245" ht="22.5" customHeight="1">
       <c r="A245" s="3" t="s">
-        <v>978</v>
+        <v>991</v>
       </c>
       <c r="B245" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12634,13 +12850,13 @@
       </c>
       <c r="C245" s="6"/>
       <c r="D245" s="3" t="s">
-        <v>943</v>
+        <v>956</v>
       </c>
       <c r="E245" s="18"/>
       <c r="F245" s="19"/>
       <c r="G245" s="9"/>
       <c r="H245" s="3" t="s">
-        <v>979</v>
+        <v>992</v>
       </c>
       <c r="I245" s="7" t="s">
         <v>16</v>
@@ -12650,21 +12866,21 @@
     </row>
     <row r="246" ht="22.5" customHeight="1">
       <c r="A246" s="3" t="s">
-        <v>980</v>
+        <v>993</v>
       </c>
       <c r="B246" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fr. Doctorin,  (-)</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>981</v>
+        <v>994</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="18"/>
       <c r="F246" s="19"/>
       <c r="G246" s="9"/>
       <c r="H246" s="3" t="s">
-        <v>982</v>
+        <v>995</v>
       </c>
       <c r="I246" s="7" t="s">
         <v>16</v>
@@ -12674,17 +12890,17 @@
     </row>
     <row r="247" ht="22.5" customHeight="1">
       <c r="A247" s="3" t="s">
-        <v>983</v>
+        <v>996</v>
       </c>
       <c r="B247" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kusen, Jost von (1570-1630)</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>984</v>
+        <v>997</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>985</v>
+        <v>998</v>
       </c>
       <c r="E247" s="5">
         <v>1570.0</v>
@@ -12693,10 +12909,10 @@
         <v>1630.0</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>986</v>
+        <v>999</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>987</v>
+        <v>1000</v>
       </c>
       <c r="I247" s="7" t="s">
         <v>16</v>
@@ -12706,7 +12922,7 @@
     </row>
     <row r="248" ht="22.5" customHeight="1">
       <c r="A248" s="3" t="s">
-        <v>988</v>
+        <v>1001</v>
       </c>
       <c r="B248" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12722,7 +12938,7 @@
       <c r="F248" s="19"/>
       <c r="G248" s="9"/>
       <c r="H248" s="3" t="s">
-        <v>989</v>
+        <v>1002</v>
       </c>
       <c r="I248" s="7" t="s">
         <v>16</v>
@@ -12732,21 +12948,21 @@
     </row>
     <row r="249" ht="22.5" customHeight="1">
       <c r="A249" s="3" t="s">
-        <v>990</v>
+        <v>1003</v>
       </c>
       <c r="B249" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gessner,  (-)</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>991</v>
+        <v>1004</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="18"/>
       <c r="F249" s="19"/>
       <c r="G249" s="9"/>
       <c r="H249" s="3" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="I249" s="7" t="s">
         <v>16</v>
@@ -12756,17 +12972,17 @@
     </row>
     <row r="250" ht="22.5" customHeight="1">
       <c r="A250" s="3" t="s">
-        <v>993</v>
+        <v>1006</v>
       </c>
       <c r="B250" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wöllwein, Johann Anton (1616-1659)</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>994</v>
+        <v>1007</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>995</v>
+        <v>1008</v>
       </c>
       <c r="E250" s="5">
         <v>1616.0</v>
@@ -12775,10 +12991,10 @@
         <v>1659.0</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>996</v>
+        <v>1009</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>997</v>
+        <v>1010</v>
       </c>
       <c r="I250" s="7" t="s">
         <v>16</v>
@@ -12788,7 +13004,7 @@
     </row>
     <row r="251" ht="22.5" customHeight="1">
       <c r="A251" s="3" t="s">
-        <v>998</v>
+        <v>1011</v>
       </c>
       <c r="B251" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12808,19 +13024,19 @@
       </c>
       <c r="G251" s="9"/>
       <c r="H251" s="3" t="s">
-        <v>999</v>
+        <v>1012</v>
       </c>
       <c r="I251" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J251" s="8" t="s">
-        <v>1000</v>
+        <v>1013</v>
       </c>
       <c r="K251" s="9"/>
     </row>
     <row r="252" ht="22.5" customHeight="1">
       <c r="A252" s="3" t="s">
-        <v>1001</v>
+        <v>1014</v>
       </c>
       <c r="B252" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12830,39 +13046,39 @@
         <v>12</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>1002</v>
+        <v>1015</v>
       </c>
       <c r="E252" s="5">
         <v>1635.0</v>
       </c>
       <c r="F252" s="17" t="s">
-        <v>1003</v>
+        <v>1016</v>
       </c>
       <c r="G252" s="9"/>
       <c r="H252" s="3" t="s">
-        <v>1004</v>
+        <v>1017</v>
       </c>
       <c r="I252" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J252" s="8" t="s">
-        <v>1005</v>
+        <v>1018</v>
       </c>
       <c r="K252" s="9"/>
     </row>
     <row r="253" ht="22.5" customHeight="1">
       <c r="A253" s="3" t="s">
-        <v>1006</v>
+        <v>1019</v>
       </c>
       <c r="B253" s="4" t="str">
         <f t="shared" si="1"/>
         <v>de Ruyter, Michiel (1607-1676)</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>1007</v>
+        <v>1020</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>1008</v>
+        <v>1021</v>
       </c>
       <c r="E253" s="5">
         <v>1607.0</v>
@@ -12871,10 +13087,10 @@
         <v>1676.0</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>1009</v>
+        <v>1022</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>1010</v>
+        <v>1023</v>
       </c>
       <c r="I253" s="7" t="s">
         <v>16</v>
@@ -12884,21 +13100,21 @@
     </row>
     <row r="254" ht="22.5" customHeight="1">
       <c r="A254" s="3" t="s">
-        <v>1011</v>
+        <v>1024</v>
       </c>
       <c r="B254" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Frau Oberstin,  (-)</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>1012</v>
+        <v>1025</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="18"/>
       <c r="F254" s="19"/>
       <c r="G254" s="9"/>
       <c r="H254" s="3" t="s">
-        <v>1013</v>
+        <v>1026</v>
       </c>
       <c r="I254" s="7" t="s">
         <v>16</v>
@@ -12908,23 +13124,23 @@
     </row>
     <row r="255" ht="22.5" customHeight="1">
       <c r="A255" s="3" t="s">
-        <v>1014</v>
+        <v>1027</v>
       </c>
       <c r="B255" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vulcanus,  (-)</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>1015</v>
+        <v>1028</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="18"/>
       <c r="F255" s="19"/>
       <c r="G255" s="3" t="s">
-        <v>1016</v>
+        <v>1029</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>1017</v>
+        <v>1030</v>
       </c>
       <c r="I255" s="7" t="s">
         <v>239</v>
@@ -12934,23 +13150,23 @@
     </row>
     <row r="256" ht="22.5" customHeight="1">
       <c r="A256" s="3" t="s">
-        <v>1018</v>
+        <v>1031</v>
       </c>
       <c r="B256" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esau,  (-)</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>1019</v>
+        <v>1032</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="18"/>
       <c r="F256" s="19"/>
       <c r="G256" s="3" t="s">
-        <v>1020</v>
+        <v>1033</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>1021</v>
+        <v>1034</v>
       </c>
       <c r="I256" s="7" t="s">
         <v>276</v>
@@ -12960,23 +13176,23 @@
     </row>
     <row r="257" ht="22.5" customHeight="1">
       <c r="A257" s="3" t="s">
-        <v>1022</v>
+        <v>1035</v>
       </c>
       <c r="B257" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Danaos,  (-)</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>1023</v>
+        <v>1036</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="18"/>
       <c r="F257" s="19"/>
       <c r="G257" s="3" t="s">
-        <v>1024</v>
+        <v>1037</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>1025</v>
+        <v>1038</v>
       </c>
       <c r="I257" s="7" t="s">
         <v>239</v>
@@ -12986,20 +13202,20 @@
     </row>
     <row r="258" ht="22.5" customHeight="1">
       <c r="A258" s="3" t="s">
-        <v>1026</v>
+        <v>1039</v>
       </c>
       <c r="B258" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Medusa,  (-)</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>1027</v>
+        <v>1040</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="18"/>
       <c r="F258" s="19"/>
       <c r="G258" s="3" t="s">
-        <v>1028</v>
+        <v>1041</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>239</v>
@@ -13012,20 +13228,20 @@
     </row>
     <row r="259" ht="22.5" customHeight="1">
       <c r="A259" s="3" t="s">
-        <v>1029</v>
+        <v>1042</v>
       </c>
       <c r="B259" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pluton,  (-)</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>1030</v>
+        <v>1043</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="18"/>
       <c r="F259" s="19"/>
       <c r="G259" s="3" t="s">
-        <v>1031</v>
+        <v>1044</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>239</v>
@@ -13038,20 +13254,20 @@
     </row>
     <row r="260" ht="22.5" customHeight="1">
       <c r="A260" s="3" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="B260" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mercur,  (-)</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>1033</v>
+        <v>1046</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="18"/>
       <c r="F260" s="19"/>
       <c r="G260" s="3" t="s">
-        <v>1034</v>
+        <v>1047</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>239</v>
@@ -13064,20 +13280,20 @@
     </row>
     <row r="261" ht="22.5" customHeight="1">
       <c r="A261" s="3" t="s">
-        <v>1035</v>
+        <v>1048</v>
       </c>
       <c r="B261" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Perseus,  (-)</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>1036</v>
+        <v>1049</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="18"/>
       <c r="F261" s="19"/>
       <c r="G261" s="3" t="s">
-        <v>1037</v>
+        <v>1050</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>239</v>
@@ -13090,23 +13306,23 @@
     </row>
     <row r="262" ht="22.5" customHeight="1">
       <c r="A262" s="3" t="s">
-        <v>1038</v>
+        <v>1051</v>
       </c>
       <c r="B262" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Atropos,  (-)</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>1039</v>
+        <v>1052</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="18"/>
       <c r="F262" s="19"/>
       <c r="G262" s="3" t="s">
-        <v>1040</v>
+        <v>1053</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="I262" s="7" t="s">
         <v>239</v>
@@ -13116,23 +13332,23 @@
     </row>
     <row r="263" ht="22.5" customHeight="1">
       <c r="A263" s="3" t="s">
-        <v>1042</v>
+        <v>1055</v>
       </c>
       <c r="B263" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Barbara von Nikomedien,  (-)</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>1043</v>
+        <v>1056</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="18"/>
       <c r="F263" s="19"/>
       <c r="G263" s="3" t="s">
-        <v>1044</v>
+        <v>1057</v>
       </c>
       <c r="H263" s="3" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="I263" s="7" t="s">
         <v>276</v>
@@ -13142,7 +13358,7 @@
     </row>
     <row r="264" ht="22.5" customHeight="1">
       <c r="A264" s="3" t="s">
-        <v>1046</v>
+        <v>1059</v>
       </c>
       <c r="B264" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13156,7 +13372,7 @@
       <c r="F264" s="19"/>
       <c r="G264" s="9"/>
       <c r="H264" s="3" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="I264" s="13"/>
       <c r="J264" s="9"/>
@@ -13164,7 +13380,7 @@
     </row>
     <row r="265" ht="22.5" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="B265" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13178,7 +13394,7 @@
       <c r="F265" s="19"/>
       <c r="G265" s="9"/>
       <c r="H265" s="3" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="I265" s="13"/>
       <c r="J265" s="9"/>
@@ -13186,21 +13402,21 @@
     </row>
     <row r="266" ht="22.5" customHeight="1">
       <c r="A266" s="3" t="s">
-        <v>1049</v>
+        <v>1062</v>
       </c>
       <c r="B266" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Karl,  (-)</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>1050</v>
+        <v>1063</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="18"/>
       <c r="F266" s="19"/>
       <c r="G266" s="9"/>
       <c r="H266" s="3" t="s">
-        <v>1051</v>
+        <v>1064</v>
       </c>
       <c r="I266" s="7" t="s">
         <v>16</v>
@@ -13210,21 +13426,21 @@
     </row>
     <row r="267" ht="22.5" customHeight="1">
       <c r="A267" s="3" t="s">
-        <v>1052</v>
+        <v>1065</v>
       </c>
       <c r="B267" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Duraeum,  (-)</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>1053</v>
+        <v>1066</v>
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="18"/>
       <c r="F267" s="19"/>
       <c r="G267" s="9"/>
       <c r="H267" s="3" t="s">
-        <v>1054</v>
+        <v>1067</v>
       </c>
       <c r="I267" s="13"/>
       <c r="J267" s="9"/>
@@ -13232,17 +13448,17 @@
     </row>
     <row r="268" ht="22.5" customHeight="1">
       <c r="A268" s="3" t="s">
-        <v>1055</v>
+        <v>1068</v>
       </c>
       <c r="B268" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zesen, Philipp von (1619-1689)</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>1056</v>
+        <v>1069</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>1057</v>
+        <v>1070</v>
       </c>
       <c r="E268" s="5">
         <v>1619.0</v>
@@ -13251,7 +13467,7 @@
         <v>1689.0</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>1058</v>
+        <v>1071</v>
       </c>
       <c r="H268" s="3"/>
       <c r="I268" s="7" t="s">
@@ -13262,23 +13478,23 @@
     </row>
     <row r="269" ht="22.5" customHeight="1">
       <c r="A269" s="3" t="s">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="B269" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lucretia,  (-)</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="D269" s="3"/>
       <c r="E269" s="18"/>
       <c r="F269" s="19"/>
       <c r="G269" s="3" t="s">
-        <v>1061</v>
+        <v>1074</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>1062</v>
+        <v>1075</v>
       </c>
       <c r="I269" s="7" t="s">
         <v>239</v>
@@ -13288,23 +13504,23 @@
     </row>
     <row r="270" ht="22.5" customHeight="1">
       <c r="A270" s="3" t="s">
-        <v>1063</v>
+        <v>1076</v>
       </c>
       <c r="B270" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ovid,  (-)</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>1064</v>
+        <v>1077</v>
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="18"/>
       <c r="F270" s="19"/>
       <c r="G270" s="3" t="s">
-        <v>1065</v>
+        <v>1078</v>
       </c>
       <c r="H270" s="3" t="s">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="I270" s="7" t="s">
         <v>16</v>
@@ -13314,50 +13530,50 @@
     </row>
     <row r="271" ht="22.5" customHeight="1">
       <c r="A271" s="3" t="s">
-        <v>1067</v>
+        <v>1080</v>
       </c>
       <c r="B271" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schweizer, Johann Caspar (1619/1620-1684/1688)</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>1068</v>
+        <v>1081</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>1069</v>
+        <v>1082</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>1070</v>
+        <v>1083</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>1071</v>
+        <v>1084</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>1072</v>
+        <v>1085</v>
       </c>
       <c r="H271" s="3" t="s">
-        <v>1073</v>
+        <v>1086</v>
       </c>
       <c r="I271" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J271" s="8" t="s">
-        <v>1074</v>
+        <v>1087</v>
       </c>
       <c r="K271" s="3" t="s">
-        <v>1075</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="272" ht="22.5" customHeight="1">
       <c r="A272" s="3" t="s">
-        <v>1076</v>
+        <v>1089</v>
       </c>
       <c r="B272" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Herder, Johann Heinrich (1629-1665)</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>1077</v>
+        <v>1090</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>44</v>
@@ -13369,10 +13585,10 @@
         <v>1665.0</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>1078</v>
+        <v>1091</v>
       </c>
       <c r="H272" s="3" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="I272" s="7" t="s">
         <v>16</v>
@@ -13382,23 +13598,23 @@
     </row>
     <row r="273" ht="22.5" customHeight="1">
       <c r="A273" s="3" t="s">
-        <v>1080</v>
+        <v>1093</v>
       </c>
       <c r="B273" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Elischa,  (-)</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>1081</v>
+        <v>1094</v>
       </c>
       <c r="D273" s="3"/>
       <c r="E273" s="18"/>
       <c r="F273" s="19"/>
       <c r="G273" s="3" t="s">
-        <v>1082</v>
+        <v>1095</v>
       </c>
       <c r="H273" s="3" t="s">
-        <v>1083</v>
+        <v>1096</v>
       </c>
       <c r="I273" s="7" t="s">
         <v>276</v>
@@ -13408,23 +13624,23 @@
     </row>
     <row r="274" ht="22.5" customHeight="1">
       <c r="A274" s="3" t="s">
-        <v>1084</v>
+        <v>1097</v>
       </c>
       <c r="B274" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Johannes der Täufer,  (-)</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>1085</v>
+        <v>1098</v>
       </c>
       <c r="D274" s="3"/>
       <c r="E274" s="18"/>
       <c r="F274" s="19"/>
       <c r="G274" s="3" t="s">
-        <v>1086</v>
+        <v>1099</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>1087</v>
+        <v>1100</v>
       </c>
       <c r="I274" s="7" t="s">
         <v>276</v>
@@ -13434,29 +13650,29 @@
     </row>
     <row r="275" ht="22.5" customHeight="1">
       <c r="A275" s="3" t="s">
-        <v>1088</v>
+        <v>1101</v>
       </c>
       <c r="B275" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caesar, Gaius Iulius (100 v. Chr.-44 v. Chr.)</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>1089</v>
+        <v>1102</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>1090</v>
+        <v>1103</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>1091</v>
+        <v>1104</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>1092</v>
+        <v>1105</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>1093</v>
+        <v>1106</v>
       </c>
       <c r="H275" s="3" t="s">
-        <v>1094</v>
+        <v>1107</v>
       </c>
       <c r="I275" s="7" t="s">
         <v>16</v>
@@ -13466,23 +13682,23 @@
     </row>
     <row r="276" ht="22.5" customHeight="1">
       <c r="A276" s="3" t="s">
-        <v>1095</v>
+        <v>1108</v>
       </c>
       <c r="B276" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Helios,  (-)</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>1096</v>
+        <v>1109</v>
       </c>
       <c r="D276" s="3"/>
       <c r="E276" s="18"/>
       <c r="F276" s="19"/>
       <c r="G276" s="3" t="s">
-        <v>1097</v>
+        <v>1110</v>
       </c>
       <c r="H276" s="3" t="s">
-        <v>1098</v>
+        <v>1111</v>
       </c>
       <c r="I276" s="7" t="s">
         <v>239</v>
@@ -13492,14 +13708,14 @@
     </row>
     <row r="277" ht="22.5" customHeight="1">
       <c r="A277" s="3" t="s">
-        <v>1099</v>
+        <v>1112</v>
       </c>
       <c r="B277" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Suevus,  (-)</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>1100</v>
+        <v>1113</v>
       </c>
       <c r="D277" s="3"/>
       <c r="E277" s="18"/>
@@ -13518,51 +13734,51 @@
     </row>
     <row r="278" ht="22.5" customHeight="1">
       <c r="A278" s="3" t="s">
-        <v>1101</v>
+        <v>1114</v>
       </c>
       <c r="B278" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Momos,  (-)</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>1102</v>
+        <v>1115</v>
       </c>
       <c r="D278" s="3"/>
       <c r="E278" s="18"/>
       <c r="F278" s="19"/>
       <c r="G278" s="3" t="s">
-        <v>1103</v>
+        <v>1116</v>
       </c>
       <c r="H278" s="3" t="s">
-        <v>1104</v>
+        <v>1117</v>
       </c>
       <c r="I278" s="7" t="s">
         <v>239</v>
       </c>
       <c r="J278" s="10" t="s">
-        <v>1105</v>
+        <v>1118</v>
       </c>
       <c r="K278" s="9"/>
     </row>
     <row r="279" ht="22.5" customHeight="1">
       <c r="A279" s="3" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
       <c r="B279" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Galatea,  (-)</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>1107</v>
+        <v>1120</v>
       </c>
       <c r="D279" s="3"/>
       <c r="E279" s="18"/>
       <c r="F279" s="19"/>
       <c r="G279" s="3" t="s">
-        <v>1108</v>
+        <v>1121</v>
       </c>
       <c r="H279" s="3" t="s">
-        <v>1109</v>
+        <v>1122</v>
       </c>
       <c r="I279" s="7" t="s">
         <v>239</v>
@@ -13572,80 +13788,80 @@
     </row>
     <row r="280" ht="22.5" customHeight="1">
       <c r="A280" s="3" t="s">
-        <v>1110</v>
+        <v>1123</v>
       </c>
       <c r="B280" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Escher vom Luchs‏‎, Hans Heinrich (‎1644-1714)</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>1111</v>
+        <v>1124</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E280" s="17" t="s">
-        <v>1112</v>
+        <v>1125</v>
       </c>
       <c r="F280" s="5">
         <v>1714.0</v>
       </c>
       <c r="G280" s="9"/>
       <c r="H280" s="3" t="s">
-        <v>1113</v>
+        <v>1126</v>
       </c>
       <c r="I280" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J280" s="10" t="s">
-        <v>1114</v>
+        <v>1127</v>
       </c>
       <c r="K280" s="10" t="s">
-        <v>1115</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="281" ht="22.5" customHeight="1">
       <c r="A281" s="3" t="s">
-        <v>1116</v>
+        <v>1129</v>
       </c>
       <c r="B281" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Agapetus,  (6. Jh.-6. Jh.)</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>1117</v>
+        <v>1130</v>
       </c>
       <c r="D281" s="3"/>
       <c r="E281" s="17" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>1118</v>
+        <v>1131</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>1119</v>
+        <v>1132</v>
       </c>
       <c r="H281" s="3" t="s">
-        <v>1120</v>
+        <v>1133</v>
       </c>
       <c r="I281" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J281" s="10" t="s">
-        <v>1121</v>
+        <v>1134</v>
       </c>
       <c r="K281" s="15"/>
     </row>
     <row r="282" ht="22.5" customHeight="1">
       <c r="A282" s="3" t="s">
-        <v>1122</v>
+        <v>1135</v>
       </c>
       <c r="B282" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Justinian I.,  (482-565)</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>1123</v>
+        <v>1136</v>
       </c>
       <c r="D282" s="3"/>
       <c r="E282" s="17">
@@ -13655,7 +13871,7 @@
         <v>565.0</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>1124</v>
+        <v>1137</v>
       </c>
       <c r="H282" s="3" t="s">
         <v>374</v>
@@ -13668,14 +13884,14 @@
     </row>
     <row r="283" ht="22.5" customHeight="1">
       <c r="A283" s="3" t="s">
-        <v>1125</v>
+        <v>1138</v>
       </c>
       <c r="B283" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Theodora I.,  (497-548)</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>1126</v>
+        <v>1139</v>
       </c>
       <c r="D283" s="3"/>
       <c r="E283" s="17">
@@ -13685,10 +13901,10 @@
         <v>548.0</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>1127</v>
+        <v>1140</v>
       </c>
       <c r="H283" s="3" t="s">
-        <v>1128</v>
+        <v>1141</v>
       </c>
       <c r="I283" s="7" t="s">
         <v>16</v>
@@ -13698,33 +13914,33 @@
     </row>
     <row r="284" ht="22.5" customHeight="1">
       <c r="A284" s="3" t="s">
-        <v>1129</v>
+        <v>1142</v>
       </c>
       <c r="B284" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Israel,  (-)</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
       <c r="D284" s="3"/>
       <c r="E284" s="17"/>
       <c r="F284" s="5"/>
       <c r="G284" s="9"/>
       <c r="H284" s="3" t="s">
-        <v>1131</v>
+        <v>1144</v>
       </c>
       <c r="I284" s="7" t="s">
         <v>276</v>
       </c>
       <c r="J284" s="10" t="s">
-        <v>1132</v>
+        <v>1145</v>
       </c>
       <c r="K284" s="15"/>
     </row>
     <row r="285" ht="22.5" customHeight="1">
       <c r="A285" s="3" t="s">
-        <v>1133</v>
+        <v>1146</v>
       </c>
       <c r="B285" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13734,7 +13950,7 @@
         <v>12</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>1134</v>
+        <v>1147</v>
       </c>
       <c r="E285" s="17">
         <v>1530.0</v>
@@ -13743,22 +13959,22 @@
         <v>1576.0</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>1135</v>
+        <v>1148</v>
       </c>
       <c r="H285" s="3" t="s">
-        <v>1136</v>
+        <v>1149</v>
       </c>
       <c r="I285" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J285" s="10" t="s">
-        <v>1137</v>
+        <v>1150</v>
       </c>
       <c r="K285" s="15"/>
     </row>
     <row r="286" ht="22.5" customHeight="1">
       <c r="A286" s="3" t="s">
-        <v>1138</v>
+        <v>1151</v>
       </c>
       <c r="B286" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13778,29 +13994,29 @@
       </c>
       <c r="G286" s="9"/>
       <c r="H286" s="3" t="s">
-        <v>1139</v>
+        <v>1152</v>
       </c>
       <c r="I286" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J286" s="10" t="s">
-        <v>1140</v>
+        <v>1153</v>
       </c>
       <c r="K286" s="15"/>
     </row>
     <row r="287" ht="22.5" customHeight="1">
       <c r="A287" s="3" t="s">
-        <v>1141</v>
+        <v>1154</v>
       </c>
       <c r="B287" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fäsi, Magdalena (1583-1665)</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>1142</v>
+        <v>1155</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>1143</v>
+        <v>1156</v>
       </c>
       <c r="E287" s="17">
         <v>1583.0</v>
@@ -13810,35 +14026,35 @@
       </c>
       <c r="G287" s="9"/>
       <c r="H287" s="3" t="s">
-        <v>1144</v>
+        <v>1157</v>
       </c>
       <c r="I287" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J287" s="10" t="s">
-        <v>1145</v>
+        <v>1158</v>
       </c>
       <c r="K287" s="15"/>
     </row>
     <row r="288" ht="22.5" customHeight="1">
       <c r="A288" s="3" t="s">
-        <v>1146</v>
+        <v>1159</v>
       </c>
       <c r="B288" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Katharina von Alexandrien,  (-)</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>1147</v>
+        <v>1160</v>
       </c>
       <c r="D288" s="3"/>
       <c r="E288" s="17"/>
       <c r="F288" s="5"/>
       <c r="G288" s="3" t="s">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="H288" s="3" t="s">
-        <v>1149</v>
+        <v>1162</v>
       </c>
       <c r="I288" s="7" t="s">
         <v>239</v>
@@ -13848,7 +14064,7 @@
     </row>
     <row r="289" ht="22.5" customHeight="1">
       <c r="A289" s="3" t="s">
-        <v>1150</v>
+        <v>1163</v>
       </c>
       <c r="B289" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13868,101 +14084,135 @@
       </c>
       <c r="G289" s="9"/>
       <c r="H289" s="3" t="s">
-        <v>1151</v>
+        <v>1164</v>
       </c>
       <c r="I289" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J289" s="10" t="s">
-        <v>1152</v>
+        <v>1165</v>
       </c>
       <c r="K289" s="15"/>
     </row>
     <row r="290" ht="22.5" customHeight="1">
       <c r="A290" s="3" t="s">
-        <v>1153</v>
+        <v>1166</v>
       </c>
       <c r="B290" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simeon,  (-)</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>1154</v>
+        <v>1167</v>
       </c>
       <c r="D290" s="3"/>
       <c r="E290" s="17"/>
       <c r="F290" s="5"/>
       <c r="G290" s="3" t="s">
-        <v>1155</v>
+        <v>1168</v>
       </c>
       <c r="H290" s="3" t="s">
-        <v>1156</v>
+        <v>1169</v>
       </c>
       <c r="I290" s="7" t="s">
         <v>276</v>
       </c>
       <c r="J290" s="10" t="s">
-        <v>1157</v>
+        <v>1170</v>
       </c>
       <c r="K290" s="15"/>
     </row>
     <row r="291" ht="22.5" customHeight="1">
       <c r="A291" s="3" t="s">
-        <v>1158</v>
+        <v>1171</v>
       </c>
       <c r="B291" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>,  (-)</v>
-      </c>
-      <c r="C291" s="6"/>
+        <v>M. G. H. H. H. D. J. H. H.,  (-)</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>1172</v>
+      </c>
       <c r="D291" s="3"/>
       <c r="E291" s="17"/>
       <c r="F291" s="5"/>
       <c r="G291" s="9"/>
       <c r="H291" s="3"/>
-      <c r="I291" s="7"/>
+      <c r="I291" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="J291" s="15"/>
-      <c r="K291" s="15"/>
+      <c r="K291" s="15" t="s">
+        <v>1173</v>
+      </c>
     </row>
     <row r="292" ht="22.5" customHeight="1">
       <c r="A292" s="3" t="s">
-        <v>1159</v>
+        <v>1174</v>
       </c>
       <c r="B292" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>,  (-)</v>
-      </c>
-      <c r="C292" s="6"/>
+        <v>Horaz,  (65 v. Chr.-8 v. Chr.)</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>1175</v>
+      </c>
       <c r="D292" s="3"/>
-      <c r="E292" s="17"/>
-      <c r="F292" s="5"/>
-      <c r="G292" s="9"/>
-      <c r="H292" s="3"/>
-      <c r="I292" s="7"/>
+      <c r="E292" s="17" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F292" s="5" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H292" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I292" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="J292" s="15"/>
       <c r="K292" s="15"/>
     </row>
     <row r="293" ht="22.5" customHeight="1">
       <c r="A293" s="3" t="s">
-        <v>1160</v>
+        <v>1179</v>
       </c>
       <c r="B293" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>,  (-)</v>
-      </c>
-      <c r="C293" s="6"/>
-      <c r="D293" s="3"/>
-      <c r="E293" s="17"/>
-      <c r="F293" s="5"/>
-      <c r="G293" s="9"/>
-      <c r="H293" s="3"/>
-      <c r="I293" s="7"/>
-      <c r="J293" s="15"/>
+        <v>Lavater, Hans Conrad (1609-1703)</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E293" s="17">
+        <v>1609.0</v>
+      </c>
+      <c r="F293" s="5">
+        <v>1703.0</v>
+      </c>
+      <c r="G293" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H293" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="I293" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J293" s="12" t="s">
+        <v>1183</v>
+      </c>
       <c r="K293" s="15"/>
     </row>
     <row r="294" ht="22.5" customHeight="1">
       <c r="A294" s="3" t="s">
-        <v>1161</v>
+        <v>1184</v>
       </c>
       <c r="B294" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13980,7 +14230,7 @@
     </row>
     <row r="295" ht="22.5" customHeight="1">
       <c r="A295" s="3" t="s">
-        <v>1162</v>
+        <v>1185</v>
       </c>
       <c r="B295" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13998,7 +14248,7 @@
     </row>
     <row r="296" ht="22.5" customHeight="1">
       <c r="A296" s="3" t="s">
-        <v>1163</v>
+        <v>1186</v>
       </c>
       <c r="B296" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14016,7 +14266,7 @@
     </row>
     <row r="297" ht="22.5" customHeight="1">
       <c r="A297" s="3" t="s">
-        <v>1164</v>
+        <v>1187</v>
       </c>
       <c r="B297" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14034,7 +14284,7 @@
     </row>
     <row r="298" ht="22.5" customHeight="1">
       <c r="A298" s="3" t="s">
-        <v>1165</v>
+        <v>1188</v>
       </c>
       <c r="B298" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14052,7 +14302,7 @@
     </row>
     <row r="299" ht="22.5" customHeight="1">
       <c r="A299" s="3" t="s">
-        <v>1166</v>
+        <v>1189</v>
       </c>
       <c r="B299" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14070,7 +14320,7 @@
     </row>
     <row r="300" ht="22.5" customHeight="1">
       <c r="A300" s="3" t="s">
-        <v>1167</v>
+        <v>1190</v>
       </c>
       <c r="B300" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14088,7 +14338,7 @@
     </row>
     <row r="301" ht="22.5" customHeight="1">
       <c r="A301" s="3" t="s">
-        <v>1168</v>
+        <v>1191</v>
       </c>
       <c r="B301" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14106,7 +14356,7 @@
     </row>
     <row r="302" ht="22.5" customHeight="1">
       <c r="A302" s="3" t="s">
-        <v>1169</v>
+        <v>1192</v>
       </c>
       <c r="B302" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14124,7 +14374,7 @@
     </row>
     <row r="303" ht="22.5" customHeight="1">
       <c r="A303" s="3" t="s">
-        <v>1170</v>
+        <v>1193</v>
       </c>
       <c r="B303" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14142,7 +14392,7 @@
     </row>
     <row r="304" ht="22.5" customHeight="1">
       <c r="A304" s="3" t="s">
-        <v>1171</v>
+        <v>1194</v>
       </c>
       <c r="B304" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14160,7 +14410,7 @@
     </row>
     <row r="305" ht="22.5" customHeight="1">
       <c r="A305" s="3" t="s">
-        <v>1172</v>
+        <v>1195</v>
       </c>
       <c r="B305" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14178,7 +14428,7 @@
     </row>
     <row r="306" ht="22.5" customHeight="1">
       <c r="A306" s="3" t="s">
-        <v>1173</v>
+        <v>1196</v>
       </c>
       <c r="B306" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14196,7 +14446,7 @@
     </row>
     <row r="307" ht="22.5" customHeight="1">
       <c r="A307" s="3" t="s">
-        <v>1174</v>
+        <v>1197</v>
       </c>
       <c r="B307" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14214,7 +14464,7 @@
     </row>
     <row r="308" ht="22.5" customHeight="1">
       <c r="A308" s="3" t="s">
-        <v>1175</v>
+        <v>1198</v>
       </c>
       <c r="B308" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14232,7 +14482,7 @@
     </row>
     <row r="309" ht="22.5" customHeight="1">
       <c r="A309" s="3" t="s">
-        <v>1176</v>
+        <v>1199</v>
       </c>
       <c r="B309" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14250,7 +14500,7 @@
     </row>
     <row r="310" ht="22.5" customHeight="1">
       <c r="A310" s="3" t="s">
-        <v>1177</v>
+        <v>1200</v>
       </c>
       <c r="B310" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14354,28 +14604,35 @@
     <hyperlink r:id="rId76" ref="J202"/>
     <hyperlink r:id="rId77" ref="J203"/>
     <hyperlink r:id="rId78" ref="J204"/>
-    <hyperlink r:id="rId79" ref="J211"/>
-    <hyperlink r:id="rId80" ref="J212"/>
-    <hyperlink r:id="rId81" ref="J216"/>
-    <hyperlink r:id="rId82" ref="J217"/>
-    <hyperlink r:id="rId83" ref="J224"/>
-    <hyperlink r:id="rId84" ref="J251"/>
-    <hyperlink r:id="rId85" ref="J252"/>
-    <hyperlink r:id="rId86" ref="J271"/>
-    <hyperlink r:id="rId87" ref="J278"/>
-    <hyperlink r:id="rId88" ref="J280"/>
-    <hyperlink r:id="rId89" ref="K280"/>
-    <hyperlink r:id="rId90" ref="J281"/>
-    <hyperlink r:id="rId91" ref="J284"/>
-    <hyperlink r:id="rId92" ref="J285"/>
-    <hyperlink r:id="rId93" ref="J286"/>
-    <hyperlink r:id="rId94" ref="J287"/>
-    <hyperlink r:id="rId95" ref="J289"/>
-    <hyperlink r:id="rId96" ref="J290"/>
+    <hyperlink r:id="rId79" ref="J205"/>
+    <hyperlink r:id="rId80" ref="J206"/>
+    <hyperlink r:id="rId81" ref="J207"/>
+    <hyperlink r:id="rId82" ref="K208"/>
+    <hyperlink r:id="rId83" ref="J211"/>
+    <hyperlink r:id="rId84" ref="J212"/>
+    <hyperlink r:id="rId85" ref="J213"/>
+    <hyperlink r:id="rId86" ref="J214"/>
+    <hyperlink r:id="rId87" ref="J216"/>
+    <hyperlink r:id="rId88" ref="J217"/>
+    <hyperlink r:id="rId89" ref="J224"/>
+    <hyperlink r:id="rId90" ref="J251"/>
+    <hyperlink r:id="rId91" ref="J252"/>
+    <hyperlink r:id="rId92" ref="J271"/>
+    <hyperlink r:id="rId93" ref="J278"/>
+    <hyperlink r:id="rId94" ref="J280"/>
+    <hyperlink r:id="rId95" ref="K280"/>
+    <hyperlink r:id="rId96" ref="J281"/>
+    <hyperlink r:id="rId97" ref="J284"/>
+    <hyperlink r:id="rId98" ref="J285"/>
+    <hyperlink r:id="rId99" ref="J286"/>
+    <hyperlink r:id="rId100" ref="J287"/>
+    <hyperlink r:id="rId101" ref="J289"/>
+    <hyperlink r:id="rId102" ref="J290"/>
+    <hyperlink r:id="rId103" ref="J293"/>
   </hyperlinks>
-  <drawing r:id="rId97"/>
+  <drawing r:id="rId104"/>
   <tableParts count="1">
-    <tablePart r:id="rId99"/>
+    <tablePart r:id="rId106"/>
   </tableParts>
 </worksheet>
 </file>
@@ -14397,16 +14654,16 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1178</v>
+        <v>1201</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1180</v>
+        <v>1203</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -14417,179 +14674,179 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1181</v>
+        <v>1204</v>
       </c>
       <c r="B2" s="23" t="str">
         <f t="shared" ref="B2:B132" si="1">CONCATENATE(C2)</f>
         <v>Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1184</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1185</v>
+        <v>1208</v>
       </c>
       <c r="B3" s="23" t="str">
         <f t="shared" si="1"/>
         <v>Basel</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1186</v>
+        <v>1209</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1184</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1187</v>
+        <v>1210</v>
       </c>
       <c r="B4" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Eidgenossenschaft</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1188</v>
+        <v>1211</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1189</v>
+        <v>1212</v>
       </c>
       <c r="E4" s="21"/>
       <c r="F4" s="3" t="s">
-        <v>1190</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1191</v>
+        <v>1214</v>
       </c>
       <c r="B5" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Limmat</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1192</v>
+        <v>1215</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="7" t="s">
-        <v>1193</v>
+        <v>1216</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1194</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1195</v>
+        <v>1218</v>
       </c>
       <c r="B6" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Weinfelden</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1196</v>
+        <v>1219</v>
       </c>
       <c r="D6" s="25"/>
       <c r="E6" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1197</v>
+        <v>1220</v>
       </c>
       <c r="B7" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Main</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1198</v>
+        <v>1221</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="7" t="s">
-        <v>1193</v>
+        <v>1216</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1194</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1199</v>
+        <v>1222</v>
       </c>
       <c r="B8" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Zürichsee</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1200</v>
+        <v>1223</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="7" t="s">
-        <v>1193</v>
+        <v>1216</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1201</v>
+        <v>1224</v>
       </c>
       <c r="B9" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Thalwil</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1202</v>
+        <v>1225</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1203</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1204</v>
+        <v>1227</v>
       </c>
       <c r="B10" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bern</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1205</v>
+        <v>1228</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1184</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1206</v>
+        <v>1229</v>
       </c>
       <c r="B11" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Gottstatt</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1207</v>
+        <v>1230</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="13"/>
@@ -14597,325 +14854,325 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1208</v>
+        <v>1231</v>
       </c>
       <c r="B12" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Thorberg</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1209</v>
+        <v>1232</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1210</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1211</v>
+        <v>1234</v>
       </c>
       <c r="B13" s="24" t="str">
         <f t="shared" si="1"/>
         <v>London</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1212</v>
+        <v>1235</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1213</v>
+        <v>1236</v>
       </c>
       <c r="B14" s="24" t="str">
         <f t="shared" si="1"/>
         <v>England</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1214</v>
+        <v>1237</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="7" t="s">
-        <v>1215</v>
+        <v>1238</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1216</v>
+        <v>1239</v>
       </c>
       <c r="B15" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bethlehem</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1217</v>
+        <v>1240</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1218</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1219</v>
+        <v>1242</v>
       </c>
       <c r="B16" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Parnass </v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1220</v>
+        <v>1243</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="7" t="s">
-        <v>1221</v>
+        <v>1244</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1222</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1223</v>
+        <v>1246</v>
       </c>
       <c r="B17" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Traubenberg</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1224</v>
+        <v>1247</v>
       </c>
       <c r="D17" s="25"/>
       <c r="E17" s="13"/>
       <c r="F17" s="3" t="s">
-        <v>1225</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1226</v>
+        <v>1249</v>
       </c>
       <c r="B18" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Babylon</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1227</v>
+        <v>1250</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1228</v>
+        <v>1251</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1229</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1230</v>
+        <v>1253</v>
       </c>
       <c r="B19" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Canaan</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1231</v>
+        <v>1254</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="7" t="s">
-        <v>1232</v>
+        <v>1255</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1233</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1234</v>
+        <v>1257</v>
       </c>
       <c r="B20" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Ägypten</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1235</v>
+        <v>1258</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1236</v>
+        <v>1259</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1215</v>
+        <v>1238</v>
       </c>
       <c r="F20" s="9"/>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1237</v>
+        <v>1260</v>
       </c>
       <c r="B21" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Hermon</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1238</v>
+        <v>1261</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="7" t="s">
-        <v>1221</v>
+        <v>1244</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1239</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1240</v>
+        <v>1263</v>
       </c>
       <c r="B22" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Jerusalem</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1241</v>
+        <v>1264</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1242</v>
+        <v>1265</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1243</v>
+        <v>1266</v>
       </c>
       <c r="B23" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Jordan</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1244</v>
+        <v>1267</v>
       </c>
       <c r="D23" s="25"/>
       <c r="E23" s="7" t="s">
-        <v>1193</v>
+        <v>1216</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1245</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1246</v>
+        <v>1269</v>
       </c>
       <c r="B24" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Rotes Meer</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1247</v>
+        <v>1270</v>
       </c>
       <c r="D24" s="25"/>
       <c r="E24" s="7" t="s">
-        <v>1193</v>
+        <v>1216</v>
       </c>
       <c r="F24" s="9"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1248</v>
+        <v>1271</v>
       </c>
       <c r="B25" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Juda</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1249</v>
+        <v>1272</v>
       </c>
       <c r="D25" s="25"/>
       <c r="E25" s="13"/>
       <c r="F25" s="3" t="s">
-        <v>1250</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1251</v>
+        <v>1274</v>
       </c>
       <c r="B26" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Moab</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1252</v>
+        <v>1275</v>
       </c>
       <c r="D26" s="25"/>
       <c r="E26" s="13"/>
       <c r="F26" s="3" t="s">
-        <v>1253</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1254</v>
+        <v>1277</v>
       </c>
       <c r="B27" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Ammon</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1255</v>
+        <v>1278</v>
       </c>
       <c r="D27" s="25"/>
       <c r="E27" s="13"/>
       <c r="F27" s="3" t="s">
-        <v>1256</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1257</v>
+        <v>1280</v>
       </c>
       <c r="B28" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Zion</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1258</v>
+        <v>1281</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>1259</v>
+        <v>1282</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1221</v>
+        <v>1244</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>1260</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1261</v>
+        <v>1284</v>
       </c>
       <c r="B29" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Assur</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1262</v>
+        <v>1285</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="13"/>
@@ -14923,101 +15180,101 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1263</v>
+        <v>1286</v>
       </c>
       <c r="B30" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Israel</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1130</v>
+        <v>1143</v>
       </c>
       <c r="D30" s="25"/>
       <c r="E30" s="13"/>
       <c r="F30" s="3" t="s">
-        <v>1264</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1265</v>
+        <v>1288</v>
       </c>
       <c r="B31" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Nazaret</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1266</v>
+        <v>1289</v>
       </c>
       <c r="D31" s="25"/>
       <c r="E31" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>1267</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1268</v>
+        <v>1291</v>
       </c>
       <c r="B32" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Rom</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1269</v>
+        <v>1292</v>
       </c>
       <c r="D32" s="25"/>
       <c r="E32" s="13"/>
       <c r="F32" s="3" t="s">
-        <v>1270</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1271</v>
+        <v>1294</v>
       </c>
       <c r="B33" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Samaria</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1272</v>
+        <v>1295</v>
       </c>
       <c r="D33" s="25"/>
       <c r="E33" s="13"/>
       <c r="F33" s="3" t="s">
-        <v>1273</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1274</v>
+        <v>1297</v>
       </c>
       <c r="B34" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kedronbach</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1275</v>
+        <v>1298</v>
       </c>
       <c r="D34" s="25"/>
       <c r="E34" s="13"/>
       <c r="F34" s="3" t="s">
-        <v>1276</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1277</v>
+        <v>1300</v>
       </c>
       <c r="B35" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Garten von Getsemani</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1278</v>
+        <v>1301</v>
       </c>
       <c r="D35" s="25"/>
       <c r="E35" s="13"/>
@@ -15025,14 +15282,14 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1279</v>
+        <v>1302</v>
       </c>
       <c r="B36" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Urdorf</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1280</v>
+        <v>1303</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="13"/>
@@ -15040,14 +15297,14 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1281</v>
+        <v>1304</v>
       </c>
       <c r="B37" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Geiren-Rein</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1282</v>
+        <v>1305</v>
       </c>
       <c r="D37" s="25"/>
       <c r="E37" s="13"/>
@@ -15055,14 +15312,14 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1283</v>
+        <v>1306</v>
       </c>
       <c r="B38" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Aeügst</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1284</v>
+        <v>1307</v>
       </c>
       <c r="D38" s="25"/>
       <c r="E38" s="13"/>
@@ -15070,14 +15327,14 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1285</v>
+        <v>1308</v>
       </c>
       <c r="B39" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Riedt</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1286</v>
+        <v>1309</v>
       </c>
       <c r="D39" s="25"/>
       <c r="E39" s="13"/>
@@ -15085,14 +15342,14 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1287</v>
+        <v>1310</v>
       </c>
       <c r="B40" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Europa</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1288</v>
+        <v>1311</v>
       </c>
       <c r="D40" s="25"/>
       <c r="E40" s="13"/>
@@ -15100,48 +15357,48 @@
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>1289</v>
+        <v>1312</v>
       </c>
       <c r="B41" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Osir</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1290</v>
+        <v>1313</v>
       </c>
       <c r="D41" s="25"/>
       <c r="E41" s="13"/>
       <c r="F41" s="3" t="s">
-        <v>1291</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>1292</v>
+        <v>1315</v>
       </c>
       <c r="B42" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Basadingen</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1293</v>
+        <v>1316</v>
       </c>
       <c r="D42" s="25"/>
       <c r="E42" s="13"/>
       <c r="F42" s="3" t="s">
-        <v>1294</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>1295</v>
+        <v>1318</v>
       </c>
       <c r="B43" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Diessenhofen</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1296</v>
+        <v>1319</v>
       </c>
       <c r="D43" s="25"/>
       <c r="E43" s="13"/>
@@ -15149,50 +15406,50 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>1297</v>
+        <v>1320</v>
       </c>
       <c r="B44" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Rhein</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1298</v>
+        <v>1321</v>
       </c>
       <c r="D44" s="25"/>
       <c r="E44" s="7" t="s">
-        <v>1193</v>
+        <v>1216</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1194</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>1299</v>
+        <v>1322</v>
       </c>
       <c r="B45" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Arabisches Reich</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1300</v>
+        <v>1323</v>
       </c>
       <c r="D45" s="25"/>
       <c r="E45" s="13"/>
       <c r="F45" s="3" t="s">
-        <v>1301</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>1302</v>
+        <v>1325</v>
       </c>
       <c r="B46" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Libanon</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1303</v>
+        <v>1326</v>
       </c>
       <c r="D46" s="25"/>
       <c r="E46" s="13"/>
@@ -15200,105 +15457,105 @@
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>1304</v>
+        <v>1327</v>
       </c>
       <c r="B47" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Emmaus</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1305</v>
+        <v>1328</v>
       </c>
       <c r="D47" s="25"/>
       <c r="E47" s="13"/>
       <c r="F47" s="3" t="s">
-        <v>1306</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>1307</v>
+        <v>1330</v>
       </c>
       <c r="B48" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Helikon</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1308</v>
+        <v>1331</v>
       </c>
       <c r="D48" s="25"/>
       <c r="E48" s="7" t="s">
-        <v>1221</v>
+        <v>1244</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>1309</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>1310</v>
+        <v>1333</v>
       </c>
       <c r="B49" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Pindos</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1311</v>
+        <v>1334</v>
       </c>
       <c r="D49" s="25"/>
       <c r="E49" s="7" t="s">
-        <v>1221</v>
+        <v>1244</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>1312</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>1313</v>
+        <v>1336</v>
       </c>
       <c r="B50" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Neckar</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1314</v>
+        <v>1337</v>
       </c>
       <c r="D50" s="25"/>
       <c r="E50" s="7" t="s">
-        <v>1193</v>
+        <v>1216</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1315</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>1316</v>
+        <v>1339</v>
       </c>
       <c r="B51" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kurpfalz</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1317</v>
+        <v>1340</v>
       </c>
       <c r="D51" s="25"/>
       <c r="E51" s="13"/>
       <c r="F51" s="3" t="s">
-        <v>1318</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>1319</v>
+        <v>1342</v>
       </c>
       <c r="B52" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Eglisau</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1320</v>
+        <v>1343</v>
       </c>
       <c r="D52" s="25"/>
       <c r="E52" s="13"/>
@@ -15306,14 +15563,14 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>1321</v>
+        <v>1344</v>
       </c>
       <c r="B53" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Altenklingen</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1322</v>
+        <v>1345</v>
       </c>
       <c r="D53" s="25"/>
       <c r="E53" s="13"/>
@@ -15321,14 +15578,14 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>1323</v>
+        <v>1346</v>
       </c>
       <c r="B54" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Altorff</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1324</v>
+        <v>1347</v>
       </c>
       <c r="D54" s="25"/>
       <c r="E54" s="13"/>
@@ -15336,65 +15593,65 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>1325</v>
+        <v>1348</v>
       </c>
       <c r="B55" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Glarus</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1326</v>
+        <v>1349</v>
       </c>
       <c r="D55" s="25"/>
       <c r="E55" s="13"/>
       <c r="F55" s="3" t="s">
-        <v>1184</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>1327</v>
+        <v>1350</v>
       </c>
       <c r="B56" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Reformierte Kirche Berg am Irchel</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1328</v>
+        <v>1351</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>1329</v>
+        <v>1352</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="3"/>
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>1330</v>
+        <v>1353</v>
       </c>
       <c r="B57" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Sodom</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1331</v>
+        <v>1354</v>
       </c>
       <c r="D57" s="25"/>
       <c r="E57" s="13"/>
       <c r="F57" s="3" t="s">
-        <v>1332</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>1333</v>
+        <v>1356</v>
       </c>
       <c r="B58" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Haus zur Sonnenblume</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1334</v>
+        <v>1357</v>
       </c>
       <c r="D58" s="25"/>
       <c r="E58" s="13"/>
@@ -15402,126 +15659,126 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>1335</v>
+        <v>1358</v>
       </c>
       <c r="B59" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Geissturm</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1336</v>
+        <v>1359</v>
       </c>
       <c r="D59" s="25"/>
       <c r="E59" s="13"/>
       <c r="F59" s="3" t="s">
-        <v>1337</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>1338</v>
+        <v>1361</v>
       </c>
       <c r="B60" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Konstantinopel</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1339</v>
+        <v>1362</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>1340</v>
+        <v>1363</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F60" s="3"/>
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>1341</v>
+        <v>1364</v>
       </c>
       <c r="B61" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Stein am Rhein</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1342</v>
+        <v>1365</v>
       </c>
       <c r="D61" s="25"/>
       <c r="E61" s="13"/>
       <c r="F61" s="3" t="s">
-        <v>1343</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>1344</v>
+        <v>1367</v>
       </c>
       <c r="B62" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Marburg</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1345</v>
+        <v>1368</v>
       </c>
       <c r="D62" s="25"/>
       <c r="E62" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>1346</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>1347</v>
+        <v>1370</v>
       </c>
       <c r="B63" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Elbląg</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1348</v>
+        <v>1371</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>1349</v>
+        <v>1372</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>1350</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>1351</v>
+        <v>1374</v>
       </c>
       <c r="B64" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Preussen</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1352</v>
+        <v>1375</v>
       </c>
       <c r="D64" s="25"/>
       <c r="E64" s="7" t="s">
-        <v>1215</v>
+        <v>1238</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>1353</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>1354</v>
+        <v>1377</v>
       </c>
       <c r="B65" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Heilbäder Baden</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1355</v>
+        <v>1378</v>
       </c>
       <c r="D65" s="25"/>
       <c r="E65" s="13"/>
@@ -15529,31 +15786,31 @@
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>1356</v>
+        <v>1379</v>
       </c>
       <c r="B66" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bad Schinznach</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1357</v>
+        <v>1380</v>
       </c>
       <c r="D66" s="25"/>
       <c r="E66" s="13"/>
       <c r="F66" s="3" t="s">
-        <v>1358</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>1359</v>
+        <v>1382</v>
       </c>
       <c r="B67" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Gyrenbad</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1360</v>
+        <v>1383</v>
       </c>
       <c r="D67" s="25"/>
       <c r="E67" s="13"/>
@@ -15561,48 +15818,48 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>1361</v>
+        <v>1384</v>
       </c>
       <c r="B68" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wängibad</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1362</v>
+        <v>1385</v>
       </c>
       <c r="D68" s="25"/>
       <c r="E68" s="13"/>
       <c r="F68" s="8" t="s">
-        <v>1363</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>1364</v>
+        <v>1387</v>
       </c>
       <c r="B69" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Aeugst</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1365</v>
+        <v>1388</v>
       </c>
       <c r="D69" s="25"/>
       <c r="E69" s="13"/>
       <c r="F69" s="3" t="s">
-        <v>1294</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>1366</v>
+        <v>1389</v>
       </c>
       <c r="B70" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Bassersdorf</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1367</v>
+        <v>1390</v>
       </c>
       <c r="D70" s="25"/>
       <c r="E70" s="13"/>
@@ -15610,14 +15867,14 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>1368</v>
+        <v>1391</v>
       </c>
       <c r="B71" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Hauptwil</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1369</v>
+        <v>1392</v>
       </c>
       <c r="D71" s="25"/>
       <c r="E71" s="13"/>
@@ -15625,14 +15882,14 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>1370</v>
+        <v>1393</v>
       </c>
       <c r="B72" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Schaffhausen</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1371</v>
+        <v>1394</v>
       </c>
       <c r="D72" s="25"/>
       <c r="E72" s="13"/>
@@ -15640,131 +15897,133 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>1372</v>
+        <v>1395</v>
       </c>
       <c r="B73" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wädenswil</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1373</v>
+        <v>1396</v>
       </c>
       <c r="D73" s="25"/>
       <c r="E73" s="7" t="s">
-        <v>1374</v>
+        <v>1397</v>
       </c>
       <c r="F73" s="3"/>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>1375</v>
+        <v>1398</v>
       </c>
       <c r="B74" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Freiamt</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1376</v>
+        <v>1399</v>
       </c>
       <c r="D74" s="25"/>
       <c r="E74" s="7" t="s">
-        <v>1374</v>
+        <v>1397</v>
       </c>
       <c r="F74" s="3"/>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>1377</v>
+        <v>1400</v>
       </c>
       <c r="B75" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Grüningen</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1378</v>
+        <v>1401</v>
       </c>
       <c r="D75" s="25"/>
       <c r="E75" s="13"/>
       <c r="F75" s="3" t="s">
-        <v>1379</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>1380</v>
+        <v>1403</v>
       </c>
       <c r="B76" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kefikon</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1381</v>
+        <v>1404</v>
       </c>
       <c r="D76" s="25"/>
       <c r="E76" s="7" t="s">
-        <v>1382</v>
+        <v>1405</v>
       </c>
       <c r="F76" s="3"/>
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>1383</v>
+        <v>1406</v>
       </c>
       <c r="B77" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Maienfeld</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1384</v>
+        <v>1407</v>
       </c>
       <c r="D77" s="25"/>
       <c r="E77" s="7" t="s">
-        <v>1374</v>
+        <v>1397</v>
       </c>
       <c r="F77" s="3"/>
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>1385</v>
+        <v>1408</v>
       </c>
       <c r="B78" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>Greifensee (Schloss)</v>
+        <v>Schloss Greifensee</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1386</v>
+        <v>1409</v>
       </c>
       <c r="D78" s="25"/>
-      <c r="E78" s="13"/>
+      <c r="E78" s="7" t="s">
+        <v>1410</v>
+      </c>
       <c r="F78" s="3"/>
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>1387</v>
+        <v>1411</v>
       </c>
       <c r="B79" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Lindenhof (Zürich)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1388</v>
+        <v>1412</v>
       </c>
       <c r="D79" s="25"/>
       <c r="E79" s="13"/>
       <c r="F79" s="3" t="s">
-        <v>1389</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>1390</v>
+        <v>1414</v>
       </c>
       <c r="B80" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Galg-Brunnen (Zürich)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1391</v>
+        <v>1415</v>
       </c>
       <c r="D80" s="25"/>
       <c r="E80" s="13"/>
@@ -15772,44 +16031,48 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>1392</v>
+        <v>1416</v>
       </c>
       <c r="B81" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Altes Kornhaus (Zürich)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1393</v>
+        <v>1417</v>
       </c>
       <c r="D81" s="25"/>
-      <c r="E81" s="13"/>
+      <c r="E81" s="7" t="s">
+        <v>1410</v>
+      </c>
       <c r="F81" s="3"/>
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>1394</v>
+        <v>1418</v>
       </c>
       <c r="B82" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Sparrenberg (Zürich)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1395</v>
+        <v>1419</v>
       </c>
       <c r="D82" s="25"/>
-      <c r="E82" s="13"/>
+      <c r="E82" s="7" t="s">
+        <v>1410</v>
+      </c>
       <c r="F82" s="3"/>
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>1396</v>
+        <v>1420</v>
       </c>
       <c r="B83" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Thurgau</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1397</v>
+        <v>1421</v>
       </c>
       <c r="D83" s="25"/>
       <c r="E83" s="13"/>
@@ -15817,14 +16080,14 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>1398</v>
+        <v>1422</v>
       </c>
       <c r="B84" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Niederlande</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1399</v>
+        <v>1423</v>
       </c>
       <c r="D84" s="25"/>
       <c r="E84" s="13"/>
@@ -15832,31 +16095,31 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>1400</v>
+        <v>1424</v>
       </c>
       <c r="B85" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Holland</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1401</v>
+        <v>1425</v>
       </c>
       <c r="D85" s="25"/>
       <c r="E85" s="13"/>
       <c r="F85" s="3" t="s">
-        <v>1402</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>1403</v>
+        <v>1427</v>
       </c>
       <c r="B86" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wigoltingen</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1404</v>
+        <v>1428</v>
       </c>
       <c r="D86" s="25"/>
       <c r="E86" s="13"/>
@@ -15864,258 +16127,272 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>1405</v>
+        <v>1429</v>
       </c>
       <c r="B87" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Kastalische Quelle</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1406</v>
+        <v>1430</v>
       </c>
       <c r="D87" s="25"/>
       <c r="E87" s="7" t="s">
-        <v>1193</v>
+        <v>1216</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>1407</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>1408</v>
+        <v>1432</v>
       </c>
       <c r="B88" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Lägern</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1409</v>
+        <v>1433</v>
       </c>
       <c r="D88" s="25"/>
       <c r="E88" s="7" t="s">
-        <v>1221</v>
+        <v>1244</v>
       </c>
       <c r="F88" s="3"/>
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>1410</v>
+        <v>1434</v>
       </c>
       <c r="B89" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Texel</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1411</v>
+        <v>1435</v>
       </c>
       <c r="D89" s="25"/>
       <c r="E89" s="13"/>
       <c r="F89" s="3" t="s">
-        <v>1412</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>1413</v>
+        <v>1437</v>
       </c>
       <c r="B90" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Vlieland</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1414</v>
+        <v>1438</v>
       </c>
       <c r="D90" s="25"/>
       <c r="E90" s="13"/>
       <c r="F90" s="3" t="s">
-        <v>1412</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>1415</v>
+        <v>1439</v>
       </c>
       <c r="B91" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Indien</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1416</v>
+        <v>1440</v>
       </c>
       <c r="D91" s="25"/>
-      <c r="E91" s="13"/>
+      <c r="E91" s="7" t="s">
+        <v>1238</v>
+      </c>
       <c r="F91" s="3"/>
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>1417</v>
+        <v>1441</v>
       </c>
       <c r="B92" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wien</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>1418</v>
+        <v>1442</v>
       </c>
       <c r="D92" s="25"/>
-      <c r="E92" s="13"/>
+      <c r="E92" s="7" t="s">
+        <v>1206</v>
+      </c>
       <c r="F92" s="3"/>
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>1419</v>
+        <v>1443</v>
       </c>
       <c r="B93" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Deutschland</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1420</v>
+        <v>1444</v>
       </c>
       <c r="D93" s="25"/>
-      <c r="E93" s="13"/>
+      <c r="E93" s="7" t="s">
+        <v>1238</v>
+      </c>
       <c r="F93" s="3"/>
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>1421</v>
+        <v>1445</v>
       </c>
       <c r="B94" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Ölberg</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1422</v>
+        <v>1446</v>
       </c>
       <c r="D94" s="25"/>
       <c r="E94" s="7" t="s">
-        <v>1221</v>
+        <v>1244</v>
       </c>
       <c r="F94" s="3"/>
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>1423</v>
+        <v>1447</v>
       </c>
       <c r="B95" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Dietikon</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1424</v>
+        <v>1448</v>
       </c>
       <c r="D95" s="25"/>
       <c r="E95" s="7" t="s">
-        <v>1382</v>
+        <v>1405</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1425</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>1426</v>
+        <v>1450</v>
       </c>
       <c r="B96" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Winterthur</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1427</v>
+        <v>1451</v>
       </c>
       <c r="D96" s="25"/>
       <c r="E96" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F96" s="3"/>
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>1428</v>
+        <v>1452</v>
       </c>
       <c r="B97" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Pfalz</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1429</v>
+        <v>1453</v>
       </c>
       <c r="D97" s="25"/>
       <c r="E97" s="7" t="s">
-        <v>1232</v>
+        <v>1255</v>
       </c>
       <c r="F97" s="3"/>
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>1430</v>
+        <v>1454</v>
       </c>
       <c r="B98" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Edenkoben</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1431</v>
+        <v>1455</v>
       </c>
       <c r="D98" s="25"/>
       <c r="E98" s="7" t="s">
-        <v>1183</v>
+        <v>1206</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>1432</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>1433</v>
+        <v>1457</v>
       </c>
       <c r="B99" s="24" t="str">
         <f t="shared" si="1"/>
         <v>Wüste Juda</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1434</v>
+        <v>1458</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>1435</v>
+        <v>1459</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>1232</v>
+        <v>1255</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>1436</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>1437</v>
+        <v>1461</v>
       </c>
       <c r="B100" s="24" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="C100" s="3"/>
+        <v>Greifensee</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>1462</v>
+      </c>
       <c r="D100" s="25"/>
-      <c r="E100" s="13"/>
+      <c r="E100" s="7" t="s">
+        <v>1397</v>
+      </c>
       <c r="F100" s="3"/>
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>1438</v>
+        <v>1463</v>
       </c>
       <c r="B101" s="24" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="C101" s="3"/>
+        <v>Lichtensteig</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>1464</v>
+      </c>
       <c r="D101" s="25"/>
-      <c r="E101" s="13"/>
+      <c r="E101" s="7" t="s">
+        <v>1405</v>
+      </c>
       <c r="F101" s="3"/>
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>1439</v>
+        <v>1465</v>
       </c>
       <c r="B102" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16128,7 +16405,7 @@
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="3" t="s">
-        <v>1440</v>
+        <v>1466</v>
       </c>
       <c r="B103" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16141,7 +16418,7 @@
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>1441</v>
+        <v>1467</v>
       </c>
       <c r="B104" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16154,7 +16431,7 @@
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="3" t="s">
-        <v>1442</v>
+        <v>1468</v>
       </c>
       <c r="B105" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16167,7 +16444,7 @@
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>1443</v>
+        <v>1469</v>
       </c>
       <c r="B106" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16180,7 +16457,7 @@
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="3" t="s">
-        <v>1444</v>
+        <v>1470</v>
       </c>
       <c r="B107" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16193,7 +16470,7 @@
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>1445</v>
+        <v>1471</v>
       </c>
       <c r="B108" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16206,7 +16483,7 @@
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="3" t="s">
-        <v>1446</v>
+        <v>1472</v>
       </c>
       <c r="B109" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16219,7 +16496,7 @@
     </row>
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>1447</v>
+        <v>1473</v>
       </c>
       <c r="B110" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16232,7 +16509,7 @@
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="3" t="s">
-        <v>1448</v>
+        <v>1474</v>
       </c>
       <c r="B111" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16245,7 +16522,7 @@
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>1449</v>
+        <v>1475</v>
       </c>
       <c r="B112" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16258,7 +16535,7 @@
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="3" t="s">
-        <v>1450</v>
+        <v>1476</v>
       </c>
       <c r="B113" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16271,7 +16548,7 @@
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>1451</v>
+        <v>1477</v>
       </c>
       <c r="B114" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16284,7 +16561,7 @@
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="3" t="s">
-        <v>1452</v>
+        <v>1478</v>
       </c>
       <c r="B115" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16297,7 +16574,7 @@
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>1453</v>
+        <v>1479</v>
       </c>
       <c r="B116" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16310,7 +16587,7 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>1454</v>
+        <v>1480</v>
       </c>
       <c r="B117" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16323,7 +16600,7 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>1455</v>
+        <v>1481</v>
       </c>
       <c r="B118" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16336,7 +16613,7 @@
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>1456</v>
+        <v>1482</v>
       </c>
       <c r="B119" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16349,7 +16626,7 @@
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>1457</v>
+        <v>1483</v>
       </c>
       <c r="B120" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16362,7 +16639,7 @@
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>1458</v>
+        <v>1484</v>
       </c>
       <c r="B121" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16375,7 +16652,7 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>1459</v>
+        <v>1485</v>
       </c>
       <c r="B122" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16388,7 +16665,7 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>1460</v>
+        <v>1486</v>
       </c>
       <c r="B123" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16401,7 +16678,7 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>1461</v>
+        <v>1487</v>
       </c>
       <c r="B124" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16414,7 +16691,7 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>1462</v>
+        <v>1488</v>
       </c>
       <c r="B125" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16427,7 +16704,7 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>1463</v>
+        <v>1489</v>
       </c>
       <c r="B126" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16440,7 +16717,7 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>1464</v>
+        <v>1490</v>
       </c>
       <c r="B127" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16453,7 +16730,7 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>1465</v>
+        <v>1491</v>
       </c>
       <c r="B128" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16466,7 +16743,7 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>1466</v>
+        <v>1492</v>
       </c>
       <c r="B129" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16479,7 +16756,7 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>1467</v>
+        <v>1493</v>
       </c>
       <c r="B130" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16492,7 +16769,7 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="3" t="s">
-        <v>1468</v>
+        <v>1494</v>
       </c>
       <c r="B131" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16505,7 +16782,7 @@
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>1469</v>
+        <v>1495</v>
       </c>
       <c r="B132" s="24" t="str">
         <f t="shared" si="1"/>
@@ -16518,10 +16795,10 @@
     </row>
   </sheetData>
   <dataValidations>
+    <dataValidation type="list" allowBlank="1" sqref="E2:E132">
+      <formula1>"Stadt,Gewässer,Berg,Land,Politische Gemeinde,Region,Landvogtei,Bauwerk"</formula1>
+    </dataValidation>
     <dataValidation allowBlank="1" showDropDown="1" sqref="A2:A132 C2:C132 F2:F132"/>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E132">
-      <formula1>"Stadt,Gewässer,Berg,Land,Politische Gemeinde,Region,Landvogtei"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="F68"/>
@@ -16553,25 +16830,25 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1470</v>
+        <v>1496</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1471</v>
+        <v>1497</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1472</v>
+        <v>1498</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1473</v>
+        <v>1499</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1474</v>
+        <v>1500</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1475</v>
+        <v>1501</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
@@ -16582,109 +16859,109 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1476</v>
+        <v>1502</v>
       </c>
       <c r="B2" s="26" t="str">
         <f t="shared" ref="B2:B40" si="1">CONCATENATE(C2)</f>
         <v>Teutsche Gedichte</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1477</v>
+        <v>1503</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1478</v>
+        <v>1504</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1479</v>
+        <v>1505</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1480</v>
+        <v>1506</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>1481</v>
+        <v>1507</v>
       </c>
       <c r="I2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1482</v>
+        <v>1508</v>
       </c>
       <c r="B3" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Die Krafft der Gottseligkeit</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1483</v>
+        <v>1509</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1484</v>
+        <v>1510</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1485</v>
+        <v>1511</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1486</v>
+        <v>1512</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1487</v>
+        <v>1513</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>1488</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1489</v>
+        <v>1515</v>
       </c>
       <c r="B4" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Archetypi homiliarum in quatuor evangelia dn. nostri Iesu Christi</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1490</v>
+        <v>1516</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1491</v>
+        <v>1517</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1492</v>
+        <v>1518</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1493</v>
+        <v>1519</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="10" t="s">
-        <v>1494</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1495</v>
+        <v>1521</v>
       </c>
       <c r="B5" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Der Psalter dess Königlichen Propheten Dauids/ Jn deutsche reymen verstendiglich vnd deutlich gebracht/ mit vorgehender anzeigung der reymen weise/ auch eines jeden Psalmes Jnhalt</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1496</v>
+        <v>1522</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1497</v>
+        <v>1523</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1498</v>
+        <v>1524</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1499</v>
+        <v>1525</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="13"/>
@@ -16692,73 +16969,73 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1500</v>
+        <v>1526</v>
       </c>
       <c r="B6" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Hundert christliche Fäst-Predigen</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1501</v>
+        <v>1527</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1502</v>
+        <v>1528</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1503</v>
+        <v>1529</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1504</v>
+        <v>1530</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>1505</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1506</v>
+        <v>1532</v>
       </c>
       <c r="B7" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Spiegel der Unermesslichen Gnad Gottes gegen den rewenden bussfertigen Sünderen/ Jn XLV. Predigen vber das XV. capitel Lucae/ vom verlohrnen Schaaf/ Pfenning/ vnd Sohn verfasset</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1507</v>
+        <v>1533</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1508</v>
+        <v>1534</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1509</v>
+        <v>1535</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1186</v>
+        <v>1209</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1510</v>
+        <v>1536</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>1511</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1512</v>
+        <v>1538</v>
       </c>
       <c r="B8" s="26" t="str">
         <f t="shared" si="1"/>
         <v>verteütschte Rueh- oder Fridens-uebung</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1513</v>
+        <v>1539</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1514</v>
+        <v>1540</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="25"/>
@@ -16768,98 +17045,98 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1515</v>
+        <v>1541</v>
       </c>
       <c r="B9" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Nähefelser-Fahrt: in zehen erbaulichen Jahrzeit-Predigen zu schuldigem Danck dem Höhesten für den im Jahr 1388 gemeinen Landleuthen dess lobl. Eydgnössischen Bundorths Glarus wider ihre Feind bey und umb Nähefels verliehenen Wundersieg </v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1516</v>
+        <v>1542</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1517</v>
+        <v>1543</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1518</v>
+        <v>1544</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1519</v>
+        <v>1545</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="10" t="s">
-        <v>1520</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1521</v>
+        <v>1547</v>
       </c>
       <c r="B10" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Die vier Haubtpuncten der christlichen seligmachenden Religion: auf alle Sontag des gantzen Jahrs ordenlich abgetheilt, grundtlich nach der heiligen Schrifft erklärt und zur Erbawung gerichtet </v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1522</v>
+        <v>1548</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1523</v>
+        <v>1549</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1524</v>
+        <v>1550</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1525</v>
+        <v>1551</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>1526</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1527</v>
+        <v>1553</v>
       </c>
       <c r="B11" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Architectura von Vestungen</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1528</v>
+        <v>1554</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1529</v>
+        <v>1555</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1485</v>
+        <v>1511</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1530</v>
+        <v>1556</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="8" t="s">
-        <v>1531</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1532</v>
+        <v>1558</v>
       </c>
       <c r="B12" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Buech der Freunden Stammen</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1533</v>
+        <v>1559</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="9"/>
@@ -16870,42 +17147,42 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1534</v>
+        <v>1560</v>
       </c>
       <c r="B13" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Christen-Spiegel, das ist, Bedenkliche Erinnerungen über die Beruoffspflichten aller Ständen </v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1535</v>
+        <v>1561</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1536</v>
+        <v>1562</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1537</v>
+        <v>1563</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>1538</v>
+        <v>1564</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>1539</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1540</v>
+        <v>1566</v>
       </c>
       <c r="B14" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Viergeticht</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1541</v>
+        <v>1567</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="9"/>
@@ -16916,14 +17193,14 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1542</v>
+        <v>1568</v>
       </c>
       <c r="B15" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Regentenspiegel</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1543</v>
+        <v>1569</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="9"/>
@@ -16934,18 +17211,18 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1544</v>
+        <v>1570</v>
       </c>
       <c r="B16" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Türckischer Jammerspiegel</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1545</v>
+        <v>1571</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="3" t="s">
-        <v>1546</v>
+        <v>1572</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="9"/>
@@ -16954,92 +17231,126 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1547</v>
+        <v>1573</v>
       </c>
       <c r="B17" s="26" t="str">
         <f t="shared" si="1"/>
-        <v>Leitungs-faden</v>
+        <v>Theatrum concionum sacr. topicum</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1548</v>
+        <v>1574</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>860</v>
-      </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="9"/>
+        <v>1575</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>1577</v>
+      </c>
       <c r="H17" s="13"/>
-      <c r="I17" s="9"/>
+      <c r="I17" s="12" t="s">
+        <v>1578</v>
+      </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1549</v>
+        <v>1579</v>
       </c>
       <c r="B18" s="26" t="str">
         <f t="shared" si="1"/>
-        <v>Buch von der Seelen-angſt Chriſti</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>1550</v>
+        <v>Seelen-Angst Christi</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>1580</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1551</v>
-      </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="9"/>
+        <v>1581</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1572</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>1582</v>
+      </c>
       <c r="H18" s="13"/>
-      <c r="I18" s="9"/>
+      <c r="I18" s="8" t="s">
+        <v>1583</v>
+      </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1552</v>
+        <v>1584</v>
       </c>
       <c r="B19" s="26" t="str">
         <f t="shared" si="1"/>
-        <v>Verſuchungs-gabe</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>1553</v>
+        <v>Dichterische Versuchgabe</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>1585</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1554</v>
-      </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="9"/>
+        <v>1586</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>1588</v>
+      </c>
       <c r="H19" s="13"/>
-      <c r="I19" s="9"/>
+      <c r="I19" s="12" t="s">
+        <v>1589</v>
+      </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1555</v>
+        <v>1590</v>
       </c>
       <c r="B20" s="26" t="str">
         <f t="shared" si="1"/>
-        <v>Kriegsbüchlin</v>
+        <v>Kriegs-Büchlein</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1556</v>
-      </c>
-      <c r="D20" s="25"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="9"/>
+        <v>1591</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>1594</v>
+      </c>
       <c r="H20" s="13"/>
-      <c r="I20" s="9"/>
+      <c r="I20" s="12" t="s">
+        <v>1595</v>
+      </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1557</v>
+        <v>1596</v>
       </c>
       <c r="B21" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Buch der Psalmen</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1558</v>
+        <v>1597</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="9"/>
@@ -17050,149 +17361,167 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1559</v>
+        <v>1598</v>
       </c>
       <c r="B22" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Sterbensspiegel/ das ist sonnenklare Vorstellung menschlicher Nichtigkeit durch alle Staend und Geschlechter</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1560</v>
+        <v>1599</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1561</v>
+        <v>1600</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1509</v>
+        <v>1535</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>1562</v>
+        <v>1601</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>1563</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1564</v>
+        <v>1603</v>
       </c>
       <c r="B23" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Warhaffte/ vnd in Gottes Wort wol gegründte Widerlegung Des newlich im Truck außgegangnen ohn-Catholischen Gesprächs von Religion oder Glaubens sachen/ geneñt der Augenspiegel</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1565</v>
+        <v>1604</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1566</v>
+        <v>1605</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1567</v>
+        <v>1606</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>1182</v>
+        <v>1205</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1562</v>
+        <v>1601</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>1568</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1569</v>
+        <v>1608</v>
       </c>
       <c r="B24" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Augspiegels Wahrer Religion Erster Theil</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1570</v>
+        <v>1609</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>1571</v>
+        <v>1610</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1572</v>
+        <v>1611</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1573</v>
+        <v>1612</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1574</v>
+        <v>1613</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>1575</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1576</v>
+        <v>1615</v>
       </c>
       <c r="B25" s="26" t="str">
         <f t="shared" si="1"/>
         <v>De kracht der Godsaligheyt</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1577</v>
+        <v>1616</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>1578</v>
+        <v>1617</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1579</v>
+        <v>1618</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>1580</v>
+        <v>1619</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>1581</v>
+        <v>1620</v>
       </c>
       <c r="H25" s="13"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1582</v>
+        <v>1621</v>
       </c>
       <c r="B26" s="26" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="9"/>
+        <v>Christlicher Wandersmann</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>1625</v>
+      </c>
       <c r="H26" s="13"/>
-      <c r="I26" s="9"/>
+      <c r="I26" s="8" t="s">
+        <v>1626</v>
+      </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1583</v>
+        <v>1627</v>
       </c>
       <c r="B27" s="26" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="25"/>
+        <v>"Bernerischer Apothecker-Tax"</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>876</v>
+      </c>
       <c r="E27" s="9"/>
       <c r="F27" s="25"/>
       <c r="G27" s="9"/>
       <c r="H27" s="13"/>
-      <c r="I27" s="9"/>
+      <c r="I27" s="3" t="s">
+        <v>1629</v>
+      </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1584</v>
+        <v>1630</v>
       </c>
       <c r="B28" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17208,7 +17537,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1585</v>
+        <v>1631</v>
       </c>
       <c r="B29" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17224,7 +17553,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1586</v>
+        <v>1632</v>
       </c>
       <c r="B30" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17240,7 +17569,7 @@
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1587</v>
+        <v>1633</v>
       </c>
       <c r="B31" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17256,7 +17585,7 @@
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1588</v>
+        <v>1634</v>
       </c>
       <c r="B32" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17272,7 +17601,7 @@
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1589</v>
+        <v>1635</v>
       </c>
       <c r="B33" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17288,7 +17617,7 @@
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1590</v>
+        <v>1636</v>
       </c>
       <c r="B34" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17304,7 +17633,7 @@
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1591</v>
+        <v>1637</v>
       </c>
       <c r="B35" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17320,7 +17649,7 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1592</v>
+        <v>1638</v>
       </c>
       <c r="B36" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17336,7 +17665,7 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1593</v>
+        <v>1639</v>
       </c>
       <c r="B37" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17352,7 +17681,7 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1594</v>
+        <v>1640</v>
       </c>
       <c r="B38" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17368,7 +17697,7 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1595</v>
+        <v>1641</v>
       </c>
       <c r="B39" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17384,7 +17713,7 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1596</v>
+        <v>1642</v>
       </c>
       <c r="B40" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17414,13 +17743,18 @@
     <hyperlink r:id="rId6" ref="I10"/>
     <hyperlink r:id="rId7" ref="I11"/>
     <hyperlink r:id="rId8" ref="I13"/>
-    <hyperlink r:id="rId9" ref="I22"/>
-    <hyperlink r:id="rId10" ref="I23"/>
-    <hyperlink r:id="rId11" ref="I24"/>
+    <hyperlink r:id="rId9" ref="I17"/>
+    <hyperlink r:id="rId10" ref="I18"/>
+    <hyperlink r:id="rId11" ref="I19"/>
+    <hyperlink r:id="rId12" ref="I20"/>
+    <hyperlink r:id="rId13" ref="I22"/>
+    <hyperlink r:id="rId14" ref="I23"/>
+    <hyperlink r:id="rId15" ref="I24"/>
+    <hyperlink r:id="rId16" ref="I26"/>
   </hyperlinks>
-  <drawing r:id="rId12"/>
+  <drawing r:id="rId17"/>
   <tableParts count="1">
-    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId19"/>
   </tableParts>
 </worksheet>
 </file>
@@ -17441,19 +17775,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1597</v>
+        <v>1643</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1598</v>
+        <v>1644</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -17461,69 +17795,69 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1599</v>
+        <v>1645</v>
       </c>
       <c r="B2" s="26" t="str">
         <f t="shared" ref="B2:B34" si="1">CONCATENATE(C2)</f>
         <v>Rat Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1600</v>
+        <v>1646</v>
       </c>
       <c r="D2" s="25"/>
       <c r="E2" s="27" t="s">
-        <v>1601</v>
+        <v>1647</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1602</v>
+        <v>1648</v>
       </c>
       <c r="B3" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Fruchtbringende Gesellschaft</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1603</v>
+        <v>1649</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1604</v>
+        <v>1650</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>1605</v>
+        <v>1651</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1606</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1607</v>
+        <v>1653</v>
       </c>
       <c r="B4" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Deutschgesinnte Genossenschaft (Lilien-Zunft)</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1608</v>
+        <v>1654</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1609</v>
+        <v>1655</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1610</v>
+        <v>1656</v>
       </c>
       <c r="B5" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Parthenicum</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1611</v>
+        <v>1657</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="13"/>
@@ -17531,134 +17865,134 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1612</v>
+        <v>1658</v>
       </c>
       <c r="B6" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Carolinum Zürich</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1613</v>
+        <v>1659</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1614</v>
+        <v>1660</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="3" t="s">
-        <v>1615</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1616</v>
+        <v>1662</v>
       </c>
       <c r="B7" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Sanhedrin</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1617</v>
+        <v>1663</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="13"/>
       <c r="F7" s="3" t="s">
-        <v>1618</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1619</v>
+        <v>1665</v>
       </c>
       <c r="B8" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Bürgerbibliothek Zürich</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1620</v>
+        <v>1666</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1621</v>
+        <v>1667</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="3" t="s">
-        <v>1622</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1623</v>
+        <v>1669</v>
       </c>
       <c r="B9" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Grossmünster</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1624</v>
+        <v>1670</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1625</v>
+        <v>1671</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1626</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1627</v>
+        <v>1673</v>
       </c>
       <c r="B10" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Fraumünster Zürich</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1628</v>
+        <v>1674</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1629</v>
+        <v>1675</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="3" t="s">
-        <v>1630</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1631</v>
+        <v>1677</v>
       </c>
       <c r="B11" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Philipps-Universität Marburg</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1632</v>
+        <v>1678</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1633</v>
+        <v>1679</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="9"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1634</v>
+        <v>1680</v>
       </c>
       <c r="B12" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kartäuser</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1635</v>
+        <v>1681</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1636</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1637</v>
+        <v>1683</v>
       </c>
       <c r="B13" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17671,7 +18005,7 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1638</v>
+        <v>1684</v>
       </c>
       <c r="B14" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17684,7 +18018,7 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1639</v>
+        <v>1685</v>
       </c>
       <c r="B15" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17697,7 +18031,7 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1640</v>
+        <v>1686</v>
       </c>
       <c r="B16" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17710,7 +18044,7 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1641</v>
+        <v>1687</v>
       </c>
       <c r="B17" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17723,7 +18057,7 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1642</v>
+        <v>1688</v>
       </c>
       <c r="B18" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17736,7 +18070,7 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1643</v>
+        <v>1689</v>
       </c>
       <c r="B19" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17749,7 +18083,7 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1644</v>
+        <v>1690</v>
       </c>
       <c r="B20" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17762,7 +18096,7 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1645</v>
+        <v>1691</v>
       </c>
       <c r="B21" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17775,7 +18109,7 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1646</v>
+        <v>1692</v>
       </c>
       <c r="B22" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17788,7 +18122,7 @@
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1647</v>
+        <v>1693</v>
       </c>
       <c r="B23" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17801,7 +18135,7 @@
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1648</v>
+        <v>1694</v>
       </c>
       <c r="B24" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17814,7 +18148,7 @@
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1649</v>
+        <v>1695</v>
       </c>
       <c r="B25" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17827,7 +18161,7 @@
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1650</v>
+        <v>1696</v>
       </c>
       <c r="B26" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17840,7 +18174,7 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1651</v>
+        <v>1697</v>
       </c>
       <c r="B27" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17853,7 +18187,7 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1652</v>
+        <v>1698</v>
       </c>
       <c r="B28" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17866,7 +18200,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1653</v>
+        <v>1699</v>
       </c>
       <c r="B29" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17879,7 +18213,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1654</v>
+        <v>1700</v>
       </c>
       <c r="B30" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17892,7 +18226,7 @@
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1655</v>
+        <v>1701</v>
       </c>
       <c r="B31" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17905,7 +18239,7 @@
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1656</v>
+        <v>1702</v>
       </c>
       <c r="B32" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17918,7 +18252,7 @@
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1657</v>
+        <v>1703</v>
       </c>
       <c r="B33" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17931,7 +18265,7 @@
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1658</v>
+        <v>1704</v>
       </c>
       <c r="B34" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17972,19 +18306,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1659</v>
+        <v>1705</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1660</v>
+        <v>1706</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1661</v>
+        <v>1707</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1662</v>
+        <v>1708</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -17992,26 +18326,26 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1663</v>
+        <v>1709</v>
       </c>
       <c r="B2" s="23" t="str">
         <f t="shared" ref="B2:B8" si="1">CONCATENATE(C2)</f>
         <v>Runs</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1664</v>
+        <v>1710</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1665</v>
+        <v>1711</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>1666</v>
+        <v>1712</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1667</v>
+        <v>1713</v>
       </c>
       <c r="B3" s="23" t="str">
         <f t="shared" si="1"/>
@@ -18024,7 +18358,7 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1668</v>
+        <v>1714</v>
       </c>
       <c r="B4" s="23" t="str">
         <f t="shared" si="1"/>
@@ -18037,7 +18371,7 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1669</v>
+        <v>1715</v>
       </c>
       <c r="B5" s="23" t="str">
         <f t="shared" si="1"/>
@@ -18050,7 +18384,7 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1670</v>
+        <v>1716</v>
       </c>
       <c r="B6" s="23" t="str">
         <f t="shared" si="1"/>
@@ -18063,7 +18397,7 @@
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1671</v>
+        <v>1717</v>
       </c>
       <c r="B7" s="23" t="str">
         <f t="shared" si="1"/>
@@ -18076,7 +18410,7 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1672</v>
+        <v>1718</v>
       </c>
       <c r="B8" s="23" t="str">
         <f t="shared" si="1"/>

--- a/gsheet/xlsx/entities.xlsx
+++ b/gsheet/xlsx/entities.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2324" uniqueCount="1824">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2330" uniqueCount="1827">
   <si>
     <t>Person-ID</t>
   </si>
@@ -1937,16 +1937,31 @@
     <t>person_138</t>
   </si>
   <si>
-    <t>G. H.</t>
+    <t>Hess</t>
+  </si>
+  <si>
+    <t>1089547692</t>
+  </si>
+  <si>
+    <t>Ratsherr, Obvergobt</t>
+  </si>
+  <si>
+    <t>https://www.hfls.ch/humo-gen/birthday_family/1/F101119?main_person=I289248</t>
   </si>
   <si>
     <t>person_139</t>
   </si>
   <si>
-    <t>J. C.</t>
-  </si>
-  <si>
-    <t>Frau des G. H.</t>
+    <t>Schweizer</t>
+  </si>
+  <si>
+    <t>Kleophea</t>
+  </si>
+  <si>
+    <t>Ehefrau von Georg Hess</t>
+  </si>
+  <si>
+    <t>https://www.hfls.ch/humo-gen/birthday_family/1/F101119?main_person=I289249</t>
   </si>
   <si>
     <t>person_140</t>
@@ -2308,9 +2323,6 @@
   </si>
   <si>
     <t>person_171</t>
-  </si>
-  <si>
-    <t>Hess</t>
   </si>
   <si>
     <t>Caspar</t>
@@ -3579,9 +3591,6 @@
   </si>
   <si>
     <t>person_276</t>
-  </si>
-  <si>
-    <t>Schweizer</t>
   </si>
   <si>
     <t>1619/1620</t>
@@ -10221,59 +10230,79 @@
       </c>
       <c r="B135" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>G. H.,  (-)</v>
+        <v>Hess, Georg (1615-1680)</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="D135" s="3"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="5"/>
-      <c r="G135" s="9"/>
-      <c r="H135" s="3"/>
+      <c r="D135" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E135" s="5">
+        <v>1615.0</v>
+      </c>
+      <c r="F135" s="5">
+        <v>1680.0</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>631</v>
+      </c>
       <c r="I135" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J135" s="9"/>
+      <c r="J135" s="8" t="s">
+        <v>632</v>
+      </c>
       <c r="K135" s="9"/>
     </row>
     <row r="136" ht="22.5" customHeight="1">
       <c r="A136" s="3" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B136" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>J. C.,  (-)</v>
+        <v>Schweizer, Kleophea (1607-1686)</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="D136" s="3"/>
-      <c r="E136" s="5"/>
-      <c r="F136" s="5"/>
+        <v>634</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="E136" s="5">
+        <v>1607.0</v>
+      </c>
+      <c r="F136" s="5">
+        <v>1686.0</v>
+      </c>
       <c r="G136" s="9"/>
       <c r="H136" s="3" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="I136" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J136" s="9"/>
+      <c r="J136" s="10" t="s">
+        <v>637</v>
+      </c>
       <c r="K136" s="9"/>
     </row>
     <row r="137" ht="22.5" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B137" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Hercules von (1617-1686)</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="E137" s="5">
         <v>1617.0</v>
@@ -10282,30 +10311,30 @@
         <v>1686.0</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="H137" s="3"/>
       <c r="I137" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J137" s="8" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="K137" s="9"/>
     </row>
     <row r="138" ht="22.5" customHeight="1">
       <c r="A138" s="3" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="B138" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis, Barbara Dorothea von (1629-1660)</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="E138" s="5">
         <v>1629.0</v>
@@ -10315,26 +10344,26 @@
       </c>
       <c r="G138" s="9"/>
       <c r="H138" s="3" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="I138" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J138" s="8" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="K138" s="9"/>
     </row>
     <row r="139" ht="22.5" customHeight="1">
       <c r="A139" s="3" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B139" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. L.,  (-)</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="5"/>
@@ -10349,21 +10378,21 @@
     </row>
     <row r="140" ht="22.5" customHeight="1">
       <c r="A140" s="3" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="B140" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. A.,  (-)</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
       <c r="G140" s="9"/>
       <c r="H140" s="3" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="I140" s="7" t="s">
         <v>16</v>
@@ -10373,21 +10402,21 @@
     </row>
     <row r="141" ht="22.5" customHeight="1">
       <c r="A141" s="3" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="B141" s="4" t="str">
         <f t="shared" si="1"/>
         <v>B. M.,  (-)</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="D141" s="3"/>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
       <c r="G141" s="9"/>
       <c r="H141" s="3" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="I141" s="7" t="s">
         <v>16</v>
@@ -10397,73 +10426,73 @@
     </row>
     <row r="142" ht="22.5" customHeight="1">
       <c r="A142" s="3" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="B142" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. H.,  (-)</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="9"/>
       <c r="H142" s="3" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="I142" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J142" s="10" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="K142" s="9"/>
     </row>
     <row r="143" ht="22.5" customHeight="1">
       <c r="A143" s="3" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="B143" s="4" t="str">
         <f t="shared" si="1"/>
         <v>D. M.,  (-)</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="D143" s="3"/>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
       <c r="G143" s="9"/>
       <c r="H143" s="3" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="I143" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J143" s="10" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="K143" s="9"/>
     </row>
     <row r="144" ht="22.5" customHeight="1">
       <c r="A144" s="3" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="B144" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gottfrid,  (-)</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
       <c r="G144" s="9"/>
       <c r="H144" s="3" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="I144" s="7" t="s">
         <v>16</v>
@@ -10473,7 +10502,7 @@
     </row>
     <row r="145" ht="22.5" customHeight="1">
       <c r="A145" s="3" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="B145" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10487,7 +10516,7 @@
       <c r="F145" s="5"/>
       <c r="G145" s="9"/>
       <c r="H145" s="3" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="I145" s="7" t="s">
         <v>16</v>
@@ -10497,21 +10526,21 @@
     </row>
     <row r="146" ht="22.5" customHeight="1">
       <c r="A146" s="3" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="B146" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. C. Schw.,  (-)</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="D146" s="3"/>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
       <c r="G146" s="9"/>
       <c r="H146" s="3" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="I146" s="7" t="s">
         <v>16</v>
@@ -10521,21 +10550,21 @@
     </row>
     <row r="147" ht="22.5" customHeight="1">
       <c r="A147" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="B147" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. K.,  (-)</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="D147" s="3"/>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
       <c r="G147" s="9"/>
       <c r="H147" s="3" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="I147" s="7" t="s">
         <v>16</v>
@@ -10545,14 +10574,14 @@
     </row>
     <row r="148" ht="22.5" customHeight="1">
       <c r="A148" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="B148" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ott, Hans Heinrich (-)</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>71</v>
@@ -10569,14 +10598,14 @@
     </row>
     <row r="149" ht="22.5" customHeight="1">
       <c r="A149" s="3" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="B149" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. W.,  (-)</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="D149" s="3"/>
       <c r="E149" s="5"/>
@@ -10591,21 +10620,21 @@
     </row>
     <row r="150" ht="22.5" customHeight="1">
       <c r="A150" s="3" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="B150" s="4" t="str">
         <f t="shared" si="1"/>
         <v>V. L.,  (-)</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="D150" s="3"/>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
       <c r="G150" s="9"/>
       <c r="H150" s="3" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="I150" s="7" t="s">
         <v>16</v>
@@ -10615,14 +10644,14 @@
     </row>
     <row r="151" ht="22.5" customHeight="1">
       <c r="A151" s="3" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="B151" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. Sch.,  (-)</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="D151" s="3"/>
       <c r="E151" s="5"/>
@@ -10637,21 +10666,21 @@
     </row>
     <row r="152" ht="22.5" customHeight="1">
       <c r="A152" s="3" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B152" s="4" t="str">
         <f t="shared" si="1"/>
         <v>S. H.,  (-)</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
       <c r="G152" s="9"/>
       <c r="H152" s="3" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="I152" s="7" t="s">
         <v>16</v>
@@ -10661,14 +10690,14 @@
     </row>
     <row r="153" ht="22.5" customHeight="1">
       <c r="A153" s="3" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="B153" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. H. H.,  (-)</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="5"/>
@@ -10679,55 +10708,55 @@
         <v>16</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="K153" s="9"/>
     </row>
     <row r="154" ht="22.5" customHeight="1">
       <c r="A154" s="3" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="B154" s="4" t="str">
         <f t="shared" si="1"/>
         <v>E. W.,  (-)</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="D154" s="3"/>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="9"/>
       <c r="H154" s="3" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="I154" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J154" s="10" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="K154" s="9"/>
     </row>
     <row r="155" ht="22.5" customHeight="1">
       <c r="A155" s="3" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="B155" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Koller, Elisabeth (-)</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
       <c r="G155" s="9"/>
       <c r="H155" s="3" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="I155" s="7" t="s">
         <v>16</v>
@@ -10739,17 +10768,17 @@
     </row>
     <row r="156" ht="22.5" customHeight="1">
       <c r="A156" s="3" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="B156" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lobwasser, Ambrosius (1515-1585)</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="E156" s="5">
         <v>1515.0</v>
@@ -10758,10 +10787,10 @@
         <v>1585.0</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="I156" s="7" t="s">
         <v>16</v>
@@ -10771,14 +10800,14 @@
     </row>
     <row r="157" ht="22.5" customHeight="1">
       <c r="A157" s="3" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="B157" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vollenweider, Jakob (1594-1647)</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>330</v>
@@ -10790,10 +10819,10 @@
         <v>1647.0</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="I157" s="7" t="s">
         <v>16</v>
@@ -10803,7 +10832,7 @@
     </row>
     <row r="158" ht="22.5" customHeight="1">
       <c r="A158" s="3" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="B158" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10813,7 +10842,7 @@
         <v>232</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
       <c r="E158" s="5">
         <v>1606.0</v>
@@ -10822,7 +10851,7 @@
         <v>1660.0</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>235</v>
@@ -10835,17 +10864,17 @@
     </row>
     <row r="159" ht="22.5" customHeight="1">
       <c r="A159" s="3" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="B159" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Burkhard, Hans Konrad (1613-1681)</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="E159" s="5">
         <v>1613.0</v>
@@ -10854,10 +10883,10 @@
         <v>1681.0</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="I159" s="7" t="s">
         <v>16</v>
@@ -10867,14 +10896,14 @@
     </row>
     <row r="160" ht="22.5" customHeight="1">
       <c r="A160" s="3" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="B160" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ardüser, Johann (1585-1665)</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>109</v>
@@ -10886,40 +10915,40 @@
         <v>1665.0</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="I160" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J160" s="12" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="K160" s="9"/>
     </row>
     <row r="161" ht="22.5" customHeight="1">
       <c r="A161" s="3" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="B161" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hegner, Diethelm  (-)</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
       <c r="G161" s="3" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="I161" s="7" t="s">
         <v>16</v>
@@ -10929,17 +10958,17 @@
     </row>
     <row r="162" ht="22.5" customHeight="1">
       <c r="A162" s="3" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="B162" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Trigland, Jacobus (1583-1654)</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="E162" s="18">
         <v>1583.0</v>
@@ -10948,10 +10977,10 @@
         <v>1654.0</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="I162" s="7" t="s">
         <v>16</v>
@@ -10961,17 +10990,17 @@
     </row>
     <row r="163" ht="22.5" customHeight="1">
       <c r="A163" s="3" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="B163" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwinger, Theodor (?) (1597-1654)</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="E163" s="5">
         <v>1597.0</v>
@@ -10980,32 +11009,32 @@
         <v>1654.0</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="I163" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J163" s="10" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="K163" s="3"/>
     </row>
     <row r="164" ht="22.5" customHeight="1">
       <c r="A164" s="3" t="s">
-        <v>729</v>
+        <v>734</v>
       </c>
       <c r="B164" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Genath, Johann Jacob (1582-1654)</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="E164" s="5">
         <v>1582.0</v>
@@ -11014,10 +11043,10 @@
         <v>1654.0</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>732</v>
+        <v>737</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="I164" s="7" t="s">
         <v>16</v>
@@ -11027,49 +11056,49 @@
     </row>
     <row r="165" ht="22.5" customHeight="1">
       <c r="A165" s="3" t="s">
-        <v>734</v>
+        <v>739</v>
       </c>
       <c r="B165" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Escher vom Luchs‏, Johannes (‎1646-1659)</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>126</v>
       </c>
       <c r="E165" s="19" t="s">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="F165" s="5">
         <v>1659.0</v>
       </c>
       <c r="G165" s="9"/>
       <c r="H165" s="3" t="s">
-        <v>737</v>
+        <v>742</v>
       </c>
       <c r="I165" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J165" s="10" t="s">
-        <v>738</v>
+        <v>743</v>
       </c>
       <c r="K165" s="9"/>
     </row>
     <row r="166" ht="22.5" customHeight="1">
       <c r="A166" s="3" t="s">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="B166" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hess, Caspar (1578-1631)</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>740</v>
+        <v>629</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="E166" s="5">
         <v>1578.0</v>
@@ -11078,29 +11107,29 @@
         <v>1631.0</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="I166" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J166" s="10" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="K166" s="9"/>
     </row>
     <row r="167" ht="22.5" customHeight="1">
       <c r="A167" s="3" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="B167" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wolf, Johann Jakob (1601-1641)</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>32</v>
@@ -11112,29 +11141,29 @@
         <v>1641.0</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="I167" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J167" s="10" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="K167" s="9"/>
     </row>
     <row r="168" ht="22.5" customHeight="1">
       <c r="A168" s="3" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B168" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spörri, Felix (1581-1643)</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>90</v>
@@ -11146,24 +11175,24 @@
         <v>1643.0</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="I168" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="K168" s="3" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="169" ht="22.5" customHeight="1">
       <c r="A169" s="3" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="B169" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11173,7 +11202,7 @@
         <v>12</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="E169" s="5">
         <v>1604.0</v>
@@ -11189,20 +11218,20 @@
         <v>16</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="K169" s="9"/>
     </row>
     <row r="170" ht="22.5" customHeight="1">
       <c r="A170" s="3" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B170" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther, Rudolf (1519-1586)</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>146</v>
@@ -11214,38 +11243,38 @@
         <v>1586.0</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="I170" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J170" s="10" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="K170" s="9"/>
     </row>
     <row r="171" ht="22.5" customHeight="1">
       <c r="A171" s="3" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B171" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Weiss, Caspar (-)</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="E171" s="20"/>
       <c r="F171" s="21"/>
       <c r="G171" s="9"/>
       <c r="H171" s="22" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="I171" s="7" t="s">
         <v>16</v>
@@ -11255,7 +11284,7 @@
     </row>
     <row r="172" ht="22.5" customHeight="1">
       <c r="A172" s="3" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B172" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11269,7 +11298,7 @@
       <c r="F172" s="21"/>
       <c r="G172" s="9"/>
       <c r="H172" s="22" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="I172" s="7" t="s">
         <v>16</v>
@@ -11279,21 +11308,21 @@
     </row>
     <row r="173" ht="22.5" customHeight="1">
       <c r="A173" s="3" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B173" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bas,  (-)</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="20"/>
       <c r="F173" s="21"/>
       <c r="G173" s="9"/>
       <c r="H173" s="3" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="I173" s="23"/>
       <c r="J173" s="9"/>
@@ -11301,82 +11330,82 @@
     </row>
     <row r="174" ht="22.5" customHeight="1">
       <c r="A174" s="3" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B174" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gw., H. H. J. (-)</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="E174" s="20"/>
       <c r="F174" s="21"/>
       <c r="G174" s="9"/>
       <c r="H174" s="3" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="I174" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J174" s="9"/>
       <c r="K174" s="10" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
     </row>
     <row r="175" ht="22.5" customHeight="1">
       <c r="A175" s="3" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="B175" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hofmeister, Johann (‎1622-‎1656‎)</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>109</v>
       </c>
       <c r="E175" s="19" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="F175" s="19" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="G175" s="9"/>
       <c r="H175" s="3" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="I175" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="K175" s="9"/>
     </row>
     <row r="176" ht="22.5" customHeight="1">
       <c r="A176" s="3" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B176" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Cyrene, Simon von (-)</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="E176" s="20"/>
       <c r="F176" s="21"/>
       <c r="G176" s="3" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>258</v>
@@ -11389,20 +11418,20 @@
     </row>
     <row r="177" ht="22.5" customHeight="1">
       <c r="A177" s="3" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B177" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thomas,  (-)</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="20"/>
       <c r="F177" s="21"/>
       <c r="G177" s="3" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>353</v>
@@ -11415,23 +11444,23 @@
     </row>
     <row r="178" ht="22.5" customHeight="1">
       <c r="A178" s="3" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B178" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Phaeton,  (-)</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="20"/>
       <c r="F178" s="21"/>
       <c r="G178" s="3" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="I178" s="7" t="s">
         <v>240</v>
@@ -11441,14 +11470,14 @@
     </row>
     <row r="179" ht="22.5" customHeight="1">
       <c r="A179" s="3" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B179" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lukas,  (-)</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="D179" s="3"/>
       <c r="E179" s="20"/>
@@ -11465,20 +11494,20 @@
     </row>
     <row r="180" ht="22.5" customHeight="1">
       <c r="A180" s="3" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="B180" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pallas Athena,  (-)</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="20"/>
       <c r="F180" s="21"/>
       <c r="G180" s="3" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>240</v>
@@ -11491,23 +11520,23 @@
     </row>
     <row r="181" ht="22.5" customHeight="1">
       <c r="A181" s="3" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="B181" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bacchus,  (-)</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="D181" s="3"/>
       <c r="E181" s="20"/>
       <c r="F181" s="21"/>
       <c r="G181" s="3" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="I181" s="7" t="s">
         <v>240</v>
@@ -11517,23 +11546,23 @@
     </row>
     <row r="182" ht="22.5" customHeight="1">
       <c r="A182" s="3" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B182" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Darius I.,  (-)</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="20"/>
       <c r="F182" s="21"/>
       <c r="G182" s="3" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="I182" s="7" t="s">
         <v>16</v>
@@ -11543,23 +11572,23 @@
     </row>
     <row r="183" ht="22.5" customHeight="1">
       <c r="A183" s="3" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="B183" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kyros II.,  (-)</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="D183" s="3"/>
       <c r="E183" s="20"/>
       <c r="F183" s="21"/>
       <c r="G183" s="3" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="I183" s="7" t="s">
         <v>16</v>
@@ -11569,25 +11598,25 @@
     </row>
     <row r="184" ht="22.5" customHeight="1">
       <c r="A184" s="3" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="B184" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hippo, Augustinus von (-)</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="E184" s="20"/>
       <c r="F184" s="21"/>
       <c r="G184" s="3" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="I184" s="7" t="s">
         <v>16</v>
@@ -11597,23 +11626,23 @@
     </row>
     <row r="185" ht="22.5" customHeight="1">
       <c r="A185" s="3" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="B185" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lazarus,  (-)</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="D185" s="3"/>
       <c r="E185" s="20"/>
       <c r="F185" s="21"/>
       <c r="G185" s="3" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="I185" s="7" t="s">
         <v>258</v>
@@ -11623,23 +11652,23 @@
     </row>
     <row r="186" ht="22.5" customHeight="1">
       <c r="A186" s="3" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="B186" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lot,  (-)</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="20"/>
       <c r="F186" s="21"/>
       <c r="G186" s="3" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="I186" s="7" t="s">
         <v>258</v>
@@ -11649,17 +11678,17 @@
     </row>
     <row r="187" ht="22.5" customHeight="1">
       <c r="A187" s="3" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="B187" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gyger, Johann Rudolf (1603-1662)</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="E187" s="5">
         <v>1603.0</v>
@@ -11668,10 +11697,10 @@
         <v>1662.0</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="I187" s="7" t="s">
         <v>16</v>
@@ -11681,7 +11710,7 @@
     </row>
     <row r="188" ht="22.5" customHeight="1">
       <c r="A188" s="3" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="B188" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11694,16 +11723,16 @@
         <v>13</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="F188" s="5">
         <v>1690.0</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="I188" s="7" t="s">
         <v>16</v>
@@ -11713,17 +11742,17 @@
     </row>
     <row r="189" ht="22.5" customHeight="1">
       <c r="A189" s="3" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="B189" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bachofen, Johann Ulrich (1643-1700)</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="E189" s="5">
         <v>1643.0</v>
@@ -11732,32 +11761,32 @@
         <v>1700.0</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="I189" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J189" s="10" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="K189" s="9"/>
     </row>
     <row r="190" ht="22.5" customHeight="1">
       <c r="A190" s="3" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="B190" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grebel, Hans Konrad (1615-1674)</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="E190" s="5">
         <v>1615.0</v>
@@ -11766,61 +11795,61 @@
         <v>1674.0</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="I190" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="K190" s="9"/>
     </row>
     <row r="191" ht="22.5" customHeight="1">
       <c r="A191" s="3" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="B191" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gossweiler, Emerentia (1620-‎1686)</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="E191" s="5">
         <v>1620.0</v>
       </c>
       <c r="F191" s="19" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="G191" s="9"/>
       <c r="H191" s="3" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="I191" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J191" s="10" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="K191" s="9"/>
     </row>
     <row r="192" ht="22.5" customHeight="1">
       <c r="A192" s="3" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="B192" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lochmann, Heinrich (1613-1667)</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>38</v>
@@ -11832,29 +11861,29 @@
         <v>1667.0</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J192" s="8" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="K192" s="9"/>
     </row>
     <row r="193" ht="22.5" customHeight="1">
       <c r="A193" s="3" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="B193" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Johann Jakob (1602-1668)</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>32</v>
@@ -11866,32 +11895,32 @@
         <v>1668.0</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J193" s="8" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="K193" s="9"/>
     </row>
     <row r="194" ht="22.5" customHeight="1">
       <c r="A194" s="3" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="B194" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orelli, Anna (1606-1681)</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="E194" s="5">
         <v>1606.0</v>
@@ -11901,29 +11930,29 @@
       </c>
       <c r="G194" s="9"/>
       <c r="H194" s="3" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="I194" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J194" s="10" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="K194" s="9"/>
     </row>
     <row r="195" ht="22.5" customHeight="1">
       <c r="A195" s="3" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="B195" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Eberhard, Hans Kaspar (1645-1723)</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="E195" s="5">
         <v>1645.0</v>
@@ -11933,29 +11962,29 @@
       </c>
       <c r="G195" s="9"/>
       <c r="H195" s="3" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J195" s="10" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="K195" s="9"/>
     </row>
     <row r="196" ht="22.5" customHeight="1">
       <c r="A196" s="3" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="B196" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirt‏, Katharina (1644-1717)</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="E196" s="5">
         <v>1644.0</v>
@@ -11965,26 +11994,26 @@
       </c>
       <c r="G196" s="9"/>
       <c r="H196" s="3" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="I196" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J196" s="10" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="K196" s="9"/>
     </row>
     <row r="197" ht="22.5" customHeight="1">
       <c r="A197" s="3" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B197" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grob, Hans Jakob (1639-1712)</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>228</v>
@@ -11996,22 +12025,22 @@
         <v>1712.0</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="I197" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J197" s="8" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="K197" s="9"/>
     </row>
     <row r="198" ht="22.5" customHeight="1">
       <c r="A198" s="3" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="B198" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12021,39 +12050,39 @@
         <v>70</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="E198" s="5">
         <v>1648.0</v>
       </c>
       <c r="F198" s="19" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="G198" s="9"/>
       <c r="H198" s="3" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="I198" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J198" s="10" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="K198" s="9"/>
     </row>
     <row r="199" ht="22.5" customHeight="1">
       <c r="A199" s="3" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="B199" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klingler, Kaspar (1642-1677)</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="E199" s="5">
         <v>1642.0</v>
@@ -12063,26 +12092,26 @@
       </c>
       <c r="G199" s="9"/>
       <c r="H199" s="3" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="I199" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J199" s="14" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="K199" s="9"/>
     </row>
     <row r="200" ht="22.5" customHeight="1">
       <c r="A200" s="3" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="B200" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöndli, Dorothea (1646-1711)</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>489</v>
@@ -12095,29 +12124,29 @@
       </c>
       <c r="G200" s="9"/>
       <c r="H200" s="3" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="I200" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J200" s="10" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="K200" s="9"/>
     </row>
     <row r="201" ht="22.5" customHeight="1">
       <c r="A201" s="3" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="B201" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Hans Caspar (1617-1691)</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="E201" s="5">
         <v>1617.0</v>
@@ -12126,32 +12155,32 @@
         <v>1691.0</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="K201" s="9"/>
     </row>
     <row r="202" ht="22.5" customHeight="1">
       <c r="A202" s="3" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="B202" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Salomon (1580-1652)</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="E202" s="5">
         <v>1580.0</v>
@@ -12160,64 +12189,64 @@
         <v>1652.0</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J202" s="8" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="K202" s="9"/>
     </row>
     <row r="203" ht="22.5" customHeight="1">
       <c r="A203" s="3" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="B203" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis-Soglio, Maria Ursina von  (‎1600-1663‎)</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="E203" s="19" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="F203" s="24" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="G203" s="9"/>
       <c r="H203" s="3" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J203" s="8" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="K203" s="9"/>
     </row>
     <row r="204" ht="22.5" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="B204" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Brügger, Andreas von (1588-1653)</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="E204" s="5">
         <v>1588.0</v>
@@ -12226,32 +12255,32 @@
         <v>1653.0</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="I204" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J204" s="8" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="K204" s="9"/>
     </row>
     <row r="205" ht="22.5" customHeight="1">
       <c r="A205" s="3" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="B205" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Anhorn, Bartholomäus (1616-1700)</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="E205" s="5">
         <v>1616.0</v>
@@ -12260,29 +12289,29 @@
         <v>1700.0</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="I205" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J205" s="12" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="K205" s="9"/>
     </row>
     <row r="206" ht="22.5" customHeight="1">
       <c r="A206" s="3" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="B206" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wild, Abraham (1628-1689)</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>305</v>
@@ -12294,29 +12323,29 @@
         <v>1689.0</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J206" s="12" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="K206" s="9"/>
     </row>
     <row r="207" ht="22.5" customHeight="1">
       <c r="A207" s="3" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B207" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grob, Johannes (1643-1697)</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>126</v>
@@ -12328,24 +12357,24 @@
         <v>1697.0</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J207" s="12" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="K207" s="3" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
     </row>
     <row r="208" ht="22.5" customHeight="1">
       <c r="A208" s="3" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B208" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12359,19 +12388,19 @@
       <c r="F208" s="21"/>
       <c r="G208" s="9"/>
       <c r="H208" s="3" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="I208" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J208" s="9"/>
       <c r="K208" s="10" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
     </row>
     <row r="209" ht="22.5" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B209" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12390,10 +12419,10 @@
         <v>1673.0</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="I209" s="7" t="s">
         <v>16</v>
@@ -12403,21 +12432,21 @@
     </row>
     <row r="210" ht="22.5" customHeight="1">
       <c r="A210" s="3" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B210" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Oeri,  (-)</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="20"/>
       <c r="F210" s="21"/>
       <c r="G210" s="9"/>
       <c r="H210" s="3" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="I210" s="7" t="s">
         <v>16</v>
@@ -12427,49 +12456,49 @@
     </row>
     <row r="211" ht="22.5" customHeight="1">
       <c r="A211" s="3" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B211" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Keller vom Steinbock‏, Anna Kleophea (‎1609-1673)</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="F211" s="5">
         <v>1673.0</v>
       </c>
       <c r="G211" s="9"/>
       <c r="H211" s="3" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="I211" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J211" s="8" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="K211" s="9"/>
     </row>
     <row r="212" ht="22.5" customHeight="1">
       <c r="A212" s="3" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="B212" s="4" t="str">
         <f t="shared" si="1"/>
         <v>von Sultz, Johann Ludwig II. (1626-1687)</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="E212" s="5">
         <v>1626.0</v>
@@ -12478,64 +12507,64 @@
         <v>1687.0</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="I212" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J212" s="8" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="K212" s="9"/>
     </row>
     <row r="213" ht="22.5" customHeight="1">
       <c r="A213" s="3" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="B213" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Egli, Samuel (1627/29-1666)</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="E213" s="19" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="F213" s="5">
         <v>1666.0</v>
       </c>
       <c r="G213" s="9"/>
       <c r="H213" s="3" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="I213" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J213" s="10" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="K213" s="9"/>
     </row>
     <row r="214" ht="22.5" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B214" s="4" t="str">
         <f t="shared" si="1"/>
         <v>von Breitenlandenberg, Wildhans (1410-1444)</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="E214" s="5">
         <v>1410.0</v>
@@ -12545,26 +12574,26 @@
       </c>
       <c r="G214" s="9"/>
       <c r="H214" s="3" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="I214" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J214" s="10" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="K214" s="9"/>
     </row>
     <row r="215" ht="22.5" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="B215" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pfarrherr,  (-)</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="20"/>
@@ -12579,17 +12608,17 @@
     </row>
     <row r="216" ht="22.5" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B216" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid von Schwarzenhorn, Johann Rudolf (1590-1667)</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="E216" s="5">
         <v>1590.0</v>
@@ -12598,29 +12627,29 @@
         <v>1667.0</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="I216" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J216" s="8" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="K216" s="9"/>
     </row>
     <row r="217" ht="22.5" customHeight="1">
       <c r="A217" s="3" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B217" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid, Felix (-1598)</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>90</v>
@@ -12631,26 +12660,26 @@
       </c>
       <c r="G217" s="9"/>
       <c r="H217" s="3" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="I217" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J217" s="8" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="K217" s="9"/>
     </row>
     <row r="218" ht="22.5" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="B218" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hessen, Heinrich (-)</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>38</v>
@@ -12659,7 +12688,7 @@
       <c r="F218" s="21"/>
       <c r="G218" s="9"/>
       <c r="H218" s="3" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="I218" s="7" t="s">
         <v>16</v>
@@ -12669,17 +12698,17 @@
     </row>
     <row r="219" ht="22.5" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B219" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulr., H. (-)</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="E219" s="20"/>
       <c r="F219" s="21"/>
@@ -12695,7 +12724,7 @@
     </row>
     <row r="220" ht="22.5" customHeight="1">
       <c r="A220" s="3" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="B220" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12705,13 +12734,13 @@
         <v>62</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="E220" s="20"/>
       <c r="F220" s="21"/>
       <c r="G220" s="9"/>
       <c r="H220" s="3" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>16</v>
@@ -12721,7 +12750,7 @@
     </row>
     <row r="221" ht="22.5" customHeight="1">
       <c r="A221" s="3" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B221" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12735,7 +12764,7 @@
       <c r="F221" s="21"/>
       <c r="G221" s="9"/>
       <c r="H221" s="3" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="I221" s="7" t="s">
         <v>16</v>
@@ -12745,14 +12774,14 @@
     </row>
     <row r="222" ht="22.5" customHeight="1">
       <c r="A222" s="3" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="B222" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Locher,  (-)</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="20"/>
@@ -12767,17 +12796,17 @@
     </row>
     <row r="223" ht="22.5" customHeight="1">
       <c r="A223" s="3" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B223" s="4" t="str">
         <f t="shared" si="1"/>
         <v>König, Caspar (-)</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="E223" s="20"/>
       <c r="F223" s="21"/>
@@ -12789,7 +12818,7 @@
     </row>
     <row r="224" ht="22.5" customHeight="1">
       <c r="A224" s="3" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="B224" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12811,7 +12840,7 @@
         <v>72</v>
       </c>
       <c r="H224" s="22" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="I224" s="7" t="s">
         <v>16</v>
@@ -12823,7 +12852,7 @@
     </row>
     <row r="225" ht="22.5" customHeight="1">
       <c r="A225" s="3" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="B225" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12837,7 +12866,7 @@
       <c r="F225" s="21"/>
       <c r="G225" s="9"/>
       <c r="H225" s="3" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>16</v>
@@ -12847,17 +12876,17 @@
     </row>
     <row r="226" ht="22.5" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="B226" s="4" t="str">
         <f t="shared" si="1"/>
         <v>O., Jacob U. (-)</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="E226" s="20"/>
       <c r="F226" s="21"/>
@@ -12873,21 +12902,21 @@
     </row>
     <row r="227" ht="22.5" customHeight="1">
       <c r="A227" s="3" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="B227" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schneeberger,  (-)</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="20"/>
       <c r="F227" s="21"/>
       <c r="G227" s="9"/>
       <c r="H227" s="3" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="I227" s="7" t="s">
         <v>16</v>
@@ -12897,17 +12926,17 @@
     </row>
     <row r="228" ht="22.5" customHeight="1">
       <c r="A228" s="3" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="B228" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwingli, Ulrich (1484-1531)</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="E228" s="5">
         <v>1484.0</v>
@@ -12916,10 +12945,10 @@
         <v>1531.0</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="I228" s="7" t="s">
         <v>16</v>
@@ -12929,14 +12958,14 @@
     </row>
     <row r="229" ht="22.5" customHeight="1">
       <c r="A229" s="3" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="B229" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bullinger, Heinrich (1504-1575)</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>38</v>
@@ -12948,10 +12977,10 @@
         <v>1575.0</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="I229" s="7" t="s">
         <v>16</v>
@@ -12961,14 +12990,14 @@
     </row>
     <row r="230" ht="22.5" customHeight="1">
       <c r="A230" s="3" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="B230" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther, Rudolf (1519-1586)</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>146</v>
@@ -12980,7 +13009,7 @@
         <v>1586.0</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="H230" s="3"/>
       <c r="I230" s="7" t="s">
@@ -12991,14 +13020,14 @@
     </row>
     <row r="231" ht="22.5" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="B231" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Breitinger, Johann Jakob (1575-1645)</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>32</v>
@@ -13010,7 +13039,7 @@
         <v>1645.0</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="H231" s="3"/>
       <c r="I231" s="7" t="s">
@@ -13021,17 +13050,17 @@
     </row>
     <row r="232" ht="22.5" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="B232" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jrminger, Jacob (1588-1649)</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="E232" s="5">
         <v>1588.0</v>
@@ -13040,7 +13069,7 @@
         <v>1649.0</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="H232" s="3"/>
       <c r="I232" s="7" t="s">
@@ -13051,14 +13080,14 @@
     </row>
     <row r="233" ht="22.5" customHeight="1">
       <c r="A233" s="3" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="B233" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fries, Jakob (-)</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>330</v>
@@ -13075,25 +13104,25 @@
     </row>
     <row r="234" ht="22.5" customHeight="1">
       <c r="A234" s="3" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="B234" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Geiger, Joh. Rud. (-)</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="E234" s="20"/>
       <c r="F234" s="21"/>
       <c r="G234" s="3" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="I234" s="7" t="s">
         <v>16</v>
@@ -13103,17 +13132,17 @@
     </row>
     <row r="235" ht="22.5" customHeight="1">
       <c r="A235" s="3" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="B235" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maurer, C. (-)</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="E235" s="20"/>
       <c r="F235" s="21"/>
@@ -13127,17 +13156,17 @@
     </row>
     <row r="236" ht="22.5" customHeight="1">
       <c r="A236" s="3" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="B236" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Suter, C. (-)</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="E236" s="20"/>
       <c r="F236" s="21"/>
@@ -13151,7 +13180,7 @@
     </row>
     <row r="237" ht="22.5" customHeight="1">
       <c r="A237" s="3" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="B237" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13161,7 +13190,7 @@
         <v>605</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="E237" s="20"/>
       <c r="F237" s="21"/>
@@ -13177,17 +13206,17 @@
     </row>
     <row r="238" ht="22.5" customHeight="1">
       <c r="A238" s="3" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="B238" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wirtz, H. C. (-)</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="E238" s="20"/>
       <c r="F238" s="21"/>
@@ -13201,7 +13230,7 @@
     </row>
     <row r="239" ht="22.5" customHeight="1">
       <c r="A239" s="3" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="B239" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13211,12 +13240,12 @@
         <v>610</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="E239" s="20"/>
       <c r="F239" s="21"/>
       <c r="G239" s="3" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="H239" s="3"/>
       <c r="I239" s="7" t="s">
@@ -13227,22 +13256,22 @@
     </row>
     <row r="240" ht="22.5" customHeight="1">
       <c r="A240" s="3" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="B240" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hospinianus, R. (-)</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="E240" s="20"/>
       <c r="F240" s="21"/>
       <c r="G240" s="3" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="H240" s="3"/>
       <c r="I240" s="7" t="s">
@@ -13253,17 +13282,17 @@
     </row>
     <row r="241" ht="22.5" customHeight="1">
       <c r="A241" s="3" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="B241" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Erni, H. (-)</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="E241" s="20"/>
       <c r="F241" s="21"/>
@@ -13277,17 +13306,17 @@
     </row>
     <row r="242" ht="22.5" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="B242" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Tomman, P. (-)</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="E242" s="20"/>
       <c r="F242" s="21"/>
@@ -13301,17 +13330,17 @@
     </row>
     <row r="243" ht="22.5" customHeight="1">
       <c r="A243" s="3" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="B243" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Stukki, R. (-)</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="E243" s="20"/>
       <c r="F243" s="21"/>
@@ -13325,17 +13354,17 @@
     </row>
     <row r="244" ht="22.5" customHeight="1">
       <c r="A244" s="3" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="B244" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zeller, H. (-)</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="E244" s="20"/>
       <c r="F244" s="21"/>
@@ -13349,7 +13378,7 @@
     </row>
     <row r="245" ht="22.5" customHeight="1">
       <c r="A245" s="3" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B245" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13357,13 +13386,13 @@
       </c>
       <c r="C245" s="6"/>
       <c r="D245" s="3" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="E245" s="20"/>
       <c r="F245" s="21"/>
       <c r="G245" s="9"/>
       <c r="H245" s="3" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="I245" s="7" t="s">
         <v>16</v>
@@ -13373,21 +13402,21 @@
     </row>
     <row r="246" ht="22.5" customHeight="1">
       <c r="A246" s="3" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="B246" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fr. Doctorin,  (-)</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="20"/>
       <c r="F246" s="21"/>
       <c r="G246" s="9"/>
       <c r="H246" s="3" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="I246" s="7" t="s">
         <v>16</v>
@@ -13397,17 +13426,17 @@
     </row>
     <row r="247" ht="22.5" customHeight="1">
       <c r="A247" s="3" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="B247" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kusen, Jost von (1570-1630)</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="E247" s="5">
         <v>1570.0</v>
@@ -13416,10 +13445,10 @@
         <v>1630.0</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="I247" s="7" t="s">
         <v>16</v>
@@ -13429,14 +13458,14 @@
     </row>
     <row r="248" ht="22.5" customHeight="1">
       <c r="A248" s="3" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="B248" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Johann Heinrich (1575-1630)</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>44</v>
@@ -13448,36 +13477,36 @@
         <v>1630.0</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="H248" s="3" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="I248" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J248" s="14" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="K248" s="9"/>
     </row>
     <row r="249" ht="22.5" customHeight="1">
       <c r="A249" s="3" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="B249" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gessner,  (-)</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="20"/>
       <c r="F249" s="21"/>
       <c r="G249" s="9"/>
       <c r="H249" s="3" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="I249" s="7" t="s">
         <v>16</v>
@@ -13487,17 +13516,17 @@
     </row>
     <row r="250" ht="22.5" customHeight="1">
       <c r="A250" s="3" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="B250" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wöllwein, Johann Anton (1616-1659)</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="E250" s="5">
         <v>1616.0</v>
@@ -13506,10 +13535,10 @@
         <v>1659.0</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="I250" s="7" t="s">
         <v>16</v>
@@ -13519,17 +13548,17 @@
     </row>
     <row r="251" ht="22.5" customHeight="1">
       <c r="A251" s="3" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="B251" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Anna (1613-1667)</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="E251" s="5">
         <v>1613.0</v>
@@ -13539,19 +13568,19 @@
       </c>
       <c r="G251" s="9"/>
       <c r="H251" s="3" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="I251" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J251" s="8" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="K251" s="9"/>
     </row>
     <row r="252" ht="22.5" customHeight="1">
       <c r="A252" s="3" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="B252" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13561,39 +13590,39 @@
         <v>12</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="E252" s="5">
         <v>1635.0</v>
       </c>
       <c r="F252" s="19" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="G252" s="9"/>
       <c r="H252" s="3" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="I252" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J252" s="8" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="K252" s="9"/>
     </row>
     <row r="253" ht="22.5" customHeight="1">
       <c r="A253" s="3" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="B253" s="4" t="str">
         <f t="shared" si="1"/>
         <v>de Ruyter, Michiel (1607-1676)</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="E253" s="5">
         <v>1607.0</v>
@@ -13602,10 +13631,10 @@
         <v>1676.0</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="I253" s="7" t="s">
         <v>16</v>
@@ -13615,21 +13644,21 @@
     </row>
     <row r="254" ht="22.5" customHeight="1">
       <c r="A254" s="3" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="B254" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Frau Oberstin,  (-)</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="20"/>
       <c r="F254" s="21"/>
       <c r="G254" s="9"/>
       <c r="H254" s="3" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="I254" s="7" t="s">
         <v>16</v>
@@ -13639,23 +13668,23 @@
     </row>
     <row r="255" ht="22.5" customHeight="1">
       <c r="A255" s="3" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="B255" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vulcanus,  (-)</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="20"/>
       <c r="F255" s="21"/>
       <c r="G255" s="3" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="I255" s="7" t="s">
         <v>240</v>
@@ -13665,23 +13694,23 @@
     </row>
     <row r="256" ht="22.5" customHeight="1">
       <c r="A256" s="3" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="B256" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esau,  (-)</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="20"/>
       <c r="F256" s="21"/>
       <c r="G256" s="3" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="I256" s="7" t="s">
         <v>258</v>
@@ -13691,23 +13720,23 @@
     </row>
     <row r="257" ht="22.5" customHeight="1">
       <c r="A257" s="3" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="B257" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Danaos,  (-)</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="20"/>
       <c r="F257" s="21"/>
       <c r="G257" s="3" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="I257" s="7" t="s">
         <v>240</v>
@@ -13717,20 +13746,20 @@
     </row>
     <row r="258" ht="22.5" customHeight="1">
       <c r="A258" s="3" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="B258" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Medusa,  (-)</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="20"/>
       <c r="F258" s="21"/>
       <c r="G258" s="3" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>240</v>
@@ -13743,20 +13772,20 @@
     </row>
     <row r="259" ht="22.5" customHeight="1">
       <c r="A259" s="3" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="B259" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pluton,  (-)</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="20"/>
       <c r="F259" s="21"/>
       <c r="G259" s="3" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>240</v>
@@ -13769,20 +13798,20 @@
     </row>
     <row r="260" ht="22.5" customHeight="1">
       <c r="A260" s="3" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="B260" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Mercur,  (-)</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="20"/>
       <c r="F260" s="21"/>
       <c r="G260" s="3" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>240</v>
@@ -13795,20 +13824,20 @@
     </row>
     <row r="261" ht="22.5" customHeight="1">
       <c r="A261" s="3" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="B261" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Perseus,  (-)</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="20"/>
       <c r="F261" s="21"/>
       <c r="G261" s="3" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>240</v>
@@ -13821,23 +13850,23 @@
     </row>
     <row r="262" ht="22.5" customHeight="1">
       <c r="A262" s="3" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="B262" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Atropos,  (-)</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="20"/>
       <c r="F262" s="21"/>
       <c r="G262" s="3" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="I262" s="7" t="s">
         <v>240</v>
@@ -13847,23 +13876,23 @@
     </row>
     <row r="263" ht="22.5" customHeight="1">
       <c r="A263" s="3" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="B263" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Barbara von Nikomedien,  (-)</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="20"/>
       <c r="F263" s="21"/>
       <c r="G263" s="3" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="H263" s="3" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="I263" s="7" t="s">
         <v>258</v>
@@ -13873,7 +13902,7 @@
     </row>
     <row r="264" ht="22.5" customHeight="1">
       <c r="A264" s="3" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="B264" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13887,7 +13916,7 @@
       <c r="F264" s="21"/>
       <c r="G264" s="9"/>
       <c r="H264" s="3" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="I264" s="13"/>
       <c r="J264" s="9"/>
@@ -13895,7 +13924,7 @@
     </row>
     <row r="265" ht="22.5" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="B265" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13909,7 +13938,7 @@
       <c r="F265" s="21"/>
       <c r="G265" s="9"/>
       <c r="H265" s="3" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="I265" s="13"/>
       <c r="J265" s="9"/>
@@ -13917,21 +13946,21 @@
     </row>
     <row r="266" ht="22.5" customHeight="1">
       <c r="A266" s="3" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="B266" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Karl,  (-)</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="20"/>
       <c r="F266" s="21"/>
       <c r="G266" s="9"/>
       <c r="H266" s="3" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="I266" s="7" t="s">
         <v>16</v>
@@ -13941,21 +13970,21 @@
     </row>
     <row r="267" ht="22.5" customHeight="1">
       <c r="A267" s="3" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="B267" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Duraeum,  (-)</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="20"/>
       <c r="F267" s="21"/>
       <c r="G267" s="9"/>
       <c r="H267" s="3" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="I267" s="13"/>
       <c r="J267" s="9"/>
@@ -13963,17 +13992,17 @@
     </row>
     <row r="268" ht="22.5" customHeight="1">
       <c r="A268" s="3" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="B268" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zesen, Philipp von (1619-1689)</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E268" s="5">
         <v>1619.0</v>
@@ -13982,7 +14011,7 @@
         <v>1689.0</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="H268" s="3"/>
       <c r="I268" s="7" t="s">
@@ -13993,23 +14022,23 @@
     </row>
     <row r="269" ht="22.5" customHeight="1">
       <c r="A269" s="3" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="B269" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lucretia,  (-)</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="D269" s="3"/>
       <c r="E269" s="20"/>
       <c r="F269" s="21"/>
       <c r="G269" s="3" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="I269" s="7" t="s">
         <v>240</v>
@@ -14019,23 +14048,23 @@
     </row>
     <row r="270" ht="22.5" customHeight="1">
       <c r="A270" s="3" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="B270" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ovid,  (-)</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="20"/>
       <c r="F270" s="21"/>
       <c r="G270" s="3" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="H270" s="3" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="I270" s="7" t="s">
         <v>16</v>
@@ -14045,50 +14074,50 @@
     </row>
     <row r="271" ht="22.5" customHeight="1">
       <c r="A271" s="3" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="B271" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schweizer, Johann Caspar (1619/1620-1684/1688)</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>1139</v>
+        <v>634</v>
       </c>
       <c r="D271" s="3" t="s">
         <v>620</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="G271" s="3" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="H271" s="3" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="I271" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J271" s="8" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="K271" s="3" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="272" ht="22.5" customHeight="1">
       <c r="A272" s="3" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="B272" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Herder, Johann Heinrich (1629-1665)</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>44</v>
@@ -14100,10 +14129,10 @@
         <v>1665.0</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="H272" s="3" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="I272" s="7" t="s">
         <v>16</v>
@@ -14113,23 +14142,23 @@
     </row>
     <row r="273" ht="22.5" customHeight="1">
       <c r="A273" s="3" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="B273" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Elischa,  (-)</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="D273" s="3"/>
       <c r="E273" s="20"/>
       <c r="F273" s="21"/>
       <c r="G273" s="3" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="H273" s="3" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="I273" s="7" t="s">
         <v>258</v>
@@ -14139,23 +14168,23 @@
     </row>
     <row r="274" ht="22.5" customHeight="1">
       <c r="A274" s="3" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="B274" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Johannes der Täufer,  (-)</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="D274" s="3"/>
       <c r="E274" s="20"/>
       <c r="F274" s="21"/>
       <c r="G274" s="3" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="I274" s="7" t="s">
         <v>258</v>
@@ -14165,29 +14194,29 @@
     </row>
     <row r="275" ht="22.5" customHeight="1">
       <c r="A275" s="3" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="B275" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caesar, Gaius Iulius (100 v. Chr.-44 v. Chr.)</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="H275" s="3" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="I275" s="7" t="s">
         <v>16</v>
@@ -14197,23 +14226,23 @@
     </row>
     <row r="276" ht="22.5" customHeight="1">
       <c r="A276" s="3" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="B276" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Helios,  (-)</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="D276" s="3"/>
       <c r="E276" s="20"/>
       <c r="F276" s="21"/>
       <c r="G276" s="3" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="H276" s="3" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="I276" s="7" t="s">
         <v>240</v>
@@ -14223,14 +14252,14 @@
     </row>
     <row r="277" ht="22.5" customHeight="1">
       <c r="A277" s="3" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="B277" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Suevus,  (-)</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="D277" s="3"/>
       <c r="E277" s="20"/>
@@ -14249,51 +14278,51 @@
     </row>
     <row r="278" ht="22.5" customHeight="1">
       <c r="A278" s="3" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="B278" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Momos,  (-)</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="D278" s="3"/>
       <c r="E278" s="20"/>
       <c r="F278" s="21"/>
       <c r="G278" s="3" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="H278" s="3" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="I278" s="7" t="s">
         <v>240</v>
       </c>
       <c r="J278" s="10" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="K278" s="9"/>
     </row>
     <row r="279" ht="22.5" customHeight="1">
       <c r="A279" s="3" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="B279" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Galatea,  (-)</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="D279" s="3"/>
       <c r="E279" s="20"/>
       <c r="F279" s="21"/>
       <c r="G279" s="3" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="H279" s="3" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="I279" s="7" t="s">
         <v>240</v>
@@ -14303,80 +14332,80 @@
     </row>
     <row r="280" ht="22.5" customHeight="1">
       <c r="A280" s="3" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="B280" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Escher vom Luchs‏‎, Hans Heinrich (‎1644-1714)</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>71</v>
       </c>
       <c r="E280" s="19" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="F280" s="5">
         <v>1714.0</v>
       </c>
       <c r="G280" s="9"/>
       <c r="H280" s="3" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="I280" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J280" s="10" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="K280" s="10" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="281" ht="22.5" customHeight="1">
       <c r="A281" s="3" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="B281" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Agapetus,  (6. Jh.-6. Jh.)</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="D281" s="3"/>
       <c r="E281" s="19" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="H281" s="3" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="I281" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J281" s="10" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="K281" s="17"/>
     </row>
     <row r="282" ht="22.5" customHeight="1">
       <c r="A282" s="3" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="B282" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Justinian I.,  (482-565)</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="D282" s="3"/>
       <c r="E282" s="19">
@@ -14386,10 +14415,10 @@
         <v>565.0</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="H282" s="3" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="I282" s="7" t="s">
         <v>16</v>
@@ -14399,14 +14428,14 @@
     </row>
     <row r="283" ht="22.5" customHeight="1">
       <c r="A283" s="3" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="B283" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Theodora I.,  (497-548)</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="D283" s="3"/>
       <c r="E283" s="19">
@@ -14416,10 +14445,10 @@
         <v>548.0</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="H283" s="3" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="I283" s="7" t="s">
         <v>16</v>
@@ -14429,33 +14458,33 @@
     </row>
     <row r="284" ht="22.5" customHeight="1">
       <c r="A284" s="3" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="B284" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Israel,  (-)</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D284" s="3"/>
       <c r="E284" s="19"/>
       <c r="F284" s="5"/>
       <c r="G284" s="9"/>
       <c r="H284" s="3" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="I284" s="7" t="s">
         <v>258</v>
       </c>
       <c r="J284" s="10" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="K284" s="17"/>
     </row>
     <row r="285" ht="22.5" customHeight="1">
       <c r="A285" s="3" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="B285" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14465,7 +14494,7 @@
         <v>12</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="E285" s="19">
         <v>1530.0</v>
@@ -14474,22 +14503,22 @@
         <v>1576.0</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="H285" s="3" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="I285" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J285" s="10" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="K285" s="17"/>
     </row>
     <row r="286" ht="22.5" customHeight="1">
       <c r="A286" s="3" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="B286" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14499,7 +14528,7 @@
         <v>610</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="E286" s="19">
         <v>1595.0</v>
@@ -14509,26 +14538,26 @@
       </c>
       <c r="G286" s="9"/>
       <c r="H286" s="3" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="I286" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J286" s="10" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="K286" s="17"/>
     </row>
     <row r="287" ht="22.5" customHeight="1">
       <c r="A287" s="3" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="B287" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fäsi, Magdalena (1583-1665)</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="D287" s="3" t="s">
         <v>606</v>
@@ -14541,35 +14570,35 @@
       </c>
       <c r="G287" s="9"/>
       <c r="H287" s="3" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="I287" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J287" s="10" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="K287" s="17"/>
     </row>
     <row r="288" ht="22.5" customHeight="1">
       <c r="A288" s="3" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="B288" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Katharina von Alexandrien,  (-)</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="D288" s="3"/>
       <c r="E288" s="19"/>
       <c r="F288" s="5"/>
       <c r="G288" s="3" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="H288" s="3" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="I288" s="7" t="s">
         <v>240</v>
@@ -14579,7 +14608,7 @@
     </row>
     <row r="289" ht="22.5" customHeight="1">
       <c r="A289" s="3" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="B289" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14599,54 +14628,54 @@
       </c>
       <c r="G289" s="9"/>
       <c r="H289" s="3" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="I289" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J289" s="10" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="K289" s="17"/>
     </row>
     <row r="290" ht="22.5" customHeight="1">
       <c r="A290" s="3" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B290" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simeon,  (-)</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="D290" s="3"/>
       <c r="E290" s="19"/>
       <c r="F290" s="5"/>
       <c r="G290" s="3" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="H290" s="3" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="I290" s="7" t="s">
         <v>258</v>
       </c>
       <c r="J290" s="10" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="K290" s="17"/>
     </row>
     <row r="291" ht="22.5" customHeight="1">
       <c r="A291" s="3" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="B291" s="4" t="str">
         <f t="shared" si="1"/>
         <v>M. G. H. H. H. D. J. H. H.,  (-)</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="D291" s="3"/>
       <c r="E291" s="19"/>
@@ -14658,32 +14687,32 @@
       </c>
       <c r="J291" s="17"/>
       <c r="K291" s="17" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="292" ht="22.5" customHeight="1">
       <c r="A292" s="3" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="B292" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Horaz,  (65 v. Chr.-8 v. Chr.)</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="D292" s="3"/>
       <c r="E292" s="19" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="F292" s="5" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="H292" s="3" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="I292" s="7" t="s">
         <v>16</v>
@@ -14693,17 +14722,17 @@
     </row>
     <row r="293" ht="22.5" customHeight="1">
       <c r="A293" s="3" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="B293" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lavater, Hans Conrad (1609-1703)</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="E293" s="19">
         <v>1609.0</v>
@@ -14712,150 +14741,150 @@
         <v>1703.0</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="H293" s="3" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="I293" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J293" s="12" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="K293" s="17"/>
     </row>
     <row r="294" ht="22.5" customHeight="1">
       <c r="A294" s="3" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="B294" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Josef von Arimathäa,  (-)</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="D294" s="3"/>
       <c r="E294" s="19"/>
       <c r="F294" s="5"/>
       <c r="G294" s="3" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="H294" s="3" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="I294" s="7" t="s">
         <v>258</v>
       </c>
       <c r="J294" s="17" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="K294" s="17"/>
     </row>
     <row r="295" ht="22.5" customHeight="1">
       <c r="A295" s="3" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="B295" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maria Magdalena,  (-)</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="D295" s="3"/>
       <c r="E295" s="19"/>
       <c r="F295" s="5"/>
       <c r="G295" s="3" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="H295" s="3" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="I295" s="7" t="s">
         <v>258</v>
       </c>
       <c r="J295" s="10" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="K295" s="17"/>
     </row>
     <row r="296" ht="22.5" customHeight="1">
       <c r="A296" s="3" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="B296" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Merib-Baal,  (-)</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="D296" s="3"/>
       <c r="E296" s="19"/>
       <c r="F296" s="5"/>
       <c r="G296" s="3" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="H296" s="3" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="I296" s="7" t="s">
         <v>258</v>
       </c>
       <c r="J296" s="10" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="K296" s="17"/>
     </row>
     <row r="297" ht="22.5" customHeight="1">
       <c r="A297" s="3" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="B297" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Aurora,  (-)</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="D297" s="3"/>
       <c r="E297" s="19"/>
       <c r="F297" s="5"/>
       <c r="G297" s="3" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
       <c r="H297" s="3" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="I297" s="7" t="s">
         <v>240</v>
       </c>
       <c r="J297" s="10" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="K297" s="17"/>
     </row>
     <row r="298" ht="22.5" customHeight="1">
       <c r="A298" s="3" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="B298" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Isler, Elisabeth (-)</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="E298" s="19"/>
       <c r="F298" s="5"/>
       <c r="G298" s="9"/>
       <c r="H298" s="3" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="I298" s="7" t="s">
         <v>16</v>
@@ -14865,55 +14894,55 @@
     </row>
     <row r="299" ht="22.5" customHeight="1">
       <c r="A299" s="3" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="B299" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Escher vom Luchs‏, Hans Heinrich (‎1616-1690‎)</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="D299" s="3" t="s">
         <v>71</v>
       </c>
       <c r="E299" s="19" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="F299" s="19" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="G299" s="9"/>
       <c r="H299" s="3" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="I299" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J299" s="10" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="K299" s="17"/>
     </row>
     <row r="300" ht="22.5" customHeight="1">
       <c r="A300" s="3" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="B300" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Verlorener Sohn,  (-)</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
       <c r="D300" s="3"/>
       <c r="E300" s="19"/>
       <c r="F300" s="5"/>
       <c r="G300" s="3" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="H300" s="3" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="I300" s="7" t="s">
         <v>258</v>
@@ -14923,14 +14952,14 @@
     </row>
     <row r="301" ht="22.5" customHeight="1">
       <c r="A301" s="3" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="B301" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. G. Mr. H.,  (-)</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="D301" s="3"/>
       <c r="E301" s="19"/>
@@ -14943,7 +14972,7 @@
     </row>
     <row r="302" ht="22.5" customHeight="1">
       <c r="A302" s="3" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="B302" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14962,22 +14991,22 @@
         <v>1664.0</v>
       </c>
       <c r="G302" s="3" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="H302" s="3" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="I302" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J302" s="14" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="K302" s="17"/>
     </row>
     <row r="303" ht="22.5" customHeight="1">
       <c r="A303" s="3" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="B303" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14995,7 +15024,7 @@
     </row>
     <row r="304" ht="22.5" customHeight="1">
       <c r="A304" s="3" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="B304" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15013,7 +15042,7 @@
     </row>
     <row r="305" ht="22.5" customHeight="1">
       <c r="A305" s="3" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="B305" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15031,7 +15060,7 @@
     </row>
     <row r="306" ht="22.5" customHeight="1">
       <c r="A306" s="3" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="B306" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15049,7 +15078,7 @@
     </row>
     <row r="307" ht="22.5" customHeight="1">
       <c r="A307" s="3" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="B307" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15067,7 +15096,7 @@
     </row>
     <row r="308" ht="22.5" customHeight="1">
       <c r="A308" s="3" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="B308" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15085,7 +15114,7 @@
     </row>
     <row r="309" ht="22.5" customHeight="1">
       <c r="A309" s="3" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="B309" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15103,7 +15132,7 @@
     </row>
     <row r="310" ht="22.5" customHeight="1">
       <c r="A310" s="3" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="B310" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15205,74 +15234,76 @@
     <hyperlink r:id="rId74" ref="J132"/>
     <hyperlink r:id="rId75" ref="J133"/>
     <hyperlink r:id="rId76" ref="J134"/>
-    <hyperlink r:id="rId77" ref="J137"/>
-    <hyperlink r:id="rId78" ref="J138"/>
-    <hyperlink r:id="rId79" ref="J142"/>
-    <hyperlink r:id="rId80" ref="J143"/>
-    <hyperlink r:id="rId81" ref="J153"/>
-    <hyperlink r:id="rId82" ref="J154"/>
-    <hyperlink r:id="rId83" ref="J155"/>
-    <hyperlink r:id="rId84" ref="J160"/>
-    <hyperlink r:id="rId85" ref="J163"/>
-    <hyperlink r:id="rId86" location="person_I298580" ref="J165"/>
-    <hyperlink r:id="rId87" ref="J166"/>
-    <hyperlink r:id="rId88" ref="J167"/>
-    <hyperlink r:id="rId89" ref="J168"/>
-    <hyperlink r:id="rId90" ref="J169"/>
-    <hyperlink r:id="rId91" ref="J170"/>
-    <hyperlink r:id="rId92" ref="K174"/>
-    <hyperlink r:id="rId93" location="person_I295072" ref="J175"/>
-    <hyperlink r:id="rId94" ref="J189"/>
-    <hyperlink r:id="rId95" ref="J190"/>
-    <hyperlink r:id="rId96" ref="J191"/>
-    <hyperlink r:id="rId97" ref="J192"/>
-    <hyperlink r:id="rId98" ref="J193"/>
-    <hyperlink r:id="rId99" ref="J194"/>
-    <hyperlink r:id="rId100" ref="J195"/>
-    <hyperlink r:id="rId101" ref="J196"/>
-    <hyperlink r:id="rId102" ref="J197"/>
-    <hyperlink r:id="rId103" ref="J198"/>
-    <hyperlink r:id="rId104" ref="J199"/>
-    <hyperlink r:id="rId105" ref="J200"/>
-    <hyperlink r:id="rId106" ref="J201"/>
-    <hyperlink r:id="rId107" ref="J202"/>
-    <hyperlink r:id="rId108" ref="J203"/>
-    <hyperlink r:id="rId109" ref="J204"/>
-    <hyperlink r:id="rId110" ref="J205"/>
-    <hyperlink r:id="rId111" ref="J206"/>
-    <hyperlink r:id="rId112" ref="J207"/>
-    <hyperlink r:id="rId113" ref="K208"/>
-    <hyperlink r:id="rId114" ref="J211"/>
-    <hyperlink r:id="rId115" ref="J212"/>
-    <hyperlink r:id="rId116" ref="J213"/>
-    <hyperlink r:id="rId117" ref="J214"/>
-    <hyperlink r:id="rId118" ref="J216"/>
-    <hyperlink r:id="rId119" ref="J217"/>
-    <hyperlink r:id="rId120" ref="J224"/>
-    <hyperlink r:id="rId121" ref="J248"/>
-    <hyperlink r:id="rId122" ref="J251"/>
-    <hyperlink r:id="rId123" ref="J252"/>
-    <hyperlink r:id="rId124" ref="J271"/>
-    <hyperlink r:id="rId125" ref="J278"/>
-    <hyperlink r:id="rId126" ref="J280"/>
-    <hyperlink r:id="rId127" ref="K280"/>
-    <hyperlink r:id="rId128" ref="J281"/>
-    <hyperlink r:id="rId129" ref="J284"/>
-    <hyperlink r:id="rId130" ref="J285"/>
-    <hyperlink r:id="rId131" ref="J286"/>
-    <hyperlink r:id="rId132" ref="J287"/>
-    <hyperlink r:id="rId133" ref="J289"/>
-    <hyperlink r:id="rId134" ref="J290"/>
-    <hyperlink r:id="rId135" ref="J293"/>
-    <hyperlink r:id="rId136" ref="J295"/>
-    <hyperlink r:id="rId137" ref="J296"/>
-    <hyperlink r:id="rId138" ref="J297"/>
-    <hyperlink r:id="rId139" location="person_I298580" ref="J299"/>
-    <hyperlink r:id="rId140" ref="J302"/>
+    <hyperlink r:id="rId77" ref="J135"/>
+    <hyperlink r:id="rId78" ref="J136"/>
+    <hyperlink r:id="rId79" ref="J137"/>
+    <hyperlink r:id="rId80" ref="J138"/>
+    <hyperlink r:id="rId81" ref="J142"/>
+    <hyperlink r:id="rId82" ref="J143"/>
+    <hyperlink r:id="rId83" ref="J153"/>
+    <hyperlink r:id="rId84" ref="J154"/>
+    <hyperlink r:id="rId85" ref="J155"/>
+    <hyperlink r:id="rId86" ref="J160"/>
+    <hyperlink r:id="rId87" ref="J163"/>
+    <hyperlink r:id="rId88" location="person_I298580" ref="J165"/>
+    <hyperlink r:id="rId89" ref="J166"/>
+    <hyperlink r:id="rId90" ref="J167"/>
+    <hyperlink r:id="rId91" ref="J168"/>
+    <hyperlink r:id="rId92" ref="J169"/>
+    <hyperlink r:id="rId93" ref="J170"/>
+    <hyperlink r:id="rId94" ref="K174"/>
+    <hyperlink r:id="rId95" location="person_I295072" ref="J175"/>
+    <hyperlink r:id="rId96" ref="J189"/>
+    <hyperlink r:id="rId97" ref="J190"/>
+    <hyperlink r:id="rId98" ref="J191"/>
+    <hyperlink r:id="rId99" ref="J192"/>
+    <hyperlink r:id="rId100" ref="J193"/>
+    <hyperlink r:id="rId101" ref="J194"/>
+    <hyperlink r:id="rId102" ref="J195"/>
+    <hyperlink r:id="rId103" ref="J196"/>
+    <hyperlink r:id="rId104" ref="J197"/>
+    <hyperlink r:id="rId105" ref="J198"/>
+    <hyperlink r:id="rId106" ref="J199"/>
+    <hyperlink r:id="rId107" ref="J200"/>
+    <hyperlink r:id="rId108" ref="J201"/>
+    <hyperlink r:id="rId109" ref="J202"/>
+    <hyperlink r:id="rId110" ref="J203"/>
+    <hyperlink r:id="rId111" ref="J204"/>
+    <hyperlink r:id="rId112" ref="J205"/>
+    <hyperlink r:id="rId113" ref="J206"/>
+    <hyperlink r:id="rId114" ref="J207"/>
+    <hyperlink r:id="rId115" ref="K208"/>
+    <hyperlink r:id="rId116" ref="J211"/>
+    <hyperlink r:id="rId117" ref="J212"/>
+    <hyperlink r:id="rId118" ref="J213"/>
+    <hyperlink r:id="rId119" ref="J214"/>
+    <hyperlink r:id="rId120" ref="J216"/>
+    <hyperlink r:id="rId121" ref="J217"/>
+    <hyperlink r:id="rId122" ref="J224"/>
+    <hyperlink r:id="rId123" ref="J248"/>
+    <hyperlink r:id="rId124" ref="J251"/>
+    <hyperlink r:id="rId125" ref="J252"/>
+    <hyperlink r:id="rId126" ref="J271"/>
+    <hyperlink r:id="rId127" ref="J278"/>
+    <hyperlink r:id="rId128" ref="J280"/>
+    <hyperlink r:id="rId129" ref="K280"/>
+    <hyperlink r:id="rId130" ref="J281"/>
+    <hyperlink r:id="rId131" ref="J284"/>
+    <hyperlink r:id="rId132" ref="J285"/>
+    <hyperlink r:id="rId133" ref="J286"/>
+    <hyperlink r:id="rId134" ref="J287"/>
+    <hyperlink r:id="rId135" ref="J289"/>
+    <hyperlink r:id="rId136" ref="J290"/>
+    <hyperlink r:id="rId137" ref="J293"/>
+    <hyperlink r:id="rId138" ref="J295"/>
+    <hyperlink r:id="rId139" ref="J296"/>
+    <hyperlink r:id="rId140" ref="J297"/>
+    <hyperlink r:id="rId141" location="person_I298580" ref="J299"/>
+    <hyperlink r:id="rId142" ref="J302"/>
   </hyperlinks>
-  <drawing r:id="rId141"/>
+  <drawing r:id="rId143"/>
   <tableParts count="1">
-    <tablePart r:id="rId143"/>
+    <tablePart r:id="rId145"/>
   </tableParts>
 </worksheet>
 </file>
@@ -15294,16 +15325,16 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -15314,179 +15345,179 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="B2" s="25" t="str">
         <f t="shared" ref="B2:B132" si="1">CONCATENATE(C2)</f>
         <v>Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="B3" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Basel</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="B4" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Eidgenossenschaft</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="E4" s="23"/>
       <c r="F4" s="3" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="B5" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Limmat</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="7" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="B6" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Weinfelden</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="D6" s="27"/>
       <c r="E6" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="B7" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Main</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="D7" s="27"/>
       <c r="E7" s="7" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="B8" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Zürichsee</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="D8" s="27"/>
       <c r="E8" s="7" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="B9" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Thalwil</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="B10" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Bern</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="D10" s="27"/>
       <c r="E10" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="B11" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Gottstatt</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="D11" s="27"/>
       <c r="E11" s="13"/>
@@ -15494,325 +15525,325 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="B12" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Thorberg</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="B13" s="26" t="str">
         <f t="shared" si="1"/>
         <v>London</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="B14" s="26" t="str">
         <f t="shared" si="1"/>
         <v>England</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="7" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="B15" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Bethlehem</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="B16" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Parnass </v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="7" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="B17" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Traubenberg</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="D17" s="27"/>
       <c r="E17" s="13"/>
       <c r="F17" s="3" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="B18" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Babylon</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="B19" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Canaan</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="7" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="B20" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Ägypten</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="F20" s="9"/>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="B21" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Hermon</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="D21" s="27"/>
       <c r="E21" s="7" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="B22" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Jerusalem</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
       <c r="B23" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Jordan</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="D23" s="27"/>
       <c r="E23" s="7" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="B24" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Rotes Meer</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="7" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="F24" s="9"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="B25" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Juda</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="13"/>
       <c r="F25" s="3" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="B26" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Moab</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="D26" s="27"/>
       <c r="E26" s="13"/>
       <c r="F26" s="3" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="B27" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Ammon</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="13"/>
       <c r="F27" s="3" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="B28" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Zion</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="B29" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Assur</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="D29" s="27"/>
       <c r="E29" s="13"/>
@@ -15820,181 +15851,181 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
       <c r="B30" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Israel</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="D30" s="27"/>
       <c r="E30" s="13"/>
       <c r="F30" s="3" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="B31" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Nazaret</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="D31" s="27"/>
       <c r="E31" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
       <c r="B32" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Rom</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="13"/>
       <c r="F32" s="3" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="B33" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Samaria</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="B34" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kedronbach</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="D34" s="27"/>
       <c r="E34" s="7" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="B35" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Garten von Getsemani</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="D35" s="27"/>
       <c r="E35" s="7" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="F35" s="3"/>
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="B36" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Urdorf</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="D36" s="27"/>
       <c r="E36" s="7" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="B37" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Geiren-Rein</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="D37" s="27"/>
       <c r="E37" s="7" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="F37" s="3"/>
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="B38" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Aeügst</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="B39" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Riedt</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="13"/>
@@ -16002,14 +16033,14 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="B40" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Europa</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="D40" s="27"/>
       <c r="E40" s="13"/>
@@ -16017,52 +16048,52 @@
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="B41" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Osir</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="B42" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Basadingen</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="D42" s="27"/>
       <c r="E42" s="13"/>
       <c r="F42" s="3" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
       <c r="B43" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Diessenhofen</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="13"/>
@@ -16070,50 +16101,50 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="B44" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Rhein</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="D44" s="27"/>
       <c r="E44" s="7" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="B45" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Arabisches Reich</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="D45" s="27"/>
       <c r="E45" s="13"/>
       <c r="F45" s="3" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="B46" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Libanon</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="D46" s="27"/>
       <c r="E46" s="13"/>
@@ -16121,105 +16152,105 @@
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="B47" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Emmaus</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="D47" s="27"/>
       <c r="E47" s="13"/>
       <c r="F47" s="3" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="B48" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Helikon</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="D48" s="27"/>
       <c r="E48" s="7" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="B49" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Pindos</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="D49" s="27"/>
       <c r="E49" s="7" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="B50" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Neckar</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="D50" s="27"/>
       <c r="E50" s="7" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="B51" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kurpfalz</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="D51" s="27"/>
       <c r="E51" s="13"/>
       <c r="F51" s="3" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="B52" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Eglisau</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
       <c r="D52" s="27"/>
       <c r="E52" s="13"/>
@@ -16227,14 +16258,14 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="B53" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Altenklingen</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="D53" s="27"/>
       <c r="E53" s="13"/>
@@ -16242,14 +16273,14 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="B54" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Altorff</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="D54" s="27"/>
       <c r="E54" s="13"/>
@@ -16257,65 +16288,65 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="B55" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Glarus</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="D55" s="27"/>
       <c r="E55" s="13"/>
       <c r="F55" s="3" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="B56" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Reformierte Kirche Berg am Irchel</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="3"/>
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
       <c r="B57" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Sodom</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="D57" s="27"/>
       <c r="E57" s="13"/>
       <c r="F57" s="3" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="B58" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Haus zur Sonnenblume</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="D58" s="27"/>
       <c r="E58" s="13"/>
@@ -16323,126 +16354,126 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="B59" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Geissturm</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
       <c r="D59" s="27"/>
       <c r="E59" s="13"/>
       <c r="F59" s="3" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="B60" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Konstantinopel</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F60" s="3"/>
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
       <c r="B61" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Stein am Rhein</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1457</v>
+        <v>1460</v>
       </c>
       <c r="D61" s="27"/>
       <c r="E61" s="13"/>
       <c r="F61" s="3" t="s">
-        <v>1458</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="B62" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Marburg</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
       <c r="D62" s="27"/>
       <c r="E62" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
       <c r="B63" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Elbląg</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
       <c r="B64" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Preussen</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="D64" s="27"/>
       <c r="E64" s="7" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="B65" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Heilbäder Baden</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="D65" s="27"/>
       <c r="E65" s="13"/>
@@ -16450,31 +16481,31 @@
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
       <c r="B66" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Bad Schinznach</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
       <c r="D66" s="27"/>
       <c r="E66" s="13"/>
       <c r="F66" s="3" t="s">
-        <v>1473</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
       <c r="B67" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Gyrenbad</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="D67" s="27"/>
       <c r="E67" s="13"/>
@@ -16482,48 +16513,48 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="B68" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Wängibad</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="D68" s="27"/>
       <c r="E68" s="13"/>
       <c r="F68" s="8" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="B69" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Aeugst</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
       <c r="D69" s="27"/>
       <c r="E69" s="13"/>
       <c r="F69" s="3" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="B70" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Bassersdorf</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="D70" s="27"/>
       <c r="E70" s="13"/>
@@ -16531,14 +16562,14 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
       <c r="B71" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Hauptwil</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
       <c r="D71" s="27"/>
       <c r="E71" s="13"/>
@@ -16546,14 +16577,14 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>1485</v>
+        <v>1488</v>
       </c>
       <c r="B72" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Schaffhausen</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
       <c r="D72" s="27"/>
       <c r="E72" s="13"/>
@@ -16561,133 +16592,133 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
       <c r="B73" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Wädenswil</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1488</v>
+        <v>1491</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="7" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="F73" s="3"/>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="B74" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Freiamt</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="7" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="F74" s="3"/>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="B75" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Grüningen</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="13"/>
       <c r="F75" s="3" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="B76" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kefikon</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="7" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="F76" s="3"/>
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B77" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Maienfeld</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="7" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="F77" s="3"/>
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="B78" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Schloss Greifensee</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="7" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="F78" s="3"/>
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="B79" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Lindenhof (Zürich)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="13"/>
       <c r="F79" s="3" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
       <c r="B80" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Galg-Brunnen (Zürich)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="13"/>
@@ -16695,48 +16726,48 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="B81" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Altes Kornhaus (Zürich)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="7" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="F81" s="3"/>
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="B82" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Sparrenberg (Zürich)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="7" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="F82" s="3"/>
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
       <c r="B83" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Thurgau</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="13"/>
@@ -16744,14 +16775,14 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="B84" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Niederlande</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="13"/>
@@ -16759,31 +16790,31 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
       <c r="B85" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Holland</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="D85" s="27"/>
       <c r="E85" s="13"/>
       <c r="F85" s="3" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>1518</v>
+        <v>1521</v>
       </c>
       <c r="B86" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Wigoltingen</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1519</v>
+        <v>1522</v>
       </c>
       <c r="D86" s="27"/>
       <c r="E86" s="13"/>
@@ -16791,291 +16822,291 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
       <c r="B87" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kastalische Quelle</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
       <c r="D87" s="27"/>
       <c r="E87" s="7" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
       <c r="B88" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Lägern</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
       <c r="D88" s="27"/>
       <c r="E88" s="7" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="F88" s="3"/>
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
       <c r="B89" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Texel</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
       <c r="D89" s="27"/>
       <c r="E89" s="13"/>
       <c r="F89" s="3" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
       <c r="B90" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Vlieland</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
       <c r="D90" s="27"/>
       <c r="E90" s="13"/>
       <c r="F90" s="3" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
       <c r="B91" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Indien</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1531</v>
+        <v>1534</v>
       </c>
       <c r="D91" s="27"/>
       <c r="E91" s="7" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="F91" s="3"/>
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>1532</v>
+        <v>1535</v>
       </c>
       <c r="B92" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Wien</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>1533</v>
+        <v>1536</v>
       </c>
       <c r="D92" s="27"/>
       <c r="E92" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F92" s="3"/>
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
       <c r="B93" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Deutschland</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="D93" s="27"/>
       <c r="E93" s="7" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="F93" s="3"/>
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
       <c r="B94" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Ölberg</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1537</v>
+        <v>1540</v>
       </c>
       <c r="D94" s="27"/>
       <c r="E94" s="7" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="F94" s="3"/>
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>1538</v>
+        <v>1541</v>
       </c>
       <c r="B95" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Dietikon</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1539</v>
+        <v>1542</v>
       </c>
       <c r="D95" s="27"/>
       <c r="E95" s="7" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="B96" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Winterthur</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="D96" s="27"/>
       <c r="E96" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F96" s="3"/>
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="B97" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Pfalz</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1544</v>
+        <v>1547</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="7" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="F97" s="3"/>
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>1545</v>
+        <v>1548</v>
       </c>
       <c r="B98" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Edenkoben</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1546</v>
+        <v>1549</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="7" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>1547</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>1548</v>
+        <v>1551</v>
       </c>
       <c r="B99" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Wüste Juda</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1549</v>
+        <v>1552</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>1551</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>1552</v>
+        <v>1555</v>
       </c>
       <c r="B100" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Greifensee</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1553</v>
+        <v>1556</v>
       </c>
       <c r="D100" s="27"/>
       <c r="E100" s="7" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
       <c r="F100" s="3"/>
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
       <c r="B101" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Lichtensteig</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="D101" s="27"/>
       <c r="E101" s="7" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="F101" s="3"/>
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="B102" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Golgotha</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="E102" s="13"/>
       <c r="F102" s="3" t="s">
-        <v>1559</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="3" t="s">
-        <v>1560</v>
+        <v>1563</v>
       </c>
       <c r="B103" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17088,7 +17119,7 @@
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="B104" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17101,7 +17132,7 @@
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="3" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="B105" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17114,7 +17145,7 @@
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="B106" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17127,7 +17158,7 @@
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="3" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="B107" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17140,7 +17171,7 @@
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="B108" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17153,7 +17184,7 @@
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="3" t="s">
-        <v>1566</v>
+        <v>1569</v>
       </c>
       <c r="B109" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17166,7 +17197,7 @@
     </row>
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>1567</v>
+        <v>1570</v>
       </c>
       <c r="B110" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17179,7 +17210,7 @@
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="3" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
       <c r="B111" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17192,7 +17223,7 @@
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="B112" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17205,7 +17236,7 @@
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="3" t="s">
-        <v>1570</v>
+        <v>1573</v>
       </c>
       <c r="B113" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17218,7 +17249,7 @@
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>1571</v>
+        <v>1574</v>
       </c>
       <c r="B114" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17231,7 +17262,7 @@
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="3" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="B115" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17244,7 +17275,7 @@
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>1573</v>
+        <v>1576</v>
       </c>
       <c r="B116" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17257,7 +17288,7 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="B117" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17270,7 +17301,7 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="B118" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17283,7 +17314,7 @@
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="B119" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17296,7 +17327,7 @@
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="B120" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17309,7 +17340,7 @@
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="B121" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17322,7 +17353,7 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="B122" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17335,7 +17366,7 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="B123" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17348,7 +17379,7 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
       <c r="B124" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17361,7 +17392,7 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="B125" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17374,7 +17405,7 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="B126" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17387,7 +17418,7 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>1584</v>
+        <v>1587</v>
       </c>
       <c r="B127" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17400,7 +17431,7 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="B128" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17413,7 +17444,7 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
       <c r="B129" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17426,7 +17457,7 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>1587</v>
+        <v>1590</v>
       </c>
       <c r="B130" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17439,7 +17470,7 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="3" t="s">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="B131" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17452,7 +17483,7 @@
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>1589</v>
+        <v>1592</v>
       </c>
       <c r="B132" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17500,25 +17531,25 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1590</v>
+        <v>1593</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1595</v>
+        <v>1598</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
@@ -17529,109 +17560,109 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="B2" s="28" t="str">
         <f t="shared" ref="B2:B40" si="1">CONCATENATE(C2)</f>
         <v>Teutsche Gedichte</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1597</v>
+        <v>1600</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="I2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="B3" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Die Krafft der Gottseligkeit</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="B4" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Archetypi homiliarum in quatuor evangelia dn. nostri Iesu Christi</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="10" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="B5" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Der Psalter dess Königlichen Propheten Dauids/ Jn deutsche reymen verstendiglich vnd deutlich gebracht/ mit vorgehender anzeigung der reymen weise/ auch eines jeden Psalmes Jnhalt</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1617</v>
+        <v>1620</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="13"/>
@@ -17639,73 +17670,73 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="B6" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Hundert christliche Fäst-Predigen</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1622</v>
+        <v>1625</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1624</v>
+        <v>1627</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="B7" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Spiegel der Unermesslichen Gnad Gottes gegen den rewenden bussfertigen Sünderen/ Jn XLV. Predigen vber das XV. capitel Lucae/ vom verlohrnen Schaaf/ Pfenning/ vnd Sohn verfasset</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="B8" s="28" t="str">
         <f t="shared" si="1"/>
         <v>verteütschte Rueh- oder Fridens-uebung</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1634</v>
+        <v>1637</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="27"/>
@@ -17715,98 +17746,98 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="B9" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Nähefelser-Fahrt: in zehen erbaulichen Jahrzeit-Predigen zu schuldigem Danck dem Höhesten für den im Jahr 1388 gemeinen Landleuthen dess lobl. Eydgnössischen Bundorths Glarus wider ihre Feind bey und umb Nähefels verliehenen Wundersieg </v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1638</v>
+        <v>1641</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="10" t="s">
-        <v>1640</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1641</v>
+        <v>1644</v>
       </c>
       <c r="B10" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Die vier Haubtpuncten der christlichen seligmachenden Religion: auf alle Sontag des gantzen Jahrs ordenlich abgetheilt, grundtlich nach der heiligen Schrifft erklärt und zur Erbawung gerichtet </v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>1646</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1647</v>
+        <v>1650</v>
       </c>
       <c r="B11" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Architectura von Vestungen</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1649</v>
+        <v>1652</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1650</v>
+        <v>1653</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="8" t="s">
-        <v>1651</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="B12" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Buech der Freunden Stammen</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1653</v>
+        <v>1656</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="9"/>
@@ -17817,42 +17848,42 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1654</v>
+        <v>1657</v>
       </c>
       <c r="B13" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Christen-Spiegel, das ist, Bedenkliche Erinnerungen über die Beruoffspflichten aller Ständen </v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1655</v>
+        <v>1658</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="B14" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Viergeticht</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="9"/>
@@ -17863,14 +17894,14 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="B15" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Regentenspiegel</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="9"/>
@@ -17881,18 +17912,18 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
       <c r="B16" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Türckischer Jammerspiegel</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="3" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="F16" s="27"/>
       <c r="G16" s="9"/>
@@ -17901,292 +17932,292 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
       <c r="B17" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Theatrum concionum sacr. topicum</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>1669</v>
+        <v>1672</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="12" t="s">
-        <v>1672</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
       <c r="B18" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Seelen-Angst Christi</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1674</v>
+        <v>1677</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1675</v>
+        <v>1678</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="8" t="s">
-        <v>1677</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1678</v>
+        <v>1681</v>
       </c>
       <c r="B19" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Dichterische Versuchgabe</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1679</v>
+        <v>1682</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1680</v>
+        <v>1683</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1681</v>
+        <v>1684</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="12" t="s">
-        <v>1683</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1684</v>
+        <v>1687</v>
       </c>
       <c r="B20" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Kriegs-Büchlein</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1686</v>
+        <v>1689</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1687</v>
+        <v>1690</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="12" t="s">
-        <v>1689</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
       <c r="B21" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Außerleßne Psalmen Davids</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>1692</v>
+        <v>1695</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="10" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1695</v>
+        <v>1698</v>
       </c>
       <c r="B22" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Sterbensspiegel/ das ist sonnenklare Vorstellung menschlicher Nichtigkeit durch alle Staend und Geschlechter</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1632</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>1696</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>1697</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>1629</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>1291</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>1693</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>1698</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1699</v>
+        <v>1702</v>
       </c>
       <c r="B23" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Warhaffte/ vnd in Gottes Wort wol gegründte Widerlegung Des newlich im Truck außgegangnen ohn-Catholischen Gesprächs von Religion oder Glaubens sachen/ geneñt der Augenspiegel</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1701</v>
+        <v>1704</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1704</v>
+        <v>1707</v>
       </c>
       <c r="B24" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Augspiegels Wahrer Religion Erster Theil</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1707</v>
+        <v>1710</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1708</v>
+        <v>1711</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1709</v>
+        <v>1712</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>1710</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1711</v>
+        <v>1714</v>
       </c>
       <c r="B25" s="28" t="str">
         <f t="shared" si="1"/>
         <v>De kracht der Godsaligheyt</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1712</v>
+        <v>1715</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1714</v>
+        <v>1717</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>1715</v>
+        <v>1718</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>1716</v>
+        <v>1719</v>
       </c>
       <c r="H25" s="13"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1717</v>
+        <v>1720</v>
       </c>
       <c r="B26" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Christlicher Wandersmann</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1718</v>
+        <v>1721</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>1720</v>
+        <v>1723</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>1721</v>
+        <v>1724</v>
       </c>
       <c r="H26" s="13"/>
       <c r="I26" s="8" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1723</v>
+        <v>1726</v>
       </c>
       <c r="B27" s="28" t="str">
         <f t="shared" si="1"/>
         <v>"Bernerischer Apothecker-Tax"</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1724</v>
+        <v>1727</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>615</v>
@@ -18196,40 +18227,40 @@
       <c r="G27" s="9"/>
       <c r="H27" s="13"/>
       <c r="I27" s="3" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1726</v>
+        <v>1729</v>
       </c>
       <c r="B28" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Wolriechende geistliche Violblumen für eingründige Seelen</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1727</v>
+        <v>1730</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>1692</v>
+        <v>1695</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>1729</v>
+        <v>1732</v>
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="12" t="s">
-        <v>1730</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
       <c r="B29" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18245,7 +18276,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1732</v>
+        <v>1735</v>
       </c>
       <c r="B30" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18261,7 +18292,7 @@
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="B31" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18277,7 +18308,7 @@
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="B32" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18293,7 +18324,7 @@
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
       <c r="B33" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18309,7 +18340,7 @@
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
       <c r="B34" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18325,7 +18356,7 @@
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="B35" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18341,7 +18372,7 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
       <c r="B36" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18357,7 +18388,7 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
       <c r="B37" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18373,7 +18404,7 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
       <c r="B38" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18389,7 +18420,7 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
       <c r="B39" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18405,7 +18436,7 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="B40" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18469,19 +18500,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -18489,69 +18520,69 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
       <c r="B2" s="28" t="str">
         <f t="shared" ref="B2:B34" si="1">CONCATENATE(C2)</f>
         <v>Rat Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
       <c r="D2" s="27"/>
       <c r="E2" s="29" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="B3" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Fruchtbringende Gesellschaft</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>1751</v>
+        <v>1754</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="B4" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Deutschgesinnte Genossenschaft (Lilien-Zunft)</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1754</v>
+        <v>1757</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1755</v>
+        <v>1758</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="B5" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Parthenicum</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="13"/>
@@ -18559,172 +18590,172 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="B6" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Carolinum Zürich</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1759</v>
+        <v>1762</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="3" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="B7" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Sanhedrin</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1764</v>
+        <v>1767</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="3" t="s">
-        <v>1765</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1766</v>
+        <v>1769</v>
       </c>
       <c r="B8" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Bürgerbibliothek Zürich</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1767</v>
+        <v>1770</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="3" t="s">
-        <v>1769</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1770</v>
+        <v>1773</v>
       </c>
       <c r="B9" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Grossmünster Zürich</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1771</v>
+        <v>1774</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1772</v>
+        <v>1775</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1774</v>
+        <v>1777</v>
       </c>
       <c r="B10" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Fraumünster Zürich</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1775</v>
+        <v>1778</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="3" t="s">
-        <v>1777</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1778</v>
+        <v>1781</v>
       </c>
       <c r="B11" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Philipps-Universität Marburg</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1780</v>
+        <v>1783</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="9"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1781</v>
+        <v>1784</v>
       </c>
       <c r="B12" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Kartäuser</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1782</v>
+        <v>1785</v>
       </c>
       <c r="D12" s="21"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1784</v>
+        <v>1787</v>
       </c>
       <c r="B13" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Alumnorum</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1785</v>
+        <v>1788</v>
       </c>
       <c r="D13" s="30">
         <v>1.15712505E9</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="3" t="s">
-        <v>1786</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1787</v>
+        <v>1790</v>
       </c>
       <c r="B14" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Schützengesellschaft der Stadt Zürich</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1788</v>
+        <v>1791</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>1789</v>
+        <v>1792</v>
       </c>
       <c r="E14" s="13"/>
       <c r="F14" s="9"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1790</v>
+        <v>1793</v>
       </c>
       <c r="B15" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18737,7 +18768,7 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1791</v>
+        <v>1794</v>
       </c>
       <c r="B16" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18750,7 +18781,7 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1792</v>
+        <v>1795</v>
       </c>
       <c r="B17" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18763,7 +18794,7 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1793</v>
+        <v>1796</v>
       </c>
       <c r="B18" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18776,7 +18807,7 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1794</v>
+        <v>1797</v>
       </c>
       <c r="B19" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18789,7 +18820,7 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1795</v>
+        <v>1798</v>
       </c>
       <c r="B20" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18802,7 +18833,7 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1796</v>
+        <v>1799</v>
       </c>
       <c r="B21" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18815,7 +18846,7 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="B22" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18828,7 +18859,7 @@
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1798</v>
+        <v>1801</v>
       </c>
       <c r="B23" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18841,7 +18872,7 @@
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1799</v>
+        <v>1802</v>
       </c>
       <c r="B24" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18854,7 +18885,7 @@
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1800</v>
+        <v>1803</v>
       </c>
       <c r="B25" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18867,7 +18898,7 @@
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1801</v>
+        <v>1804</v>
       </c>
       <c r="B26" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18880,7 +18911,7 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1802</v>
+        <v>1805</v>
       </c>
       <c r="B27" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18893,7 +18924,7 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1803</v>
+        <v>1806</v>
       </c>
       <c r="B28" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18906,7 +18937,7 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1804</v>
+        <v>1807</v>
       </c>
       <c r="B29" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18919,7 +18950,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="B30" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18932,7 +18963,7 @@
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1806</v>
+        <v>1809</v>
       </c>
       <c r="B31" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18945,7 +18976,7 @@
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1807</v>
+        <v>1810</v>
       </c>
       <c r="B32" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18958,7 +18989,7 @@
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1808</v>
+        <v>1811</v>
       </c>
       <c r="B33" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18971,7 +19002,7 @@
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1809</v>
+        <v>1812</v>
       </c>
       <c r="B34" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19012,19 +19043,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1811</v>
+        <v>1814</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1812</v>
+        <v>1815</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -19032,26 +19063,26 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1814</v>
+        <v>1817</v>
       </c>
       <c r="B2" s="25" t="str">
         <f t="shared" ref="B2:B8" si="1">CONCATENATE(C2)</f>
         <v>Runs</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1815</v>
+        <v>1818</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="E2" s="31" t="s">
-        <v>1817</v>
+        <v>1820</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1818</v>
+        <v>1821</v>
       </c>
       <c r="B3" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19064,7 +19095,7 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="B4" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19077,7 +19108,7 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="B5" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19090,7 +19121,7 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1821</v>
+        <v>1824</v>
       </c>
       <c r="B6" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19103,7 +19134,7 @@
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="B7" s="25" t="str">
         <f t="shared" si="1"/>
@@ -19116,7 +19147,7 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1823</v>
+        <v>1826</v>
       </c>
       <c r="B8" s="25" t="str">
         <f t="shared" si="1"/>

--- a/gsheet/xlsx/entities.xlsx
+++ b/gsheet/xlsx/entities.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="1901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2438" uniqueCount="1903">
   <si>
     <t>Person-ID</t>
   </si>
@@ -223,7 +223,26 @@
     <t>Pfarrer zu Thalwil</t>
   </si>
   <si>
-    <t>https://suche.staatsarchiv.djiktzh.ch/detail.aspx?ID=1960657</t>
+    <r>
+      <rPr>
+        <color rgb="FF434343"/>
+        <u/>
+      </rPr>
+      <t>https://suche.staatsarchiv.djiktzh.ch/detail.aspx?ID=1960657</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>http://www.hfls.ch/humo-gen/family/1/F111542?main_person=I322385</t>
+    </r>
   </si>
   <si>
     <t>person_010</t>
@@ -2363,9 +2382,22 @@
     <t>Herder</t>
   </si>
   <si>
+    <t>1089544901</t>
+  </si>
+  <si>
+    <t>Pfarrer und Konrektor in der Pfalz</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>http://www.hfls.ch/humo-gen/family/1/F137889?main_person=I317050</t>
+    </r>
     <r>
       <rPr/>
-      <t xml:space="preserve">evtl. </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -2379,15 +2411,25 @@
     <t>person_157</t>
   </si>
   <si>
-    <t>E. W.</t>
-  </si>
-  <si>
-    <t>Frau des H. H. H.; evtl. Wüst?</t>
+    <t>Wüst</t>
+  </si>
+  <si>
+    <t>Ehefrau von Hans Heinrich Herder</t>
   </si>
   <si>
     <r>
-      <rPr/>
-      <t xml:space="preserve">evtl. </t>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>http://www.hfls.ch/humo-gen/family/1/F137889?main_person=I375790</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+        <u/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -2404,7 +2446,29 @@
     <t>Koller</t>
   </si>
   <si>
-    <t>Frau des Pfarrers Georg Müller</t>
+    <t>Zweite Ehefrau von Georg Müller</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF434343"/>
+        <u/>
+      </rPr>
+      <t>https://suche.staatsarchiv.djiktzh.ch/detail.aspx?ID=1960657</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1F1F1F"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>http://www.hfls.ch/humo-gen/family/1/F145987?main_person=I324410</t>
+    </r>
   </si>
   <si>
     <t>person_161</t>
@@ -3395,7 +3459,7 @@
     <t>person_229</t>
   </si>
   <si>
-    <t>Obmann, Bürgermeister 1655-1669</t>
+    <t>Bürgermeister von Zürich, Obmann gemeiner Klöster, Zunftmeister der Widderzunft</t>
   </si>
   <si>
     <t>person_230</t>
@@ -3895,12 +3959,6 @@
     <t>person_277</t>
   </si>
   <si>
-    <t>1089544901</t>
-  </si>
-  <si>
-    <t>Pfarrer und Konrektor in der Pfalz</t>
-  </si>
-  <si>
     <t>person_278</t>
   </si>
   <si>
@@ -4758,6 +4816,9 @@
   </si>
   <si>
     <t>Libanon</t>
+  </si>
+  <si>
+    <t>Staat in Vorderasien</t>
   </si>
   <si>
     <t>place_046</t>
@@ -7039,7 +7100,7 @@
       <c r="I10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="10" t="s">
         <v>68</v>
       </c>
       <c r="K10" s="9"/>
@@ -11177,91 +11238,107 @@
       </c>
       <c r="B153" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Herder,  (-)</v>
+        <v>Herder, Hans Heinrich (1629-1665)</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="D153" s="3"/>
-      <c r="E153" s="5"/>
-      <c r="F153" s="5"/>
-      <c r="G153" s="9"/>
-      <c r="H153" s="3"/>
+      <c r="D153" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E153" s="5">
+        <v>1629.0</v>
+      </c>
+      <c r="F153" s="5">
+        <v>1665.0</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>741</v>
+      </c>
       <c r="I153" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J153" s="10" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K153" s="9"/>
     </row>
     <row r="154" ht="22.5" customHeight="1">
       <c r="A154" s="3" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B154" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>E. W.,  (-)</v>
+        <v>Wüst, Elisabeth (-1699)</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="D154" s="3"/>
+        <v>744</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>713</v>
+      </c>
       <c r="E154" s="5"/>
-      <c r="F154" s="5"/>
+      <c r="F154" s="5">
+        <v>1699.0</v>
+      </c>
       <c r="G154" s="9"/>
       <c r="H154" s="3" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="I154" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J154" s="10" t="s">
-        <v>744</v>
+      <c r="J154" s="14" t="s">
+        <v>746</v>
       </c>
       <c r="K154" s="9"/>
     </row>
     <row r="155" ht="22.5" customHeight="1">
       <c r="A155" s="3" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B155" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Koller, Elisabeth (-)</v>
+        <v>Koller, Elisabeth (1622-)</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="E155" s="5"/>
+      <c r="E155" s="5">
+        <v>1622.0</v>
+      </c>
       <c r="F155" s="5"/>
       <c r="G155" s="9"/>
       <c r="H155" s="3" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="I155" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J155" s="8" t="s">
-        <v>68</v>
+      <c r="J155" s="10" t="s">
+        <v>750</v>
       </c>
       <c r="K155" s="9"/>
     </row>
     <row r="156" ht="22.5" customHeight="1">
       <c r="A156" s="3" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="B156" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lobwasser, Ambrosius (1515-1585)</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="E156" s="5">
         <v>1515.0</v>
@@ -11270,10 +11347,10 @@
         <v>1585.0</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="I156" s="7" t="s">
         <v>16</v>
@@ -11283,14 +11360,14 @@
     </row>
     <row r="157" ht="22.5" customHeight="1">
       <c r="A157" s="3" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B157" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vollenweider, Jakob (1594-1647)</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>330</v>
@@ -11302,10 +11379,10 @@
         <v>1647.0</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="I157" s="7" t="s">
         <v>16</v>
@@ -11315,7 +11392,7 @@
     </row>
     <row r="158" ht="22.5" customHeight="1">
       <c r="A158" s="3" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B158" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11325,7 +11402,7 @@
         <v>232</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="E158" s="5">
         <v>1606.0</v>
@@ -11334,7 +11411,7 @@
         <v>1660.0</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="H158" s="3" t="s">
         <v>235</v>
@@ -11347,14 +11424,14 @@
     </row>
     <row r="159" ht="22.5" customHeight="1">
       <c r="A159" s="3" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="B159" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Burkhard, Hans Konrad (1613-1681)</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>696</v>
@@ -11366,10 +11443,10 @@
         <v>1681.0</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="I159" s="7" t="s">
         <v>16</v>
@@ -11379,14 +11456,14 @@
     </row>
     <row r="160" ht="22.5" customHeight="1">
       <c r="A160" s="3" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B160" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ardüser, Johann (1585-1665)</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>109</v>
@@ -11398,40 +11475,40 @@
         <v>1665.0</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="I160" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J160" s="12" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="K160" s="9"/>
     </row>
     <row r="161" ht="22.5" customHeight="1">
       <c r="A161" s="3" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B161" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hegner, Diethelm  (-)</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
       <c r="G161" s="3" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="I161" s="7" t="s">
         <v>16</v>
@@ -11441,17 +11518,17 @@
     </row>
     <row r="162" ht="22.5" customHeight="1">
       <c r="A162" s="3" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B162" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Trigland, Jacobus (1583-1654)</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="E162" s="18">
         <v>1583.0</v>
@@ -11460,10 +11537,10 @@
         <v>1654.0</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="I162" s="7" t="s">
         <v>16</v>
@@ -11473,17 +11550,17 @@
     </row>
     <row r="163" ht="22.5" customHeight="1">
       <c r="A163" s="3" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="B163" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwinger, Theodor (?) (1597-1654)</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="E163" s="5">
         <v>1597.0</v>
@@ -11492,32 +11569,32 @@
         <v>1654.0</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="I163" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J163" s="10" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="K163" s="3"/>
     </row>
     <row r="164" ht="22.5" customHeight="1">
       <c r="A164" s="3" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B164" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Genath, Johann Jacob (1582-1654)</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="E164" s="5">
         <v>1582.0</v>
@@ -11526,10 +11603,10 @@
         <v>1654.0</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="I164" s="7" t="s">
         <v>16</v>
@@ -11539,39 +11616,39 @@
     </row>
     <row r="165" ht="22.5" customHeight="1">
       <c r="A165" s="3" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="B165" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Escher vom Luchs‏, Johannes (‎1646-1659)</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>126</v>
       </c>
       <c r="E165" s="19" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="F165" s="5">
         <v>1659.0</v>
       </c>
       <c r="G165" s="9"/>
       <c r="H165" s="3" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="I165" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J165" s="10" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="K165" s="9"/>
     </row>
     <row r="166" ht="22.5" customHeight="1">
       <c r="A166" s="3" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B166" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11581,7 +11658,7 @@
         <v>662</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="E166" s="5">
         <v>1578.0</v>
@@ -11590,22 +11667,22 @@
         <v>1631.0</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="I166" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J166" s="10" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="K166" s="9"/>
     </row>
     <row r="167" ht="22.5" customHeight="1">
       <c r="A167" s="3" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B167" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11624,29 +11701,29 @@
         <v>1641.0</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="I167" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J167" s="10" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="K167" s="9"/>
     </row>
     <row r="168" ht="22.5" customHeight="1">
       <c r="A168" s="3" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B168" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spörri, Felix (1581-1643)</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>90</v>
@@ -11658,24 +11735,24 @@
         <v>1643.0</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="I168" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J168" s="8" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="K168" s="3" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="169" ht="22.5" customHeight="1">
       <c r="A169" s="3" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="B169" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11685,7 +11762,7 @@
         <v>12</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E169" s="5">
         <v>1604.0</v>
@@ -11701,20 +11778,20 @@
         <v>16</v>
       </c>
       <c r="J169" s="8" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="K169" s="9"/>
     </row>
     <row r="170" ht="22.5" customHeight="1">
       <c r="A170" s="3" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="B170" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther, Rudolf (1519-1586)</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>146</v>
@@ -11726,38 +11803,38 @@
         <v>1586.0</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="I170" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J170" s="10" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="K170" s="9"/>
     </row>
     <row r="171" ht="22.5" customHeight="1">
       <c r="A171" s="3" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B171" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Weiss, Caspar (-)</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="E171" s="20"/>
       <c r="F171" s="21"/>
       <c r="G171" s="9"/>
       <c r="H171" s="22" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="I171" s="7" t="s">
         <v>16</v>
@@ -11767,7 +11844,7 @@
     </row>
     <row r="172" ht="22.5" customHeight="1">
       <c r="A172" s="3" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B172" s="4" t="str">
         <f t="shared" si="1"/>
@@ -11781,7 +11858,7 @@
       <c r="F172" s="21"/>
       <c r="G172" s="9"/>
       <c r="H172" s="22" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="I172" s="7" t="s">
         <v>16</v>
@@ -11791,21 +11868,21 @@
     </row>
     <row r="173" ht="22.5" customHeight="1">
       <c r="A173" s="3" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="B173" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bas,  (-)</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="20"/>
       <c r="F173" s="21"/>
       <c r="G173" s="9"/>
       <c r="H173" s="3" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="I173" s="23"/>
       <c r="J173" s="9"/>
@@ -11813,82 +11890,82 @@
     </row>
     <row r="174" ht="22.5" customHeight="1">
       <c r="A174" s="3" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B174" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gw., H. H. J. (-)</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E174" s="20"/>
       <c r="F174" s="21"/>
       <c r="G174" s="9"/>
       <c r="H174" s="3" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="I174" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J174" s="9"/>
       <c r="K174" s="10" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
     </row>
     <row r="175" ht="22.5" customHeight="1">
       <c r="A175" s="3" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B175" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hofmeister, Johann (‎1622-‎1656‎)</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>109</v>
       </c>
       <c r="E175" s="19" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="F175" s="19" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="G175" s="9"/>
       <c r="H175" s="3" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="I175" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J175" s="8" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="K175" s="9"/>
     </row>
     <row r="176" ht="22.5" customHeight="1">
       <c r="A176" s="3" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B176" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Cyrene, Simon von (-)</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E176" s="20"/>
       <c r="F176" s="21"/>
       <c r="G176" s="3" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>258</v>
@@ -11901,20 +11978,20 @@
     </row>
     <row r="177" ht="22.5" customHeight="1">
       <c r="A177" s="3" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B177" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Thomas,  (-)</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="20"/>
       <c r="F177" s="21"/>
       <c r="G177" s="3" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="H177" s="3" t="s">
         <v>354</v>
@@ -11927,23 +12004,23 @@
     </row>
     <row r="178" ht="22.5" customHeight="1">
       <c r="A178" s="3" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="B178" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Phaeton,  (-)</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="20"/>
       <c r="F178" s="21"/>
       <c r="G178" s="3" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="I178" s="7" t="s">
         <v>240</v>
@@ -11953,14 +12030,14 @@
     </row>
     <row r="179" ht="22.5" customHeight="1">
       <c r="A179" s="3" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B179" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lukas,  (-)</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="D179" s="3"/>
       <c r="E179" s="20"/>
@@ -11977,23 +12054,23 @@
     </row>
     <row r="180" ht="22.5" customHeight="1">
       <c r="A180" s="3" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B180" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Athene,  (-)</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D180" s="3"/>
       <c r="E180" s="20"/>
       <c r="F180" s="21"/>
       <c r="G180" s="3" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="I180" s="7" t="s">
         <v>240</v>
@@ -12003,23 +12080,23 @@
     </row>
     <row r="181" ht="22.5" customHeight="1">
       <c r="A181" s="3" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B181" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bacchus,  (-)</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="D181" s="3"/>
       <c r="E181" s="20"/>
       <c r="F181" s="21"/>
       <c r="G181" s="3" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="I181" s="7" t="s">
         <v>240</v>
@@ -12029,23 +12106,23 @@
     </row>
     <row r="182" ht="22.5" customHeight="1">
       <c r="A182" s="3" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="B182" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Darius I.,  (-)</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="20"/>
       <c r="F182" s="21"/>
       <c r="G182" s="3" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="I182" s="7" t="s">
         <v>16</v>
@@ -12055,23 +12132,23 @@
     </row>
     <row r="183" ht="22.5" customHeight="1">
       <c r="A183" s="3" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B183" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kyros II.,  (-)</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="D183" s="3"/>
       <c r="E183" s="20"/>
       <c r="F183" s="21"/>
       <c r="G183" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="H183" s="3" t="s">
         <v>864</v>
-      </c>
-      <c r="H183" s="3" t="s">
-        <v>861</v>
       </c>
       <c r="I183" s="7" t="s">
         <v>16</v>
@@ -12081,25 +12158,25 @@
     </row>
     <row r="184" ht="22.5" customHeight="1">
       <c r="A184" s="3" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="B184" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hippo, Augustinus von (-)</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="E184" s="20"/>
       <c r="F184" s="21"/>
       <c r="G184" s="3" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="I184" s="7" t="s">
         <v>16</v>
@@ -12109,23 +12186,23 @@
     </row>
     <row r="185" ht="22.5" customHeight="1">
       <c r="A185" s="3" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B185" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lazarus,  (-)</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="D185" s="3"/>
       <c r="E185" s="20"/>
       <c r="F185" s="21"/>
       <c r="G185" s="3" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="I185" s="7" t="s">
         <v>258</v>
@@ -12135,23 +12212,23 @@
     </row>
     <row r="186" ht="22.5" customHeight="1">
       <c r="A186" s="3" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B186" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lot,  (-)</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="20"/>
       <c r="F186" s="21"/>
       <c r="G186" s="3" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="I186" s="7" t="s">
         <v>258</v>
@@ -12161,17 +12238,17 @@
     </row>
     <row r="187" ht="22.5" customHeight="1">
       <c r="A187" s="3" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="B187" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gyger, Johann Rudolf (1603-1662)</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="E187" s="5">
         <v>1603.0</v>
@@ -12180,10 +12257,10 @@
         <v>1662.0</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="I187" s="7" t="s">
         <v>16</v>
@@ -12193,7 +12270,7 @@
     </row>
     <row r="188" ht="22.5" customHeight="1">
       <c r="A188" s="3" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B188" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12206,16 +12283,16 @@
         <v>13</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="F188" s="5">
         <v>1690.0</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="I188" s="7" t="s">
         <v>16</v>
@@ -12225,17 +12302,17 @@
     </row>
     <row r="189" ht="22.5" customHeight="1">
       <c r="A189" s="3" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="B189" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bachofen, Johann Ulrich (1643-1700)</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="E189" s="5">
         <v>1643.0</v>
@@ -12244,29 +12321,29 @@
         <v>1700.0</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="I189" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J189" s="10" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="K189" s="9"/>
     </row>
     <row r="190" ht="22.5" customHeight="1">
       <c r="A190" s="3" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B190" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grebel, Hans Konrad (1615-1674)</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="D190" s="3" t="s">
         <v>696</v>
@@ -12278,61 +12355,61 @@
         <v>1674.0</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="I190" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J190" s="8" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="K190" s="9"/>
     </row>
     <row r="191" ht="22.5" customHeight="1">
       <c r="A191" s="3" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B191" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gossweiler, Emerentia (1620-‎1686)</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="E191" s="5">
         <v>1620.0</v>
       </c>
       <c r="F191" s="19" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="G191" s="9"/>
       <c r="H191" s="3" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="I191" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J191" s="10" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="K191" s="9"/>
     </row>
     <row r="192" ht="22.5" customHeight="1">
       <c r="A192" s="3" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B192" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lochmann, Heinrich (1613-1667)</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>38</v>
@@ -12344,29 +12421,29 @@
         <v>1667.0</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J192" s="8" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="K192" s="9"/>
     </row>
     <row r="193" ht="22.5" customHeight="1">
       <c r="A193" s="3" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="B193" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Johann Jakob (1602-1668)</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D193" s="3" t="s">
         <v>32</v>
@@ -12378,32 +12455,32 @@
         <v>1668.0</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J193" s="8" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="K193" s="9"/>
     </row>
     <row r="194" ht="22.5" customHeight="1">
       <c r="A194" s="3" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="B194" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Orelli, Anna (1606-1681)</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="E194" s="5">
         <v>1606.0</v>
@@ -12413,29 +12490,29 @@
       </c>
       <c r="G194" s="9"/>
       <c r="H194" s="3" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="I194" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J194" s="10" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="K194" s="9"/>
     </row>
     <row r="195" ht="22.5" customHeight="1">
       <c r="A195" s="3" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="B195" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Eberhard, Hans Kaspar (1645-1723)</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E195" s="5">
         <v>1645.0</v>
@@ -12445,29 +12522,29 @@
       </c>
       <c r="G195" s="9"/>
       <c r="H195" s="3" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J195" s="10" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="K195" s="9"/>
     </row>
     <row r="196" ht="22.5" customHeight="1">
       <c r="A196" s="3" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B196" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirt‏, Katharina (1644-1717)</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="E196" s="5">
         <v>1644.0</v>
@@ -12477,26 +12554,26 @@
       </c>
       <c r="G196" s="9"/>
       <c r="H196" s="3" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="I196" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J196" s="10" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="K196" s="9"/>
     </row>
     <row r="197" ht="22.5" customHeight="1">
       <c r="A197" s="3" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B197" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grob, Hans Jakob (1639-1712)</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>228</v>
@@ -12508,22 +12585,22 @@
         <v>1712.0</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="I197" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J197" s="8" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="K197" s="9"/>
     </row>
     <row r="198" ht="22.5" customHeight="1">
       <c r="A198" s="3" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B198" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12533,39 +12610,39 @@
         <v>70</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="E198" s="5">
         <v>1648.0</v>
       </c>
       <c r="F198" s="19" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="G198" s="9"/>
       <c r="H198" s="3" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="I198" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J198" s="10" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="K198" s="9"/>
     </row>
     <row r="199" ht="22.5" customHeight="1">
       <c r="A199" s="3" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="B199" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Klingler, Kaspar (1642-1677)</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E199" s="5">
         <v>1642.0</v>
@@ -12575,26 +12652,26 @@
       </c>
       <c r="G199" s="9"/>
       <c r="H199" s="3" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="I199" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J199" s="14" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="K199" s="9"/>
     </row>
     <row r="200" ht="22.5" customHeight="1">
       <c r="A200" s="3" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B200" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Spöndli, Dorothea (1646-1711)</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>497</v>
@@ -12607,29 +12684,29 @@
       </c>
       <c r="G200" s="9"/>
       <c r="H200" s="3" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="I200" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J200" s="10" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="K200" s="9"/>
     </row>
     <row r="201" ht="22.5" customHeight="1">
       <c r="A201" s="3" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B201" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Hans Caspar (1617-1691)</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="E201" s="5">
         <v>1617.0</v>
@@ -12638,29 +12715,29 @@
         <v>1691.0</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J201" s="8" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="K201" s="9"/>
     </row>
     <row r="202" ht="22.5" customHeight="1">
       <c r="A202" s="3" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="B202" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Salomon (1580-1652)</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>723</v>
@@ -12672,64 +12749,64 @@
         <v>1652.0</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="H202" s="3" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J202" s="8" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="K202" s="9"/>
     </row>
     <row r="203" ht="22.5" customHeight="1">
       <c r="A203" s="3" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B203" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Salis-Soglio, Maria Ursina von  (‎1600-1663‎)</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E203" s="19" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="F203" s="24" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="G203" s="9"/>
       <c r="H203" s="3" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J203" s="8" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="K203" s="9"/>
     </row>
     <row r="204" ht="22.5" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="B204" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Brügger, Andreas von (1588-1653)</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="E204" s="5">
         <v>1588.0</v>
@@ -12738,32 +12815,32 @@
         <v>1653.0</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="I204" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J204" s="8" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="K204" s="9"/>
     </row>
     <row r="205" ht="22.5" customHeight="1">
       <c r="A205" s="3" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="B205" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Anhorn, Bartholomäus (1616-1700)</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="E205" s="5">
         <v>1616.0</v>
@@ -12772,29 +12849,29 @@
         <v>1700.0</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="I205" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J205" s="12" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="K205" s="9"/>
     </row>
     <row r="206" ht="22.5" customHeight="1">
       <c r="A206" s="3" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B206" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wild, Abraham (1628-1689)</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>305</v>
@@ -12806,29 +12883,29 @@
         <v>1689.0</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J206" s="12" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="K206" s="9"/>
     </row>
     <row r="207" ht="22.5" customHeight="1">
       <c r="A207" s="3" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="B207" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Grob, Johannes (1643-1697)</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="D207" s="3" t="s">
         <v>126</v>
@@ -12840,24 +12917,24 @@
         <v>1697.0</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J207" s="12" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="K207" s="3" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
     </row>
     <row r="208" ht="22.5" customHeight="1">
       <c r="A208" s="3" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B208" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12871,19 +12948,19 @@
       <c r="F208" s="21"/>
       <c r="G208" s="9"/>
       <c r="H208" s="3" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="I208" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J208" s="9"/>
       <c r="K208" s="10" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
     </row>
     <row r="209" ht="22.5" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="B209" s="4" t="str">
         <f t="shared" si="1"/>
@@ -12902,10 +12979,10 @@
         <v>1673.0</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="I209" s="7" t="s">
         <v>16</v>
@@ -12915,21 +12992,21 @@
     </row>
     <row r="210" ht="22.5" customHeight="1">
       <c r="A210" s="3" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B210" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Oeri,  (-)</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="20"/>
       <c r="F210" s="21"/>
       <c r="G210" s="9"/>
       <c r="H210" s="3" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="I210" s="7" t="s">
         <v>16</v>
@@ -12939,49 +13016,49 @@
     </row>
     <row r="211" ht="22.5" customHeight="1">
       <c r="A211" s="3" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="B211" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Keller vom Steinbock‏, Anna Kleophea (‎1609-1673)</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="F211" s="5">
         <v>1673.0</v>
       </c>
       <c r="G211" s="9"/>
       <c r="H211" s="3" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="I211" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J211" s="8" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="K211" s="9"/>
     </row>
     <row r="212" ht="22.5" customHeight="1">
       <c r="A212" s="3" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="B212" s="4" t="str">
         <f t="shared" si="1"/>
         <v>von Sultz, Johann Ludwig II. (1626-1687)</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="E212" s="5">
         <v>1626.0</v>
@@ -12990,64 +13067,64 @@
         <v>1687.0</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="I212" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J212" s="8" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="K212" s="9"/>
     </row>
     <row r="213" ht="22.5" customHeight="1">
       <c r="A213" s="3" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="B213" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Egli, Samuel (1627/29-1666)</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="E213" s="19" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="F213" s="5">
         <v>1666.0</v>
       </c>
       <c r="G213" s="9"/>
       <c r="H213" s="3" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="I213" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J213" s="10" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="K213" s="9"/>
     </row>
     <row r="214" ht="22.5" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="B214" s="4" t="str">
         <f t="shared" si="1"/>
         <v>von Breitenlandenberg, Wildhans (1410-1444)</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="E214" s="5">
         <v>1410.0</v>
@@ -13057,26 +13134,26 @@
       </c>
       <c r="G214" s="9"/>
       <c r="H214" s="3" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="I214" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J214" s="10" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="K214" s="9"/>
     </row>
     <row r="215" ht="22.5" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="B215" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pfarrherr,  (-)</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="20"/>
@@ -13091,17 +13168,17 @@
     </row>
     <row r="216" ht="22.5" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="B216" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid von Schwarzenhorn, Johann Rudolf (1590-1667)</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="E216" s="5">
         <v>1590.0</v>
@@ -13110,54 +13187,54 @@
         <v>1667.0</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="I216" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J216" s="8" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="K216" s="9"/>
     </row>
     <row r="217" ht="22.5" customHeight="1">
       <c r="A217" s="3" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="B217" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schmid, Felix (‎1539-1597)</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>90</v>
       </c>
       <c r="E217" s="19" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="F217" s="5">
         <v>1597.0</v>
       </c>
       <c r="G217" s="9"/>
       <c r="H217" s="3" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="I217" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J217" s="10" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="K217" s="9"/>
     </row>
     <row r="218" ht="22.5" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B218" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13177,29 +13254,29 @@
       </c>
       <c r="G218" s="9"/>
       <c r="H218" s="3" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="I218" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J218" s="8" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="K218" s="9"/>
     </row>
     <row r="219" ht="22.5" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="B219" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulr., H. (-)</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="E219" s="20"/>
       <c r="F219" s="21"/>
@@ -13215,7 +13292,7 @@
     </row>
     <row r="220" ht="22.5" customHeight="1">
       <c r="A220" s="3" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="B220" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13225,7 +13302,7 @@
         <v>62</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="E220" s="5">
         <v>1627.0</v>
@@ -13234,22 +13311,22 @@
         <v>1674.0</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J220" s="10" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="K220" s="9"/>
     </row>
     <row r="221" ht="22.5" customHeight="1">
       <c r="A221" s="3" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="B221" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13259,7 +13336,7 @@
         <v>62</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="E221" s="18">
         <v>1594.0</v>
@@ -13268,68 +13345,68 @@
         <v>1666.0</v>
       </c>
       <c r="G221" s="6" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="I221" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J221" s="8" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="K221" s="9"/>
     </row>
     <row r="222" ht="22.5" customHeight="1">
       <c r="A222" s="3" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="B222" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Locher, Hans Melchior (-)</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="E222" s="20"/>
       <c r="F222" s="21"/>
       <c r="G222" s="9"/>
       <c r="H222" s="3" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="I222" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J222" s="10" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="K222" s="3" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="223" ht="22.5" customHeight="1">
       <c r="A223" s="3" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="B223" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caspar,  (-)</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="D223" s="3"/>
       <c r="E223" s="20"/>
       <c r="F223" s="21"/>
       <c r="G223" s="6" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="I223" s="7" t="s">
         <v>258</v>
@@ -13339,17 +13416,17 @@
     </row>
     <row r="224" ht="22.5" customHeight="1">
       <c r="A224" s="3" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="B224" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>Rahn, Johann Heinrich (1593-1669)</v>
+        <v>Rahn, Hans Heinrich (1593-1669)</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="E224" s="5">
         <v>1593.0</v>
@@ -13361,7 +13438,7 @@
         <v>72</v>
       </c>
       <c r="H224" s="22" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="I224" s="7" t="s">
         <v>16</v>
@@ -13373,7 +13450,7 @@
     </row>
     <row r="225" ht="22.5" customHeight="1">
       <c r="A225" s="3" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="B225" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13387,7 +13464,7 @@
       <c r="F225" s="21"/>
       <c r="G225" s="9"/>
       <c r="H225" s="3" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>16</v>
@@ -13397,17 +13474,17 @@
     </row>
     <row r="226" ht="22.5" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="B226" s="4" t="str">
         <f t="shared" si="1"/>
         <v>O., Jacob U. (-)</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="E226" s="20"/>
       <c r="F226" s="21"/>
@@ -13423,21 +13500,21 @@
     </row>
     <row r="227" ht="22.5" customHeight="1">
       <c r="A227" s="3" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B227" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Schneeberger,  (-)</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="20"/>
       <c r="F227" s="21"/>
       <c r="G227" s="9"/>
       <c r="H227" s="3" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="I227" s="7" t="s">
         <v>16</v>
@@ -13447,17 +13524,17 @@
     </row>
     <row r="228" ht="22.5" customHeight="1">
       <c r="A228" s="3" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="B228" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zwingli, Ulrich (1484-1531)</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="E228" s="5">
         <v>1484.0</v>
@@ -13466,10 +13543,10 @@
         <v>1531.0</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="I228" s="7" t="s">
         <v>16</v>
@@ -13479,14 +13556,14 @@
     </row>
     <row r="229" ht="22.5" customHeight="1">
       <c r="A229" s="3" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="B229" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Bullinger, Heinrich (1504-1575)</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>38</v>
@@ -13498,10 +13575,10 @@
         <v>1575.0</v>
       </c>
       <c r="G229" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H229" s="3" t="s">
         <v>1071</v>
-      </c>
-      <c r="H229" s="3" t="s">
-        <v>1068</v>
       </c>
       <c r="I229" s="7" t="s">
         <v>16</v>
@@ -13511,14 +13588,14 @@
     </row>
     <row r="230" ht="22.5" customHeight="1">
       <c r="A230" s="3" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="B230" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gwalther, Rudolf (1519-1586)</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>146</v>
@@ -13530,7 +13607,7 @@
         <v>1586.0</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="H230" s="3"/>
       <c r="I230" s="7" t="s">
@@ -13541,14 +13618,14 @@
     </row>
     <row r="231" ht="22.5" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="B231" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Breitinger, Johann Jakob (1575-1645)</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>32</v>
@@ -13560,7 +13637,7 @@
         <v>1645.0</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="H231" s="3"/>
       <c r="I231" s="7" t="s">
@@ -13571,17 +13648,17 @@
     </row>
     <row r="232" ht="22.5" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="B232" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Jrminger, Jacob (1588-1649)</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="E232" s="5">
         <v>1588.0</v>
@@ -13590,7 +13667,7 @@
         <v>1649.0</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="H232" s="3"/>
       <c r="I232" s="7" t="s">
@@ -13601,14 +13678,14 @@
     </row>
     <row r="233" ht="22.5" customHeight="1">
       <c r="A233" s="3" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="B233" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fries, Jakob (-)</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>330</v>
@@ -13625,25 +13702,25 @@
     </row>
     <row r="234" ht="22.5" customHeight="1">
       <c r="A234" s="3" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="B234" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Geiger, Joh. Rud. (-)</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="E234" s="20"/>
       <c r="F234" s="21"/>
       <c r="G234" s="3" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="I234" s="7" t="s">
         <v>16</v>
@@ -13653,17 +13730,17 @@
     </row>
     <row r="235" ht="22.5" customHeight="1">
       <c r="A235" s="3" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="B235" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maurer, C. (-)</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="E235" s="20"/>
       <c r="F235" s="21"/>
@@ -13677,17 +13754,17 @@
     </row>
     <row r="236" ht="22.5" customHeight="1">
       <c r="A236" s="3" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="B236" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Suter, C. (-)</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="E236" s="20"/>
       <c r="F236" s="21"/>
@@ -13701,7 +13778,7 @@
     </row>
     <row r="237" ht="22.5" customHeight="1">
       <c r="A237" s="3" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="B237" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13711,7 +13788,7 @@
         <v>637</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="E237" s="20"/>
       <c r="F237" s="21"/>
@@ -13727,17 +13804,17 @@
     </row>
     <row r="238" ht="22.5" customHeight="1">
       <c r="A238" s="3" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="B238" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wirtz, H. C. (-)</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="E238" s="20"/>
       <c r="F238" s="21"/>
@@ -13751,7 +13828,7 @@
     </row>
     <row r="239" ht="22.5" customHeight="1">
       <c r="A239" s="3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="B239" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13761,12 +13838,12 @@
         <v>642</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="E239" s="20"/>
       <c r="F239" s="21"/>
       <c r="G239" s="3" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="H239" s="3"/>
       <c r="I239" s="7" t="s">
@@ -13777,22 +13854,22 @@
     </row>
     <row r="240" ht="22.5" customHeight="1">
       <c r="A240" s="3" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="B240" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hospinianus, R. (-)</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="E240" s="20"/>
       <c r="F240" s="21"/>
       <c r="G240" s="3" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="H240" s="3"/>
       <c r="I240" s="7" t="s">
@@ -13803,17 +13880,17 @@
     </row>
     <row r="241" ht="22.5" customHeight="1">
       <c r="A241" s="3" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="B241" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Erni, H. (-)</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="E241" s="20"/>
       <c r="F241" s="21"/>
@@ -13827,17 +13904,17 @@
     </row>
     <row r="242" ht="22.5" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="B242" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Tomman, P. (-)</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="E242" s="20"/>
       <c r="F242" s="21"/>
@@ -13851,17 +13928,17 @@
     </row>
     <row r="243" ht="22.5" customHeight="1">
       <c r="A243" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="B243" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Stukki, R. (-)</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="E243" s="20"/>
       <c r="F243" s="21"/>
@@ -13875,17 +13952,17 @@
     </row>
     <row r="244" ht="22.5" customHeight="1">
       <c r="A244" s="3" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="B244" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zeller, H. (-)</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="E244" s="20"/>
       <c r="F244" s="21"/>
@@ -13899,7 +13976,7 @@
     </row>
     <row r="245" ht="22.5" customHeight="1">
       <c r="A245" s="3" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="B245" s="4" t="str">
         <f t="shared" si="1"/>
@@ -13907,13 +13984,13 @@
       </c>
       <c r="C245" s="6"/>
       <c r="D245" s="3" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="E245" s="20"/>
       <c r="F245" s="21"/>
       <c r="G245" s="9"/>
       <c r="H245" s="3" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="I245" s="7" t="s">
         <v>16</v>
@@ -13923,21 +14000,21 @@
     </row>
     <row r="246" ht="22.5" customHeight="1">
       <c r="A246" s="3" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="B246" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fr. Doctorin,  (-)</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="20"/>
       <c r="F246" s="21"/>
       <c r="G246" s="9"/>
       <c r="H246" s="3" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="I246" s="7" t="s">
         <v>16</v>
@@ -13947,17 +14024,17 @@
     </row>
     <row r="247" ht="22.5" customHeight="1">
       <c r="A247" s="3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="B247" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Kusen, Jost von (1570-1630)</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="E247" s="5">
         <v>1570.0</v>
@@ -13966,10 +14043,10 @@
         <v>1630.0</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="I247" s="7" t="s">
         <v>16</v>
@@ -13979,14 +14056,14 @@
     </row>
     <row r="248" ht="22.5" customHeight="1">
       <c r="A248" s="3" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="B248" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ulrich, Johann Heinrich (1575-1630)</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>44</v>
@@ -13998,36 +14075,36 @@
         <v>1630.0</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="H248" s="3" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="I248" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J248" s="14" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="K248" s="9"/>
     </row>
     <row r="249" ht="22.5" customHeight="1">
       <c r="A249" s="3" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="B249" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Gessner,  (-)</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="D249" s="3"/>
       <c r="E249" s="20"/>
       <c r="F249" s="21"/>
       <c r="G249" s="9"/>
       <c r="H249" s="3" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="I249" s="7" t="s">
         <v>16</v>
@@ -14037,17 +14114,17 @@
     </row>
     <row r="250" ht="22.5" customHeight="1">
       <c r="A250" s="3" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="B250" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Wöllwein, Johann Anton (1616-1659)</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="E250" s="5">
         <v>1616.0</v>
@@ -14056,10 +14133,10 @@
         <v>1659.0</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="I250" s="7" t="s">
         <v>16</v>
@@ -14069,17 +14146,17 @@
     </row>
     <row r="251" ht="22.5" customHeight="1">
       <c r="A251" s="3" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="B251" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Hirzel, Anna (1613-1667)</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="E251" s="5">
         <v>1613.0</v>
@@ -14089,19 +14166,19 @@
       </c>
       <c r="G251" s="9"/>
       <c r="H251" s="3" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="I251" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J251" s="8" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="K251" s="9"/>
     </row>
     <row r="252" ht="22.5" customHeight="1">
       <c r="A252" s="3" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="B252" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14111,39 +14188,39 @@
         <v>12</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="E252" s="5">
         <v>1635.0</v>
       </c>
       <c r="F252" s="19" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="G252" s="9"/>
       <c r="H252" s="3" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="I252" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J252" s="8" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="K252" s="9"/>
     </row>
     <row r="253" ht="22.5" customHeight="1">
       <c r="A253" s="3" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="B253" s="4" t="str">
         <f t="shared" si="1"/>
         <v>de Ruyter, Michiel (1607-1676)</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="E253" s="5">
         <v>1607.0</v>
@@ -14152,10 +14229,10 @@
         <v>1676.0</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="H253" s="3" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="I253" s="7" t="s">
         <v>16</v>
@@ -14165,21 +14242,21 @@
     </row>
     <row r="254" ht="22.5" customHeight="1">
       <c r="A254" s="3" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="B254" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Frau Oberstin,  (-)</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="20"/>
       <c r="F254" s="21"/>
       <c r="G254" s="9"/>
       <c r="H254" s="3" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="I254" s="7" t="s">
         <v>16</v>
@@ -14189,23 +14266,23 @@
     </row>
     <row r="255" ht="22.5" customHeight="1">
       <c r="A255" s="3" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="B255" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Vulcanus,  (-)</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="20"/>
       <c r="F255" s="21"/>
       <c r="G255" s="3" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="H255" s="3" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="I255" s="7" t="s">
         <v>240</v>
@@ -14215,23 +14292,23 @@
     </row>
     <row r="256" ht="22.5" customHeight="1">
       <c r="A256" s="3" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="B256" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Esau,  (-)</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="20"/>
       <c r="F256" s="21"/>
       <c r="G256" s="3" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="I256" s="7" t="s">
         <v>258</v>
@@ -14241,23 +14318,23 @@
     </row>
     <row r="257" ht="22.5" customHeight="1">
       <c r="A257" s="3" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="B257" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Danaos,  (-)</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="D257" s="3"/>
       <c r="E257" s="20"/>
       <c r="F257" s="21"/>
       <c r="G257" s="3" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="I257" s="7" t="s">
         <v>240</v>
@@ -14267,23 +14344,23 @@
     </row>
     <row r="258" ht="22.5" customHeight="1">
       <c r="A258" s="3" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="B258" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Medusa,  (-)</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="D258" s="3"/>
       <c r="E258" s="20"/>
       <c r="F258" s="21"/>
       <c r="G258" s="3" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="H258" s="3" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="I258" s="7" t="s">
         <v>240</v>
@@ -14293,23 +14370,23 @@
     </row>
     <row r="259" ht="22.5" customHeight="1">
       <c r="A259" s="3" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="B259" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pluton,  (-)</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="D259" s="3"/>
       <c r="E259" s="20"/>
       <c r="F259" s="21"/>
       <c r="G259" s="3" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="H259" s="3" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="I259" s="7" t="s">
         <v>240</v>
@@ -14319,23 +14396,23 @@
     </row>
     <row r="260" ht="22.5" customHeight="1">
       <c r="A260" s="3" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="B260" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Merkur,  (-)</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="20"/>
       <c r="F260" s="21"/>
       <c r="G260" s="3" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="H260" s="3" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="I260" s="7" t="s">
         <v>240</v>
@@ -14345,23 +14422,23 @@
     </row>
     <row r="261" ht="22.5" customHeight="1">
       <c r="A261" s="3" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="B261" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Perseus,  (-)</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="20"/>
       <c r="F261" s="21"/>
       <c r="G261" s="3" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="H261" s="3" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="I261" s="7" t="s">
         <v>240</v>
@@ -14371,23 +14448,23 @@
     </row>
     <row r="262" ht="22.5" customHeight="1">
       <c r="A262" s="3" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="B262" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Atropos,  (-)</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="D262" s="3"/>
       <c r="E262" s="20"/>
       <c r="F262" s="21"/>
       <c r="G262" s="3" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="I262" s="7" t="s">
         <v>240</v>
@@ -14397,23 +14474,23 @@
     </row>
     <row r="263" ht="22.5" customHeight="1">
       <c r="A263" s="3" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="B263" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Barbara von Nikomedien,  (-)</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="20"/>
       <c r="F263" s="21"/>
       <c r="G263" s="3" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="H263" s="3" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="I263" s="7" t="s">
         <v>258</v>
@@ -14423,7 +14500,7 @@
     </row>
     <row r="264" ht="22.5" customHeight="1">
       <c r="A264" s="3" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
       <c r="B264" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14437,7 +14514,7 @@
       <c r="F264" s="21"/>
       <c r="G264" s="9"/>
       <c r="H264" s="3" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="I264" s="13"/>
       <c r="J264" s="9"/>
@@ -14445,7 +14522,7 @@
     </row>
     <row r="265" ht="22.5" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>1188</v>
+        <v>1191</v>
       </c>
       <c r="B265" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14459,7 +14536,7 @@
       <c r="F265" s="21"/>
       <c r="G265" s="9"/>
       <c r="H265" s="3" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="I265" s="13"/>
       <c r="J265" s="9"/>
@@ -14467,53 +14544,53 @@
     </row>
     <row r="266" ht="22.5" customHeight="1">
       <c r="A266" s="3" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="B266" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Karl I. Ludwig,  (1617/1618-1680)</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="5" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="F266" s="18">
         <v>1680.0</v>
       </c>
       <c r="G266" s="3" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="H266" s="3" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="I266" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J266" s="10" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="K266" s="9"/>
     </row>
     <row r="267" ht="22.5" customHeight="1">
       <c r="A267" s="3" t="s">
-        <v>1195</v>
+        <v>1198</v>
       </c>
       <c r="B267" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Duraeum,  (-)</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="20"/>
       <c r="F267" s="21"/>
       <c r="G267" s="9"/>
       <c r="H267" s="3" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="I267" s="13"/>
       <c r="J267" s="9"/>
@@ -14521,17 +14598,17 @@
     </row>
     <row r="268" ht="22.5" customHeight="1">
       <c r="A268" s="3" t="s">
-        <v>1198</v>
+        <v>1201</v>
       </c>
       <c r="B268" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Zesen, Philipp von (1619-1689)</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="E268" s="5">
         <v>1619.0</v>
@@ -14540,7 +14617,7 @@
         <v>1689.0</v>
       </c>
       <c r="G268" s="3" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="H268" s="3"/>
       <c r="I268" s="7" t="s">
@@ -14551,23 +14628,23 @@
     </row>
     <row r="269" ht="22.5" customHeight="1">
       <c r="A269" s="3" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="B269" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lucretia,  (-)</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="D269" s="3"/>
       <c r="E269" s="20"/>
       <c r="F269" s="21"/>
       <c r="G269" s="3" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="H269" s="3" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="I269" s="7" t="s">
         <v>240</v>
@@ -14577,23 +14654,23 @@
     </row>
     <row r="270" ht="22.5" customHeight="1">
       <c r="A270" s="3" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="B270" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Ovid,  (-)</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="20"/>
       <c r="F270" s="21"/>
       <c r="G270" s="3" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="H270" s="3" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="I270" s="7" t="s">
         <v>16</v>
@@ -14603,7 +14680,7 @@
     </row>
     <row r="271" ht="22.5" customHeight="1">
       <c r="A271" s="3" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="B271" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14616,16 +14693,16 @@
         <v>652</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="G271" s="3" t="s">
         <v>708</v>
       </c>
       <c r="H271" s="3" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="I271" s="7" t="s">
         <v>16</v>
@@ -14634,12 +14711,12 @@
         <v>710</v>
       </c>
       <c r="K271" s="3" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="272" ht="22.5" customHeight="1">
       <c r="A272" s="3" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="B272" s="4" t="str">
         <f t="shared" si="1"/>
@@ -14658,10 +14735,10 @@
         <v>1665.0</v>
       </c>
       <c r="G272" s="3" t="s">
-        <v>1216</v>
+        <v>740</v>
       </c>
       <c r="H272" s="3" t="s">
-        <v>1217</v>
+        <v>741</v>
       </c>
       <c r="I272" s="7" t="s">
         <v>16</v>
@@ -14671,23 +14748,23 @@
     </row>
     <row r="273" ht="22.5" customHeight="1">
       <c r="A273" s="3" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B273" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Elischa,  (-)</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="D273" s="3"/>
       <c r="E273" s="20"/>
       <c r="F273" s="21"/>
       <c r="G273" s="3" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H273" s="3" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="I273" s="7" t="s">
         <v>258</v>
@@ -14697,23 +14774,23 @@
     </row>
     <row r="274" ht="22.5" customHeight="1">
       <c r="A274" s="3" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B274" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Johannes der Täufer,  (-)</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="D274" s="3"/>
       <c r="E274" s="20"/>
       <c r="F274" s="21"/>
       <c r="G274" s="3" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="I274" s="7" t="s">
         <v>258</v>
@@ -14723,29 +14800,29 @@
     </row>
     <row r="275" ht="22.5" customHeight="1">
       <c r="A275" s="3" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B275" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Caesar, Gaius Iulius (100 v. Chr.-44 v. Chr.)</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="E275" s="5" t="s">
         <v>578</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="G275" s="3" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H275" s="3" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="I275" s="7" t="s">
         <v>16</v>
@@ -14755,23 +14832,23 @@
     </row>
     <row r="276" ht="22.5" customHeight="1">
       <c r="A276" s="3" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B276" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Helios,  (-)</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="D276" s="3"/>
       <c r="E276" s="20"/>
       <c r="F276" s="21"/>
       <c r="G276" s="3" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H276" s="3" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="I276" s="7" t="s">
         <v>240</v>
@@ -14781,14 +14858,14 @@
     </row>
     <row r="277" ht="22.5" customHeight="1">
       <c r="A277" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B277" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Suevus,  (-)</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D277" s="3"/>
       <c r="E277" s="20"/>
@@ -14807,51 +14884,51 @@
     </row>
     <row r="278" ht="22.5" customHeight="1">
       <c r="A278" s="3" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B278" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Momos,  (-)</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D278" s="3"/>
       <c r="E278" s="20"/>
       <c r="F278" s="21"/>
       <c r="G278" s="3" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H278" s="3" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="I278" s="7" t="s">
         <v>240</v>
       </c>
       <c r="J278" s="10" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="K278" s="9"/>
     </row>
     <row r="279" ht="22.5" customHeight="1">
       <c r="A279" s="3" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B279" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Galatea,  (-)</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="D279" s="3"/>
       <c r="E279" s="20"/>
       <c r="F279" s="21"/>
       <c r="G279" s="3" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H279" s="3" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="I279" s="7" t="s">
         <v>240</v>
@@ -14861,80 +14938,80 @@
     </row>
     <row r="280" ht="22.5" customHeight="1">
       <c r="A280" s="3" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B280" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Escher vom Luchs‏‎, Hans Heinrich (‎1644-1714)</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>71</v>
       </c>
       <c r="E280" s="19" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="F280" s="5">
         <v>1714.0</v>
       </c>
       <c r="G280" s="9"/>
       <c r="H280" s="3" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="I280" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J280" s="10" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="K280" s="10" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="281" ht="22.5" customHeight="1">
       <c r="A281" s="3" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B281" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Agapetus,  (6. Jh.-6. Jh.)</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D281" s="3"/>
       <c r="E281" s="19" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="G281" s="3" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H281" s="3" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="I281" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J281" s="10" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="K281" s="17"/>
     </row>
     <row r="282" ht="22.5" customHeight="1">
       <c r="A282" s="3" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B282" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Justinian I.,  (482-565)</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D282" s="3"/>
       <c r="E282" s="19">
@@ -14944,10 +15021,10 @@
         <v>565.0</v>
       </c>
       <c r="G282" s="3" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H282" s="3" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="I282" s="7" t="s">
         <v>16</v>
@@ -14957,14 +15034,14 @@
     </row>
     <row r="283" ht="22.5" customHeight="1">
       <c r="A283" s="3" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B283" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Theodora I.,  (497-548)</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="D283" s="3"/>
       <c r="E283" s="19">
@@ -14974,10 +15051,10 @@
         <v>548.0</v>
       </c>
       <c r="G283" s="3" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H283" s="3" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="I283" s="7" t="s">
         <v>16</v>
@@ -14987,33 +15064,33 @@
     </row>
     <row r="284" ht="22.5" customHeight="1">
       <c r="A284" s="3" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B284" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Israel,  (-)</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D284" s="3"/>
       <c r="E284" s="19"/>
       <c r="F284" s="5"/>
       <c r="G284" s="9"/>
       <c r="H284" s="3" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="I284" s="7" t="s">
         <v>258</v>
       </c>
       <c r="J284" s="10" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="K284" s="17"/>
     </row>
     <row r="285" ht="22.5" customHeight="1">
       <c r="A285" s="3" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B285" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15023,7 +15100,7 @@
         <v>12</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="E285" s="19">
         <v>1530.0</v>
@@ -15032,22 +15109,22 @@
         <v>1576.0</v>
       </c>
       <c r="G285" s="3" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H285" s="3" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="I285" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J285" s="10" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="K285" s="17"/>
     </row>
     <row r="286" ht="22.5" customHeight="1">
       <c r="A286" s="3" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B286" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15057,7 +15134,7 @@
         <v>642</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="E286" s="19">
         <v>1595.0</v>
@@ -15067,26 +15144,26 @@
       </c>
       <c r="G286" s="9"/>
       <c r="H286" s="3" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="I286" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J286" s="10" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="K286" s="17"/>
     </row>
     <row r="287" ht="22.5" customHeight="1">
       <c r="A287" s="3" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B287" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fäsi, Magdalena (1583-1665)</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="D287" s="3" t="s">
         <v>638</v>
@@ -15099,35 +15176,35 @@
       </c>
       <c r="G287" s="9"/>
       <c r="H287" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="I287" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J287" s="10" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="K287" s="17"/>
     </row>
     <row r="288" ht="22.5" customHeight="1">
       <c r="A288" s="3" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B288" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Katharina von Alexandrien,  (-)</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="D288" s="3"/>
       <c r="E288" s="19"/>
       <c r="F288" s="5"/>
       <c r="G288" s="3" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H288" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="I288" s="7" t="s">
         <v>240</v>
@@ -15137,7 +15214,7 @@
     </row>
     <row r="289" ht="22.5" customHeight="1">
       <c r="A289" s="3" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B289" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15157,54 +15234,54 @@
       </c>
       <c r="G289" s="9"/>
       <c r="H289" s="3" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="I289" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J289" s="10" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="K289" s="17"/>
     </row>
     <row r="290" ht="22.5" customHeight="1">
       <c r="A290" s="3" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B290" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Simeon,  (-)</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D290" s="3"/>
       <c r="E290" s="19"/>
       <c r="F290" s="5"/>
       <c r="G290" s="3" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H290" s="3" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="I290" s="7" t="s">
         <v>258</v>
       </c>
       <c r="J290" s="10" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="K290" s="17"/>
     </row>
     <row r="291" ht="22.5" customHeight="1">
       <c r="A291" s="3" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B291" s="4" t="str">
         <f t="shared" si="1"/>
         <v>M. G. H. H. H. D. J. H. H.,  (-)</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D291" s="3"/>
       <c r="E291" s="19"/>
@@ -15216,32 +15293,32 @@
       </c>
       <c r="J291" s="17"/>
       <c r="K291" s="17" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="292" ht="22.5" customHeight="1">
       <c r="A292" s="3" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B292" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Horaz,  (65 v. Chr.-8 v. Chr.)</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="D292" s="3"/>
       <c r="E292" s="19" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="F292" s="5" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H292" s="3" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="I292" s="7" t="s">
         <v>16</v>
@@ -15251,17 +15328,17 @@
     </row>
     <row r="293" ht="22.5" customHeight="1">
       <c r="A293" s="3" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B293" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Lavater, Hans Conrad (1609-1703)</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="E293" s="19">
         <v>1609.0</v>
@@ -15270,141 +15347,141 @@
         <v>1703.0</v>
       </c>
       <c r="G293" s="3" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H293" s="3" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="I293" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J293" s="12" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="K293" s="17"/>
     </row>
     <row r="294" ht="22.5" customHeight="1">
       <c r="A294" s="3" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B294" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Josef von Arimathäa,  (-)</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D294" s="3"/>
       <c r="E294" s="19"/>
       <c r="F294" s="5"/>
       <c r="G294" s="3" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H294" s="3" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="I294" s="7" t="s">
         <v>258</v>
       </c>
       <c r="J294" s="17" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="K294" s="17"/>
     </row>
     <row r="295" ht="22.5" customHeight="1">
       <c r="A295" s="3" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B295" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Maria Magdalena,  (-)</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D295" s="3"/>
       <c r="E295" s="19"/>
       <c r="F295" s="5"/>
       <c r="G295" s="3" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H295" s="3" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="I295" s="7" t="s">
         <v>258</v>
       </c>
       <c r="J295" s="10" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="K295" s="17"/>
     </row>
     <row r="296" ht="22.5" customHeight="1">
       <c r="A296" s="3" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B296" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Merib-Baal,  (-)</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D296" s="3"/>
       <c r="E296" s="19"/>
       <c r="F296" s="5"/>
       <c r="G296" s="3" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H296" s="3" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="I296" s="7" t="s">
         <v>258</v>
       </c>
       <c r="J296" s="10" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="K296" s="17"/>
     </row>
     <row r="297" ht="22.5" customHeight="1">
       <c r="A297" s="3" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B297" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Aurora,  (-)</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="D297" s="3"/>
       <c r="E297" s="19"/>
       <c r="F297" s="5"/>
       <c r="G297" s="3" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H297" s="3" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="I297" s="7" t="s">
         <v>240</v>
       </c>
       <c r="J297" s="10" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="K297" s="17"/>
     </row>
     <row r="298" ht="22.5" customHeight="1">
       <c r="A298" s="3" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B298" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Isler, Elisabeth (-)</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D298" s="3" t="s">
         <v>713</v>
@@ -15413,7 +15490,7 @@
       <c r="F298" s="5"/>
       <c r="G298" s="9"/>
       <c r="H298" s="3" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="I298" s="7" t="s">
         <v>16</v>
@@ -15423,55 +15500,55 @@
     </row>
     <row r="299" ht="22.5" customHeight="1">
       <c r="A299" s="3" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B299" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Escher vom Luchs‏, Hans Heinrich (‎1616-1690‎)</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="D299" s="3" t="s">
         <v>71</v>
       </c>
       <c r="E299" s="19" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="F299" s="19" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="G299" s="9"/>
       <c r="H299" s="3" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="I299" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J299" s="10" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="K299" s="17"/>
     </row>
     <row r="300" ht="22.5" customHeight="1">
       <c r="A300" s="3" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B300" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Verlorener Sohn,  (-)</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="D300" s="3"/>
       <c r="E300" s="19"/>
       <c r="F300" s="5"/>
       <c r="G300" s="3" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H300" s="3" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="I300" s="7" t="s">
         <v>258</v>
@@ -15481,14 +15558,14 @@
     </row>
     <row r="301" ht="22.5" customHeight="1">
       <c r="A301" s="3" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B301" s="4" t="str">
         <f t="shared" si="1"/>
         <v>H. G. Mr. H.,  (-)</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="D301" s="3"/>
       <c r="E301" s="19"/>
@@ -15501,7 +15578,7 @@
     </row>
     <row r="302" ht="22.5" customHeight="1">
       <c r="A302" s="3" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B302" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15520,32 +15597,32 @@
         <v>1664.0</v>
       </c>
       <c r="G302" s="3" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H302" s="3" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="I302" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J302" s="14" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="K302" s="17"/>
     </row>
     <row r="303" ht="22.5" customHeight="1">
       <c r="A303" s="3" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B303" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Werdmüller, Johann Georg (1616-1678)</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="E303" s="18">
         <v>1616.0</v>
@@ -15554,22 +15631,22 @@
         <v>1678.0</v>
       </c>
       <c r="G303" s="3" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H303" s="3" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="I303" s="7" t="s">
         <v>16</v>
       </c>
       <c r="J303" s="10" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="K303" s="17"/>
     </row>
     <row r="304" ht="22.5" customHeight="1">
       <c r="A304" s="3" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B304" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15587,7 +15664,7 @@
     </row>
     <row r="305" ht="22.5" customHeight="1">
       <c r="A305" s="3" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B305" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15605,7 +15682,7 @@
     </row>
     <row r="306" ht="22.5" customHeight="1">
       <c r="A306" s="3" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B306" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15623,7 +15700,7 @@
     </row>
     <row r="307" ht="22.5" customHeight="1">
       <c r="A307" s="3" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B307" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15641,7 +15718,7 @@
     </row>
     <row r="308" ht="22.5" customHeight="1">
       <c r="A308" s="3" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B308" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15659,7 +15736,7 @@
     </row>
     <row r="309" ht="22.5" customHeight="1">
       <c r="A309" s="3" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B309" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15677,7 +15754,7 @@
     </row>
     <row r="310" ht="22.5" customHeight="1">
       <c r="A310" s="3" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B310" s="4" t="str">
         <f t="shared" si="1"/>
@@ -15898,16 +15975,16 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -15918,179 +15995,179 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B2" s="25" t="str">
         <f t="shared" ref="B2:B132" si="1">CONCATENATE(C2)</f>
         <v>Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B3" s="25" t="str">
         <f t="shared" si="1"/>
         <v>Basel</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B4" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Eidgenossenschaft</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="E4" s="23"/>
       <c r="F4" s="3" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B5" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Limmat</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="7" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B6" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Weinfelden</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D6" s="27"/>
       <c r="E6" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B7" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Main</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="D7" s="27"/>
       <c r="E7" s="7" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B8" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Zürichsee</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="D8" s="27"/>
       <c r="E8" s="7" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B9" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Thalwil</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="D9" s="27"/>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B10" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Bern</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="D10" s="27"/>
       <c r="E10" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B11" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Gottstatt</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="D11" s="27"/>
       <c r="E11" s="13"/>
@@ -16098,325 +16175,325 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B12" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Thorberg</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B13" s="26" t="str">
         <f t="shared" si="1"/>
         <v>London</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B14" s="26" t="str">
         <f t="shared" si="1"/>
         <v>England</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="7" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="F14" s="9"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B15" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Bethlehem</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B16" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Parnass </v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="7" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B17" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Traubenberg</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="D17" s="27"/>
       <c r="E17" s="13"/>
       <c r="F17" s="3" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B18" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Babylon</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B19" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Canaan</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="7" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B20" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Ägypten</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="F20" s="9"/>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B21" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Hermon</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="D21" s="27"/>
       <c r="E21" s="7" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B22" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Jerusalem</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B23" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Jordan</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="D23" s="27"/>
       <c r="E23" s="7" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B24" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Rotes Meer</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="7" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="F24" s="9"/>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B25" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Juda</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="13"/>
       <c r="F25" s="3" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B26" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Moab</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="D26" s="27"/>
       <c r="E26" s="13"/>
       <c r="F26" s="3" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B27" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Ammon</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="D27" s="27"/>
       <c r="E27" s="13"/>
       <c r="F27" s="3" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B28" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Zion</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B29" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Assur</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="D29" s="27"/>
       <c r="E29" s="13"/>
@@ -16424,181 +16501,181 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B30" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Israel</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D30" s="27"/>
       <c r="E30" s="13"/>
       <c r="F30" s="3" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B31" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Nazaret</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="D31" s="27"/>
       <c r="E31" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B32" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Rom</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="D32" s="27"/>
       <c r="E32" s="13"/>
       <c r="F32" s="3" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B33" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Samaria</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B34" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kedronbach</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="D34" s="27"/>
       <c r="E34" s="7" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B35" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Garten von Getsemani</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="D35" s="27"/>
       <c r="E35" s="7" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="F35" s="3"/>
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B36" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Urdorf</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="D36" s="27"/>
       <c r="E36" s="7" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B37" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Geiren-Rein</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="D37" s="27"/>
       <c r="E37" s="7" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="F37" s="3"/>
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B38" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Aeugst</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B39" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Riedt</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="13"/>
@@ -16606,14 +16683,14 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B40" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Europa</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="D40" s="27"/>
       <c r="E40" s="13"/>
@@ -16621,232 +16698,236 @@
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B41" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Osir</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B42" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Basadingen</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="D42" s="27"/>
       <c r="E42" s="13"/>
       <c r="F42" s="3" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B43" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Diessenhofen</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="7" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B44" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Rhein</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="D44" s="27"/>
       <c r="E44" s="7" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B45" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Arabisches Reich</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="D45" s="27"/>
       <c r="E45" s="13"/>
       <c r="F45" s="3" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B46" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Libanon</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="D46" s="27"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="3"/>
+      <c r="E46" s="7" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>1494</v>
+      </c>
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="B47" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Emmaus</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="D47" s="27"/>
       <c r="E47" s="13"/>
       <c r="F47" s="3" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="B48" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Helikon</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="D48" s="27"/>
       <c r="E48" s="7" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="3" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="B49" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Pindos</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="D49" s="27"/>
       <c r="E49" s="7" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="B50" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Neckar</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="D50" s="27"/>
       <c r="E50" s="7" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="B51" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kurpfalz</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="D51" s="27"/>
       <c r="E51" s="13"/>
       <c r="F51" s="3" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B52" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Eglisau</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="D52" s="27"/>
       <c r="E52" s="7" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="3" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="B53" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Altenklingen</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="D53" s="27"/>
       <c r="E53" s="13"/>
@@ -16854,14 +16935,14 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="B54" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Altorff</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="D54" s="27"/>
       <c r="E54" s="13"/>
@@ -16869,65 +16950,65 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="B55" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Glarus</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="D55" s="27"/>
       <c r="E55" s="13"/>
       <c r="F55" s="3" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B56" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Reformierte Kirche Berg am Irchel</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="3"/>
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="B57" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Sodom</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="D57" s="27"/>
       <c r="E57" s="13"/>
       <c r="F57" s="3" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="3" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="B58" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Haus zur Sonnenblume</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="D58" s="27"/>
       <c r="E58" s="13"/>
@@ -16935,128 +17016,128 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="B59" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Geissturm</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="D59" s="27"/>
       <c r="E59" s="7" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="B60" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Konstantinopel</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F60" s="3"/>
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="B61" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Stein am Rhein</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="D61" s="27"/>
       <c r="E61" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F61" s="3"/>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="B62" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Marburg</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="D62" s="27"/>
       <c r="E62" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="3" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="B63" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Elbląg</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="B64" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Preussen</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="D64" s="27"/>
       <c r="E64" s="7" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="B65" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Heilbäder Baden</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="D65" s="27"/>
       <c r="E65" s="13"/>
@@ -17064,84 +17145,84 @@
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="3" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="B66" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Bad Schinznach</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="D66" s="27"/>
       <c r="E66" s="13"/>
       <c r="F66" s="3" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B67" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Girenbad</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="E67" s="13"/>
       <c r="F67" s="3" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B68" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Wängibad</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="D68" s="27"/>
       <c r="E68" s="13"/>
       <c r="F68" s="10" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="B69" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Aeugst am Albis</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="D69" s="27"/>
       <c r="E69" s="7" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F69" s="3"/>
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B70" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Bassersdorf</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="D70" s="27"/>
       <c r="E70" s="13"/>
@@ -17149,31 +17230,31 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="B71" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Hauptwil</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="D71" s="27"/>
       <c r="E71" s="7" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F71" s="3"/>
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="B72" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Schaffhausen</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="D72" s="27"/>
       <c r="E72" s="13"/>
@@ -17181,133 +17262,133 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="3" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="B73" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Wädenswil</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="7" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="F73" s="3"/>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="3" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="B74" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Freiamt</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="7" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="F74" s="3"/>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="3" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="B75" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Grüningen</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="7" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="F75" s="3"/>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="3" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="B76" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kefikon</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="7" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F76" s="3"/>
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="B77" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Maienfeld</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="7" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="F77" s="3"/>
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="3" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B78" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Schloss Greifensee</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="7" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="F78" s="3"/>
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="3" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="B79" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Lindenhof (Zürich)</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="D79" s="27"/>
       <c r="E79" s="13"/>
       <c r="F79" s="3" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="3" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B80" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Galg-Brunnen (Zürich)</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="13"/>
@@ -17315,48 +17396,48 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="3" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="B81" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kornhaus (Zürich)</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="7" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="F81" s="3"/>
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="3" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="B82" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Sparrenberg (Zürich)</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="7" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="F82" s="3"/>
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="3" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="B83" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Thurgau</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="13"/>
@@ -17364,14 +17445,14 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B84" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Niederlande</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="13"/>
@@ -17379,31 +17460,31 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="3" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="B85" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Holland</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="D85" s="27"/>
       <c r="E85" s="13"/>
       <c r="F85" s="3" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="3" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="B86" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Wigoltingen</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="D86" s="27"/>
       <c r="E86" s="13"/>
@@ -17411,378 +17492,378 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="3" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="B87" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Kastalische Quelle</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="D87" s="27"/>
       <c r="E87" s="7" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="3" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="B88" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Lägern</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="D88" s="27"/>
       <c r="E88" s="7" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F88" s="3"/>
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="3" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="B89" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Texel</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="D89" s="27"/>
       <c r="E89" s="13"/>
       <c r="F89" s="3" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="3" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="B90" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Vlieland</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="D90" s="27"/>
       <c r="E90" s="13"/>
       <c r="F90" s="3" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="3" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="B91" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Indien</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="D91" s="27"/>
       <c r="E91" s="7" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="F91" s="3"/>
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="3" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="B92" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Wien</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="D92" s="27"/>
       <c r="E92" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F92" s="3"/>
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="B93" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Deutschland</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="D93" s="27"/>
       <c r="E93" s="7" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="F93" s="3"/>
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="3" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="B94" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Ölberg</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="D94" s="27"/>
       <c r="E94" s="7" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F94" s="3"/>
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="3" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="B95" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Dietikon</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="D95" s="27"/>
       <c r="E95" s="7" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="3" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="B96" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Winterthur</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="D96" s="27"/>
       <c r="E96" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F96" s="3"/>
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="3" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="B97" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Pfalz</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="7" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="F97" s="3"/>
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="B98" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Edenkoben</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="D98" s="27"/>
       <c r="E98" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="3" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="B99" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Wüste Juda</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="3" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="B100" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Greifensee</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="D100" s="27"/>
       <c r="E100" s="7" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="F100" s="3"/>
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="3" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="B101" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Lichtensteig</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="D101" s="27"/>
       <c r="E101" s="7" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F101" s="3"/>
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="3" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="B102" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Golgotha</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="E102" s="13"/>
       <c r="F102" s="3" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="3" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="B103" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Heidelberg</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="D103" s="27"/>
       <c r="E103" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F103" s="3"/>
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="3" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="B104" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Lindenhofbrunnen</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="D104" s="27"/>
       <c r="E104" s="7" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="F104" s="3"/>
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="3" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="B105" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Osmanisches Reich</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="D105" s="27"/>
       <c r="E105" s="7" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="F105" s="3"/>
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="B106" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Frauenfeld</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="D106" s="27"/>
       <c r="E106" s="7" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F106" s="3"/>
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="3" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="B107" s="26" t="str">
         <f t="shared" si="1"/>
         <v>Regensdorf</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="D107" s="27"/>
       <c r="E107" s="7" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="3" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="B108" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17795,7 +17876,7 @@
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="3" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="B109" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17808,7 +17889,7 @@
     </row>
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="3" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="B110" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17821,7 +17902,7 @@
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="3" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="B111" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17834,7 +17915,7 @@
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="B112" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17847,7 +17928,7 @@
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="3" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="B113" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17860,7 +17941,7 @@
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="B114" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17873,7 +17954,7 @@
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="3" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="B115" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17886,7 +17967,7 @@
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="B116" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17899,7 +17980,7 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="B117" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17912,7 +17993,7 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="B118" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17925,7 +18006,7 @@
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="B119" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17938,7 +18019,7 @@
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="B120" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17951,7 +18032,7 @@
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="B121" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17964,7 +18045,7 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="B122" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17977,7 +18058,7 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="B123" s="26" t="str">
         <f t="shared" si="1"/>
@@ -17990,7 +18071,7 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="B124" s="26" t="str">
         <f t="shared" si="1"/>
@@ -18003,7 +18084,7 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="B125" s="26" t="str">
         <f t="shared" si="1"/>
@@ -18016,7 +18097,7 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="B126" s="26" t="str">
         <f t="shared" si="1"/>
@@ -18029,7 +18110,7 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="B127" s="26" t="str">
         <f t="shared" si="1"/>
@@ -18042,7 +18123,7 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="B128" s="26" t="str">
         <f t="shared" si="1"/>
@@ -18055,7 +18136,7 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="B129" s="26" t="str">
         <f t="shared" si="1"/>
@@ -18068,7 +18149,7 @@
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="B130" s="26" t="str">
         <f t="shared" si="1"/>
@@ -18081,7 +18162,7 @@
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="3" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="B131" s="26" t="str">
         <f t="shared" si="1"/>
@@ -18094,7 +18175,7 @@
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="B132" s="26" t="str">
         <f t="shared" si="1"/>
@@ -18142,25 +18223,25 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>8</v>
@@ -18171,109 +18252,109 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="B2" s="28" t="str">
         <f t="shared" ref="B2:B40" si="1">CONCATENATE(C2)</f>
         <v>Teutsche Gedichte</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="I2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="B3" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Die Krafft der Gottseligkeit</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="B4" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Archetypi homiliarum in quatuor evangelia dn. nostri Iesu Christi</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="10" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="B5" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Der Psalter dess Königlichen Propheten Dauids/ Jn deutsche reymen verstendiglich vnd deutlich gebracht/ mit vorgehender anzeigung der reymen weise/ auch eines jeden Psalmes Jnhalt</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="13"/>
@@ -18281,73 +18362,73 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="B6" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Hundert christliche Fäst-Predigen</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="12" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="B7" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Spiegel der Unermesslichen Gnad Gottes gegen den rewenden bussfertigen Sünderen/ Jn XLV. Predigen vber das XV. capitel Lucae/ vom verlohrnen Schaaf/ Pfenning/ vnd Sohn verfasset</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="12" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="B8" s="28" t="str">
         <f t="shared" si="1"/>
         <v>verteütschte Rueh- oder Fridens-uebung</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="27"/>
@@ -18357,98 +18438,98 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="B9" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Nähefelser-Fahrt: in zehen erbaulichen Jahrzeit-Predigen zu schuldigem Danck dem Höhesten für den im Jahr 1388 gemeinen Landleuthen dess lobl. Eydgnössischen Bundorths Glarus wider ihre Feind bey und umb Nähefels verliehenen Wundersieg </v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="10" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="B10" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Die vier Haubtpuncten der christlichen seligmachenden Religion: auf alle Sontag des gantzen Jahrs ordenlich abgetheilt, grundtlich nach der heiligen Schrifft erklärt und zur Erbawung gerichtet </v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="B11" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Architectura von Vestungen</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="8" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="B12" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Buech der Freunden Stammen</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="9"/>
@@ -18459,42 +18540,42 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="B13" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Christen-Spiegel, das ist, Bedenkliche Erinnerungen über die Beruoffspflichten aller Ständen </v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="12" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="B14" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Viergeticht</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="9"/>
@@ -18505,14 +18586,14 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="B15" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Regentenspiegel</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="9"/>
@@ -18523,18 +18604,18 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="B16" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Türckischer Jammerspiegel</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="D16" s="27"/>
       <c r="E16" s="3" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="F16" s="27"/>
       <c r="G16" s="9"/>
@@ -18543,292 +18624,292 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="B17" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Theatrum concionum sacr. topicum</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="12" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="B18" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Seelen-Angst Christi</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="8" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="B19" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Dichterische Versuchgabe</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="12" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="B20" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Kriegs-Büchlein</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="12" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="B21" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Außerleßne Psalmen Davids</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="10" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B22" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>Sterbensspiegel/ das ist sonnenklare Vorstellung menschlicher Nichtigkeit durch alle Staend und Geschlechter</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>1776</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>1772</v>
-      </c>
-      <c r="B22" s="28" t="str">
-        <f t="shared" si="1"/>
-        <v>Sterbensspiegel/ das ist sonnenklare Vorstellung menschlicher Nichtigkeit durch alle Staend und Geschlechter</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>1773</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>1774</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>1706</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>1363</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>1770</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="12" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="B23" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Warhaffte/ vnd in Gottes Wort wol gegründte Widerlegung Des newlich im Truck außgegangnen ohn-Catholischen Gesprächs von Religion oder Glaubens sachen/ geneñt der Augenspiegel</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="12" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="B24" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Augspiegels Wahrer Religion Erster Theil</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="H24" s="13"/>
       <c r="I24" s="12" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="B25" s="28" t="str">
         <f t="shared" si="1"/>
         <v>De kracht der Godsaligheyt</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="H25" s="13"/>
       <c r="I25" s="9"/>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="B26" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Christlicher Wandersmann</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="H26" s="13"/>
       <c r="I26" s="8" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="B27" s="28" t="str">
         <f t="shared" si="1"/>
         <v>"Bernerischer Apothecker-Tax"</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>647</v>
@@ -18838,40 +18919,40 @@
       <c r="G27" s="9"/>
       <c r="H27" s="13"/>
       <c r="I27" s="3" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="B28" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Wolriechende geistliche Violblumen für eingründige Seelen</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="12" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="B29" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18887,7 +18968,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="B30" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18903,7 +18984,7 @@
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="B31" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18919,7 +19000,7 @@
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="B32" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18935,7 +19016,7 @@
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="B33" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18951,7 +19032,7 @@
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="B34" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18967,7 +19048,7 @@
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="B35" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18983,7 +19064,7 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="B36" s="28" t="str">
         <f t="shared" si="1"/>
@@ -18999,7 +19080,7 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="B37" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19015,7 +19096,7 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="B38" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19031,7 +19112,7 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="B39" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19047,7 +19128,7 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="B40" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19111,19 +19192,19 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
@@ -19131,69 +19212,69 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="B2" s="28" t="str">
         <f t="shared" ref="B2:B34" si="1">CONCATENATE(C2)</f>
         <v>Rat Zürich</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="D2" s="27"/>
       <c r="E2" s="29" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="F2" s="9"/>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="B3" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Fruchtbringende Gesellschaft</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="B4" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Deutschgesinnte Genossenschaft (Lilien-Zunft)</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="B5" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Parthenicum</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="13"/>
@@ -19201,172 +19282,172 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="B6" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Carolinum Zürich</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="3" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="B7" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Sanhedrin</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="3" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="B8" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Bürgerbibliothek Zürich</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="E8" s="13"/>
       <c r="F8" s="3" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="B9" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Grossmünster Zürich</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="3" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="B10" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Fraumünster Zürich</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="3" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="B11" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Philipps-Universität Marburg</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="9"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="B12" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Kartäuser</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="D12" s="21"/>
       <c r="E12" s="13"/>
       <c r="F12" s="3" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="B13" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Collegium Alumnorum</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="D13" s="30">
         <v>1.15712505E9</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="3" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="B14" s="28" t="str">
         <f t="shared" si="1"/>
         <v>Schützengesellschaft der Stadt Zürich</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="E14" s="13"/>
       <c r="F14" s="9"/>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="B15" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19379,7 +19460,7 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="B16" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19392,7 +19473,7 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="B17" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19405,7 +19486,7 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="B18" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19418,7 +19499,7 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="B19" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19431,7 +19512,7 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="B20" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19444,7 +19525,7 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="B21" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19457,7 +19538,7 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="B22" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19470,7 +19551,7 @@
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="B23" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19483,7 +19564,7 @@
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="B24" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19496,7 +19577,7 @@
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="B25" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19509,7 +19590,7 @@
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="B26" s="28" t="str">
         <f t="shared" si="1"/>
@@ -19522,7 +19603,7 @@
     </row>
     <row r="27" ht="22.5" customHeight